--- a/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
@@ -204,7 +204,7 @@
     <col min="1" max="1" width="10.8" customWidth="1"/>
     <col min="2" max="2" width="54" customWidth="1"/>
     <col min="3" max="3" width="10.8" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="10.8" customWidth="1"/>
     <col min="5" max="5" width="12.15" customWidth="1"/>
     <col min="6" max="6" width="14.850000000000001" customWidth="1"/>
     <col min="7" max="7" width="12.15" customWidth="1"/>
@@ -280,22 +280,22 @@
         </is>
       </c>
       <c t="n" r="C3">
-        <v>82.5141</v>
+        <v>49.9359</v>
       </c>
       <c t="n" r="D3">
-        <v>658.6544</v>
+        <v>661.1949</v>
       </c>
       <c t="n" r="E3">
-        <v>684.9614</v>
+        <v>687.6372</v>
       </c>
       <c t="n" r="F3">
-        <v>653.3867</v>
+        <v>655.7870</v>
       </c>
       <c t="n" r="G3">
-        <v>606.0772</v>
+        <v>612.8734</v>
       </c>
       <c t="n" r="H3">
-        <v>1519.1498</v>
+        <v>1531.1610</v>
       </c>
     </row>
     <row r="4">
@@ -310,19 +310,19 @@
         </is>
       </c>
       <c t="n" r="C4">
-        <v>16.5914</v>
+        <v>16.4462</v>
       </c>
       <c t="n" r="D4">
-        <v>20.4979</v>
+        <v>20.4276</v>
       </c>
       <c t="n" r="E4">
-        <v>250.6679</v>
+        <v>249.7680</v>
       </c>
       <c t="n" r="F4">
-        <v>20.8144</v>
+        <v>20.9596</v>
       </c>
       <c t="n" r="G4">
-        <v>386.6122</v>
+        <v>371.1857</v>
       </c>
     </row>
     <row r="5">
@@ -337,19 +337,19 @@
         </is>
       </c>
       <c t="n" r="C5">
-        <v>0.9220</v>
+        <v>0.8849</v>
       </c>
       <c t="n" r="D5">
-        <v>3.2505</v>
+        <v>3.2580</v>
       </c>
       <c t="n" r="E5">
-        <v>27.6985</v>
+        <v>27.7106</v>
       </c>
       <c t="n" r="F5">
-        <v>3.2995</v>
+        <v>3.3252</v>
       </c>
       <c t="n" r="G5">
-        <v>365.6499</v>
+        <v>363.6558</v>
       </c>
     </row>
     <row r="6">
@@ -364,22 +364,22 @@
         </is>
       </c>
       <c t="n" r="C6">
-        <v>-0.8759</v>
+        <v>-0.4359</v>
       </c>
       <c t="n" r="D6">
-        <v>42.1614</v>
+        <v>41.7351</v>
       </c>
       <c t="n" r="E6">
-        <v>52.8663</v>
+        <v>52.7421</v>
       </c>
       <c t="n" r="F6">
-        <v>42.3918</v>
+        <v>42.3060</v>
       </c>
       <c t="n" r="G6">
-        <v>239.9238</v>
+        <v>239.8058</v>
       </c>
       <c t="n" r="H6">
-        <v>332.9446</v>
+        <v>332.7346</v>
       </c>
     </row>
     <row r="7">
@@ -394,22 +394,22 @@
         </is>
       </c>
       <c t="n" r="C7">
-        <v>-0.0188</v>
+        <v>-0.0191</v>
       </c>
       <c t="n" r="D7">
-        <v>-0.0532</v>
+        <v>-0.0510</v>
       </c>
       <c t="n" r="E7">
-        <v>192.4971</v>
+        <v>192.5052</v>
       </c>
       <c t="n" r="F7">
-        <v>-0.0557</v>
+        <v>-0.0575</v>
       </c>
       <c t="n" r="G7">
-        <v>191.4229</v>
+        <v>191.4246</v>
       </c>
       <c t="n" r="H7">
-        <v>166505.9194</v>
+        <v>166578.3293</v>
       </c>
     </row>
     <row r="8">
@@ -424,19 +424,19 @@
         </is>
       </c>
       <c t="n" r="C8">
-        <v>-0.0018</v>
+        <v>-0.0426</v>
       </c>
       <c t="n" r="D8">
-        <v>4.0237</v>
+        <v>3.9983</v>
       </c>
       <c t="n" r="E8">
-        <v>4.0016</v>
+        <v>3.9832</v>
       </c>
       <c t="n" r="F8">
-        <v>4.0314</v>
+        <v>4.0050</v>
       </c>
       <c t="n" r="G8">
-        <v>152.6240</v>
+        <v>152.6541</v>
       </c>
     </row>
     <row r="9">
@@ -451,19 +451,19 @@
         </is>
       </c>
       <c t="n" r="C9">
-        <v>0.4101</v>
+        <v>0.2508</v>
       </c>
       <c t="n" r="D9">
-        <v>0.7342</v>
+        <v>0.5845</v>
       </c>
       <c t="n" r="E9">
-        <v>140.6435</v>
+        <v>140.3441</v>
       </c>
       <c t="n" r="F9">
-        <v>1.2065</v>
+        <v>1.0586</v>
       </c>
       <c t="n" r="G9">
-        <v>143.2411</v>
+        <v>142.5827</v>
       </c>
     </row>
     <row r="10">
@@ -478,19 +478,19 @@
         </is>
       </c>
       <c t="n" r="C10">
-        <v>0.6130</v>
+        <v>1.1290</v>
       </c>
       <c t="n" r="D10">
-        <v>4.5258</v>
+        <v>5.1699</v>
       </c>
       <c t="n" r="E10">
-        <v>22.1777</v>
+        <v>23.8419</v>
       </c>
       <c t="n" r="F10">
-        <v>4.7907</v>
+        <v>5.5496</v>
       </c>
       <c t="n" r="G10">
-        <v>106.3581</v>
+        <v>108.6668</v>
       </c>
     </row>
     <row r="11">
@@ -505,22 +505,22 @@
         </is>
       </c>
       <c t="n" r="C11">
-        <v>65.7233</v>
+        <v>65.6671</v>
       </c>
       <c t="n" r="D11">
-        <v>68.2877</v>
+        <v>68.2342</v>
       </c>
       <c t="n" r="E11">
-        <v>69.7029</v>
+        <v>69.7102</v>
       </c>
       <c t="n" r="F11">
-        <v>55.0878</v>
+        <v>55.1024</v>
       </c>
       <c t="n" r="G11">
-        <v>88.3013</v>
+        <v>88.2986</v>
       </c>
       <c t="n" r="H11">
-        <v>114.8453</v>
+        <v>114.8671</v>
       </c>
     </row>
     <row r="12">
@@ -535,25 +535,25 @@
         </is>
       </c>
       <c t="n" r="C12">
-        <v>1.4119</v>
+        <v>1.4927</v>
       </c>
       <c t="n" r="D12">
-        <v>33.3271</v>
+        <v>33.4520</v>
       </c>
       <c t="n" r="E12">
-        <v>81.3572</v>
+        <v>76.4689</v>
       </c>
       <c t="n" r="F12">
-        <v>33.3418</v>
+        <v>33.4830</v>
       </c>
       <c t="n" r="G12">
-        <v>82.1362</v>
+        <v>82.3383</v>
       </c>
       <c t="n" r="H12">
-        <v>298.0536</v>
+        <v>298.4602</v>
       </c>
       <c t="n" r="I12">
-        <v>1675.4496</v>
+        <v>1676.7474</v>
       </c>
     </row>
     <row r="13">
@@ -568,25 +568,25 @@
         </is>
       </c>
       <c t="n" r="C13">
-        <v>1.0880</v>
+        <v>0.6043</v>
       </c>
       <c t="n" r="D13">
-        <v>2.0757</v>
+        <v>1.7998</v>
       </c>
       <c t="n" r="E13">
-        <v>39.8898</v>
+        <v>39.7712</v>
       </c>
       <c t="n" r="F13">
-        <v>2.0085</v>
+        <v>1.6346</v>
       </c>
       <c t="n" r="G13">
-        <v>63.1196</v>
+        <v>62.7995</v>
       </c>
       <c t="n" r="H13">
-        <v>330.6670</v>
+        <v>329.0871</v>
       </c>
       <c t="n" r="I13">
-        <v>1102.0288</v>
+        <v>1097.6227</v>
       </c>
     </row>
     <row r="14">
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c t="n" r="C14">
-        <v>-0.1917</v>
+        <v>-0.1946</v>
       </c>
       <c t="n" r="D14">
-        <v>-1.1526</v>
+        <v>-1.2518</v>
       </c>
       <c t="n" r="E14">
-        <v>20.0395</v>
+        <v>20.0059</v>
       </c>
       <c t="n" r="F14">
-        <v>-1.0240</v>
+        <v>-1.0347</v>
       </c>
       <c t="n" r="G14">
-        <v>62.0383</v>
+        <v>61.6136</v>
       </c>
       <c t="n" r="H14">
-        <v>700.1950</v>
+        <v>700.9257</v>
       </c>
     </row>
     <row r="15">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c t="n" r="C15">
-        <v>-0.1170</v>
+        <v>-0.1210</v>
       </c>
       <c t="n" r="D15">
-        <v>0.2754</v>
+        <v>0.2645</v>
       </c>
       <c t="n" r="E15">
-        <v>60.0204</v>
+        <v>60.0007</v>
       </c>
       <c t="n" r="F15">
-        <v>-4.4227</v>
+        <v>-4.4467</v>
       </c>
       <c t="n" r="G15">
-        <v>58.6158</v>
+        <v>58.5980</v>
       </c>
     </row>
     <row r="16">
@@ -658,19 +658,19 @@
         </is>
       </c>
       <c t="n" r="C16">
-        <v>3.5458</v>
+        <v>3.4211</v>
       </c>
       <c t="n" r="D16">
-        <v>10.0843</v>
+        <v>10.0683</v>
       </c>
       <c t="n" r="E16">
-        <v>27.6147</v>
+        <v>27.8146</v>
       </c>
       <c t="n" r="F16">
-        <v>10.1786</v>
+        <v>10.7209</v>
       </c>
       <c t="n" r="G16">
-        <v>58.4478</v>
+        <v>58.5365</v>
       </c>
     </row>
     <row r="17">
@@ -685,19 +685,19 @@
         </is>
       </c>
       <c t="n" r="C17">
-        <v>3.3727</v>
+        <v>3.1567</v>
       </c>
       <c t="n" r="D17">
-        <v>13.6034</v>
+        <v>13.4527</v>
       </c>
       <c t="n" r="E17">
-        <v>26.5626</v>
+        <v>26.6534</v>
       </c>
       <c t="n" r="F17">
-        <v>17.1099</v>
+        <v>17.5595</v>
       </c>
       <c t="n" r="G17">
-        <v>57.7262</v>
+        <v>57.5816</v>
       </c>
     </row>
     <row r="18">
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c t="n" r="C18">
-        <v>1.1743</v>
+        <v>0.7382</v>
       </c>
       <c t="n" r="D18">
-        <v>1.9566</v>
+        <v>1.9294</v>
       </c>
       <c t="n" r="E18">
-        <v>51.2814</v>
+        <v>51.3749</v>
       </c>
       <c t="n" r="F18">
-        <v>48.1454</v>
+        <v>48.1724</v>
       </c>
       <c t="n" r="G18">
-        <v>56.9541</v>
+        <v>57.0553</v>
       </c>
       <c t="n" r="H18">
-        <v>463.8334</v>
+        <v>463.8822</v>
       </c>
     </row>
     <row r="19">
@@ -742,19 +742,19 @@
         </is>
       </c>
       <c t="n" r="C19">
-        <v>3.6047</v>
+        <v>3.3717</v>
       </c>
       <c t="n" r="D19">
-        <v>10.0316</v>
+        <v>10.1037</v>
       </c>
       <c t="n" r="E19">
-        <v>22.1632</v>
+        <v>22.2075</v>
       </c>
       <c t="n" r="F19">
-        <v>10.8995</v>
+        <v>11.3425</v>
       </c>
       <c t="n" r="G19">
-        <v>55.4613</v>
+        <v>55.7589</v>
       </c>
     </row>
     <row r="20">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c t="n" r="C20">
-        <v>3.6044</v>
+        <v>3.3713</v>
       </c>
       <c t="n" r="D20">
-        <v>10.0305</v>
+        <v>10.1026</v>
       </c>
       <c t="n" r="E20">
-        <v>22.1607</v>
+        <v>22.2050</v>
       </c>
       <c t="n" r="F20">
-        <v>10.8984</v>
+        <v>11.3413</v>
       </c>
       <c t="n" r="G20">
-        <v>55.4534</v>
+        <v>55.7510</v>
       </c>
     </row>
     <row r="21">
@@ -796,106 +796,106 @@
         </is>
       </c>
       <c t="n" r="C21">
-        <v>0.2530</v>
+        <v>0.2314</v>
       </c>
       <c t="n" r="D21">
-        <v>0.7760</v>
+        <v>0.7925</v>
       </c>
       <c t="n" r="E21">
-        <v>54.7715</v>
+        <v>54.7421</v>
       </c>
       <c t="n" r="F21">
-        <v>0.8862</v>
+        <v>0.8745</v>
       </c>
       <c t="n" r="G21">
-        <v>55.1328</v>
+        <v>55.1414</v>
       </c>
       <c t="n" r="H21">
-        <v>410.2529</v>
+        <v>410.1936</v>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">RGF</t>
+          <t xml:space="preserve">BRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. TSL PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C22">
-        <v>-0.0911</v>
+        <v>5.6688</v>
       </c>
       <c t="n" r="D22">
-        <v>6.5038</v>
+        <v>23.4188</v>
       </c>
       <c t="n" r="E22">
-        <v>34.7086</v>
+        <v>27.8396</v>
       </c>
       <c t="n" r="F22">
-        <v>6.6833</v>
+        <v>29.0142</v>
       </c>
       <c t="n" r="G22">
-        <v>55.0111</v>
+        <v>55.0993</v>
       </c>
     </row>
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">OYK</t>
+          <t xml:space="preserve">RGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ÇEŞME GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. TSL PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C23">
-        <v>-0.1953</v>
+        <v>-0.1234</v>
       </c>
       <c t="n" r="D23">
-        <v>-0.2258</v>
+        <v>6.4031</v>
       </c>
       <c t="n" r="E23">
-        <v>55.3995</v>
+        <v>34.7071</v>
       </c>
       <c t="n" r="F23">
-        <v>-0.2265</v>
+        <v>6.7104</v>
       </c>
       <c t="n" r="G23">
-        <v>54.4195</v>
-      </c>
-      <c t="n" r="H23">
-        <v>172.5629</v>
+        <v>54.7889</v>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">BRE</t>
+          <t xml:space="preserve">OYK</t>
         </is>
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ÇEŞME GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C24">
-        <v>4.9608</v>
+        <v>-0.1976</v>
       </c>
       <c t="n" r="D24">
-        <v>28.0124</v>
+        <v>-0.2278</v>
       </c>
       <c t="n" r="E24">
-        <v>26.6155</v>
+        <v>55.3964</v>
       </c>
       <c t="n" r="F24">
-        <v>27.8430</v>
+        <v>-0.2279</v>
       </c>
       <c t="n" r="G24">
-        <v>54.3924</v>
+        <v>54.4182</v>
+      </c>
+      <c t="n" r="H24">
+        <v>172.5458</v>
       </c>
     </row>
     <row r="25">
@@ -910,19 +910,19 @@
         </is>
       </c>
       <c t="n" r="C25">
-        <v>1.0480</v>
+        <v>3.9215</v>
       </c>
       <c t="n" r="D25">
-        <v>7.8846</v>
+        <v>10.2996</v>
       </c>
       <c t="n" r="E25">
-        <v>20.4447</v>
+        <v>23.4381</v>
       </c>
       <c t="n" r="F25">
-        <v>11.2843</v>
+        <v>14.4072</v>
       </c>
       <c t="n" r="G25">
-        <v>50.2596</v>
+        <v>53.7421</v>
       </c>
     </row>
     <row r="26">
@@ -937,25 +937,25 @@
         </is>
       </c>
       <c t="n" r="C26">
-        <v>-1.5942</v>
+        <v>-0.3196</v>
       </c>
       <c t="n" r="D26">
-        <v>-1.4531</v>
+        <v>-1.4485</v>
       </c>
       <c t="n" r="E26">
-        <v>28.4838</v>
+        <v>28.4755</v>
       </c>
       <c t="n" r="F26">
-        <v>-1.6377</v>
+        <v>-1.6782</v>
       </c>
       <c t="n" r="G26">
-        <v>48.7730</v>
+        <v>49.0218</v>
       </c>
       <c t="n" r="H26">
-        <v>168.0746</v>
+        <v>168.1694</v>
       </c>
       <c t="n" r="I26">
-        <v>1144.4471</v>
+        <v>1143.9352</v>
       </c>
     </row>
     <row r="27">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c t="n" r="C27">
-        <v>5.5031</v>
+        <v>5.2464</v>
       </c>
       <c t="n" r="D27">
-        <v>12.5228</v>
+        <v>12.1702</v>
       </c>
       <c t="n" r="E27">
-        <v>21.9705</v>
+        <v>21.5104</v>
       </c>
       <c t="n" r="F27">
-        <v>13.0854</v>
+        <v>13.2347</v>
       </c>
       <c t="n" r="G27">
-        <v>48.4465</v>
+        <v>48.7624</v>
       </c>
     </row>
     <row r="28">
@@ -997,25 +997,25 @@
         </is>
       </c>
       <c t="n" r="C28">
-        <v>-0.5913</v>
+        <v>-0.3231</v>
       </c>
       <c t="n" r="D28">
-        <v>-0.4156</v>
+        <v>-0.4379</v>
       </c>
       <c t="n" r="E28">
-        <v>16.0621</v>
+        <v>16.0229</v>
       </c>
       <c t="n" r="F28">
-        <v>-0.5492</v>
+        <v>-0.5905</v>
       </c>
       <c t="n" r="G28">
-        <v>47.9761</v>
+        <v>48.0517</v>
       </c>
       <c t="n" r="H28">
-        <v>196.7851</v>
+        <v>196.7674</v>
       </c>
       <c t="n" r="I28">
-        <v>1323.4711</v>
+        <v>1322.8794</v>
       </c>
     </row>
     <row r="29">
@@ -1030,22 +1030,22 @@
         </is>
       </c>
       <c t="n" r="C29">
-        <v>0.3637</v>
+        <v>0.3521</v>
       </c>
       <c t="n" r="D29">
-        <v>6.3009</v>
+        <v>6.3392</v>
       </c>
       <c t="n" r="E29">
-        <v>43.8343</v>
+        <v>43.8700</v>
       </c>
       <c t="n" r="F29">
-        <v>5.8811</v>
+        <v>5.9540</v>
       </c>
       <c t="n" r="G29">
-        <v>45.2375</v>
+        <v>45.3101</v>
       </c>
       <c t="n" r="H29">
-        <v>461.4564</v>
+        <v>462.0709</v>
       </c>
     </row>
     <row r="30">
@@ -1060,19 +1060,19 @@
         </is>
       </c>
       <c t="n" r="C30">
-        <v>3.0483</v>
+        <v>2.8684</v>
       </c>
       <c t="n" r="D30">
-        <v>8.7259</v>
+        <v>8.6006</v>
       </c>
       <c t="n" r="E30">
-        <v>19.1755</v>
+        <v>19.2092</v>
       </c>
       <c t="n" r="F30">
-        <v>9.4938</v>
+        <v>9.8802</v>
       </c>
       <c t="n" r="G30">
-        <v>44.6320</v>
+        <v>44.1275</v>
       </c>
     </row>
     <row r="31">
@@ -1087,49 +1087,46 @@
         </is>
       </c>
       <c t="n" r="C31">
-        <v>-0.1359</v>
+        <v>-0.1825</v>
       </c>
       <c t="n" r="D31">
-        <v>1.4242</v>
+        <v>0.4411</v>
       </c>
       <c t="n" r="E31">
-        <v>31.0097</v>
+        <v>29.4093</v>
       </c>
       <c t="n" r="F31">
-        <v>1.4976</v>
+        <v>1.5365</v>
       </c>
       <c t="n" r="G31">
-        <v>44.0584</v>
+        <v>44.0946</v>
       </c>
     </row>
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">KGB</t>
+          <t xml:space="preserve">ZGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C32">
-        <v>0.1525</v>
+        <v>1.9259</v>
       </c>
       <c t="n" r="D32">
-        <v>0.5353</v>
+        <v>4.8246</v>
       </c>
       <c t="n" r="E32">
-        <v>38.6962</v>
+        <v>23.9574</v>
       </c>
       <c t="n" r="F32">
-        <v>0.7510</v>
+        <v>8.6174</v>
       </c>
       <c t="n" r="G32">
-        <v>41.7132</v>
-      </c>
-      <c t="n" r="H32">
-        <v>241.7701</v>
+        <v>42.2838</v>
       </c>
     </row>
     <row r="33">
@@ -1144,232 +1141,235 @@
         </is>
       </c>
       <c t="n" r="C33">
-        <v>-0.2499</v>
+        <v>-0.0189</v>
       </c>
       <c t="n" r="D33">
-        <v>0.3320</v>
+        <v>0.1572</v>
       </c>
       <c t="n" r="E33">
-        <v>26.8929</v>
+        <v>27.1041</v>
       </c>
       <c t="n" r="F33">
-        <v>0.3182</v>
+        <v>0.3329</v>
       </c>
       <c t="n" r="G33">
-        <v>41.6918</v>
+        <v>41.7864</v>
       </c>
     </row>
     <row r="34">
       <c t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">RG3</t>
+          <t xml:space="preserve">KGB</t>
         </is>
       </c>
       <c t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TRAKYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C34">
-        <v>-0.0848</v>
+        <v>0.1386</v>
       </c>
       <c t="n" r="D34">
-        <v>-0.3747</v>
+        <v>0.5258</v>
       </c>
       <c t="n" r="E34">
-        <v>42.2785</v>
+        <v>38.6575</v>
       </c>
       <c t="n" r="F34">
-        <v>-0.4816</v>
+        <v>0.7297</v>
       </c>
       <c t="n" r="G34">
-        <v>41.6788</v>
+        <v>41.7390</v>
       </c>
       <c t="n" r="H34">
-        <v>212.2022</v>
+        <v>241.7662</v>
       </c>
     </row>
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">KGG</t>
+          <t xml:space="preserve">RG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TRAKYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C35">
-        <v>0.1535</v>
+        <v>-0.0890</v>
       </c>
       <c t="n" r="D35">
-        <v>0.0178</v>
+        <v>-0.3856</v>
       </c>
       <c t="n" r="E35">
-        <v>41.1414</v>
+        <v>42.2618</v>
       </c>
       <c t="n" r="F35">
-        <v>0.3368</v>
+        <v>-0.4969</v>
       </c>
       <c t="n" r="G35">
-        <v>41.4418</v>
+        <v>41.6646</v>
       </c>
       <c t="n" r="H35">
-        <v>251.9206</v>
+        <v>212.8836</v>
       </c>
     </row>
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">MPG</t>
+          <t xml:space="preserve">KGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM (TL) FONU</t>
+          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C36">
-        <v>0.5458</v>
+        <v>0.1453</v>
       </c>
       <c t="n" r="D36">
-        <v>-0.4353</v>
+        <v>0.0139</v>
       </c>
       <c t="n" r="E36">
-        <v>28.9771</v>
+        <v>41.1440</v>
       </c>
       <c t="n" r="F36">
-        <v>1.4187</v>
+        <v>0.3037</v>
       </c>
       <c t="n" r="G36">
-        <v>40.8457</v>
+        <v>41.4705</v>
       </c>
       <c t="n" r="H36">
-        <v>172.2860</v>
-      </c>
-      <c t="n" r="I36">
-        <v>399.9897</v>
+        <v>251.8717</v>
       </c>
     </row>
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">ISZ</t>
+          <t xml:space="preserve">MPG</t>
         </is>
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM (TL) FONU</t>
         </is>
       </c>
       <c t="n" r="C37">
-        <v>0.5720</v>
+        <v>0.5334</v>
       </c>
       <c t="n" r="D37">
-        <v>1.7730</v>
+        <v>1.5264</v>
       </c>
       <c t="n" r="E37">
-        <v>16.3828</v>
+        <v>28.9773</v>
       </c>
       <c t="n" r="F37">
-        <v>1.9607</v>
+        <v>1.4664</v>
       </c>
       <c t="n" r="G37">
-        <v>40.3052</v>
+        <v>40.7948</v>
       </c>
       <c t="n" r="H37">
-        <v>295.3888</v>
+        <v>172.1344</v>
       </c>
       <c t="n" r="I37">
-        <v>916.5609</v>
+        <v>400.2252</v>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">IIY</t>
+          <t xml:space="preserve">ISZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ  GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C38">
-        <v>1.2229</v>
+        <v>0.4770</v>
       </c>
       <c t="n" r="D38">
-        <v>4.1430</v>
+        <v>1.7306</v>
       </c>
       <c t="n" r="E38">
-        <v>14.3794</v>
+        <v>16.3147</v>
       </c>
       <c t="n" r="F38">
-        <v>3.0802</v>
+        <v>1.9858</v>
       </c>
       <c t="n" r="G38">
-        <v>39.3961</v>
+        <v>40.2224</v>
       </c>
       <c t="n" r="H38">
-        <v>141.0008</v>
+        <v>295.3469</v>
       </c>
       <c t="n" r="I38">
-        <v>259.0503</v>
+        <v>916.1899</v>
       </c>
     </row>
     <row r="39">
       <c t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">RGO</t>
+          <t xml:space="preserve">IIY</t>
         </is>
       </c>
       <c t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. GÖKSU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ  GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C39">
-        <v>0.6144</v>
+        <v>1.2115</v>
       </c>
       <c t="n" r="D39">
-        <v>2.1444</v>
+        <v>4.1586</v>
       </c>
       <c t="n" r="E39">
-        <v>31.4113</v>
+        <v>14.3031</v>
       </c>
       <c t="n" r="F39">
-        <v>2.6405</v>
+        <v>3.1722</v>
       </c>
       <c t="n" r="G39">
-        <v>38.9187</v>
+        <v>39.4973</v>
+      </c>
+      <c t="n" r="H39">
+        <v>140.8770</v>
+      </c>
+      <c t="n" r="I39">
+        <v>259.3235</v>
       </c>
     </row>
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">ZGU</t>
+          <t xml:space="preserve">RGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. GÖKSU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C40">
-        <v>0.5672</v>
+        <v>0.6747</v>
       </c>
       <c t="n" r="D40">
-        <v>3.3242</v>
+        <v>2.0175</v>
       </c>
       <c t="n" r="E40">
-        <v>21.5463</v>
+        <v>31.1682</v>
       </c>
       <c t="n" r="F40">
-        <v>6.5964</v>
+        <v>2.6449</v>
       </c>
       <c t="n" r="G40">
-        <v>38.7655</v>
+        <v>38.7740</v>
       </c>
     </row>
     <row r="41">
@@ -1384,25 +1384,25 @@
         </is>
       </c>
       <c t="n" r="C41">
-        <v>-1.2804</v>
+        <v>-1.2939</v>
       </c>
       <c t="n" r="D41">
-        <v>-0.4393</v>
+        <v>-0.9271</v>
       </c>
       <c t="n" r="E41">
-        <v>23.8512</v>
+        <v>23.8465</v>
       </c>
       <c t="n" r="F41">
-        <v>-0.4773</v>
+        <v>-0.5077</v>
       </c>
       <c t="n" r="G41">
-        <v>38.3109</v>
+        <v>38.3819</v>
       </c>
       <c t="n" r="H41">
-        <v>326.8652</v>
+        <v>326.7809</v>
       </c>
       <c t="n" r="I41">
-        <v>714.4358</v>
+        <v>713.3477</v>
       </c>
     </row>
     <row r="42">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c t="n" r="C42">
-        <v>1.3851</v>
+        <v>1.4526</v>
       </c>
       <c t="n" r="D42">
-        <v>4.1513</v>
+        <v>4.1690</v>
       </c>
       <c t="n" r="E42">
-        <v>13.8807</v>
+        <v>13.8739</v>
       </c>
       <c t="n" r="F42">
-        <v>4.4065</v>
+        <v>4.6557</v>
       </c>
       <c t="n" r="G42">
-        <v>37.4066</v>
+        <v>37.3984</v>
       </c>
       <c t="n" r="H42">
-        <v>178.9201</v>
+        <v>179.3917</v>
       </c>
       <c t="n" r="I42">
-        <v>414.9218</v>
+        <v>415.2467</v>
       </c>
     </row>
     <row r="43">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c t="n" r="C43">
-        <v>-1.2523</v>
+        <v>-0.6746</v>
       </c>
       <c t="n" r="D43">
-        <v>3.4597</v>
+        <v>3.9166</v>
       </c>
       <c t="n" r="E43">
-        <v>32.7820</v>
+        <v>32.8264</v>
       </c>
       <c t="n" r="F43">
-        <v>11.6144</v>
+        <v>11.6476</v>
       </c>
       <c t="n" r="G43">
-        <v>37.1684</v>
+        <v>37.1655</v>
       </c>
       <c t="n" r="H43">
-        <v>829.7793</v>
+        <v>828.1794</v>
       </c>
     </row>
     <row r="44">
@@ -1480,262 +1480,256 @@
         </is>
       </c>
       <c t="n" r="C44">
-        <v>-0.0671</v>
+        <v>-0.0777</v>
       </c>
       <c t="n" r="D44">
-        <v>-0.4144</v>
+        <v>-0.4225</v>
       </c>
       <c t="n" r="E44">
-        <v>32.6827</v>
+        <v>32.6603</v>
       </c>
       <c t="n" r="F44">
-        <v>-0.4525</v>
+        <v>-0.4729</v>
       </c>
       <c t="n" r="G44">
-        <v>35.5647</v>
+        <v>35.5507</v>
       </c>
       <c t="n" r="H44">
-        <v>243.3909</v>
+        <v>243.3309</v>
       </c>
       <c t="n" r="I44">
-        <v>921.8272</v>
+        <v>921.6440</v>
       </c>
     </row>
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">NNP</t>
+          <t xml:space="preserve">DIG</t>
         </is>
       </c>
       <c t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AVANTAJ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C45">
-        <v>0.4460</v>
+        <v>2.3958</v>
       </c>
       <c t="n" r="D45">
-        <v>2.7282</v>
+        <v>6.7762</v>
       </c>
       <c t="n" r="E45">
-        <v>27.0163</v>
+        <v>15.3126</v>
       </c>
       <c t="n" r="F45">
-        <v>1.9984</v>
+        <v>7.8448</v>
       </c>
       <c t="n" r="G45">
-        <v>34.7237</v>
-      </c>
-      <c t="n" r="H45">
-        <v>573.9506</v>
+        <v>35.3824</v>
       </c>
     </row>
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">RGK</t>
+          <t xml:space="preserve">NNP</t>
         </is>
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AVANTAJ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C46">
-        <v>-0.0231</v>
+        <v>0.4003</v>
       </c>
       <c t="n" r="D46">
-        <v>-0.1090</v>
+        <v>1.7875</v>
       </c>
       <c t="n" r="E46">
-        <v>34.0472</v>
+        <v>26.8353</v>
       </c>
       <c t="n" r="F46">
-        <v>-0.1109</v>
+        <v>2.0651</v>
       </c>
       <c t="n" r="G46">
-        <v>34.5303</v>
+        <v>34.7918</v>
+      </c>
+      <c t="n" r="H46">
+        <v>574.4833</v>
       </c>
     </row>
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">FNI</t>
+          <t xml:space="preserve">RGK</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C47">
-        <v>0.5250</v>
+        <v>-0.0257</v>
       </c>
       <c t="n" r="D47">
-        <v>1.5243</v>
+        <v>-0.1105</v>
       </c>
       <c t="n" r="E47">
-        <v>28.5148</v>
+        <v>34.0455</v>
       </c>
       <c t="n" r="F47">
-        <v>1.5194</v>
+        <v>-0.1146</v>
       </c>
       <c t="n" r="G47">
-        <v>33.8604</v>
+        <v>34.5368</v>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">NG2</t>
+          <t xml:space="preserve">FNR</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C48">
-        <v>0.2664</v>
+        <v>3.0868</v>
       </c>
       <c t="n" r="D48">
-        <v>0.7622</v>
+        <v>3.4783</v>
       </c>
       <c t="n" r="E48">
-        <v>31.5140</v>
+        <v>14.8393</v>
       </c>
       <c t="n" r="F48">
-        <v>1.1172</v>
+        <v>5.5444</v>
       </c>
       <c t="n" r="G48">
-        <v>32.9995</v>
-      </c>
-      <c t="n" r="H48">
-        <v>318.8145</v>
+        <v>34.3918</v>
       </c>
     </row>
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">YG1</t>
+          <t xml:space="preserve">FNI</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LOTUS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C49">
-        <v>-0.0144</v>
+        <v>0.5217</v>
       </c>
       <c t="n" r="D49">
-        <v>-0.1175</v>
+        <v>1.5230</v>
       </c>
       <c t="n" r="E49">
-        <v>10.3498</v>
+        <v>28.5031</v>
       </c>
       <c t="n" r="F49">
-        <v>-0.1180</v>
+        <v>1.5079</v>
       </c>
       <c t="n" r="G49">
-        <v>32.3253</v>
-      </c>
-      <c t="n" r="H49">
-        <v>429.2684</v>
+        <v>33.8499</v>
       </c>
     </row>
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">UCG</t>
+          <t xml:space="preserve">NG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C50">
-        <v>0.5799</v>
+        <v>0.2614</v>
       </c>
       <c t="n" r="D50">
-        <v>-0.1529</v>
+        <v>0.7627</v>
       </c>
       <c t="n" r="E50">
-        <v>31.6562</v>
+        <v>31.5167</v>
       </c>
       <c t="n" r="F50">
-        <v>0.4734</v>
+        <v>1.1074</v>
       </c>
       <c t="n" r="G50">
-        <v>31.8131</v>
+        <v>33.0069</v>
       </c>
       <c t="n" r="H50">
-        <v>691.4660</v>
-      </c>
-      <c t="n" r="I50">
-        <v>1782.4255</v>
+        <v>317.8006</v>
       </c>
     </row>
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">AZ3</t>
+          <t xml:space="preserve">YG1</t>
         </is>
       </c>
       <c t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LOTUS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C51">
-        <v>-0.0485</v>
+        <v>0.4742</v>
       </c>
       <c t="n" r="D51">
-        <v>-0.2510</v>
+        <v>0.3355</v>
       </c>
       <c t="n" r="E51">
-        <v>32.7916</v>
+        <v>10.8474</v>
       </c>
       <c t="n" r="F51">
-        <v>-2.9932</v>
+        <v>0.3311</v>
       </c>
       <c t="n" r="G51">
-        <v>31.6412</v>
+        <v>32.5821</v>
       </c>
       <c t="n" r="H51">
-        <v>214.7908</v>
-      </c>
-      <c t="n" r="I51">
-        <v>679.5810</v>
+        <v>303.4796</v>
       </c>
     </row>
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">FT1</t>
+          <t xml:space="preserve">AZ3</t>
         </is>
       </c>
       <c t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C52">
-        <v>0.0991</v>
+        <v>-0.0083</v>
       </c>
       <c t="n" r="D52">
-        <v>0.1794</v>
+        <v>-0.2344</v>
       </c>
       <c t="n" r="E52">
-        <v>6.2082</v>
+        <v>32.8103</v>
       </c>
       <c t="n" r="F52">
-        <v>0.2067</v>
+        <v>-2.9934</v>
       </c>
       <c t="n" r="G52">
-        <v>31.5382</v>
+        <v>31.6646</v>
+      </c>
+      <c t="n" r="H52">
+        <v>214.8461</v>
+      </c>
+      <c t="n" r="I52">
+        <v>679.5801</v>
       </c>
     </row>
     <row r="53">
@@ -1750,253 +1744,253 @@
         </is>
       </c>
       <c t="n" r="C53">
-        <v>2.5639</v>
+        <v>2.4393</v>
       </c>
       <c t="n" r="D53">
-        <v>4.8928</v>
+        <v>4.8179</v>
       </c>
       <c t="n" r="E53">
-        <v>12.4182</v>
+        <v>12.4497</v>
       </c>
       <c t="n" r="F53">
-        <v>5.9939</v>
+        <v>6.2846</v>
       </c>
       <c t="n" r="G53">
-        <v>31.2963</v>
+        <v>31.4894</v>
       </c>
     </row>
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">GF1</t>
+          <t xml:space="preserve">FT1</t>
         </is>
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C54">
-        <v>-0.0080</v>
+        <v>0.0787</v>
       </c>
       <c t="n" r="D54">
-        <v>0.2599</v>
+        <v>0.1866</v>
       </c>
       <c t="n" r="E54">
-        <v>29.1930</v>
+        <v>5.8729</v>
       </c>
       <c t="n" r="F54">
-        <v>0.2690</v>
+        <v>0.2096</v>
       </c>
       <c t="n" r="G54">
-        <v>31.1969</v>
+        <v>31.3265</v>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">ITG</t>
+          <t xml:space="preserve">UCG</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. QUASAR İSTANBUL TİCARİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C55">
-        <v>0.3319</v>
+        <v>0.1641</v>
       </c>
       <c t="n" r="D55">
-        <v>1.0877</v>
+        <v>-0.5592</v>
       </c>
       <c t="n" r="E55">
-        <v>13.2805</v>
+        <v>31.1447</v>
       </c>
       <c t="n" r="F55">
-        <v>1.3312</v>
+        <v>0.0639</v>
       </c>
       <c t="n" r="G55">
-        <v>30.9802</v>
+        <v>31.2762</v>
       </c>
       <c t="n" r="H55">
-        <v>156.3436</v>
+        <v>685.0407</v>
       </c>
       <c t="n" r="I55">
-        <v>485.9817</v>
+        <v>1774.5406</v>
       </c>
     </row>
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">IRG</t>
+          <t xml:space="preserve">GF1</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C56">
-        <v>1.5356</v>
+        <v>-0.0208</v>
       </c>
       <c t="n" r="D56">
-        <v>3.6626</v>
+        <v>0.2541</v>
       </c>
       <c t="n" r="E56">
-        <v>12.6526</v>
+        <v>29.1911</v>
       </c>
       <c t="n" r="F56">
-        <v>3.5478</v>
+        <v>0.2589</v>
       </c>
       <c t="n" r="G56">
-        <v>30.3923</v>
+        <v>31.2107</v>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">NUY</t>
+          <t xml:space="preserve">TUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C57">
-        <v>1.2905</v>
+        <v>1.6260</v>
       </c>
       <c t="n" r="D57">
-        <v>3.6867</v>
+        <v>3.0139</v>
       </c>
       <c t="n" r="E57">
-        <v>21.3265</v>
+        <v>39.1982</v>
       </c>
       <c t="n" r="F57">
-        <v>4.4779</v>
+        <v>3.6239</v>
       </c>
       <c t="n" r="G57">
-        <v>30.1982</v>
+        <v>30.9880</v>
       </c>
     </row>
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">AZ1</t>
+          <t xml:space="preserve">ITG</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. QUASAR İSTANBUL TİCARİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C58">
-        <v>0.0538</v>
+        <v>0.3237</v>
       </c>
       <c t="n" r="D58">
-        <v>0.8427</v>
+        <v>1.0788</v>
       </c>
       <c t="n" r="E58">
-        <v>27.7741</v>
+        <v>12.9920</v>
       </c>
       <c t="n" r="F58">
-        <v>-5.9624</v>
+        <v>1.3296</v>
       </c>
       <c t="n" r="G58">
-        <v>30.0588</v>
+        <v>30.8967</v>
       </c>
       <c t="n" r="H58">
-        <v>172.0791</v>
+        <v>156.3085</v>
       </c>
       <c t="n" r="I58">
-        <v>832.2883</v>
+        <v>486.0769</v>
       </c>
     </row>
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">ROG</t>
+          <t xml:space="preserve">IRG</t>
         </is>
       </c>
       <c t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C59">
-        <v>0.2253</v>
+        <v>1.4696</v>
       </c>
       <c t="n" r="D59">
-        <v>0.7619</v>
+        <v>3.6972</v>
       </c>
       <c t="n" r="E59">
-        <v>27.8761</v>
+        <v>12.7576</v>
       </c>
       <c t="n" r="F59">
-        <v>1.0455</v>
+        <v>3.6799</v>
       </c>
       <c t="n" r="G59">
-        <v>29.6075</v>
+        <v>30.5078</v>
       </c>
     </row>
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">AG6</t>
+          <t xml:space="preserve">AZ1</t>
         </is>
       </c>
       <c t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C60">
-        <v>0.1368</v>
+        <v>0.0588</v>
       </c>
       <c t="n" r="D60">
-        <v>0.2885</v>
+        <v>0.8659</v>
       </c>
       <c t="n" r="E60">
-        <v>28.6861</v>
+        <v>27.7110</v>
       </c>
       <c t="n" r="F60">
-        <v>0.3119</v>
+        <v>-5.9663</v>
       </c>
       <c t="n" r="G60">
-        <v>29.1550</v>
+        <v>30.0445</v>
       </c>
       <c t="n" r="H60">
-        <v>233.1791</v>
+        <v>172.0671</v>
       </c>
       <c t="n" r="I60">
-        <v>353.5445</v>
+        <v>832.2498</v>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">IUL</t>
+          <t xml:space="preserve">ROG</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İNAN 3 ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C61">
-        <v>0.2413</v>
+        <v>0.2180</v>
       </c>
       <c t="n" r="D61">
-        <v>0.6323</v>
+        <v>0.7603</v>
       </c>
       <c t="n" r="E61">
-        <v>26.5341</v>
+        <v>27.8818</v>
       </c>
       <c t="n" r="F61">
-        <v>2.2655</v>
+        <v>1.0508</v>
       </c>
       <c t="n" r="G61">
-        <v>28.6762</v>
+        <v>29.6396</v>
       </c>
     </row>
     <row r="62">
@@ -2011,670 +2005,667 @@
         </is>
       </c>
       <c t="n" r="C62">
-        <v>-1.9466</v>
+        <v>-1.5663</v>
       </c>
       <c t="n" r="D62">
-        <v>4.8656</v>
+        <v>5.4630</v>
       </c>
       <c t="n" r="E62">
-        <v>16.5081</v>
+        <v>16.6228</v>
       </c>
       <c t="n" r="F62">
-        <v>5.3796</v>
+        <v>5.9295</v>
       </c>
       <c t="n" r="G62">
-        <v>28.2555</v>
+        <v>29.3010</v>
       </c>
     </row>
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">RMO</t>
+          <t xml:space="preserve">AG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. MONO PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C63">
-        <v>-0.0184</v>
+        <v>0.1124</v>
       </c>
       <c t="n" r="D63">
-        <v>-0.0569</v>
+        <v>0.2692</v>
       </c>
       <c t="n" r="E63">
-        <v>28.1666</v>
+        <v>28.6691</v>
       </c>
       <c t="n" r="F63">
-        <v>-0.0662</v>
+        <v>0.3171</v>
       </c>
       <c t="n" r="G63">
-        <v>28.0150</v>
+        <v>29.1424</v>
+      </c>
+      <c t="n" r="H63">
+        <v>232.2198</v>
+      </c>
+      <c t="n" r="I63">
+        <v>353.5679</v>
       </c>
     </row>
     <row r="64">
       <c t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">OFG</t>
+          <t xml:space="preserve">IUL</t>
         </is>
       </c>
       <c t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. FORM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İNAN 3 ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C64">
-        <v>1.1292</v>
+        <v>0.3264</v>
       </c>
       <c t="n" r="D64">
-        <v>-1.3799</v>
+        <v>0.7502</v>
       </c>
       <c t="n" r="E64">
-        <v>25.6533</v>
+        <v>26.6912</v>
       </c>
       <c t="n" r="F64">
-        <v>-20.3708</v>
+        <v>2.4519</v>
       </c>
       <c t="n" r="G64">
-        <v>27.2848</v>
-      </c>
-      <c t="n" r="H64">
-        <v>242.9349</v>
-      </c>
-      <c t="n" r="I64">
-        <v>1974.4874</v>
+        <v>28.8352</v>
       </c>
     </row>
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">FNR</t>
+          <t xml:space="preserve">RMO</t>
         </is>
       </c>
       <c t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. MONO PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C65">
-        <v>-4.7223</v>
+        <v>-0.0281</v>
       </c>
       <c t="n" r="D65">
-        <v>-4.1387</v>
+        <v>-0.0677</v>
       </c>
       <c t="n" r="E65">
-        <v>7.8503</v>
+        <v>28.1527</v>
       </c>
       <c t="n" r="F65">
-        <v>-1.6393</v>
+        <v>-0.0774</v>
       </c>
       <c t="n" r="G65">
-        <v>27.0885</v>
+        <v>28.0005</v>
       </c>
     </row>
     <row r="66">
       <c t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">UKA</t>
+          <t xml:space="preserve">OFG</t>
         </is>
       </c>
       <c t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. KONUT ALFA KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. FORM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C66">
-        <v>2.0216</v>
+        <v>0.5044</v>
       </c>
       <c t="n" r="D66">
-        <v>4.0475</v>
+        <v>-1.3513</v>
       </c>
       <c t="n" r="E66">
-        <v>16.0554</v>
+        <v>25.5619</v>
       </c>
       <c t="n" r="F66">
-        <v>4.1339</v>
+        <v>-20.3815</v>
       </c>
       <c t="n" r="G66">
-        <v>26.9919</v>
+        <v>27.2707</v>
       </c>
       <c t="n" r="H66">
-        <v>134.1363</v>
+        <v>242.8641</v>
       </c>
       <c t="n" r="I66">
-        <v>634083.2878</v>
+        <v>1974.2092</v>
       </c>
     </row>
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">RP7</t>
+          <t xml:space="preserve">UKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. TURESİF GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. KONUT ALFA KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C67">
-        <v>-4.2029</v>
+        <v>1.6962</v>
       </c>
       <c t="n" r="D67">
-        <v>-1.1375</v>
+        <v>4.0199</v>
       </c>
       <c t="n" r="E67">
-        <v>25.6175</v>
+        <v>16.0575</v>
       </c>
       <c t="n" r="F67">
-        <v>-0.2752</v>
+        <v>4.1887</v>
       </c>
       <c t="n" r="G67">
-        <v>26.1849</v>
+        <v>26.9692</v>
       </c>
       <c t="n" r="H67">
-        <v>136.7909</v>
+        <v>134.3915</v>
       </c>
       <c t="n" r="I67">
-        <v>981.2934</v>
+        <v>634416.9966</v>
       </c>
     </row>
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">UNC</t>
+          <t xml:space="preserve">RP7</t>
         </is>
       </c>
       <c t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. TURESİF GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C68">
-        <v>0.4208</v>
+        <v>-2.3005</v>
       </c>
       <c t="n" r="D68">
-        <v>1.7699</v>
+        <v>-1.1791</v>
       </c>
       <c t="n" r="E68">
-        <v>8.7572</v>
+        <v>25.5605</v>
       </c>
       <c t="n" r="F68">
-        <v>1.7512</v>
+        <v>-0.3230</v>
       </c>
       <c t="n" r="G68">
-        <v>25.9887</v>
+        <v>26.1229</v>
       </c>
       <c t="n" r="H68">
-        <v>77.3205</v>
+        <v>48.9862</v>
+      </c>
+      <c t="n" r="I68">
+        <v>980.7751</v>
       </c>
     </row>
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">IDG</t>
+          <t xml:space="preserve">UNC</t>
         </is>
       </c>
       <c t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C69">
-        <v>1.1701</v>
+        <v>0.4047</v>
       </c>
       <c t="n" r="D69">
-        <v>3.9528</v>
+        <v>1.7723</v>
       </c>
       <c t="n" r="E69">
-        <v>17.7343</v>
+        <v>8.7476</v>
       </c>
       <c t="n" r="F69">
-        <v>4.0928</v>
+        <v>1.7342</v>
       </c>
       <c t="n" r="G69">
-        <v>25.7798</v>
+        <v>25.8750</v>
       </c>
       <c t="n" r="H69">
-        <v>217.5706</v>
-      </c>
-      <c t="n" r="I69">
-        <v>495.7846</v>
+        <v>76.9309</v>
       </c>
     </row>
     <row r="70">
       <c t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">AG7</t>
+          <t xml:space="preserve">NUY</t>
         </is>
       </c>
       <c t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. METROPOL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C70">
-        <v>4.1435</v>
+        <v>-2.3565</v>
       </c>
       <c t="n" r="D70">
-        <v>4.8976</v>
+        <v>0.0025</v>
       </c>
       <c t="n" r="E70">
-        <v>14.5973</v>
+        <v>17.0701</v>
       </c>
       <c t="n" r="F70">
-        <v>0.8873</v>
+        <v>0.8748</v>
       </c>
       <c t="n" r="G70">
-        <v>25.3595</v>
-      </c>
-      <c t="n" r="H70">
-        <v>331.3025</v>
-      </c>
-      <c t="n" r="I70">
-        <v>835.5519</v>
+        <v>25.7410</v>
       </c>
     </row>
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">ZUG</t>
+          <t xml:space="preserve">IDG</t>
         </is>
       </c>
       <c t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C71">
-        <v>-0.0935</v>
+        <v>1.0766</v>
       </c>
       <c t="n" r="D71">
-        <v>-0.2448</v>
+        <v>3.9074</v>
       </c>
       <c t="n" r="E71">
-        <v>25.1329</v>
+        <v>17.7105</v>
       </c>
       <c t="n" r="F71">
-        <v>-0.0515</v>
+        <v>4.0086</v>
       </c>
       <c t="n" r="G71">
-        <v>25.1489</v>
+        <v>25.7313</v>
       </c>
       <c t="n" r="H71">
-        <v>199.1519</v>
+        <v>218.1188</v>
       </c>
       <c t="n" r="I71">
-        <v>399.9318</v>
+        <v>495.8422</v>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">NUZ</t>
+          <t xml:space="preserve">AG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. METROPOL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C72">
-        <v>1.3345</v>
+        <v>4.2053</v>
       </c>
       <c t="n" r="D72">
-        <v>3.3731</v>
+        <v>4.9620</v>
       </c>
       <c t="n" r="E72">
-        <v>-0.7276</v>
+        <v>14.5994</v>
       </c>
       <c t="n" r="F72">
-        <v>3.6413</v>
+        <v>0.9913</v>
       </c>
       <c t="n" r="G72">
-        <v>25.1237</v>
+        <v>25.4429</v>
       </c>
       <c t="n" r="H72">
-        <v>160.7357</v>
+        <v>331.4080</v>
+      </c>
+      <c t="n" r="I72">
+        <v>836.5159</v>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">RG6</t>
+          <t xml:space="preserve">NUZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İZMİR TARİHİ KEMERALTI GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C73">
-        <v>-2.7452</v>
+        <v>1.1035</v>
       </c>
       <c t="n" r="D73">
-        <v>-2.4726</v>
+        <v>3.4517</v>
       </c>
       <c t="n" r="E73">
-        <v>7.7237</v>
+        <v>-0.6342</v>
       </c>
       <c t="n" r="F73">
-        <v>-2.8387</v>
+        <v>3.7603</v>
       </c>
       <c t="n" r="G73">
-        <v>24.6090</v>
+        <v>25.1871</v>
+      </c>
+      <c t="n" r="H73">
+        <v>161.0645</v>
       </c>
     </row>
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">RP3</t>
+          <t xml:space="preserve">IVB</t>
         </is>
       </c>
       <c t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRUPA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ SANAYİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C74">
-        <v>-3.5374</v>
+        <v>0.3899</v>
       </c>
       <c t="n" r="D74">
-        <v>5.5130</v>
+        <v>-0.1184</v>
       </c>
       <c t="n" r="E74">
-        <v>24.7024</v>
+        <v>23.1966</v>
       </c>
       <c t="n" r="F74">
-        <v>-1.6064</v>
+        <v>-0.1202</v>
       </c>
       <c t="n" r="G74">
-        <v>23.9160</v>
-      </c>
-      <c t="n" r="H74">
-        <v>251.9927</v>
-      </c>
-      <c t="n" r="I74">
-        <v>789.8127</v>
+        <v>24.9192</v>
       </c>
     </row>
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">IVB</t>
+          <t xml:space="preserve">ZUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ SANAYİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C75">
-        <v>0.3949</v>
+        <v>-0.0487</v>
       </c>
       <c t="n" r="D75">
-        <v>-0.1111</v>
+        <v>-0.2291</v>
       </c>
       <c t="n" r="E75">
-        <v>23.1991</v>
+        <v>24.8243</v>
       </c>
       <c t="n" r="F75">
-        <v>-0.1110</v>
+        <v>-0.0125</v>
       </c>
       <c t="n" r="G75">
-        <v>23.6200</v>
+        <v>24.8240</v>
+      </c>
+      <c t="n" r="H75">
+        <v>199.1824</v>
+      </c>
+      <c t="n" r="I75">
+        <v>400.1217</v>
       </c>
     </row>
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">AG5</t>
+          <t xml:space="preserve">RG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DÜKKAN GAYRIMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İZMİR TARİHİ KEMERALTI GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C76">
-        <v>6.9731</v>
+        <v>-2.5394</v>
       </c>
       <c t="n" r="D76">
-        <v>8.3267</v>
+        <v>-2.3701</v>
       </c>
       <c t="n" r="E76">
-        <v>16.7311</v>
+        <v>7.9144</v>
       </c>
       <c t="n" r="F76">
-        <v>6.9303</v>
+        <v>-2.8293</v>
       </c>
       <c t="n" r="G76">
-        <v>23.3531</v>
+        <v>24.6737</v>
       </c>
       <c t="n" r="H76">
-        <v>244.5771</v>
-      </c>
-      <c t="n" r="I76">
-        <v>781.0277</v>
+        <v>148.5617</v>
       </c>
     </row>
     <row r="77">
       <c t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">RG2</t>
+          <t xml:space="preserve">AG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DÜKKAN GAYRIMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C77">
-        <v>-0.0436</v>
+        <v>6.6660</v>
       </c>
       <c t="n" r="D77">
-        <v>-0.6416</v>
+        <v>8.3395</v>
       </c>
       <c t="n" r="E77">
-        <v>23.0273</v>
+        <v>16.1036</v>
       </c>
       <c t="n" r="F77">
-        <v>-0.6335</v>
+        <v>6.8673</v>
       </c>
       <c t="n" r="G77">
-        <v>21.7714</v>
+        <v>22.9697</v>
       </c>
       <c t="n" r="H77">
-        <v>171.1560</v>
+        <v>244.2210</v>
+      </c>
+      <c t="n" r="I77">
+        <v>780.5087</v>
       </c>
     </row>
     <row r="78">
       <c t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">BGY</t>
+          <t xml:space="preserve">RG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C78">
-        <v>0.2568</v>
+        <v>-0.1117</v>
       </c>
       <c t="n" r="D78">
-        <v>0.9521</v>
+        <v>-0.6170</v>
       </c>
       <c t="n" r="E78">
-        <v>3.7165</v>
+        <v>23.0708</v>
       </c>
       <c t="n" r="F78">
-        <v>1.1555</v>
+        <v>-0.7313</v>
       </c>
       <c t="n" r="G78">
-        <v>21.3002</v>
+        <v>21.8492</v>
       </c>
       <c t="n" r="H78">
-        <v>263.2981</v>
-      </c>
-      <c t="n" r="I78">
-        <v>794.5143</v>
+        <v>170.8890</v>
       </c>
     </row>
     <row r="79">
       <c t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">ZG6</t>
+          <t xml:space="preserve">BGY</t>
         </is>
       </c>
       <c t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C79">
-        <v>-0.1024</v>
+        <v>0.2064</v>
       </c>
       <c t="n" r="D79">
-        <v>-0.3062</v>
+        <v>0.8273</v>
       </c>
       <c t="n" r="E79">
-        <v>22.1001</v>
+        <v>3.7303</v>
       </c>
       <c t="n" r="F79">
-        <v>-2.4427</v>
+        <v>1.2037</v>
       </c>
       <c t="n" r="G79">
-        <v>21.2916</v>
+        <v>21.3204</v>
       </c>
       <c t="n" r="H79">
-        <v>48.1336</v>
+        <v>263.6715</v>
+      </c>
+      <c t="n" r="I79">
+        <v>794.3975</v>
       </c>
     </row>
     <row r="80">
       <c t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">RP9</t>
+          <t xml:space="preserve">ZG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NEVA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C80">
-        <v>0.7353</v>
+        <v>-0.1061</v>
       </c>
       <c t="n" r="D80">
-        <v>1.1415</v>
+        <v>-0.3160</v>
       </c>
       <c t="n" r="E80">
-        <v>17.6206</v>
+        <v>22.0880</v>
       </c>
       <c t="n" r="F80">
-        <v>1.2173</v>
+        <v>-2.4662</v>
       </c>
       <c t="n" r="G80">
-        <v>21.0916</v>
+        <v>21.2828</v>
       </c>
       <c t="n" r="H80">
-        <v>203.2423</v>
-      </c>
-      <c t="n" r="I80">
-        <v>1195.4561</v>
+        <v>47.9592</v>
       </c>
     </row>
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">OGM</t>
+          <t xml:space="preserve">GGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C81">
-        <v>0.2711</v>
+        <v>0.6648</v>
       </c>
       <c t="n" r="D81">
-        <v>1.0205</v>
+        <v>1.4266</v>
       </c>
       <c t="n" r="E81">
-        <v>5.6743</v>
+        <v>12.0244</v>
       </c>
       <c t="n" r="F81">
-        <v>1.1072</v>
+        <v>1.5204</v>
       </c>
       <c t="n" r="G81">
-        <v>20.9135</v>
-      </c>
-      <c t="n" r="H81">
-        <v>221.1986</v>
-      </c>
-      <c t="n" r="I81">
-        <v>989.5022</v>
+        <v>21.2383</v>
       </c>
     </row>
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">GGF</t>
+          <t xml:space="preserve">OGM</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C82">
-        <v>0.0465</v>
+        <v>0.2741</v>
       </c>
       <c t="n" r="D82">
-        <v>0.8543</v>
+        <v>1.0226</v>
       </c>
       <c t="n" r="E82">
-        <v>11.5922</v>
+        <v>5.6474</v>
       </c>
       <c t="n" r="F82">
-        <v>0.9956</v>
+        <v>1.1127</v>
       </c>
       <c t="n" r="G82">
-        <v>20.7354</v>
+        <v>20.9072</v>
+      </c>
+      <c t="n" r="H82">
+        <v>220.9849</v>
+      </c>
+      <c t="n" r="I82">
+        <v>989.5397</v>
       </c>
     </row>
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">AZ6</t>
+          <t xml:space="preserve">RP9</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NEVA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C83">
-        <v>-0.6040</v>
+        <v>0.7650</v>
       </c>
       <c t="n" r="D83">
-        <v>1.0538</v>
+        <v>1.0326</v>
       </c>
       <c t="n" r="E83">
-        <v>15.6728</v>
+        <v>17.5358</v>
       </c>
       <c t="n" r="F83">
-        <v>-2.8803</v>
+        <v>1.2386</v>
       </c>
       <c t="n" r="G83">
-        <v>20.4996</v>
+        <v>20.8610</v>
       </c>
       <c t="n" r="H83">
-        <v>150.2243</v>
+        <v>203.2982</v>
       </c>
       <c t="n" r="I83">
-        <v>419.6801</v>
+        <v>1195.3621</v>
       </c>
     </row>
     <row r="84">
@@ -2689,484 +2680,490 @@
         </is>
       </c>
       <c t="n" r="C84">
-        <v>-1.6249</v>
+        <v>-1.6319</v>
       </c>
       <c t="n" r="D84">
-        <v>0.0303</v>
+        <v>0.0326</v>
       </c>
       <c t="n" r="E84">
-        <v>16.6056</v>
+        <v>16.6012</v>
       </c>
       <c t="n" r="F84">
-        <v>0.4935</v>
+        <v>0.4919</v>
       </c>
       <c t="n" r="G84">
-        <v>20.2479</v>
+        <v>20.2335</v>
       </c>
       <c t="n" r="H84">
-        <v>367.5280</v>
+        <v>367.9244</v>
       </c>
     </row>
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">OG2</t>
+          <t xml:space="preserve">RP3</t>
         </is>
       </c>
       <c t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.UFUK KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRUPA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C85">
-        <v>0.1105</v>
+        <v>-5.7235</v>
       </c>
       <c t="n" r="D85">
-        <v>0.4327</v>
+        <v>2.2528</v>
       </c>
       <c t="n" r="E85">
-        <v>15.4572</v>
+        <v>20.8053</v>
       </c>
       <c t="n" r="F85">
-        <v>0.4361</v>
+        <v>-4.6694</v>
       </c>
       <c t="n" r="G85">
-        <v>19.4169</v>
+        <v>19.8974</v>
       </c>
       <c t="n" r="H85">
-        <v>116.3348</v>
+        <v>242.3643</v>
       </c>
       <c t="n" r="I85">
-        <v>1160.1933</v>
+        <v>755.6181</v>
       </c>
     </row>
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">MGA</t>
+          <t xml:space="preserve">AZ6</t>
         </is>
       </c>
       <c t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C86">
-        <v>0.4211</v>
+        <v>-0.5200</v>
       </c>
       <c t="n" r="D86">
-        <v>0.7414</v>
+        <v>1.2875</v>
       </c>
       <c t="n" r="E86">
-        <v>14.8760</v>
+        <v>15.4218</v>
       </c>
       <c t="n" r="F86">
-        <v>-1.1311</v>
+        <v>-2.8758</v>
       </c>
       <c t="n" r="G86">
-        <v>19.3127</v>
+        <v>19.8359</v>
       </c>
       <c t="n" r="H86">
-        <v>151.3996</v>
+        <v>150.3234</v>
+      </c>
+      <c t="n" r="I86">
+        <v>419.7042</v>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">PGB</t>
+          <t xml:space="preserve">OG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.UFUK KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C87">
-        <v>-0.2265</v>
+        <v>0.1025</v>
       </c>
       <c t="n" r="D87">
-        <v>0.2575</v>
+        <v>0.4314</v>
       </c>
       <c t="n" r="E87">
-        <v>19.1462</v>
+        <v>15.4518</v>
       </c>
       <c t="n" r="F87">
-        <v>-0.0450</v>
+        <v>0.4182</v>
       </c>
       <c t="n" r="G87">
-        <v>18.8384</v>
+        <v>19.4088</v>
+      </c>
+      <c t="n" r="H87">
+        <v>116.2959</v>
+      </c>
+      <c t="n" r="I87">
+        <v>1160.0881</v>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">RP2</t>
+          <t xml:space="preserve">MGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C88">
-        <v>0.1357</v>
+        <v>0.2855</v>
       </c>
       <c t="n" r="D88">
-        <v>1.4124</v>
+        <v>1.0217</v>
       </c>
       <c t="n" r="E88">
-        <v>16.2756</v>
+        <v>11.2876</v>
       </c>
       <c t="n" r="F88">
-        <v>1.6983</v>
+        <v>-1.0245</v>
       </c>
       <c t="n" r="G88">
-        <v>18.0550</v>
+        <v>19.4061</v>
       </c>
       <c t="n" r="H88">
-        <v>142.2439</v>
-      </c>
-      <c t="n" r="I88">
-        <v>446.3208</v>
+        <v>151.4504</v>
       </c>
     </row>
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">YD4</t>
+          <t xml:space="preserve">PGB</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C89">
-        <v>-0.5217</v>
+        <v>-0.2413</v>
       </c>
       <c t="n" r="D89">
-        <v>-0.4769</v>
+        <v>0.2548</v>
       </c>
       <c t="n" r="E89">
-        <v>11.1646</v>
+        <v>19.1438</v>
       </c>
       <c t="n" r="F89">
-        <v>-0.5280</v>
+        <v>-0.0442</v>
       </c>
       <c t="n" r="G89">
-        <v>17.9849</v>
-      </c>
-      <c t="n" r="H89">
-        <v>246.7988</v>
-      </c>
-      <c t="n" r="I89">
-        <v>1012.5069</v>
+        <v>18.8357</v>
       </c>
     </row>
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">NUF</t>
+          <t xml:space="preserve">RP2</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. D VİZYON GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C90">
-        <v>-0.1292</v>
+        <v>1.9273</v>
       </c>
       <c t="n" r="D90">
-        <v>-0.3913</v>
+        <v>2.2265</v>
       </c>
       <c t="n" r="E90">
-        <v>26.9060</v>
+        <v>16.9769</v>
       </c>
       <c t="n" r="F90">
-        <v>-0.4160</v>
+        <v>2.5195</v>
       </c>
       <c t="n" r="G90">
-        <v>17.7542</v>
+        <v>18.6191</v>
       </c>
       <c t="n" r="H90">
-        <v>776.3132</v>
+        <v>144.1613</v>
+      </c>
+      <c t="n" r="I90">
+        <v>450.7499</v>
       </c>
     </row>
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">NMC</t>
+          <t xml:space="preserve">YD4</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. M CHARM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C91">
-        <v>-1.5225</v>
+        <v>-0.6046</v>
       </c>
       <c t="n" r="D91">
-        <v>-1.0481</v>
+        <v>-0.5453</v>
       </c>
       <c t="n" r="E91">
-        <v>25.6729</v>
+        <v>11.1792</v>
       </c>
       <c t="n" r="F91">
-        <v>-0.8520</v>
+        <v>-0.5762</v>
       </c>
       <c t="n" r="G91">
-        <v>17.7114</v>
+        <v>17.9934</v>
       </c>
       <c t="n" r="H91">
-        <v>215.9524</v>
+        <v>245.6093</v>
+      </c>
+      <c t="n" r="I91">
+        <v>1005.4946</v>
       </c>
     </row>
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">YD3</t>
+          <t xml:space="preserve">NMC</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. M CHARM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C92">
-        <v>-1.2639</v>
+        <v>-1.5452</v>
       </c>
       <c t="n" r="D92">
-        <v>-1.9653</v>
+        <v>-1.0605</v>
       </c>
       <c t="n" r="E92">
-        <v>11.9173</v>
+        <v>25.6662</v>
       </c>
       <c t="n" r="F92">
-        <v>-2.0581</v>
+        <v>-0.8589</v>
       </c>
       <c t="n" r="G92">
-        <v>17.2451</v>
+        <v>17.8069</v>
       </c>
       <c t="n" r="H92">
-        <v>148.9502</v>
-      </c>
-      <c t="n" r="I92">
-        <v>676.7604</v>
+        <v>215.9493</v>
       </c>
     </row>
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">ABZ</t>
+          <t xml:space="preserve">NUF</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. D VİZYON GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C93">
-        <v>-0.2505</v>
+        <v>-0.1338</v>
       </c>
       <c t="n" r="D93">
-        <v>-0.2524</v>
+        <v>-0.3925</v>
       </c>
       <c t="n" r="E93">
-        <v>5.3816</v>
+        <v>26.9058</v>
       </c>
       <c t="n" r="F93">
-        <v>-0.5033</v>
+        <v>-0.4383</v>
       </c>
       <c t="n" r="G93">
-        <v>16.9189</v>
+        <v>17.7086</v>
+      </c>
+      <c t="n" r="H93">
+        <v>775.9078</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">OYZ</t>
+          <t xml:space="preserve">YD3</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş.BEREKET KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C94">
-        <v>0.1127</v>
+        <v>-0.7094</v>
       </c>
       <c t="n" r="D94">
-        <v>0.9029</v>
+        <v>-2.1168</v>
       </c>
       <c t="n" r="E94">
-        <v>6.5423</v>
+        <v>11.7872</v>
       </c>
       <c t="n" r="F94">
-        <v>-0.7101</v>
+        <v>-2.2580</v>
       </c>
       <c t="n" r="G94">
-        <v>16.7436</v>
+        <v>17.0749</v>
       </c>
       <c t="n" r="H94">
-        <v>320.7594</v>
+        <v>148.4104</v>
       </c>
       <c t="n" r="I94">
-        <v>1600.6724</v>
+        <v>674.8979</v>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">PKA</t>
+          <t xml:space="preserve">ABZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş V METROWAY KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C95">
-        <v>-0.0100</v>
+        <v>-0.2509</v>
       </c>
       <c t="n" r="D95">
-        <v>-0.0441</v>
+        <v>-0.2529</v>
       </c>
       <c t="n" r="E95">
-        <v>16.1271</v>
+        <v>5.3811</v>
       </c>
       <c t="n" r="F95">
-        <v>-0.0436</v>
+        <v>-0.5037</v>
       </c>
       <c t="n" r="G95">
-        <v>16.0202</v>
-      </c>
-      <c t="n" r="H95">
-        <v>580.2128</v>
+        <v>16.9182</v>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">OGI</t>
+          <t xml:space="preserve">OYZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş.BEREKET KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C96">
-        <v>2.8647</v>
+        <v>-0.2185</v>
       </c>
       <c t="n" r="D96">
-        <v>-0.3881</v>
+        <v>0.8960</v>
       </c>
       <c t="n" r="E96">
-        <v>2.1811</v>
+        <v>6.1853</v>
       </c>
       <c t="n" r="F96">
-        <v>-0.0877</v>
+        <v>-0.7018</v>
       </c>
       <c t="n" r="G96">
-        <v>15.7026</v>
+        <v>16.7488</v>
       </c>
       <c t="n" r="H96">
-        <v>0.3178</v>
+        <v>320.7136</v>
       </c>
       <c t="n" r="I96">
-        <v>57.8867</v>
+        <v>1600.8154</v>
       </c>
     </row>
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">NUE</t>
+          <t xml:space="preserve">PKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. EGÇ KONUT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş V METROWAY KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C97">
-        <v>-0.3135</v>
+        <v>-0.0069</v>
       </c>
       <c t="n" r="D97">
-        <v>2.5881</v>
+        <v>-0.0444</v>
       </c>
       <c t="n" r="E97">
-        <v>15.9965</v>
+        <v>16.1270</v>
       </c>
       <c t="n" r="F97">
-        <v>3.2315</v>
+        <v>-0.0439</v>
       </c>
       <c t="n" r="G97">
-        <v>15.3038</v>
+        <v>16.0200</v>
       </c>
       <c t="n" r="H97">
-        <v>186.8713</v>
+        <v>580.1905</v>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">NUS</t>
+          <t xml:space="preserve">OGI</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ALTINCI KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C98">
-        <v>-0.2227</v>
+        <v>0.0602</v>
       </c>
       <c t="n" r="D98">
-        <v>-0.6077</v>
+        <v>-0.4735</v>
       </c>
       <c t="n" r="E98">
-        <v>16.6317</v>
+        <v>2.2381</v>
       </c>
       <c t="n" r="F98">
-        <v>-0.6499</v>
+        <v>-0.0124</v>
       </c>
       <c t="n" r="G98">
-        <v>14.9321</v>
+        <v>15.5615</v>
+      </c>
+      <c t="n" r="H98">
+        <v>0.4150</v>
+      </c>
+      <c t="n" r="I98">
+        <v>58.0061</v>
       </c>
     </row>
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">AZ2</t>
+          <t xml:space="preserve">NUE</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. EGÇ KONUT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C99">
-        <v>-0.1885</v>
+        <v>-0.2949</v>
       </c>
       <c t="n" r="D99">
-        <v>1.4573</v>
+        <v>2.6822</v>
       </c>
       <c t="n" r="E99">
-        <v>4.9625</v>
+        <v>15.4390</v>
       </c>
       <c t="n" r="F99">
-        <v>1.1856</v>
+        <v>3.3166</v>
       </c>
       <c t="n" r="G99">
-        <v>14.4278</v>
+        <v>15.3945</v>
       </c>
       <c t="n" r="H99">
-        <v>266.1527</v>
-      </c>
-      <c t="n" r="I99">
-        <v>1199.9661</v>
+        <v>187.1221</v>
       </c>
     </row>
     <row r="100">
@@ -3181,55 +3178,52 @@
         </is>
       </c>
       <c t="n" r="C100">
-        <v>-0.1544</v>
+        <v>5.0319</v>
       </c>
       <c t="n" r="D100">
-        <v>1.1630</v>
+        <v>3.3496</v>
       </c>
       <c t="n" r="E100">
-        <v>13.2361</v>
+        <v>15.0972</v>
       </c>
       <c t="n" r="F100">
-        <v>2.9726</v>
+        <v>5.3496</v>
       </c>
       <c t="n" r="G100">
-        <v>13.9983</v>
+        <v>15.3335</v>
       </c>
       <c t="n" r="H100">
-        <v>90.1486</v>
+        <v>94.4843</v>
       </c>
       <c t="n" r="I100">
-        <v>433.7825</v>
+        <v>445.9275</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">NG4</t>
+          <t xml:space="preserve">NUS</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ALTINCI KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C101">
-        <v>0.2371</v>
+        <v>-0.2293</v>
       </c>
       <c t="n" r="D101">
-        <v>-0.0180</v>
+        <v>-0.6073</v>
       </c>
       <c t="n" r="E101">
-        <v>13.7648</v>
+        <v>16.6327</v>
       </c>
       <c t="n" r="F101">
-        <v>-0.9271</v>
+        <v>-0.6818</v>
       </c>
       <c t="n" r="G101">
-        <v>13.7601</v>
-      </c>
-      <c t="n" r="H101">
-        <v>225.5432</v>
+        <v>14.9723</v>
       </c>
     </row>
     <row r="102">
@@ -3244,25 +3238,25 @@
         </is>
       </c>
       <c t="n" r="C102">
-        <v>0.4910</v>
+        <v>0.4825</v>
       </c>
       <c t="n" r="D102">
-        <v>1.3513</v>
+        <v>1.1942</v>
       </c>
       <c t="n" r="E102">
-        <v>13.5377</v>
+        <v>13.4033</v>
       </c>
       <c t="n" r="F102">
-        <v>1.8186</v>
+        <v>1.8129</v>
       </c>
       <c t="n" r="G102">
-        <v>13.7571</v>
+        <v>14.7067</v>
       </c>
       <c t="n" r="H102">
-        <v>261.8549</v>
+        <v>262.7884</v>
       </c>
       <c t="n" r="I102">
-        <v>477.7011</v>
+        <v>470.3759</v>
       </c>
     </row>
     <row r="103">
@@ -3277,436 +3271,439 @@
         </is>
       </c>
       <c t="n" r="C103">
-        <v>-7.6619</v>
+        <v>3.7099</v>
       </c>
       <c t="n" r="D103">
-        <v>-6.5975</v>
+        <v>-5.1391</v>
       </c>
       <c t="n" r="E103">
-        <v>9.3547</v>
+        <v>10.6247</v>
       </c>
       <c t="n" r="F103">
-        <v>-5.6193</v>
+        <v>-4.2088</v>
       </c>
       <c t="n" r="G103">
-        <v>13.5200</v>
+        <v>14.4643</v>
       </c>
       <c t="n" r="H103">
-        <v>107.0596</v>
+        <v>110.1683</v>
       </c>
       <c t="n" r="I103">
-        <v>358.0688</v>
+        <v>364.6851</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">RKG</t>
+          <t xml:space="preserve">AZ2</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. NEF GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C104">
-        <v>-0.0698</v>
+        <v>-0.1521</v>
       </c>
       <c t="n" r="D104">
-        <v>-0.3376</v>
+        <v>1.5688</v>
       </c>
       <c t="n" r="E104">
-        <v>13.5306</v>
+        <v>4.8576</v>
       </c>
       <c t="n" r="F104">
-        <v>-0.5205</v>
+        <v>1.1718</v>
       </c>
       <c t="n" r="G104">
-        <v>13.0543</v>
+        <v>14.4009</v>
       </c>
       <c t="n" r="H104">
-        <v>493.8211</v>
+        <v>266.1105</v>
+      </c>
+      <c t="n" r="I104">
+        <v>1199.7892</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">ZVE</t>
+          <t xml:space="preserve">NG4</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C105">
-        <v>0.0009</v>
+        <v>0.2357</v>
       </c>
       <c t="n" r="D105">
-        <v>0.1644</v>
+        <v>-0.0210</v>
       </c>
       <c t="n" r="E105">
-        <v>-1.0185</v>
+        <v>13.7615</v>
       </c>
       <c t="n" r="F105">
-        <v>0.1632</v>
+        <v>-0.9338</v>
       </c>
       <c t="n" r="G105">
-        <v>13.0048</v>
+        <v>13.7480</v>
       </c>
       <c t="n" r="H105">
-        <v>124.6408</v>
+        <v>225.2176</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">NH2</t>
+          <t xml:space="preserve">RKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş CORNERSTONE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. NEF GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C106">
-        <v>0.7791</v>
+        <v>-0.0550</v>
       </c>
       <c t="n" r="D106">
-        <v>2.1231</v>
+        <v>-0.3434</v>
       </c>
       <c t="n" r="E106">
-        <v>11.7332</v>
+        <v>13.5135</v>
       </c>
       <c t="n" r="F106">
-        <v>3.1170</v>
+        <v>-0.5403</v>
       </c>
       <c t="n" r="G106">
-        <v>12.8490</v>
+        <v>13.0384</v>
+      </c>
+      <c t="n" r="H106">
+        <v>493.5934</v>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">ILN</t>
+          <t xml:space="preserve">ZVE</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. FOLKART BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C107">
-        <v>2.5788</v>
+        <v>0.0043</v>
       </c>
       <c t="n" r="D107">
-        <v>2.4443</v>
+        <v>0.1769</v>
       </c>
       <c t="n" r="E107">
-        <v>4.1073</v>
+        <v>-1.0062</v>
       </c>
       <c t="n" r="F107">
-        <v>2.4534</v>
+        <v>0.1706</v>
       </c>
       <c t="n" r="G107">
-        <v>12.8257</v>
+        <v>13.0177</v>
+      </c>
+      <c t="n" r="H107">
+        <v>124.6210</v>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">YG7</t>
+          <t xml:space="preserve">ILN</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. FOLKART BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C108">
-        <v>0.0926</v>
+        <v>0.0462</v>
       </c>
       <c t="n" r="D108">
-        <v>0.8793</v>
+        <v>2.4458</v>
       </c>
       <c t="n" r="E108">
-        <v>9.9650</v>
+        <v>3.8011</v>
       </c>
       <c t="n" r="F108">
-        <v>0.8318</v>
+        <v>2.4462</v>
       </c>
       <c t="n" r="G108">
-        <v>12.6802</v>
-      </c>
-      <c t="n" r="H108">
-        <v>-18.6744</v>
+        <v>12.7818</v>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">OYE</t>
+          <t xml:space="preserve">YG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALTINCI KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C109">
-        <v>0.0987</v>
+        <v>0.0732</v>
       </c>
       <c t="n" r="D109">
-        <v>1.0450</v>
+        <v>0.7943</v>
       </c>
       <c t="n" r="E109">
-        <v>9.4323</v>
+        <v>9.8780</v>
       </c>
       <c t="n" r="F109">
-        <v>-1.1357</v>
+        <v>0.7901</v>
       </c>
       <c t="n" r="G109">
-        <v>12.4284</v>
+        <v>12.5106</v>
       </c>
       <c t="n" r="H109">
-        <v>201.5412</v>
-      </c>
-      <c t="n" r="I109">
-        <v>576.3229</v>
+        <v>-18.6150</v>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">NUA</t>
+          <t xml:space="preserve">NH2</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. FORTİS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş CORNERSTONE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C110">
-        <v>-0.0083</v>
+        <v>0.6743</v>
       </c>
       <c t="n" r="D110">
-        <v>0.3522</v>
+        <v>1.8849</v>
       </c>
       <c t="n" r="E110">
-        <v>27.4676</v>
+        <v>11.7996</v>
       </c>
       <c t="n" r="F110">
-        <v>0.2724</v>
+        <v>3.1599</v>
       </c>
       <c t="n" r="G110">
-        <v>11.2345</v>
-      </c>
-      <c t="n" r="H110">
-        <v>134.3527</v>
+        <v>12.5028</v>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">NYD</t>
+          <t xml:space="preserve">OYE</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİLGE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALTINCI KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C111">
-        <v>-3.7995</v>
+        <v>-0.3379</v>
       </c>
       <c t="n" r="D111">
-        <v>-5.1096</v>
+        <v>1.0338</v>
       </c>
       <c t="n" r="E111">
-        <v>33.3272</v>
+        <v>8.9209</v>
       </c>
       <c t="n" r="F111">
-        <v>-5.0944</v>
+        <v>-1.1373</v>
       </c>
       <c t="n" r="G111">
-        <v>10.5628</v>
+        <v>12.4328</v>
       </c>
       <c t="n" r="H111">
-        <v>403.6714</v>
+        <v>201.5077</v>
+      </c>
+      <c t="n" r="I111">
+        <v>576.3121</v>
       </c>
     </row>
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">HDU</t>
+          <t xml:space="preserve">NUA</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. FORTİS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C112">
-        <v>-0.0660</v>
+        <v>-0.0140</v>
       </c>
       <c t="n" r="D112">
-        <v>-0.1947</v>
+        <v>0.3562</v>
       </c>
       <c t="n" r="E112">
-        <v>10.9010</v>
+        <v>27.6009</v>
       </c>
       <c t="n" r="F112">
-        <v>-0.2043</v>
+        <v>0.2745</v>
       </c>
       <c t="n" r="G112">
-        <v>10.4244</v>
+        <v>11.3253</v>
+      </c>
+      <c t="n" r="H112">
+        <v>134.3598</v>
       </c>
     </row>
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">IN9</t>
+          <t xml:space="preserve">NYD</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. NEFES EGE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİLGE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C113">
-        <v>-0.3207</v>
+        <v>-1.5302</v>
       </c>
       <c t="n" r="D113">
-        <v>-1.2080</v>
+        <v>-5.0781</v>
       </c>
       <c t="n" r="E113">
-        <v>12.3964</v>
+        <v>33.4195</v>
       </c>
       <c t="n" r="F113">
-        <v>-1.2561</v>
+        <v>-5.1400</v>
       </c>
       <c t="n" r="G113">
-        <v>10.3158</v>
+        <v>10.5655</v>
+      </c>
+      <c t="n" r="H113">
+        <v>402.0754</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">RBG</t>
+          <t xml:space="preserve">HDU</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C114">
-        <v>0.4408</v>
+        <v>-0.0690</v>
       </c>
       <c t="n" r="D114">
-        <v>0.6844</v>
+        <v>-0.1962</v>
       </c>
       <c t="n" r="E114">
-        <v>6.5395</v>
+        <v>10.8998</v>
       </c>
       <c t="n" r="F114">
-        <v>1.1927</v>
+        <v>-0.2146</v>
       </c>
       <c t="n" r="G114">
-        <v>9.6620</v>
+        <v>10.4173</v>
       </c>
     </row>
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">ERP</t>
+          <t xml:space="preserve">IN9</t>
         </is>
       </c>
       <c t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">QİNVEST PORTFÖY YÖNETİMİ A.Ş. RE PİE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. NEFES EGE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C115">
-        <v>0.1278</v>
+        <v>-0.3348</v>
       </c>
       <c t="n" r="D115">
-        <v>0.5587</v>
+        <v>-1.2184</v>
       </c>
       <c t="n" r="E115">
-        <v>2.3927</v>
+        <v>12.3985</v>
       </c>
       <c t="n" r="F115">
-        <v>0.9441</v>
+        <v>-1.3088</v>
       </c>
       <c t="n" r="G115">
-        <v>9.3748</v>
-      </c>
-      <c t="n" r="H115">
-        <v>129.1889</v>
-      </c>
-      <c t="n" r="I115">
-        <v>422.9562</v>
+        <v>10.3221</v>
       </c>
     </row>
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">NAG</t>
+          <t xml:space="preserve">RBG</t>
         </is>
       </c>
       <c t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AKS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C116">
-        <v>-0.0920</v>
+        <v>0.4296</v>
       </c>
       <c t="n" r="D116">
-        <v>-0.2311</v>
+        <v>0.6828</v>
       </c>
       <c t="n" r="E116">
-        <v>9.0221</v>
+        <v>6.5572</v>
       </c>
       <c t="n" r="F116">
-        <v>-0.1584</v>
+        <v>1.2074</v>
       </c>
       <c t="n" r="G116">
-        <v>8.9465</v>
-      </c>
-      <c t="n" r="H116">
-        <v>253.3377</v>
+        <v>9.4645</v>
       </c>
     </row>
     <row r="117">
       <c t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">RG9</t>
+          <t xml:space="preserve">ERP</t>
         </is>
       </c>
       <c t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN AVM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">QİNVEST PORTFÖY YÖNETİMİ A.Ş. RE PİE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C117">
-        <v>0.2331</v>
+        <v>0.1099</v>
       </c>
       <c t="n" r="D117">
-        <v>1.6837</v>
+        <v>0.3645</v>
       </c>
       <c t="n" r="E117">
-        <v>8.3547</v>
+        <v>2.3710</v>
       </c>
       <c t="n" r="F117">
-        <v>1.6776</v>
+        <v>0.9318</v>
       </c>
       <c t="n" r="G117">
-        <v>8.9362</v>
+        <v>9.3656</v>
       </c>
       <c t="n" r="H117">
-        <v>124.3114</v>
+        <v>129.0135</v>
+      </c>
+      <c t="n" r="I117">
+        <v>422.4041</v>
       </c>
     </row>
     <row r="118">
@@ -3721,804 +3718,816 @@
         </is>
       </c>
       <c t="n" r="C118">
-        <v>-0.1116</v>
+        <v>-0.1121</v>
       </c>
       <c t="n" r="D118">
-        <v>-0.1809</v>
+        <v>-0.1771</v>
       </c>
       <c t="n" r="E118">
-        <v>9.2320</v>
+        <v>9.2265</v>
       </c>
       <c t="n" r="F118">
-        <v>-0.1464</v>
+        <v>-0.1488</v>
       </c>
       <c t="n" r="G118">
-        <v>8.8996</v>
+        <v>8.9764</v>
       </c>
     </row>
     <row r="119">
       <c t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">NRY</t>
+          <t xml:space="preserve">RG9</t>
         </is>
       </c>
       <c t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ROYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN AVM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C119">
-        <v>-0.5496</v>
+        <v>0.2303</v>
       </c>
       <c t="n" r="D119">
-        <v>-0.5425</v>
+        <v>1.7098</v>
       </c>
       <c t="n" r="E119">
-        <v>9.0241</v>
+        <v>8.3433</v>
       </c>
       <c t="n" r="F119">
-        <v>-0.2763</v>
+        <v>1.6618</v>
       </c>
       <c t="n" r="G119">
-        <v>8.5011</v>
+        <v>8.9294</v>
+      </c>
+      <c t="n" r="H119">
+        <v>124.1082</v>
       </c>
     </row>
     <row r="120">
       <c t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">NH4</t>
+          <t xml:space="preserve">NAG</t>
         </is>
       </c>
       <c t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AKS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C120">
-        <v>0.0237</v>
+        <v>-0.0954</v>
       </c>
       <c t="n" r="D120">
-        <v>0.2648</v>
+        <v>-0.2331</v>
       </c>
       <c t="n" r="E120">
-        <v>3.8119</v>
+        <v>9.0309</v>
       </c>
       <c t="n" r="F120">
-        <v>0.4010</v>
+        <v>-0.1689</v>
       </c>
       <c t="n" r="G120">
-        <v>8.4903</v>
+        <v>8.8604</v>
       </c>
       <c t="n" r="H120">
-        <v>244.8812</v>
+        <v>253.3288</v>
       </c>
     </row>
     <row r="121">
       <c t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">NUI</t>
+          <t xml:space="preserve">NRY</t>
         </is>
       </c>
       <c t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. TİCARİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ROYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C121">
-        <v>0.3941</v>
+        <v>-0.3636</v>
       </c>
       <c t="n" r="D121">
-        <v>-1.8803</v>
+        <v>-0.5505</v>
       </c>
       <c t="n" r="E121">
-        <v>7.5681</v>
+        <v>9.0161</v>
       </c>
       <c t="n" r="F121">
-        <v>-1.3898</v>
+        <v>-0.3037</v>
       </c>
       <c t="n" r="G121">
-        <v>8.4590</v>
+        <v>8.5567</v>
       </c>
     </row>
     <row r="122">
       <c t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">OCH</t>
+          <t xml:space="preserve">NH4</t>
         </is>
       </c>
       <c t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. OC HEDEF GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C122">
-        <v>0.2790</v>
+        <v>0.0235</v>
       </c>
       <c t="n" r="D122">
-        <v>0.3879</v>
+        <v>0.2777</v>
       </c>
       <c t="n" r="E122">
-        <v>6.8720</v>
+        <v>3.8265</v>
       </c>
       <c t="n" r="F122">
-        <v>0.4753</v>
+        <v>0.3998</v>
       </c>
       <c t="n" r="G122">
-        <v>7.5310</v>
+        <v>8.4699</v>
       </c>
       <c t="n" r="H122">
-        <v>113.1634</v>
+        <v>244.4645</v>
       </c>
     </row>
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">NG5</t>
+          <t xml:space="preserve">NUI</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. TİCARİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C123">
-        <v>0.0011</v>
+        <v>0.3909</v>
       </c>
       <c t="n" r="D123">
-        <v>-0.2361</v>
+        <v>-1.8893</v>
       </c>
       <c t="n" r="E123">
-        <v>12.1373</v>
+        <v>7.5602</v>
       </c>
       <c t="n" r="F123">
-        <v>-0.9517</v>
+        <v>-1.4094</v>
       </c>
       <c t="n" r="G123">
-        <v>6.7952</v>
-      </c>
-      <c t="n" r="H123">
-        <v>214.9688</v>
+        <v>8.4690</v>
       </c>
     </row>
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">RTM</t>
+          <t xml:space="preserve">NG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. TM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C124">
-        <v>-0.3691</v>
+        <v>-0.3486</v>
       </c>
       <c t="n" r="D124">
-        <v>-0.4025</v>
+        <v>-0.2303</v>
       </c>
       <c t="n" r="E124">
-        <v>7.2279</v>
+        <v>12.1215</v>
       </c>
       <c t="n" r="F124">
-        <v>-0.3780</v>
+        <v>-0.9651</v>
       </c>
       <c t="n" r="G124">
-        <v>6.5286</v>
+        <v>7.6286</v>
       </c>
       <c t="n" r="H124">
-        <v>233.4850</v>
+        <v>214.2922</v>
       </c>
     </row>
     <row r="125">
       <c t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">RG5</t>
+          <t xml:space="preserve">OCH</t>
         </is>
       </c>
       <c t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DİCLE PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. OC HEDEF GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C125">
-        <v>-0.0493</v>
+        <v>0.2904</v>
       </c>
       <c t="n" r="D125">
-        <v>-0.1434</v>
+        <v>0.4010</v>
       </c>
       <c t="n" r="E125">
-        <v>6.6234</v>
+        <v>6.9016</v>
       </c>
       <c t="n" r="F125">
-        <v>-0.1544</v>
+        <v>0.4837</v>
       </c>
       <c t="n" r="G125">
-        <v>6.3534</v>
+        <v>7.5612</v>
       </c>
       <c t="n" r="H125">
-        <v>305.8385</v>
+        <v>113.1706</v>
       </c>
     </row>
     <row r="126">
       <c t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">NUT</t>
+          <t xml:space="preserve">RTM</t>
         </is>
       </c>
       <c t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. NUROL TOWER GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. TM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C126">
-        <v>0.1456</v>
+        <v>-0.3717</v>
       </c>
       <c t="n" r="D126">
-        <v>0.9946</v>
+        <v>-0.4051</v>
       </c>
       <c t="n" r="E126">
-        <v>13.6372</v>
+        <v>7.2250</v>
       </c>
       <c t="n" r="F126">
-        <v>1.2369</v>
+        <v>-0.3807</v>
       </c>
       <c t="n" r="G126">
-        <v>5.7457</v>
+        <v>6.5282</v>
       </c>
       <c t="n" r="H126">
-        <v>195.2843</v>
+        <v>233.4347</v>
       </c>
     </row>
     <row r="127">
       <c t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">GJS</t>
+          <t xml:space="preserve">RG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. SAĞLAM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DİCLE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C127">
-        <v>0.2714</v>
+        <v>-0.0510</v>
       </c>
       <c t="n" r="D127">
-        <v>-0.2444</v>
+        <v>-0.1525</v>
       </c>
       <c t="n" r="E127">
-        <v>5.4134</v>
+        <v>6.6126</v>
       </c>
       <c t="n" r="F127">
-        <v>-0.3021</v>
+        <v>-0.1694</v>
       </c>
       <c t="n" r="G127">
-        <v>5.4980</v>
+        <v>6.3436</v>
       </c>
       <c t="n" r="H127">
-        <v>157.8977</v>
+        <v>305.7934</v>
       </c>
     </row>
     <row r="128">
       <c t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">ERS</t>
+          <t xml:space="preserve">NUT</t>
         </is>
       </c>
       <c t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. NUROL TOWER GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C128">
-        <v>0.3089</v>
+        <v>0.1424</v>
       </c>
       <c t="n" r="D128">
-        <v>1.1139</v>
+        <v>1.0157</v>
       </c>
       <c t="n" r="E128">
-        <v>11.4811</v>
+        <v>13.5526</v>
       </c>
       <c t="n" r="F128">
-        <v>1.0941</v>
+        <v>1.2558</v>
       </c>
       <c t="n" r="G128">
-        <v>5.2015</v>
+        <v>5.8338</v>
       </c>
       <c t="n" r="H128">
-        <v>154.4946</v>
+        <v>195.3364</v>
       </c>
     </row>
     <row r="129">
       <c t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">NUL</t>
+          <t xml:space="preserve">GJS</t>
         </is>
       </c>
       <c t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İGC GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. SAĞLAM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C129">
-        <v>-8.3434</v>
+        <v>0.1251</v>
       </c>
       <c t="n" r="D129">
-        <v>-10.4107</v>
+        <v>-0.3317</v>
       </c>
       <c t="n" r="E129">
-        <v>0.4179</v>
+        <v>5.3215</v>
       </c>
       <c t="n" r="F129">
-        <v>-10.4860</v>
+        <v>-0.4073</v>
       </c>
       <c t="n" r="G129">
-        <v>4.8605</v>
+        <v>5.3926</v>
+      </c>
+      <c t="n" r="H129">
+        <v>157.6383</v>
       </c>
     </row>
     <row r="130">
       <c t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">NH5</t>
+          <t xml:space="preserve">NUP</t>
         </is>
       </c>
       <c t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C130">
-        <v>1.2037</v>
+        <v>-0.0701</v>
       </c>
       <c t="n" r="D130">
-        <v>3.6950</v>
+        <v>-0.1713</v>
       </c>
       <c t="n" r="E130">
-        <v>9.1196</v>
+        <v>8.3338</v>
       </c>
       <c t="n" r="F130">
-        <v>4.0404</v>
+        <v>2.1439</v>
       </c>
       <c t="n" r="G130">
-        <v>4.5489</v>
-      </c>
-      <c t="n" r="H130">
-        <v>89.1891</v>
+        <v>5.3143</v>
       </c>
     </row>
     <row r="131">
       <c t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">HP1</t>
+          <t xml:space="preserve">ERS</t>
         </is>
       </c>
       <c t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C131">
-        <v>-0.2206</v>
+        <v>0.3079</v>
       </c>
       <c t="n" r="D131">
-        <v>-0.6724</v>
+        <v>1.1169</v>
       </c>
       <c t="n" r="E131">
-        <v>5.9064</v>
+        <v>11.4924</v>
       </c>
       <c t="n" r="F131">
-        <v>-0.7147</v>
+        <v>1.0972</v>
       </c>
       <c t="n" r="G131">
-        <v>4.4908</v>
+        <v>5.2348</v>
       </c>
       <c t="n" r="H131">
-        <v>115.1683</v>
+        <v>153.4307</v>
       </c>
     </row>
     <row r="132">
       <c t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">OO1</t>
+          <t xml:space="preserve">NUL</t>
         </is>
       </c>
       <c t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İGC GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C132">
-        <v>-0.5897</v>
+        <v>0.1507</v>
       </c>
       <c t="n" r="D132">
-        <v>-2.3185</v>
+        <v>-10.4679</v>
       </c>
       <c t="n" r="E132">
-        <v>-6.3541</v>
+        <v>0.3820</v>
       </c>
       <c t="n" r="F132">
-        <v>-2.4063</v>
+        <v>-10.4847</v>
       </c>
       <c t="n" r="G132">
-        <v>4.1289</v>
+        <v>4.8082</v>
       </c>
     </row>
     <row r="133">
       <c t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">NUP</t>
+          <t xml:space="preserve">NH5</t>
         </is>
       </c>
       <c t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C133">
-        <v>-0.0571</v>
+        <v>1.0336</v>
       </c>
       <c t="n" r="D133">
-        <v>-0.1638</v>
+        <v>3.5962</v>
       </c>
       <c t="n" r="E133">
-        <v>8.3427</v>
+        <v>9.3201</v>
       </c>
       <c t="n" r="F133">
-        <v>2.1552</v>
+        <v>4.1781</v>
       </c>
       <c t="n" r="G133">
-        <v>4.0097</v>
+        <v>4.7506</v>
+      </c>
+      <c t="n" r="H133">
+        <v>89.4453</v>
       </c>
     </row>
     <row r="134">
       <c t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">ORX</t>
+          <t xml:space="preserve">HP1</t>
         </is>
       </c>
       <c t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C134">
-        <v>-0.2530</v>
+        <v>-0.2275</v>
       </c>
       <c t="n" r="D134">
-        <v>-0.7341</v>
+        <v>-0.6733</v>
       </c>
       <c t="n" r="E134">
-        <v>0.7489</v>
+        <v>5.9073</v>
       </c>
       <c t="n" r="F134">
-        <v>-0.6514</v>
+        <v>-0.7508</v>
       </c>
       <c t="n" r="G134">
-        <v>3.7574</v>
+        <v>4.4939</v>
       </c>
       <c t="n" r="H134">
-        <v>89.5066</v>
-      </c>
-      <c t="n" r="I134">
-        <v>58.3640</v>
+        <v>114.4717</v>
       </c>
     </row>
     <row r="135">
       <c t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">RG7</t>
+          <t xml:space="preserve">ORX</t>
         </is>
       </c>
       <c t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş DOWNTOWN OFİS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C135">
-        <v>-0.2911</v>
+        <v>-0.0176</v>
       </c>
       <c t="n" r="D135">
-        <v>-0.7858</v>
+        <v>-0.7082</v>
       </c>
       <c t="n" r="E135">
-        <v>0.7015</v>
+        <v>0.8814</v>
       </c>
       <c t="n" r="F135">
-        <v>-0.8955</v>
+        <v>-0.6076</v>
       </c>
       <c t="n" r="G135">
-        <v>3.5075</v>
+        <v>4.0407</v>
+      </c>
+      <c t="n" r="H135">
+        <v>89.3869</v>
+      </c>
+      <c t="n" r="I135">
+        <v>58.4339</v>
       </c>
     </row>
     <row r="136">
       <c t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">NUK</t>
+          <t xml:space="preserve">OO1</t>
         </is>
       </c>
       <c t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C136">
-        <v>-0.1010</v>
+        <v>-0.6283</v>
       </c>
       <c t="n" r="D136">
-        <v>-0.2812</v>
+        <v>-2.3163</v>
       </c>
       <c t="n" r="E136">
-        <v>9.4891</v>
+        <v>-14.8881</v>
       </c>
       <c t="n" r="F136">
-        <v>-0.3279</v>
+        <v>-2.5156</v>
       </c>
       <c t="n" r="G136">
-        <v>3.1495</v>
-      </c>
-      <c t="n" r="H136">
-        <v>122.8977</v>
+        <v>4.0337</v>
       </c>
     </row>
     <row r="137">
       <c t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">PG2</t>
+          <t xml:space="preserve">NFE</t>
         </is>
       </c>
       <c t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C137">
-        <v>-0.1075</v>
+        <v>-0.6890</v>
       </c>
       <c t="n" r="D137">
-        <v>-0.3561</v>
+        <v>-1.5183</v>
       </c>
       <c t="n" r="E137">
-        <v>16.5243</v>
+        <v>101.3633</v>
       </c>
       <c t="n" r="F137">
-        <v>-0.5210</v>
+        <v>-2.1050</v>
       </c>
       <c t="n" r="G137">
-        <v>3.0600</v>
+        <v>3.7283</v>
       </c>
     </row>
     <row r="138">
       <c t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">NG6</t>
+          <t xml:space="preserve">RG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş DOWNTOWN OFİS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C138">
-        <v>1.0654</v>
+        <v>-0.2590</v>
       </c>
       <c t="n" r="D138">
-        <v>-1.5829</v>
+        <v>-0.6511</v>
       </c>
       <c t="n" r="E138">
-        <v>4.9466</v>
+        <v>0.6635</v>
       </c>
       <c t="n" r="F138">
-        <v>-0.8601</v>
+        <v>-0.9619</v>
       </c>
       <c t="n" r="G138">
-        <v>2.9850</v>
+        <v>3.4765</v>
       </c>
       <c t="n" r="H138">
-        <v>266.2473</v>
+        <v>170.6642</v>
       </c>
     </row>
     <row r="139">
       <c t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">RBU</t>
+          <t xml:space="preserve">NUK</t>
         </is>
       </c>
       <c t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C139">
-        <v>0.6532</v>
+        <v>-0.0975</v>
       </c>
       <c t="n" r="D139">
-        <v>-1.9067</v>
+        <v>-0.2765</v>
       </c>
       <c t="n" r="E139">
-        <v>1.8909</v>
+        <v>9.4907</v>
       </c>
       <c t="n" r="F139">
-        <v>-1.2133</v>
+        <v>-0.3389</v>
       </c>
       <c t="n" r="G139">
-        <v>2.5031</v>
+        <v>3.1544</v>
+      </c>
+      <c t="n" r="H139">
+        <v>122.1688</v>
       </c>
     </row>
     <row r="140">
       <c t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">NUC</t>
+          <t xml:space="preserve">PG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. CHARM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C140">
-        <v>-0.1193</v>
+        <v>-0.1146</v>
       </c>
       <c t="n" r="D140">
-        <v>-0.3704</v>
+        <v>-0.3518</v>
       </c>
       <c t="n" r="E140">
-        <v>7.8640</v>
+        <v>16.5296</v>
       </c>
       <c t="n" r="F140">
-        <v>-0.3699</v>
+        <v>-0.5153</v>
       </c>
       <c t="n" r="G140">
-        <v>2.2570</v>
-      </c>
-      <c t="n" r="H140">
-        <v>130.9893</v>
+        <v>3.0664</v>
       </c>
     </row>
     <row r="141">
       <c t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">NFE</t>
+          <t xml:space="preserve">NG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C141">
-        <v>-0.6835</v>
+        <v>1.0796</v>
       </c>
       <c t="n" r="D141">
-        <v>-1.9255</v>
+        <v>-1.5761</v>
       </c>
       <c t="n" r="E141">
-        <v>93.1245</v>
+        <v>4.9874</v>
       </c>
       <c t="n" r="F141">
-        <v>-2.0741</v>
+        <v>-0.7863</v>
       </c>
       <c t="n" r="G141">
-        <v>1.3828</v>
+        <v>2.8842</v>
+      </c>
+      <c t="n" r="H141">
+        <v>265.8411</v>
       </c>
     </row>
     <row r="142">
       <c t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">AHR</t>
+          <t xml:space="preserve">RBU</t>
         </is>
       </c>
       <c t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ONUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C142">
-        <v>-1.8360</v>
+        <v>0.6521</v>
       </c>
       <c t="n" r="D142">
-        <v>-1.5791</v>
+        <v>-1.9174</v>
       </c>
       <c t="n" r="E142">
-        <v>3.8359</v>
+        <v>1.8957</v>
       </c>
       <c t="n" r="F142">
-        <v>-1.5798</v>
+        <v>-1.2102</v>
       </c>
       <c t="n" r="G142">
-        <v>1.0956</v>
+        <v>2.5239</v>
       </c>
     </row>
     <row r="143">
       <c t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">OKG</t>
+          <t xml:space="preserve">NUC</t>
         </is>
       </c>
       <c t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. EMLAK JET GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. CHARM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C143">
-        <v>-1.0289</v>
+        <v>-0.0249</v>
       </c>
       <c t="n" r="D143">
-        <v>-1.8516</v>
+        <v>-0.3813</v>
       </c>
       <c t="n" r="E143">
-        <v>1.8908</v>
+        <v>7.8613</v>
       </c>
       <c t="n" r="F143">
-        <v>-1.6776</v>
+        <v>-0.3826</v>
       </c>
       <c t="n" r="G143">
-        <v>0.9228</v>
+        <v>2.2642</v>
       </c>
       <c t="n" r="H143">
-        <v>70.4102</v>
+        <v>130.9711</v>
       </c>
     </row>
     <row r="144">
       <c t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">RF3</t>
+          <t xml:space="preserve">AHR</t>
         </is>
       </c>
       <c t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ONUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C144">
-        <v>-0.1960</v>
+        <v>-1.9919</v>
       </c>
       <c t="n" r="D144">
-        <v>-0.6420</v>
+        <v>-1.5873</v>
+      </c>
+      <c t="n" r="E144">
+        <v>3.6762</v>
       </c>
       <c t="n" r="F144">
-        <v>-0.8394</v>
+        <v>-1.5841</v>
       </c>
       <c t="n" r="G144">
-        <v>0.2900</v>
+        <v>1.0921</v>
       </c>
     </row>
     <row r="145">
       <c t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">BKA</t>
+          <t xml:space="preserve">OKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ANKA GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. EMLAK JET GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C145">
+        <v>-0.1815</v>
       </c>
       <c t="n" r="D145">
-        <v>0.0000</v>
+        <v>-1.7921</v>
       </c>
       <c t="n" r="E145">
-        <v>0.0000</v>
+        <v>2.1131</v>
       </c>
       <c t="n" r="F145">
-        <v>0.0000</v>
+        <v>-1.6795</v>
       </c>
       <c t="n" r="G145">
-        <v>0.0000</v>
+        <v>0.9814</v>
       </c>
       <c t="n" r="H145">
-        <v>0.0000</v>
+        <v>70.4192</v>
       </c>
     </row>
     <row r="146">
       <c t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">HP5</t>
+          <t xml:space="preserve">BKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ANKA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D146">
@@ -4533,20 +4542,20 @@
       <c t="n" r="G146">
         <v>0.0000</v>
       </c>
+      <c t="n" r="H146">
+        <v>0.0000</v>
+      </c>
     </row>
     <row r="147">
       <c t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">HP4</t>
+          <t xml:space="preserve">HP5</t>
         </is>
       </c>
       <c t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ MASTERTÜRK GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="D147">
-        <v>0.0000</v>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="E147">
         <v>0.0000</v>
@@ -4561,19 +4570,13 @@
     <row r="148">
       <c t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">NGA</t>
+          <t xml:space="preserve">HP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C148">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="D148">
-        <v>0.0000</v>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ MASTERTÜRK GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="E148">
         <v>0.0000</v>
@@ -4588,13 +4591,16 @@
     <row r="149">
       <c t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">NFA</t>
+          <t xml:space="preserve">NGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C149">
+        <v>0.0000</v>
       </c>
       <c t="n" r="D149">
         <v>0.0000</v>
@@ -4612,12 +4618,12 @@
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">RF1</t>
+          <t xml:space="preserve">NFA</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D150">
@@ -4636,13 +4642,22 @@
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">RDO</t>
+          <t xml:space="preserve">RF1</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN OTEL GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="D151">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="E151">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="F151">
+        <v>0.0000</v>
       </c>
       <c t="n" r="G151">
         <v>0.0000</v>
@@ -4651,12 +4666,12 @@
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">RMK</t>
+          <t xml:space="preserve">RDO</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EMLAK KATILIM YENİ EVİM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN OTEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G152">
@@ -4666,12 +4681,12 @@
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">RF2</t>
+          <t xml:space="preserve">RMK</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EMLAK KATILIM YENİ EVİM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G153">
@@ -4681,12 +4696,12 @@
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">RSM</t>
+          <t xml:space="preserve">RF2</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SMART PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G154">
@@ -4696,12 +4711,12 @@
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">RSO</t>
+          <t xml:space="preserve">RSM</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SONNE PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SMART PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G155">
@@ -4711,12 +4726,12 @@
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">RTO</t>
+          <t xml:space="preserve">RSO</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TOROS PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SONNE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G156">
@@ -4726,12 +4741,12 @@
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">RGN</t>
+          <t xml:space="preserve">RTO</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TOROS PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G157">
@@ -4741,2545 +4756,2536 @@
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">IIG</t>
+          <t xml:space="preserve">RGN</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C158">
-        <v>2.1988</v>
-      </c>
-      <c t="n" r="D158">
-        <v>8.7857</v>
-      </c>
-      <c t="n" r="E158">
-        <v>17.3878</v>
-      </c>
-      <c t="n" r="F158">
-        <v>8.8798</v>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="G158">
-        <v>-0.6075</v>
-      </c>
-      <c t="n" r="H158">
-        <v>152.9490</v>
-      </c>
-      <c t="n" r="I158">
-        <v>495.5761</v>
+        <v>0.0000</v>
       </c>
     </row>
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">TUG</t>
+          <t xml:space="preserve">RF3</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C159">
-        <v>0.6510</v>
+        <v>-0.1938</v>
       </c>
       <c t="n" r="D159">
-        <v>2.1231</v>
-      </c>
-      <c t="n" r="E159">
-        <v>37.8662</v>
+        <v>-0.6460</v>
       </c>
       <c t="n" r="F159">
-        <v>2.5343</v>
+        <v>-0.8705</v>
       </c>
       <c t="n" r="G159">
-        <v>-0.6426</v>
+        <v>-0.0999</v>
       </c>
     </row>
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">NUN</t>
+          <t xml:space="preserve">IIG</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. KELEŞOĞLU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C160">
-        <v>-0.2568</v>
+        <v>2.2286</v>
       </c>
       <c t="n" r="D160">
-        <v>-0.7537</v>
+        <v>8.7756</v>
       </c>
       <c t="n" r="E160">
-        <v>-0.2517</v>
+        <v>17.3780</v>
       </c>
       <c t="n" r="F160">
-        <v>-0.7923</v>
+        <v>8.9075</v>
       </c>
       <c t="n" r="G160">
-        <v>-1.5735</v>
+        <v>-0.5874</v>
+      </c>
+      <c t="n" r="H160">
+        <v>152.9950</v>
+      </c>
+      <c t="n" r="I160">
+        <v>495.7446</v>
       </c>
     </row>
     <row r="161">
       <c t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">ZPV</t>
+          <t xml:space="preserve">NUN</t>
         </is>
       </c>
       <c t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. KELEŞOĞLU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C161">
-        <v>6.9205</v>
+        <v>-0.2665</v>
       </c>
       <c t="n" r="D161">
-        <v>6.0181</v>
+        <v>-0.7614</v>
       </c>
       <c t="n" r="E161">
-        <v>-1.6887</v>
+        <v>-0.2594</v>
       </c>
       <c t="n" r="F161">
-        <v>5.6711</v>
+        <v>-0.8364</v>
       </c>
       <c t="n" r="G161">
-        <v>-6.2306</v>
-      </c>
-      <c t="n" r="H161">
-        <v>96.5133</v>
+        <v>-1.5753</v>
       </c>
     </row>
     <row r="162">
       <c t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">OO2</t>
+          <t xml:space="preserve">ZPV</t>
         </is>
       </c>
       <c t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
         </is>
       </c>
       <c t="n" r="C162">
-        <v>-3.1293</v>
+        <v>9.2260</v>
       </c>
       <c t="n" r="D162">
-        <v>-9.9944</v>
+        <v>9.0580</v>
       </c>
       <c t="n" r="E162">
-        <v>-11.7039</v>
+        <v>1.3796</v>
       </c>
       <c t="n" r="F162">
-        <v>-10.0656</v>
+        <v>8.3204</v>
       </c>
       <c t="n" r="G162">
-        <v>-7.2981</v>
+        <v>-4.4432</v>
+      </c>
+      <c t="n" r="H162">
+        <v>100.9015</v>
       </c>
     </row>
     <row r="163">
       <c t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">RSH</t>
+          <t xml:space="preserve">OO2</t>
         </is>
       </c>
       <c t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SEYHAN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C163">
-        <v>0.1577</v>
+        <v>-2.2778</v>
       </c>
       <c t="n" r="D163">
-        <v>4.2369</v>
+        <v>-10.0637</v>
       </c>
       <c t="n" r="E163">
-        <v>4.7236</v>
+        <v>-11.8165</v>
       </c>
       <c t="n" r="F163">
-        <v>4.0574</v>
+        <v>-10.1962</v>
       </c>
       <c t="n" r="G163">
-        <v>-13.4419</v>
+        <v>-7.4137</v>
       </c>
     </row>
     <row r="164">
       <c t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">ZVD</t>
+          <t xml:space="preserve">RYZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C164">
-        <v>-0.0358</v>
+        <v>0.3820</v>
       </c>
       <c t="n" r="D164">
-        <v>-0.1007</v>
+        <v>-0.5694</v>
       </c>
       <c t="n" r="E164">
-        <v>-17.3073</v>
+        <v>2.4246</v>
       </c>
       <c t="n" r="F164">
-        <v>-0.1130</v>
+        <v>-0.2999</v>
       </c>
       <c t="n" r="G164">
-        <v>-13.9549</v>
-      </c>
-      <c t="n" r="H164">
-        <v>196.7125</v>
+        <v>-11.4637</v>
       </c>
     </row>
     <row r="165">
       <c t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">RYZ</t>
+          <t xml:space="preserve">RSH</t>
         </is>
       </c>
       <c t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SEYHAN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C165">
-        <v>0.3820</v>
+        <v>0.1634</v>
       </c>
       <c t="n" r="D165">
-        <v>-0.5656</v>
+        <v>4.2407</v>
       </c>
       <c t="n" r="E165">
-        <v>2.4214</v>
+        <v>4.7211</v>
       </c>
       <c t="n" r="F165">
-        <v>-0.2987</v>
+        <v>4.0496</v>
       </c>
       <c t="n" r="G165">
-        <v>-14.9467</v>
+        <v>-13.4431</v>
       </c>
     </row>
     <row r="166">
       <c t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">YG6</t>
+          <t xml:space="preserve">ZVD</t>
         </is>
       </c>
       <c t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MANOLYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C166">
-        <v>-0.6343</v>
+        <v>-0.0465</v>
       </c>
       <c t="n" r="D166">
-        <v>-1.5675</v>
+        <v>-0.1081</v>
       </c>
       <c t="n" r="E166">
-        <v>-17.3637</v>
+        <v>-17.3186</v>
       </c>
       <c t="n" r="F166">
-        <v>-1.6661</v>
+        <v>-0.1288</v>
       </c>
       <c t="n" r="G166">
-        <v>-18.5411</v>
+        <v>-13.9653</v>
       </c>
       <c t="n" r="H166">
-        <v>-3.0647</v>
+        <v>196.5479</v>
       </c>
     </row>
     <row r="167">
       <c t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">YG3</t>
+          <t xml:space="preserve">YG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MANOLYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C167">
-        <v>-0.3000</v>
+        <v>-0.5751</v>
       </c>
       <c t="n" r="D167">
-        <v>-0.8571</v>
+        <v>-1.5531</v>
       </c>
       <c t="n" r="E167">
-        <v>-23.3487</v>
+        <v>-17.3536</v>
       </c>
       <c t="n" r="F167">
-        <v>-0.9079</v>
+        <v>-1.7178</v>
       </c>
       <c t="n" r="G167">
-        <v>-24.4789</v>
+        <v>-18.5257</v>
       </c>
       <c t="n" r="H167">
-        <v>350.3659</v>
+        <v>-3.0052</v>
       </c>
     </row>
     <row r="168">
       <c t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">REO</t>
+          <t xml:space="preserve">YG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C168">
-        <v>-0.0162</v>
+        <v>-0.3034</v>
       </c>
       <c t="n" r="D168">
-        <v>-0.0413</v>
+        <v>-0.8454</v>
       </c>
       <c t="n" r="E168">
-        <v>-0.0849</v>
+        <v>-23.3499</v>
       </c>
       <c t="n" r="F168">
-        <v>-0.0503</v>
+        <v>-0.9445</v>
       </c>
       <c t="n" r="G168">
-        <v>-24.5060</v>
+        <v>-24.4769</v>
+      </c>
+      <c t="n" r="H168">
+        <v>350.2799</v>
       </c>
     </row>
     <row r="169">
       <c t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">AZ7</t>
+          <t xml:space="preserve">REO</t>
         </is>
       </c>
       <c t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C169">
-        <v>-0.0810</v>
+        <v>-0.0258</v>
       </c>
       <c t="n" r="D169">
-        <v>-0.2711</v>
+        <v>-0.0525</v>
       </c>
       <c t="n" r="E169">
-        <v>-50.4010</v>
+        <v>-0.0960</v>
       </c>
       <c t="n" r="F169">
-        <v>-1.0104</v>
+        <v>-0.0611</v>
       </c>
       <c t="n" r="G169">
-        <v>-30.3336</v>
-      </c>
-      <c t="n" r="H169">
-        <v>70.8820</v>
-      </c>
-      <c t="n" r="I169">
-        <v>786.5571</v>
+        <v>-24.5121</v>
       </c>
     </row>
     <row r="170">
       <c t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">YG5</t>
+          <t xml:space="preserve">AZ7</t>
         </is>
       </c>
       <c t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FULYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C170">
-        <v>-0.6675</v>
+        <v>-0.0891</v>
       </c>
       <c t="n" r="D170">
-        <v>-1.7485</v>
+        <v>-0.2966</v>
       </c>
       <c t="n" r="E170">
-        <v>-30.4545</v>
+        <v>-50.5130</v>
       </c>
       <c t="n" r="F170">
-        <v>-1.8183</v>
+        <v>-1.0450</v>
       </c>
       <c t="n" r="G170">
-        <v>-30.7811</v>
+        <v>-30.3445</v>
       </c>
       <c t="n" r="H170">
-        <v>103.0017</v>
+        <v>70.9501</v>
+      </c>
+      <c t="n" r="I170">
+        <v>786.2470</v>
       </c>
     </row>
     <row r="171">
       <c t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">RG8</t>
+          <t xml:space="preserve">YG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. MERİÇ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FULYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C171">
-        <v>-0.0814</v>
+        <v>-0.6581</v>
       </c>
       <c t="n" r="D171">
-        <v>-0.5291</v>
+        <v>-1.7317</v>
       </c>
       <c t="n" r="E171">
-        <v>-17.8745</v>
+        <v>-30.4533</v>
       </c>
       <c t="n" r="F171">
-        <v>0.0139</v>
+        <v>-1.8670</v>
       </c>
       <c t="n" r="G171">
-        <v>-40.4857</v>
+        <v>-30.7996</v>
       </c>
       <c t="n" r="H171">
-        <v>91.5266</v>
+        <v>102.9554</v>
       </c>
     </row>
     <row r="172">
       <c t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">NG3</t>
+          <t xml:space="preserve">RG8</t>
         </is>
       </c>
       <c t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. MERİÇ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C172">
-        <v>-0.2027</v>
+        <v>0.1251</v>
       </c>
       <c t="n" r="D172">
-        <v>-3.4702</v>
+        <v>-0.5689</v>
       </c>
       <c t="n" r="E172">
-        <v>5.1135</v>
+        <v>-17.9276</v>
       </c>
       <c t="n" r="F172">
-        <v>-7.3027</v>
+        <v>-0.0572</v>
       </c>
       <c t="n" r="G172">
-        <v>-40.9115</v>
+        <v>-40.5172</v>
       </c>
       <c t="n" r="H172">
-        <v>113.7008</v>
+        <v>91.3865</v>
       </c>
     </row>
     <row r="173">
       <c t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">UG2</t>
+          <t xml:space="preserve">NG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">ÜNLÜ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C173">
-        <v>-0.5033</v>
+        <v>-0.2066</v>
       </c>
       <c t="n" r="D173">
-        <v>-19.3553</v>
+        <v>-3.4706</v>
       </c>
       <c t="n" r="E173">
-        <v>-40.6941</v>
+        <v>5.1055</v>
       </c>
       <c t="n" r="F173">
-        <v>-51.9351</v>
+        <v>-7.3207</v>
       </c>
       <c t="n" r="G173">
-        <v>-41.6329</v>
+        <v>-40.9118</v>
       </c>
       <c t="n" r="H173">
-        <v>21.3473</v>
-      </c>
-      <c t="n" r="I173">
-        <v>217.9894</v>
+        <v>113.6861</v>
       </c>
     </row>
     <row r="174">
       <c t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">NH3</t>
+          <t xml:space="preserve">UG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY  YÖNETİMİ A.Ş TÜRKAZ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ÜNLÜ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C174">
-        <v>-11.1077</v>
+        <v>-0.2427</v>
       </c>
       <c t="n" r="D174">
-        <v>-23.7292</v>
+        <v>-18.2532</v>
       </c>
       <c t="n" r="E174">
-        <v>-25.4954</v>
+        <v>-40.6808</v>
       </c>
       <c t="n" r="F174">
-        <v>-26.0467</v>
+        <v>-51.9295</v>
       </c>
       <c t="n" r="G174">
-        <v>-43.1350</v>
+        <v>-41.5951</v>
       </c>
       <c t="n" r="H174">
-        <v>40.6382</v>
+        <v>-2.5485</v>
+      </c>
+      <c t="n" r="I174">
+        <v>218.0267</v>
       </c>
     </row>
     <row r="175">
       <c t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">IY1</t>
+          <t xml:space="preserve">NH3</t>
         </is>
       </c>
       <c t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. V STATÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY  YÖNETİMİ A.Ş TÜRKAZ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C175">
-        <v>-78.5784</v>
+        <v>-11.1098</v>
       </c>
       <c t="n" r="D175">
-        <v>-80.0108</v>
+        <v>-23.7305</v>
       </c>
       <c t="n" r="E175">
-        <v>-56.6807</v>
+        <v>-25.5125</v>
       </c>
       <c t="n" r="F175">
-        <v>-80.0192</v>
+        <v>-26.0550</v>
       </c>
       <c t="n" r="G175">
-        <v>-45.1039</v>
+        <v>-43.1103</v>
+      </c>
+      <c t="n" r="H175">
+        <v>40.6260</v>
       </c>
     </row>
     <row r="176">
       <c t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">RG1</t>
+          <t xml:space="preserve">IY1</t>
         </is>
       </c>
       <c t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. YILDIZ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. V STATÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C176">
-        <v>0.6071</v>
+        <v>-78.6285</v>
       </c>
       <c t="n" r="D176">
-        <v>-2.9973</v>
+        <v>-80.0655</v>
       </c>
       <c t="n" r="E176">
-        <v>-10.1131</v>
+        <v>-56.7992</v>
       </c>
       <c t="n" r="F176">
-        <v>-15.2301</v>
+        <v>-80.0809</v>
       </c>
       <c t="n" r="G176">
-        <v>-60.0825</v>
-      </c>
-      <c t="n" r="H176">
-        <v>-22.2081</v>
-      </c>
-      <c t="n" r="I176">
-        <v>322.9895</v>
+        <v>-45.0830</v>
       </c>
     </row>
     <row r="177">
       <c t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">GF3</t>
+          <t xml:space="preserve">NGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C177">
-        <v>-8.8450</v>
+        <v>2.7760</v>
       </c>
       <c t="n" r="D177">
-        <v>-21.0463</v>
+        <v>12.0474</v>
       </c>
       <c t="n" r="E177">
-        <v>435.2073</v>
+        <v>15.5703</v>
       </c>
       <c t="n" r="F177">
-        <v>-21.0480</v>
+        <v>11.3400</v>
       </c>
       <c t="n" r="G177">
-        <v>-60.7327</v>
+        <v>-47.4933</v>
       </c>
     </row>
     <row r="178">
       <c t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">NGO</t>
+          <t xml:space="preserve">RG1</t>
         </is>
       </c>
       <c t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. YILDIZ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C178">
-        <v>3.0920</v>
+        <v>2.1550</v>
       </c>
       <c t="n" r="D178">
-        <v>11.9630</v>
+        <v>6.9659</v>
       </c>
       <c t="n" r="E178">
-        <v>15.4056</v>
+        <v>-10.9495</v>
       </c>
       <c t="n" r="F178">
-        <v>11.0171</v>
+        <v>-14.3322</v>
       </c>
       <c t="n" r="G178">
-        <v>-60.8075</v>
+        <v>-59.6633</v>
+      </c>
+      <c t="n" r="H178">
+        <v>-21.3855</v>
+      </c>
+      <c t="n" r="I178">
+        <v>327.2153</v>
       </c>
     </row>
     <row r="179">
       <c t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">RP5</t>
+          <t xml:space="preserve">GF3</t>
         </is>
       </c>
       <c t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş.MİLENYUM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C179">
-        <v>15.4932</v>
+        <v>-10.2980</v>
       </c>
       <c t="n" r="D179">
-        <v>23.1851</v>
+        <v>-26.1516</v>
       </c>
       <c t="n" r="E179">
-        <v>-59.5600</v>
+        <v>462.9757</v>
       </c>
       <c t="n" r="F179">
-        <v>82.1661</v>
+        <v>-26.1544</v>
       </c>
       <c t="n" r="G179">
-        <v>-62.2088</v>
-      </c>
-      <c t="n" r="H179">
-        <v>-63.4855</v>
-      </c>
-      <c t="n" r="I179">
-        <v>-2.6624</v>
+        <v>-61.5071</v>
       </c>
     </row>
     <row r="180">
       <c t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">YD1</t>
+          <t xml:space="preserve">RP5</t>
         </is>
       </c>
       <c t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş.MİLENYUM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C180">
-        <v>-93.9591</v>
+        <v>13.0723</v>
       </c>
       <c t="n" r="D180">
-        <v>-77.0677</v>
+        <v>28.5343</v>
       </c>
       <c t="n" r="E180">
-        <v>-75.8932</v>
+        <v>-60.5138</v>
       </c>
       <c t="n" r="F180">
-        <v>-77.0869</v>
+        <v>77.9675</v>
       </c>
       <c t="n" r="G180">
-        <v>-67.4878</v>
+        <v>-62.8638</v>
       </c>
       <c t="n" r="H180">
-        <v>-84.9537</v>
+        <v>-64.3190</v>
       </c>
       <c t="n" r="I180">
-        <v>-45.0192</v>
+        <v>-4.8908</v>
       </c>
     </row>
     <row r="181">
       <c t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">YG2</t>
+          <t xml:space="preserve">YD1</t>
         </is>
       </c>
       <c t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYÇİÇEĞİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C181">
-        <v>-87.7193</v>
+        <v>-22.2493</v>
       </c>
       <c t="n" r="D181">
-        <v>-93.9130</v>
+        <v>-77.0473</v>
       </c>
       <c t="n" r="E181">
-        <v>-96.2567</v>
+        <v>-75.8801</v>
       </c>
       <c t="n" r="F181">
-        <v>-93.9130</v>
+        <v>-77.0808</v>
       </c>
       <c t="n" r="G181">
-        <v>-98.9811</v>
+        <v>-67.4734</v>
       </c>
       <c t="n" r="H181">
-        <v>-99.9998</v>
+        <v>-84.9475</v>
+      </c>
+      <c t="n" r="I181">
+        <v>-45.0047</v>
       </c>
     </row>
     <row r="182">
       <c t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">MMG</t>
+          <t xml:space="preserve">YG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MEYDAN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYÇİÇEĞİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C182">
-        <v>-98.9069</v>
+        <v>-87.7193</v>
       </c>
       <c t="n" r="D182">
-        <v>-99.1370</v>
+        <v>-98.7931</v>
       </c>
       <c t="n" r="E182">
-        <v>-99.0836</v>
+        <v>-96.2567</v>
       </c>
       <c t="n" r="F182">
-        <v>-99.1447</v>
+        <v>-93.9130</v>
       </c>
       <c t="n" r="G182">
-        <v>-99.1809</v>
+        <v>-98.9811</v>
       </c>
       <c t="n" r="H182">
-        <v>-98.6001</v>
+        <v>-99.9998</v>
       </c>
     </row>
     <row r="183">
       <c t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">SGF</t>
+          <t xml:space="preserve">MMG</t>
         </is>
       </c>
       <c t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. SOFAZ ÖZEL GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MEYDAN GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C183">
+        <v>-98.8772</v>
+      </c>
+      <c t="n" r="D183">
+        <v>-99.1164</v>
+      </c>
+      <c t="n" r="E183">
+        <v>-99.0616</v>
+      </c>
+      <c t="n" r="F183">
+        <v>-99.1243</v>
+      </c>
+      <c t="n" r="G183">
+        <v>-99.1604</v>
+      </c>
+      <c t="n" r="H183">
+        <v>-98.5649</v>
       </c>
     </row>
     <row r="184">
       <c t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">NKB</t>
+          <t xml:space="preserve">SGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV BEŞİKTAŞ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. SOFAZ ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">NEV</t>
+          <t xml:space="preserve">NKB</t>
         </is>
       </c>
       <c t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV KADIKÖY KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV BEŞİKTAŞ KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">NKE</t>
+          <t xml:space="preserve">NEV</t>
         </is>
       </c>
       <c t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV KADIKÖY KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">MUG</t>
+          <t xml:space="preserve">NKE</t>
         </is>
       </c>
       <c t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C187">
-        <v>0.4191</v>
-      </c>
-      <c t="n" r="D187">
-        <v>2.2518</v>
-      </c>
-      <c t="n" r="F187">
-        <v>2.9478</v>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV KATILIM GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="188">
       <c t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">BGV</t>
+          <t xml:space="preserve">MUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C188">
+        <v>0.9924</v>
+      </c>
+      <c t="n" r="D188">
+        <v>2.9548</v>
+      </c>
+      <c t="n" r="F188">
+        <v>3.6258</v>
       </c>
     </row>
     <row r="189">
       <c t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">BGA</t>
+          <t xml:space="preserve">BGV</t>
         </is>
       </c>
       <c t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">ALLBATROSS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">AB2</t>
+          <t xml:space="preserve">BGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">ALLBATROSS PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C190">
-        <v>-16.7240</v>
-      </c>
-      <c t="n" r="D190">
-        <v>-36.9994</v>
-      </c>
-      <c t="n" r="F190">
-        <v>-38.2147</v>
+          <t xml:space="preserve">ALLBATROSS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="191">
       <c t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">AY2</t>
+          <t xml:space="preserve">AB2</t>
         </is>
       </c>
       <c t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ARVA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALLBATROSS PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C191">
-        <v>-10.2423</v>
+        <v>-17.6214</v>
       </c>
       <c t="n" r="D191">
-        <v>-30.2073</v>
+        <v>-38.0980</v>
       </c>
       <c t="n" r="F191">
-        <v>-29.1806</v>
+        <v>-40.4373</v>
       </c>
     </row>
     <row r="192">
       <c t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">BGO</t>
+          <t xml:space="preserve">AY2</t>
         </is>
       </c>
       <c t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BAHAR GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ARVA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C192">
+        <v>-10.5085</v>
+      </c>
+      <c t="n" r="D192">
+        <v>-63.2375</v>
+      </c>
+      <c t="n" r="F192">
+        <v>-28.8435</v>
       </c>
     </row>
     <row r="193">
       <c t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">TLG</t>
+          <t xml:space="preserve">BGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C193">
-        <v>1.1286</v>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BAHAR GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="194">
       <c t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">AY1</t>
+          <t xml:space="preserve">TLG</t>
         </is>
       </c>
       <c t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BMS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C194">
-        <v>0.7333</v>
-      </c>
-      <c t="n" r="D194">
-        <v>1.3027</v>
-      </c>
-      <c t="n" r="F194">
-        <v>1.8231</v>
+        <v>1.1290</v>
       </c>
     </row>
     <row r="195">
       <c t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">DGR</t>
+          <t xml:space="preserve">AY1</t>
         </is>
       </c>
       <c t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞRUL GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BMS GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C195">
+        <v>0.7742</v>
+      </c>
+      <c t="n" r="D195">
+        <v>1.3433</v>
+      </c>
+      <c t="n" r="F195">
+        <v>1.8543</v>
       </c>
     </row>
     <row r="196">
       <c t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">DRO</t>
+          <t xml:space="preserve">DGR</t>
         </is>
       </c>
       <c t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞRUL PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞRUL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">AN4</t>
+          <t xml:space="preserve">DRO</t>
         </is>
       </c>
       <c t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞRUL PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">TG2</t>
+          <t xml:space="preserve">AN4</t>
         </is>
       </c>
       <c t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">TUP</t>
+          <t xml:space="preserve">TG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. TÜRKEL BİRDALLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">UGP</t>
+          <t xml:space="preserve">TUP</t>
         </is>
       </c>
       <c t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. TÜRKEL BİRDALLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">NGC</t>
+          <t xml:space="preserve">UGP</t>
         </is>
       </c>
       <c t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">ANATOLİA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MG HARBOUR GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C201">
-        <v>6.0909</v>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="202">
       <c t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">GYU</t>
+          <t xml:space="preserve">NGC</t>
         </is>
       </c>
       <c t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLİA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MG HARBOUR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C202">
-        <v>1.7097</v>
+        <v>1.1628</v>
       </c>
       <c t="n" r="D202">
-        <v>419.6573</v>
-      </c>
-      <c t="n" r="E202">
-        <v>461.3167</v>
-      </c>
-      <c t="n" r="F202">
-        <v>421.7573</v>
+        <v>1.3600</v>
       </c>
     </row>
     <row r="203">
       <c t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">DGG</t>
+          <t xml:space="preserve">GYU</t>
         </is>
       </c>
       <c t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C203">
-        <v>7.3319</v>
+        <v>1.6623</v>
       </c>
       <c t="n" r="D203">
-        <v>45.4550</v>
+        <v>418.7024</v>
       </c>
       <c t="n" r="E203">
-        <v>60.2337</v>
+        <v>461.5674</v>
       </c>
       <c t="n" r="F203">
-        <v>46.4610</v>
+        <v>423.2155</v>
       </c>
     </row>
     <row r="204">
       <c t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">OGN</t>
+          <t xml:space="preserve">DGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C204">
+        <v>12.1191</v>
+      </c>
+      <c t="n" r="D204">
+        <v>44.7362</v>
+      </c>
+      <c t="n" r="E204">
+        <v>59.7120</v>
+      </c>
+      <c t="n" r="F204">
+        <v>46.4654</v>
       </c>
     </row>
     <row r="205">
       <c t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">SGG</t>
+          <t xml:space="preserve">OGN</t>
         </is>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C205">
-        <v>-0.0457</v>
-      </c>
-      <c t="n" r="D205">
-        <v>-0.1094</v>
-      </c>
-      <c t="n" r="E205">
-        <v>19.4137</v>
-      </c>
-      <c t="n" r="F205">
-        <v>-0.1298</v>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="206">
       <c t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">YGG</t>
+          <t xml:space="preserve">SGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C206">
-        <v>-0.8234</v>
+        <v>-0.0479</v>
+      </c>
+      <c t="n" r="D206">
+        <v>-0.1102</v>
+      </c>
+      <c t="n" r="E206">
+        <v>19.4046</v>
+      </c>
+      <c t="n" r="F206">
+        <v>-0.1358</v>
       </c>
     </row>
     <row r="207">
       <c t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">BGU</t>
+          <t xml:space="preserve">YGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C207">
+        <v>-0.0311</v>
       </c>
     </row>
     <row r="208">
       <c t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">ON3</t>
+          <t xml:space="preserve">BGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C208">
-        <v>3.1984</v>
-      </c>
-      <c t="n" r="D208">
-        <v>9.0169</v>
-      </c>
-      <c t="n" r="E208">
-        <v>19.5457</v>
-      </c>
-      <c t="n" r="F208">
-        <v>9.7853</v>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="209">
       <c t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">ONU</t>
+          <t xml:space="preserve">ON3</t>
         </is>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C209">
-        <v>-0.1021</v>
+        <v>2.9227</v>
       </c>
       <c t="n" r="D209">
-        <v>-0.3105</v>
+        <v>8.8029</v>
+      </c>
+      <c t="n" r="E209">
+        <v>19.5296</v>
       </c>
       <c t="n" r="F209">
-        <v>-0.3100</v>
+        <v>10.1283</v>
       </c>
     </row>
     <row r="210">
       <c t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">BAK</t>
+          <t xml:space="preserve">RZ1</t>
         </is>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BAKIRCI PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C210">
-        <v>-0.8890</v>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="211">
       <c t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">BLM</t>
+          <t xml:space="preserve">ONU</t>
         </is>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BALMUMCU PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C211">
-        <v>0.4541</v>
+        <v>-0.1080</v>
+      </c>
+      <c t="n" r="D211">
+        <v>-0.3304</v>
+      </c>
+      <c t="n" r="F211">
+        <v>-0.3296</v>
       </c>
     </row>
     <row r="212">
       <c t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">BNE</t>
+          <t xml:space="preserve">BAK</t>
         </is>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BENESTA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BAKIRCI PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C212">
-        <v>-0.0340</v>
+        <v>-0.9912</v>
       </c>
       <c t="n" r="D212">
-        <v>-0.0975</v>
-      </c>
-      <c t="n" r="E212">
-        <v>12.7772</v>
-      </c>
-      <c t="n" r="F212">
-        <v>-0.1054</v>
+        <v>6.7233</v>
       </c>
     </row>
     <row r="213">
       <c t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">BN2</t>
+          <t xml:space="preserve">BLM</t>
         </is>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BENESTA-2 PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BALMUMCU PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C213">
-        <v>0.8097</v>
-      </c>
-      <c t="n" r="D213">
-        <v>3.1200</v>
-      </c>
-      <c t="n" r="E213">
-        <v>12.5577</v>
-      </c>
-      <c t="n" r="F213">
-        <v>3.1209</v>
+        <v>0.2386</v>
       </c>
     </row>
     <row r="214">
       <c t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">GTR</t>
+          <t xml:space="preserve">BNE</t>
         </is>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. GÖKTÜRK-3 PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BENESTA PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C214">
-        <v>-99.7301</v>
+        <v>-0.0370</v>
       </c>
       <c t="n" r="D214">
-        <v>-99.7637</v>
+        <v>-0.0989</v>
       </c>
       <c t="n" r="E214">
-        <v>-99.9827</v>
+        <v>12.7750</v>
       </c>
       <c t="n" r="F214">
-        <v>-99.9616</v>
+        <v>-0.1119</v>
       </c>
     </row>
     <row r="215">
       <c t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">BRP</t>
+          <t xml:space="preserve">BN2</t>
         </is>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BENESTA-2 PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C215">
+        <v>0.8054</v>
+      </c>
+      <c t="n" r="D215">
+        <v>3.1186</v>
+      </c>
+      <c t="n" r="E215">
+        <v>12.5459</v>
+      </c>
+      <c t="n" r="F215">
+        <v>3.1182</v>
       </c>
     </row>
     <row r="216">
       <c t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">ZDR</t>
+          <t xml:space="preserve">GTR</t>
         </is>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. GÖKTÜRK-3 PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C216">
+        <v>-99.8272</v>
+      </c>
+      <c t="n" r="D216">
+        <v>-99.8495</v>
+      </c>
+      <c t="n" r="E216">
+        <v>-99.9877</v>
+      </c>
+      <c t="n" r="F216">
+        <v>-99.9752</v>
       </c>
     </row>
     <row r="217">
       <c t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">IGJ</t>
+          <t xml:space="preserve">BRP</t>
         </is>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C217">
-        <v>0.3629</v>
-      </c>
-      <c t="n" r="D217">
-        <v>0.3804</v>
-      </c>
-      <c t="n" r="E217">
-        <v>36.7075</v>
-      </c>
-      <c t="n" r="F217">
-        <v>0.4598</v>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="218">
       <c t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">TOP</t>
+          <t xml:space="preserve">ZDR</t>
         </is>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. TOPRAKTAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">ZUC</t>
+          <t xml:space="preserve">IGJ</t>
         </is>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C219">
+        <v>0.3206</v>
+      </c>
+      <c t="n" r="D219">
+        <v>0.3654</v>
+      </c>
+      <c t="n" r="E219">
+        <v>36.6957</v>
+      </c>
+      <c t="n" r="F219">
+        <v>0.4958</v>
       </c>
     </row>
     <row r="220">
       <c t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">BG1</t>
+          <t xml:space="preserve">TOP</t>
         </is>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">BULLS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. TOPRAKTAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">BP1</t>
+          <t xml:space="preserve">ZUC</t>
         </is>
       </c>
       <c t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">BULLS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">DLT</t>
+          <t xml:space="preserve">BG1</t>
         </is>
       </c>
       <c t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">BULLS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">BES</t>
+          <t xml:space="preserve">BP1</t>
         </is>
       </c>
       <c t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">BULLS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">DKG</t>
+          <t xml:space="preserve">DLT</t>
         </is>
       </c>
       <c t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">DDO</t>
+          <t xml:space="preserve">BES</t>
         </is>
       </c>
       <c t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C225">
-        <v>1.8965</v>
-      </c>
-      <c t="n" r="D225">
-        <v>1.5831</v>
-      </c>
-      <c t="n" r="F225">
-        <v>6.3470</v>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="226">
       <c t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">DIG</t>
+          <t xml:space="preserve">DKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C226">
-        <v>2.7182</v>
-      </c>
-      <c t="n" r="D226">
-        <v>6.9781</v>
-      </c>
-      <c t="n" r="E226">
-        <v>15.2802</v>
-      </c>
-      <c t="n" r="F226">
-        <v>7.6134</v>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="227">
       <c t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">DYD</t>
+          <t xml:space="preserve">DDO</t>
         </is>
       </c>
       <c t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C227">
+        <v>6.0658</v>
+      </c>
+      <c t="n" r="D227">
+        <v>5.5082</v>
+      </c>
+      <c t="n" r="F227">
+        <v>12.6673</v>
       </c>
     </row>
     <row r="228">
       <c t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">FN6</t>
+          <t xml:space="preserve">DYD</t>
         </is>
       </c>
       <c t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">FDR</t>
+          <t xml:space="preserve">FN6</t>
         </is>
       </c>
       <c t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C229">
-        <v>2.9490</v>
-      </c>
-      <c t="n" r="D229">
-        <v>7.3209</v>
-      </c>
-      <c t="n" r="E229">
-        <v>15.9538</v>
-      </c>
-      <c t="n" r="F229">
-        <v>7.9485</v>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="230">
       <c t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">FLG</t>
+          <t xml:space="preserve">FDR</t>
         </is>
       </c>
       <c t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. FLORYA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C230">
-        <v>3.1352</v>
+        <v>2.6718</v>
       </c>
       <c t="n" r="D230">
-        <v>9.5180</v>
+        <v>6.8458</v>
       </c>
       <c t="n" r="E230">
-        <v>19.3830</v>
+        <v>15.9447</v>
       </c>
       <c t="n" r="F230">
-        <v>10.2050</v>
+        <v>8.0977</v>
       </c>
     </row>
     <row r="231">
       <c t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">FGR</t>
+          <t xml:space="preserve">FLG</t>
         </is>
       </c>
       <c t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. GRN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. FLORYA PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C231">
-        <v>-0.0258</v>
+        <v>3.1970</v>
       </c>
       <c t="n" r="D231">
-        <v>0.7810</v>
+        <v>9.4956</v>
+      </c>
+      <c t="n" r="E231">
+        <v>19.6465</v>
       </c>
       <c t="n" r="F231">
-        <v>1.2114</v>
+        <v>10.7365</v>
       </c>
     </row>
     <row r="232">
       <c t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">FG2</t>
+          <t xml:space="preserve">FGR</t>
         </is>
       </c>
       <c t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. GRN GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C232">
+        <v>0.2682</v>
+      </c>
+      <c t="n" r="D232">
+        <v>0.9310</v>
+      </c>
+      <c t="n" r="E232">
+        <v>3.8559</v>
+      </c>
+      <c t="n" r="F232">
+        <v>1.4513</v>
       </c>
     </row>
     <row r="233">
       <c t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">FCN</t>
+          <t xml:space="preserve">FG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C233">
-        <v>2.9490</v>
-      </c>
-      <c t="n" r="D233">
-        <v>7.3209</v>
-      </c>
-      <c t="n" r="E233">
-        <v>15.9538</v>
-      </c>
-      <c t="n" r="F233">
-        <v>7.9485</v>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="234">
       <c t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">FG3</t>
+          <t xml:space="preserve">FCN</t>
         </is>
       </c>
       <c t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C234">
+        <v>2.6718</v>
+      </c>
+      <c t="n" r="D234">
+        <v>6.8458</v>
+      </c>
+      <c t="n" r="E234">
+        <v>15.9447</v>
+      </c>
+      <c t="n" r="F234">
+        <v>8.0977</v>
       </c>
     </row>
     <row r="235">
       <c t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">YSZ</t>
+          <t xml:space="preserve">FG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FYSZ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">FTI</t>
+          <t xml:space="preserve">YSZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FYSZ KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">FTT</t>
+          <t xml:space="preserve">FTI</t>
         </is>
       </c>
       <c t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. TRİO GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C237">
-        <v>-3.0929</v>
-      </c>
-      <c t="n" r="D237">
-        <v>-83.7417</v>
-      </c>
-      <c t="n" r="F237">
-        <v>-84.8395</v>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="238">
       <c t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">OLG</t>
+          <t xml:space="preserve">FTT</t>
         </is>
       </c>
       <c t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">GOLDEN GLOBAL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. TRİO GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C238">
+        <v>-2.0365</v>
+      </c>
+      <c t="n" r="D238">
+        <v>-82.5474</v>
+      </c>
+      <c t="n" r="F238">
+        <v>-84.7257</v>
       </c>
     </row>
     <row r="239">
       <c t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">OLP</t>
+          <t xml:space="preserve">OLG</t>
         </is>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">GOLDEN GLOBAL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">GOLDEN GLOBAL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">HVG</t>
+          <t xml:space="preserve">OLP</t>
         </is>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C240">
-        <v>-0.0517</v>
-      </c>
-      <c t="n" r="D240">
-        <v>-0.1463</v>
-      </c>
-      <c t="n" r="E240">
-        <v>30.4737</v>
-      </c>
-      <c t="n" r="F240">
-        <v>-0.1574</v>
+          <t xml:space="preserve">GOLDEN GLOBAL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="241">
       <c t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">HGG</t>
+          <t xml:space="preserve">HVG</t>
         </is>
       </c>
       <c t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C241">
-        <v>-0.0752</v>
+        <v>-0.0534</v>
       </c>
       <c t="n" r="D241">
-        <v>-0.2383</v>
+        <v>-0.1447</v>
       </c>
       <c t="n" r="E241">
-        <v>1625.0594</v>
+        <v>30.4732</v>
       </c>
       <c t="n" r="F241">
-        <v>-0.2459</v>
+        <v>-0.1653</v>
       </c>
     </row>
     <row r="242">
       <c t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">HV2</t>
+          <t xml:space="preserve">HGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C242">
+        <v>-0.1004</v>
+      </c>
+      <c t="n" r="D242">
+        <v>-0.2493</v>
+      </c>
+      <c t="n" r="E242">
+        <v>1628.1503</v>
+      </c>
+      <c t="n" r="F242">
+        <v>-0.2691</v>
       </c>
     </row>
     <row r="243">
       <c t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">HG2</t>
+          <t xml:space="preserve">HV2</t>
         </is>
       </c>
       <c t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">HVY</t>
+          <t xml:space="preserve">HG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YENİ UFUKLAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">HLN</t>
+          <t xml:space="preserve">HVY</t>
         </is>
       </c>
       <c t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C245">
-        <v>-4.2207</v>
-      </c>
-      <c t="n" r="D245">
-        <v>-13.9792</v>
-      </c>
-      <c t="n" r="F245">
-        <v>-14.5809</v>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YENİ UFUKLAR GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="246">
       <c t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">HMP</t>
+          <t xml:space="preserve">HLN</t>
         </is>
       </c>
       <c t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C246">
-        <v>-4.8714</v>
+        <v>-4.9013</v>
       </c>
       <c t="n" r="D246">
-        <v>-14.5929</v>
-      </c>
-      <c t="n" r="E246">
-        <v>-21.5908</v>
+        <v>-14.3343</v>
       </c>
       <c t="n" r="F246">
-        <v>-15.1863</v>
+        <v>-15.6161</v>
       </c>
     </row>
     <row r="247">
       <c t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">HIK</t>
+          <t xml:space="preserve">HMP</t>
         </is>
       </c>
       <c t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C247">
+        <v>-5.3363</v>
+      </c>
+      <c t="n" r="D247">
+        <v>-14.8699</v>
+      </c>
+      <c t="n" r="E247">
+        <v>-22.6217</v>
+      </c>
+      <c t="n" r="F247">
+        <v>-16.0559</v>
       </c>
     </row>
     <row r="248">
       <c t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">HG8</t>
+          <t xml:space="preserve">HIK</t>
         </is>
       </c>
       <c t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">HMA</t>
+          <t xml:space="preserve">HG8</t>
         </is>
       </c>
       <c t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">IRJ</t>
+          <t xml:space="preserve">HMA</t>
         </is>
       </c>
       <c t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">IE1</t>
+          <t xml:space="preserve">IRJ</t>
         </is>
       </c>
       <c t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">IY3</t>
+          <t xml:space="preserve">IE1</t>
         </is>
       </c>
       <c t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C252">
-        <v>-79.4861</v>
-      </c>
-      <c t="n" r="D252">
-        <v>-81.7777</v>
-      </c>
-      <c t="n" r="E252">
-        <v>2940.7692</v>
-      </c>
-      <c t="n" r="F252">
-        <v>-81.7851</v>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="253">
       <c t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">IY2</t>
+          <t xml:space="preserve">IY3</t>
         </is>
       </c>
       <c t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C253">
-        <v>-1.4494</v>
+        <v>-79.5759</v>
       </c>
       <c t="n" r="D253">
-        <v>-12.9482</v>
+        <v>-81.8716</v>
+      </c>
+      <c t="n" r="E253">
+        <v>2925.1672</v>
       </c>
       <c t="n" r="F253">
-        <v>-12.9848</v>
+        <v>-81.8852</v>
       </c>
     </row>
     <row r="254">
       <c t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">VMG</t>
+          <t xml:space="preserve">IY2</t>
         </is>
       </c>
       <c t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C254">
-        <v>-4.7578</v>
+        <v>-1.5004</v>
       </c>
       <c t="n" r="D254">
-        <v>-5.2927</v>
-      </c>
-      <c t="n" r="E254">
-        <v>49.2763</v>
+        <v>-13.1319</v>
       </c>
       <c t="n" r="F254">
-        <v>-3.3080</v>
+        <v>-13.1988</v>
       </c>
     </row>
     <row r="255">
       <c t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">VMP</t>
+          <t xml:space="preserve">VMG</t>
         </is>
       </c>
       <c t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C255">
+        <v>-5.9477</v>
+      </c>
+      <c t="n" r="D255">
+        <v>-6.4682</v>
+      </c>
+      <c t="n" r="E255">
+        <v>-9.3487</v>
+      </c>
+      <c t="n" r="F255">
+        <v>-4.5460</v>
       </c>
     </row>
     <row r="256">
       <c t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">KPE</t>
+          <t xml:space="preserve">VMP</t>
         </is>
       </c>
       <c t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. KAR PAYI ÖDEYEN GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C256">
-        <v>3.1036</v>
+          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="257">
       <c t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">RIN</t>
+          <t xml:space="preserve">KPE</t>
         </is>
       </c>
       <c t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. RİNNOVA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. KAR PAYI ÖDEYEN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C257">
-        <v>0.4800</v>
+        <v>2.9240</v>
       </c>
     </row>
     <row r="258">
       <c t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">ITO</t>
+          <t xml:space="preserve">RIN</t>
         </is>
       </c>
       <c t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. T-FON PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. RİNNOVA PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C258">
+        <v>0.0630</v>
       </c>
     </row>
     <row r="259">
       <c t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">UNO</t>
+          <t xml:space="preserve">ITO</t>
         </is>
       </c>
       <c t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. UNİCON PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. T-FON PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">YAL</t>
+          <t xml:space="preserve">UNO</t>
         </is>
       </c>
       <c t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C260">
-        <v>68.8784</v>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. UNİCON PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="261">
       <c t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">YLP</t>
+          <t xml:space="preserve">YAL</t>
         </is>
       </c>
       <c t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C261">
+        <v>70.7990</v>
       </c>
     </row>
     <row r="262">
       <c t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">KL2</t>
+          <t xml:space="preserve">YLP</t>
         </is>
       </c>
       <c t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">KALENDER GAYRİMENKUL PORTFÖY YÖNETİMİ A.Ş. KONUTFON GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="I262">
-        <v>0.0000</v>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="263">
       <c t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">KL1</t>
+          <t xml:space="preserve">KBN</t>
         </is>
       </c>
       <c t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">KALENDER GAYRİMENKUL PORTFÖY YÖNETİMİ A.Ş. TRAKYA GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="I263">
-        <v>0.0000</v>
+          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C263">
+        <v>2.2015</v>
+      </c>
+      <c t="n" r="D263">
+        <v>6.7752</v>
+      </c>
+      <c t="n" r="F263">
+        <v>7.8034</v>
       </c>
     </row>
     <row r="264">
       <c t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">KBN</t>
+          <t xml:space="preserve">KKR</t>
         </is>
       </c>
       <c t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C264">
-        <v>2.5022</v>
+        <v>2.2037</v>
       </c>
       <c t="n" r="D264">
-        <v>7.2216</v>
+        <v>6.7545</v>
       </c>
       <c t="n" r="F264">
-        <v>7.5929</v>
+        <v>7.7829</v>
       </c>
     </row>
     <row r="265">
       <c t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">KKR</t>
+          <t xml:space="preserve">MDG</t>
         </is>
       </c>
       <c t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C265">
-        <v>2.5044</v>
-      </c>
-      <c t="n" r="D265">
-        <v>7.2192</v>
-      </c>
-      <c t="n" r="F265">
-        <v>7.5721</v>
+          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="266">
       <c t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">MDG</t>
+          <t xml:space="preserve">NAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞAN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C266">
+        <v>-30.3469</v>
+      </c>
+      <c t="n" r="D266">
+        <v>-27.7503</v>
+      </c>
+      <c t="n" r="E266">
+        <v>-23.3555</v>
+      </c>
+      <c t="n" r="F266">
+        <v>-27.2058</v>
       </c>
     </row>
     <row r="267">
       <c t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">NAA</t>
+          <t xml:space="preserve">NGB</t>
         </is>
       </c>
       <c t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C267">
-        <v>-30.0129</v>
-      </c>
-      <c t="n" r="D267">
-        <v>-27.4883</v>
-      </c>
-      <c t="n" r="E267">
-        <v>-23.1295</v>
-      </c>
-      <c t="n" r="F267">
-        <v>-27.1655</v>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="268">
       <c t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">NGB</t>
+          <t xml:space="preserve">NBR</t>
         </is>
       </c>
       <c t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C268">
+        <v>-0.6556</v>
+      </c>
+      <c t="n" r="D268">
+        <v>25.9505</v>
+      </c>
+      <c t="n" r="E268">
+        <v>-33.2036</v>
+      </c>
+      <c t="n" r="F268">
+        <v>95.8457</v>
       </c>
     </row>
     <row r="269">
       <c t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">NBR</t>
+          <t xml:space="preserve">NGD</t>
         </is>
       </c>
       <c t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C269">
-        <v>-0.6641</v>
-      </c>
-      <c t="n" r="D269">
-        <v>117.4926</v>
-      </c>
-      <c t="n" r="E269">
-        <v>-33.9654</v>
-      </c>
-      <c t="n" r="F269">
-        <v>95.9515</v>
+        <v>19.0189</v>
       </c>
     </row>
     <row r="270">
       <c t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">NGD</t>
+          <t xml:space="preserve">GNC</t>
         </is>
       </c>
       <c t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. GNC KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C270">
-        <v>7.6195</v>
+        <v>-0.3505</v>
+      </c>
+      <c t="n" r="D270">
+        <v>-1.1257</v>
+      </c>
+      <c t="n" r="F270">
+        <v>-2.2681</v>
       </c>
     </row>
     <row r="271">
       <c t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">GNC</t>
+          <t xml:space="preserve">NIK</t>
         </is>
       </c>
       <c t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. GNC KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C271">
-        <v>-0.4167</v>
+        <v>-74.1998</v>
       </c>
       <c t="n" r="D271">
-        <v>-1.9636</v>
+        <v>-87.8869</v>
+      </c>
+      <c t="n" r="E271">
+        <v>-41.9080</v>
       </c>
       <c t="n" r="F271">
-        <v>-2.2215</v>
+        <v>136.8199</v>
       </c>
     </row>
     <row r="272">
       <c t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">NIK</t>
+          <t xml:space="preserve">NGR</t>
         </is>
       </c>
       <c t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C272">
-        <v>-71.7508</v>
-      </c>
-      <c t="n" r="D272">
-        <v>273.4087</v>
-      </c>
-      <c t="n" r="E272">
-        <v>-40.1570</v>
-      </c>
-      <c t="n" r="F272">
-        <v>157.9553</v>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. RİVA PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="273">
       <c t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">NGR</t>
+          <t xml:space="preserve">NGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. RİVA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">NGU</t>
+          <t xml:space="preserve">NBP</t>
         </is>
       </c>
       <c t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C274">
+        <v>-0.0727</v>
+      </c>
+      <c t="n" r="D274">
+        <v>-10.3956</v>
+      </c>
+      <c t="n" r="F274">
+        <v>-9.7137</v>
       </c>
     </row>
     <row r="275">
       <c t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">NBP</t>
+          <t xml:space="preserve">NP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C275">
-        <v>-0.0571</v>
-      </c>
-      <c t="n" r="D275">
-        <v>-10.0973</v>
-      </c>
-      <c t="n" r="F275">
-        <v>-9.7011</v>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="276">
       <c t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">NP4</t>
+          <t xml:space="preserve">NKN</t>
         </is>
       </c>
       <c t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C276">
+        <v>2.9690</v>
+      </c>
+      <c t="n" r="D276">
+        <v>-61.7160</v>
+      </c>
+      <c t="n" r="E276">
+        <v>-99.1385</v>
+      </c>
+      <c t="n" r="F276">
+        <v>-98.1794</v>
       </c>
     </row>
     <row r="277">
       <c t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">NKN</t>
+          <t xml:space="preserve">MAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C277">
-        <v>3.2579</v>
-      </c>
-      <c t="n" r="D277">
-        <v>-98.1557</v>
-      </c>
-      <c t="n" r="E277">
-        <v>-99.2458</v>
-      </c>
-      <c t="n" r="F277">
-        <v>-98.1850</v>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. MAANAA LEVENT PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="278">
       <c t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">MAA</t>
+          <t xml:space="preserve">NGM</t>
         </is>
       </c>
       <c t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. MAANAA LEVENT PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C278">
+        <v>-0.2988</v>
+      </c>
+      <c t="n" r="D278">
+        <v>0.9455</v>
+      </c>
+      <c t="n" r="E278">
+        <v>-97.8891</v>
+      </c>
+      <c t="n" r="F278">
+        <v>0.8311</v>
       </c>
     </row>
     <row r="279">
       <c t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">NGM</t>
+          <t xml:space="preserve">NBA</t>
         </is>
       </c>
       <c t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C279">
-        <v>0.5603</v>
+        <v>-29.3166</v>
       </c>
       <c t="n" r="D279">
-        <v>1.5849</v>
+        <v>-32.9216</v>
       </c>
       <c t="n" r="E279">
-        <v>-98.3569</v>
+        <v>1622.0389</v>
       </c>
       <c t="n" r="F279">
-        <v>1.7000</v>
+        <v>-33.0242</v>
       </c>
     </row>
     <row r="280">
       <c t="inlineStr" r="A280">
         <is>
-          <t xml:space="preserve">NBA</t>
+          <t xml:space="preserve">NP5</t>
         </is>
       </c>
       <c t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C280">
-        <v>-29.3663</v>
-      </c>
-      <c t="n" r="D280">
-        <v>-32.9681</v>
-      </c>
-      <c t="n" r="E280">
-        <v>1527.8121</v>
-      </c>
-      <c t="n" r="F280">
-        <v>-33.0232</v>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="281">
       <c t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">NP5</t>
+          <t xml:space="preserve">ND4</t>
         </is>
       </c>
       <c t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">ND4</t>
+          <t xml:space="preserve">NIP</t>
         </is>
       </c>
       <c t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C282">
+        <v>-0.5258</v>
+      </c>
+      <c t="n" r="D282">
+        <v>-29.8484</v>
+      </c>
+      <c t="n" r="E282">
+        <v>4930.0205</v>
+      </c>
+      <c t="n" r="F282">
+        <v>12086.5408</v>
       </c>
     </row>
     <row r="283">
       <c t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">NIP</t>
+          <t xml:space="preserve">NPO</t>
         </is>
       </c>
       <c t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C283">
-        <v>-0.5335</v>
+        <v>-0.0265</v>
       </c>
       <c t="n" r="D283">
-        <v>13581.9359</v>
-      </c>
-      <c t="n" r="E283">
-        <v>4758.2843</v>
+        <v>-0.0809</v>
       </c>
       <c t="n" r="F283">
-        <v>12095.5908</v>
+        <v>-0.0028</v>
       </c>
     </row>
     <row r="284">
       <c t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">NPO</t>
+          <t xml:space="preserve">NR3</t>
         </is>
       </c>
       <c t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C284">
-        <v>0.1092</v>
-      </c>
-      <c t="n" r="D284">
-        <v>0.0490</v>
-      </c>
-      <c t="n" r="F284">
-        <v>0.1352</v>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="285">
       <c t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">NR3</t>
+          <t xml:space="preserve">NU3</t>
         </is>
       </c>
       <c t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">NU3</t>
+          <t xml:space="preserve">OG4</t>
         </is>
       </c>
       <c t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">OG4</t>
+          <t xml:space="preserve">OGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C287">
+        <v>-74.0068</v>
       </c>
     </row>
     <row r="288">
       <c t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">OGG</t>
+          <t xml:space="preserve">OLN</t>
         </is>
       </c>
       <c t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C288">
-        <v>-72.1709</v>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="289">
       <c t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">OLN</t>
+          <t xml:space="preserve">FGY</t>
         </is>
       </c>
       <c t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C289">
+        <v>0.7451</v>
+      </c>
+      <c t="n" r="D289">
+        <v>2.7743</v>
+      </c>
+      <c t="n" r="E289">
+        <v>10.4732</v>
+      </c>
+      <c t="n" r="F289">
+        <v>3.1428</v>
       </c>
     </row>
     <row r="290">
       <c t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">FGY</t>
+          <t xml:space="preserve">BCP</t>
         </is>
       </c>
       <c t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C290">
-        <v>1.2730</v>
-      </c>
-      <c t="n" r="D290">
-        <v>3.1981</v>
-      </c>
-      <c t="n" r="E290">
-        <v>10.8352</v>
-      </c>
-      <c t="n" r="F290">
-        <v>3.4218</v>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="291">
       <c t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">BCP</t>
+          <t xml:space="preserve">GF4</t>
         </is>
       </c>
       <c t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C291">
+        <v>-25.4480</v>
+      </c>
+      <c t="n" r="D291">
+        <v>-56.6852</v>
+      </c>
+      <c t="n" r="E291">
+        <v>-56.6945</v>
+      </c>
+      <c t="n" r="F291">
+        <v>-56.2096</v>
       </c>
     </row>
     <row r="292">
       <c t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">GF4</t>
+          <t xml:space="preserve">OGK</t>
         </is>
       </c>
       <c t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C292">
-        <v>-21.8110</v>
-      </c>
-      <c t="n" r="D292">
-        <v>-53.9194</v>
-      </c>
-      <c t="n" r="E292">
-        <v>-54.1524</v>
-      </c>
-      <c t="n" r="F292">
-        <v>-53.6532</v>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. GENYAP KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="293">
@@ -7378,16 +7384,16 @@
         </is>
       </c>
       <c t="n" r="C298">
-        <v>3.6572</v>
+        <v>3.2768</v>
       </c>
       <c t="n" r="D298">
-        <v>10.3516</v>
+        <v>9.9987</v>
       </c>
       <c t="n" r="E298">
-        <v>20.8026</v>
+        <v>20.8834</v>
       </c>
       <c t="n" r="F298">
-        <v>11.2621</v>
+        <v>11.5281</v>
       </c>
     </row>
     <row r="299">
@@ -7402,13 +7408,13 @@
         </is>
       </c>
       <c t="n" r="C299">
-        <v>3.5391</v>
+        <v>3.1927</v>
       </c>
       <c t="n" r="D299">
-        <v>9.6448</v>
+        <v>9.2087</v>
       </c>
       <c t="n" r="F299">
-        <v>10.5643</v>
+        <v>10.7377</v>
       </c>
     </row>
     <row r="300">
@@ -7435,13 +7441,13 @@
         </is>
       </c>
       <c t="n" r="C301">
-        <v>4.0344</v>
+        <v>3.7484</v>
       </c>
       <c t="n" r="D301">
-        <v>11.7455</v>
+        <v>11.5326</v>
       </c>
       <c t="n" r="F301">
-        <v>12.7700</v>
+        <v>13.2541</v>
       </c>
     </row>
     <row r="302">
@@ -7456,7 +7462,7 @@
         </is>
       </c>
       <c t="n" r="C302">
-        <v>-52.9486</v>
+        <v>-69.9261</v>
       </c>
     </row>
     <row r="303">
@@ -7471,7 +7477,10 @@
         </is>
       </c>
       <c t="n" r="C303">
-        <v>0.0130</v>
+        <v>-0.0263</v>
+      </c>
+      <c t="n" r="D303">
+        <v>-1.2779</v>
       </c>
     </row>
     <row r="304">
@@ -7486,16 +7495,16 @@
         </is>
       </c>
       <c t="n" r="C304">
-        <v>1.1420</v>
+        <v>1.0004</v>
       </c>
       <c t="n" r="D304">
-        <v>6.0766</v>
+        <v>5.8596</v>
       </c>
       <c t="n" r="E304">
-        <v>14.7007</v>
+        <v>14.6163</v>
       </c>
       <c t="n" r="F304">
-        <v>6.6078</v>
+        <v>6.8044</v>
       </c>
     </row>
     <row r="305">
@@ -7534,16 +7543,16 @@
         </is>
       </c>
       <c t="n" r="C307">
-        <v>2.1091</v>
+        <v>1.6514</v>
       </c>
       <c t="n" r="D307">
-        <v>4.2738</v>
+        <v>3.7770</v>
       </c>
       <c t="n" r="E307">
-        <v>12.4584</v>
+        <v>12.0968</v>
       </c>
       <c t="n" r="F307">
-        <v>4.9620</v>
+        <v>4.9355</v>
       </c>
     </row>
     <row r="308">
@@ -7582,16 +7591,16 @@
         </is>
       </c>
       <c t="n" r="C310">
-        <v>-0.0819</v>
+        <v>-0.0870</v>
       </c>
       <c t="n" r="D310">
-        <v>-0.2161</v>
+        <v>-0.2220</v>
       </c>
       <c t="n" r="E310">
-        <v>0.6129</v>
+        <v>0.5997</v>
       </c>
       <c t="n" r="F310">
-        <v>-0.2203</v>
+        <v>-0.2439</v>
       </c>
     </row>
     <row r="311">
@@ -7630,13 +7639,13 @@
         </is>
       </c>
       <c t="n" r="C313">
-        <v>-0.0539</v>
+        <v>-0.0597</v>
       </c>
       <c t="n" r="D313">
-        <v>-0.1463</v>
+        <v>-0.1495</v>
       </c>
       <c t="n" r="F313">
-        <v>-0.1486</v>
+        <v>-0.1672</v>
       </c>
     </row>
     <row r="314">
@@ -7663,16 +7672,16 @@
         </is>
       </c>
       <c t="n" r="C315">
-        <v>-0.1568</v>
+        <v>-0.1593</v>
       </c>
       <c t="n" r="D315">
-        <v>-0.3505</v>
+        <v>-0.3507</v>
       </c>
       <c t="n" r="E315">
-        <v>3.0303</v>
+        <v>3.0292</v>
       </c>
       <c t="n" r="F315">
-        <v>-0.3678</v>
+        <v>-0.3798</v>
       </c>
     </row>
     <row r="316">
@@ -7687,7 +7696,7 @@
         </is>
       </c>
       <c t="n" r="C316">
-        <v>-0.1158</v>
+        <v>-0.1117</v>
       </c>
     </row>
     <row r="317">
@@ -7756,13 +7765,13 @@
         </is>
       </c>
       <c t="n" r="C321">
-        <v>-0.1236</v>
+        <v>-0.1428</v>
       </c>
       <c t="n" r="D321">
-        <v>-0.1531</v>
+        <v>-0.1618</v>
       </c>
       <c t="n" r="F321">
-        <v>-0.1432</v>
+        <v>-0.1473</v>
       </c>
     </row>
     <row r="322">
@@ -7780,40 +7789,52 @@
     <row r="323">
       <c t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">ZEP</t>
+          <t xml:space="preserve">TUC</t>
         </is>
       </c>
       <c t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. EMLAK KONUT GELİR PAYLAŞIMI BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C323">
-        <v>2.8372</v>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="324">
       <c t="inlineStr" r="A324">
         <is>
+          <t xml:space="preserve">ZEP</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B324">
+        <is>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. EMLAK KONUT GELİR PAYLAŞIMI BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C324">
+        <v>2.9535</v>
+      </c>
+    </row>
+    <row r="325">
+      <c t="inlineStr" r="A325">
+        <is>
           <t xml:space="preserve">YOR</t>
         </is>
       </c>
-      <c t="inlineStr" r="B324">
+      <c t="inlineStr" r="B325">
         <is>
           <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ORKİDE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
-      <c t="n" r="C324">
+      <c t="n" r="C325">
         <v>0.0000</v>
       </c>
-      <c t="n" r="D324">
-        <v>0.0212</v>
-      </c>
-      <c t="n" r="E324">
+      <c t="n" r="D325">
         <v>0.0000</v>
       </c>
-      <c t="n" r="F324">
-        <v>0.0000</v>
+      <c t="n" r="E325">
+        <v>-0.0212</v>
+      </c>
+      <c t="n" r="F325">
+        <v>-0.0212</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
@@ -280,22 +280,22 @@
         </is>
       </c>
       <c t="n" r="C3">
-        <v>49.9359</v>
+        <v>38.4340</v>
       </c>
       <c t="n" r="D3">
-        <v>661.1949</v>
+        <v>663.3135</v>
       </c>
       <c t="n" r="E3">
-        <v>687.6372</v>
+        <v>689.8545</v>
       </c>
       <c t="n" r="F3">
-        <v>655.7870</v>
+        <v>657.9327</v>
       </c>
       <c t="n" r="G3">
-        <v>612.8734</v>
+        <v>614.8973</v>
       </c>
       <c t="n" r="H3">
-        <v>1531.1610</v>
+        <v>1536.9019</v>
       </c>
     </row>
     <row r="4">
@@ -310,19 +310,19 @@
         </is>
       </c>
       <c t="n" r="C4">
-        <v>16.4462</v>
+        <v>16.3799</v>
       </c>
       <c t="n" r="D4">
-        <v>20.4276</v>
+        <v>20.4247</v>
       </c>
       <c t="n" r="E4">
-        <v>249.7680</v>
+        <v>250.0029</v>
       </c>
       <c t="n" r="F4">
-        <v>20.9596</v>
+        <v>20.9993</v>
       </c>
       <c t="n" r="G4">
-        <v>371.1857</v>
+        <v>371.3404</v>
       </c>
     </row>
     <row r="5">
@@ -337,19 +337,19 @@
         </is>
       </c>
       <c t="n" r="C5">
-        <v>0.8849</v>
+        <v>0.9151</v>
       </c>
       <c t="n" r="D5">
-        <v>3.2580</v>
+        <v>3.2844</v>
       </c>
       <c t="n" r="E5">
-        <v>27.7106</v>
+        <v>27.7233</v>
       </c>
       <c t="n" r="F5">
-        <v>3.3252</v>
+        <v>3.3581</v>
       </c>
       <c t="n" r="G5">
-        <v>363.6558</v>
+        <v>363.8036</v>
       </c>
     </row>
     <row r="6">
@@ -364,22 +364,22 @@
         </is>
       </c>
       <c t="n" r="C6">
-        <v>-0.4359</v>
+        <v>-0.4393</v>
       </c>
       <c t="n" r="D6">
-        <v>41.7351</v>
+        <v>41.6652</v>
       </c>
       <c t="n" r="E6">
-        <v>52.7421</v>
+        <v>52.7432</v>
       </c>
       <c t="n" r="F6">
-        <v>42.3060</v>
+        <v>42.2849</v>
       </c>
       <c t="n" r="G6">
-        <v>239.8058</v>
+        <v>239.7554</v>
       </c>
       <c t="n" r="H6">
-        <v>332.7346</v>
+        <v>332.6875</v>
       </c>
     </row>
     <row r="7">
@@ -394,22 +394,22 @@
         </is>
       </c>
       <c t="n" r="C7">
-        <v>-0.0191</v>
+        <v>-0.0184</v>
       </c>
       <c t="n" r="D7">
         <v>-0.0510</v>
       </c>
       <c t="n" r="E7">
-        <v>192.5052</v>
+        <v>192.5053</v>
       </c>
       <c t="n" r="F7">
-        <v>-0.0575</v>
+        <v>-0.0579</v>
       </c>
       <c t="n" r="G7">
-        <v>191.4246</v>
+        <v>191.4236</v>
       </c>
       <c t="n" r="H7">
-        <v>166578.3293</v>
+        <v>166601.9938</v>
       </c>
     </row>
     <row r="8">
@@ -424,19 +424,19 @@
         </is>
       </c>
       <c t="n" r="C8">
-        <v>-0.0426</v>
+        <v>-0.0171</v>
       </c>
       <c t="n" r="D8">
-        <v>3.9983</v>
+        <v>4.0120</v>
       </c>
       <c t="n" r="E8">
         <v>3.9832</v>
       </c>
       <c t="n" r="F8">
-        <v>4.0050</v>
+        <v>4.0194</v>
       </c>
       <c t="n" r="G8">
-        <v>152.6541</v>
+        <v>152.6891</v>
       </c>
     </row>
     <row r="9">
@@ -451,19 +451,19 @@
         </is>
       </c>
       <c t="n" r="C9">
-        <v>0.2508</v>
+        <v>0.2810</v>
       </c>
       <c t="n" r="D9">
-        <v>0.5845</v>
+        <v>0.5991</v>
       </c>
       <c t="n" r="E9">
-        <v>140.3441</v>
+        <v>140.3522</v>
       </c>
       <c t="n" r="F9">
-        <v>1.0586</v>
+        <v>1.0740</v>
       </c>
       <c t="n" r="G9">
-        <v>142.5827</v>
+        <v>142.6196</v>
       </c>
     </row>
     <row r="10">
@@ -478,19 +478,19 @@
         </is>
       </c>
       <c t="n" r="C10">
-        <v>1.1290</v>
+        <v>1.3181</v>
       </c>
       <c t="n" r="D10">
-        <v>5.1699</v>
+        <v>5.0691</v>
       </c>
       <c t="n" r="E10">
-        <v>23.8419</v>
+        <v>23.7338</v>
       </c>
       <c t="n" r="F10">
-        <v>5.5496</v>
+        <v>5.4665</v>
       </c>
       <c t="n" r="G10">
-        <v>108.6668</v>
+        <v>108.5025</v>
       </c>
     </row>
     <row r="11">
@@ -505,22 +505,22 @@
         </is>
       </c>
       <c t="n" r="C11">
-        <v>65.6671</v>
+        <v>65.7232</v>
       </c>
       <c t="n" r="D11">
-        <v>68.2342</v>
+        <v>68.2410</v>
       </c>
       <c t="n" r="E11">
-        <v>69.7102</v>
+        <v>69.7206</v>
       </c>
       <c t="n" r="F11">
-        <v>55.1024</v>
+        <v>55.1195</v>
       </c>
       <c t="n" r="G11">
-        <v>88.2986</v>
+        <v>88.3194</v>
       </c>
       <c t="n" r="H11">
-        <v>114.8671</v>
+        <v>114.8904</v>
       </c>
     </row>
     <row r="12">
@@ -535,25 +535,25 @@
         </is>
       </c>
       <c t="n" r="C12">
-        <v>1.4927</v>
+        <v>1.6796</v>
       </c>
       <c t="n" r="D12">
-        <v>33.4520</v>
+        <v>33.5616</v>
       </c>
       <c t="n" r="E12">
-        <v>76.4689</v>
+        <v>76.6123</v>
       </c>
       <c t="n" r="F12">
-        <v>33.4830</v>
+        <v>33.5952</v>
       </c>
       <c t="n" r="G12">
-        <v>82.3383</v>
+        <v>82.4916</v>
       </c>
       <c t="n" r="H12">
-        <v>298.4602</v>
+        <v>298.7604</v>
       </c>
       <c t="n" r="I12">
-        <v>1676.7474</v>
+        <v>1678.2107</v>
       </c>
     </row>
     <row r="13">
@@ -568,25 +568,25 @@
         </is>
       </c>
       <c t="n" r="C13">
-        <v>0.6043</v>
+        <v>0.2308</v>
       </c>
       <c t="n" r="D13">
-        <v>1.7998</v>
+        <v>1.4069</v>
       </c>
       <c t="n" r="E13">
-        <v>39.7712</v>
+        <v>38.9221</v>
       </c>
       <c t="n" r="F13">
-        <v>1.6346</v>
+        <v>1.2731</v>
       </c>
       <c t="n" r="G13">
-        <v>62.7995</v>
+        <v>62.2204</v>
       </c>
       <c t="n" r="H13">
-        <v>329.0871</v>
+        <v>327.5609</v>
       </c>
       <c t="n" r="I13">
-        <v>1097.6227</v>
+        <v>1093.3631</v>
       </c>
     </row>
     <row r="14">
@@ -601,76 +601,76 @@
         </is>
       </c>
       <c t="n" r="C14">
-        <v>-0.1946</v>
+        <v>-0.1905</v>
       </c>
       <c t="n" r="D14">
-        <v>-1.2518</v>
+        <v>-1.2714</v>
       </c>
       <c t="n" r="E14">
-        <v>20.0059</v>
+        <v>19.9762</v>
       </c>
       <c t="n" r="F14">
-        <v>-1.0347</v>
+        <v>-1.0368</v>
       </c>
       <c t="n" r="G14">
-        <v>61.6136</v>
+        <v>61.6102</v>
       </c>
       <c t="n" r="H14">
-        <v>700.9257</v>
+        <v>687.8717</v>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">AR9</t>
+          <t xml:space="preserve">TNG</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TUNA PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C15">
-        <v>-0.1210</v>
+        <v>3.5784</v>
       </c>
       <c t="n" r="D15">
-        <v>0.2645</v>
+        <v>10.2367</v>
       </c>
       <c t="n" r="E15">
-        <v>60.0007</v>
+        <v>27.7308</v>
       </c>
       <c t="n" r="F15">
-        <v>-4.4467</v>
+        <v>11.0058</v>
       </c>
       <c t="n" r="G15">
-        <v>58.5980</v>
+        <v>58.9444</v>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">TNG</t>
+          <t xml:space="preserve">AR9</t>
         </is>
       </c>
       <c t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TUNA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C16">
-        <v>3.4211</v>
+        <v>-0.1147</v>
       </c>
       <c t="n" r="D16">
-        <v>10.0683</v>
+        <v>0.2650</v>
       </c>
       <c t="n" r="E16">
-        <v>27.8146</v>
+        <v>60.0181</v>
       </c>
       <c t="n" r="F16">
-        <v>10.7209</v>
+        <v>-4.4489</v>
       </c>
       <c t="n" r="G16">
-        <v>58.5365</v>
+        <v>58.5944</v>
       </c>
     </row>
     <row r="17">
@@ -685,19 +685,19 @@
         </is>
       </c>
       <c t="n" r="C17">
-        <v>3.1567</v>
+        <v>3.3634</v>
       </c>
       <c t="n" r="D17">
-        <v>13.4527</v>
+        <v>13.7107</v>
       </c>
       <c t="n" r="E17">
-        <v>26.6534</v>
+        <v>26.6098</v>
       </c>
       <c t="n" r="F17">
-        <v>17.5595</v>
+        <v>17.8915</v>
       </c>
       <c t="n" r="G17">
-        <v>57.5816</v>
+        <v>58.0267</v>
       </c>
     </row>
     <row r="18">
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c t="n" r="C18">
-        <v>0.7382</v>
+        <v>0.7355</v>
       </c>
       <c t="n" r="D18">
-        <v>1.9294</v>
+        <v>1.9256</v>
       </c>
       <c t="n" r="E18">
-        <v>51.3749</v>
+        <v>51.3542</v>
       </c>
       <c t="n" r="F18">
-        <v>48.1724</v>
+        <v>48.1720</v>
       </c>
       <c t="n" r="G18">
-        <v>57.0553</v>
+        <v>57.0549</v>
       </c>
       <c t="n" r="H18">
-        <v>463.8822</v>
+        <v>463.6040</v>
       </c>
     </row>
     <row r="19">
@@ -742,19 +742,19 @@
         </is>
       </c>
       <c t="n" r="C19">
-        <v>3.3717</v>
+        <v>3.6296</v>
       </c>
       <c t="n" r="D19">
-        <v>10.1037</v>
+        <v>10.3709</v>
       </c>
       <c t="n" r="E19">
-        <v>22.2075</v>
+        <v>22.2055</v>
       </c>
       <c t="n" r="F19">
-        <v>11.3425</v>
+        <v>11.7386</v>
       </c>
       <c t="n" r="G19">
-        <v>55.7589</v>
+        <v>56.3131</v>
       </c>
     </row>
     <row r="20">
@@ -769,76 +769,76 @@
         </is>
       </c>
       <c t="n" r="C20">
-        <v>3.3713</v>
+        <v>3.6293</v>
       </c>
       <c t="n" r="D20">
-        <v>10.1026</v>
+        <v>10.3698</v>
       </c>
       <c t="n" r="E20">
-        <v>22.2050</v>
+        <v>22.2029</v>
       </c>
       <c t="n" r="F20">
-        <v>11.3413</v>
+        <v>11.7374</v>
       </c>
       <c t="n" r="G20">
-        <v>55.7510</v>
+        <v>56.3051</v>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">OGC</t>
+          <t xml:space="preserve">BRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÇATI KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C21">
-        <v>0.2314</v>
+        <v>5.8091</v>
       </c>
       <c t="n" r="D21">
-        <v>0.7925</v>
+        <v>23.5889</v>
       </c>
       <c t="n" r="E21">
-        <v>54.7421</v>
+        <v>28.0627</v>
       </c>
       <c t="n" r="F21">
-        <v>0.8745</v>
+        <v>29.2276</v>
       </c>
       <c t="n" r="G21">
-        <v>55.1414</v>
-      </c>
-      <c t="n" r="H21">
-        <v>410.1936</v>
+        <v>55.3558</v>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">BRE</t>
+          <t xml:space="preserve">OGC</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÇATI KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C22">
-        <v>5.6688</v>
+        <v>0.2539</v>
       </c>
       <c t="n" r="D22">
-        <v>23.4188</v>
+        <v>0.8036</v>
       </c>
       <c t="n" r="E22">
-        <v>27.8396</v>
+        <v>54.7589</v>
       </c>
       <c t="n" r="F22">
-        <v>29.0142</v>
+        <v>0.8867</v>
       </c>
       <c t="n" r="G22">
-        <v>55.0993</v>
+        <v>55.1602</v>
+      </c>
+      <c t="n" r="H22">
+        <v>410.2554</v>
       </c>
     </row>
     <row r="23">
@@ -853,19 +853,19 @@
         </is>
       </c>
       <c t="n" r="C23">
-        <v>-0.1234</v>
+        <v>-0.0454</v>
       </c>
       <c t="n" r="D23">
-        <v>6.4031</v>
+        <v>6.4483</v>
       </c>
       <c t="n" r="E23">
-        <v>34.7071</v>
+        <v>34.7521</v>
       </c>
       <c t="n" r="F23">
-        <v>6.7104</v>
+        <v>6.7809</v>
       </c>
       <c t="n" r="G23">
-        <v>54.7889</v>
+        <v>54.8913</v>
       </c>
     </row>
     <row r="24">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c t="n" r="C24">
-        <v>-0.1976</v>
+        <v>-0.1975</v>
       </c>
       <c t="n" r="D24">
-        <v>-0.2278</v>
+        <v>-0.2277</v>
       </c>
       <c t="n" r="E24">
-        <v>55.3964</v>
+        <v>55.3956</v>
       </c>
       <c t="n" r="F24">
-        <v>-0.2279</v>
+        <v>-0.2277</v>
       </c>
       <c t="n" r="G24">
-        <v>54.4182</v>
+        <v>54.4186</v>
       </c>
       <c t="n" r="H24">
-        <v>172.5458</v>
+        <v>172.5429</v>
       </c>
     </row>
     <row r="25">
@@ -910,19 +910,19 @@
         </is>
       </c>
       <c t="n" r="C25">
-        <v>3.9215</v>
+        <v>4.0431</v>
       </c>
       <c t="n" r="D25">
-        <v>10.2996</v>
+        <v>9.8262</v>
       </c>
       <c t="n" r="E25">
-        <v>23.4381</v>
+        <v>22.5906</v>
       </c>
       <c t="n" r="F25">
-        <v>14.4072</v>
+        <v>13.9823</v>
       </c>
       <c t="n" r="G25">
-        <v>53.7421</v>
+        <v>53.1711</v>
       </c>
     </row>
     <row r="26">
@@ -937,25 +937,25 @@
         </is>
       </c>
       <c t="n" r="C26">
-        <v>-0.3196</v>
+        <v>-0.2483</v>
       </c>
       <c t="n" r="D26">
-        <v>-1.4485</v>
+        <v>-1.4530</v>
       </c>
       <c t="n" r="E26">
-        <v>28.4755</v>
+        <v>28.4774</v>
       </c>
       <c t="n" r="F26">
-        <v>-1.6782</v>
+        <v>-1.6888</v>
       </c>
       <c t="n" r="G26">
-        <v>49.0218</v>
+        <v>49.0056</v>
       </c>
       <c t="n" r="H26">
-        <v>168.1694</v>
+        <v>168.1622</v>
       </c>
       <c t="n" r="I26">
-        <v>1143.9352</v>
+        <v>1143.8004</v>
       </c>
     </row>
     <row r="27">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c t="n" r="C27">
-        <v>5.2464</v>
+        <v>5.2062</v>
       </c>
       <c t="n" r="D27">
-        <v>12.1702</v>
+        <v>12.1777</v>
       </c>
       <c t="n" r="E27">
-        <v>21.5104</v>
+        <v>21.4912</v>
       </c>
       <c t="n" r="F27">
-        <v>13.2347</v>
+        <v>13.3428</v>
       </c>
       <c t="n" r="G27">
-        <v>48.7624</v>
+        <v>48.9044</v>
       </c>
     </row>
     <row r="28">
@@ -997,25 +997,25 @@
         </is>
       </c>
       <c t="n" r="C28">
-        <v>-0.3231</v>
+        <v>-0.3173</v>
       </c>
       <c t="n" r="D28">
-        <v>-0.4379</v>
+        <v>-0.4466</v>
       </c>
       <c t="n" r="E28">
-        <v>16.0229</v>
+        <v>16.0231</v>
       </c>
       <c t="n" r="F28">
-        <v>-0.5905</v>
+        <v>-0.6048</v>
       </c>
       <c t="n" r="G28">
-        <v>48.0517</v>
+        <v>48.0304</v>
       </c>
       <c t="n" r="H28">
-        <v>196.7674</v>
+        <v>196.7634</v>
       </c>
       <c t="n" r="I28">
-        <v>1322.8794</v>
+        <v>1322.6747</v>
       </c>
     </row>
     <row r="29">
@@ -1030,22 +1030,22 @@
         </is>
       </c>
       <c t="n" r="C29">
-        <v>0.3521</v>
+        <v>0.4478</v>
       </c>
       <c t="n" r="D29">
-        <v>6.3392</v>
+        <v>6.3322</v>
       </c>
       <c t="n" r="E29">
-        <v>43.8700</v>
+        <v>43.8113</v>
       </c>
       <c t="n" r="F29">
-        <v>5.9540</v>
+        <v>5.9610</v>
       </c>
       <c t="n" r="G29">
-        <v>45.3101</v>
+        <v>45.3198</v>
       </c>
       <c t="n" r="H29">
-        <v>462.0709</v>
+        <v>462.0295</v>
       </c>
     </row>
     <row r="30">
@@ -1060,19 +1060,19 @@
         </is>
       </c>
       <c t="n" r="C30">
-        <v>2.8684</v>
+        <v>3.1266</v>
       </c>
       <c t="n" r="D30">
-        <v>8.6006</v>
+        <v>8.8385</v>
       </c>
       <c t="n" r="E30">
-        <v>19.2092</v>
+        <v>19.1955</v>
       </c>
       <c t="n" r="F30">
-        <v>9.8802</v>
+        <v>10.2256</v>
       </c>
       <c t="n" r="G30">
-        <v>44.1275</v>
+        <v>44.5805</v>
       </c>
     </row>
     <row r="31">
@@ -1087,19 +1087,19 @@
         </is>
       </c>
       <c t="n" r="C31">
-        <v>-0.1825</v>
+        <v>-1.0655</v>
       </c>
       <c t="n" r="D31">
-        <v>0.4411</v>
+        <v>0.4781</v>
       </c>
       <c t="n" r="E31">
-        <v>29.4093</v>
+        <v>29.4101</v>
       </c>
       <c t="n" r="F31">
-        <v>1.5365</v>
+        <v>1.5859</v>
       </c>
       <c t="n" r="G31">
-        <v>44.0946</v>
+        <v>44.1648</v>
       </c>
     </row>
     <row r="32">
@@ -1114,19 +1114,19 @@
         </is>
       </c>
       <c t="n" r="C32">
-        <v>1.9259</v>
+        <v>2.0891</v>
       </c>
       <c t="n" r="D32">
-        <v>4.8246</v>
+        <v>4.5820</v>
       </c>
       <c t="n" r="E32">
-        <v>23.9574</v>
+        <v>24.1203</v>
       </c>
       <c t="n" r="F32">
-        <v>8.6174</v>
+        <v>8.6367</v>
       </c>
       <c t="n" r="G32">
-        <v>42.2838</v>
+        <v>42.3091</v>
       </c>
     </row>
     <row r="33">
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c t="n" r="C33">
-        <v>-0.0189</v>
+        <v>-0.0187</v>
       </c>
       <c t="n" r="D33">
-        <v>0.1572</v>
+        <v>0.1757</v>
       </c>
       <c t="n" r="E33">
-        <v>27.1041</v>
+        <v>27.2619</v>
       </c>
       <c t="n" r="F33">
-        <v>0.3329</v>
+        <v>0.3228</v>
       </c>
       <c t="n" r="G33">
-        <v>41.7864</v>
+        <v>41.7720</v>
       </c>
     </row>
     <row r="34">
@@ -1168,22 +1168,22 @@
         </is>
       </c>
       <c t="n" r="C34">
-        <v>0.1386</v>
+        <v>0.1616</v>
       </c>
       <c t="n" r="D34">
-        <v>0.5258</v>
+        <v>0.5329</v>
       </c>
       <c t="n" r="E34">
-        <v>38.6575</v>
+        <v>38.6483</v>
       </c>
       <c t="n" r="F34">
-        <v>0.7297</v>
+        <v>0.7344</v>
       </c>
       <c t="n" r="G34">
-        <v>41.7390</v>
+        <v>41.7455</v>
       </c>
       <c t="n" r="H34">
-        <v>241.7662</v>
+        <v>241.8217</v>
       </c>
     </row>
     <row r="35">
@@ -1198,22 +1198,25 @@
         </is>
       </c>
       <c t="n" r="C35">
-        <v>-0.0890</v>
+        <v>-0.0775</v>
       </c>
       <c t="n" r="D35">
-        <v>-0.3856</v>
+        <v>-0.3774</v>
       </c>
       <c t="n" r="E35">
-        <v>42.2618</v>
+        <v>42.2755</v>
       </c>
       <c t="n" r="F35">
-        <v>-0.4969</v>
+        <v>-0.4977</v>
       </c>
       <c t="n" r="G35">
-        <v>41.6646</v>
+        <v>41.6633</v>
       </c>
       <c t="n" r="H35">
-        <v>212.8836</v>
+        <v>212.7006</v>
+      </c>
+      <c t="n" r="I35">
+        <v>720.0143</v>
       </c>
     </row>
     <row r="36">
@@ -1228,22 +1231,22 @@
         </is>
       </c>
       <c t="n" r="C36">
-        <v>0.1453</v>
+        <v>0.1600</v>
       </c>
       <c t="n" r="D36">
-        <v>0.0139</v>
+        <v>0.0142</v>
       </c>
       <c t="n" r="E36">
-        <v>41.1440</v>
+        <v>41.1454</v>
       </c>
       <c t="n" r="F36">
-        <v>0.3037</v>
+        <v>0.2981</v>
       </c>
       <c t="n" r="G36">
-        <v>41.4705</v>
+        <v>41.4626</v>
       </c>
       <c t="n" r="H36">
-        <v>251.8717</v>
+        <v>251.8922</v>
       </c>
     </row>
     <row r="37">
@@ -1258,25 +1261,25 @@
         </is>
       </c>
       <c t="n" r="C37">
-        <v>0.5334</v>
+        <v>0.5399</v>
       </c>
       <c t="n" r="D37">
-        <v>1.5264</v>
+        <v>1.5438</v>
       </c>
       <c t="n" r="E37">
-        <v>28.9773</v>
+        <v>28.9772</v>
       </c>
       <c t="n" r="F37">
-        <v>1.4664</v>
+        <v>1.4951</v>
       </c>
       <c t="n" r="G37">
-        <v>40.7948</v>
+        <v>40.8346</v>
       </c>
       <c t="n" r="H37">
-        <v>172.1344</v>
+        <v>172.2116</v>
       </c>
       <c t="n" r="I37">
-        <v>400.2252</v>
+        <v>400.3666</v>
       </c>
     </row>
     <row r="38">
@@ -1291,25 +1294,25 @@
         </is>
       </c>
       <c t="n" r="C38">
-        <v>0.4770</v>
+        <v>0.4574</v>
       </c>
       <c t="n" r="D38">
-        <v>1.7306</v>
+        <v>1.7529</v>
       </c>
       <c t="n" r="E38">
-        <v>16.3147</v>
+        <v>16.2042</v>
       </c>
       <c t="n" r="F38">
-        <v>1.9858</v>
+        <v>2.0160</v>
       </c>
       <c t="n" r="G38">
-        <v>40.2224</v>
+        <v>40.2639</v>
       </c>
       <c t="n" r="H38">
-        <v>295.3469</v>
+        <v>295.4192</v>
       </c>
       <c t="n" r="I38">
-        <v>916.1899</v>
+        <v>916.3664</v>
       </c>
     </row>
     <row r="39">
@@ -1324,25 +1327,25 @@
         </is>
       </c>
       <c t="n" r="C39">
-        <v>1.2115</v>
+        <v>1.4009</v>
       </c>
       <c t="n" r="D39">
-        <v>4.1586</v>
+        <v>4.3621</v>
       </c>
       <c t="n" r="E39">
-        <v>14.3031</v>
+        <v>14.4794</v>
       </c>
       <c t="n" r="F39">
-        <v>3.1722</v>
+        <v>3.4006</v>
       </c>
       <c t="n" r="G39">
-        <v>39.4973</v>
+        <v>39.8062</v>
       </c>
       <c t="n" r="H39">
-        <v>140.8770</v>
+        <v>141.3387</v>
       </c>
       <c t="n" r="I39">
-        <v>259.3235</v>
+        <v>260.1093</v>
       </c>
     </row>
     <row r="40">
@@ -1357,19 +1360,19 @@
         </is>
       </c>
       <c t="n" r="C40">
-        <v>0.6747</v>
+        <v>0.6885</v>
       </c>
       <c t="n" r="D40">
-        <v>2.0175</v>
+        <v>2.0327</v>
       </c>
       <c t="n" r="E40">
-        <v>31.1682</v>
+        <v>31.1879</v>
       </c>
       <c t="n" r="F40">
-        <v>2.6449</v>
+        <v>2.6604</v>
       </c>
       <c t="n" r="G40">
-        <v>38.7740</v>
+        <v>38.7950</v>
       </c>
     </row>
     <row r="41">
@@ -1384,25 +1387,25 @@
         </is>
       </c>
       <c t="n" r="C41">
-        <v>-1.2939</v>
+        <v>-1.2829</v>
       </c>
       <c t="n" r="D41">
-        <v>-0.9271</v>
+        <v>-0.9274</v>
       </c>
       <c t="n" r="E41">
-        <v>23.8465</v>
+        <v>23.8423</v>
       </c>
       <c t="n" r="F41">
-        <v>-0.5077</v>
+        <v>-0.5135</v>
       </c>
       <c t="n" r="G41">
-        <v>38.3819</v>
+        <v>38.3739</v>
       </c>
       <c t="n" r="H41">
-        <v>326.7809</v>
+        <v>326.7755</v>
       </c>
       <c t="n" r="I41">
-        <v>713.3477</v>
+        <v>713.3006</v>
       </c>
     </row>
     <row r="42">
@@ -1417,25 +1420,25 @@
         </is>
       </c>
       <c t="n" r="C42">
-        <v>1.4526</v>
+        <v>1.3434</v>
       </c>
       <c t="n" r="D42">
-        <v>4.1690</v>
+        <v>4.1728</v>
       </c>
       <c t="n" r="E42">
-        <v>13.8739</v>
+        <v>13.8710</v>
       </c>
       <c t="n" r="F42">
-        <v>4.6557</v>
+        <v>4.7038</v>
       </c>
       <c t="n" r="G42">
-        <v>37.3984</v>
+        <v>37.4616</v>
       </c>
       <c t="n" r="H42">
-        <v>179.3917</v>
+        <v>179.4454</v>
       </c>
       <c t="n" r="I42">
-        <v>415.2467</v>
+        <v>415.3460</v>
       </c>
     </row>
     <row r="43">
@@ -1450,82 +1453,82 @@
         </is>
       </c>
       <c t="n" r="C43">
-        <v>-0.6746</v>
+        <v>-0.6070</v>
       </c>
       <c t="n" r="D43">
-        <v>3.9166</v>
+        <v>3.9485</v>
       </c>
       <c t="n" r="E43">
-        <v>32.8264</v>
+        <v>32.8791</v>
       </c>
       <c t="n" r="F43">
-        <v>11.6476</v>
+        <v>11.6847</v>
       </c>
       <c t="n" r="G43">
-        <v>37.1655</v>
+        <v>37.2111</v>
       </c>
       <c t="n" r="H43">
-        <v>828.1794</v>
+        <v>827.9473</v>
       </c>
     </row>
     <row r="44">
       <c t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">RP1</t>
+          <t xml:space="preserve">DIG</t>
         </is>
       </c>
       <c t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NOVADA URFA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C44">
-        <v>-0.0777</v>
+        <v>2.6957</v>
       </c>
       <c t="n" r="D44">
-        <v>-0.4225</v>
+        <v>7.0236</v>
       </c>
       <c t="n" r="E44">
-        <v>32.6603</v>
+        <v>15.3244</v>
       </c>
       <c t="n" r="F44">
-        <v>-0.4729</v>
+        <v>8.1805</v>
       </c>
       <c t="n" r="G44">
-        <v>35.5507</v>
-      </c>
-      <c t="n" r="H44">
-        <v>243.3309</v>
-      </c>
-      <c t="n" r="I44">
-        <v>921.6440</v>
+        <v>35.8039</v>
       </c>
     </row>
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">DIG</t>
+          <t xml:space="preserve">RP1</t>
         </is>
       </c>
       <c t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NOVADA URFA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C45">
-        <v>2.3958</v>
+        <v>-0.0768</v>
       </c>
       <c t="n" r="D45">
-        <v>6.7762</v>
+        <v>-0.4222</v>
       </c>
       <c t="n" r="E45">
-        <v>15.3126</v>
+        <v>32.6745</v>
       </c>
       <c t="n" r="F45">
-        <v>7.8448</v>
+        <v>-0.4733</v>
       </c>
       <c t="n" r="G45">
-        <v>35.3824</v>
+        <v>35.5502</v>
+      </c>
+      <c t="n" r="H45">
+        <v>243.3331</v>
+      </c>
+      <c t="n" r="I45">
+        <v>921.6445</v>
       </c>
     </row>
     <row r="46">
@@ -1540,22 +1543,22 @@
         </is>
       </c>
       <c t="n" r="C46">
-        <v>0.4003</v>
+        <v>0.4670</v>
       </c>
       <c t="n" r="D46">
-        <v>1.7875</v>
+        <v>1.8009</v>
       </c>
       <c t="n" r="E46">
-        <v>26.8353</v>
+        <v>26.9693</v>
       </c>
       <c t="n" r="F46">
-        <v>2.0651</v>
+        <v>2.1417</v>
       </c>
       <c t="n" r="G46">
-        <v>34.7918</v>
+        <v>34.8928</v>
       </c>
       <c t="n" r="H46">
-        <v>574.4833</v>
+        <v>575.0190</v>
       </c>
     </row>
     <row r="47">
@@ -1570,103 +1573,103 @@
         </is>
       </c>
       <c t="n" r="C47">
-        <v>-0.0257</v>
+        <v>-0.0219</v>
       </c>
       <c t="n" r="D47">
-        <v>-0.1105</v>
+        <v>-0.1092</v>
       </c>
       <c t="n" r="E47">
-        <v>34.0455</v>
+        <v>34.0435</v>
       </c>
       <c t="n" r="F47">
-        <v>-0.1146</v>
+        <v>-0.1137</v>
       </c>
       <c t="n" r="G47">
-        <v>34.5368</v>
+        <v>34.5380</v>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">FNR</t>
+          <t xml:space="preserve">FNI</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C48">
-        <v>3.0868</v>
+        <v>0.5279</v>
       </c>
       <c t="n" r="D48">
-        <v>3.4783</v>
+        <v>1.5275</v>
       </c>
       <c t="n" r="E48">
-        <v>14.8393</v>
+        <v>28.4913</v>
       </c>
       <c t="n" r="F48">
-        <v>5.5444</v>
+        <v>1.5120</v>
       </c>
       <c t="n" r="G48">
-        <v>34.3918</v>
+        <v>33.8552</v>
       </c>
     </row>
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">FNI</t>
+          <t xml:space="preserve">NG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C49">
-        <v>0.5217</v>
+        <v>0.2696</v>
       </c>
       <c t="n" r="D49">
-        <v>1.5230</v>
+        <v>0.7660</v>
       </c>
       <c t="n" r="E49">
-        <v>28.5031</v>
+        <v>31.5198</v>
       </c>
       <c t="n" r="F49">
-        <v>1.5079</v>
+        <v>1.1087</v>
       </c>
       <c t="n" r="G49">
-        <v>33.8499</v>
+        <v>33.0085</v>
+      </c>
+      <c t="n" r="H49">
+        <v>317.2330</v>
       </c>
     </row>
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">NG2</t>
+          <t xml:space="preserve">FNR</t>
         </is>
       </c>
       <c t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C50">
-        <v>0.2614</v>
+        <v>1.7201</v>
       </c>
       <c t="n" r="D50">
-        <v>0.7627</v>
+        <v>-2.0453</v>
       </c>
       <c t="n" r="E50">
-        <v>31.5167</v>
+        <v>14.0621</v>
       </c>
       <c t="n" r="F50">
-        <v>1.1074</v>
+        <v>4.4160</v>
       </c>
       <c t="n" r="G50">
-        <v>33.0069</v>
-      </c>
-      <c t="n" r="H50">
-        <v>317.8006</v>
+        <v>32.9549</v>
       </c>
     </row>
     <row r="51">
@@ -1681,82 +1684,82 @@
         </is>
       </c>
       <c t="n" r="C51">
-        <v>0.4742</v>
+        <v>0.6586</v>
       </c>
       <c t="n" r="D51">
-        <v>0.3355</v>
+        <v>0.4951</v>
       </c>
       <c t="n" r="E51">
-        <v>10.8474</v>
+        <v>10.8472</v>
       </c>
       <c t="n" r="F51">
-        <v>0.3311</v>
+        <v>0.3318</v>
       </c>
       <c t="n" r="G51">
-        <v>32.5821</v>
+        <v>32.5829</v>
       </c>
       <c t="n" r="H51">
-        <v>303.4796</v>
+        <v>303.4834</v>
       </c>
     </row>
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">AZ3</t>
+          <t xml:space="preserve">HRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C52">
-        <v>-0.0083</v>
+        <v>2.5807</v>
       </c>
       <c t="n" r="D52">
-        <v>-0.2344</v>
+        <v>4.9545</v>
       </c>
       <c t="n" r="E52">
-        <v>32.8103</v>
+        <v>12.4221</v>
       </c>
       <c t="n" r="F52">
-        <v>-2.9934</v>
+        <v>6.4993</v>
       </c>
       <c t="n" r="G52">
-        <v>31.6646</v>
-      </c>
-      <c t="n" r="H52">
-        <v>214.8461</v>
-      </c>
-      <c t="n" r="I52">
-        <v>679.5801</v>
+        <v>31.7550</v>
       </c>
     </row>
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">HRE</t>
+          <t xml:space="preserve">AZ3</t>
         </is>
       </c>
       <c t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C53">
-        <v>2.4393</v>
+        <v>-0.0083</v>
       </c>
       <c t="n" r="D53">
-        <v>4.8179</v>
+        <v>-0.2317</v>
       </c>
       <c t="n" r="E53">
-        <v>12.4497</v>
+        <v>32.8627</v>
       </c>
       <c t="n" r="F53">
-        <v>6.2846</v>
+        <v>-2.9933</v>
       </c>
       <c t="n" r="G53">
-        <v>31.4894</v>
+        <v>31.6647</v>
+      </c>
+      <c t="n" r="H53">
+        <v>214.8526</v>
+      </c>
+      <c t="n" r="I53">
+        <v>679.5806</v>
       </c>
     </row>
     <row r="54">
@@ -1771,19 +1774,19 @@
         </is>
       </c>
       <c t="n" r="C54">
-        <v>0.0787</v>
+        <v>0.1077</v>
       </c>
       <c t="n" r="D54">
-        <v>0.1866</v>
+        <v>0.2043</v>
       </c>
       <c t="n" r="E54">
-        <v>5.8729</v>
+        <v>5.5427</v>
       </c>
       <c t="n" r="F54">
-        <v>0.2096</v>
+        <v>0.2304</v>
       </c>
       <c t="n" r="G54">
-        <v>31.3265</v>
+        <v>31.3538</v>
       </c>
     </row>
     <row r="55">
@@ -1798,25 +1801,25 @@
         </is>
       </c>
       <c t="n" r="C55">
-        <v>0.1641</v>
+        <v>0.1846</v>
       </c>
       <c t="n" r="D55">
-        <v>-0.5592</v>
+        <v>-0.5688</v>
       </c>
       <c t="n" r="E55">
-        <v>31.1447</v>
+        <v>31.1520</v>
       </c>
       <c t="n" r="F55">
-        <v>0.0639</v>
+        <v>0.0622</v>
       </c>
       <c t="n" r="G55">
-        <v>31.2762</v>
+        <v>31.2739</v>
       </c>
       <c t="n" r="H55">
-        <v>685.0407</v>
+        <v>684.3063</v>
       </c>
       <c t="n" r="I55">
-        <v>1774.5406</v>
+        <v>1774.4790</v>
       </c>
     </row>
     <row r="56">
@@ -1831,79 +1834,79 @@
         </is>
       </c>
       <c t="n" r="C56">
-        <v>-0.0208</v>
+        <v>-0.0013</v>
       </c>
       <c t="n" r="D56">
-        <v>0.2541</v>
+        <v>0.2616</v>
       </c>
       <c t="n" r="E56">
-        <v>29.1911</v>
+        <v>29.1956</v>
       </c>
       <c t="n" r="F56">
-        <v>0.2589</v>
+        <v>0.2688</v>
       </c>
       <c t="n" r="G56">
-        <v>31.2107</v>
+        <v>31.2236</v>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">TUG</t>
+          <t xml:space="preserve">ITG</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. QUASAR İSTANBUL TİCARİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C57">
-        <v>1.6260</v>
+        <v>0.2059</v>
       </c>
       <c t="n" r="D57">
-        <v>3.0139</v>
+        <v>1.0854</v>
       </c>
       <c t="n" r="E57">
-        <v>39.1982</v>
+        <v>12.9936</v>
       </c>
       <c t="n" r="F57">
-        <v>3.6239</v>
+        <v>1.3368</v>
       </c>
       <c t="n" r="G57">
-        <v>30.9880</v>
+        <v>30.9060</v>
+      </c>
+      <c t="n" r="H57">
+        <v>156.3226</v>
+      </c>
+      <c t="n" r="I57">
+        <v>486.1387</v>
       </c>
     </row>
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">ITG</t>
+          <t xml:space="preserve">TUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. QUASAR İSTANBUL TİCARİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C58">
-        <v>0.3237</v>
+        <v>1.5818</v>
       </c>
       <c t="n" r="D58">
-        <v>1.0788</v>
+        <v>2.7771</v>
       </c>
       <c t="n" r="E58">
-        <v>12.9920</v>
+        <v>39.1651</v>
       </c>
       <c t="n" r="F58">
-        <v>1.3296</v>
+        <v>3.4344</v>
       </c>
       <c t="n" r="G58">
-        <v>30.8967</v>
-      </c>
-      <c t="n" r="H58">
-        <v>156.3085</v>
-      </c>
-      <c t="n" r="I58">
-        <v>486.0769</v>
+        <v>30.7485</v>
       </c>
     </row>
     <row r="59">
@@ -1918,19 +1921,19 @@
         </is>
       </c>
       <c t="n" r="C59">
-        <v>1.4696</v>
+        <v>1.4539</v>
       </c>
       <c t="n" r="D59">
-        <v>3.6972</v>
+        <v>3.8069</v>
       </c>
       <c t="n" r="E59">
-        <v>12.7576</v>
+        <v>12.8428</v>
       </c>
       <c t="n" r="F59">
-        <v>3.6799</v>
+        <v>3.8051</v>
       </c>
       <c t="n" r="G59">
-        <v>30.5078</v>
+        <v>30.6653</v>
       </c>
     </row>
     <row r="60">
@@ -1945,25 +1948,25 @@
         </is>
       </c>
       <c t="n" r="C60">
-        <v>0.0588</v>
+        <v>0.0753</v>
       </c>
       <c t="n" r="D60">
-        <v>0.8659</v>
+        <v>0.8635</v>
       </c>
       <c t="n" r="E60">
-        <v>27.7110</v>
+        <v>27.7429</v>
       </c>
       <c t="n" r="F60">
-        <v>-5.9663</v>
+        <v>-5.9617</v>
       </c>
       <c t="n" r="G60">
-        <v>30.0445</v>
+        <v>30.0509</v>
       </c>
       <c t="n" r="H60">
-        <v>172.0671</v>
+        <v>172.0561</v>
       </c>
       <c t="n" r="I60">
-        <v>832.2498</v>
+        <v>832.2956</v>
       </c>
     </row>
     <row r="61">
@@ -1978,19 +1981,19 @@
         </is>
       </c>
       <c t="n" r="C61">
-        <v>0.2180</v>
+        <v>0.2290</v>
       </c>
       <c t="n" r="D61">
-        <v>0.7603</v>
+        <v>0.7692</v>
       </c>
       <c t="n" r="E61">
-        <v>27.8818</v>
+        <v>27.8864</v>
       </c>
       <c t="n" r="F61">
-        <v>1.0508</v>
+        <v>1.0611</v>
       </c>
       <c t="n" r="G61">
-        <v>29.6396</v>
+        <v>29.6529</v>
       </c>
     </row>
     <row r="62">
@@ -2005,19 +2008,19 @@
         </is>
       </c>
       <c t="n" r="C62">
-        <v>-1.5663</v>
+        <v>-1.3007</v>
       </c>
       <c t="n" r="D62">
-        <v>5.4630</v>
+        <v>5.0651</v>
       </c>
       <c t="n" r="E62">
-        <v>16.6228</v>
+        <v>16.5245</v>
       </c>
       <c t="n" r="F62">
-        <v>5.9295</v>
+        <v>6.1327</v>
       </c>
       <c t="n" r="G62">
-        <v>29.3010</v>
+        <v>29.5491</v>
       </c>
     </row>
     <row r="63">
@@ -2032,25 +2035,25 @@
         </is>
       </c>
       <c t="n" r="C63">
-        <v>0.1124</v>
+        <v>0.1226</v>
       </c>
       <c t="n" r="D63">
-        <v>0.2692</v>
+        <v>0.2796</v>
       </c>
       <c t="n" r="E63">
-        <v>28.6691</v>
+        <v>28.6646</v>
       </c>
       <c t="n" r="F63">
-        <v>0.3171</v>
+        <v>0.3323</v>
       </c>
       <c t="n" r="G63">
-        <v>29.1424</v>
+        <v>29.1621</v>
       </c>
       <c t="n" r="H63">
-        <v>232.2198</v>
+        <v>232.0558</v>
       </c>
       <c t="n" r="I63">
-        <v>353.5679</v>
+        <v>353.6370</v>
       </c>
     </row>
     <row r="64">
@@ -2065,19 +2068,19 @@
         </is>
       </c>
       <c t="n" r="C64">
-        <v>0.3264</v>
+        <v>0.3397</v>
       </c>
       <c t="n" r="D64">
-        <v>0.7502</v>
+        <v>0.7411</v>
       </c>
       <c t="n" r="E64">
-        <v>26.6912</v>
+        <v>26.6602</v>
       </c>
       <c t="n" r="F64">
-        <v>2.4519</v>
+        <v>2.4512</v>
       </c>
       <c t="n" r="G64">
-        <v>28.8352</v>
+        <v>28.8342</v>
       </c>
     </row>
     <row r="65">
@@ -2092,19 +2095,19 @@
         </is>
       </c>
       <c t="n" r="C65">
-        <v>-0.0281</v>
+        <v>-0.0181</v>
       </c>
       <c t="n" r="D65">
-        <v>-0.0677</v>
+        <v>-0.0587</v>
       </c>
       <c t="n" r="E65">
         <v>28.1527</v>
       </c>
       <c t="n" r="F65">
-        <v>-0.0774</v>
+        <v>-0.0775</v>
       </c>
       <c t="n" r="G65">
-        <v>28.0005</v>
+        <v>28.0004</v>
       </c>
     </row>
     <row r="66">
@@ -2119,25 +2122,25 @@
         </is>
       </c>
       <c t="n" r="C66">
-        <v>0.5044</v>
+        <v>0.5187</v>
       </c>
       <c t="n" r="D66">
-        <v>-1.3513</v>
+        <v>-1.4026</v>
       </c>
       <c t="n" r="E66">
-        <v>25.5619</v>
+        <v>25.5663</v>
       </c>
       <c t="n" r="F66">
-        <v>-20.3815</v>
+        <v>-20.3785</v>
       </c>
       <c t="n" r="G66">
-        <v>27.2707</v>
+        <v>27.2754</v>
       </c>
       <c t="n" r="H66">
-        <v>242.8641</v>
+        <v>242.8497</v>
       </c>
       <c t="n" r="I66">
-        <v>1974.2092</v>
+        <v>1974.2866</v>
       </c>
     </row>
     <row r="67">
@@ -2152,25 +2155,25 @@
         </is>
       </c>
       <c t="n" r="C67">
-        <v>1.6962</v>
+        <v>1.6201</v>
       </c>
       <c t="n" r="D67">
-        <v>4.0199</v>
+        <v>4.0577</v>
       </c>
       <c t="n" r="E67">
-        <v>16.0575</v>
+        <v>16.1114</v>
       </c>
       <c t="n" r="F67">
-        <v>4.1887</v>
+        <v>4.2407</v>
       </c>
       <c t="n" r="G67">
-        <v>26.9692</v>
+        <v>27.0326</v>
       </c>
       <c t="n" r="H67">
-        <v>134.3915</v>
+        <v>134.5447</v>
       </c>
       <c t="n" r="I67">
-        <v>634416.9966</v>
+        <v>634733.9698</v>
       </c>
     </row>
     <row r="68">
@@ -2185,25 +2188,25 @@
         </is>
       </c>
       <c t="n" r="C68">
-        <v>-2.3005</v>
+        <v>-2.2945</v>
       </c>
       <c t="n" r="D68">
-        <v>-1.1791</v>
+        <v>-1.1774</v>
       </c>
       <c t="n" r="E68">
-        <v>25.5605</v>
+        <v>25.5661</v>
       </c>
       <c t="n" r="F68">
-        <v>-0.3230</v>
+        <v>-0.3186</v>
       </c>
       <c t="n" r="G68">
-        <v>26.1229</v>
+        <v>26.1284</v>
       </c>
       <c t="n" r="H68">
-        <v>48.9862</v>
+        <v>49.0745</v>
       </c>
       <c t="n" r="I68">
-        <v>980.7751</v>
+        <v>980.8229</v>
       </c>
     </row>
     <row r="69">
@@ -2218,22 +2221,22 @@
         </is>
       </c>
       <c t="n" r="C69">
-        <v>0.4047</v>
+        <v>0.4268</v>
       </c>
       <c t="n" r="D69">
-        <v>1.7723</v>
+        <v>1.7835</v>
       </c>
       <c t="n" r="E69">
-        <v>8.7476</v>
+        <v>8.7410</v>
       </c>
       <c t="n" r="F69">
-        <v>1.7342</v>
+        <v>1.7416</v>
       </c>
       <c t="n" r="G69">
-        <v>25.8750</v>
+        <v>25.8841</v>
       </c>
       <c t="n" r="H69">
-        <v>76.9309</v>
+        <v>76.8387</v>
       </c>
     </row>
     <row r="70">
@@ -2248,19 +2251,19 @@
         </is>
       </c>
       <c t="n" r="C70">
-        <v>-2.3565</v>
+        <v>-2.3028</v>
       </c>
       <c t="n" r="D70">
-        <v>0.0025</v>
+        <v>0.0537</v>
       </c>
       <c t="n" r="E70">
-        <v>17.0701</v>
+        <v>17.0688</v>
       </c>
       <c t="n" r="F70">
-        <v>0.8748</v>
+        <v>0.9482</v>
       </c>
       <c t="n" r="G70">
-        <v>25.7410</v>
+        <v>25.8325</v>
       </c>
     </row>
     <row r="71">
@@ -2275,25 +2278,25 @@
         </is>
       </c>
       <c t="n" r="C71">
-        <v>1.0766</v>
+        <v>0.2519</v>
       </c>
       <c t="n" r="D71">
-        <v>3.9074</v>
+        <v>2.7131</v>
       </c>
       <c t="n" r="E71">
-        <v>17.7105</v>
+        <v>16.5892</v>
       </c>
       <c t="n" r="F71">
-        <v>4.0086</v>
+        <v>4.0686</v>
       </c>
       <c t="n" r="G71">
-        <v>25.7313</v>
+        <v>25.8039</v>
       </c>
       <c t="n" r="H71">
-        <v>218.1188</v>
+        <v>218.2915</v>
       </c>
       <c t="n" r="I71">
-        <v>495.8422</v>
+        <v>496.2383</v>
       </c>
     </row>
     <row r="72">
@@ -2308,25 +2311,25 @@
         </is>
       </c>
       <c t="n" r="C72">
-        <v>4.2053</v>
+        <v>4.2987</v>
       </c>
       <c t="n" r="D72">
-        <v>4.9620</v>
+        <v>5.0642</v>
       </c>
       <c t="n" r="E72">
-        <v>14.5994</v>
+        <v>14.6140</v>
       </c>
       <c t="n" r="F72">
-        <v>0.9913</v>
+        <v>1.0838</v>
       </c>
       <c t="n" r="G72">
-        <v>25.4429</v>
+        <v>25.5578</v>
       </c>
       <c t="n" r="H72">
-        <v>331.4080</v>
+        <v>331.7830</v>
       </c>
       <c t="n" r="I72">
-        <v>836.5159</v>
+        <v>837.3736</v>
       </c>
     </row>
     <row r="73">
@@ -2341,22 +2344,22 @@
         </is>
       </c>
       <c t="n" r="C73">
-        <v>1.1035</v>
+        <v>1.1990</v>
       </c>
       <c t="n" r="D73">
-        <v>3.4517</v>
+        <v>3.5388</v>
       </c>
       <c t="n" r="E73">
-        <v>-0.6342</v>
+        <v>-0.5443</v>
       </c>
       <c t="n" r="F73">
-        <v>3.7603</v>
+        <v>3.8804</v>
       </c>
       <c t="n" r="G73">
-        <v>25.1871</v>
+        <v>25.3320</v>
       </c>
       <c t="n" r="H73">
-        <v>161.0645</v>
+        <v>161.3750</v>
       </c>
     </row>
     <row r="74">
@@ -2371,19 +2374,19 @@
         </is>
       </c>
       <c t="n" r="C74">
-        <v>0.3899</v>
+        <v>0.3997</v>
       </c>
       <c t="n" r="D74">
-        <v>-0.1184</v>
+        <v>-0.1144</v>
       </c>
       <c t="n" r="E74">
-        <v>23.1966</v>
+        <v>23.1944</v>
       </c>
       <c t="n" r="F74">
-        <v>-0.1202</v>
+        <v>-0.1176</v>
       </c>
       <c t="n" r="G74">
-        <v>24.9192</v>
+        <v>24.9224</v>
       </c>
     </row>
     <row r="75">
@@ -2398,25 +2401,25 @@
         </is>
       </c>
       <c t="n" r="C75">
-        <v>-0.0487</v>
+        <v>-0.0912</v>
       </c>
       <c t="n" r="D75">
-        <v>-0.2291</v>
+        <v>-0.2267</v>
       </c>
       <c t="n" r="E75">
-        <v>24.8243</v>
+        <v>25.3035</v>
       </c>
       <c t="n" r="F75">
-        <v>-0.0125</v>
+        <v>-0.0113</v>
       </c>
       <c t="n" r="G75">
-        <v>24.8240</v>
+        <v>24.8255</v>
       </c>
       <c t="n" r="H75">
-        <v>199.1824</v>
+        <v>199.1905</v>
       </c>
       <c t="n" r="I75">
-        <v>400.1217</v>
+        <v>400.1274</v>
       </c>
     </row>
     <row r="76">
@@ -2431,22 +2434,22 @@
         </is>
       </c>
       <c t="n" r="C76">
-        <v>-2.5394</v>
+        <v>-2.4070</v>
       </c>
       <c t="n" r="D76">
-        <v>-2.3701</v>
+        <v>-2.3081</v>
       </c>
       <c t="n" r="E76">
-        <v>7.9144</v>
+        <v>7.9693</v>
       </c>
       <c t="n" r="F76">
-        <v>-2.8293</v>
+        <v>-2.7337</v>
       </c>
       <c t="n" r="G76">
-        <v>24.6737</v>
+        <v>24.7963</v>
       </c>
       <c t="n" r="H76">
-        <v>148.5617</v>
+        <v>148.7803</v>
       </c>
     </row>
     <row r="77">
@@ -2461,25 +2464,25 @@
         </is>
       </c>
       <c t="n" r="C77">
-        <v>6.6660</v>
+        <v>6.6901</v>
       </c>
       <c t="n" r="D77">
-        <v>8.3395</v>
+        <v>8.4296</v>
       </c>
       <c t="n" r="E77">
-        <v>16.1036</v>
+        <v>16.1127</v>
       </c>
       <c t="n" r="F77">
-        <v>6.8673</v>
+        <v>6.9018</v>
       </c>
       <c t="n" r="G77">
-        <v>22.9697</v>
+        <v>23.0094</v>
       </c>
       <c t="n" r="H77">
-        <v>244.2210</v>
+        <v>244.3006</v>
       </c>
       <c t="n" r="I77">
-        <v>780.5087</v>
+        <v>780.7930</v>
       </c>
     </row>
     <row r="78">
@@ -2494,22 +2497,22 @@
         </is>
       </c>
       <c t="n" r="C78">
-        <v>-0.1117</v>
+        <v>-0.1086</v>
       </c>
       <c t="n" r="D78">
-        <v>-0.6170</v>
+        <v>-0.6178</v>
       </c>
       <c t="n" r="E78">
-        <v>23.0708</v>
+        <v>23.0722</v>
       </c>
       <c t="n" r="F78">
-        <v>-0.7313</v>
+        <v>-0.7304</v>
       </c>
       <c t="n" r="G78">
-        <v>21.8492</v>
+        <v>21.8503</v>
       </c>
       <c t="n" r="H78">
-        <v>170.8890</v>
+        <v>170.8874</v>
       </c>
     </row>
     <row r="79">
@@ -2524,148 +2527,151 @@
         </is>
       </c>
       <c t="n" r="C79">
-        <v>0.2064</v>
+        <v>0.3853</v>
       </c>
       <c t="n" r="D79">
-        <v>0.8273</v>
+        <v>0.9974</v>
       </c>
       <c t="n" r="E79">
-        <v>3.7303</v>
+        <v>3.8578</v>
       </c>
       <c t="n" r="F79">
-        <v>1.2037</v>
+        <v>1.3766</v>
       </c>
       <c t="n" r="G79">
-        <v>21.3204</v>
+        <v>21.5277</v>
       </c>
       <c t="n" r="H79">
-        <v>263.6715</v>
+        <v>264.2885</v>
       </c>
       <c t="n" r="I79">
-        <v>794.3975</v>
+        <v>795.8364</v>
       </c>
     </row>
     <row r="80">
       <c t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">ZG6</t>
+          <t xml:space="preserve">GGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C80">
-        <v>-0.1061</v>
+        <v>0.8276</v>
       </c>
       <c t="n" r="D80">
-        <v>-0.3160</v>
+        <v>1.5037</v>
       </c>
       <c t="n" r="E80">
-        <v>22.0880</v>
+        <v>12.0653</v>
       </c>
       <c t="n" r="F80">
-        <v>-2.4662</v>
+        <v>1.6249</v>
       </c>
       <c t="n" r="G80">
-        <v>21.2828</v>
+        <v>21.3632</v>
       </c>
       <c t="n" r="H80">
-        <v>47.9592</v>
+        <v>77.0228</v>
       </c>
     </row>
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">GGF</t>
+          <t xml:space="preserve">ZG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C81">
-        <v>0.6648</v>
+        <v>-0.1003</v>
       </c>
       <c t="n" r="D81">
-        <v>1.4266</v>
+        <v>-0.3159</v>
       </c>
       <c t="n" r="E81">
-        <v>12.0244</v>
+        <v>22.0979</v>
       </c>
       <c t="n" r="F81">
-        <v>1.5204</v>
+        <v>-2.4688</v>
       </c>
       <c t="n" r="G81">
-        <v>21.2383</v>
+        <v>21.2796</v>
+      </c>
+      <c t="n" r="H81">
+        <v>47.5690</v>
       </c>
     </row>
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">OGM</t>
+          <t xml:space="preserve">RP9</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NEVA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C82">
-        <v>0.2741</v>
+        <v>0.8342</v>
       </c>
       <c t="n" r="D82">
-        <v>1.0226</v>
+        <v>1.1143</v>
       </c>
       <c t="n" r="E82">
-        <v>5.6474</v>
+        <v>17.6255</v>
       </c>
       <c t="n" r="F82">
-        <v>1.1127</v>
+        <v>1.3039</v>
       </c>
       <c t="n" r="G82">
-        <v>20.9072</v>
+        <v>20.9390</v>
       </c>
       <c t="n" r="H82">
-        <v>220.9849</v>
+        <v>175.1511</v>
       </c>
       <c t="n" r="I82">
-        <v>989.5397</v>
+        <v>1195.9372</v>
       </c>
     </row>
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">RP9</t>
+          <t xml:space="preserve">OGM</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NEVA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C83">
-        <v>0.7650</v>
+        <v>0.2717</v>
       </c>
       <c t="n" r="D83">
-        <v>1.0326</v>
+        <v>1.0226</v>
       </c>
       <c t="n" r="E83">
-        <v>17.5358</v>
+        <v>5.6481</v>
       </c>
       <c t="n" r="F83">
-        <v>1.2386</v>
+        <v>1.1120</v>
       </c>
       <c t="n" r="G83">
-        <v>20.8610</v>
+        <v>20.9064</v>
       </c>
       <c t="n" r="H83">
-        <v>203.2982</v>
+        <v>220.9937</v>
       </c>
       <c t="n" r="I83">
-        <v>1195.3621</v>
+        <v>989.5497</v>
       </c>
     </row>
     <row r="84">
@@ -2680,22 +2686,22 @@
         </is>
       </c>
       <c t="n" r="C84">
-        <v>-1.6319</v>
+        <v>-1.6227</v>
       </c>
       <c t="n" r="D84">
-        <v>0.0326</v>
+        <v>0.0426</v>
       </c>
       <c t="n" r="E84">
-        <v>16.6012</v>
+        <v>16.6119</v>
       </c>
       <c t="n" r="F84">
-        <v>0.4919</v>
+        <v>0.5022</v>
       </c>
       <c t="n" r="G84">
-        <v>20.2335</v>
+        <v>20.2458</v>
       </c>
       <c t="n" r="H84">
-        <v>367.9244</v>
+        <v>367.8531</v>
       </c>
     </row>
     <row r="85">
@@ -2710,25 +2716,25 @@
         </is>
       </c>
       <c t="n" r="C85">
-        <v>-5.7235</v>
+        <v>-5.7022</v>
       </c>
       <c t="n" r="D85">
-        <v>2.2528</v>
+        <v>2.2788</v>
       </c>
       <c t="n" r="E85">
-        <v>20.8053</v>
+        <v>20.8228</v>
       </c>
       <c t="n" r="F85">
-        <v>-4.6694</v>
+        <v>-4.6640</v>
       </c>
       <c t="n" r="G85">
-        <v>19.8974</v>
+        <v>19.9042</v>
       </c>
       <c t="n" r="H85">
-        <v>242.3643</v>
+        <v>242.3612</v>
       </c>
       <c t="n" r="I85">
-        <v>755.6181</v>
+        <v>754.5937</v>
       </c>
     </row>
     <row r="86">
@@ -2743,148 +2749,151 @@
         </is>
       </c>
       <c t="n" r="C86">
-        <v>-0.5200</v>
+        <v>-0.4624</v>
       </c>
       <c t="n" r="D86">
-        <v>1.2875</v>
+        <v>1.2391</v>
       </c>
       <c t="n" r="E86">
-        <v>15.4218</v>
+        <v>15.5877</v>
       </c>
       <c t="n" r="F86">
-        <v>-2.8758</v>
+        <v>-2.8525</v>
       </c>
       <c t="n" r="G86">
-        <v>19.8359</v>
+        <v>19.8646</v>
       </c>
       <c t="n" r="H86">
-        <v>150.3234</v>
+        <v>150.2604</v>
       </c>
       <c t="n" r="I86">
-        <v>419.7042</v>
+        <v>419.8286</v>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">OG2</t>
+          <t xml:space="preserve">MGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.UFUK KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C87">
-        <v>0.1025</v>
+        <v>0.4949</v>
       </c>
       <c t="n" r="D87">
-        <v>0.4314</v>
+        <v>1.2297</v>
       </c>
       <c t="n" r="E87">
-        <v>15.4518</v>
+        <v>11.5224</v>
       </c>
       <c t="n" r="F87">
-        <v>0.4182</v>
+        <v>-0.8133</v>
       </c>
       <c t="n" r="G87">
-        <v>19.4088</v>
+        <v>19.6608</v>
       </c>
       <c t="n" r="H87">
-        <v>116.2959</v>
-      </c>
-      <c t="n" r="I87">
-        <v>1160.0881</v>
+        <v>151.9130</v>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">MGA</t>
+          <t xml:space="preserve">OG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.UFUK KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C88">
-        <v>0.2855</v>
+        <v>0.1029</v>
       </c>
       <c t="n" r="D88">
-        <v>1.0217</v>
+        <v>-0.0927</v>
       </c>
       <c t="n" r="E88">
-        <v>11.2876</v>
+        <v>15.4435</v>
       </c>
       <c t="n" r="F88">
-        <v>-1.0245</v>
+        <v>0.4174</v>
       </c>
       <c t="n" r="G88">
-        <v>19.4061</v>
+        <v>19.4078</v>
       </c>
       <c t="n" r="H88">
-        <v>151.4504</v>
+        <v>116.2940</v>
+      </c>
+      <c t="n" r="I88">
+        <v>1160.0780</v>
       </c>
     </row>
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">PGB</t>
+          <t xml:space="preserve">RP2</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C89">
-        <v>-0.2413</v>
+        <v>2.6481</v>
       </c>
       <c t="n" r="D89">
-        <v>0.2548</v>
+        <v>3.0054</v>
       </c>
       <c t="n" r="E89">
-        <v>19.1438</v>
+        <v>17.6216</v>
       </c>
       <c t="n" r="F89">
-        <v>-0.0442</v>
+        <v>3.1668</v>
       </c>
       <c t="n" r="G89">
-        <v>18.8357</v>
+        <v>19.3680</v>
+      </c>
+      <c t="n" r="H89">
+        <v>145.7554</v>
+      </c>
+      <c t="n" r="I89">
+        <v>453.5488</v>
       </c>
     </row>
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">RP2</t>
+          <t xml:space="preserve">PGB</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C90">
-        <v>1.9273</v>
+        <v>-0.2399</v>
       </c>
       <c t="n" r="D90">
-        <v>2.2265</v>
+        <v>0.2568</v>
       </c>
       <c t="n" r="E90">
-        <v>16.9769</v>
+        <v>19.1433</v>
       </c>
       <c t="n" r="F90">
-        <v>2.5195</v>
+        <v>-0.0417</v>
       </c>
       <c t="n" r="G90">
-        <v>18.6191</v>
+        <v>18.8387</v>
       </c>
       <c t="n" r="H90">
-        <v>144.1613</v>
-      </c>
-      <c t="n" r="I90">
-        <v>450.7499</v>
+        <v>1434.1642</v>
       </c>
     </row>
     <row r="91">
@@ -2899,25 +2908,25 @@
         </is>
       </c>
       <c t="n" r="C91">
-        <v>-0.6046</v>
+        <v>-0.5953</v>
       </c>
       <c t="n" r="D91">
-        <v>-0.5453</v>
+        <v>-0.4660</v>
       </c>
       <c t="n" r="E91">
-        <v>11.1792</v>
+        <v>11.1793</v>
       </c>
       <c t="n" r="F91">
-        <v>-0.5762</v>
+        <v>-0.5815</v>
       </c>
       <c t="n" r="G91">
-        <v>17.9934</v>
+        <v>17.9871</v>
       </c>
       <c t="n" r="H91">
-        <v>245.6093</v>
+        <v>245.6086</v>
       </c>
       <c t="n" r="I91">
-        <v>1005.4946</v>
+        <v>1005.4354</v>
       </c>
     </row>
     <row r="92">
@@ -2932,22 +2941,22 @@
         </is>
       </c>
       <c t="n" r="C92">
-        <v>-1.5452</v>
+        <v>-1.5361</v>
       </c>
       <c t="n" r="D92">
-        <v>-1.0605</v>
+        <v>-1.0560</v>
       </c>
       <c t="n" r="E92">
-        <v>25.6662</v>
+        <v>25.6620</v>
       </c>
       <c t="n" r="F92">
-        <v>-0.8589</v>
+        <v>-0.8534</v>
       </c>
       <c t="n" r="G92">
-        <v>17.8069</v>
+        <v>17.8135</v>
       </c>
       <c t="n" r="H92">
-        <v>215.9493</v>
+        <v>215.9735</v>
       </c>
     </row>
     <row r="93">
@@ -2962,334 +2971,334 @@
         </is>
       </c>
       <c t="n" r="C93">
-        <v>-0.1338</v>
+        <v>-0.1250</v>
       </c>
       <c t="n" r="D93">
-        <v>-0.3925</v>
+        <v>-0.3927</v>
       </c>
       <c t="n" r="E93">
-        <v>26.9058</v>
+        <v>26.9057</v>
       </c>
       <c t="n" r="F93">
-        <v>-0.4383</v>
+        <v>-0.4427</v>
       </c>
       <c t="n" r="G93">
-        <v>17.7086</v>
+        <v>17.7034</v>
       </c>
       <c t="n" r="H93">
-        <v>775.9078</v>
+        <v>775.8448</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">YD3</t>
+          <t xml:space="preserve">FRG</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C94">
-        <v>-0.7094</v>
+        <v>7.0590</v>
       </c>
       <c t="n" r="D94">
-        <v>-2.1168</v>
+        <v>5.4563</v>
       </c>
       <c t="n" r="E94">
-        <v>11.7872</v>
+        <v>16.8611</v>
       </c>
       <c t="n" r="F94">
-        <v>-2.2580</v>
+        <v>7.2086</v>
       </c>
       <c t="n" r="G94">
-        <v>17.0749</v>
+        <v>17.3687</v>
       </c>
       <c t="n" r="H94">
-        <v>148.4104</v>
+        <v>97.9332</v>
       </c>
       <c t="n" r="I94">
-        <v>674.8979</v>
+        <v>455.4947</v>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">ABZ</t>
+          <t xml:space="preserve">YD3</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C95">
-        <v>-0.2509</v>
+        <v>-0.7075</v>
       </c>
       <c t="n" r="D95">
-        <v>-0.2529</v>
+        <v>-2.1200</v>
       </c>
       <c t="n" r="E95">
-        <v>5.3811</v>
+        <v>11.7811</v>
       </c>
       <c t="n" r="F95">
-        <v>-0.5037</v>
+        <v>-2.2657</v>
       </c>
       <c t="n" r="G95">
-        <v>16.9182</v>
+        <v>17.0657</v>
+      </c>
+      <c t="n" r="H95">
+        <v>148.4175</v>
+      </c>
+      <c t="n" r="I95">
+        <v>674.8369</v>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">OYZ</t>
+          <t xml:space="preserve">ABZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş.BEREKET KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C96">
-        <v>-0.2185</v>
+        <v>-0.2509</v>
       </c>
       <c t="n" r="D96">
-        <v>0.8960</v>
+        <v>-0.2528</v>
       </c>
       <c t="n" r="E96">
-        <v>6.1853</v>
+        <v>5.3808</v>
       </c>
       <c t="n" r="F96">
-        <v>-0.7018</v>
+        <v>-0.5036</v>
       </c>
       <c t="n" r="G96">
-        <v>16.7488</v>
-      </c>
-      <c t="n" r="H96">
-        <v>320.7136</v>
-      </c>
-      <c t="n" r="I96">
-        <v>1600.8154</v>
+        <v>16.9182</v>
       </c>
     </row>
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">PKA</t>
+          <t xml:space="preserve">OYZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş V METROWAY KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş.BEREKET KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C97">
-        <v>-0.0069</v>
+        <v>-0.2090</v>
       </c>
       <c t="n" r="D97">
-        <v>-0.0444</v>
+        <v>0.9069</v>
       </c>
       <c t="n" r="E97">
-        <v>16.1270</v>
+        <v>6.1915</v>
       </c>
       <c t="n" r="F97">
-        <v>-0.0439</v>
+        <v>-0.6882</v>
       </c>
       <c t="n" r="G97">
-        <v>16.0200</v>
+        <v>16.7648</v>
       </c>
       <c t="n" r="H97">
-        <v>580.1905</v>
+        <v>320.7547</v>
+      </c>
+      <c t="n" r="I97">
+        <v>1601.0485</v>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">OGI</t>
+          <t xml:space="preserve">PKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş V METROWAY KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C98">
-        <v>0.0602</v>
+        <v>-0.0087</v>
       </c>
       <c t="n" r="D98">
-        <v>-0.4735</v>
+        <v>-0.0461</v>
       </c>
       <c t="n" r="E98">
-        <v>2.2381</v>
+        <v>16.1238</v>
       </c>
       <c t="n" r="F98">
-        <v>-0.0124</v>
+        <v>-0.0457</v>
       </c>
       <c t="n" r="G98">
-        <v>15.5615</v>
+        <v>16.0178</v>
       </c>
       <c t="n" r="H98">
-        <v>0.4150</v>
-      </c>
-      <c t="n" r="I98">
-        <v>58.0061</v>
+        <v>580.1703</v>
       </c>
     </row>
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">NUE</t>
+          <t xml:space="preserve">RP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. EGÇ KONUT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C99">
-        <v>-0.2949</v>
+        <v>5.2350</v>
       </c>
       <c t="n" r="D99">
-        <v>2.6822</v>
+        <v>-3.7793</v>
       </c>
       <c t="n" r="E99">
-        <v>15.4390</v>
+        <v>11.8266</v>
       </c>
       <c t="n" r="F99">
-        <v>3.3166</v>
+        <v>-2.9489</v>
       </c>
       <c t="n" r="G99">
-        <v>15.3945</v>
+        <v>15.9699</v>
       </c>
       <c t="n" r="H99">
-        <v>187.1221</v>
+        <v>113.0278</v>
+      </c>
+      <c t="n" r="I99">
+        <v>370.7074</v>
       </c>
     </row>
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">FRG</t>
+          <t xml:space="preserve">OGI</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C100">
-        <v>5.0319</v>
+        <v>0.2297</v>
       </c>
       <c t="n" r="D100">
-        <v>3.3496</v>
+        <v>-0.4147</v>
       </c>
       <c t="n" r="E100">
-        <v>15.0972</v>
+        <v>2.2572</v>
       </c>
       <c t="n" r="F100">
-        <v>5.3496</v>
+        <v>0.0873</v>
       </c>
       <c t="n" r="G100">
-        <v>15.3335</v>
+        <v>15.6768</v>
       </c>
       <c t="n" r="H100">
-        <v>94.4843</v>
+        <v>0.5146</v>
       </c>
       <c t="n" r="I100">
-        <v>445.9275</v>
+        <v>58.1636</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">NUS</t>
+          <t xml:space="preserve">NUE</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ALTINCI KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. EGÇ KONUT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C101">
-        <v>-0.2293</v>
+        <v>-0.1749</v>
       </c>
       <c t="n" r="D101">
-        <v>-0.6073</v>
+        <v>2.5415</v>
       </c>
       <c t="n" r="E101">
-        <v>16.6327</v>
+        <v>15.8088</v>
       </c>
       <c t="n" r="F101">
-        <v>-0.6818</v>
+        <v>3.4126</v>
       </c>
       <c t="n" r="G101">
-        <v>14.9723</v>
+        <v>15.5017</v>
+      </c>
+      <c t="n" r="H101">
+        <v>187.3909</v>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">RAS</t>
+          <t xml:space="preserve">NUS</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ALTINCI KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C102">
-        <v>0.4825</v>
+        <v>-0.2167</v>
       </c>
       <c t="n" r="D102">
-        <v>1.1942</v>
+        <v>-0.6074</v>
       </c>
       <c t="n" r="E102">
-        <v>13.4033</v>
+        <v>16.6328</v>
       </c>
       <c t="n" r="F102">
-        <v>1.8129</v>
+        <v>-0.6882</v>
       </c>
       <c t="n" r="G102">
-        <v>14.7067</v>
-      </c>
-      <c t="n" r="H102">
-        <v>262.7884</v>
-      </c>
-      <c t="n" r="I102">
-        <v>470.3759</v>
+        <v>14.9649</v>
       </c>
     </row>
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">RP4</t>
+          <t xml:space="preserve">RAS</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C103">
-        <v>3.7099</v>
+        <v>0.5512</v>
       </c>
       <c t="n" r="D103">
-        <v>-5.1391</v>
+        <v>1.2682</v>
       </c>
       <c t="n" r="E103">
-        <v>10.6247</v>
+        <v>13.4690</v>
       </c>
       <c t="n" r="F103">
-        <v>-4.2088</v>
+        <v>1.8833</v>
       </c>
       <c t="n" r="G103">
-        <v>14.4643</v>
+        <v>14.7859</v>
       </c>
       <c t="n" r="H103">
-        <v>110.1683</v>
+        <v>262.7569</v>
       </c>
       <c t="n" r="I103">
-        <v>364.6851</v>
+        <v>478.0410</v>
       </c>
     </row>
     <row r="104">
@@ -3304,25 +3313,25 @@
         </is>
       </c>
       <c t="n" r="C104">
-        <v>-0.1521</v>
+        <v>-0.1244</v>
       </c>
       <c t="n" r="D104">
-        <v>1.5688</v>
+        <v>1.5427</v>
       </c>
       <c t="n" r="E104">
-        <v>4.8576</v>
+        <v>4.9311</v>
       </c>
       <c t="n" r="F104">
-        <v>1.1718</v>
+        <v>1.1770</v>
       </c>
       <c t="n" r="G104">
-        <v>14.4009</v>
+        <v>14.4068</v>
       </c>
       <c t="n" r="H104">
-        <v>266.1105</v>
+        <v>266.0410</v>
       </c>
       <c t="n" r="I104">
-        <v>1199.7892</v>
+        <v>1199.8562</v>
       </c>
     </row>
     <row r="105">
@@ -3337,82 +3346,82 @@
         </is>
       </c>
       <c t="n" r="C105">
-        <v>0.2357</v>
+        <v>0.2388</v>
       </c>
       <c t="n" r="D105">
-        <v>-0.0210</v>
+        <v>-0.0212</v>
       </c>
       <c t="n" r="E105">
-        <v>13.7615</v>
+        <v>13.7581</v>
       </c>
       <c t="n" r="F105">
-        <v>-0.9338</v>
+        <v>-0.9348</v>
       </c>
       <c t="n" r="G105">
-        <v>13.7480</v>
+        <v>13.7469</v>
       </c>
       <c t="n" r="H105">
-        <v>225.2176</v>
+        <v>225.2795</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">RKG</t>
+          <t xml:space="preserve">ZVE</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. NEF GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C106">
-        <v>-0.0550</v>
+        <v>0.0306</v>
       </c>
       <c t="n" r="D106">
-        <v>-0.3434</v>
+        <v>0.1960</v>
       </c>
       <c t="n" r="E106">
-        <v>13.5135</v>
+        <v>-0.9909</v>
       </c>
       <c t="n" r="F106">
-        <v>-0.5403</v>
+        <v>0.1891</v>
       </c>
       <c t="n" r="G106">
-        <v>13.0384</v>
+        <v>13.0387</v>
       </c>
       <c t="n" r="H106">
-        <v>493.5934</v>
+        <v>124.6486</v>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">ZVE</t>
+          <t xml:space="preserve">RKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. NEF GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C107">
-        <v>0.0043</v>
+        <v>-0.0530</v>
       </c>
       <c t="n" r="D107">
-        <v>0.1769</v>
+        <v>-0.3435</v>
       </c>
       <c t="n" r="E107">
-        <v>-1.0062</v>
+        <v>13.5135</v>
       </c>
       <c t="n" r="F107">
-        <v>0.1706</v>
+        <v>-0.5412</v>
       </c>
       <c t="n" r="G107">
-        <v>13.0177</v>
+        <v>13.0373</v>
       </c>
       <c t="n" r="H107">
-        <v>124.6210</v>
+        <v>493.5624</v>
       </c>
     </row>
     <row r="108">
@@ -3427,76 +3436,76 @@
         </is>
       </c>
       <c t="n" r="C108">
-        <v>0.0462</v>
+        <v>0.0526</v>
       </c>
       <c t="n" r="D108">
-        <v>2.4458</v>
+        <v>2.3645</v>
       </c>
       <c t="n" r="E108">
-        <v>3.8011</v>
+        <v>3.7820</v>
       </c>
       <c t="n" r="F108">
-        <v>2.4462</v>
+        <v>2.4456</v>
       </c>
       <c t="n" r="G108">
-        <v>12.7818</v>
+        <v>12.7811</v>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">YG7</t>
+          <t xml:space="preserve">NH2</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş CORNERSTONE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C109">
-        <v>0.0732</v>
+        <v>0.7748</v>
       </c>
       <c t="n" r="D109">
-        <v>0.7943</v>
+        <v>2.1272</v>
       </c>
       <c t="n" r="E109">
-        <v>9.8780</v>
+        <v>11.8396</v>
       </c>
       <c t="n" r="F109">
-        <v>0.7901</v>
+        <v>3.2629</v>
       </c>
       <c t="n" r="G109">
-        <v>12.5106</v>
-      </c>
-      <c t="n" r="H109">
-        <v>-18.6150</v>
+        <v>12.6152</v>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">NH2</t>
+          <t xml:space="preserve">YG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş CORNERSTONE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C110">
-        <v>0.6743</v>
+        <v>0.0855</v>
       </c>
       <c t="n" r="D110">
-        <v>1.8849</v>
+        <v>0.7895</v>
       </c>
       <c t="n" r="E110">
-        <v>11.7996</v>
+        <v>9.8550</v>
       </c>
       <c t="n" r="F110">
-        <v>3.1599</v>
+        <v>0.7789</v>
       </c>
       <c t="n" r="G110">
-        <v>12.5028</v>
+        <v>12.4982</v>
+      </c>
+      <c t="n" r="H110">
+        <v>-18.6170</v>
       </c>
     </row>
     <row r="111">
@@ -3511,25 +3520,25 @@
         </is>
       </c>
       <c t="n" r="C111">
-        <v>-0.3379</v>
+        <v>-0.3221</v>
       </c>
       <c t="n" r="D111">
-        <v>1.0338</v>
+        <v>1.0479</v>
       </c>
       <c t="n" r="E111">
-        <v>8.9209</v>
+        <v>8.9065</v>
       </c>
       <c t="n" r="F111">
-        <v>-1.1373</v>
+        <v>-1.1223</v>
       </c>
       <c t="n" r="G111">
-        <v>12.4328</v>
+        <v>12.4498</v>
       </c>
       <c t="n" r="H111">
-        <v>201.5077</v>
+        <v>201.5445</v>
       </c>
       <c t="n" r="I111">
-        <v>576.3121</v>
+        <v>576.4143</v>
       </c>
     </row>
     <row r="112">
@@ -3544,22 +3553,22 @@
         </is>
       </c>
       <c t="n" r="C112">
-        <v>-0.0140</v>
+        <v>0.0358</v>
       </c>
       <c t="n" r="D112">
-        <v>0.3562</v>
+        <v>0.4014</v>
       </c>
       <c t="n" r="E112">
-        <v>27.6009</v>
+        <v>27.6600</v>
       </c>
       <c t="n" r="F112">
-        <v>0.2745</v>
+        <v>0.3195</v>
       </c>
       <c t="n" r="G112">
-        <v>11.3253</v>
+        <v>11.3752</v>
       </c>
       <c t="n" r="H112">
-        <v>134.3598</v>
+        <v>134.4708</v>
       </c>
     </row>
     <row r="113">
@@ -3574,22 +3583,22 @@
         </is>
       </c>
       <c t="n" r="C113">
-        <v>-1.5302</v>
+        <v>-1.5034</v>
       </c>
       <c t="n" r="D113">
-        <v>-5.0781</v>
+        <v>-5.0636</v>
       </c>
       <c t="n" r="E113">
-        <v>33.4195</v>
+        <v>33.4125</v>
       </c>
       <c t="n" r="F113">
-        <v>-5.1400</v>
+        <v>-5.1233</v>
       </c>
       <c t="n" r="G113">
-        <v>10.5655</v>
+        <v>10.5849</v>
       </c>
       <c t="n" r="H113">
-        <v>402.0754</v>
+        <v>401.7085</v>
       </c>
     </row>
     <row r="114">
@@ -3604,19 +3613,19 @@
         </is>
       </c>
       <c t="n" r="C114">
-        <v>-0.0690</v>
+        <v>-0.0644</v>
       </c>
       <c t="n" r="D114">
         <v>-0.1962</v>
       </c>
       <c t="n" r="E114">
-        <v>10.8998</v>
+        <v>10.8980</v>
       </c>
       <c t="n" r="F114">
-        <v>-0.2146</v>
+        <v>-0.2163</v>
       </c>
       <c t="n" r="G114">
-        <v>10.4173</v>
+        <v>10.4154</v>
       </c>
     </row>
     <row r="115">
@@ -3631,19 +3640,19 @@
         </is>
       </c>
       <c t="n" r="C115">
-        <v>-0.3348</v>
+        <v>-0.3130</v>
       </c>
       <c t="n" r="D115">
-        <v>-1.2184</v>
+        <v>-1.2108</v>
       </c>
       <c t="n" r="E115">
-        <v>12.3985</v>
+        <v>12.3996</v>
       </c>
       <c t="n" r="F115">
-        <v>-1.3088</v>
+        <v>-1.3187</v>
       </c>
       <c t="n" r="G115">
-        <v>10.3221</v>
+        <v>10.3111</v>
       </c>
     </row>
     <row r="116">
@@ -3658,19 +3667,19 @@
         </is>
       </c>
       <c t="n" r="C116">
-        <v>0.4296</v>
+        <v>0.4433</v>
       </c>
       <c t="n" r="D116">
-        <v>0.6828</v>
+        <v>0.6958</v>
       </c>
       <c t="n" r="E116">
-        <v>6.5572</v>
+        <v>6.5669</v>
       </c>
       <c t="n" r="F116">
-        <v>1.2074</v>
+        <v>1.2241</v>
       </c>
       <c t="n" r="G116">
-        <v>9.4645</v>
+        <v>9.4824</v>
       </c>
     </row>
     <row r="117">
@@ -3685,25 +3694,25 @@
         </is>
       </c>
       <c t="n" r="C117">
-        <v>0.1099</v>
+        <v>0.1252</v>
       </c>
       <c t="n" r="D117">
-        <v>0.3645</v>
+        <v>0.3542</v>
       </c>
       <c t="n" r="E117">
-        <v>2.3710</v>
+        <v>1.9962</v>
       </c>
       <c t="n" r="F117">
-        <v>0.9318</v>
+        <v>0.9389</v>
       </c>
       <c t="n" r="G117">
-        <v>9.3656</v>
+        <v>9.3732</v>
       </c>
       <c t="n" r="H117">
-        <v>129.0135</v>
+        <v>128.9605</v>
       </c>
       <c t="n" r="I117">
-        <v>422.4041</v>
+        <v>422.0214</v>
       </c>
     </row>
     <row r="118">
@@ -3718,19 +3727,19 @@
         </is>
       </c>
       <c t="n" r="C118">
-        <v>-0.1121</v>
+        <v>-0.1112</v>
       </c>
       <c t="n" r="D118">
         <v>-0.1771</v>
       </c>
       <c t="n" r="E118">
-        <v>9.2265</v>
+        <v>9.2261</v>
       </c>
       <c t="n" r="F118">
-        <v>-0.1488</v>
+        <v>-0.1492</v>
       </c>
       <c t="n" r="G118">
-        <v>8.9764</v>
+        <v>8.9759</v>
       </c>
     </row>
     <row r="119">
@@ -3745,22 +3754,22 @@
         </is>
       </c>
       <c t="n" r="C119">
-        <v>0.2303</v>
+        <v>0.2327</v>
       </c>
       <c t="n" r="D119">
         <v>1.7098</v>
       </c>
       <c t="n" r="E119">
-        <v>8.3433</v>
+        <v>8.3491</v>
       </c>
       <c t="n" r="F119">
-        <v>1.6618</v>
+        <v>1.6610</v>
       </c>
       <c t="n" r="G119">
-        <v>8.9294</v>
+        <v>8.9285</v>
       </c>
       <c t="n" r="H119">
-        <v>124.1082</v>
+        <v>125.1200</v>
       </c>
     </row>
     <row r="120">
@@ -3775,286 +3784,286 @@
         </is>
       </c>
       <c t="n" r="C120">
-        <v>-0.0954</v>
+        <v>-0.0902</v>
       </c>
       <c t="n" r="D120">
-        <v>-0.2331</v>
+        <v>-0.2327</v>
       </c>
       <c t="n" r="E120">
-        <v>9.0309</v>
+        <v>9.0310</v>
       </c>
       <c t="n" r="F120">
-        <v>-0.1689</v>
+        <v>-0.1701</v>
       </c>
       <c t="n" r="G120">
-        <v>8.8604</v>
+        <v>8.8590</v>
       </c>
       <c t="n" r="H120">
-        <v>253.3288</v>
+        <v>253.3341</v>
       </c>
     </row>
     <row r="121">
       <c t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">NRY</t>
+          <t xml:space="preserve">NH4</t>
         </is>
       </c>
       <c t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ROYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C121">
-        <v>-0.3636</v>
+        <v>0.1902</v>
       </c>
       <c t="n" r="D121">
-        <v>-0.5505</v>
+        <v>0.4293</v>
       </c>
       <c t="n" r="E121">
-        <v>9.0161</v>
+        <v>3.9809</v>
       </c>
       <c t="n" r="F121">
-        <v>-0.3037</v>
+        <v>0.5493</v>
       </c>
       <c t="n" r="G121">
-        <v>8.5567</v>
+        <v>8.6314</v>
+      </c>
+      <c t="n" r="H121">
+        <v>244.9131</v>
       </c>
     </row>
     <row r="122">
       <c t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">NH4</t>
+          <t xml:space="preserve">NUI</t>
         </is>
       </c>
       <c t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. TİCARİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C122">
-        <v>0.0235</v>
+        <v>0.4008</v>
       </c>
       <c t="n" r="D122">
-        <v>0.2777</v>
+        <v>-1.8910</v>
       </c>
       <c t="n" r="E122">
-        <v>3.8265</v>
+        <v>7.5536</v>
       </c>
       <c t="n" r="F122">
-        <v>0.3998</v>
+        <v>-1.4120</v>
       </c>
       <c t="n" r="G122">
-        <v>8.4699</v>
-      </c>
-      <c t="n" r="H122">
-        <v>244.4645</v>
+        <v>8.4661</v>
       </c>
     </row>
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">NUI</t>
+          <t xml:space="preserve">NRY</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. TİCARİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ROYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C123">
-        <v>0.3909</v>
+        <v>-0.5014</v>
       </c>
       <c t="n" r="D123">
-        <v>-1.8893</v>
+        <v>-0.7011</v>
       </c>
       <c t="n" r="E123">
-        <v>7.5602</v>
+        <v>8.8451</v>
       </c>
       <c t="n" r="F123">
-        <v>-1.4094</v>
+        <v>-0.4585</v>
       </c>
       <c t="n" r="G123">
-        <v>8.4690</v>
+        <v>8.3882</v>
       </c>
     </row>
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">NG5</t>
+          <t xml:space="preserve">OCH</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. OC HEDEF GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C124">
-        <v>-0.3486</v>
+        <v>0.4488</v>
       </c>
       <c t="n" r="D124">
-        <v>-0.2303</v>
+        <v>0.5649</v>
       </c>
       <c t="n" r="E124">
-        <v>12.1215</v>
+        <v>7.0865</v>
       </c>
       <c t="n" r="F124">
-        <v>-0.9651</v>
+        <v>0.6468</v>
       </c>
       <c t="n" r="G124">
-        <v>7.6286</v>
+        <v>7.7358</v>
       </c>
       <c t="n" r="H124">
-        <v>214.2922</v>
+        <v>113.5580</v>
       </c>
     </row>
     <row r="125">
       <c t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">OCH</t>
+          <t xml:space="preserve">NG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. OC HEDEF GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C125">
-        <v>0.2904</v>
+        <v>-0.3512</v>
       </c>
       <c t="n" r="D125">
-        <v>0.4010</v>
+        <v>-0.2361</v>
       </c>
       <c t="n" r="E125">
-        <v>6.9016</v>
+        <v>12.1047</v>
       </c>
       <c t="n" r="F125">
-        <v>0.4837</v>
+        <v>-0.9725</v>
       </c>
       <c t="n" r="G125">
-        <v>7.5612</v>
+        <v>7.6206</v>
       </c>
       <c t="n" r="H125">
-        <v>113.1706</v>
+        <v>213.8131</v>
       </c>
     </row>
     <row r="126">
       <c t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">RTM</t>
+          <t xml:space="preserve">GJS</t>
         </is>
       </c>
       <c t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. TM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. SAĞLAM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C126">
-        <v>-0.3717</v>
+        <v>1.2519</v>
       </c>
       <c t="n" r="D126">
-        <v>-0.4051</v>
+        <v>0.7867</v>
       </c>
       <c t="n" r="E126">
-        <v>7.2250</v>
+        <v>6.5034</v>
       </c>
       <c t="n" r="F126">
-        <v>-0.3807</v>
+        <v>0.7087</v>
       </c>
       <c t="n" r="G126">
-        <v>6.5282</v>
+        <v>6.5736</v>
       </c>
       <c t="n" r="H126">
-        <v>233.4347</v>
+        <v>160.5295</v>
       </c>
     </row>
     <row r="127">
       <c t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">RG5</t>
+          <t xml:space="preserve">RTM</t>
         </is>
       </c>
       <c t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DİCLE PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. TM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C127">
-        <v>-0.0510</v>
+        <v>-0.3717</v>
       </c>
       <c t="n" r="D127">
-        <v>-0.1525</v>
+        <v>-0.4051</v>
       </c>
       <c t="n" r="E127">
-        <v>6.6126</v>
+        <v>7.2249</v>
       </c>
       <c t="n" r="F127">
-        <v>-0.1694</v>
+        <v>-0.3807</v>
       </c>
       <c t="n" r="G127">
-        <v>6.3436</v>
+        <v>6.5282</v>
       </c>
       <c t="n" r="H127">
-        <v>305.7934</v>
+        <v>233.4225</v>
       </c>
     </row>
     <row r="128">
       <c t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">NUT</t>
+          <t xml:space="preserve">RG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. NUROL TOWER GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DİCLE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C128">
-        <v>0.1424</v>
+        <v>-0.0486</v>
       </c>
       <c t="n" r="D128">
-        <v>1.0157</v>
+        <v>-0.1464</v>
       </c>
       <c t="n" r="E128">
-        <v>13.5526</v>
+        <v>6.6123</v>
       </c>
       <c t="n" r="F128">
-        <v>1.2558</v>
+        <v>-0.1706</v>
       </c>
       <c t="n" r="G128">
-        <v>5.8338</v>
+        <v>6.3423</v>
       </c>
       <c t="n" r="H128">
-        <v>195.3364</v>
+        <v>305.7944</v>
       </c>
     </row>
     <row r="129">
       <c t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">GJS</t>
+          <t xml:space="preserve">NUT</t>
         </is>
       </c>
       <c t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. SAĞLAM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. NUROL TOWER GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C129">
-        <v>0.1251</v>
+        <v>0.1706</v>
       </c>
       <c t="n" r="D129">
-        <v>-0.3317</v>
+        <v>1.0018</v>
       </c>
       <c t="n" r="E129">
-        <v>5.3215</v>
+        <v>13.6055</v>
       </c>
       <c t="n" r="F129">
-        <v>-0.4073</v>
+        <v>1.2786</v>
       </c>
       <c t="n" r="G129">
-        <v>5.3926</v>
+        <v>5.8576</v>
       </c>
       <c t="n" r="H129">
-        <v>157.6383</v>
+        <v>195.4043</v>
       </c>
     </row>
     <row r="130">
@@ -4069,19 +4078,19 @@
         </is>
       </c>
       <c t="n" r="C130">
-        <v>-0.0701</v>
+        <v>-0.0597</v>
       </c>
       <c t="n" r="D130">
-        <v>-0.1713</v>
+        <v>-0.1737</v>
       </c>
       <c t="n" r="E130">
-        <v>8.3338</v>
+        <v>8.3413</v>
       </c>
       <c t="n" r="F130">
-        <v>2.1439</v>
+        <v>2.1459</v>
       </c>
       <c t="n" r="G130">
-        <v>5.3143</v>
+        <v>5.3164</v>
       </c>
     </row>
     <row r="131">
@@ -4096,79 +4105,79 @@
         </is>
       </c>
       <c t="n" r="C131">
-        <v>0.3079</v>
+        <v>0.3168</v>
       </c>
       <c t="n" r="D131">
-        <v>1.1169</v>
+        <v>1.1221</v>
       </c>
       <c t="n" r="E131">
-        <v>11.4924</v>
+        <v>11.4997</v>
       </c>
       <c t="n" r="F131">
-        <v>1.0972</v>
+        <v>1.1027</v>
       </c>
       <c t="n" r="G131">
-        <v>5.2348</v>
+        <v>5.2405</v>
       </c>
       <c t="n" r="H131">
-        <v>153.4307</v>
+        <v>153.4354</v>
       </c>
     </row>
     <row r="132">
       <c t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">NUL</t>
+          <t xml:space="preserve">NH5</t>
         </is>
       </c>
       <c t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İGC GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C132">
-        <v>0.1507</v>
+        <v>1.1655</v>
       </c>
       <c t="n" r="D132">
-        <v>-10.4679</v>
+        <v>3.7197</v>
       </c>
       <c t="n" r="E132">
-        <v>0.3820</v>
+        <v>9.5106</v>
       </c>
       <c t="n" r="F132">
-        <v>-10.4847</v>
+        <v>4.3490</v>
       </c>
       <c t="n" r="G132">
-        <v>4.8082</v>
+        <v>4.9225</v>
+      </c>
+      <c t="n" r="H132">
+        <v>89.7578</v>
       </c>
     </row>
     <row r="133">
       <c t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">NH5</t>
+          <t xml:space="preserve">NUL</t>
         </is>
       </c>
       <c t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İGC GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C133">
-        <v>1.0336</v>
+        <v>0.1624</v>
       </c>
       <c t="n" r="D133">
-        <v>3.5962</v>
+        <v>-10.4716</v>
       </c>
       <c t="n" r="E133">
-        <v>9.3201</v>
+        <v>0.3478</v>
       </c>
       <c t="n" r="F133">
-        <v>4.1781</v>
+        <v>-10.4767</v>
       </c>
       <c t="n" r="G133">
-        <v>4.7506</v>
-      </c>
-      <c t="n" r="H133">
-        <v>89.4453</v>
+        <v>4.8175</v>
       </c>
     </row>
     <row r="134">
@@ -4183,22 +4192,22 @@
         </is>
       </c>
       <c t="n" r="C134">
-        <v>-0.2275</v>
+        <v>-0.2122</v>
       </c>
       <c t="n" r="D134">
-        <v>-0.6733</v>
+        <v>-0.6730</v>
       </c>
       <c t="n" r="E134">
-        <v>5.9073</v>
+        <v>5.9079</v>
       </c>
       <c t="n" r="F134">
-        <v>-0.7508</v>
+        <v>-0.7575</v>
       </c>
       <c t="n" r="G134">
-        <v>4.4939</v>
+        <v>4.4868</v>
       </c>
       <c t="n" r="H134">
-        <v>114.4717</v>
+        <v>114.2572</v>
       </c>
     </row>
     <row r="135">
@@ -4213,25 +4222,25 @@
         </is>
       </c>
       <c t="n" r="C135">
-        <v>-0.0176</v>
+        <v>0.1223</v>
       </c>
       <c t="n" r="D135">
-        <v>-0.7082</v>
+        <v>-0.6123</v>
       </c>
       <c t="n" r="E135">
-        <v>0.8814</v>
+        <v>0.9030</v>
       </c>
       <c t="n" r="F135">
-        <v>-0.6076</v>
+        <v>-0.5080</v>
       </c>
       <c t="n" r="G135">
-        <v>4.0407</v>
+        <v>4.1449</v>
       </c>
       <c t="n" r="H135">
-        <v>89.3869</v>
+        <v>89.5028</v>
       </c>
       <c t="n" r="I135">
-        <v>58.4339</v>
+        <v>58.5926</v>
       </c>
     </row>
     <row r="136">
@@ -4246,19 +4255,19 @@
         </is>
       </c>
       <c t="n" r="C136">
-        <v>-0.6283</v>
+        <v>-0.5863</v>
       </c>
       <c t="n" r="D136">
-        <v>-2.3163</v>
+        <v>-2.3181</v>
       </c>
       <c t="n" r="E136">
-        <v>-14.8881</v>
+        <v>-14.8953</v>
       </c>
       <c t="n" r="F136">
-        <v>-2.5156</v>
+        <v>-2.5362</v>
       </c>
       <c t="n" r="G136">
-        <v>4.0337</v>
+        <v>4.0117</v>
       </c>
     </row>
     <row r="137">
@@ -4273,19 +4282,19 @@
         </is>
       </c>
       <c t="n" r="C137">
-        <v>-0.6890</v>
+        <v>-0.6757</v>
       </c>
       <c t="n" r="D137">
-        <v>-1.5183</v>
+        <v>-1.5224</v>
       </c>
       <c t="n" r="E137">
-        <v>101.3633</v>
+        <v>100.7576</v>
       </c>
       <c t="n" r="F137">
-        <v>-2.1050</v>
+        <v>-2.1099</v>
       </c>
       <c t="n" r="G137">
-        <v>3.7283</v>
+        <v>3.7231</v>
       </c>
     </row>
     <row r="138">
@@ -4300,22 +4309,22 @@
         </is>
       </c>
       <c t="n" r="C138">
-        <v>-0.2590</v>
+        <v>-0.2477</v>
       </c>
       <c t="n" r="D138">
-        <v>-0.6511</v>
+        <v>-0.8518</v>
       </c>
       <c t="n" r="E138">
-        <v>0.6635</v>
+        <v>0.6638</v>
       </c>
       <c t="n" r="F138">
-        <v>-0.9619</v>
+        <v>-0.9675</v>
       </c>
       <c t="n" r="G138">
-        <v>3.4765</v>
+        <v>3.4707</v>
       </c>
       <c t="n" r="H138">
-        <v>170.6642</v>
+        <v>170.0628</v>
       </c>
     </row>
     <row r="139">
@@ -4330,22 +4339,22 @@
         </is>
       </c>
       <c t="n" r="C139">
-        <v>-0.0975</v>
+        <v>-0.0923</v>
       </c>
       <c t="n" r="D139">
-        <v>-0.2765</v>
+        <v>-0.2747</v>
       </c>
       <c t="n" r="E139">
-        <v>9.4907</v>
+        <v>9.4876</v>
       </c>
       <c t="n" r="F139">
-        <v>-0.3389</v>
+        <v>-0.3402</v>
       </c>
       <c t="n" r="G139">
-        <v>3.1544</v>
+        <v>3.1530</v>
       </c>
       <c t="n" r="H139">
-        <v>122.1688</v>
+        <v>122.0140</v>
       </c>
     </row>
     <row r="140">
@@ -4360,19 +4369,22 @@
         </is>
       </c>
       <c t="n" r="C140">
-        <v>-0.1146</v>
+        <v>-0.1102</v>
       </c>
       <c t="n" r="D140">
-        <v>-0.3518</v>
+        <v>-0.3455</v>
       </c>
       <c t="n" r="E140">
-        <v>16.5296</v>
+        <v>16.5359</v>
       </c>
       <c t="n" r="F140">
-        <v>-0.5153</v>
+        <v>-0.5088</v>
       </c>
       <c t="n" r="G140">
-        <v>3.0664</v>
+        <v>3.0732</v>
+      </c>
+      <c t="n" r="H140">
+        <v>267.6223</v>
       </c>
     </row>
     <row r="141">
@@ -4387,22 +4399,22 @@
         </is>
       </c>
       <c t="n" r="C141">
-        <v>1.0796</v>
+        <v>1.0824</v>
       </c>
       <c t="n" r="D141">
-        <v>-1.5761</v>
+        <v>-0.2814</v>
       </c>
       <c t="n" r="E141">
-        <v>4.9874</v>
+        <v>4.9562</v>
       </c>
       <c t="n" r="F141">
-        <v>-0.7863</v>
+        <v>-0.7894</v>
       </c>
       <c t="n" r="G141">
-        <v>2.8842</v>
+        <v>2.8810</v>
       </c>
       <c t="n" r="H141">
-        <v>265.8411</v>
+        <v>265.8296</v>
       </c>
     </row>
     <row r="142">
@@ -4417,19 +4429,19 @@
         </is>
       </c>
       <c t="n" r="C142">
-        <v>0.6521</v>
+        <v>0.6589</v>
       </c>
       <c t="n" r="D142">
-        <v>-1.9174</v>
+        <v>-1.9145</v>
       </c>
       <c t="n" r="E142">
-        <v>1.8957</v>
+        <v>1.8985</v>
       </c>
       <c t="n" r="F142">
-        <v>-1.2102</v>
+        <v>-1.2042</v>
       </c>
       <c t="n" r="G142">
-        <v>2.5239</v>
+        <v>2.5301</v>
       </c>
     </row>
     <row r="143">
@@ -4444,22 +4456,22 @@
         </is>
       </c>
       <c t="n" r="C143">
-        <v>-0.0249</v>
+        <v>-0.0070</v>
       </c>
       <c t="n" r="D143">
-        <v>-0.3813</v>
+        <v>-0.3700</v>
       </c>
       <c t="n" r="E143">
-        <v>7.8613</v>
+        <v>7.8618</v>
       </c>
       <c t="n" r="F143">
-        <v>-0.3826</v>
+        <v>-0.3728</v>
       </c>
       <c t="n" r="G143">
-        <v>2.2642</v>
+        <v>2.2743</v>
       </c>
       <c t="n" r="H143">
-        <v>130.9711</v>
+        <v>130.9976</v>
       </c>
     </row>
     <row r="144">
@@ -4474,19 +4486,19 @@
         </is>
       </c>
       <c t="n" r="C144">
-        <v>-1.9919</v>
+        <v>-1.9900</v>
       </c>
       <c t="n" r="D144">
-        <v>-1.5873</v>
+        <v>-1.5851</v>
       </c>
       <c t="n" r="E144">
-        <v>3.6762</v>
+        <v>3.6778</v>
       </c>
       <c t="n" r="F144">
-        <v>-1.5841</v>
+        <v>-1.5812</v>
       </c>
       <c t="n" r="G144">
-        <v>1.0921</v>
+        <v>1.0950</v>
       </c>
     </row>
     <row r="145">
@@ -4501,22 +4513,22 @@
         </is>
       </c>
       <c t="n" r="C145">
-        <v>-0.1815</v>
+        <v>-0.1356</v>
       </c>
       <c t="n" r="D145">
-        <v>-1.7921</v>
+        <v>-1.7573</v>
       </c>
       <c t="n" r="E145">
-        <v>2.1131</v>
+        <v>2.1406</v>
       </c>
       <c t="n" r="F145">
-        <v>-1.6795</v>
+        <v>-1.6423</v>
       </c>
       <c t="n" r="G145">
-        <v>0.9814</v>
+        <v>1.0196</v>
       </c>
       <c t="n" r="H145">
-        <v>70.4192</v>
+        <v>70.4913</v>
       </c>
     </row>
     <row r="146">
@@ -4780,16 +4792,16 @@
         </is>
       </c>
       <c t="n" r="C159">
-        <v>-0.1938</v>
+        <v>-0.1325</v>
       </c>
       <c t="n" r="D159">
-        <v>-0.6460</v>
+        <v>-0.6459</v>
       </c>
       <c t="n" r="F159">
-        <v>-0.8705</v>
+        <v>-0.8738</v>
       </c>
       <c t="n" r="G159">
-        <v>-0.0999</v>
+        <v>-0.1032</v>
       </c>
     </row>
     <row r="160">
@@ -4804,25 +4816,25 @@
         </is>
       </c>
       <c t="n" r="C160">
-        <v>2.2286</v>
+        <v>2.1698</v>
       </c>
       <c t="n" r="D160">
-        <v>8.7756</v>
+        <v>8.7863</v>
       </c>
       <c t="n" r="E160">
-        <v>17.3780</v>
+        <v>17.3612</v>
       </c>
       <c t="n" r="F160">
-        <v>8.9075</v>
+        <v>8.9296</v>
       </c>
       <c t="n" r="G160">
-        <v>-0.5874</v>
+        <v>-0.5672</v>
       </c>
       <c t="n" r="H160">
-        <v>152.9950</v>
+        <v>153.0418</v>
       </c>
       <c t="n" r="I160">
-        <v>495.7446</v>
+        <v>495.8691</v>
       </c>
     </row>
     <row r="161">
@@ -4837,19 +4849,19 @@
         </is>
       </c>
       <c t="n" r="C161">
-        <v>-0.2665</v>
+        <v>-0.2495</v>
       </c>
       <c t="n" r="D161">
-        <v>-0.7614</v>
+        <v>-0.7629</v>
       </c>
       <c t="n" r="E161">
-        <v>-0.2594</v>
+        <v>-0.2610</v>
       </c>
       <c t="n" r="F161">
-        <v>-0.8364</v>
+        <v>-0.8452</v>
       </c>
       <c t="n" r="G161">
-        <v>-1.5753</v>
+        <v>-1.5840</v>
       </c>
     </row>
     <row r="162">
@@ -4864,22 +4876,22 @@
         </is>
       </c>
       <c t="n" r="C162">
-        <v>9.2260</v>
+        <v>9.1011</v>
       </c>
       <c t="n" r="D162">
-        <v>9.0580</v>
+        <v>8.7438</v>
       </c>
       <c t="n" r="E162">
-        <v>1.3796</v>
+        <v>2.5161</v>
       </c>
       <c t="n" r="F162">
-        <v>8.3204</v>
+        <v>7.8282</v>
       </c>
       <c t="n" r="G162">
-        <v>-4.4432</v>
+        <v>-4.8774</v>
       </c>
       <c t="n" r="H162">
-        <v>100.9015</v>
+        <v>99.8856</v>
       </c>
     </row>
     <row r="163">
@@ -4894,19 +4906,19 @@
         </is>
       </c>
       <c t="n" r="C163">
-        <v>-2.2778</v>
+        <v>-2.2270</v>
       </c>
       <c t="n" r="D163">
-        <v>-10.0637</v>
+        <v>-10.0737</v>
       </c>
       <c t="n" r="E163">
-        <v>-11.8165</v>
+        <v>-11.8306</v>
       </c>
       <c t="n" r="F163">
-        <v>-10.1962</v>
+        <v>-10.2211</v>
       </c>
       <c t="n" r="G163">
-        <v>-7.4137</v>
+        <v>-7.4394</v>
       </c>
     </row>
     <row r="164">
@@ -4921,19 +4933,19 @@
         </is>
       </c>
       <c t="n" r="C164">
-        <v>0.3820</v>
+        <v>0.3860</v>
       </c>
       <c t="n" r="D164">
-        <v>-0.5694</v>
+        <v>-0.5679</v>
       </c>
       <c t="n" r="E164">
-        <v>2.4246</v>
+        <v>2.4264</v>
       </c>
       <c t="n" r="F164">
-        <v>-0.2999</v>
+        <v>-0.2973</v>
       </c>
       <c t="n" r="G164">
-        <v>-11.4637</v>
+        <v>-11.4613</v>
       </c>
     </row>
     <row r="165">
@@ -4948,19 +4960,19 @@
         </is>
       </c>
       <c t="n" r="C165">
-        <v>0.1634</v>
+        <v>0.1829</v>
       </c>
       <c t="n" r="D165">
-        <v>4.2407</v>
+        <v>4.2777</v>
       </c>
       <c t="n" r="E165">
-        <v>4.7211</v>
+        <v>4.7470</v>
       </c>
       <c t="n" r="F165">
-        <v>4.0496</v>
+        <v>4.0743</v>
       </c>
       <c t="n" r="G165">
-        <v>-13.4431</v>
+        <v>-13.4226</v>
       </c>
     </row>
     <row r="166">
@@ -4975,22 +4987,22 @@
         </is>
       </c>
       <c t="n" r="C166">
-        <v>-0.0465</v>
+        <v>-0.0352</v>
       </c>
       <c t="n" r="D166">
-        <v>-0.1081</v>
+        <v>-0.1082</v>
       </c>
       <c t="n" r="E166">
-        <v>-17.3186</v>
+        <v>-17.3192</v>
       </c>
       <c t="n" r="F166">
-        <v>-0.1288</v>
+        <v>-0.1296</v>
       </c>
       <c t="n" r="G166">
-        <v>-13.9653</v>
+        <v>-13.9660</v>
       </c>
       <c t="n" r="H166">
-        <v>196.5479</v>
+        <v>196.5131</v>
       </c>
     </row>
     <row r="167">
@@ -5005,22 +5017,22 @@
         </is>
       </c>
       <c t="n" r="C167">
-        <v>-0.5751</v>
+        <v>-0.5482</v>
       </c>
       <c t="n" r="D167">
-        <v>-1.5531</v>
+        <v>-1.5650</v>
       </c>
       <c t="n" r="E167">
-        <v>-17.3536</v>
+        <v>-17.3543</v>
       </c>
       <c t="n" r="F167">
-        <v>-1.7178</v>
+        <v>-1.7429</v>
       </c>
       <c t="n" r="G167">
-        <v>-18.5257</v>
+        <v>-18.5465</v>
       </c>
       <c t="n" r="H167">
-        <v>-3.0052</v>
+        <v>-3.0119</v>
       </c>
     </row>
     <row r="168">
@@ -5035,22 +5047,22 @@
         </is>
       </c>
       <c t="n" r="C168">
-        <v>-0.3034</v>
+        <v>-0.2887</v>
       </c>
       <c t="n" r="D168">
-        <v>-0.8454</v>
+        <v>-0.8455</v>
       </c>
       <c t="n" r="E168">
-        <v>-23.3499</v>
+        <v>-23.3501</v>
       </c>
       <c t="n" r="F168">
-        <v>-0.9445</v>
+        <v>-0.9518</v>
       </c>
       <c t="n" r="G168">
-        <v>-24.4769</v>
+        <v>-24.4825</v>
       </c>
       <c t="n" r="H168">
-        <v>350.2799</v>
+        <v>350.2733</v>
       </c>
     </row>
     <row r="169">
@@ -5065,13 +5077,13 @@
         </is>
       </c>
       <c t="n" r="C169">
-        <v>-0.0258</v>
+        <v>-0.0160</v>
       </c>
       <c t="n" r="D169">
         <v>-0.0525</v>
       </c>
       <c t="n" r="E169">
-        <v>-0.0960</v>
+        <v>-0.0856</v>
       </c>
       <c t="n" r="F169">
         <v>-0.0611</v>
@@ -5092,25 +5104,25 @@
         </is>
       </c>
       <c t="n" r="C170">
-        <v>-0.0891</v>
+        <v>-0.0790</v>
       </c>
       <c t="n" r="D170">
-        <v>-0.2966</v>
+        <v>-0.2925</v>
       </c>
       <c t="n" r="E170">
-        <v>-50.5130</v>
+        <v>-50.6041</v>
       </c>
       <c t="n" r="F170">
-        <v>-1.0450</v>
+        <v>-1.0418</v>
       </c>
       <c t="n" r="G170">
-        <v>-30.3445</v>
+        <v>-30.3422</v>
       </c>
       <c t="n" r="H170">
-        <v>70.9501</v>
+        <v>70.9595</v>
       </c>
       <c t="n" r="I170">
-        <v>786.2470</v>
+        <v>786.2764</v>
       </c>
     </row>
     <row r="171">
@@ -5125,22 +5137,22 @@
         </is>
       </c>
       <c t="n" r="C171">
-        <v>-0.6581</v>
+        <v>-0.6548</v>
       </c>
       <c t="n" r="D171">
-        <v>-1.7317</v>
+        <v>-1.7448</v>
       </c>
       <c t="n" r="E171">
-        <v>-30.4533</v>
+        <v>-30.4544</v>
       </c>
       <c t="n" r="F171">
-        <v>-1.8670</v>
+        <v>-1.8909</v>
       </c>
       <c t="n" r="G171">
-        <v>-30.7996</v>
+        <v>-30.8165</v>
       </c>
       <c t="n" r="H171">
-        <v>102.9554</v>
+        <v>102.9260</v>
       </c>
     </row>
     <row r="172">
@@ -5155,22 +5167,22 @@
         </is>
       </c>
       <c t="n" r="C172">
-        <v>0.1251</v>
+        <v>0.1529</v>
       </c>
       <c t="n" r="D172">
-        <v>-0.5689</v>
+        <v>-0.5650</v>
       </c>
       <c t="n" r="E172">
-        <v>-17.9276</v>
+        <v>-17.9148</v>
       </c>
       <c t="n" r="F172">
-        <v>-0.0572</v>
+        <v>-0.0417</v>
       </c>
       <c t="n" r="G172">
-        <v>-40.5172</v>
+        <v>-40.5079</v>
       </c>
       <c t="n" r="H172">
-        <v>91.3865</v>
+        <v>91.4134</v>
       </c>
     </row>
     <row r="173">
@@ -5185,22 +5197,22 @@
         </is>
       </c>
       <c t="n" r="C173">
-        <v>-0.2066</v>
+        <v>-0.1990</v>
       </c>
       <c t="n" r="D173">
-        <v>-3.4706</v>
+        <v>-3.4709</v>
       </c>
       <c t="n" r="E173">
-        <v>5.1055</v>
+        <v>5.0995</v>
       </c>
       <c t="n" r="F173">
-        <v>-7.3207</v>
+        <v>-7.3243</v>
       </c>
       <c t="n" r="G173">
-        <v>-40.9118</v>
+        <v>-40.9141</v>
       </c>
       <c t="n" r="H173">
-        <v>113.6861</v>
+        <v>113.6813</v>
       </c>
     </row>
     <row r="174">
@@ -5215,25 +5227,25 @@
         </is>
       </c>
       <c t="n" r="C174">
-        <v>-0.2427</v>
+        <v>-0.4478</v>
       </c>
       <c t="n" r="D174">
-        <v>-18.2532</v>
+        <v>-18.4382</v>
       </c>
       <c t="n" r="E174">
-        <v>-40.6808</v>
+        <v>-40.7979</v>
       </c>
       <c t="n" r="F174">
-        <v>-51.9295</v>
+        <v>-52.0249</v>
       </c>
       <c t="n" r="G174">
-        <v>-41.5951</v>
+        <v>-41.7111</v>
       </c>
       <c t="n" r="H174">
-        <v>-2.5485</v>
+        <v>-2.7363</v>
       </c>
       <c t="n" r="I174">
-        <v>218.0267</v>
+        <v>217.3950</v>
       </c>
     </row>
     <row r="175">
@@ -5248,76 +5260,76 @@
         </is>
       </c>
       <c t="n" r="C175">
-        <v>-11.1098</v>
+        <v>-4.1174</v>
       </c>
       <c t="n" r="D175">
-        <v>-23.7305</v>
+        <v>-23.7500</v>
       </c>
       <c t="n" r="E175">
-        <v>-25.5125</v>
+        <v>-25.5489</v>
       </c>
       <c t="n" r="F175">
-        <v>-26.0550</v>
+        <v>-26.0754</v>
       </c>
       <c t="n" r="G175">
-        <v>-43.1103</v>
+        <v>-43.1260</v>
       </c>
       <c t="n" r="H175">
-        <v>40.6260</v>
+        <v>40.5884</v>
       </c>
     </row>
     <row r="176">
       <c t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">IY1</t>
+          <t xml:space="preserve">NGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. V STATÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C176">
-        <v>-78.6285</v>
+        <v>3.0037</v>
       </c>
       <c t="n" r="D176">
-        <v>-80.0655</v>
+        <v>12.1224</v>
       </c>
       <c t="n" r="E176">
-        <v>-56.7992</v>
+        <v>15.7597</v>
       </c>
       <c t="n" r="F176">
-        <v>-80.0809</v>
+        <v>11.6873</v>
       </c>
       <c t="n" r="G176">
-        <v>-45.0830</v>
+        <v>-47.3296</v>
       </c>
     </row>
     <row r="177">
       <c t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">NGO</t>
+          <t xml:space="preserve">IY1</t>
         </is>
       </c>
       <c t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. V STATÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C177">
-        <v>2.7760</v>
+        <v>-82.7363</v>
       </c>
       <c t="n" r="D177">
-        <v>12.0474</v>
+        <v>-83.9038</v>
       </c>
       <c t="n" r="E177">
-        <v>15.5703</v>
+        <v>-76.8902</v>
       </c>
       <c t="n" r="F177">
-        <v>11.3400</v>
+        <v>-83.9186</v>
       </c>
       <c t="n" r="G177">
-        <v>-47.4933</v>
+        <v>-55.6636</v>
       </c>
     </row>
     <row r="178">
@@ -5332,25 +5344,25 @@
         </is>
       </c>
       <c t="n" r="C178">
-        <v>2.1550</v>
+        <v>2.9650</v>
       </c>
       <c t="n" r="D178">
-        <v>6.9659</v>
+        <v>7.0209</v>
       </c>
       <c t="n" r="E178">
-        <v>-10.9495</v>
+        <v>-9.7866</v>
       </c>
       <c t="n" r="F178">
-        <v>-14.3322</v>
+        <v>-13.7445</v>
       </c>
       <c t="n" r="G178">
-        <v>-59.6633</v>
+        <v>-59.3866</v>
       </c>
       <c t="n" r="H178">
-        <v>-21.3855</v>
+        <v>-20.8463</v>
       </c>
       <c t="n" r="I178">
-        <v>327.2153</v>
+        <v>330.1256</v>
       </c>
     </row>
     <row r="179">
@@ -5365,85 +5377,85 @@
         </is>
       </c>
       <c t="n" r="C179">
-        <v>-10.2980</v>
+        <v>-14.5731</v>
       </c>
       <c t="n" r="D179">
-        <v>-26.1516</v>
+        <v>-30.1232</v>
       </c>
       <c t="n" r="E179">
-        <v>462.9757</v>
+        <v>442.8826</v>
       </c>
       <c t="n" r="F179">
-        <v>-26.1544</v>
+        <v>-30.1259</v>
       </c>
       <c t="n" r="G179">
-        <v>-61.5071</v>
+        <v>-63.5773</v>
       </c>
     </row>
     <row r="180">
       <c t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">RP5</t>
+          <t xml:space="preserve">YD1</t>
         </is>
       </c>
       <c t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş.MİLENYUM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C180">
-        <v>13.0723</v>
+        <v>-22.7260</v>
       </c>
       <c t="n" r="D180">
-        <v>28.5343</v>
+        <v>-77.0688</v>
       </c>
       <c t="n" r="E180">
-        <v>-60.5138</v>
+        <v>-75.8932</v>
       </c>
       <c t="n" r="F180">
-        <v>77.9675</v>
+        <v>-77.1033</v>
       </c>
       <c t="n" r="G180">
-        <v>-62.8638</v>
+        <v>-67.5054</v>
       </c>
       <c t="n" r="H180">
-        <v>-64.3190</v>
+        <v>-84.9616</v>
       </c>
       <c t="n" r="I180">
-        <v>-4.8908</v>
+        <v>-45.0587</v>
       </c>
     </row>
     <row r="181">
       <c t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">YD1</t>
+          <t xml:space="preserve">RP5</t>
         </is>
       </c>
       <c t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş.MİLENYUM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C181">
-        <v>-22.2493</v>
+        <v>-2.5262</v>
       </c>
       <c t="n" r="D181">
-        <v>-77.0473</v>
+        <v>12.2127</v>
       </c>
       <c t="n" r="E181">
-        <v>-75.8801</v>
+        <v>-65.4639</v>
       </c>
       <c t="n" r="F181">
-        <v>-77.0808</v>
+        <v>55.5164</v>
       </c>
       <c t="n" r="G181">
-        <v>-67.4734</v>
+        <v>-67.5486</v>
       </c>
       <c t="n" r="H181">
-        <v>-84.9475</v>
+        <v>-68.8094</v>
       </c>
       <c t="n" r="I181">
-        <v>-45.0047</v>
+        <v>-16.8900</v>
       </c>
     </row>
     <row r="182">
@@ -5488,22 +5500,22 @@
         </is>
       </c>
       <c t="n" r="C183">
-        <v>-98.8772</v>
+        <v>-98.8497</v>
       </c>
       <c t="n" r="D183">
-        <v>-99.1164</v>
+        <v>-99.0940</v>
       </c>
       <c t="n" r="E183">
-        <v>-99.0616</v>
+        <v>-99.0381</v>
       </c>
       <c t="n" r="F183">
-        <v>-99.1243</v>
+        <v>-99.1020</v>
       </c>
       <c t="n" r="G183">
-        <v>-99.1604</v>
+        <v>-99.1391</v>
       </c>
       <c t="n" r="H183">
-        <v>-98.5649</v>
+        <v>-98.5285</v>
       </c>
     </row>
     <row r="184">
@@ -5566,13 +5578,13 @@
         </is>
       </c>
       <c t="n" r="C188">
-        <v>0.9924</v>
+        <v>1.0120</v>
       </c>
       <c t="n" r="D188">
-        <v>2.9548</v>
+        <v>2.9589</v>
       </c>
       <c t="n" r="F188">
-        <v>3.6258</v>
+        <v>3.6430</v>
       </c>
     </row>
     <row r="189">
@@ -5611,13 +5623,13 @@
         </is>
       </c>
       <c t="n" r="C191">
-        <v>-17.6214</v>
+        <v>-16.3732</v>
       </c>
       <c t="n" r="D191">
-        <v>-38.0980</v>
+        <v>-38.1159</v>
       </c>
       <c t="n" r="F191">
-        <v>-40.4373</v>
+        <v>-40.6957</v>
       </c>
     </row>
     <row r="192">
@@ -5632,13 +5644,13 @@
         </is>
       </c>
       <c t="n" r="C192">
-        <v>-10.5085</v>
+        <v>-10.2068</v>
       </c>
       <c t="n" r="D192">
-        <v>-63.2375</v>
+        <v>-63.1088</v>
       </c>
       <c t="n" r="F192">
-        <v>-28.8435</v>
+        <v>-28.5179</v>
       </c>
     </row>
     <row r="193">
@@ -5665,7 +5677,7 @@
         </is>
       </c>
       <c t="n" r="C194">
-        <v>1.1290</v>
+        <v>1.1416</v>
       </c>
     </row>
     <row r="195">
@@ -5680,13 +5692,13 @@
         </is>
       </c>
       <c t="n" r="C195">
-        <v>0.7742</v>
+        <v>0.8035</v>
       </c>
       <c t="n" r="D195">
-        <v>1.3433</v>
+        <v>1.3490</v>
       </c>
       <c t="n" r="F195">
-        <v>1.8543</v>
+        <v>1.8603</v>
       </c>
     </row>
     <row r="196">
@@ -5773,10 +5785,10 @@
         </is>
       </c>
       <c t="n" r="C202">
-        <v>1.1628</v>
+        <v>1.4583</v>
       </c>
       <c t="n" r="D202">
-        <v>1.3600</v>
+        <v>1.9144</v>
       </c>
     </row>
     <row r="203">
@@ -5791,16 +5803,16 @@
         </is>
       </c>
       <c t="n" r="C203">
-        <v>1.6623</v>
+        <v>1.8045</v>
       </c>
       <c t="n" r="D203">
-        <v>418.7024</v>
+        <v>419.1642</v>
       </c>
       <c t="n" r="E203">
-        <v>461.5674</v>
+        <v>460.9434</v>
       </c>
       <c t="n" r="F203">
-        <v>423.2155</v>
+        <v>424.2458</v>
       </c>
     </row>
     <row r="204">
@@ -5815,16 +5827,16 @@
         </is>
       </c>
       <c t="n" r="C204">
-        <v>12.1191</v>
+        <v>12.1074</v>
       </c>
       <c t="n" r="D204">
-        <v>44.7362</v>
+        <v>44.6009</v>
       </c>
       <c t="n" r="E204">
-        <v>59.7120</v>
+        <v>59.2135</v>
       </c>
       <c t="n" r="F204">
-        <v>46.4654</v>
+        <v>46.4845</v>
       </c>
     </row>
     <row r="205">
@@ -5851,16 +5863,16 @@
         </is>
       </c>
       <c t="n" r="C206">
-        <v>-0.0479</v>
+        <v>-0.0451</v>
       </c>
       <c t="n" r="D206">
-        <v>-0.1102</v>
+        <v>-0.1099</v>
       </c>
       <c t="n" r="E206">
-        <v>19.4046</v>
+        <v>19.4004</v>
       </c>
       <c t="n" r="F206">
-        <v>-0.1358</v>
+        <v>-0.1365</v>
       </c>
     </row>
     <row r="207">
@@ -5875,7 +5887,7 @@
         </is>
       </c>
       <c t="n" r="C207">
-        <v>-0.0311</v>
+        <v>-0.0215</v>
       </c>
     </row>
     <row r="208">
@@ -5902,16 +5914,16 @@
         </is>
       </c>
       <c t="n" r="C209">
-        <v>2.9227</v>
+        <v>3.1458</v>
       </c>
       <c t="n" r="D209">
-        <v>8.8029</v>
+        <v>9.0482</v>
       </c>
       <c t="n" r="E209">
-        <v>19.5296</v>
+        <v>19.5427</v>
       </c>
       <c t="n" r="F209">
-        <v>10.1283</v>
+        <v>10.4844</v>
       </c>
     </row>
     <row r="210">
@@ -5938,10 +5950,10 @@
         </is>
       </c>
       <c t="n" r="C211">
-        <v>-0.1080</v>
+        <v>-0.1081</v>
       </c>
       <c t="n" r="D211">
-        <v>-0.3304</v>
+        <v>-0.3305</v>
       </c>
       <c t="n" r="F211">
         <v>-0.3296</v>
@@ -5959,10 +5971,10 @@
         </is>
       </c>
       <c t="n" r="C212">
-        <v>-0.9912</v>
+        <v>-0.9089</v>
       </c>
       <c t="n" r="D212">
-        <v>6.7233</v>
+        <v>6.7241</v>
       </c>
     </row>
     <row r="213">
@@ -5977,7 +5989,7 @@
         </is>
       </c>
       <c t="n" r="C213">
-        <v>0.2386</v>
+        <v>-0.1809</v>
       </c>
     </row>
     <row r="214">
@@ -5992,16 +6004,16 @@
         </is>
       </c>
       <c t="n" r="C214">
-        <v>-0.0370</v>
+        <v>-0.0350</v>
       </c>
       <c t="n" r="D214">
-        <v>-0.0989</v>
+        <v>-0.0990</v>
       </c>
       <c t="n" r="E214">
-        <v>12.7750</v>
+        <v>12.7749</v>
       </c>
       <c t="n" r="F214">
-        <v>-0.1119</v>
+        <v>-0.1129</v>
       </c>
     </row>
     <row r="215">
@@ -6016,16 +6028,16 @@
         </is>
       </c>
       <c t="n" r="C215">
-        <v>0.8054</v>
+        <v>0.7999</v>
       </c>
       <c t="n" r="D215">
-        <v>3.1186</v>
+        <v>3.1065</v>
       </c>
       <c t="n" r="E215">
-        <v>12.5459</v>
+        <v>12.5354</v>
       </c>
       <c t="n" r="F215">
-        <v>3.1182</v>
+        <v>3.1072</v>
       </c>
     </row>
     <row r="216">
@@ -6040,16 +6052,16 @@
         </is>
       </c>
       <c t="n" r="C216">
-        <v>-99.8272</v>
+        <v>-86.6379</v>
       </c>
       <c t="n" r="D216">
-        <v>-99.8495</v>
+        <v>-99.8625</v>
       </c>
       <c t="n" r="E216">
-        <v>-99.9877</v>
+        <v>-99.9887</v>
       </c>
       <c t="n" r="F216">
-        <v>-99.9752</v>
+        <v>-99.9773</v>
       </c>
     </row>
     <row r="217">
@@ -6088,16 +6100,16 @@
         </is>
       </c>
       <c t="n" r="C219">
-        <v>0.3206</v>
+        <v>0.3694</v>
       </c>
       <c t="n" r="D219">
-        <v>0.3654</v>
+        <v>0.4013</v>
       </c>
       <c t="n" r="E219">
-        <v>36.6957</v>
+        <v>36.6673</v>
       </c>
       <c t="n" r="F219">
-        <v>0.4958</v>
+        <v>0.5422</v>
       </c>
     </row>
     <row r="220">
@@ -6196,13 +6208,13 @@
         </is>
       </c>
       <c t="n" r="C227">
-        <v>6.0658</v>
+        <v>5.5335</v>
       </c>
       <c t="n" r="D227">
-        <v>5.5082</v>
+        <v>5.6438</v>
       </c>
       <c t="n" r="F227">
-        <v>12.6673</v>
+        <v>11.2714</v>
       </c>
     </row>
     <row r="228">
@@ -6241,16 +6253,16 @@
         </is>
       </c>
       <c t="n" r="C230">
-        <v>2.6718</v>
+        <v>0.8778</v>
       </c>
       <c t="n" r="D230">
-        <v>6.8458</v>
+        <v>4.9719</v>
       </c>
       <c t="n" r="E230">
-        <v>15.9447</v>
+        <v>13.6637</v>
       </c>
       <c t="n" r="F230">
-        <v>8.0977</v>
+        <v>6.2829</v>
       </c>
     </row>
     <row r="231">
@@ -6265,16 +6277,16 @@
         </is>
       </c>
       <c t="n" r="C231">
-        <v>3.1970</v>
+        <v>3.0341</v>
       </c>
       <c t="n" r="D231">
-        <v>9.4956</v>
+        <v>9.5231</v>
       </c>
       <c t="n" r="E231">
-        <v>19.6465</v>
+        <v>20.6683</v>
       </c>
       <c t="n" r="F231">
-        <v>10.7365</v>
+        <v>10.8772</v>
       </c>
     </row>
     <row r="232">
@@ -6289,16 +6301,16 @@
         </is>
       </c>
       <c t="n" r="C232">
-        <v>0.2682</v>
+        <v>0.7844</v>
       </c>
       <c t="n" r="D232">
-        <v>0.9310</v>
+        <v>1.2849</v>
       </c>
       <c t="n" r="E232">
-        <v>3.8559</v>
+        <v>3.9829</v>
       </c>
       <c t="n" r="F232">
-        <v>1.4513</v>
+        <v>1.7877</v>
       </c>
     </row>
     <row r="233">
@@ -6325,16 +6337,16 @@
         </is>
       </c>
       <c t="n" r="C234">
-        <v>2.6718</v>
+        <v>0.9651</v>
       </c>
       <c t="n" r="D234">
-        <v>6.8458</v>
+        <v>5.0627</v>
       </c>
       <c t="n" r="E234">
-        <v>15.9447</v>
+        <v>13.7621</v>
       </c>
       <c t="n" r="F234">
-        <v>8.0977</v>
+        <v>6.3749</v>
       </c>
     </row>
     <row r="235">
@@ -6385,13 +6397,13 @@
         </is>
       </c>
       <c t="n" r="C238">
-        <v>-2.0365</v>
+        <v>-1.8464</v>
       </c>
       <c t="n" r="D238">
-        <v>-82.5474</v>
+        <v>-82.3180</v>
       </c>
       <c t="n" r="F238">
-        <v>-84.7257</v>
+        <v>-84.7276</v>
       </c>
     </row>
     <row r="239">
@@ -6430,16 +6442,16 @@
         </is>
       </c>
       <c t="n" r="C241">
-        <v>-0.0534</v>
+        <v>-0.0502</v>
       </c>
       <c t="n" r="D241">
-        <v>-0.1447</v>
+        <v>-0.1443</v>
       </c>
       <c t="n" r="E241">
-        <v>30.4732</v>
+        <v>30.4730</v>
       </c>
       <c t="n" r="F241">
-        <v>-0.1653</v>
+        <v>-0.1669</v>
       </c>
     </row>
     <row r="242">
@@ -6454,16 +6466,16 @@
         </is>
       </c>
       <c t="n" r="C242">
-        <v>-0.1004</v>
+        <v>-0.0718</v>
       </c>
       <c t="n" r="D242">
-        <v>-0.2493</v>
+        <v>-0.2370</v>
       </c>
       <c t="n" r="E242">
-        <v>1628.1503</v>
+        <v>1624.6856</v>
       </c>
       <c t="n" r="F242">
-        <v>-0.2691</v>
+        <v>-0.2592</v>
       </c>
     </row>
     <row r="243">
@@ -6514,13 +6526,13 @@
         </is>
       </c>
       <c t="n" r="C246">
-        <v>-4.9013</v>
+        <v>-4.1349</v>
       </c>
       <c t="n" r="D246">
-        <v>-14.3343</v>
+        <v>-14.1724</v>
       </c>
       <c t="n" r="F246">
-        <v>-15.6161</v>
+        <v>-15.5964</v>
       </c>
     </row>
     <row r="247">
@@ -6535,16 +6547,16 @@
         </is>
       </c>
       <c t="n" r="C247">
-        <v>-5.3363</v>
+        <v>-4.6059</v>
       </c>
       <c t="n" r="D247">
-        <v>-14.8699</v>
+        <v>-14.7149</v>
       </c>
       <c t="n" r="E247">
-        <v>-22.6217</v>
+        <v>-22.8546</v>
       </c>
       <c t="n" r="F247">
-        <v>-16.0559</v>
+        <v>-16.0197</v>
       </c>
     </row>
     <row r="248">
@@ -6598,1242 +6610,1266 @@
     <row r="252">
       <c t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">IE1</t>
+          <t xml:space="preserve">BRY</t>
         </is>
       </c>
       <c t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BORYAL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">IY3</t>
+          <t xml:space="preserve">IDT</t>
         </is>
       </c>
       <c t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C253">
-        <v>-79.5759</v>
-      </c>
-      <c t="n" r="D253">
-        <v>-81.8716</v>
-      </c>
-      <c t="n" r="E253">
-        <v>2925.1672</v>
-      </c>
-      <c t="n" r="F253">
-        <v>-81.8852</v>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. GELİŞİM TRAKYA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="254">
       <c t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">IY2</t>
+          <t xml:space="preserve">IE1</t>
         </is>
       </c>
       <c t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C254">
-        <v>-1.5004</v>
-      </c>
-      <c t="n" r="D254">
-        <v>-13.1319</v>
-      </c>
-      <c t="n" r="F254">
-        <v>-13.1988</v>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="255">
       <c t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">VMG</t>
+          <t xml:space="preserve">IY3</t>
         </is>
       </c>
       <c t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C255">
-        <v>-5.9477</v>
+        <v>-86.9959</v>
       </c>
       <c t="n" r="D255">
-        <v>-6.4682</v>
+        <v>-88.4657</v>
       </c>
       <c t="n" r="E255">
-        <v>-9.3487</v>
+        <v>-75.2623</v>
       </c>
       <c t="n" r="F255">
-        <v>-4.5460</v>
+        <v>-88.4760</v>
       </c>
     </row>
     <row r="256">
       <c t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">VMP</t>
+          <t xml:space="preserve">IY2</t>
         </is>
       </c>
       <c t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C256">
+        <v>-1.4050</v>
+      </c>
+      <c t="n" r="D256">
+        <v>-13.1597</v>
+      </c>
+      <c t="n" r="F256">
+        <v>-13.2416</v>
       </c>
     </row>
     <row r="257">
       <c t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">KPE</t>
+          <t xml:space="preserve">VMG</t>
         </is>
       </c>
       <c t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. KAR PAYI ÖDEYEN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C257">
-        <v>2.9240</v>
+        <v>-5.9294</v>
+      </c>
+      <c t="n" r="D257">
+        <v>-6.4677</v>
+      </c>
+      <c t="n" r="E257">
+        <v>-9.3565</v>
+      </c>
+      <c t="n" r="F257">
+        <v>-4.5530</v>
       </c>
     </row>
     <row r="258">
       <c t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">RIN</t>
+          <t xml:space="preserve">VMP</t>
         </is>
       </c>
       <c t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. RİNNOVA PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C258">
-        <v>0.0630</v>
+          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="259">
       <c t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">ITO</t>
+          <t xml:space="preserve">KPE</t>
         </is>
       </c>
       <c t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. T-FON PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. KAR PAYI ÖDEYEN GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C259">
+        <v>3.1592</v>
       </c>
     </row>
     <row r="260">
       <c t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">UNO</t>
+          <t xml:space="preserve">RIN</t>
         </is>
       </c>
       <c t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. UNİCON PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. RİNNOVA PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C260">
+        <v>0.1328</v>
       </c>
     </row>
     <row r="261">
       <c t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">YAL</t>
+          <t xml:space="preserve">ITO</t>
         </is>
       </c>
       <c t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C261">
-        <v>70.7990</v>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. T-FON PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="262">
       <c t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">YLP</t>
+          <t xml:space="preserve">UNO</t>
         </is>
       </c>
       <c t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. UNİCON PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">KBN</t>
+          <t xml:space="preserve">YAL</t>
         </is>
       </c>
       <c t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C263">
-        <v>2.2015</v>
-      </c>
-      <c t="n" r="D263">
-        <v>6.7752</v>
-      </c>
-      <c t="n" r="F263">
-        <v>7.8034</v>
+        <v>80.6154</v>
       </c>
     </row>
     <row r="264">
       <c t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">KKR</t>
+          <t xml:space="preserve">YLP</t>
         </is>
       </c>
       <c t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C264">
-        <v>2.2037</v>
-      </c>
-      <c t="n" r="D264">
-        <v>6.7545</v>
-      </c>
-      <c t="n" r="F264">
-        <v>7.7829</v>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="265">
       <c t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">MDG</t>
+          <t xml:space="preserve">KBN</t>
         </is>
       </c>
       <c t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞAN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C265">
+        <v>2.4402</v>
+      </c>
+      <c t="n" r="D265">
+        <v>6.9822</v>
+      </c>
+      <c t="n" r="F265">
+        <v>8.0964</v>
       </c>
     </row>
     <row r="266">
       <c t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">NAA</t>
+          <t xml:space="preserve">KKR</t>
         </is>
       </c>
       <c t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C266">
-        <v>-30.3469</v>
+        <v>2.4423</v>
       </c>
       <c t="n" r="D266">
-        <v>-27.7503</v>
-      </c>
-      <c t="n" r="E266">
-        <v>-23.3555</v>
+        <v>6.9616</v>
       </c>
       <c t="n" r="F266">
-        <v>-27.2058</v>
+        <v>8.0759</v>
       </c>
     </row>
     <row r="267">
       <c t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">NGB</t>
+          <t xml:space="preserve">MDG</t>
         </is>
       </c>
       <c t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">NBR</t>
+          <t xml:space="preserve">NAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C268">
-        <v>-0.6556</v>
+        <v>-30.3727</v>
       </c>
       <c t="n" r="D268">
-        <v>25.9505</v>
+        <v>-27.7859</v>
       </c>
       <c t="n" r="E268">
-        <v>-33.2036</v>
+        <v>-23.5600</v>
       </c>
       <c t="n" r="F268">
-        <v>95.8457</v>
+        <v>-27.1962</v>
       </c>
     </row>
     <row r="269">
       <c t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">NGD</t>
+          <t xml:space="preserve">NGB</t>
         </is>
       </c>
       <c t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C269">
-        <v>19.0189</v>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="270">
       <c t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">GNC</t>
+          <t xml:space="preserve">NBR</t>
         </is>
       </c>
       <c t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. GNC KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C270">
-        <v>-0.3505</v>
+        <v>-0.4679</v>
       </c>
       <c t="n" r="D270">
-        <v>-1.1257</v>
+        <v>25.9719</v>
+      </c>
+      <c t="n" r="E270">
+        <v>-33.2627</v>
       </c>
       <c t="n" r="F270">
-        <v>-2.2681</v>
+        <v>95.8267</v>
       </c>
     </row>
     <row r="271">
       <c t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">NIK</t>
+          <t xml:space="preserve">NGD</t>
         </is>
       </c>
       <c t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C271">
-        <v>-74.1998</v>
-      </c>
-      <c t="n" r="D271">
-        <v>-87.8869</v>
-      </c>
-      <c t="n" r="E271">
-        <v>-41.9080</v>
-      </c>
-      <c t="n" r="F271">
-        <v>136.8199</v>
+        <v>21.6732</v>
       </c>
     </row>
     <row r="272">
       <c t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">NGR</t>
+          <t xml:space="preserve">GNC</t>
         </is>
       </c>
       <c t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. RİVA PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. GNC KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C272">
+        <v>-0.3314</v>
+      </c>
+      <c t="n" r="D272">
+        <v>-1.0915</v>
+      </c>
+      <c t="n" r="F272">
+        <v>-2.2774</v>
       </c>
     </row>
     <row r="273">
       <c t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">NGU</t>
+          <t xml:space="preserve">NIK</t>
         </is>
       </c>
       <c t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C273">
+        <v>-74.0298</v>
+      </c>
+      <c t="n" r="D273">
+        <v>-87.8295</v>
+      </c>
+      <c t="n" r="E273">
+        <v>-41.8884</v>
+      </c>
+      <c t="n" r="F273">
+        <v>137.2579</v>
       </c>
     </row>
     <row r="274">
       <c t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">NBP</t>
+          <t xml:space="preserve">NGR</t>
         </is>
       </c>
       <c t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C274">
-        <v>-0.0727</v>
-      </c>
-      <c t="n" r="D274">
-        <v>-10.3956</v>
-      </c>
-      <c t="n" r="F274">
-        <v>-9.7137</v>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. RİVA PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="275">
       <c t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">NP4</t>
+          <t xml:space="preserve">NGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">NKN</t>
+          <t xml:space="preserve">NBP</t>
         </is>
       </c>
       <c t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C276">
-        <v>2.9690</v>
+        <v>-0.0547</v>
       </c>
       <c t="n" r="D276">
-        <v>-61.7160</v>
-      </c>
-      <c t="n" r="E276">
-        <v>-99.1385</v>
+        <v>-10.4514</v>
       </c>
       <c t="n" r="F276">
-        <v>-98.1794</v>
+        <v>-9.7078</v>
       </c>
     </row>
     <row r="277">
       <c t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">MAA</t>
+          <t xml:space="preserve">NP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. MAANAA LEVENT PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">NGM</t>
+          <t xml:space="preserve">NKN</t>
         </is>
       </c>
       <c t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C278">
-        <v>-0.2988</v>
+        <v>3.1447</v>
       </c>
       <c t="n" r="D278">
-        <v>0.9455</v>
+        <v>-61.3858</v>
       </c>
       <c t="n" r="E278">
-        <v>-97.8891</v>
+        <v>-99.1136</v>
       </c>
       <c t="n" r="F278">
-        <v>0.8311</v>
+        <v>-98.1739</v>
       </c>
     </row>
     <row r="279">
       <c t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">NBA</t>
+          <t xml:space="preserve">MAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C279">
-        <v>-29.3166</v>
-      </c>
-      <c t="n" r="D279">
-        <v>-32.9216</v>
-      </c>
-      <c t="n" r="E279">
-        <v>1622.0389</v>
-      </c>
-      <c t="n" r="F279">
-        <v>-33.0242</v>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. MAANAA LEVENT PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="280">
       <c t="inlineStr" r="A280">
         <is>
-          <t xml:space="preserve">NP5</t>
+          <t xml:space="preserve">NGM</t>
         </is>
       </c>
       <c t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C280">
+        <v>-0.2988</v>
+      </c>
+      <c t="n" r="D280">
+        <v>0.9074</v>
+      </c>
+      <c t="n" r="E280">
+        <v>-97.7611</v>
+      </c>
+      <c t="n" r="F280">
+        <v>0.8311</v>
       </c>
     </row>
     <row r="281">
       <c t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">ND4</t>
+          <t xml:space="preserve">NBA</t>
         </is>
       </c>
       <c t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C281">
+        <v>-29.2836</v>
+      </c>
+      <c t="n" r="D281">
+        <v>-32.9171</v>
+      </c>
+      <c t="n" r="E281">
+        <v>1640.2534</v>
+      </c>
+      <c t="n" r="F281">
+        <v>-33.0291</v>
       </c>
     </row>
     <row r="282">
       <c t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">NIP</t>
+          <t xml:space="preserve">NP5</t>
         </is>
       </c>
       <c t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C282">
-        <v>-0.5258</v>
-      </c>
-      <c t="n" r="D282">
-        <v>-29.8484</v>
-      </c>
-      <c t="n" r="E282">
-        <v>4930.0205</v>
-      </c>
-      <c t="n" r="F282">
-        <v>12086.5408</v>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="283">
       <c t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">NPO</t>
+          <t xml:space="preserve">ND4</t>
         </is>
       </c>
       <c t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C283">
-        <v>-0.0265</v>
-      </c>
-      <c t="n" r="D283">
-        <v>-0.0809</v>
-      </c>
-      <c t="n" r="F283">
-        <v>-0.0028</v>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="284">
       <c t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">NR3</t>
+          <t xml:space="preserve">NIP</t>
         </is>
       </c>
       <c t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C284">
+        <v>-0.4558</v>
+      </c>
+      <c t="n" r="D284">
+        <v>-29.8326</v>
+      </c>
+      <c t="n" r="E284">
+        <v>4951.9575</v>
+      </c>
+      <c t="n" r="F284">
+        <v>12087.6221</v>
       </c>
     </row>
     <row r="285">
       <c t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">NU3</t>
+          <t xml:space="preserve">NPO</t>
         </is>
       </c>
       <c t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C285">
+        <v>-0.0170</v>
+      </c>
+      <c t="n" r="D285">
+        <v>-0.0597</v>
+      </c>
+      <c t="n" r="F285">
+        <v>-0.0069</v>
       </c>
     </row>
     <row r="286">
       <c t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">OG4</t>
+          <t xml:space="preserve">NR3</t>
         </is>
       </c>
       <c t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">OGG</t>
+          <t xml:space="preserve">NU3</t>
         </is>
       </c>
       <c t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C287">
-        <v>-74.0068</v>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="288">
       <c t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">OLN</t>
+          <t xml:space="preserve">OG4</t>
         </is>
       </c>
       <c t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">FGY</t>
+          <t xml:space="preserve">OGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C289">
-        <v>0.7451</v>
-      </c>
-      <c t="n" r="D289">
-        <v>2.7743</v>
-      </c>
-      <c t="n" r="E289">
-        <v>10.4732</v>
-      </c>
-      <c t="n" r="F289">
-        <v>3.1428</v>
+        <v>-74.0642</v>
       </c>
     </row>
     <row r="290">
       <c t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">BCP</t>
+          <t xml:space="preserve">OLN</t>
         </is>
       </c>
       <c t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">GF4</t>
+          <t xml:space="preserve">FGY</t>
         </is>
       </c>
       <c t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C291">
-        <v>-25.4480</v>
+        <v>0.7365</v>
       </c>
       <c t="n" r="D291">
-        <v>-56.6852</v>
+        <v>2.7579</v>
       </c>
       <c t="n" r="E291">
-        <v>-56.6945</v>
+        <v>10.3845</v>
       </c>
       <c t="n" r="F291">
-        <v>-56.2096</v>
+        <v>3.1485</v>
       </c>
     </row>
     <row r="292">
       <c t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">OGK</t>
+          <t xml:space="preserve">BCP</t>
         </is>
       </c>
       <c t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. GENYAP KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">BP2</t>
+          <t xml:space="preserve">GF4</t>
         </is>
       </c>
       <c t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C293">
+        <v>-26.4456</v>
+      </c>
+      <c t="n" r="D293">
+        <v>-57.3572</v>
+      </c>
+      <c t="n" r="E293">
+        <v>-57.3283</v>
+      </c>
+      <c t="n" r="F293">
+        <v>-56.8417</v>
       </c>
     </row>
     <row r="294">
       <c t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">ORF</t>
+          <t xml:space="preserve">OGK</t>
         </is>
       </c>
       <c t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AGREGA PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C294">
-        <v>-0.0050</v>
-      </c>
-      <c t="n" r="D294">
-        <v>-0.0050</v>
-      </c>
-      <c t="n" r="E294">
-        <v>-0.0050</v>
-      </c>
-      <c t="n" r="F294">
-        <v>-0.0050</v>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. GENYAP KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="295">
       <c t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">OAZ</t>
+          <t xml:space="preserve">BP2</t>
         </is>
       </c>
       <c t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYYILDIZ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C295">
-        <v>-0.0050</v>
-      </c>
-      <c t="n" r="D295">
-        <v>-0.0050</v>
-      </c>
-      <c t="n" r="E295">
-        <v>-0.0050</v>
-      </c>
-      <c t="n" r="F295">
-        <v>-0.0050</v>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="296">
       <c t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">OO4</t>
+          <t xml:space="preserve">ORF</t>
         </is>
       </c>
       <c t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AGREGA PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C296">
+        <v>-0.0050</v>
+      </c>
+      <c t="n" r="D296">
+        <v>-0.0050</v>
+      </c>
+      <c t="n" r="E296">
+        <v>-0.0050</v>
+      </c>
+      <c t="n" r="F296">
+        <v>-0.0050</v>
       </c>
     </row>
     <row r="297">
       <c t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">OO3</t>
+          <t xml:space="preserve">OAZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYYILDIZ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C297">
+        <v>-0.0050</v>
+      </c>
+      <c t="n" r="D297">
+        <v>-0.0050</v>
+      </c>
+      <c t="n" r="E297">
+        <v>-4.9948</v>
+      </c>
+      <c t="n" r="F297">
+        <v>-0.0050</v>
       </c>
     </row>
     <row r="298">
       <c t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">BCI</t>
+          <t xml:space="preserve">OO4</t>
         </is>
       </c>
       <c t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C298">
-        <v>3.2768</v>
-      </c>
-      <c t="n" r="D298">
-        <v>9.9987</v>
-      </c>
-      <c t="n" r="E298">
-        <v>20.8834</v>
-      </c>
-      <c t="n" r="F298">
-        <v>11.5281</v>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="299">
       <c t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">PGN</t>
+          <t xml:space="preserve">OO3</t>
         </is>
       </c>
       <c t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C299">
-        <v>3.1927</v>
-      </c>
-      <c t="n" r="D299">
-        <v>9.2087</v>
-      </c>
-      <c t="n" r="F299">
-        <v>10.7377</v>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="300">
       <c t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">DDG</t>
+          <t xml:space="preserve">BCI</t>
         </is>
       </c>
       <c t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C300">
+        <v>3.5424</v>
+      </c>
+      <c t="n" r="D300">
+        <v>10.2683</v>
+      </c>
+      <c t="n" r="E300">
+        <v>21.2047</v>
+      </c>
+      <c t="n" r="F300">
+        <v>11.9334</v>
       </c>
     </row>
     <row r="301">
       <c t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">KCI</t>
+          <t xml:space="preserve">PGN</t>
         </is>
       </c>
       <c t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C301">
-        <v>3.7484</v>
+        <v>3.4545</v>
       </c>
       <c t="n" r="D301">
-        <v>11.5326</v>
+        <v>9.4748</v>
       </c>
       <c t="n" r="F301">
-        <v>13.2541</v>
+        <v>11.1410</v>
       </c>
     </row>
     <row r="302">
       <c t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">UUG</t>
+          <t xml:space="preserve">DDG</t>
         </is>
       </c>
       <c t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C302">
-        <v>-69.9261</v>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="303">
       <c t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">GY2</t>
+          <t xml:space="preserve">KCI</t>
         </is>
       </c>
       <c t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">QINVEST PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C303">
-        <v>-0.0263</v>
+        <v>4.0382</v>
       </c>
       <c t="n" r="D303">
-        <v>-1.2779</v>
+        <v>11.8255</v>
+      </c>
+      <c t="n" r="F303">
+        <v>13.6987</v>
       </c>
     </row>
     <row r="304">
       <c t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">GM1</t>
+          <t xml:space="preserve">UUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">QİNVEST PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C304">
-        <v>1.0004</v>
-      </c>
-      <c t="n" r="D304">
-        <v>5.8596</v>
-      </c>
-      <c t="n" r="E304">
-        <v>14.6163</v>
-      </c>
-      <c t="n" r="F304">
-        <v>6.8044</v>
+        <v>-69.7205</v>
       </c>
     </row>
     <row r="305">
       <c t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">RI5</t>
+          <t xml:space="preserve">GY2</t>
         </is>
       </c>
       <c t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">QINVEST PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C305">
+        <v>-0.0031</v>
+      </c>
+      <c t="n" r="D305">
+        <v>-1.2558</v>
       </c>
     </row>
     <row r="306">
       <c t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">RE5</t>
+          <t xml:space="preserve">GM1</t>
         </is>
       </c>
       <c t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">QİNVEST PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C306">
+        <v>1.0788</v>
+      </c>
+      <c t="n" r="D306">
+        <v>6.0919</v>
+      </c>
+      <c t="n" r="E306">
+        <v>14.5645</v>
+      </c>
+      <c t="n" r="F306">
+        <v>7.1189</v>
       </c>
     </row>
     <row r="307">
       <c t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">RKP</t>
+          <t xml:space="preserve">RI5</t>
         </is>
       </c>
       <c t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C307">
-        <v>1.6514</v>
-      </c>
-      <c t="n" r="D307">
-        <v>3.7770</v>
-      </c>
-      <c t="n" r="E307">
-        <v>12.0968</v>
-      </c>
-      <c t="n" r="F307">
-        <v>4.9355</v>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="308">
       <c t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">RI4</t>
+          <t xml:space="preserve">RE5</t>
         </is>
       </c>
       <c t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">RE4</t>
+          <t xml:space="preserve">RKP</t>
         </is>
       </c>
       <c t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C309">
+        <v>1.9605</v>
+      </c>
+      <c t="n" r="D309">
+        <v>3.9165</v>
+      </c>
+      <c t="n" r="E309">
+        <v>12.2913</v>
+      </c>
+      <c t="n" r="F309">
+        <v>5.1732</v>
       </c>
     </row>
     <row r="310">
       <c t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">EPG</t>
+          <t xml:space="preserve">RI4</t>
         </is>
       </c>
       <c t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C310">
-        <v>-0.0870</v>
-      </c>
-      <c t="n" r="D310">
-        <v>-0.2220</v>
-      </c>
-      <c t="n" r="E310">
-        <v>0.5997</v>
-      </c>
-      <c t="n" r="F310">
-        <v>-0.2439</v>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="311">
       <c t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">RE2</t>
+          <t xml:space="preserve">RE4</t>
         </is>
       </c>
       <c t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">RIP</t>
+          <t xml:space="preserve">EPG</t>
         </is>
       </c>
       <c t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İSTANBUL PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C312">
+        <v>-0.0745</v>
+      </c>
+      <c t="n" r="D312">
+        <v>-0.2175</v>
+      </c>
+      <c t="n" r="E312">
+        <v>0.6052</v>
+      </c>
+      <c t="n" r="F312">
+        <v>-0.2409</v>
       </c>
     </row>
     <row r="313">
       <c t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">RE3</t>
+          <t xml:space="preserve">RE2</t>
         </is>
       </c>
       <c t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C313">
-        <v>-0.0597</v>
-      </c>
-      <c t="n" r="D313">
-        <v>-0.1495</v>
-      </c>
-      <c t="n" r="F313">
-        <v>-0.1672</v>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="314">
       <c t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">REI</t>
+          <t xml:space="preserve">RIP</t>
         </is>
       </c>
       <c t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İSTANBUL PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">RNG</t>
+          <t xml:space="preserve">RE3</t>
         </is>
       </c>
       <c t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C315">
-        <v>-0.1593</v>
+        <v>-0.0525</v>
       </c>
       <c t="n" r="D315">
-        <v>-0.3507</v>
-      </c>
-      <c t="n" r="E315">
-        <v>3.0292</v>
+        <v>-0.1471</v>
       </c>
       <c t="n" r="F315">
-        <v>-0.3798</v>
+        <v>-0.1657</v>
       </c>
     </row>
     <row r="316">
       <c t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">ROR</t>
+          <t xml:space="preserve">REI</t>
         </is>
       </c>
       <c t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C316">
-        <v>-0.1117</v>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="317">
       <c t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">RGU</t>
+          <t xml:space="preserve">RNG</t>
         </is>
       </c>
       <c t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C317">
+        <v>-0.1543</v>
+      </c>
+      <c t="n" r="D317">
+        <v>-0.3506</v>
+      </c>
+      <c t="n" r="E317">
+        <v>3.0285</v>
+      </c>
+      <c t="n" r="F317">
+        <v>-0.3821</v>
       </c>
     </row>
     <row r="318">
       <c t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">RZB</t>
+          <t xml:space="preserve">ROR</t>
         </is>
       </c>
       <c t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. SEBA CENTER GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="E318">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="F318">
-        <v>0.0000</v>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C318">
+        <v>-0.1281</v>
       </c>
     </row>
     <row r="319">
       <c t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">SEB</t>
+          <t xml:space="preserve">RGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. SEBA CENTER PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">RTR</t>
+          <t xml:space="preserve">RZB</t>
         </is>
       </c>
       <c t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. TRAKYA GELİŞİM GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. SEBA CENTER GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="E320">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="F320">
+        <v>0.0000</v>
       </c>
     </row>
     <row r="321">
       <c t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">TCE</t>
+          <t xml:space="preserve">SEB</t>
         </is>
       </c>
       <c t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">TACİRLER PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C321">
-        <v>-0.1428</v>
-      </c>
-      <c t="n" r="D321">
-        <v>-0.1618</v>
-      </c>
-      <c t="n" r="F321">
-        <v>-0.1473</v>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. SEBA CENTER PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="322">
       <c t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">TN1</t>
+          <t xml:space="preserve">RTR</t>
         </is>
       </c>
       <c t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. TRAKYA GELİŞİM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">TUC</t>
+          <t xml:space="preserve">TCE</t>
         </is>
       </c>
       <c t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">TACİRLER PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C323">
+        <v>-0.1174</v>
+      </c>
+      <c t="n" r="D323">
+        <v>-0.1486</v>
+      </c>
+      <c t="n" r="F323">
+        <v>-0.1320</v>
       </c>
     </row>
     <row r="324">
       <c t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">ZEP</t>
+          <t xml:space="preserve">TN1</t>
         </is>
       </c>
       <c t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. EMLAK KONUT GELİR PAYLAŞIMI BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C324">
-        <v>2.9535</v>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="325">
       <c t="inlineStr" r="A325">
         <is>
+          <t xml:space="preserve">TUC</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B325">
+        <is>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c t="inlineStr" r="A326">
+        <is>
+          <t xml:space="preserve">ZEP</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B326">
+        <is>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. EMLAK KONUT GELİR PAYLAŞIMI BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C326">
+        <v>2.7790</v>
+      </c>
+    </row>
+    <row r="327">
+      <c t="inlineStr" r="A327">
+        <is>
           <t xml:space="preserve">YOR</t>
         </is>
       </c>
-      <c t="inlineStr" r="B325">
+      <c t="inlineStr" r="B327">
         <is>
           <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ORKİDE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
-      <c t="n" r="C325">
+      <c t="n" r="C327">
         <v>0.0000</v>
       </c>
-      <c t="n" r="D325">
+      <c t="n" r="D327">
         <v>0.0000</v>
       </c>
-      <c t="n" r="E325">
-        <v>-0.0212</v>
-      </c>
-      <c t="n" r="F325">
+      <c t="n" r="E327">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="F327">
         <v>-0.0212</v>
       </c>
     </row>

--- a/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
@@ -280,22 +280,22 @@
         </is>
       </c>
       <c t="n" r="C3">
-        <v>38.4340</v>
+        <v>38.5442</v>
       </c>
       <c t="n" r="D3">
-        <v>663.3135</v>
+        <v>663.9365</v>
       </c>
       <c t="n" r="E3">
-        <v>689.8545</v>
+        <v>690.5221</v>
       </c>
       <c t="n" r="F3">
-        <v>657.9327</v>
+        <v>658.5364</v>
       </c>
       <c t="n" r="G3">
-        <v>614.8973</v>
+        <v>615.4397</v>
       </c>
       <c t="n" r="H3">
-        <v>1536.9019</v>
+        <v>768.8653</v>
       </c>
     </row>
     <row r="4">
@@ -310,19 +310,19 @@
         </is>
       </c>
       <c t="n" r="C4">
-        <v>16.3799</v>
+        <v>16.4096</v>
       </c>
       <c t="n" r="D4">
-        <v>20.4247</v>
+        <v>20.4133</v>
       </c>
       <c t="n" r="E4">
-        <v>250.0029</v>
+        <v>250.4856</v>
       </c>
       <c t="n" r="F4">
-        <v>20.9993</v>
+        <v>21.0302</v>
       </c>
       <c t="n" r="G4">
-        <v>371.3404</v>
+        <v>373.6999</v>
       </c>
     </row>
     <row r="5">
@@ -337,19 +337,19 @@
         </is>
       </c>
       <c t="n" r="C5">
-        <v>0.9151</v>
+        <v>0.9248</v>
       </c>
       <c t="n" r="D5">
-        <v>3.2844</v>
+        <v>2.6400</v>
       </c>
       <c t="n" r="E5">
-        <v>27.7233</v>
+        <v>27.7278</v>
       </c>
       <c t="n" r="F5">
-        <v>3.3581</v>
+        <v>3.3680</v>
       </c>
       <c t="n" r="G5">
-        <v>363.8036</v>
+        <v>362.1213</v>
       </c>
     </row>
     <row r="6">
@@ -364,22 +364,22 @@
         </is>
       </c>
       <c t="n" r="C6">
-        <v>-0.4393</v>
+        <v>-0.4334</v>
       </c>
       <c t="n" r="D6">
-        <v>41.6652</v>
+        <v>41.6864</v>
       </c>
       <c t="n" r="E6">
-        <v>52.7432</v>
+        <v>52.7639</v>
       </c>
       <c t="n" r="F6">
-        <v>42.2849</v>
+        <v>42.2934</v>
       </c>
       <c t="n" r="G6">
-        <v>239.7554</v>
+        <v>239.7901</v>
       </c>
       <c t="n" r="H6">
-        <v>332.6875</v>
+        <v>332.7632</v>
       </c>
     </row>
     <row r="7">
@@ -394,22 +394,22 @@
         </is>
       </c>
       <c t="n" r="C7">
-        <v>-0.0184</v>
+        <v>-0.0188</v>
       </c>
       <c t="n" r="D7">
         <v>-0.0510</v>
       </c>
       <c t="n" r="E7">
-        <v>192.5053</v>
+        <v>192.5057</v>
       </c>
       <c t="n" r="F7">
-        <v>-0.0579</v>
+        <v>-0.0583</v>
       </c>
       <c t="n" r="G7">
-        <v>191.4236</v>
+        <v>191.4237</v>
       </c>
       <c t="n" r="H7">
-        <v>166601.9938</v>
+        <v>166674.2475</v>
       </c>
     </row>
     <row r="8">
@@ -424,19 +424,19 @@
         </is>
       </c>
       <c t="n" r="C8">
-        <v>-0.0171</v>
+        <v>-0.0165</v>
       </c>
       <c t="n" r="D8">
-        <v>4.0120</v>
+        <v>4.0113</v>
       </c>
       <c t="n" r="E8">
-        <v>3.9832</v>
+        <v>3.9846</v>
       </c>
       <c t="n" r="F8">
-        <v>4.0194</v>
+        <v>4.0200</v>
       </c>
       <c t="n" r="G8">
-        <v>152.6891</v>
+        <v>152.7062</v>
       </c>
     </row>
     <row r="9">
@@ -451,628 +451,628 @@
         </is>
       </c>
       <c t="n" r="C9">
-        <v>0.2810</v>
+        <v>0.7321</v>
       </c>
       <c t="n" r="D9">
-        <v>0.5991</v>
+        <v>1.0503</v>
       </c>
       <c t="n" r="E9">
-        <v>140.3522</v>
+        <v>141.4673</v>
       </c>
       <c t="n" r="F9">
-        <v>1.0740</v>
+        <v>1.5287</v>
       </c>
       <c t="n" r="G9">
-        <v>142.6196</v>
+        <v>143.4277</v>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">TGI</t>
+          <t xml:space="preserve">PBA</t>
         </is>
       </c>
       <c t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALBATROS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C10">
-        <v>1.3181</v>
+        <v>65.7297</v>
       </c>
       <c t="n" r="D10">
-        <v>5.0691</v>
+        <v>68.2357</v>
       </c>
       <c t="n" r="E10">
-        <v>23.7338</v>
+        <v>69.7721</v>
       </c>
       <c t="n" r="F10">
-        <v>5.4665</v>
+        <v>55.1256</v>
       </c>
       <c t="n" r="G10">
-        <v>108.5025</v>
+        <v>88.2723</v>
+      </c>
+      <c t="n" r="H10">
+        <v>114.8975</v>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">PBA</t>
+          <t xml:space="preserve">AB1</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALBATROS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKFEN GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C11">
-        <v>65.7232</v>
+        <v>1.8155</v>
       </c>
       <c t="n" r="D11">
-        <v>68.2410</v>
+        <v>33.7358</v>
       </c>
       <c t="n" r="E11">
-        <v>69.7206</v>
+        <v>76.7799</v>
       </c>
       <c t="n" r="F11">
-        <v>55.1195</v>
+        <v>33.7737</v>
       </c>
       <c t="n" r="G11">
-        <v>88.3194</v>
+        <v>82.7312</v>
       </c>
       <c t="n" r="H11">
-        <v>114.8904</v>
+        <v>299.3021</v>
+      </c>
+      <c t="n" r="I11">
+        <v>1680.4858</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">AB1</t>
+          <t xml:space="preserve">VVF</t>
         </is>
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">AKFEN GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C12">
-        <v>1.6796</v>
+        <v>0.2502</v>
       </c>
       <c t="n" r="D12">
-        <v>33.5616</v>
+        <v>1.3946</v>
       </c>
       <c t="n" r="E12">
-        <v>76.6123</v>
+        <v>38.8293</v>
       </c>
       <c t="n" r="F12">
-        <v>33.5952</v>
+        <v>1.2928</v>
       </c>
       <c t="n" r="G12">
-        <v>82.4916</v>
+        <v>61.8246</v>
       </c>
       <c t="n" r="H12">
-        <v>298.7604</v>
+        <v>327.6451</v>
       </c>
       <c t="n" r="I12">
-        <v>1678.2107</v>
+        <v>1093.5944</v>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">VVF</t>
+          <t xml:space="preserve">NFG</t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C13">
-        <v>0.2308</v>
+        <v>-0.1926</v>
       </c>
       <c t="n" r="D13">
-        <v>1.4069</v>
+        <v>-1.2911</v>
       </c>
       <c t="n" r="E13">
-        <v>38.9221</v>
+        <v>19.9658</v>
       </c>
       <c t="n" r="F13">
-        <v>1.2731</v>
+        <v>-1.0389</v>
       </c>
       <c t="n" r="G13">
-        <v>62.2204</v>
+        <v>61.5458</v>
       </c>
       <c t="n" r="H13">
-        <v>327.5609</v>
-      </c>
-      <c t="n" r="I13">
-        <v>1093.3631</v>
+        <v>687.4074</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">NFG</t>
+          <t xml:space="preserve">TNG</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TUNA PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C14">
-        <v>-0.1905</v>
+        <v>3.6930</v>
       </c>
       <c t="n" r="D14">
-        <v>-1.2714</v>
+        <v>10.2107</v>
       </c>
       <c t="n" r="E14">
-        <v>19.9762</v>
+        <v>27.7339</v>
       </c>
       <c t="n" r="F14">
-        <v>-1.0368</v>
+        <v>11.1286</v>
       </c>
       <c t="n" r="G14">
-        <v>61.6102</v>
-      </c>
-      <c t="n" r="H14">
-        <v>687.8717</v>
+        <v>58.6057</v>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">TNG</t>
+          <t xml:space="preserve">AR9</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TUNA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C15">
-        <v>3.5784</v>
+        <v>-0.1175</v>
       </c>
       <c t="n" r="D15">
-        <v>10.2367</v>
+        <v>0.2719</v>
       </c>
       <c t="n" r="E15">
-        <v>27.7308</v>
+        <v>60.0179</v>
       </c>
       <c t="n" r="F15">
-        <v>11.0058</v>
+        <v>-4.4515</v>
       </c>
       <c t="n" r="G15">
-        <v>58.9444</v>
+        <v>58.5923</v>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">AR9</t>
+          <t xml:space="preserve">NG8</t>
         </is>
       </c>
       <c t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C16">
-        <v>-0.1147</v>
+        <v>3.4549</v>
       </c>
       <c t="n" r="D16">
-        <v>0.2650</v>
+        <v>15.9008</v>
       </c>
       <c t="n" r="E16">
-        <v>60.0181</v>
+        <v>26.5867</v>
       </c>
       <c t="n" r="F16">
-        <v>-4.4489</v>
+        <v>17.9959</v>
       </c>
       <c t="n" r="G16">
-        <v>58.5944</v>
+        <v>57.6053</v>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">NG8</t>
+          <t xml:space="preserve">HP2</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C17">
-        <v>3.3634</v>
+        <v>0.7395</v>
       </c>
       <c t="n" r="D17">
-        <v>13.7107</v>
+        <v>1.9263</v>
       </c>
       <c t="n" r="E17">
-        <v>26.6098</v>
+        <v>51.3543</v>
       </c>
       <c t="n" r="F17">
-        <v>17.8915</v>
+        <v>48.1779</v>
       </c>
       <c t="n" r="G17">
-        <v>58.0267</v>
+        <v>57.0520</v>
+      </c>
+      <c t="n" r="H17">
+        <v>463.7955</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">HP2</t>
+          <t xml:space="preserve">VBI</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C18">
-        <v>0.7355</v>
+        <v>3.7489</v>
       </c>
       <c t="n" r="D18">
-        <v>1.9256</v>
+        <v>10.3797</v>
       </c>
       <c t="n" r="E18">
-        <v>51.3542</v>
+        <v>22.2001</v>
       </c>
       <c t="n" r="F18">
-        <v>48.1720</v>
+        <v>11.8672</v>
       </c>
       <c t="n" r="G18">
-        <v>57.0549</v>
-      </c>
-      <c t="n" r="H18">
-        <v>463.6040</v>
+        <v>55.8535</v>
       </c>
     </row>
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">VBI</t>
+          <t xml:space="preserve">VIK</t>
         </is>
       </c>
       <c t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C19">
-        <v>3.6296</v>
+        <v>3.7485</v>
       </c>
       <c t="n" r="D19">
-        <v>10.3709</v>
+        <v>10.3786</v>
       </c>
       <c t="n" r="E19">
-        <v>22.2055</v>
+        <v>22.1976</v>
       </c>
       <c t="n" r="F19">
-        <v>11.7386</v>
+        <v>11.8659</v>
       </c>
       <c t="n" r="G19">
-        <v>56.3131</v>
+        <v>55.8455</v>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">VIK</t>
+          <t xml:space="preserve">OGC</t>
         </is>
       </c>
       <c t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÇATI KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C20">
-        <v>3.6293</v>
+        <v>0.2578</v>
       </c>
       <c t="n" r="D20">
-        <v>10.3698</v>
+        <v>0.8077</v>
       </c>
       <c t="n" r="E20">
-        <v>22.2029</v>
+        <v>1.3233</v>
       </c>
       <c t="n" r="F20">
-        <v>11.7374</v>
+        <v>0.8907</v>
       </c>
       <c t="n" r="G20">
-        <v>56.3051</v>
+        <v>55.1749</v>
+      </c>
+      <c t="n" r="H20">
+        <v>410.2755</v>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">BRE</t>
+          <t xml:space="preserve">RGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. TSL PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C21">
-        <v>5.8091</v>
+        <v>-0.0294</v>
       </c>
       <c t="n" r="D21">
-        <v>23.5889</v>
+        <v>6.4413</v>
       </c>
       <c t="n" r="E21">
-        <v>28.0627</v>
+        <v>19.5817</v>
       </c>
       <c t="n" r="F21">
-        <v>29.2276</v>
+        <v>6.7981</v>
       </c>
       <c t="n" r="G21">
-        <v>55.3558</v>
+        <v>54.8295</v>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">OGC</t>
+          <t xml:space="preserve">BRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÇATI KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C22">
-        <v>0.2539</v>
+        <v>5.8655</v>
       </c>
       <c t="n" r="D22">
-        <v>0.8036</v>
+        <v>23.6185</v>
       </c>
       <c t="n" r="E22">
-        <v>54.7589</v>
+        <v>28.1429</v>
       </c>
       <c t="n" r="F22">
-        <v>0.8867</v>
+        <v>29.2965</v>
       </c>
       <c t="n" r="G22">
-        <v>55.1602</v>
-      </c>
-      <c t="n" r="H22">
-        <v>410.2554</v>
+        <v>54.4696</v>
       </c>
     </row>
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">RGF</t>
+          <t xml:space="preserve">OYK</t>
         </is>
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. TSL PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ÇEŞME GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C23">
-        <v>-0.0454</v>
+        <v>-0.1974</v>
       </c>
       <c t="n" r="D23">
-        <v>6.4483</v>
+        <v>-0.2277</v>
       </c>
       <c t="n" r="E23">
-        <v>34.7521</v>
+        <v>55.3983</v>
       </c>
       <c t="n" r="F23">
-        <v>6.7809</v>
+        <v>-0.2276</v>
       </c>
       <c t="n" r="G23">
-        <v>54.8913</v>
+        <v>54.4175</v>
+      </c>
+      <c t="n" r="H23">
+        <v>172.5362</v>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">OYK</t>
+          <t xml:space="preserve">NO1</t>
         </is>
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ÇEŞME GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C24">
-        <v>-0.1975</v>
+        <v>4.2614</v>
       </c>
       <c t="n" r="D24">
-        <v>-0.2277</v>
+        <v>12.4414</v>
       </c>
       <c t="n" r="E24">
-        <v>55.3956</v>
+        <v>22.7164</v>
       </c>
       <c t="n" r="F24">
-        <v>-0.2277</v>
+        <v>14.2214</v>
       </c>
       <c t="n" r="G24">
-        <v>54.4186</v>
-      </c>
-      <c t="n" r="H24">
-        <v>172.5429</v>
+        <v>52.9474</v>
       </c>
     </row>
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">NO1</t>
+          <t xml:space="preserve">YD7</t>
         </is>
       </c>
       <c t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.KARDELEN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C25">
-        <v>4.0431</v>
+        <v>-0.2549</v>
       </c>
       <c t="n" r="D25">
-        <v>9.8262</v>
+        <v>-1.4334</v>
       </c>
       <c t="n" r="E25">
-        <v>22.5906</v>
+        <v>28.4783</v>
       </c>
       <c t="n" r="F25">
-        <v>13.9823</v>
+        <v>-1.6953</v>
       </c>
       <c t="n" r="G25">
-        <v>53.1711</v>
+        <v>49.0209</v>
+      </c>
+      <c t="n" r="H25">
+        <v>168.2097</v>
+      </c>
+      <c t="n" r="I25">
+        <v>1143.7179</v>
       </c>
     </row>
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">YD7</t>
+          <t xml:space="preserve">RAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.KARDELEN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. AVRUPA-ANADOLU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C26">
-        <v>-0.2483</v>
+        <v>5.2470</v>
       </c>
       <c t="n" r="D26">
-        <v>-1.4530</v>
+        <v>12.1236</v>
       </c>
       <c t="n" r="E26">
-        <v>28.4774</v>
+        <v>21.4125</v>
       </c>
       <c t="n" r="F26">
-        <v>-1.6888</v>
+        <v>13.3868</v>
       </c>
       <c t="n" r="G26">
-        <v>49.0056</v>
-      </c>
-      <c t="n" r="H26">
-        <v>168.1622</v>
-      </c>
-      <c t="n" r="I26">
-        <v>1143.8004</v>
+        <v>48.4177</v>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">RAA</t>
+          <t xml:space="preserve">YD5</t>
         </is>
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. AVRUPA-ANADOLU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C27">
-        <v>5.2062</v>
+        <v>-0.3224</v>
       </c>
       <c t="n" r="D27">
-        <v>12.1777</v>
+        <v>-0.4400</v>
       </c>
       <c t="n" r="E27">
-        <v>21.4912</v>
+        <v>16.0243</v>
       </c>
       <c t="n" r="F27">
-        <v>13.3428</v>
+        <v>-0.6099</v>
       </c>
       <c t="n" r="G27">
-        <v>48.9044</v>
+        <v>48.0917</v>
+      </c>
+      <c t="n" r="H27">
+        <v>196.8592</v>
+      </c>
+      <c t="n" r="I27">
+        <v>1322.6018</v>
       </c>
     </row>
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">YD5</t>
+          <t xml:space="preserve">NG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C28">
-        <v>-0.3173</v>
+        <v>0.4648</v>
       </c>
       <c t="n" r="D28">
-        <v>-0.4466</v>
+        <v>6.3053</v>
       </c>
       <c t="n" r="E28">
-        <v>16.0231</v>
+        <v>43.8100</v>
       </c>
       <c t="n" r="F28">
-        <v>-0.6048</v>
+        <v>5.9789</v>
       </c>
       <c t="n" r="G28">
-        <v>48.0304</v>
+        <v>45.3199</v>
       </c>
       <c t="n" r="H28">
-        <v>196.7634</v>
-      </c>
-      <c t="n" r="I28">
-        <v>1322.6747</v>
+        <v>461.9253</v>
       </c>
     </row>
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">NG7</t>
+          <t xml:space="preserve">YYF</t>
         </is>
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C29">
-        <v>0.4478</v>
+        <v>3.2293</v>
       </c>
       <c t="n" r="D29">
-        <v>6.3322</v>
+        <v>8.8464</v>
       </c>
       <c t="n" r="E29">
-        <v>43.8113</v>
+        <v>19.1909</v>
       </c>
       <c t="n" r="F29">
-        <v>5.9610</v>
+        <v>10.3354</v>
       </c>
       <c t="n" r="G29">
-        <v>45.3198</v>
-      </c>
-      <c t="n" r="H29">
-        <v>462.0295</v>
+        <v>44.5413</v>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">YYF</t>
+          <t xml:space="preserve">TGI</t>
         </is>
       </c>
       <c t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C30">
-        <v>3.1266</v>
+        <v>1.3492</v>
       </c>
       <c t="n" r="D30">
-        <v>8.8385</v>
+        <v>5.0639</v>
       </c>
       <c t="n" r="E30">
-        <v>19.1955</v>
+        <v>23.9206</v>
       </c>
       <c t="n" r="F30">
-        <v>10.2256</v>
+        <v>5.4988</v>
       </c>
       <c t="n" r="G30">
-        <v>44.5805</v>
+        <v>44.3240</v>
       </c>
     </row>
     <row r="31">
@@ -1087,19 +1087,19 @@
         </is>
       </c>
       <c t="n" r="C31">
-        <v>-1.0655</v>
+        <v>-1.0515</v>
       </c>
       <c t="n" r="D31">
-        <v>0.4781</v>
+        <v>0.4793</v>
       </c>
       <c t="n" r="E31">
-        <v>29.4101</v>
+        <v>29.4095</v>
       </c>
       <c t="n" r="F31">
-        <v>1.5859</v>
+        <v>1.6003</v>
       </c>
       <c t="n" r="G31">
-        <v>44.1648</v>
+        <v>44.1598</v>
       </c>
     </row>
     <row r="32">
@@ -1114,19 +1114,19 @@
         </is>
       </c>
       <c t="n" r="C32">
-        <v>2.0891</v>
+        <v>2.1967</v>
       </c>
       <c t="n" r="D32">
-        <v>4.5820</v>
+        <v>4.9212</v>
       </c>
       <c t="n" r="E32">
-        <v>24.1203</v>
+        <v>24.7670</v>
       </c>
       <c t="n" r="F32">
-        <v>8.6367</v>
+        <v>8.7512</v>
       </c>
       <c t="n" r="G32">
-        <v>42.3091</v>
+        <v>42.3891</v>
       </c>
     </row>
     <row r="33">
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c t="n" r="C33">
-        <v>-0.0187</v>
+        <v>-0.0210</v>
       </c>
       <c t="n" r="D33">
-        <v>0.1757</v>
+        <v>0.2470</v>
       </c>
       <c t="n" r="E33">
-        <v>27.2619</v>
+        <v>27.7403</v>
       </c>
       <c t="n" r="F33">
-        <v>0.3228</v>
+        <v>0.3204</v>
       </c>
       <c t="n" r="G33">
-        <v>41.7720</v>
+        <v>41.7825</v>
       </c>
     </row>
     <row r="34">
@@ -1168,22 +1168,25 @@
         </is>
       </c>
       <c t="n" r="C34">
-        <v>0.1616</v>
+        <v>0.1605</v>
       </c>
       <c t="n" r="D34">
-        <v>0.5329</v>
+        <v>0.5340</v>
       </c>
       <c t="n" r="E34">
-        <v>38.6483</v>
+        <v>38.6429</v>
       </c>
       <c t="n" r="F34">
-        <v>0.7344</v>
+        <v>0.7333</v>
       </c>
       <c t="n" r="G34">
-        <v>41.7455</v>
+        <v>41.7431</v>
       </c>
       <c t="n" r="H34">
-        <v>241.8217</v>
+        <v>241.8867</v>
+      </c>
+      <c t="n" r="I34">
+        <v>848.0395</v>
       </c>
     </row>
     <row r="35">
@@ -1198,25 +1201,25 @@
         </is>
       </c>
       <c t="n" r="C35">
-        <v>-0.0775</v>
+        <v>-0.0784</v>
       </c>
       <c t="n" r="D35">
-        <v>-0.3774</v>
+        <v>-0.3341</v>
       </c>
       <c t="n" r="E35">
-        <v>42.2755</v>
+        <v>42.2751</v>
       </c>
       <c t="n" r="F35">
-        <v>-0.4977</v>
+        <v>-0.4986</v>
       </c>
       <c t="n" r="G35">
         <v>41.6633</v>
       </c>
       <c t="n" r="H35">
-        <v>212.7006</v>
+        <v>212.9996</v>
       </c>
       <c t="n" r="I35">
-        <v>720.0143</v>
+        <v>723.3385</v>
       </c>
     </row>
     <row r="36">
@@ -1231,22 +1234,22 @@
         </is>
       </c>
       <c t="n" r="C36">
-        <v>0.1600</v>
+        <v>0.1535</v>
       </c>
       <c t="n" r="D36">
-        <v>0.0142</v>
+        <v>0.0135</v>
       </c>
       <c t="n" r="E36">
-        <v>41.1454</v>
+        <v>41.1467</v>
       </c>
       <c t="n" r="F36">
-        <v>0.2981</v>
+        <v>0.2917</v>
       </c>
       <c t="n" r="G36">
-        <v>41.4626</v>
+        <v>41.4623</v>
       </c>
       <c t="n" r="H36">
-        <v>251.8922</v>
+        <v>251.9383</v>
       </c>
     </row>
     <row r="37">
@@ -1261,25 +1264,25 @@
         </is>
       </c>
       <c t="n" r="C37">
-        <v>0.5399</v>
+        <v>0.5530</v>
       </c>
       <c t="n" r="D37">
-        <v>1.5438</v>
+        <v>1.5452</v>
       </c>
       <c t="n" r="E37">
         <v>28.9772</v>
       </c>
       <c t="n" r="F37">
-        <v>1.4951</v>
+        <v>1.5084</v>
       </c>
       <c t="n" r="G37">
-        <v>40.8346</v>
+        <v>40.7973</v>
       </c>
       <c t="n" r="H37">
-        <v>172.2116</v>
+        <v>172.2282</v>
       </c>
       <c t="n" r="I37">
-        <v>400.3666</v>
+        <v>400.4321</v>
       </c>
     </row>
     <row r="38">
@@ -1294,25 +1297,25 @@
         </is>
       </c>
       <c t="n" r="C38">
-        <v>0.4574</v>
+        <v>0.4609</v>
       </c>
       <c t="n" r="D38">
-        <v>1.7529</v>
+        <v>1.7486</v>
       </c>
       <c t="n" r="E38">
-        <v>16.2042</v>
+        <v>16.2012</v>
       </c>
       <c t="n" r="F38">
-        <v>2.0160</v>
+        <v>2.0195</v>
       </c>
       <c t="n" r="G38">
-        <v>40.2639</v>
+        <v>40.2528</v>
       </c>
       <c t="n" r="H38">
-        <v>295.4192</v>
+        <v>295.3139</v>
       </c>
       <c t="n" r="I38">
-        <v>916.3664</v>
+        <v>916.2844</v>
       </c>
     </row>
     <row r="39">
@@ -1327,25 +1330,25 @@
         </is>
       </c>
       <c t="n" r="C39">
-        <v>1.4009</v>
+        <v>1.4809</v>
       </c>
       <c t="n" r="D39">
-        <v>4.3621</v>
+        <v>4.4272</v>
       </c>
       <c t="n" r="E39">
-        <v>14.4794</v>
+        <v>14.5111</v>
       </c>
       <c t="n" r="F39">
-        <v>3.4006</v>
+        <v>3.4822</v>
       </c>
       <c t="n" r="G39">
-        <v>39.8062</v>
+        <v>39.8793</v>
       </c>
       <c t="n" r="H39">
-        <v>141.3387</v>
+        <v>141.4796</v>
       </c>
       <c t="n" r="I39">
-        <v>260.1093</v>
+        <v>260.3882</v>
       </c>
     </row>
     <row r="40">
@@ -1360,19 +1363,19 @@
         </is>
       </c>
       <c t="n" r="C40">
-        <v>0.6885</v>
+        <v>0.6933</v>
       </c>
       <c t="n" r="D40">
-        <v>2.0327</v>
+        <v>2.0372</v>
       </c>
       <c t="n" r="E40">
-        <v>31.1879</v>
+        <v>31.1440</v>
       </c>
       <c t="n" r="F40">
-        <v>2.6604</v>
+        <v>2.6653</v>
       </c>
       <c t="n" r="G40">
-        <v>38.7950</v>
+        <v>38.6921</v>
       </c>
     </row>
     <row r="41">
@@ -1387,25 +1390,25 @@
         </is>
       </c>
       <c t="n" r="C41">
-        <v>-1.2829</v>
+        <v>-1.2889</v>
       </c>
       <c t="n" r="D41">
-        <v>-0.9274</v>
+        <v>-0.9279</v>
       </c>
       <c t="n" r="E41">
-        <v>23.8423</v>
+        <v>23.8410</v>
       </c>
       <c t="n" r="F41">
-        <v>-0.5135</v>
+        <v>-0.5195</v>
       </c>
       <c t="n" r="G41">
-        <v>38.3739</v>
+        <v>38.3745</v>
       </c>
       <c t="n" r="H41">
-        <v>326.7755</v>
+        <v>326.8208</v>
       </c>
       <c t="n" r="I41">
-        <v>713.3006</v>
+        <v>713.2516</v>
       </c>
     </row>
     <row r="42">
@@ -1420,25 +1423,25 @@
         </is>
       </c>
       <c t="n" r="C42">
-        <v>1.3434</v>
+        <v>1.3904</v>
       </c>
       <c t="n" r="D42">
-        <v>4.1728</v>
+        <v>4.1735</v>
       </c>
       <c t="n" r="E42">
-        <v>13.8710</v>
+        <v>13.8696</v>
       </c>
       <c t="n" r="F42">
-        <v>4.7038</v>
+        <v>4.7524</v>
       </c>
       <c t="n" r="G42">
-        <v>37.4616</v>
+        <v>37.4575</v>
       </c>
       <c t="n" r="H42">
-        <v>179.4454</v>
+        <v>179.3659</v>
       </c>
       <c t="n" r="I42">
-        <v>415.3460</v>
+        <v>415.4173</v>
       </c>
     </row>
     <row r="43">
@@ -1453,22 +1456,22 @@
         </is>
       </c>
       <c t="n" r="C43">
-        <v>-0.6070</v>
+        <v>-0.6252</v>
       </c>
       <c t="n" r="D43">
-        <v>3.9485</v>
+        <v>3.9451</v>
       </c>
       <c t="n" r="E43">
-        <v>32.8791</v>
+        <v>32.8739</v>
       </c>
       <c t="n" r="F43">
-        <v>11.6847</v>
+        <v>11.6642</v>
       </c>
       <c t="n" r="G43">
-        <v>37.2111</v>
+        <v>37.1170</v>
       </c>
       <c t="n" r="H43">
-        <v>827.9473</v>
+        <v>826.2060</v>
       </c>
     </row>
     <row r="44">
@@ -1483,19 +1486,19 @@
         </is>
       </c>
       <c t="n" r="C44">
-        <v>2.6957</v>
+        <v>2.7705</v>
       </c>
       <c t="n" r="D44">
-        <v>7.0236</v>
+        <v>7.0161</v>
       </c>
       <c t="n" r="E44">
-        <v>15.3244</v>
+        <v>15.3130</v>
       </c>
       <c t="n" r="F44">
-        <v>8.1805</v>
+        <v>8.2592</v>
       </c>
       <c t="n" r="G44">
-        <v>35.8039</v>
+        <v>35.8490</v>
       </c>
     </row>
     <row r="45">
@@ -1510,166 +1513,166 @@
         </is>
       </c>
       <c t="n" r="C45">
-        <v>-0.0768</v>
+        <v>-0.0774</v>
       </c>
       <c t="n" r="D45">
-        <v>-0.4222</v>
+        <v>-0.4221</v>
       </c>
       <c t="n" r="E45">
-        <v>32.6745</v>
+        <v>32.6747</v>
       </c>
       <c t="n" r="F45">
-        <v>-0.4733</v>
+        <v>-0.4739</v>
       </c>
       <c t="n" r="G45">
-        <v>35.5502</v>
+        <v>35.5503</v>
       </c>
       <c t="n" r="H45">
-        <v>243.3331</v>
+        <v>243.3410</v>
       </c>
       <c t="n" r="I45">
-        <v>921.6445</v>
+        <v>921.6639</v>
       </c>
     </row>
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">NNP</t>
+          <t xml:space="preserve">FNR</t>
         </is>
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AVANTAJ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C46">
-        <v>0.4670</v>
+        <v>1.9159</v>
       </c>
       <c t="n" r="D46">
-        <v>1.8009</v>
+        <v>-1.7477</v>
       </c>
       <c t="n" r="E46">
-        <v>26.9693</v>
+        <v>15.7780</v>
       </c>
       <c t="n" r="F46">
-        <v>2.1417</v>
+        <v>4.6171</v>
       </c>
       <c t="n" r="G46">
-        <v>34.8928</v>
-      </c>
-      <c t="n" r="H46">
-        <v>575.0190</v>
+        <v>35.2007</v>
       </c>
     </row>
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">RGK</t>
+          <t xml:space="preserve">NNP</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AVANTAJ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C47">
-        <v>-0.0219</v>
+        <v>0.4870</v>
       </c>
       <c t="n" r="D47">
-        <v>-0.1092</v>
+        <v>1.8100</v>
       </c>
       <c t="n" r="E47">
-        <v>34.0435</v>
+        <v>26.8803</v>
       </c>
       <c t="n" r="F47">
-        <v>-0.1137</v>
+        <v>2.1621</v>
       </c>
       <c t="n" r="G47">
-        <v>34.5380</v>
+        <v>34.8309</v>
+      </c>
+      <c t="n" r="H47">
+        <v>575.2487</v>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">FNI</t>
+          <t xml:space="preserve">RGK</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C48">
-        <v>0.5279</v>
+        <v>-0.0224</v>
       </c>
       <c t="n" r="D48">
-        <v>1.5275</v>
+        <v>-0.1093</v>
       </c>
       <c t="n" r="E48">
-        <v>28.4913</v>
+        <v>34.0428</v>
       </c>
       <c t="n" r="F48">
-        <v>1.5120</v>
+        <v>-0.1143</v>
       </c>
       <c t="n" r="G48">
-        <v>33.8552</v>
+        <v>34.5353</v>
       </c>
     </row>
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">NG2</t>
+          <t xml:space="preserve">FNI</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C49">
-        <v>0.2696</v>
+        <v>0.5285</v>
       </c>
       <c t="n" r="D49">
-        <v>0.7660</v>
+        <v>1.5285</v>
       </c>
       <c t="n" r="E49">
-        <v>31.5198</v>
+        <v>28.4869</v>
       </c>
       <c t="n" r="F49">
-        <v>1.1087</v>
+        <v>1.5125</v>
       </c>
       <c t="n" r="G49">
-        <v>33.0085</v>
-      </c>
-      <c t="n" r="H49">
-        <v>317.2330</v>
+        <v>33.8528</v>
       </c>
     </row>
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">FNR</t>
+          <t xml:space="preserve">NG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C50">
-        <v>1.7201</v>
+        <v>0.2682</v>
       </c>
       <c t="n" r="D50">
-        <v>-2.0453</v>
+        <v>0.7665</v>
       </c>
       <c t="n" r="E50">
-        <v>14.0621</v>
+        <v>31.5208</v>
       </c>
       <c t="n" r="F50">
-        <v>4.4160</v>
+        <v>1.1074</v>
       </c>
       <c t="n" r="G50">
-        <v>32.9549</v>
+        <v>33.0089</v>
+      </c>
+      <c t="n" r="H50">
+        <v>316.3629</v>
       </c>
     </row>
     <row r="51">
@@ -1684,202 +1687,202 @@
         </is>
       </c>
       <c t="n" r="C51">
-        <v>0.6586</v>
+        <v>0.4448</v>
       </c>
       <c t="n" r="D51">
-        <v>0.4951</v>
+        <v>0.4842</v>
       </c>
       <c t="n" r="E51">
-        <v>10.8472</v>
+        <v>10.6838</v>
       </c>
       <c t="n" r="F51">
-        <v>0.3318</v>
+        <v>0.1187</v>
       </c>
       <c t="n" r="G51">
-        <v>32.5829</v>
+        <v>32.2818</v>
       </c>
       <c t="n" r="H51">
-        <v>303.4834</v>
+        <v>302.6305</v>
       </c>
     </row>
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">HRE</t>
+          <t xml:space="preserve">AZ3</t>
         </is>
       </c>
       <c t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C52">
-        <v>2.5807</v>
+        <v>-0.0082</v>
       </c>
       <c t="n" r="D52">
-        <v>4.9545</v>
+        <v>-0.2014</v>
       </c>
       <c t="n" r="E52">
-        <v>12.4221</v>
+        <v>32.8664</v>
       </c>
       <c t="n" r="F52">
-        <v>6.4993</v>
+        <v>-2.9933</v>
       </c>
       <c t="n" r="G52">
-        <v>31.7550</v>
+        <v>31.6679</v>
+      </c>
+      <c t="n" r="H52">
+        <v>214.8774</v>
+      </c>
+      <c t="n" r="I52">
+        <v>684.3906</v>
       </c>
     </row>
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">AZ3</t>
+          <t xml:space="preserve">HRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C53">
-        <v>-0.0083</v>
+        <v>2.6472</v>
       </c>
       <c t="n" r="D53">
-        <v>-0.2317</v>
+        <v>4.9499</v>
       </c>
       <c t="n" r="E53">
-        <v>32.8627</v>
+        <v>12.4041</v>
       </c>
       <c t="n" r="F53">
-        <v>-2.9933</v>
+        <v>6.5683</v>
       </c>
       <c t="n" r="G53">
-        <v>31.6647</v>
-      </c>
-      <c t="n" r="H53">
-        <v>214.8526</v>
-      </c>
-      <c t="n" r="I53">
-        <v>679.5806</v>
+        <v>31.4821</v>
       </c>
     </row>
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">FT1</t>
+          <t xml:space="preserve">UCG</t>
         </is>
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C54">
-        <v>0.1077</v>
+        <v>0.1933</v>
       </c>
       <c t="n" r="D54">
-        <v>0.2043</v>
+        <v>-0.5509</v>
       </c>
       <c t="n" r="E54">
-        <v>5.5427</v>
+        <v>31.2305</v>
       </c>
       <c t="n" r="F54">
-        <v>0.2304</v>
+        <v>0.0708</v>
       </c>
       <c t="n" r="G54">
-        <v>31.3538</v>
+        <v>31.2550</v>
+      </c>
+      <c t="n" r="H54">
+        <v>683.9051</v>
+      </c>
+      <c t="n" r="I54">
+        <v>1727.9606</v>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">UCG</t>
+          <t xml:space="preserve">GF1</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C55">
-        <v>0.1846</v>
+        <v>-0.0026</v>
       </c>
       <c t="n" r="D55">
-        <v>-0.5688</v>
+        <v>0.0398</v>
       </c>
       <c t="n" r="E55">
-        <v>31.1520</v>
+        <v>29.1979</v>
       </c>
       <c t="n" r="F55">
-        <v>0.0622</v>
+        <v>0.2675</v>
       </c>
       <c t="n" r="G55">
-        <v>31.2739</v>
-      </c>
-      <c t="n" r="H55">
-        <v>684.3063</v>
-      </c>
-      <c t="n" r="I55">
-        <v>1774.4790</v>
+        <v>31.2183</v>
       </c>
     </row>
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">GF1</t>
+          <t xml:space="preserve">ITG</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. QUASAR İSTANBUL TİCARİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C56">
-        <v>-0.0013</v>
+        <v>0.2117</v>
       </c>
       <c t="n" r="D56">
-        <v>0.2616</v>
+        <v>1.0852</v>
       </c>
       <c t="n" r="E56">
-        <v>29.1956</v>
+        <v>12.9971</v>
       </c>
       <c t="n" r="F56">
-        <v>0.2688</v>
+        <v>1.3427</v>
       </c>
       <c t="n" r="G56">
-        <v>31.2236</v>
+        <v>30.8888</v>
+      </c>
+      <c t="n" r="H56">
+        <v>156.4625</v>
+      </c>
+      <c t="n" r="I56">
+        <v>486.1972</v>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">ITG</t>
+          <t xml:space="preserve">FT1</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. QUASAR İSTANBUL TİCARİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C57">
-        <v>0.2059</v>
+        <v>0.1108</v>
       </c>
       <c t="n" r="D57">
-        <v>1.0854</v>
+        <v>0.2046</v>
       </c>
       <c t="n" r="E57">
-        <v>12.9936</v>
+        <v>5.4323</v>
       </c>
       <c t="n" r="F57">
-        <v>1.3368</v>
+        <v>0.2335</v>
       </c>
       <c t="n" r="G57">
-        <v>30.9060</v>
-      </c>
-      <c t="n" r="H57">
-        <v>156.3226</v>
-      </c>
-      <c t="n" r="I57">
-        <v>486.1387</v>
+        <v>30.8558</v>
       </c>
     </row>
     <row r="58">
@@ -1894,19 +1897,19 @@
         </is>
       </c>
       <c t="n" r="C58">
-        <v>1.5818</v>
+        <v>1.6981</v>
       </c>
       <c t="n" r="D58">
-        <v>2.7771</v>
+        <v>3.0403</v>
       </c>
       <c t="n" r="E58">
-        <v>39.1651</v>
+        <v>39.5913</v>
       </c>
       <c t="n" r="F58">
-        <v>3.4344</v>
+        <v>3.5528</v>
       </c>
       <c t="n" r="G58">
-        <v>30.7485</v>
+        <v>30.8199</v>
       </c>
     </row>
     <row r="59">
@@ -1921,19 +1924,19 @@
         </is>
       </c>
       <c t="n" r="C59">
-        <v>1.4539</v>
+        <v>1.4902</v>
       </c>
       <c t="n" r="D59">
-        <v>3.8069</v>
+        <v>3.8134</v>
       </c>
       <c t="n" r="E59">
-        <v>12.8428</v>
+        <v>12.8687</v>
       </c>
       <c t="n" r="F59">
-        <v>3.8051</v>
+        <v>3.8423</v>
       </c>
       <c t="n" r="G59">
-        <v>30.6653</v>
+        <v>30.7050</v>
       </c>
     </row>
     <row r="60">
@@ -1948,25 +1951,25 @@
         </is>
       </c>
       <c t="n" r="C60">
-        <v>0.0753</v>
+        <v>0.0703</v>
       </c>
       <c t="n" r="D60">
-        <v>0.8635</v>
+        <v>0.8767</v>
       </c>
       <c t="n" r="E60">
-        <v>27.7429</v>
+        <v>27.7138</v>
       </c>
       <c t="n" r="F60">
-        <v>-5.9617</v>
+        <v>-5.9664</v>
       </c>
       <c t="n" r="G60">
-        <v>30.0509</v>
+        <v>30.0095</v>
       </c>
       <c t="n" r="H60">
-        <v>172.0561</v>
+        <v>172.0164</v>
       </c>
       <c t="n" r="I60">
-        <v>832.2956</v>
+        <v>827.9675</v>
       </c>
     </row>
     <row r="61">
@@ -1981,79 +1984,79 @@
         </is>
       </c>
       <c t="n" r="C61">
-        <v>0.2290</v>
+        <v>0.2309</v>
       </c>
       <c t="n" r="D61">
-        <v>0.7692</v>
+        <v>0.7698</v>
       </c>
       <c t="n" r="E61">
-        <v>27.8864</v>
+        <v>27.8871</v>
       </c>
       <c t="n" r="F61">
-        <v>1.0611</v>
+        <v>1.0631</v>
       </c>
       <c t="n" r="G61">
-        <v>29.6529</v>
+        <v>29.6533</v>
       </c>
     </row>
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">GF2</t>
+          <t xml:space="preserve">AG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C62">
-        <v>-1.3007</v>
+        <v>0.1277</v>
       </c>
       <c t="n" r="D62">
-        <v>5.0651</v>
+        <v>0.2799</v>
       </c>
       <c t="n" r="E62">
-        <v>16.5245</v>
+        <v>28.6761</v>
       </c>
       <c t="n" r="F62">
-        <v>6.1327</v>
+        <v>0.3374</v>
       </c>
       <c t="n" r="G62">
-        <v>29.5491</v>
+        <v>29.1447</v>
+      </c>
+      <c t="n" r="H62">
+        <v>231.8186</v>
+      </c>
+      <c t="n" r="I62">
+        <v>353.6600</v>
       </c>
     </row>
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">AG6</t>
+          <t xml:space="preserve">GF2</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C63">
-        <v>0.1226</v>
+        <v>-1.3897</v>
       </c>
       <c t="n" r="D63">
-        <v>0.2796</v>
+        <v>4.9207</v>
       </c>
       <c t="n" r="E63">
-        <v>28.6646</v>
+        <v>16.3126</v>
       </c>
       <c t="n" r="F63">
-        <v>0.3323</v>
+        <v>6.0371</v>
       </c>
       <c t="n" r="G63">
-        <v>29.1621</v>
-      </c>
-      <c t="n" r="H63">
-        <v>232.0558</v>
-      </c>
-      <c t="n" r="I63">
-        <v>353.6370</v>
+        <v>29.1309</v>
       </c>
     </row>
     <row r="64">
@@ -2068,19 +2071,19 @@
         </is>
       </c>
       <c t="n" r="C64">
-        <v>0.3397</v>
+        <v>0.3534</v>
       </c>
       <c t="n" r="D64">
-        <v>0.7411</v>
+        <v>0.7213</v>
       </c>
       <c t="n" r="E64">
-        <v>26.6602</v>
+        <v>26.7208</v>
       </c>
       <c t="n" r="F64">
-        <v>2.4512</v>
+        <v>2.4652</v>
       </c>
       <c t="n" r="G64">
-        <v>28.8342</v>
+        <v>28.8128</v>
       </c>
     </row>
     <row r="65">
@@ -2095,19 +2098,19 @@
         </is>
       </c>
       <c t="n" r="C65">
-        <v>-0.0181</v>
+        <v>-0.0182</v>
       </c>
       <c t="n" r="D65">
         <v>-0.0587</v>
       </c>
       <c t="n" r="E65">
-        <v>28.1527</v>
+        <v>28.1661</v>
       </c>
       <c t="n" r="F65">
         <v>-0.0775</v>
       </c>
       <c t="n" r="G65">
-        <v>28.0004</v>
+        <v>27.9999</v>
       </c>
     </row>
     <row r="66">
@@ -2122,25 +2125,25 @@
         </is>
       </c>
       <c t="n" r="C66">
-        <v>0.5187</v>
+        <v>0.5103</v>
       </c>
       <c t="n" r="D66">
-        <v>-1.4026</v>
+        <v>-1.3974</v>
       </c>
       <c t="n" r="E66">
-        <v>25.5663</v>
+        <v>25.4636</v>
       </c>
       <c t="n" r="F66">
-        <v>-20.3785</v>
+        <v>-20.3852</v>
       </c>
       <c t="n" r="G66">
-        <v>27.2754</v>
+        <v>27.2124</v>
       </c>
       <c t="n" r="H66">
-        <v>242.8497</v>
+        <v>242.8301</v>
       </c>
       <c t="n" r="I66">
-        <v>1974.2866</v>
+        <v>1974.1136</v>
       </c>
     </row>
     <row r="67">
@@ -2155,25 +2158,25 @@
         </is>
       </c>
       <c t="n" r="C67">
-        <v>1.6201</v>
+        <v>1.6412</v>
       </c>
       <c t="n" r="D67">
-        <v>4.0577</v>
+        <v>4.0697</v>
       </c>
       <c t="n" r="E67">
-        <v>16.1114</v>
+        <v>16.1231</v>
       </c>
       <c t="n" r="F67">
-        <v>4.2407</v>
+        <v>4.2624</v>
       </c>
       <c t="n" r="G67">
-        <v>27.0326</v>
+        <v>27.2070</v>
       </c>
       <c t="n" r="H67">
-        <v>134.5447</v>
+        <v>134.6370</v>
       </c>
       <c t="n" r="I67">
-        <v>634733.9698</v>
+        <v>634865.8160</v>
       </c>
     </row>
     <row r="68">
@@ -2188,25 +2191,25 @@
         </is>
       </c>
       <c t="n" r="C68">
-        <v>-2.2945</v>
+        <v>-2.2901</v>
       </c>
       <c t="n" r="D68">
-        <v>-1.1774</v>
+        <v>-1.1737</v>
       </c>
       <c t="n" r="E68">
-        <v>25.5661</v>
+        <v>25.5706</v>
       </c>
       <c t="n" r="F68">
-        <v>-0.3186</v>
+        <v>-0.3142</v>
       </c>
       <c t="n" r="G68">
-        <v>26.1284</v>
+        <v>26.1252</v>
       </c>
       <c t="n" r="H68">
-        <v>49.0745</v>
+        <v>49.1261</v>
       </c>
       <c t="n" r="I68">
-        <v>980.8229</v>
+        <v>980.8711</v>
       </c>
     </row>
     <row r="69">
@@ -2221,22 +2224,22 @@
         </is>
       </c>
       <c t="n" r="C69">
-        <v>0.4268</v>
+        <v>0.4252</v>
       </c>
       <c t="n" r="D69">
-        <v>1.7835</v>
+        <v>1.7858</v>
       </c>
       <c t="n" r="E69">
-        <v>8.7410</v>
+        <v>8.7402</v>
       </c>
       <c t="n" r="F69">
-        <v>1.7416</v>
+        <v>1.7400</v>
       </c>
       <c t="n" r="G69">
-        <v>25.8841</v>
+        <v>25.8615</v>
       </c>
       <c t="n" r="H69">
-        <v>76.8387</v>
+        <v>76.5582</v>
       </c>
     </row>
     <row r="70">
@@ -2251,19 +2254,19 @@
         </is>
       </c>
       <c t="n" r="C70">
-        <v>-2.3028</v>
+        <v>-2.2812</v>
       </c>
       <c t="n" r="D70">
-        <v>0.0537</v>
+        <v>0.0538</v>
       </c>
       <c t="n" r="E70">
-        <v>17.0688</v>
+        <v>17.0685</v>
       </c>
       <c t="n" r="F70">
-        <v>0.9482</v>
+        <v>0.9705</v>
       </c>
       <c t="n" r="G70">
-        <v>25.8325</v>
+        <v>25.8178</v>
       </c>
     </row>
     <row r="71">
@@ -2278,25 +2281,25 @@
         </is>
       </c>
       <c t="n" r="C71">
-        <v>0.2519</v>
+        <v>0.2742</v>
       </c>
       <c t="n" r="D71">
-        <v>2.7131</v>
+        <v>2.7163</v>
       </c>
       <c t="n" r="E71">
-        <v>16.5892</v>
+        <v>16.5918</v>
       </c>
       <c t="n" r="F71">
-        <v>4.0686</v>
+        <v>4.0919</v>
       </c>
       <c t="n" r="G71">
-        <v>25.8039</v>
+        <v>25.8105</v>
       </c>
       <c t="n" r="H71">
-        <v>218.2915</v>
+        <v>217.4913</v>
       </c>
       <c t="n" r="I71">
-        <v>496.2383</v>
+        <v>496.3803</v>
       </c>
     </row>
     <row r="72">
@@ -2311,25 +2314,25 @@
         </is>
       </c>
       <c t="n" r="C72">
-        <v>4.2987</v>
+        <v>4.2449</v>
       </c>
       <c t="n" r="D72">
-        <v>5.0642</v>
+        <v>4.9991</v>
       </c>
       <c t="n" r="E72">
-        <v>14.6140</v>
+        <v>14.3031</v>
       </c>
       <c t="n" r="F72">
-        <v>1.0838</v>
+        <v>1.0317</v>
       </c>
       <c t="n" r="G72">
-        <v>25.5578</v>
+        <v>25.4134</v>
       </c>
       <c t="n" r="H72">
-        <v>331.7830</v>
+        <v>331.5304</v>
       </c>
       <c t="n" r="I72">
-        <v>837.3736</v>
+        <v>836.8908</v>
       </c>
     </row>
     <row r="73">
@@ -2344,22 +2347,22 @@
         </is>
       </c>
       <c t="n" r="C73">
-        <v>1.1990</v>
+        <v>1.2338</v>
       </c>
       <c t="n" r="D73">
-        <v>3.5388</v>
+        <v>3.5435</v>
       </c>
       <c t="n" r="E73">
-        <v>-0.5443</v>
+        <v>-0.5179</v>
       </c>
       <c t="n" r="F73">
-        <v>3.8804</v>
+        <v>3.9162</v>
       </c>
       <c t="n" r="G73">
-        <v>25.3320</v>
+        <v>25.2447</v>
       </c>
       <c t="n" r="H73">
-        <v>161.3750</v>
+        <v>161.4964</v>
       </c>
     </row>
     <row r="74">
@@ -2374,19 +2377,19 @@
         </is>
       </c>
       <c t="n" r="C74">
-        <v>0.3997</v>
+        <v>0.3986</v>
       </c>
       <c t="n" r="D74">
-        <v>-0.1144</v>
+        <v>-0.1141</v>
       </c>
       <c t="n" r="E74">
-        <v>23.1944</v>
+        <v>23.1971</v>
       </c>
       <c t="n" r="F74">
-        <v>-0.1176</v>
+        <v>-0.1187</v>
       </c>
       <c t="n" r="G74">
-        <v>24.9224</v>
+        <v>24.9209</v>
       </c>
     </row>
     <row r="75">
@@ -2401,25 +2404,25 @@
         </is>
       </c>
       <c t="n" r="C75">
-        <v>-0.0912</v>
+        <v>-0.0927</v>
       </c>
       <c t="n" r="D75">
-        <v>-0.2267</v>
+        <v>-0.2271</v>
       </c>
       <c t="n" r="E75">
-        <v>25.3035</v>
+        <v>25.3036</v>
       </c>
       <c t="n" r="F75">
-        <v>-0.0113</v>
+        <v>-0.0128</v>
       </c>
       <c t="n" r="G75">
-        <v>24.8255</v>
+        <v>24.8238</v>
       </c>
       <c t="n" r="H75">
-        <v>199.1905</v>
+        <v>199.2004</v>
       </c>
       <c t="n" r="I75">
-        <v>400.1274</v>
+        <v>400.1177</v>
       </c>
     </row>
     <row r="76">
@@ -2434,211 +2437,211 @@
         </is>
       </c>
       <c t="n" r="C76">
-        <v>-2.4070</v>
+        <v>-2.2949</v>
       </c>
       <c t="n" r="D76">
-        <v>-2.3081</v>
+        <v>-2.1705</v>
       </c>
       <c t="n" r="E76">
-        <v>7.9693</v>
+        <v>8.0738</v>
       </c>
       <c t="n" r="F76">
-        <v>-2.7337</v>
+        <v>-2.6221</v>
       </c>
       <c t="n" r="G76">
-        <v>24.7963</v>
+        <v>24.7842</v>
       </c>
       <c t="n" r="H76">
-        <v>148.7803</v>
+        <v>148.9886</v>
       </c>
     </row>
     <row r="77">
       <c t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">AG5</t>
+          <t xml:space="preserve">RP3</t>
         </is>
       </c>
       <c t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DÜKKAN GAYRIMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRUPA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C77">
-        <v>6.6901</v>
+        <v>-2.6530</v>
       </c>
       <c t="n" r="D77">
-        <v>8.4296</v>
+        <v>5.5911</v>
       </c>
       <c t="n" r="E77">
-        <v>16.1127</v>
+        <v>24.7643</v>
       </c>
       <c t="n" r="F77">
-        <v>6.9018</v>
+        <v>-1.5813</v>
       </c>
       <c t="n" r="G77">
-        <v>23.0094</v>
+        <v>23.7132</v>
       </c>
       <c t="n" r="H77">
-        <v>244.3006</v>
+        <v>253.3243</v>
       </c>
       <c t="n" r="I77">
-        <v>780.7930</v>
+        <v>781.4171</v>
       </c>
     </row>
     <row r="78">
       <c t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">RG2</t>
+          <t xml:space="preserve">AG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DÜKKAN GAYRIMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C78">
-        <v>-0.1086</v>
+        <v>6.6994</v>
       </c>
       <c t="n" r="D78">
-        <v>-0.6178</v>
+        <v>8.4335</v>
       </c>
       <c t="n" r="E78">
-        <v>23.0722</v>
+        <v>16.2060</v>
       </c>
       <c t="n" r="F78">
-        <v>-0.7304</v>
+        <v>6.9111</v>
       </c>
       <c t="n" r="G78">
-        <v>21.8503</v>
+        <v>23.0808</v>
       </c>
       <c t="n" r="H78">
-        <v>170.8874</v>
+        <v>244.2187</v>
+      </c>
+      <c t="n" r="I78">
+        <v>780.8700</v>
       </c>
     </row>
     <row r="79">
       <c t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">BGY</t>
+          <t xml:space="preserve">RG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C79">
-        <v>0.3853</v>
+        <v>-0.1049</v>
       </c>
       <c t="n" r="D79">
-        <v>0.9974</v>
+        <v>-0.6136</v>
       </c>
       <c t="n" r="E79">
-        <v>3.8578</v>
+        <v>23.0877</v>
       </c>
       <c t="n" r="F79">
-        <v>1.3766</v>
+        <v>-0.7267</v>
       </c>
       <c t="n" r="G79">
-        <v>21.5277</v>
+        <v>21.8532</v>
       </c>
       <c t="n" r="H79">
-        <v>264.2885</v>
-      </c>
-      <c t="n" r="I79">
-        <v>795.8364</v>
+        <v>171.1644</v>
       </c>
     </row>
     <row r="80">
       <c t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">GGF</t>
+          <t xml:space="preserve">BGY</t>
         </is>
       </c>
       <c t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C80">
-        <v>0.8276</v>
+        <v>0.3886</v>
       </c>
       <c t="n" r="D80">
-        <v>1.5037</v>
+        <v>0.9984</v>
       </c>
       <c t="n" r="E80">
-        <v>12.0653</v>
+        <v>3.8473</v>
       </c>
       <c t="n" r="F80">
-        <v>1.6249</v>
+        <v>1.3799</v>
       </c>
       <c t="n" r="G80">
-        <v>21.3632</v>
+        <v>21.4929</v>
       </c>
       <c t="n" r="H80">
-        <v>77.0228</v>
+        <v>264.3103</v>
+      </c>
+      <c t="n" r="I80">
+        <v>795.7346</v>
       </c>
     </row>
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">ZG6</t>
+          <t xml:space="preserve">GGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C81">
-        <v>-0.1003</v>
+        <v>0.9354</v>
       </c>
       <c t="n" r="D81">
-        <v>-0.3159</v>
+        <v>1.6193</v>
       </c>
       <c t="n" r="E81">
-        <v>22.0979</v>
+        <v>12.1500</v>
       </c>
       <c t="n" r="F81">
-        <v>-2.4688</v>
+        <v>1.7335</v>
       </c>
       <c t="n" r="G81">
-        <v>21.2796</v>
+        <v>21.4575</v>
       </c>
       <c t="n" r="H81">
-        <v>47.5690</v>
+        <v>76.9137</v>
       </c>
     </row>
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">RP9</t>
+          <t xml:space="preserve">ZG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NEVA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C82">
-        <v>0.8342</v>
+        <v>-0.1031</v>
       </c>
       <c t="n" r="D82">
-        <v>1.1143</v>
+        <v>-0.3084</v>
       </c>
       <c t="n" r="E82">
-        <v>17.6255</v>
+        <v>22.0979</v>
       </c>
       <c t="n" r="F82">
-        <v>1.3039</v>
+        <v>-2.4716</v>
       </c>
       <c t="n" r="G82">
-        <v>20.9390</v>
+        <v>21.2792</v>
       </c>
       <c t="n" r="H82">
-        <v>175.1511</v>
-      </c>
-      <c t="n" r="I82">
-        <v>1195.9372</v>
+        <v>47.2009</v>
       </c>
     </row>
     <row r="83">
@@ -2653,88 +2656,88 @@
         </is>
       </c>
       <c t="n" r="C83">
-        <v>0.2717</v>
+        <v>0.2728</v>
       </c>
       <c t="n" r="D83">
-        <v>1.0226</v>
+        <v>1.0238</v>
       </c>
       <c t="n" r="E83">
-        <v>5.6481</v>
+        <v>5.6494</v>
       </c>
       <c t="n" r="F83">
-        <v>1.1120</v>
+        <v>1.1132</v>
       </c>
       <c t="n" r="G83">
-        <v>20.9064</v>
+        <v>20.9107</v>
       </c>
       <c t="n" r="H83">
-        <v>220.9937</v>
+        <v>221.0087</v>
       </c>
       <c t="n" r="I83">
-        <v>989.5497</v>
+        <v>989.6862</v>
       </c>
     </row>
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">RR4</t>
+          <t xml:space="preserve">RP9</t>
         </is>
       </c>
       <c t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ATAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NEVA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C84">
-        <v>-1.6227</v>
+        <v>0.7885</v>
       </c>
       <c t="n" r="D84">
-        <v>0.0426</v>
+        <v>1.0634</v>
       </c>
       <c t="n" r="E84">
-        <v>16.6119</v>
+        <v>17.5768</v>
       </c>
       <c t="n" r="F84">
-        <v>0.5022</v>
+        <v>1.2580</v>
       </c>
       <c t="n" r="G84">
-        <v>20.2458</v>
+        <v>20.8075</v>
       </c>
       <c t="n" r="H84">
-        <v>367.8531</v>
+        <v>175.0248</v>
+      </c>
+      <c t="n" r="I84">
+        <v>1195.6200</v>
       </c>
     </row>
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">RP3</t>
+          <t xml:space="preserve">RR4</t>
         </is>
       </c>
       <c t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRUPA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ATAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C85">
-        <v>-5.7022</v>
+        <v>-1.6197</v>
       </c>
       <c t="n" r="D85">
-        <v>2.2788</v>
+        <v>0.0453</v>
       </c>
       <c t="n" r="E85">
-        <v>20.8228</v>
+        <v>16.6135</v>
       </c>
       <c t="n" r="F85">
-        <v>-4.6640</v>
+        <v>0.5053</v>
       </c>
       <c t="n" r="G85">
-        <v>19.9042</v>
+        <v>20.2404</v>
       </c>
       <c t="n" r="H85">
-        <v>242.3612</v>
-      </c>
-      <c t="n" r="I85">
-        <v>754.5937</v>
+        <v>368.1196</v>
       </c>
     </row>
     <row r="86">
@@ -2749,25 +2752,25 @@
         </is>
       </c>
       <c t="n" r="C86">
-        <v>-0.4624</v>
+        <v>-0.4950</v>
       </c>
       <c t="n" r="D86">
-        <v>1.2391</v>
+        <v>1.3001</v>
       </c>
       <c t="n" r="E86">
-        <v>15.5877</v>
+        <v>15.3902</v>
       </c>
       <c t="n" r="F86">
-        <v>-2.8525</v>
+        <v>-2.8843</v>
       </c>
       <c t="n" r="G86">
-        <v>19.8646</v>
+        <v>19.6445</v>
       </c>
       <c t="n" r="H86">
-        <v>150.2604</v>
+        <v>150.0638</v>
       </c>
       <c t="n" r="I86">
-        <v>419.8286</v>
+        <v>418.3589</v>
       </c>
     </row>
     <row r="87">
@@ -2782,22 +2785,22 @@
         </is>
       </c>
       <c t="n" r="C87">
-        <v>0.4949</v>
+        <v>0.5004</v>
       </c>
       <c t="n" r="D87">
-        <v>1.2297</v>
+        <v>1.2128</v>
       </c>
       <c t="n" r="E87">
-        <v>11.5224</v>
+        <v>11.5283</v>
       </c>
       <c t="n" r="F87">
-        <v>-0.8133</v>
+        <v>-0.8078</v>
       </c>
       <c t="n" r="G87">
-        <v>19.6608</v>
+        <v>19.6408</v>
       </c>
       <c t="n" r="H87">
-        <v>151.9130</v>
+        <v>151.9274</v>
       </c>
     </row>
     <row r="88">
@@ -2812,88 +2815,88 @@
         </is>
       </c>
       <c t="n" r="C88">
-        <v>0.1029</v>
+        <v>0.1048</v>
       </c>
       <c t="n" r="D88">
-        <v>-0.0927</v>
+        <v>-0.0931</v>
       </c>
       <c t="n" r="E88">
-        <v>15.4435</v>
+        <v>15.4462</v>
       </c>
       <c t="n" r="F88">
-        <v>0.4174</v>
+        <v>0.4192</v>
       </c>
       <c t="n" r="G88">
-        <v>19.4078</v>
+        <v>19.4105</v>
       </c>
       <c t="n" r="H88">
-        <v>116.2940</v>
+        <v>116.2943</v>
       </c>
       <c t="n" r="I88">
-        <v>1160.0780</v>
+        <v>1160.1015</v>
       </c>
     </row>
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">RP2</t>
+          <t xml:space="preserve">PGB</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C89">
-        <v>2.6481</v>
+        <v>-0.2391</v>
       </c>
       <c t="n" r="D89">
-        <v>3.0054</v>
+        <v>0.2570</v>
       </c>
       <c t="n" r="E89">
-        <v>17.6216</v>
+        <v>19.1448</v>
       </c>
       <c t="n" r="F89">
-        <v>3.1668</v>
+        <v>-0.0409</v>
       </c>
       <c t="n" r="G89">
-        <v>19.3680</v>
+        <v>18.8359</v>
       </c>
       <c t="n" r="H89">
-        <v>145.7554</v>
-      </c>
-      <c t="n" r="I89">
-        <v>453.5488</v>
+        <v>1431.5943</v>
       </c>
     </row>
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">PGB</t>
+          <t xml:space="preserve">RP2</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C90">
-        <v>-0.2399</v>
+        <v>2.0897</v>
       </c>
       <c t="n" r="D90">
-        <v>0.2568</v>
+        <v>2.4119</v>
       </c>
       <c t="n" r="E90">
-        <v>19.1433</v>
+        <v>17.1136</v>
       </c>
       <c t="n" r="F90">
-        <v>-0.0417</v>
+        <v>2.6055</v>
       </c>
       <c t="n" r="G90">
-        <v>18.8387</v>
+        <v>18.3510</v>
       </c>
       <c t="n" r="H90">
-        <v>1434.1642</v>
+        <v>144.3757</v>
+      </c>
+      <c t="n" r="I90">
+        <v>450.4790</v>
       </c>
     </row>
     <row r="91">
@@ -2908,25 +2911,25 @@
         </is>
       </c>
       <c t="n" r="C91">
-        <v>-0.5953</v>
+        <v>-0.5997</v>
       </c>
       <c t="n" r="D91">
-        <v>-0.4660</v>
+        <v>-0.4666</v>
       </c>
       <c t="n" r="E91">
-        <v>11.1793</v>
+        <v>11.1794</v>
       </c>
       <c t="n" r="F91">
-        <v>-0.5815</v>
+        <v>-0.5859</v>
       </c>
       <c t="n" r="G91">
-        <v>17.9871</v>
+        <v>17.9869</v>
       </c>
       <c t="n" r="H91">
-        <v>245.6086</v>
+        <v>245.6469</v>
       </c>
       <c t="n" r="I91">
-        <v>1005.4354</v>
+        <v>1005.3864</v>
       </c>
     </row>
     <row r="92">
@@ -2941,22 +2944,22 @@
         </is>
       </c>
       <c t="n" r="C92">
-        <v>-1.5361</v>
+        <v>-1.5360</v>
       </c>
       <c t="n" r="D92">
-        <v>-1.0560</v>
+        <v>-1.0571</v>
       </c>
       <c t="n" r="E92">
-        <v>25.6620</v>
+        <v>25.6607</v>
       </c>
       <c t="n" r="F92">
-        <v>-0.8534</v>
+        <v>-0.8532</v>
       </c>
       <c t="n" r="G92">
-        <v>17.8135</v>
+        <v>17.8162</v>
       </c>
       <c t="n" r="H92">
-        <v>215.9735</v>
+        <v>215.9928</v>
       </c>
     </row>
     <row r="93">
@@ -2971,367 +2974,367 @@
         </is>
       </c>
       <c t="n" r="C93">
-        <v>-0.1250</v>
+        <v>-0.1295</v>
       </c>
       <c t="n" r="D93">
-        <v>-0.3927</v>
+        <v>-0.3930</v>
       </c>
       <c t="n" r="E93">
         <v>26.9057</v>
       </c>
       <c t="n" r="F93">
-        <v>-0.4427</v>
+        <v>-0.4471</v>
       </c>
       <c t="n" r="G93">
-        <v>17.7034</v>
+        <v>17.7032</v>
       </c>
       <c t="n" r="H93">
-        <v>775.8448</v>
+        <v>775.8840</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">FRG</t>
+          <t xml:space="preserve">YD3</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C94">
-        <v>7.0590</v>
+        <v>-0.7145</v>
       </c>
       <c t="n" r="D94">
-        <v>5.4563</v>
+        <v>-2.0850</v>
       </c>
       <c t="n" r="E94">
-        <v>16.8611</v>
+        <v>11.7790</v>
       </c>
       <c t="n" r="F94">
-        <v>7.2086</v>
+        <v>-2.2726</v>
       </c>
       <c t="n" r="G94">
-        <v>17.3687</v>
+        <v>17.0927</v>
       </c>
       <c t="n" r="H94">
-        <v>97.9332</v>
+        <v>148.4761</v>
       </c>
       <c t="n" r="I94">
-        <v>455.4947</v>
+        <v>674.7821</v>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">YD3</t>
+          <t xml:space="preserve">ABZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C95">
-        <v>-0.7075</v>
+        <v>-0.2508</v>
       </c>
       <c t="n" r="D95">
-        <v>-2.1200</v>
+        <v>-0.2529</v>
       </c>
       <c t="n" r="E95">
-        <v>11.7811</v>
+        <v>5.3810</v>
       </c>
       <c t="n" r="F95">
-        <v>-2.2657</v>
+        <v>-0.5036</v>
       </c>
       <c t="n" r="G95">
-        <v>17.0657</v>
-      </c>
-      <c t="n" r="H95">
-        <v>148.4175</v>
-      </c>
-      <c t="n" r="I95">
-        <v>674.8369</v>
+        <v>16.9180</v>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">ABZ</t>
+          <t xml:space="preserve">OYZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş.BEREKET KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C96">
-        <v>-0.2509</v>
+        <v>-0.2044</v>
       </c>
       <c t="n" r="D96">
-        <v>-0.2528</v>
+        <v>0.9085</v>
       </c>
       <c t="n" r="E96">
-        <v>5.3808</v>
+        <v>6.1938</v>
       </c>
       <c t="n" r="F96">
-        <v>-0.5036</v>
+        <v>-0.6836</v>
       </c>
       <c t="n" r="G96">
-        <v>16.9182</v>
+        <v>16.7667</v>
+      </c>
+      <c t="n" r="H96">
+        <v>320.7575</v>
+      </c>
+      <c t="n" r="I96">
+        <v>1601.1264</v>
       </c>
     </row>
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">OYZ</t>
+          <t xml:space="preserve">PKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş.BEREKET KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş V METROWAY KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C97">
-        <v>-0.2090</v>
+        <v>-0.0087</v>
       </c>
       <c t="n" r="D97">
-        <v>0.9069</v>
+        <v>-0.0462</v>
       </c>
       <c t="n" r="E97">
-        <v>6.1915</v>
+        <v>16.1309</v>
       </c>
       <c t="n" r="F97">
-        <v>-0.6882</v>
+        <v>-0.0458</v>
       </c>
       <c t="n" r="G97">
-        <v>16.7648</v>
+        <v>16.0179</v>
       </c>
       <c t="n" r="H97">
-        <v>320.7547</v>
-      </c>
-      <c t="n" r="I97">
-        <v>1601.0485</v>
+        <v>580.1472</v>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">PKA</t>
+          <t xml:space="preserve">OGI</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş V METROWAY KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C98">
-        <v>-0.0087</v>
+        <v>0.2706</v>
       </c>
       <c t="n" r="D98">
-        <v>-0.0461</v>
+        <v>-0.4092</v>
       </c>
       <c t="n" r="E98">
-        <v>16.1238</v>
+        <v>2.2601</v>
       </c>
       <c t="n" r="F98">
-        <v>-0.0457</v>
+        <v>0.1282</v>
       </c>
       <c t="n" r="G98">
-        <v>16.0178</v>
+        <v>15.8312</v>
       </c>
       <c t="n" r="H98">
-        <v>580.1703</v>
+        <v>0.5737</v>
+      </c>
+      <c t="n" r="I98">
+        <v>58.2283</v>
       </c>
     </row>
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">RP4</t>
+          <t xml:space="preserve">NUE</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. EGÇ KONUT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C99">
-        <v>5.2350</v>
+        <v>-0.1827</v>
       </c>
       <c t="n" r="D99">
-        <v>-3.7793</v>
+        <v>2.5631</v>
       </c>
       <c t="n" r="E99">
-        <v>11.8266</v>
+        <v>15.5029</v>
       </c>
       <c t="n" r="F99">
-        <v>-2.9489</v>
+        <v>3.4045</v>
       </c>
       <c t="n" r="G99">
-        <v>15.9699</v>
+        <v>15.1874</v>
       </c>
       <c t="n" r="H99">
-        <v>113.0278</v>
-      </c>
-      <c t="n" r="I99">
-        <v>370.7074</v>
+        <v>187.5946</v>
       </c>
     </row>
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">OGI</t>
+          <t xml:space="preserve">NUS</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ALTINCI KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C100">
-        <v>0.2297</v>
+        <v>-0.2231</v>
       </c>
       <c t="n" r="D100">
-        <v>-0.4147</v>
+        <v>-0.6075</v>
       </c>
       <c t="n" r="E100">
-        <v>2.2572</v>
+        <v>16.6331</v>
       </c>
       <c t="n" r="F100">
-        <v>0.0873</v>
+        <v>-0.6946</v>
       </c>
       <c t="n" r="G100">
-        <v>15.6768</v>
-      </c>
-      <c t="n" r="H100">
-        <v>0.5146</v>
-      </c>
-      <c t="n" r="I100">
-        <v>58.1636</v>
+        <v>14.9597</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">NUE</t>
+          <t xml:space="preserve">FRG</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. EGÇ KONUT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C101">
-        <v>-0.1749</v>
+        <v>5.6764</v>
       </c>
       <c t="n" r="D101">
-        <v>2.5415</v>
+        <v>3.9710</v>
       </c>
       <c t="n" r="E101">
-        <v>15.8088</v>
+        <v>15.9068</v>
       </c>
       <c t="n" r="F101">
-        <v>3.4126</v>
+        <v>5.8241</v>
       </c>
       <c t="n" r="G101">
-        <v>15.5017</v>
+        <v>14.9491</v>
       </c>
       <c t="n" r="H101">
-        <v>187.3909</v>
+        <v>95.3320</v>
+      </c>
+      <c t="n" r="I101">
+        <v>448.0886</v>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">NUS</t>
+          <t xml:space="preserve">RP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ALTINCI KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C102">
-        <v>-0.2167</v>
+        <v>4.5694</v>
       </c>
       <c t="n" r="D102">
-        <v>-0.6074</v>
+        <v>-4.3926</v>
       </c>
       <c t="n" r="E102">
-        <v>16.6328</v>
+        <v>11.2718</v>
       </c>
       <c t="n" r="F102">
-        <v>-0.6882</v>
+        <v>-3.5627</v>
       </c>
       <c t="n" r="G102">
-        <v>14.9649</v>
+        <v>14.5458</v>
+      </c>
+      <c t="n" r="H102">
+        <v>111.7179</v>
+      </c>
+      <c t="n" r="I102">
+        <v>367.7609</v>
       </c>
     </row>
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">RAS</t>
+          <t xml:space="preserve">AZ2</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C103">
-        <v>0.5512</v>
+        <v>-0.1437</v>
       </c>
       <c t="n" r="D103">
-        <v>1.2682</v>
+        <v>1.5765</v>
       </c>
       <c t="n" r="E103">
-        <v>13.4690</v>
+        <v>4.8481</v>
       </c>
       <c t="n" r="F103">
-        <v>1.8833</v>
+        <v>1.1575</v>
       </c>
       <c t="n" r="G103">
-        <v>14.7859</v>
+        <v>14.3090</v>
       </c>
       <c t="n" r="H103">
-        <v>262.7569</v>
+        <v>265.8190</v>
       </c>
       <c t="n" r="I103">
-        <v>478.0410</v>
+        <v>1192.9656</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">AZ2</t>
+          <t xml:space="preserve">RAS</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C104">
-        <v>-0.1244</v>
+        <v>-0.1286</v>
       </c>
       <c t="n" r="D104">
-        <v>1.5427</v>
+        <v>0.5707</v>
       </c>
       <c t="n" r="E104">
-        <v>4.9311</v>
+        <v>12.7061</v>
       </c>
       <c t="n" r="F104">
-        <v>1.1770</v>
+        <v>1.1945</v>
       </c>
       <c t="n" r="G104">
-        <v>14.4068</v>
+        <v>13.9869</v>
       </c>
       <c t="n" r="H104">
-        <v>266.0410</v>
+        <v>260.7534</v>
       </c>
       <c t="n" r="I104">
-        <v>1199.8562</v>
+        <v>474.1199</v>
       </c>
     </row>
     <row r="105">
@@ -3346,22 +3349,22 @@
         </is>
       </c>
       <c t="n" r="C105">
-        <v>0.2388</v>
+        <v>0.2375</v>
       </c>
       <c t="n" r="D105">
-        <v>-0.0212</v>
+        <v>-0.0218</v>
       </c>
       <c t="n" r="E105">
-        <v>13.7581</v>
+        <v>13.7570</v>
       </c>
       <c t="n" r="F105">
-        <v>-0.9348</v>
+        <v>-0.9360</v>
       </c>
       <c t="n" r="G105">
-        <v>13.7469</v>
+        <v>13.7397</v>
       </c>
       <c t="n" r="H105">
-        <v>225.2795</v>
+        <v>225.1377</v>
       </c>
     </row>
     <row r="106">
@@ -3376,22 +3379,22 @@
         </is>
       </c>
       <c t="n" r="C106">
-        <v>0.0306</v>
+        <v>0.0358</v>
       </c>
       <c t="n" r="D106">
-        <v>0.1960</v>
+        <v>0.2018</v>
       </c>
       <c t="n" r="E106">
-        <v>-0.9909</v>
+        <v>-0.9860</v>
       </c>
       <c t="n" r="F106">
-        <v>0.1891</v>
+        <v>0.1944</v>
       </c>
       <c t="n" r="G106">
-        <v>13.0387</v>
+        <v>13.0455</v>
       </c>
       <c t="n" r="H106">
-        <v>124.6486</v>
+        <v>124.6410</v>
       </c>
     </row>
     <row r="107">
@@ -3406,22 +3409,22 @@
         </is>
       </c>
       <c t="n" r="C107">
-        <v>-0.0530</v>
+        <v>-0.0540</v>
       </c>
       <c t="n" r="D107">
-        <v>-0.3435</v>
+        <v>-0.3436</v>
       </c>
       <c t="n" r="E107">
-        <v>13.5135</v>
+        <v>13.7143</v>
       </c>
       <c t="n" r="F107">
-        <v>-0.5412</v>
+        <v>-0.5422</v>
       </c>
       <c t="n" r="G107">
         <v>13.0373</v>
       </c>
       <c t="n" r="H107">
-        <v>493.5624</v>
+        <v>493.5727</v>
       </c>
     </row>
     <row r="108">
@@ -3436,46 +3439,52 @@
         </is>
       </c>
       <c t="n" r="C108">
-        <v>0.0526</v>
+        <v>0.0513</v>
       </c>
       <c t="n" r="D108">
-        <v>2.3645</v>
+        <v>2.3651</v>
       </c>
       <c t="n" r="E108">
-        <v>3.7820</v>
+        <v>3.7758</v>
       </c>
       <c t="n" r="F108">
-        <v>2.4456</v>
+        <v>2.4442</v>
       </c>
       <c t="n" r="G108">
-        <v>12.7811</v>
+        <v>12.7803</v>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">NH2</t>
+          <t xml:space="preserve">OYE</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş CORNERSTONE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALTINCI KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C109">
-        <v>0.7748</v>
+        <v>-0.3203</v>
       </c>
       <c t="n" r="D109">
-        <v>2.1272</v>
+        <v>1.0477</v>
       </c>
       <c t="n" r="E109">
-        <v>11.8396</v>
+        <v>8.8973</v>
       </c>
       <c t="n" r="F109">
-        <v>3.2629</v>
+        <v>-1.1206</v>
       </c>
       <c t="n" r="G109">
-        <v>12.6152</v>
+        <v>12.4321</v>
+      </c>
+      <c t="n" r="H109">
+        <v>201.5374</v>
+      </c>
+      <c t="n" r="I109">
+        <v>576.4262</v>
       </c>
     </row>
     <row r="110">
@@ -3490,55 +3499,49 @@
         </is>
       </c>
       <c t="n" r="C110">
-        <v>0.0855</v>
+        <v>0.0776</v>
       </c>
       <c t="n" r="D110">
-        <v>0.7895</v>
+        <v>0.7893</v>
       </c>
       <c t="n" r="E110">
-        <v>9.8550</v>
+        <v>9.8483</v>
       </c>
       <c t="n" r="F110">
-        <v>0.7789</v>
+        <v>0.7710</v>
       </c>
       <c t="n" r="G110">
-        <v>12.4982</v>
+        <v>12.3494</v>
       </c>
       <c t="n" r="H110">
-        <v>-18.6170</v>
+        <v>-18.5995</v>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">OYE</t>
+          <t xml:space="preserve">NH2</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALTINCI KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş CORNERSTONE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C111">
-        <v>-0.3221</v>
+        <v>0.7978</v>
       </c>
       <c t="n" r="D111">
-        <v>1.0479</v>
+        <v>2.4673</v>
       </c>
       <c t="n" r="E111">
-        <v>8.9065</v>
+        <v>11.8439</v>
       </c>
       <c t="n" r="F111">
-        <v>-1.1223</v>
+        <v>3.2866</v>
       </c>
       <c t="n" r="G111">
-        <v>12.4498</v>
-      </c>
-      <c t="n" r="H111">
-        <v>201.5445</v>
-      </c>
-      <c t="n" r="I111">
-        <v>576.4143</v>
+        <v>12.2868</v>
       </c>
     </row>
     <row r="112">
@@ -3553,22 +3556,22 @@
         </is>
       </c>
       <c t="n" r="C112">
-        <v>0.0358</v>
+        <v>0.0386</v>
       </c>
       <c t="n" r="D112">
-        <v>0.4014</v>
+        <v>0.4043</v>
       </c>
       <c t="n" r="E112">
-        <v>27.6600</v>
+        <v>27.6667</v>
       </c>
       <c t="n" r="F112">
-        <v>0.3195</v>
+        <v>0.3223</v>
       </c>
       <c t="n" r="G112">
-        <v>11.3752</v>
+        <v>11.3779</v>
       </c>
       <c t="n" r="H112">
-        <v>134.4708</v>
+        <v>134.4985</v>
       </c>
     </row>
     <row r="113">
@@ -3583,22 +3586,22 @@
         </is>
       </c>
       <c t="n" r="C113">
-        <v>-1.5034</v>
+        <v>-1.5831</v>
       </c>
       <c t="n" r="D113">
-        <v>-5.0636</v>
+        <v>-5.1426</v>
       </c>
       <c t="n" r="E113">
-        <v>33.4125</v>
+        <v>33.3022</v>
       </c>
       <c t="n" r="F113">
-        <v>-5.1233</v>
+        <v>-5.2001</v>
       </c>
       <c t="n" r="G113">
-        <v>10.5849</v>
+        <v>10.4922</v>
       </c>
       <c t="n" r="H113">
-        <v>401.7085</v>
+        <v>400.5816</v>
       </c>
     </row>
     <row r="114">
@@ -3613,19 +3616,19 @@
         </is>
       </c>
       <c t="n" r="C114">
-        <v>-0.0644</v>
+        <v>-0.0729</v>
       </c>
       <c t="n" r="D114">
-        <v>-0.1962</v>
+        <v>-0.2028</v>
       </c>
       <c t="n" r="E114">
-        <v>10.8980</v>
+        <v>10.8904</v>
       </c>
       <c t="n" r="F114">
-        <v>-0.2163</v>
+        <v>-0.2247</v>
       </c>
       <c t="n" r="G114">
-        <v>10.4154</v>
+        <v>10.4031</v>
       </c>
     </row>
     <row r="115">
@@ -3640,46 +3643,46 @@
         </is>
       </c>
       <c t="n" r="C115">
-        <v>-0.3130</v>
+        <v>-0.3237</v>
       </c>
       <c t="n" r="D115">
-        <v>-1.2108</v>
+        <v>-1.2039</v>
       </c>
       <c t="n" r="E115">
-        <v>12.3996</v>
+        <v>12.3998</v>
       </c>
       <c t="n" r="F115">
-        <v>-1.3187</v>
+        <v>-1.3293</v>
       </c>
       <c t="n" r="G115">
-        <v>10.3111</v>
+        <v>10.3061</v>
       </c>
     </row>
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">RBG</t>
+          <t xml:space="preserve">NBA</t>
         </is>
       </c>
       <c t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C116">
-        <v>0.4433</v>
+        <v>-29.2969</v>
       </c>
       <c t="n" r="D116">
-        <v>0.6958</v>
+        <v>-32.9203</v>
       </c>
       <c t="n" r="E116">
-        <v>6.5669</v>
+        <v>1660.2416</v>
       </c>
       <c t="n" r="F116">
-        <v>1.2241</v>
+        <v>-33.0417</v>
       </c>
       <c t="n" r="G116">
-        <v>9.4824</v>
+        <v>10.0141</v>
       </c>
     </row>
     <row r="117">
@@ -3694,553 +3697,547 @@
         </is>
       </c>
       <c t="n" r="C117">
-        <v>0.1252</v>
+        <v>0.3058</v>
       </c>
       <c t="n" r="D117">
-        <v>0.3542</v>
+        <v>0.5164</v>
       </c>
       <c t="n" r="E117">
-        <v>1.9962</v>
+        <v>2.1630</v>
       </c>
       <c t="n" r="F117">
-        <v>0.9389</v>
+        <v>1.1211</v>
       </c>
       <c t="n" r="G117">
-        <v>9.3732</v>
+        <v>9.5741</v>
       </c>
       <c t="n" r="H117">
-        <v>128.9605</v>
+        <v>129.2901</v>
       </c>
       <c t="n" r="I117">
-        <v>422.0214</v>
+        <v>423.2283</v>
       </c>
     </row>
     <row r="118">
       <c t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">YG8</t>
+          <t xml:space="preserve">RBG</t>
         </is>
       </c>
       <c t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LALE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C118">
-        <v>-0.1112</v>
+        <v>0.4487</v>
       </c>
       <c t="n" r="D118">
-        <v>-0.1771</v>
+        <v>1.6727</v>
       </c>
       <c t="n" r="E118">
-        <v>9.2261</v>
+        <v>6.5715</v>
       </c>
       <c t="n" r="F118">
-        <v>-0.1492</v>
+        <v>1.2296</v>
       </c>
       <c t="n" r="G118">
-        <v>8.9759</v>
+        <v>9.2548</v>
       </c>
     </row>
     <row r="119">
       <c t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">RG9</t>
+          <t xml:space="preserve">YG8</t>
         </is>
       </c>
       <c t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN AVM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LALE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C119">
-        <v>0.2327</v>
+        <v>-0.0914</v>
       </c>
       <c t="n" r="D119">
-        <v>1.7098</v>
+        <v>-0.1569</v>
       </c>
       <c t="n" r="E119">
-        <v>8.3491</v>
+        <v>9.2482</v>
       </c>
       <c t="n" r="F119">
-        <v>1.6610</v>
+        <v>-0.1294</v>
       </c>
       <c t="n" r="G119">
-        <v>8.9285</v>
-      </c>
-      <c t="n" r="H119">
-        <v>125.1200</v>
+        <v>9.0068</v>
       </c>
     </row>
     <row r="120">
       <c t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">NAG</t>
+          <t xml:space="preserve">RG9</t>
         </is>
       </c>
       <c t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AKS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN AVM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C120">
-        <v>-0.0902</v>
+        <v>0.2283</v>
       </c>
       <c t="n" r="D120">
-        <v>-0.2327</v>
+        <v>1.7073</v>
       </c>
       <c t="n" r="E120">
-        <v>9.0310</v>
+        <v>8.3451</v>
       </c>
       <c t="n" r="F120">
-        <v>-0.1701</v>
+        <v>1.6565</v>
       </c>
       <c t="n" r="G120">
-        <v>8.8590</v>
+        <v>8.9247</v>
       </c>
       <c t="n" r="H120">
-        <v>253.3341</v>
+        <v>125.0666</v>
       </c>
     </row>
     <row r="121">
       <c t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">NH4</t>
+          <t xml:space="preserve">NAG</t>
         </is>
       </c>
       <c t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AKS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C121">
-        <v>0.1902</v>
+        <v>-0.0921</v>
       </c>
       <c t="n" r="D121">
-        <v>0.4293</v>
+        <v>-0.2429</v>
       </c>
       <c t="n" r="E121">
-        <v>3.9809</v>
+        <v>9.0311</v>
       </c>
       <c t="n" r="F121">
-        <v>0.5493</v>
+        <v>-0.1720</v>
       </c>
       <c t="n" r="G121">
-        <v>8.6314</v>
+        <v>8.8606</v>
       </c>
       <c t="n" r="H121">
-        <v>244.9131</v>
+        <v>253.3588</v>
       </c>
     </row>
     <row r="122">
       <c t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">NUI</t>
+          <t xml:space="preserve">NH4</t>
         </is>
       </c>
       <c t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. TİCARİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C122">
-        <v>0.4008</v>
+        <v>0.1948</v>
       </c>
       <c t="n" r="D122">
-        <v>-1.8910</v>
+        <v>0.4628</v>
       </c>
       <c t="n" r="E122">
-        <v>7.5536</v>
+        <v>3.9879</v>
       </c>
       <c t="n" r="F122">
-        <v>-1.4120</v>
+        <v>0.5539</v>
       </c>
       <c t="n" r="G122">
-        <v>8.4661</v>
+        <v>8.6229</v>
+      </c>
+      <c t="n" r="H122">
+        <v>244.7903</v>
       </c>
     </row>
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">NRY</t>
+          <t xml:space="preserve">NUI</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ROYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. TİCARİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C123">
-        <v>-0.5014</v>
+        <v>0.3970</v>
       </c>
       <c t="n" r="D123">
-        <v>-0.7011</v>
+        <v>-1.8938</v>
       </c>
       <c t="n" r="E123">
-        <v>8.8451</v>
+        <v>7.5511</v>
       </c>
       <c t="n" r="F123">
-        <v>-0.4585</v>
+        <v>-1.4157</v>
       </c>
       <c t="n" r="G123">
-        <v>8.3882</v>
+        <v>8.4609</v>
       </c>
     </row>
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">OCH</t>
+          <t xml:space="preserve">NRY</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. OC HEDEF GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ROYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C124">
-        <v>0.4488</v>
+        <v>-0.5061</v>
       </c>
       <c t="n" r="D124">
-        <v>0.5649</v>
+        <v>-0.7019</v>
       </c>
       <c t="n" r="E124">
-        <v>7.0865</v>
+        <v>8.8954</v>
       </c>
       <c t="n" r="F124">
-        <v>0.6468</v>
+        <v>-0.4632</v>
       </c>
       <c t="n" r="G124">
-        <v>7.7358</v>
-      </c>
-      <c t="n" r="H124">
-        <v>113.5580</v>
+        <v>8.3793</v>
       </c>
     </row>
     <row r="125">
       <c t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">NG5</t>
+          <t xml:space="preserve">OCH</t>
         </is>
       </c>
       <c t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. OC HEDEF GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C125">
-        <v>-0.3512</v>
+        <v>0.4565</v>
       </c>
       <c t="n" r="D125">
-        <v>-0.2361</v>
+        <v>0.5736</v>
       </c>
       <c t="n" r="E125">
-        <v>12.1047</v>
+        <v>7.0960</v>
       </c>
       <c t="n" r="F125">
-        <v>-0.9725</v>
+        <v>0.6546</v>
       </c>
       <c t="n" r="G125">
-        <v>7.6206</v>
+        <v>7.7475</v>
       </c>
       <c t="n" r="H125">
-        <v>213.8131</v>
+        <v>113.5683</v>
       </c>
     </row>
     <row r="126">
       <c t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">GJS</t>
+          <t xml:space="preserve">NG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. SAĞLAM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C126">
-        <v>1.2519</v>
+        <v>-0.3529</v>
       </c>
       <c t="n" r="D126">
-        <v>0.7867</v>
+        <v>-0.2362</v>
       </c>
       <c t="n" r="E126">
-        <v>6.5034</v>
+        <v>12.1039</v>
       </c>
       <c t="n" r="F126">
-        <v>0.7087</v>
+        <v>-0.9742</v>
       </c>
       <c t="n" r="G126">
-        <v>6.5736</v>
+        <v>7.6390</v>
       </c>
       <c t="n" r="H126">
-        <v>160.5295</v>
+        <v>213.9096</v>
       </c>
     </row>
     <row r="127">
       <c t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">RTM</t>
+          <t xml:space="preserve">GJS</t>
         </is>
       </c>
       <c t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. TM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. SAĞLAM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C127">
-        <v>-0.3717</v>
+        <v>1.2619</v>
       </c>
       <c t="n" r="D127">
-        <v>-0.4051</v>
+        <v>0.7981</v>
       </c>
       <c t="n" r="E127">
-        <v>7.2249</v>
+        <v>6.5156</v>
       </c>
       <c t="n" r="F127">
-        <v>-0.3807</v>
+        <v>0.7187</v>
       </c>
       <c t="n" r="G127">
-        <v>6.5282</v>
+        <v>6.5870</v>
       </c>
       <c t="n" r="H127">
-        <v>233.4225</v>
+        <v>160.5678</v>
       </c>
     </row>
     <row r="128">
       <c t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">RG5</t>
+          <t xml:space="preserve">RTM</t>
         </is>
       </c>
       <c t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DİCLE PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. TM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C128">
-        <v>-0.0486</v>
+        <v>-0.3717</v>
       </c>
       <c t="n" r="D128">
-        <v>-0.1464</v>
+        <v>-0.4051</v>
       </c>
       <c t="n" r="E128">
-        <v>6.6123</v>
+        <v>7.2274</v>
       </c>
       <c t="n" r="F128">
-        <v>-0.1706</v>
+        <v>-0.3807</v>
       </c>
       <c t="n" r="G128">
-        <v>6.3423</v>
+        <v>6.5283</v>
       </c>
       <c t="n" r="H128">
-        <v>305.7944</v>
+        <v>233.4040</v>
       </c>
     </row>
     <row r="129">
       <c t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">NUT</t>
+          <t xml:space="preserve">RG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. NUROL TOWER GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DİCLE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C129">
-        <v>0.1706</v>
+        <v>-0.0498</v>
       </c>
       <c t="n" r="D129">
-        <v>1.0018</v>
+        <v>-0.1440</v>
       </c>
       <c t="n" r="E129">
-        <v>13.6055</v>
+        <v>6.6187</v>
       </c>
       <c t="n" r="F129">
-        <v>1.2786</v>
+        <v>-0.1717</v>
       </c>
       <c t="n" r="G129">
-        <v>5.8576</v>
+        <v>6.3421</v>
       </c>
       <c t="n" r="H129">
-        <v>195.4043</v>
+        <v>305.8122</v>
       </c>
     </row>
     <row r="130">
       <c t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">NUP</t>
+          <t xml:space="preserve">NUT</t>
         </is>
       </c>
       <c t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. NUROL TOWER GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C130">
-        <v>-0.0597</v>
+        <v>0.1718</v>
       </c>
       <c t="n" r="D130">
-        <v>-0.1737</v>
+        <v>1.0062</v>
       </c>
       <c t="n" r="E130">
-        <v>8.3413</v>
+        <v>13.5607</v>
       </c>
       <c t="n" r="F130">
-        <v>2.1459</v>
+        <v>1.2799</v>
       </c>
       <c t="n" r="G130">
-        <v>5.3164</v>
+        <v>5.8143</v>
+      </c>
+      <c t="n" r="H130">
+        <v>195.4184</v>
       </c>
     </row>
     <row r="131">
       <c t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">ERS</t>
+          <t xml:space="preserve">NUP</t>
         </is>
       </c>
       <c t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C131">
-        <v>0.3168</v>
+        <v>-0.0652</v>
       </c>
       <c t="n" r="D131">
-        <v>1.1221</v>
+        <v>-0.1788</v>
       </c>
       <c t="n" r="E131">
-        <v>11.4997</v>
+        <v>8.3426</v>
       </c>
       <c t="n" r="F131">
-        <v>1.1027</v>
+        <v>2.1403</v>
       </c>
       <c t="n" r="G131">
-        <v>5.2405</v>
-      </c>
-      <c t="n" r="H131">
-        <v>153.4354</v>
+        <v>5.3166</v>
       </c>
     </row>
     <row r="132">
       <c t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">NH5</t>
+          <t xml:space="preserve">ERS</t>
         </is>
       </c>
       <c t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C132">
-        <v>1.1655</v>
+        <v>0.3183</v>
       </c>
       <c t="n" r="D132">
-        <v>3.7197</v>
+        <v>1.1235</v>
       </c>
       <c t="n" r="E132">
-        <v>9.5106</v>
+        <v>11.5029</v>
       </c>
       <c t="n" r="F132">
-        <v>4.3490</v>
+        <v>1.1042</v>
       </c>
       <c t="n" r="G132">
-        <v>4.9225</v>
+        <v>5.2217</v>
       </c>
       <c t="n" r="H132">
-        <v>89.7578</v>
+        <v>153.4289</v>
       </c>
     </row>
     <row r="133">
       <c t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">NUL</t>
+          <t xml:space="preserve">NH5</t>
         </is>
       </c>
       <c t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İGC GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C133">
-        <v>0.1624</v>
+        <v>1.2167</v>
       </c>
       <c t="n" r="D133">
-        <v>-10.4716</v>
+        <v>3.7254</v>
       </c>
       <c t="n" r="E133">
-        <v>0.3478</v>
+        <v>9.5774</v>
       </c>
       <c t="n" r="F133">
-        <v>-10.4767</v>
+        <v>4.4018</v>
       </c>
       <c t="n" r="G133">
-        <v>4.8175</v>
+        <v>4.9859</v>
+      </c>
+      <c t="n" r="H133">
+        <v>89.8582</v>
       </c>
     </row>
     <row r="134">
       <c t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">HP1</t>
+          <t xml:space="preserve">NUL</t>
         </is>
       </c>
       <c t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İGC GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C134">
-        <v>-0.2122</v>
+        <v>0.1642</v>
       </c>
       <c t="n" r="D134">
-        <v>-0.6730</v>
+        <v>-10.4818</v>
       </c>
       <c t="n" r="E134">
-        <v>5.9079</v>
+        <v>0.3363</v>
       </c>
       <c t="n" r="F134">
-        <v>-0.7575</v>
+        <v>-10.4751</v>
       </c>
       <c t="n" r="G134">
-        <v>4.4868</v>
-      </c>
-      <c t="n" r="H134">
-        <v>114.2572</v>
+        <v>4.7834</v>
       </c>
     </row>
     <row r="135">
       <c t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">ORX</t>
+          <t xml:space="preserve">HP1</t>
         </is>
       </c>
       <c t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C135">
-        <v>0.1223</v>
+        <v>-0.2245</v>
       </c>
       <c t="n" r="D135">
-        <v>-0.6123</v>
+        <v>-0.6782</v>
       </c>
       <c t="n" r="E135">
-        <v>0.9030</v>
+        <v>5.9027</v>
       </c>
       <c t="n" r="F135">
-        <v>-0.5080</v>
+        <v>-0.7698</v>
       </c>
       <c t="n" r="G135">
-        <v>4.1449</v>
+        <v>4.4807</v>
       </c>
       <c t="n" r="H135">
-        <v>89.5028</v>
-      </c>
-      <c t="n" r="I135">
-        <v>58.5926</v>
+        <v>113.8958</v>
       </c>
     </row>
     <row r="136">
@@ -4255,46 +4252,52 @@
         </is>
       </c>
       <c t="n" r="C136">
-        <v>-0.5863</v>
+        <v>-0.6071</v>
       </c>
       <c t="n" r="D136">
-        <v>-2.3181</v>
+        <v>-2.3262</v>
       </c>
       <c t="n" r="E136">
-        <v>-14.8953</v>
+        <v>-14.9058</v>
       </c>
       <c t="n" r="F136">
-        <v>-2.5362</v>
+        <v>-2.5566</v>
       </c>
       <c t="n" r="G136">
-        <v>4.0117</v>
+        <v>3.9935</v>
       </c>
     </row>
     <row r="137">
       <c t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">NFE</t>
+          <t xml:space="preserve">ORX</t>
         </is>
       </c>
       <c t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C137">
-        <v>-0.6757</v>
+        <v>-0.0067</v>
       </c>
       <c t="n" r="D137">
-        <v>-1.5224</v>
+        <v>-0.7020</v>
       </c>
       <c t="n" r="E137">
-        <v>100.7576</v>
+        <v>0.8875</v>
       </c>
       <c t="n" r="F137">
-        <v>-2.1099</v>
+        <v>-0.6362</v>
       </c>
       <c t="n" r="G137">
-        <v>3.7231</v>
+        <v>3.9540</v>
+      </c>
+      <c t="n" r="H137">
+        <v>89.1418</v>
+      </c>
+      <c t="n" r="I137">
+        <v>58.3883</v>
       </c>
     </row>
     <row r="138">
@@ -4309,265 +4312,268 @@
         </is>
       </c>
       <c t="n" r="C138">
-        <v>-0.2477</v>
+        <v>-0.2534</v>
       </c>
       <c t="n" r="D138">
-        <v>-0.8518</v>
+        <v>-0.8515</v>
       </c>
       <c t="n" r="E138">
-        <v>0.6638</v>
+        <v>0.6743</v>
       </c>
       <c t="n" r="F138">
-        <v>-0.9675</v>
+        <v>-0.9731</v>
       </c>
       <c t="n" r="G138">
-        <v>3.4707</v>
+        <v>3.4695</v>
       </c>
       <c t="n" r="H138">
-        <v>170.0628</v>
+        <v>169.6079</v>
       </c>
     </row>
     <row r="139">
       <c t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">NUK</t>
+          <t xml:space="preserve">NFE</t>
         </is>
       </c>
       <c t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C139">
-        <v>-0.0923</v>
+        <v>-0.6837</v>
       </c>
       <c t="n" r="D139">
-        <v>-0.2747</v>
+        <v>-1.5296</v>
       </c>
       <c t="n" r="E139">
-        <v>9.4876</v>
+        <v>100.5450</v>
       </c>
       <c t="n" r="F139">
-        <v>-0.3402</v>
+        <v>-2.1179</v>
       </c>
       <c t="n" r="G139">
-        <v>3.1530</v>
-      </c>
-      <c t="n" r="H139">
-        <v>122.0140</v>
+        <v>3.3765</v>
       </c>
     </row>
     <row r="140">
       <c t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">PG2</t>
+          <t xml:space="preserve">NUK</t>
         </is>
       </c>
       <c t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C140">
-        <v>-0.1102</v>
+        <v>-0.0943</v>
       </c>
       <c t="n" r="D140">
-        <v>-0.3455</v>
+        <v>-0.2737</v>
       </c>
       <c t="n" r="E140">
-        <v>16.5359</v>
+        <v>9.4862</v>
       </c>
       <c t="n" r="F140">
-        <v>-0.5088</v>
+        <v>-0.3423</v>
       </c>
       <c t="n" r="G140">
-        <v>3.0732</v>
+        <v>3.1531</v>
       </c>
       <c t="n" r="H140">
-        <v>267.6223</v>
+        <v>121.8628</v>
       </c>
     </row>
     <row r="141">
       <c t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">NG6</t>
+          <t xml:space="preserve">PG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C141">
-        <v>1.0824</v>
+        <v>-0.1882</v>
       </c>
       <c t="n" r="D141">
-        <v>-0.2814</v>
+        <v>-0.4236</v>
       </c>
       <c t="n" r="E141">
-        <v>4.9562</v>
+        <v>16.4452</v>
       </c>
       <c t="n" r="F141">
-        <v>-0.7894</v>
+        <v>-0.5865</v>
       </c>
       <c t="n" r="G141">
-        <v>2.8810</v>
+        <v>2.9929</v>
       </c>
       <c t="n" r="H141">
-        <v>265.8296</v>
+        <v>266.7169</v>
       </c>
     </row>
     <row r="142">
       <c t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">RBU</t>
+          <t xml:space="preserve">NG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C142">
-        <v>0.6589</v>
+        <v>1.1196</v>
       </c>
       <c t="n" r="D142">
-        <v>-1.9145</v>
+        <v>0.1492</v>
       </c>
       <c t="n" r="E142">
-        <v>1.8985</v>
+        <v>4.9859</v>
       </c>
       <c t="n" r="F142">
-        <v>-1.2042</v>
+        <v>-0.7529</v>
       </c>
       <c t="n" r="G142">
-        <v>2.5301</v>
+        <v>2.8819</v>
+      </c>
+      <c t="n" r="H142">
+        <v>265.9642</v>
       </c>
     </row>
     <row r="143">
       <c t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">NUC</t>
+          <t xml:space="preserve">RBU</t>
         </is>
       </c>
       <c t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. CHARM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C143">
-        <v>-0.0070</v>
+        <v>0.6606</v>
       </c>
       <c t="n" r="D143">
-        <v>-0.3700</v>
+        <v>-1.9155</v>
       </c>
       <c t="n" r="E143">
-        <v>7.8618</v>
+        <v>1.9000</v>
       </c>
       <c t="n" r="F143">
-        <v>-0.3728</v>
+        <v>-1.2025</v>
       </c>
       <c t="n" r="G143">
-        <v>2.2743</v>
-      </c>
-      <c t="n" r="H143">
-        <v>130.9976</v>
+        <v>2.5327</v>
       </c>
     </row>
     <row r="144">
       <c t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">AHR</t>
+          <t xml:space="preserve">NUC</t>
         </is>
       </c>
       <c t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ONUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. CHARM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C144">
-        <v>-1.9900</v>
+        <v>-0.0079</v>
       </c>
       <c t="n" r="D144">
-        <v>-1.5851</v>
+        <v>-0.3706</v>
       </c>
       <c t="n" r="E144">
-        <v>3.6778</v>
+        <v>7.8591</v>
       </c>
       <c t="n" r="F144">
-        <v>-1.5812</v>
+        <v>-0.3738</v>
       </c>
       <c t="n" r="G144">
-        <v>1.0950</v>
+        <v>2.2653</v>
+      </c>
+      <c t="n" r="H144">
+        <v>131.0070</v>
       </c>
     </row>
     <row r="145">
       <c t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">OKG</t>
+          <t xml:space="preserve">AHR</t>
         </is>
       </c>
       <c t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. EMLAK JET GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ONUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C145">
-        <v>-0.1356</v>
+        <v>-1.9891</v>
       </c>
       <c t="n" r="D145">
-        <v>-1.7573</v>
+        <v>-1.5848</v>
       </c>
       <c t="n" r="E145">
-        <v>2.1406</v>
+        <v>3.6843</v>
       </c>
       <c t="n" r="F145">
-        <v>-1.6423</v>
+        <v>-1.5803</v>
       </c>
       <c t="n" r="G145">
-        <v>1.0196</v>
-      </c>
-      <c t="n" r="H145">
-        <v>70.4913</v>
+        <v>1.0925</v>
       </c>
     </row>
     <row r="146">
       <c t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">BKA</t>
+          <t xml:space="preserve">OKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ANKA GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. EMLAK JET GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C146">
+        <v>-0.1324</v>
       </c>
       <c t="n" r="D146">
-        <v>0.0000</v>
+        <v>-1.7581</v>
       </c>
       <c t="n" r="E146">
-        <v>0.0000</v>
+        <v>2.1513</v>
       </c>
       <c t="n" r="F146">
-        <v>0.0000</v>
+        <v>-1.6391</v>
       </c>
       <c t="n" r="G146">
-        <v>0.0000</v>
+        <v>1.0259</v>
       </c>
       <c t="n" r="H146">
-        <v>0.0000</v>
+        <v>70.5197</v>
       </c>
     </row>
     <row r="147">
       <c t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">HP5</t>
+          <t xml:space="preserve">BKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ANKA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="D147">
+        <v>0.0000</v>
       </c>
       <c t="n" r="E147">
         <v>0.0000</v>
@@ -4578,16 +4584,19 @@
       <c t="n" r="G147">
         <v>0.0000</v>
       </c>
+      <c t="n" r="H147">
+        <v>0.0000</v>
+      </c>
     </row>
     <row r="148">
       <c t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">HP4</t>
+          <t xml:space="preserve">HP5</t>
         </is>
       </c>
       <c t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ MASTERTÜRK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="E148">
@@ -4603,19 +4612,13 @@
     <row r="149">
       <c t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">NGA</t>
+          <t xml:space="preserve">HP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C149">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="D149">
-        <v>0.0000</v>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ MASTERTÜRK GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="E149">
         <v>0.0000</v>
@@ -4630,13 +4633,16 @@
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">NFA</t>
+          <t xml:space="preserve">NGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C150">
+        <v>0.0000</v>
       </c>
       <c t="n" r="D150">
         <v>0.0000</v>
@@ -4654,12 +4660,12 @@
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">RF1</t>
+          <t xml:space="preserve">NFA</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D151">
@@ -4678,13 +4684,22 @@
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">RDO</t>
+          <t xml:space="preserve">RF1</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN OTEL GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="D152">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="E152">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="F152">
+        <v>0.0000</v>
       </c>
       <c t="n" r="G152">
         <v>0.0000</v>
@@ -4693,12 +4708,12 @@
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">RMK</t>
+          <t xml:space="preserve">RDO</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EMLAK KATILIM YENİ EVİM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN OTEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G153">
@@ -4708,12 +4723,12 @@
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">RF2</t>
+          <t xml:space="preserve">RMK</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EMLAK KATILIM YENİ EVİM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G154">
@@ -4723,12 +4738,12 @@
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">RSM</t>
+          <t xml:space="preserve">RF2</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SMART PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G155">
@@ -4738,12 +4753,12 @@
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">RSO</t>
+          <t xml:space="preserve">RSM</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SONNE PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SMART PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G156">
@@ -4753,12 +4768,12 @@
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">RTO</t>
+          <t xml:space="preserve">RSO</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TOROS PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SONNE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G157">
@@ -4768,12 +4783,12 @@
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">RGN</t>
+          <t xml:space="preserve">RTO</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TOROS PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G158">
@@ -4783,2341 +4798,2335 @@
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">RF3</t>
+          <t xml:space="preserve">RGN</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C159">
-        <v>-0.1325</v>
-      </c>
-      <c t="n" r="D159">
-        <v>-0.6459</v>
-      </c>
-      <c t="n" r="F159">
-        <v>-0.8738</v>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="G159">
-        <v>-0.1032</v>
+        <v>0.0000</v>
       </c>
     </row>
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">IIG</t>
+          <t xml:space="preserve">RF3</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C160">
-        <v>2.1698</v>
+        <v>-0.1365</v>
       </c>
       <c t="n" r="D160">
-        <v>8.7863</v>
-      </c>
-      <c t="n" r="E160">
-        <v>17.3612</v>
+        <v>-0.6466</v>
       </c>
       <c t="n" r="F160">
-        <v>8.9296</v>
+        <v>-0.8777</v>
       </c>
       <c t="n" r="G160">
-        <v>-0.5672</v>
-      </c>
-      <c t="n" r="H160">
-        <v>153.0418</v>
-      </c>
-      <c t="n" r="I160">
-        <v>495.8691</v>
+        <v>-0.4032</v>
       </c>
     </row>
     <row r="161">
       <c t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">NUN</t>
+          <t xml:space="preserve">IIG</t>
         </is>
       </c>
       <c t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. KELEŞOĞLU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C161">
-        <v>-0.2495</v>
+        <v>2.1761</v>
       </c>
       <c t="n" r="D161">
-        <v>-0.7629</v>
+        <v>8.7817</v>
       </c>
       <c t="n" r="E161">
-        <v>-0.2610</v>
+        <v>17.3563</v>
       </c>
       <c t="n" r="F161">
-        <v>-0.8452</v>
+        <v>8.9363</v>
       </c>
       <c t="n" r="G161">
-        <v>-1.5840</v>
+        <v>-0.5654</v>
+      </c>
+      <c t="n" r="H161">
+        <v>153.0514</v>
+      </c>
+      <c t="n" r="I161">
+        <v>495.9045</v>
       </c>
     </row>
     <row r="162">
       <c t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">ZPV</t>
+          <t xml:space="preserve">NUN</t>
         </is>
       </c>
       <c t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. KELEŞOĞLU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C162">
-        <v>9.1011</v>
+        <v>-0.2583</v>
       </c>
       <c t="n" r="D162">
-        <v>8.7438</v>
+        <v>-0.7645</v>
       </c>
       <c t="n" r="E162">
-        <v>2.5161</v>
+        <v>-0.2625</v>
       </c>
       <c t="n" r="F162">
-        <v>7.8282</v>
+        <v>-0.8541</v>
       </c>
       <c t="n" r="G162">
-        <v>-4.8774</v>
-      </c>
-      <c t="n" r="H162">
-        <v>99.8856</v>
+        <v>-1.5858</v>
       </c>
     </row>
     <row r="163">
       <c t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">OO2</t>
+          <t xml:space="preserve">ZPV</t>
         </is>
       </c>
       <c t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
         </is>
       </c>
       <c t="n" r="C163">
-        <v>-2.2270</v>
+        <v>8.7644</v>
       </c>
       <c t="n" r="D163">
-        <v>-10.0737</v>
+        <v>9.1403</v>
       </c>
       <c t="n" r="E163">
-        <v>-11.8306</v>
+        <v>3.4521</v>
       </c>
       <c t="n" r="F163">
-        <v>-10.2211</v>
+        <v>7.4955</v>
       </c>
       <c t="n" r="G163">
-        <v>-7.4394</v>
+        <v>-5.2960</v>
+      </c>
+      <c t="n" r="H163">
+        <v>99.1849</v>
       </c>
     </row>
     <row r="164">
       <c t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">RYZ</t>
+          <t xml:space="preserve">OO2</t>
         </is>
       </c>
       <c t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C164">
-        <v>0.3860</v>
+        <v>-2.2540</v>
       </c>
       <c t="n" r="D164">
-        <v>-0.5679</v>
+        <v>-10.0888</v>
       </c>
       <c t="n" r="E164">
-        <v>2.4264</v>
+        <v>-11.8505</v>
       </c>
       <c t="n" r="F164">
-        <v>-0.2973</v>
+        <v>-10.2459</v>
       </c>
       <c t="n" r="G164">
-        <v>-11.4613</v>
+        <v>-7.4618</v>
       </c>
     </row>
     <row r="165">
       <c t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">RSH</t>
+          <t xml:space="preserve">RYZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SEYHAN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C165">
-        <v>0.1829</v>
+        <v>0.3866</v>
       </c>
       <c t="n" r="D165">
-        <v>4.2777</v>
+        <v>-0.5683</v>
       </c>
       <c t="n" r="E165">
-        <v>4.7470</v>
+        <v>2.4273</v>
       </c>
       <c t="n" r="F165">
-        <v>4.0743</v>
+        <v>-0.2967</v>
       </c>
       <c t="n" r="G165">
-        <v>-13.4226</v>
+        <v>-11.4602</v>
       </c>
     </row>
     <row r="166">
       <c t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">ZVD</t>
+          <t xml:space="preserve">RSH</t>
         </is>
       </c>
       <c t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SEYHAN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C166">
-        <v>-0.0352</v>
+        <v>0.1897</v>
       </c>
       <c t="n" r="D166">
-        <v>-0.1082</v>
+        <v>4.2860</v>
       </c>
       <c t="n" r="E166">
-        <v>-17.3192</v>
+        <v>4.7670</v>
       </c>
       <c t="n" r="F166">
-        <v>-0.1296</v>
+        <v>4.0814</v>
       </c>
       <c t="n" r="G166">
-        <v>-13.9660</v>
-      </c>
-      <c t="n" r="H166">
-        <v>196.5131</v>
+        <v>-13.4158</v>
       </c>
     </row>
     <row r="167">
       <c t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">YG6</t>
+          <t xml:space="preserve">ZVD</t>
         </is>
       </c>
       <c t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MANOLYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C167">
-        <v>-0.5482</v>
+        <v>-0.0360</v>
       </c>
       <c t="n" r="D167">
-        <v>-1.5650</v>
+        <v>-0.1083</v>
       </c>
       <c t="n" r="E167">
-        <v>-17.3543</v>
+        <v>-17.3196</v>
       </c>
       <c t="n" r="F167">
-        <v>-1.7429</v>
+        <v>-0.1304</v>
       </c>
       <c t="n" r="G167">
-        <v>-18.5465</v>
+        <v>-13.9668</v>
       </c>
       <c t="n" r="H167">
-        <v>-3.0119</v>
+        <v>196.4797</v>
       </c>
     </row>
     <row r="168">
       <c t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">YG3</t>
+          <t xml:space="preserve">YG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MANOLYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C168">
-        <v>-0.2887</v>
+        <v>-0.5609</v>
       </c>
       <c t="n" r="D168">
-        <v>-0.8455</v>
+        <v>-1.5655</v>
       </c>
       <c t="n" r="E168">
-        <v>-23.3501</v>
+        <v>-17.3547</v>
       </c>
       <c t="n" r="F168">
-        <v>-0.9518</v>
+        <v>-1.7555</v>
       </c>
       <c t="n" r="G168">
-        <v>-24.4825</v>
+        <v>-18.5329</v>
       </c>
       <c t="n" r="H168">
-        <v>350.2733</v>
+        <v>-2.9706</v>
       </c>
     </row>
     <row r="169">
       <c t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">REO</t>
+          <t xml:space="preserve">YG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C169">
-        <v>-0.0160</v>
+        <v>-0.2961</v>
       </c>
       <c t="n" r="D169">
-        <v>-0.0525</v>
+        <v>-0.8455</v>
       </c>
       <c t="n" r="E169">
-        <v>-0.0856</v>
+        <v>-23.3503</v>
       </c>
       <c t="n" r="F169">
-        <v>-0.0611</v>
+        <v>-0.9591</v>
       </c>
       <c t="n" r="G169">
-        <v>-24.5121</v>
+        <v>-24.4787</v>
+      </c>
+      <c t="n" r="H169">
+        <v>350.3201</v>
       </c>
     </row>
     <row r="170">
       <c t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">AZ7</t>
+          <t xml:space="preserve">REO</t>
         </is>
       </c>
       <c t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C170">
-        <v>-0.0790</v>
+        <v>-0.0160</v>
       </c>
       <c t="n" r="D170">
-        <v>-0.2925</v>
+        <v>-0.0526</v>
       </c>
       <c t="n" r="E170">
-        <v>-50.6041</v>
+        <v>-0.0857</v>
       </c>
       <c t="n" r="F170">
-        <v>-1.0418</v>
+        <v>-0.0611</v>
       </c>
       <c t="n" r="G170">
-        <v>-30.3422</v>
-      </c>
-      <c t="n" r="H170">
-        <v>70.9595</v>
-      </c>
-      <c t="n" r="I170">
-        <v>786.2764</v>
+        <v>-24.5123</v>
       </c>
     </row>
     <row r="171">
       <c t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">YG5</t>
+          <t xml:space="preserve">AZ7</t>
         </is>
       </c>
       <c t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FULYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C171">
-        <v>-0.6548</v>
+        <v>-0.0799</v>
       </c>
       <c t="n" r="D171">
-        <v>-1.7448</v>
+        <v>-0.2706</v>
       </c>
       <c t="n" r="E171">
-        <v>-30.4544</v>
+        <v>-50.6351</v>
       </c>
       <c t="n" r="F171">
-        <v>-1.8909</v>
+        <v>-1.0427</v>
       </c>
       <c t="n" r="G171">
-        <v>-30.8165</v>
+        <v>-30.3407</v>
       </c>
       <c t="n" r="H171">
-        <v>102.9260</v>
+        <v>71.0477</v>
+      </c>
+      <c t="n" r="I171">
+        <v>785.2236</v>
       </c>
     </row>
     <row r="172">
       <c t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">RG8</t>
+          <t xml:space="preserve">YG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. MERİÇ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FULYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C172">
-        <v>0.1529</v>
+        <v>-0.6669</v>
       </c>
       <c t="n" r="D172">
-        <v>-0.5650</v>
+        <v>-1.7460</v>
       </c>
       <c t="n" r="E172">
-        <v>-17.9148</v>
+        <v>-30.4542</v>
       </c>
       <c t="n" r="F172">
-        <v>-0.0417</v>
+        <v>-1.9029</v>
       </c>
       <c t="n" r="G172">
-        <v>-40.5079</v>
+        <v>-30.8345</v>
       </c>
       <c t="n" r="H172">
-        <v>91.4134</v>
+        <v>102.9685</v>
       </c>
     </row>
     <row r="173">
       <c t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">NG3</t>
+          <t xml:space="preserve">RG8</t>
         </is>
       </c>
       <c t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. MERİÇ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C173">
-        <v>-0.1990</v>
+        <v>0.1793</v>
       </c>
       <c t="n" r="D173">
-        <v>-3.4709</v>
+        <v>-0.5372</v>
       </c>
       <c t="n" r="E173">
-        <v>5.0995</v>
+        <v>-17.8833</v>
       </c>
       <c t="n" r="F173">
-        <v>-7.3243</v>
+        <v>-0.0154</v>
       </c>
       <c t="n" r="G173">
-        <v>-40.9141</v>
+        <v>-40.4956</v>
       </c>
       <c t="n" r="H173">
-        <v>113.6813</v>
+        <v>91.4592</v>
       </c>
     </row>
     <row r="174">
       <c t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">UG2</t>
+          <t xml:space="preserve">NG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">ÜNLÜ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C174">
-        <v>-0.4478</v>
+        <v>-0.2029</v>
       </c>
       <c t="n" r="D174">
-        <v>-18.4382</v>
+        <v>-3.4713</v>
       </c>
       <c t="n" r="E174">
-        <v>-40.7979</v>
+        <v>5.0972</v>
       </c>
       <c t="n" r="F174">
-        <v>-52.0249</v>
+        <v>-7.3278</v>
       </c>
       <c t="n" r="G174">
-        <v>-41.7111</v>
+        <v>-40.9147</v>
       </c>
       <c t="n" r="H174">
-        <v>-2.7363</v>
-      </c>
-      <c t="n" r="I174">
-        <v>217.3950</v>
+        <v>113.6834</v>
       </c>
     </row>
     <row r="175">
       <c t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">NH3</t>
+          <t xml:space="preserve">UG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY  YÖNETİMİ A.Ş TÜRKAZ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ÜNLÜ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C175">
-        <v>-4.1174</v>
+        <v>-0.4457</v>
       </c>
       <c t="n" r="D175">
-        <v>-23.7500</v>
+        <v>-18.4531</v>
       </c>
       <c t="n" r="E175">
-        <v>-25.5489</v>
+        <v>-40.7955</v>
       </c>
       <c t="n" r="F175">
-        <v>-26.0754</v>
+        <v>-52.0240</v>
       </c>
       <c t="n" r="G175">
-        <v>-43.1260</v>
+        <v>-41.7118</v>
       </c>
       <c t="n" r="H175">
-        <v>40.5884</v>
+        <v>-2.7176</v>
+      </c>
+      <c t="n" r="I175">
+        <v>217.4015</v>
       </c>
     </row>
     <row r="176">
       <c t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">NGO</t>
+          <t xml:space="preserve">NH3</t>
         </is>
       </c>
       <c t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY  YÖNETİMİ A.Ş TÜRKAZ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C176">
-        <v>3.0037</v>
+        <v>-4.1269</v>
       </c>
       <c t="n" r="D176">
-        <v>12.1224</v>
+        <v>-23.7561</v>
       </c>
       <c t="n" r="E176">
-        <v>15.7597</v>
+        <v>-21.1829</v>
       </c>
       <c t="n" r="F176">
-        <v>11.6873</v>
+        <v>-26.0828</v>
       </c>
       <c t="n" r="G176">
-        <v>-47.3296</v>
+        <v>-43.1308</v>
+      </c>
+      <c t="n" r="H176">
+        <v>40.5794</v>
       </c>
     </row>
     <row r="177">
       <c t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">IY1</t>
+          <t xml:space="preserve">NGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. V STATÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C177">
-        <v>-82.7363</v>
+        <v>3.1090</v>
       </c>
       <c t="n" r="D177">
-        <v>-83.9038</v>
+        <v>13.0128</v>
       </c>
       <c t="n" r="E177">
-        <v>-76.8902</v>
+        <v>15.7960</v>
       </c>
       <c t="n" r="F177">
-        <v>-83.9186</v>
+        <v>11.8015</v>
       </c>
       <c t="n" r="G177">
-        <v>-55.6636</v>
+        <v>-43.6593</v>
       </c>
     </row>
     <row r="178">
       <c t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">RG1</t>
+          <t xml:space="preserve">IY1</t>
         </is>
       </c>
       <c t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. YILDIZ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. V STATÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C178">
-        <v>2.9650</v>
+        <v>-82.7493</v>
       </c>
       <c t="n" r="D178">
-        <v>7.0209</v>
+        <v>-83.9147</v>
       </c>
       <c t="n" r="E178">
-        <v>-9.7866</v>
+        <v>-76.2513</v>
       </c>
       <c t="n" r="F178">
-        <v>-13.7445</v>
+        <v>-83.9307</v>
       </c>
       <c t="n" r="G178">
-        <v>-59.3866</v>
-      </c>
-      <c t="n" r="H178">
-        <v>-20.8463</v>
-      </c>
-      <c t="n" r="I178">
-        <v>330.1256</v>
+        <v>-55.7174</v>
       </c>
     </row>
     <row r="179">
       <c t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">GF3</t>
+          <t xml:space="preserve">RG1</t>
         </is>
       </c>
       <c t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. YILDIZ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C179">
-        <v>-14.5731</v>
+        <v>2.8397</v>
       </c>
       <c t="n" r="D179">
-        <v>-30.1232</v>
+        <v>6.5514</v>
       </c>
       <c t="n" r="E179">
-        <v>442.8826</v>
+        <v>-10.0383</v>
       </c>
       <c t="n" r="F179">
-        <v>-30.1259</v>
+        <v>-13.8495</v>
       </c>
       <c t="n" r="G179">
-        <v>-63.5773</v>
+        <v>-59.4409</v>
+      </c>
+      <c t="n" r="H179">
+        <v>-20.9417</v>
+      </c>
+      <c t="n" r="I179">
+        <v>330.1898</v>
       </c>
     </row>
     <row r="180">
       <c t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">YD1</t>
+          <t xml:space="preserve">GF3</t>
         </is>
       </c>
       <c t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C180">
-        <v>-22.7260</v>
+        <v>-14.7392</v>
       </c>
       <c t="n" r="D180">
-        <v>-77.0688</v>
+        <v>-30.2450</v>
       </c>
       <c t="n" r="E180">
-        <v>-75.8932</v>
+        <v>455.3639</v>
       </c>
       <c t="n" r="F180">
-        <v>-77.1033</v>
+        <v>-30.2617</v>
       </c>
       <c t="n" r="G180">
-        <v>-67.5054</v>
-      </c>
-      <c t="n" r="H180">
-        <v>-84.9616</v>
-      </c>
-      <c t="n" r="I180">
-        <v>-45.0587</v>
+        <v>-63.4704</v>
       </c>
     </row>
     <row r="181">
       <c t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">RP5</t>
+          <t xml:space="preserve">YD1</t>
         </is>
       </c>
       <c t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş.MİLENYUM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C181">
-        <v>-2.5262</v>
+        <v>-22.8052</v>
       </c>
       <c t="n" r="D181">
-        <v>12.2127</v>
+        <v>-77.0899</v>
       </c>
       <c t="n" r="E181">
-        <v>-65.4639</v>
+        <v>-75.9150</v>
       </c>
       <c t="n" r="F181">
-        <v>55.5164</v>
+        <v>-77.1268</v>
       </c>
       <c t="n" r="G181">
-        <v>-67.5486</v>
+        <v>-67.5249</v>
       </c>
       <c t="n" r="H181">
-        <v>-68.8094</v>
+        <v>-84.9749</v>
       </c>
       <c t="n" r="I181">
-        <v>-16.8900</v>
+        <v>-45.1150</v>
       </c>
     </row>
     <row r="182">
       <c t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">YG2</t>
+          <t xml:space="preserve">RP5</t>
         </is>
       </c>
       <c t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYÇİÇEĞİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş.MİLENYUM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C182">
-        <v>-87.7193</v>
+        <v>-2.7621</v>
       </c>
       <c t="n" r="D182">
-        <v>-98.7931</v>
+        <v>11.8139</v>
       </c>
       <c t="n" r="E182">
-        <v>-96.2567</v>
+        <v>-65.5597</v>
       </c>
       <c t="n" r="F182">
-        <v>-93.9130</v>
+        <v>55.1400</v>
       </c>
       <c t="n" r="G182">
-        <v>-98.9811</v>
+        <v>-67.5942</v>
       </c>
       <c t="n" r="H182">
-        <v>-99.9998</v>
+        <v>-68.8743</v>
+      </c>
+      <c t="n" r="I182">
+        <v>-16.2808</v>
       </c>
     </row>
     <row r="183">
       <c t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">MMG</t>
+          <t xml:space="preserve">YG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MEYDAN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYÇİÇEĞİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C183">
-        <v>-98.8497</v>
+        <v>-87.7193</v>
       </c>
       <c t="n" r="D183">
-        <v>-99.0940</v>
+        <v>-98.7931</v>
       </c>
       <c t="n" r="E183">
-        <v>-99.0381</v>
+        <v>-96.2567</v>
       </c>
       <c t="n" r="F183">
-        <v>-99.1020</v>
+        <v>-93.9130</v>
       </c>
       <c t="n" r="G183">
-        <v>-99.1391</v>
+        <v>-98.9811</v>
       </c>
       <c t="n" r="H183">
-        <v>-98.5285</v>
+        <v>-99.9998</v>
       </c>
     </row>
     <row r="184">
       <c t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">SGF</t>
+          <t xml:space="preserve">MMG</t>
         </is>
       </c>
       <c t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. SOFAZ ÖZEL GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MEYDAN GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C184">
+        <v>-98.9063</v>
+      </c>
+      <c t="n" r="D184">
+        <v>-99.1386</v>
+      </c>
+      <c t="n" r="E184">
+        <v>-99.0855</v>
+      </c>
+      <c t="n" r="F184">
+        <v>-99.1462</v>
+      </c>
+      <c t="n" r="G184">
+        <v>-99.1814</v>
+      </c>
+      <c t="n" r="H184">
+        <v>-98.6004</v>
       </c>
     </row>
     <row r="185">
       <c t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">NKB</t>
+          <t xml:space="preserve">SGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV BEŞİKTAŞ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. SOFAZ ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">NEV</t>
+          <t xml:space="preserve">NKB</t>
         </is>
       </c>
       <c t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV KADIKÖY KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV BEŞİKTAŞ KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">NKE</t>
+          <t xml:space="preserve">NEV</t>
         </is>
       </c>
       <c t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV KADIKÖY KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">MUG</t>
+          <t xml:space="preserve">NKE</t>
         </is>
       </c>
       <c t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C188">
-        <v>1.0120</v>
-      </c>
-      <c t="n" r="D188">
-        <v>2.9589</v>
-      </c>
-      <c t="n" r="F188">
-        <v>3.6430</v>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV KATILIM GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="189">
       <c t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">BGV</t>
+          <t xml:space="preserve">MUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C189">
+        <v>1.1611</v>
+      </c>
+      <c t="n" r="D189">
+        <v>3.0983</v>
+      </c>
+      <c t="n" r="F189">
+        <v>3.7960</v>
       </c>
     </row>
     <row r="190">
       <c t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">BGA</t>
+          <t xml:space="preserve">BGV</t>
         </is>
       </c>
       <c t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">ALLBATROSS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">AB2</t>
+          <t xml:space="preserve">BGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">ALLBATROSS PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C191">
-        <v>-16.3732</v>
-      </c>
-      <c t="n" r="D191">
-        <v>-38.1159</v>
-      </c>
-      <c t="n" r="F191">
-        <v>-40.6957</v>
+          <t xml:space="preserve">ALLBATROSS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="192">
       <c t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">AY2</t>
+          <t xml:space="preserve">AB2</t>
         </is>
       </c>
       <c t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ARVA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALLBATROSS PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C192">
-        <v>-10.2068</v>
+        <v>-16.9701</v>
       </c>
       <c t="n" r="D192">
-        <v>-63.1088</v>
+        <v>-38.3130</v>
       </c>
       <c t="n" r="F192">
-        <v>-28.5179</v>
+        <v>-41.1190</v>
       </c>
     </row>
     <row r="193">
       <c t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">BGO</t>
+          <t xml:space="preserve">AY2</t>
         </is>
       </c>
       <c t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BAHAR GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ARVA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C193">
+        <v>-10.0726</v>
+      </c>
+      <c t="n" r="D193">
+        <v>-63.1112</v>
+      </c>
+      <c t="n" r="F193">
+        <v>-28.4110</v>
       </c>
     </row>
     <row r="194">
       <c t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">TLG</t>
+          <t xml:space="preserve">BGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C194">
-        <v>1.1416</v>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BAHAR GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="195">
       <c t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">AY1</t>
+          <t xml:space="preserve">TLG</t>
         </is>
       </c>
       <c t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BMS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C195">
-        <v>0.8035</v>
-      </c>
-      <c t="n" r="D195">
-        <v>1.3490</v>
-      </c>
-      <c t="n" r="F195">
-        <v>1.8603</v>
+        <v>1.1444</v>
       </c>
     </row>
     <row r="196">
       <c t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">DGR</t>
+          <t xml:space="preserve">AY1</t>
         </is>
       </c>
       <c t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞRUL GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BMS GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C196">
+        <v>0.8297</v>
+      </c>
+      <c t="n" r="D196">
+        <v>1.4820</v>
+      </c>
+      <c t="n" r="F196">
+        <v>1.8868</v>
       </c>
     </row>
     <row r="197">
       <c t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">DRO</t>
+          <t xml:space="preserve">DGR</t>
         </is>
       </c>
       <c t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞRUL PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞRUL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">AN4</t>
+          <t xml:space="preserve">DRO</t>
         </is>
       </c>
       <c t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞRUL PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">TG2</t>
+          <t xml:space="preserve">AN4</t>
         </is>
       </c>
       <c t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">TUP</t>
+          <t xml:space="preserve">TG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. TÜRKEL BİRDALLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">UGP</t>
+          <t xml:space="preserve">TUP</t>
         </is>
       </c>
       <c t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. TÜRKEL BİRDALLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">NGC</t>
+          <t xml:space="preserve">UGP</t>
         </is>
       </c>
       <c t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">ANATOLİA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MG HARBOUR GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C202">
-        <v>1.4583</v>
-      </c>
-      <c t="n" r="D202">
-        <v>1.9144</v>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="203">
       <c t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">GYU</t>
+          <t xml:space="preserve">NGC</t>
         </is>
       </c>
       <c t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLİA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MG HARBOUR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C203">
-        <v>1.8045</v>
+        <v>1.4880</v>
       </c>
       <c t="n" r="D203">
-        <v>419.1642</v>
-      </c>
-      <c t="n" r="E203">
-        <v>460.9434</v>
-      </c>
-      <c t="n" r="F203">
-        <v>424.2458</v>
+        <v>2.1132</v>
       </c>
     </row>
     <row r="204">
       <c t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">DGG</t>
+          <t xml:space="preserve">GYU</t>
         </is>
       </c>
       <c t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C204">
-        <v>12.1074</v>
+        <v>1.8628</v>
       </c>
       <c t="n" r="D204">
-        <v>44.6009</v>
+        <v>418.9450</v>
       </c>
       <c t="n" r="E204">
-        <v>59.2135</v>
+        <v>460.7399</v>
       </c>
       <c t="n" r="F204">
-        <v>46.4845</v>
+        <v>424.5459</v>
       </c>
     </row>
     <row r="205">
       <c t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">OGN</t>
+          <t xml:space="preserve">DGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C205">
+        <v>12.1116</v>
+      </c>
+      <c t="n" r="D205">
+        <v>44.4641</v>
+      </c>
+      <c t="n" r="E205">
+        <v>59.0411</v>
+      </c>
+      <c t="n" r="F205">
+        <v>46.4899</v>
       </c>
     </row>
     <row r="206">
       <c t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">SGG</t>
+          <t xml:space="preserve">OGN</t>
         </is>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C206">
-        <v>-0.0451</v>
-      </c>
-      <c t="n" r="D206">
-        <v>-0.1099</v>
-      </c>
-      <c t="n" r="E206">
-        <v>19.4004</v>
-      </c>
-      <c t="n" r="F206">
-        <v>-0.1365</v>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="207">
       <c t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">YGG</t>
+          <t xml:space="preserve">SGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C207">
-        <v>-0.0215</v>
+        <v>-0.0461</v>
+      </c>
+      <c t="n" r="D207">
+        <v>-0.1100</v>
+      </c>
+      <c t="n" r="E207">
+        <v>19.3977</v>
+      </c>
+      <c t="n" r="F207">
+        <v>-0.1376</v>
       </c>
     </row>
     <row r="208">
       <c t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">BGU</t>
+          <t xml:space="preserve">YGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C208">
+        <v>-0.0186</v>
       </c>
     </row>
     <row r="209">
       <c t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">ON3</t>
+          <t xml:space="preserve">BGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C209">
-        <v>3.1458</v>
-      </c>
-      <c t="n" r="D209">
-        <v>9.0482</v>
-      </c>
-      <c t="n" r="E209">
-        <v>19.5427</v>
-      </c>
-      <c t="n" r="F209">
-        <v>10.4844</v>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="210">
       <c t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">RZ1</t>
+          <t xml:space="preserve">ON3</t>
         </is>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C210">
+        <v>3.2544</v>
+      </c>
+      <c t="n" r="D210">
+        <v>9.0593</v>
+      </c>
+      <c t="n" r="E210">
+        <v>19.5462</v>
+      </c>
+      <c t="n" r="F210">
+        <v>10.6007</v>
       </c>
     </row>
     <row r="211">
       <c t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">ONU</t>
+          <t xml:space="preserve">RZ1</t>
         </is>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C211">
-        <v>-0.1081</v>
-      </c>
-      <c t="n" r="D211">
-        <v>-0.3305</v>
-      </c>
-      <c t="n" r="F211">
-        <v>-0.3296</v>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="212">
       <c t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">BAK</t>
+          <t xml:space="preserve">ONU</t>
         </is>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BAKIRCI PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C212">
-        <v>-0.9089</v>
+        <v>-0.1081</v>
       </c>
       <c t="n" r="D212">
-        <v>6.7241</v>
+        <v>-0.3217</v>
+      </c>
+      <c t="n" r="F212">
+        <v>-0.3296</v>
       </c>
     </row>
     <row r="213">
       <c t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">BLM</t>
+          <t xml:space="preserve">BAK</t>
         </is>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BALMUMCU PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BAKIRCI PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C213">
-        <v>-0.1809</v>
+        <v>-0.9368</v>
+      </c>
+      <c t="n" r="D213">
+        <v>6.7243</v>
       </c>
     </row>
     <row r="214">
       <c t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">BNE</t>
+          <t xml:space="preserve">BLM</t>
         </is>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BENESTA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BALMUMCU PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C214">
-        <v>-0.0350</v>
-      </c>
-      <c t="n" r="D214">
-        <v>-0.0990</v>
-      </c>
-      <c t="n" r="E214">
-        <v>12.7749</v>
-      </c>
-      <c t="n" r="F214">
-        <v>-0.1129</v>
+        <v>-0.1307</v>
       </c>
     </row>
     <row r="215">
       <c t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">BN2</t>
+          <t xml:space="preserve">BNE</t>
         </is>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BENESTA-2 PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BENESTA PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C215">
-        <v>0.7999</v>
+        <v>-0.0360</v>
       </c>
       <c t="n" r="D215">
-        <v>3.1065</v>
+        <v>-0.0990</v>
       </c>
       <c t="n" r="E215">
-        <v>12.5354</v>
+        <v>12.7747</v>
       </c>
       <c t="n" r="F215">
-        <v>3.1072</v>
+        <v>-0.1140</v>
       </c>
     </row>
     <row r="216">
       <c t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">GTR</t>
+          <t xml:space="preserve">BN2</t>
         </is>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. GÖKTÜRK-3 PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BENESTA-2 PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C216">
-        <v>-86.6379</v>
+        <v>0.7992</v>
       </c>
       <c t="n" r="D216">
-        <v>-99.8625</v>
+        <v>3.1140</v>
       </c>
       <c t="n" r="E216">
-        <v>-99.9887</v>
+        <v>12.5299</v>
       </c>
       <c t="n" r="F216">
-        <v>-99.9773</v>
+        <v>3.1065</v>
       </c>
     </row>
     <row r="217">
       <c t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">BRP</t>
+          <t xml:space="preserve">GTR</t>
         </is>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. GÖKTÜRK-3 PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C217">
+        <v>-87.9737</v>
+      </c>
+      <c t="n" r="D217">
+        <v>-99.8766</v>
+      </c>
+      <c t="n" r="E217">
+        <v>-99.9897</v>
+      </c>
+      <c t="n" r="F217">
+        <v>-99.9796</v>
       </c>
     </row>
     <row r="218">
       <c t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">ZDR</t>
+          <t xml:space="preserve">BRP</t>
         </is>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">IGJ</t>
+          <t xml:space="preserve">ZDR</t>
         </is>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C219">
-        <v>0.3694</v>
-      </c>
-      <c t="n" r="D219">
-        <v>0.4013</v>
-      </c>
-      <c t="n" r="E219">
-        <v>36.6673</v>
-      </c>
-      <c t="n" r="F219">
-        <v>0.5422</v>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="220">
       <c t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">TOP</t>
+          <t xml:space="preserve">IGJ</t>
         </is>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. TOPRAKTAN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C220">
+        <v>0.3803</v>
+      </c>
+      <c t="n" r="D220">
+        <v>0.4005</v>
+      </c>
+      <c t="n" r="E220">
+        <v>36.6576</v>
+      </c>
+      <c t="n" r="F220">
+        <v>0.5531</v>
       </c>
     </row>
     <row r="221">
       <c t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">ZUC</t>
+          <t xml:space="preserve">TOP</t>
         </is>
       </c>
       <c t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. TOPRAKTAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">BG1</t>
+          <t xml:space="preserve">ZUC</t>
         </is>
       </c>
       <c t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">BULLS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">BP1</t>
+          <t xml:space="preserve">BG1</t>
         </is>
       </c>
       <c t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">BULLS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">BULLS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">DLT</t>
+          <t xml:space="preserve">BP1</t>
         </is>
       </c>
       <c t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">BULLS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c t="inlineStr" r="A225">
         <is>
-          <t xml:space="preserve">BES</t>
+          <t xml:space="preserve">DLT</t>
         </is>
       </c>
       <c t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">DKG</t>
+          <t xml:space="preserve">BES</t>
         </is>
       </c>
       <c t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">DDO</t>
+          <t xml:space="preserve">DKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C227">
-        <v>5.5335</v>
-      </c>
-      <c t="n" r="D227">
-        <v>5.6438</v>
-      </c>
-      <c t="n" r="F227">
-        <v>11.2714</v>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="228">
       <c t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">DYD</t>
+          <t xml:space="preserve">DDO</t>
         </is>
       </c>
       <c t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C228">
+        <v>5.5784</v>
+      </c>
+      <c t="n" r="D228">
+        <v>7.9254</v>
+      </c>
+      <c t="n" r="E228">
+        <v>16.4845</v>
+      </c>
+      <c t="n" r="F228">
+        <v>11.3188</v>
       </c>
     </row>
     <row r="229">
       <c t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">FN6</t>
+          <t xml:space="preserve">DYD</t>
         </is>
       </c>
       <c t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">FDR</t>
+          <t xml:space="preserve">FN6</t>
         </is>
       </c>
       <c t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C230">
-        <v>0.8778</v>
-      </c>
-      <c t="n" r="D230">
-        <v>4.9719</v>
-      </c>
-      <c t="n" r="E230">
-        <v>13.6637</v>
-      </c>
-      <c t="n" r="F230">
-        <v>6.2829</v>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="231">
       <c t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">FLG</t>
+          <t xml:space="preserve">FDR</t>
         </is>
       </c>
       <c t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. FLORYA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C231">
-        <v>3.0341</v>
+        <v>0.9522</v>
       </c>
       <c t="n" r="D231">
-        <v>9.5231</v>
+        <v>4.9498</v>
       </c>
       <c t="n" r="E231">
-        <v>20.6683</v>
+        <v>13.6359</v>
       </c>
       <c t="n" r="F231">
-        <v>10.8772</v>
+        <v>6.3613</v>
       </c>
     </row>
     <row r="232">
       <c t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">FGR</t>
+          <t xml:space="preserve">FLG</t>
         </is>
       </c>
       <c t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. GRN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. FLORYA PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C232">
-        <v>0.7844</v>
+        <v>3.1368</v>
       </c>
       <c t="n" r="D232">
-        <v>1.2849</v>
+        <v>9.5185</v>
       </c>
       <c t="n" r="E232">
-        <v>3.9829</v>
+        <v>20.6639</v>
       </c>
       <c t="n" r="F232">
-        <v>1.7877</v>
+        <v>10.9878</v>
       </c>
     </row>
     <row r="233">
       <c t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">FG2</t>
+          <t xml:space="preserve">FGR</t>
         </is>
       </c>
       <c t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. GRN GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C233">
+        <v>0.7604</v>
+      </c>
+      <c t="n" r="D233">
+        <v>1.2630</v>
+      </c>
+      <c t="n" r="E233">
+        <v>3.9331</v>
+      </c>
+      <c t="n" r="F233">
+        <v>1.7634</v>
       </c>
     </row>
     <row r="234">
       <c t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">FCN</t>
+          <t xml:space="preserve">FG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C234">
-        <v>0.9651</v>
-      </c>
-      <c t="n" r="D234">
-        <v>5.0627</v>
-      </c>
-      <c t="n" r="E234">
-        <v>13.7621</v>
-      </c>
-      <c t="n" r="F234">
-        <v>6.3749</v>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="235">
       <c t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">FG3</t>
+          <t xml:space="preserve">FCN</t>
         </is>
       </c>
       <c t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C235">
+        <v>1.0394</v>
+      </c>
+      <c t="n" r="D235">
+        <v>5.0406</v>
+      </c>
+      <c t="n" r="E235">
+        <v>13.7342</v>
+      </c>
+      <c t="n" r="F235">
+        <v>6.4532</v>
       </c>
     </row>
     <row r="236">
       <c t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">YSZ</t>
+          <t xml:space="preserve">FG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FYSZ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">FTI</t>
+          <t xml:space="preserve">YSZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FYSZ KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">FTT</t>
+          <t xml:space="preserve">FTI</t>
         </is>
       </c>
       <c t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. TRİO GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C238">
-        <v>-1.8464</v>
-      </c>
-      <c t="n" r="D238">
-        <v>-82.3180</v>
-      </c>
-      <c t="n" r="F238">
-        <v>-84.7276</v>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="239">
       <c t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">OLG</t>
+          <t xml:space="preserve">FTT</t>
         </is>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">GOLDEN GLOBAL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. TRİO GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C239">
+        <v>-1.8580</v>
+      </c>
+      <c t="n" r="D239">
+        <v>-82.0821</v>
+      </c>
+      <c t="n" r="F239">
+        <v>-84.7294</v>
       </c>
     </row>
     <row r="240">
       <c t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">OLP</t>
+          <t xml:space="preserve">OLG</t>
         </is>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">GOLDEN GLOBAL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">GOLDEN GLOBAL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">HVG</t>
+          <t xml:space="preserve">OLP</t>
         </is>
       </c>
       <c t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C241">
-        <v>-0.0502</v>
-      </c>
-      <c t="n" r="D241">
-        <v>-0.1443</v>
-      </c>
-      <c t="n" r="E241">
-        <v>30.4730</v>
-      </c>
-      <c t="n" r="F241">
-        <v>-0.1669</v>
+          <t xml:space="preserve">GOLDEN GLOBAL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="242">
       <c t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">HGG</t>
+          <t xml:space="preserve">HVG</t>
         </is>
       </c>
       <c t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C242">
-        <v>-0.0718</v>
+        <v>-0.0517</v>
       </c>
       <c t="n" r="D242">
-        <v>-0.2370</v>
+        <v>-0.1439</v>
       </c>
       <c t="n" r="E242">
-        <v>1624.6856</v>
+        <v>30.4730</v>
       </c>
       <c t="n" r="F242">
-        <v>-0.2592</v>
+        <v>-0.1684</v>
       </c>
     </row>
     <row r="243">
       <c t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">HV2</t>
+          <t xml:space="preserve">HGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C243">
+        <v>-0.0740</v>
+      </c>
+      <c t="n" r="D243">
+        <v>-0.2368</v>
+      </c>
+      <c t="n" r="E243">
+        <v>1624.8544</v>
+      </c>
+      <c t="n" r="F243">
+        <v>-0.2614</v>
       </c>
     </row>
     <row r="244">
       <c t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">HG2</t>
+          <t xml:space="preserve">HV2</t>
         </is>
       </c>
       <c t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">HVY</t>
+          <t xml:space="preserve">HG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YENİ UFUKLAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">HLN</t>
+          <t xml:space="preserve">HVY</t>
         </is>
       </c>
       <c t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C246">
-        <v>-4.1349</v>
-      </c>
-      <c t="n" r="D246">
-        <v>-14.1724</v>
-      </c>
-      <c t="n" r="F246">
-        <v>-15.5964</v>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YENİ UFUKLAR GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="247">
       <c t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">HMP</t>
+          <t xml:space="preserve">HLN</t>
         </is>
       </c>
       <c t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C247">
-        <v>-4.6059</v>
+        <v>-5.5249</v>
       </c>
       <c t="n" r="D247">
-        <v>-14.7149</v>
-      </c>
-      <c t="n" r="E247">
-        <v>-22.8546</v>
+        <v>-15.2772</v>
       </c>
       <c t="n" r="F247">
-        <v>-16.0197</v>
+        <v>-16.8203</v>
       </c>
     </row>
     <row r="248">
       <c t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">HIK</t>
+          <t xml:space="preserve">HMP</t>
         </is>
       </c>
       <c t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C248">
+        <v>-5.8945</v>
+      </c>
+      <c t="n" r="D248">
+        <v>-15.7472</v>
+      </c>
+      <c t="n" r="E248">
+        <v>-23.9768</v>
+      </c>
+      <c t="n" r="F248">
+        <v>-17.1542</v>
       </c>
     </row>
     <row r="249">
       <c t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">HG8</t>
+          <t xml:space="preserve">HIK</t>
         </is>
       </c>
       <c t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">HMA</t>
+          <t xml:space="preserve">HG8</t>
         </is>
       </c>
       <c t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">IRJ</t>
+          <t xml:space="preserve">HMA</t>
         </is>
       </c>
       <c t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">BRY</t>
+          <t xml:space="preserve">IRJ</t>
         </is>
       </c>
       <c t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BORYAL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">IDT</t>
+          <t xml:space="preserve">BRY</t>
         </is>
       </c>
       <c t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. GELİŞİM TRAKYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BORYAL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">IE1</t>
+          <t xml:space="preserve">IDT</t>
         </is>
       </c>
       <c t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. GELİŞİM TRAKYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">IY3</t>
+          <t xml:space="preserve">IE1</t>
         </is>
       </c>
       <c t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C255">
-        <v>-86.9959</v>
-      </c>
-      <c t="n" r="D255">
-        <v>-88.4657</v>
-      </c>
-      <c t="n" r="E255">
-        <v>-75.2623</v>
-      </c>
-      <c t="n" r="F255">
-        <v>-88.4760</v>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="256">
       <c t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">IY2</t>
+          <t xml:space="preserve">IY3</t>
         </is>
       </c>
       <c t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C256">
-        <v>-1.4050</v>
+        <v>-87.0180</v>
       </c>
       <c t="n" r="D256">
-        <v>-13.1597</v>
+        <v>-88.4845</v>
+      </c>
+      <c t="n" r="E256">
+        <v>-74.9807</v>
       </c>
       <c t="n" r="F256">
-        <v>-13.2416</v>
+        <v>-88.4955</v>
       </c>
     </row>
     <row r="257">
       <c t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">VMG</t>
+          <t xml:space="preserve">IY2</t>
         </is>
       </c>
       <c t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C257">
-        <v>-5.9294</v>
+        <v>-1.4537</v>
       </c>
       <c t="n" r="D257">
-        <v>-6.4677</v>
-      </c>
-      <c t="n" r="E257">
-        <v>-9.3565</v>
+        <v>-13.1964</v>
       </c>
       <c t="n" r="F257">
-        <v>-4.5530</v>
+        <v>-13.2843</v>
       </c>
     </row>
     <row r="258">
       <c t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">VMP</t>
+          <t xml:space="preserve">VMG</t>
         </is>
       </c>
       <c t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C258">
+        <v>-5.9369</v>
+      </c>
+      <c t="n" r="D258">
+        <v>-6.4678</v>
+      </c>
+      <c t="n" r="E258">
+        <v>-9.3600</v>
+      </c>
+      <c t="n" r="F258">
+        <v>-4.5606</v>
       </c>
     </row>
     <row r="259">
       <c t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">KPE</t>
+          <t xml:space="preserve">VMP</t>
         </is>
       </c>
       <c t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. KAR PAYI ÖDEYEN GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C259">
-        <v>3.1592</v>
+          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="260">
       <c t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">RIN</t>
+          <t xml:space="preserve">KPE</t>
         </is>
       </c>
       <c t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. RİNNOVA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. KAR PAYI ÖDEYEN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C260">
-        <v>0.1328</v>
+        <v>3.2647</v>
       </c>
     </row>
     <row r="261">
       <c t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">ITO</t>
+          <t xml:space="preserve">RIN</t>
         </is>
       </c>
       <c t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. T-FON PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. RİNNOVA PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C261">
+        <v>0.1300</v>
       </c>
     </row>
     <row r="262">
       <c t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">UNO</t>
+          <t xml:space="preserve">ITO</t>
         </is>
       </c>
       <c t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. UNİCON PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. T-FON PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">YAL</t>
+          <t xml:space="preserve">UNO</t>
         </is>
       </c>
       <c t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C263">
-        <v>80.6154</v>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. UNİCON PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="264">
       <c t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">YLP</t>
+          <t xml:space="preserve">YAL</t>
         </is>
       </c>
       <c t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C264">
+        <v>80.6243</v>
       </c>
     </row>
     <row r="265">
       <c t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">KBN</t>
+          <t xml:space="preserve">YLP</t>
         </is>
       </c>
       <c t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C265">
-        <v>2.4402</v>
-      </c>
-      <c t="n" r="D265">
-        <v>6.9822</v>
-      </c>
-      <c t="n" r="F265">
-        <v>8.0964</v>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="266">
       <c t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">KKR</t>
+          <t xml:space="preserve">KBN</t>
         </is>
       </c>
       <c t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C266">
-        <v>2.4423</v>
+        <v>2.5175</v>
       </c>
       <c t="n" r="D266">
-        <v>6.9616</v>
+        <v>6.9813</v>
       </c>
       <c t="n" r="F266">
-        <v>8.0759</v>
+        <v>8.1779</v>
       </c>
     </row>
     <row r="267">
       <c t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">MDG</t>
+          <t xml:space="preserve">KKR</t>
         </is>
       </c>
       <c t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞAN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C267">
+        <v>2.5197</v>
+      </c>
+      <c t="n" r="D267">
+        <v>6.9607</v>
+      </c>
+      <c t="n" r="F267">
+        <v>8.1575</v>
       </c>
     </row>
     <row r="268">
       <c t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">NAA</t>
+          <t xml:space="preserve">MDG</t>
         </is>
       </c>
       <c t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C268">
-        <v>-30.3727</v>
-      </c>
-      <c t="n" r="D268">
-        <v>-27.7859</v>
-      </c>
-      <c t="n" r="E268">
-        <v>-23.5600</v>
-      </c>
-      <c t="n" r="F268">
-        <v>-27.1962</v>
+          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="269">
       <c t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">NGB</t>
+          <t xml:space="preserve">NAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C269">
+        <v>-30.3786</v>
+      </c>
+      <c t="n" r="D269">
+        <v>-27.8370</v>
+      </c>
+      <c t="n" r="E269">
+        <v>-23.5361</v>
+      </c>
+      <c t="n" r="F269">
+        <v>-27.2025</v>
       </c>
     </row>
     <row r="270">
       <c t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">NBR</t>
+          <t xml:space="preserve">NGB</t>
         </is>
       </c>
       <c t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C270">
-        <v>-0.4679</v>
-      </c>
-      <c t="n" r="D270">
-        <v>25.9719</v>
-      </c>
-      <c t="n" r="E270">
-        <v>-33.2627</v>
-      </c>
-      <c t="n" r="F270">
-        <v>95.8267</v>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="271">
       <c t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">NGD</t>
+          <t xml:space="preserve">NBR</t>
         </is>
       </c>
       <c t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C271">
-        <v>21.6732</v>
+        <v>-0.4779</v>
+      </c>
+      <c t="n" r="D271">
+        <v>28.4483</v>
+      </c>
+      <c t="n" r="E271">
+        <v>-33.1418</v>
+      </c>
+      <c t="n" r="F271">
+        <v>95.8071</v>
       </c>
     </row>
     <row r="272">
       <c t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">GNC</t>
+          <t xml:space="preserve">NGD</t>
         </is>
       </c>
       <c t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. GNC KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C272">
-        <v>-0.3314</v>
-      </c>
-      <c t="n" r="D272">
-        <v>-1.0915</v>
-      </c>
-      <c t="n" r="F272">
-        <v>-2.2774</v>
+        <v>21.7143</v>
       </c>
     </row>
     <row r="273">
       <c t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">NIK</t>
+          <t xml:space="preserve">GNC</t>
         </is>
       </c>
       <c t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. GNC KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C273">
-        <v>-74.0298</v>
+        <v>-0.3409</v>
       </c>
       <c t="n" r="D273">
-        <v>-87.8295</v>
-      </c>
-      <c t="n" r="E273">
-        <v>-41.8884</v>
+        <v>-1.0573</v>
       </c>
       <c t="n" r="F273">
-        <v>137.2579</v>
+        <v>-2.2867</v>
       </c>
     </row>
     <row r="274">
       <c t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">NGR</t>
+          <t xml:space="preserve">NIK</t>
         </is>
       </c>
       <c t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. RİVA PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C274">
+        <v>-74.0296</v>
+      </c>
+      <c t="n" r="D274">
+        <v>-86.2078</v>
+      </c>
+      <c t="n" r="E274">
+        <v>-41.3398</v>
+      </c>
+      <c t="n" r="F274">
+        <v>137.2591</v>
       </c>
     </row>
     <row r="275">
       <c t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">NGU</t>
+          <t xml:space="preserve">NGR</t>
         </is>
       </c>
       <c t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. RİVA PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">NBP</t>
+          <t xml:space="preserve">NGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C276">
-        <v>-0.0547</v>
-      </c>
-      <c t="n" r="D276">
-        <v>-10.4514</v>
-      </c>
-      <c t="n" r="F276">
-        <v>-9.7078</v>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="277">
       <c t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">NP4</t>
+          <t xml:space="preserve">NBP</t>
         </is>
       </c>
       <c t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C277">
+        <v>-0.0559</v>
+      </c>
+      <c t="n" r="D277">
+        <v>-10.5141</v>
+      </c>
+      <c t="n" r="F277">
+        <v>-9.7088</v>
       </c>
     </row>
     <row r="278">
       <c t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">NKN</t>
+          <t xml:space="preserve">NP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C278">
-        <v>3.1447</v>
-      </c>
-      <c t="n" r="D278">
-        <v>-61.3858</v>
-      </c>
-      <c t="n" r="E278">
-        <v>-99.1136</v>
-      </c>
-      <c t="n" r="F278">
-        <v>-98.1739</v>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="279">
       <c t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">MAA</t>
+          <t xml:space="preserve">NKN</t>
         </is>
       </c>
       <c t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. MAANAA LEVENT PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C279">
+        <v>3.2794</v>
+      </c>
+      <c t="n" r="D279">
+        <v>-61.1064</v>
+      </c>
+      <c t="n" r="E279">
+        <v>-99.0862</v>
+      </c>
+      <c t="n" r="F279">
+        <v>-98.1715</v>
       </c>
     </row>
     <row r="280">
       <c t="inlineStr" r="A280">
         <is>
-          <t xml:space="preserve">NGM</t>
+          <t xml:space="preserve">MAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C280">
-        <v>-0.2988</v>
-      </c>
-      <c t="n" r="D280">
-        <v>0.9074</v>
-      </c>
-      <c t="n" r="E280">
-        <v>-97.7611</v>
-      </c>
-      <c t="n" r="F280">
-        <v>0.8311</v>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. MAANAA LEVENT PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="281">
       <c t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">NBA</t>
+          <t xml:space="preserve">NGM</t>
         </is>
       </c>
       <c t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C281">
-        <v>-29.2836</v>
+        <v>-0.2988</v>
       </c>
       <c t="n" r="D281">
-        <v>-32.9171</v>
+        <v>0.9074</v>
       </c>
       <c t="n" r="E281">
-        <v>1640.2534</v>
+        <v>-97.6087</v>
       </c>
       <c t="n" r="F281">
-        <v>-33.0291</v>
+        <v>0.8311</v>
       </c>
     </row>
     <row r="282">
@@ -7156,16 +7165,16 @@
         </is>
       </c>
       <c t="n" r="C284">
-        <v>-0.4558</v>
+        <v>-0.4660</v>
       </c>
       <c t="n" r="D284">
-        <v>-29.8326</v>
+        <v>-29.8303</v>
       </c>
       <c t="n" r="E284">
-        <v>4951.9575</v>
+        <v>4985.8554</v>
       </c>
       <c t="n" r="F284">
-        <v>12087.6221</v>
+        <v>12086.3719</v>
       </c>
     </row>
     <row r="285">
@@ -7180,13 +7189,13 @@
         </is>
       </c>
       <c t="n" r="C285">
-        <v>-0.0170</v>
+        <v>-0.0224</v>
       </c>
       <c t="n" r="D285">
-        <v>-0.0597</v>
+        <v>-0.0636</v>
       </c>
       <c t="n" r="F285">
-        <v>-0.0069</v>
+        <v>-0.0123</v>
       </c>
     </row>
     <row r="286">
@@ -7237,7 +7246,7 @@
         </is>
       </c>
       <c t="n" r="C289">
-        <v>-74.0642</v>
+        <v>-74.3251</v>
       </c>
     </row>
     <row r="290">
@@ -7264,16 +7273,16 @@
         </is>
       </c>
       <c t="n" r="C291">
-        <v>0.7365</v>
+        <v>0.7347</v>
       </c>
       <c t="n" r="D291">
-        <v>2.7579</v>
+        <v>2.7212</v>
       </c>
       <c t="n" r="E291">
-        <v>10.3845</v>
+        <v>10.3562</v>
       </c>
       <c t="n" r="F291">
-        <v>3.1485</v>
+        <v>3.1466</v>
       </c>
     </row>
     <row r="292">
@@ -7300,16 +7309,16 @@
         </is>
       </c>
       <c t="n" r="C293">
-        <v>-26.4456</v>
+        <v>-26.4321</v>
       </c>
       <c t="n" r="D293">
-        <v>-57.3572</v>
+        <v>-57.3951</v>
       </c>
       <c t="n" r="E293">
-        <v>-57.3283</v>
+        <v>-57.3245</v>
       </c>
       <c t="n" r="F293">
-        <v>-56.8417</v>
+        <v>-56.8338</v>
       </c>
     </row>
     <row r="294">
@@ -7378,7 +7387,7 @@
         <v>-0.0050</v>
       </c>
       <c t="n" r="E297">
-        <v>-4.9948</v>
+        <v>-0.0050</v>
       </c>
       <c t="n" r="F297">
         <v>-0.0050</v>
@@ -7420,16 +7429,16 @@
         </is>
       </c>
       <c t="n" r="C300">
-        <v>3.5424</v>
+        <v>3.6643</v>
       </c>
       <c t="n" r="D300">
-        <v>10.2683</v>
+        <v>10.2752</v>
       </c>
       <c t="n" r="E300">
-        <v>21.2047</v>
+        <v>21.2294</v>
       </c>
       <c t="n" r="F300">
-        <v>11.9334</v>
+        <v>12.0652</v>
       </c>
     </row>
     <row r="301">
@@ -7444,13 +7453,13 @@
         </is>
       </c>
       <c t="n" r="C301">
-        <v>3.4545</v>
+        <v>3.5776</v>
       </c>
       <c t="n" r="D301">
-        <v>9.4748</v>
+        <v>9.4798</v>
       </c>
       <c t="n" r="F301">
-        <v>11.1410</v>
+        <v>11.2732</v>
       </c>
     </row>
     <row r="302">
@@ -7477,13 +7486,13 @@
         </is>
       </c>
       <c t="n" r="C303">
-        <v>4.0382</v>
+        <v>4.1660</v>
       </c>
       <c t="n" r="D303">
-        <v>11.8255</v>
+        <v>11.8232</v>
       </c>
       <c t="n" r="F303">
-        <v>13.6987</v>
+        <v>13.8384</v>
       </c>
     </row>
     <row r="304">
@@ -7498,7 +7507,7 @@
         </is>
       </c>
       <c t="n" r="C304">
-        <v>-69.7205</v>
+        <v>-70.7076</v>
       </c>
     </row>
     <row r="305">
@@ -7513,10 +7522,10 @@
         </is>
       </c>
       <c t="n" r="C305">
-        <v>-0.0031</v>
+        <v>-0.0071</v>
       </c>
       <c t="n" r="D305">
-        <v>-1.2558</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="306">
@@ -7531,16 +7540,16 @@
         </is>
       </c>
       <c t="n" r="C306">
-        <v>1.0788</v>
+        <v>1.1474</v>
       </c>
       <c t="n" r="D306">
-        <v>6.0919</v>
+        <v>6.0803</v>
       </c>
       <c t="n" r="E306">
-        <v>14.5645</v>
+        <v>14.5300</v>
       </c>
       <c t="n" r="F306">
-        <v>7.1189</v>
+        <v>7.1916</v>
       </c>
     </row>
     <row r="307">
@@ -7579,16 +7588,16 @@
         </is>
       </c>
       <c t="n" r="C309">
-        <v>1.9605</v>
+        <v>1.9942</v>
       </c>
       <c t="n" r="D309">
-        <v>3.9165</v>
+        <v>3.8541</v>
       </c>
       <c t="n" r="E309">
-        <v>12.2913</v>
+        <v>12.2201</v>
       </c>
       <c t="n" r="F309">
-        <v>5.1732</v>
+        <v>5.2080</v>
       </c>
     </row>
     <row r="310">
@@ -7627,16 +7636,16 @@
         </is>
       </c>
       <c t="n" r="C312">
-        <v>-0.0745</v>
+        <v>-0.0762</v>
       </c>
       <c t="n" r="D312">
-        <v>-0.2175</v>
+        <v>-0.2179</v>
       </c>
       <c t="n" r="E312">
-        <v>0.6052</v>
+        <v>0.6045</v>
       </c>
       <c t="n" r="F312">
-        <v>-0.2409</v>
+        <v>-0.2426</v>
       </c>
     </row>
     <row r="313">
@@ -7675,13 +7684,13 @@
         </is>
       </c>
       <c t="n" r="C315">
-        <v>-0.0525</v>
+        <v>-0.0537</v>
       </c>
       <c t="n" r="D315">
-        <v>-0.1471</v>
+        <v>-0.1474</v>
       </c>
       <c t="n" r="F315">
-        <v>-0.1657</v>
+        <v>-0.1669</v>
       </c>
     </row>
     <row r="316">
@@ -7708,16 +7717,16 @@
         </is>
       </c>
       <c t="n" r="C317">
-        <v>-0.1543</v>
+        <v>-0.1568</v>
       </c>
       <c t="n" r="D317">
-        <v>-0.3506</v>
+        <v>-0.3507</v>
       </c>
       <c t="n" r="E317">
-        <v>3.0285</v>
+        <v>3.0281</v>
       </c>
       <c t="n" r="F317">
-        <v>-0.3821</v>
+        <v>-0.3845</v>
       </c>
     </row>
     <row r="318">
@@ -7732,7 +7741,7 @@
         </is>
       </c>
       <c t="n" r="C318">
-        <v>-0.1281</v>
+        <v>-0.1290</v>
       </c>
     </row>
     <row r="319">
@@ -7801,13 +7810,13 @@
         </is>
       </c>
       <c t="n" r="C323">
-        <v>-0.1174</v>
+        <v>-0.1162</v>
       </c>
       <c t="n" r="D323">
-        <v>-0.1486</v>
+        <v>-0.1495</v>
       </c>
       <c t="n" r="F323">
-        <v>-0.1320</v>
+        <v>-0.1308</v>
       </c>
     </row>
     <row r="324">
@@ -7846,7 +7855,7 @@
         </is>
       </c>
       <c t="n" r="C326">
-        <v>2.7790</v>
+        <v>2.8818</v>
       </c>
     </row>
     <row r="327">
@@ -7864,10 +7873,10 @@
         <v>0.0000</v>
       </c>
       <c t="n" r="D327">
-        <v>0.0000</v>
+        <v>0.0212</v>
       </c>
       <c t="n" r="E327">
-        <v>0.0000</v>
+        <v>-0.1272</v>
       </c>
       <c t="n" r="F327">
         <v>-0.0212</v>

--- a/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
@@ -280,22 +280,22 @@
         </is>
       </c>
       <c t="n" r="C3">
-        <v>38.5442</v>
+        <v>38.7018</v>
       </c>
       <c t="n" r="D3">
-        <v>663.9365</v>
+        <v>664.8302</v>
       </c>
       <c t="n" r="E3">
-        <v>690.5221</v>
+        <v>691.4450</v>
       </c>
       <c t="n" r="F3">
-        <v>658.5364</v>
+        <v>659.3993</v>
       </c>
       <c t="n" r="G3">
-        <v>615.4397</v>
+        <v>616.4683</v>
       </c>
       <c t="n" r="H3">
-        <v>768.8653</v>
+        <v>769.8537</v>
       </c>
     </row>
     <row r="4">
@@ -310,19 +310,19 @@
         </is>
       </c>
       <c t="n" r="C4">
-        <v>16.4096</v>
+        <v>16.4394</v>
       </c>
       <c t="n" r="D4">
-        <v>20.4133</v>
+        <v>20.4024</v>
       </c>
       <c t="n" r="E4">
-        <v>250.4856</v>
+        <v>249.9272</v>
       </c>
       <c t="n" r="F4">
-        <v>21.0302</v>
+        <v>21.0611</v>
       </c>
       <c t="n" r="G4">
-        <v>373.6999</v>
+        <v>373.7437</v>
       </c>
     </row>
     <row r="5">
@@ -337,19 +337,19 @@
         </is>
       </c>
       <c t="n" r="C5">
-        <v>0.9248</v>
+        <v>0.9345</v>
       </c>
       <c t="n" r="D5">
-        <v>2.6400</v>
+        <v>2.6432</v>
       </c>
       <c t="n" r="E5">
-        <v>27.7278</v>
+        <v>27.7320</v>
       </c>
       <c t="n" r="F5">
-        <v>3.3680</v>
+        <v>3.3779</v>
       </c>
       <c t="n" r="G5">
-        <v>362.1213</v>
+        <v>362.4812</v>
       </c>
     </row>
     <row r="6">
@@ -364,22 +364,22 @@
         </is>
       </c>
       <c t="n" r="C6">
-        <v>-0.4334</v>
+        <v>-0.4364</v>
       </c>
       <c t="n" r="D6">
-        <v>41.6864</v>
+        <v>43.1989</v>
       </c>
       <c t="n" r="E6">
-        <v>52.7639</v>
+        <v>52.7670</v>
       </c>
       <c t="n" r="F6">
-        <v>42.2934</v>
+        <v>42.2891</v>
       </c>
       <c t="n" r="G6">
-        <v>239.7901</v>
+        <v>240.0814</v>
       </c>
       <c t="n" r="H6">
-        <v>332.7632</v>
+        <v>332.7502</v>
       </c>
     </row>
     <row r="7">
@@ -394,22 +394,22 @@
         </is>
       </c>
       <c t="n" r="C7">
-        <v>-0.0188</v>
+        <v>-0.0191</v>
       </c>
       <c t="n" r="D7">
-        <v>-0.0510</v>
+        <v>-0.0488</v>
       </c>
       <c t="n" r="E7">
-        <v>192.5057</v>
+        <v>192.5058</v>
       </c>
       <c t="n" r="F7">
-        <v>-0.0583</v>
+        <v>-0.0586</v>
       </c>
       <c t="n" r="G7">
-        <v>191.4237</v>
+        <v>191.4475</v>
       </c>
       <c t="n" r="H7">
-        <v>166674.2475</v>
+        <v>166673.6393</v>
       </c>
     </row>
     <row r="8">
@@ -424,19 +424,19 @@
         </is>
       </c>
       <c t="n" r="C8">
-        <v>-0.0165</v>
+        <v>-0.0159</v>
       </c>
       <c t="n" r="D8">
-        <v>4.0113</v>
+        <v>4.0109</v>
       </c>
       <c t="n" r="E8">
-        <v>3.9846</v>
+        <v>3.9844</v>
       </c>
       <c t="n" r="F8">
-        <v>4.0200</v>
+        <v>4.0206</v>
       </c>
       <c t="n" r="G8">
-        <v>152.7062</v>
+        <v>152.7232</v>
       </c>
     </row>
     <row r="9">
@@ -451,19 +451,19 @@
         </is>
       </c>
       <c t="n" r="C9">
-        <v>0.7321</v>
+        <v>0.7325</v>
       </c>
       <c t="n" r="D9">
-        <v>1.0503</v>
+        <v>1.0499</v>
       </c>
       <c t="n" r="E9">
-        <v>141.4673</v>
+        <v>141.4734</v>
       </c>
       <c t="n" r="F9">
-        <v>1.5287</v>
+        <v>1.5291</v>
       </c>
       <c t="n" r="G9">
-        <v>143.4277</v>
+        <v>143.3596</v>
       </c>
     </row>
     <row r="10">
@@ -478,22 +478,22 @@
         </is>
       </c>
       <c t="n" r="C10">
-        <v>65.7297</v>
+        <v>65.7361</v>
       </c>
       <c t="n" r="D10">
-        <v>68.2357</v>
+        <v>68.1865</v>
       </c>
       <c t="n" r="E10">
-        <v>69.7721</v>
+        <v>69.7758</v>
       </c>
       <c t="n" r="F10">
-        <v>55.1256</v>
+        <v>55.1316</v>
       </c>
       <c t="n" r="G10">
-        <v>88.2723</v>
+        <v>88.2606</v>
       </c>
       <c t="n" r="H10">
-        <v>114.8975</v>
+        <v>114.9058</v>
       </c>
     </row>
     <row r="11">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c t="n" r="C11">
-        <v>1.8155</v>
+        <v>1.8259</v>
       </c>
       <c t="n" r="D11">
-        <v>33.7358</v>
+        <v>33.7495</v>
       </c>
       <c t="n" r="E11">
-        <v>76.7799</v>
+        <v>76.8015</v>
       </c>
       <c t="n" r="F11">
-        <v>33.7737</v>
+        <v>33.7875</v>
       </c>
       <c t="n" r="G11">
-        <v>82.7312</v>
+        <v>82.7451</v>
       </c>
       <c t="n" r="H11">
-        <v>299.3021</v>
+        <v>299.3430</v>
       </c>
       <c t="n" r="I11">
-        <v>1680.4858</v>
+        <v>1680.0745</v>
       </c>
     </row>
     <row r="12">
@@ -541,25 +541,25 @@
         </is>
       </c>
       <c t="n" r="C12">
-        <v>0.2502</v>
+        <v>0.2698</v>
       </c>
       <c t="n" r="D12">
-        <v>1.3946</v>
+        <v>1.4034</v>
       </c>
       <c t="n" r="E12">
-        <v>38.8293</v>
+        <v>38.7401</v>
       </c>
       <c t="n" r="F12">
-        <v>1.2928</v>
+        <v>1.3126</v>
       </c>
       <c t="n" r="G12">
-        <v>61.8246</v>
+        <v>61.7123</v>
       </c>
       <c t="n" r="H12">
-        <v>327.6451</v>
+        <v>327.7286</v>
       </c>
       <c t="n" r="I12">
-        <v>1093.5944</v>
+        <v>1093.8276</v>
       </c>
     </row>
     <row r="13">
@@ -574,22 +574,22 @@
         </is>
       </c>
       <c t="n" r="C13">
-        <v>-0.1926</v>
+        <v>-0.1948</v>
       </c>
       <c t="n" r="D13">
-        <v>-1.2911</v>
+        <v>-0.3572</v>
       </c>
       <c t="n" r="E13">
-        <v>19.9658</v>
+        <v>19.9559</v>
       </c>
       <c t="n" r="F13">
-        <v>-1.0389</v>
+        <v>-1.0410</v>
       </c>
       <c t="n" r="G13">
-        <v>61.5458</v>
+        <v>61.6167</v>
       </c>
       <c t="n" r="H13">
-        <v>687.4074</v>
+        <v>687.3906</v>
       </c>
     </row>
     <row r="14">
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c t="n" r="C14">
-        <v>3.6930</v>
+        <v>3.8245</v>
       </c>
       <c t="n" r="D14">
-        <v>10.2107</v>
+        <v>10.2394</v>
       </c>
       <c t="n" r="E14">
-        <v>27.7339</v>
+        <v>27.7532</v>
       </c>
       <c t="n" r="F14">
-        <v>11.1286</v>
+        <v>11.2696</v>
       </c>
       <c t="n" r="G14">
-        <v>58.6057</v>
+        <v>58.6638</v>
       </c>
     </row>
     <row r="15">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c t="n" r="C15">
-        <v>-0.1175</v>
+        <v>-0.1202</v>
       </c>
       <c t="n" r="D15">
-        <v>0.2719</v>
+        <v>0.2721</v>
       </c>
       <c t="n" r="E15">
-        <v>60.0179</v>
+        <v>60.0178</v>
       </c>
       <c t="n" r="F15">
-        <v>-4.4515</v>
+        <v>-4.4541</v>
       </c>
       <c t="n" r="G15">
-        <v>58.5923</v>
+        <v>58.6156</v>
       </c>
     </row>
     <row r="16">
@@ -658,19 +658,19 @@
         </is>
       </c>
       <c t="n" r="C16">
-        <v>3.4549</v>
+        <v>3.5632</v>
       </c>
       <c t="n" r="D16">
-        <v>15.9008</v>
+        <v>14.5468</v>
       </c>
       <c t="n" r="E16">
-        <v>26.5867</v>
+        <v>26.5859</v>
       </c>
       <c t="n" r="F16">
-        <v>17.9959</v>
+        <v>18.1194</v>
       </c>
       <c t="n" r="G16">
-        <v>57.6053</v>
+        <v>57.5859</v>
       </c>
     </row>
     <row r="17">
@@ -685,22 +685,22 @@
         </is>
       </c>
       <c t="n" r="C17">
-        <v>0.7395</v>
+        <v>0.7467</v>
       </c>
       <c t="n" r="D17">
-        <v>1.9263</v>
+        <v>1.9341</v>
       </c>
       <c t="n" r="E17">
-        <v>51.3543</v>
+        <v>51.3594</v>
       </c>
       <c t="n" r="F17">
-        <v>48.1779</v>
+        <v>48.1886</v>
       </c>
       <c t="n" r="G17">
-        <v>57.0520</v>
+        <v>56.0158</v>
       </c>
       <c t="n" r="H17">
-        <v>463.7955</v>
+        <v>463.8363</v>
       </c>
     </row>
     <row r="18">
@@ -715,19 +715,19 @@
         </is>
       </c>
       <c t="n" r="C18">
-        <v>3.7489</v>
+        <v>3.9062</v>
       </c>
       <c t="n" r="D18">
-        <v>10.3797</v>
+        <v>10.4367</v>
       </c>
       <c t="n" r="E18">
-        <v>22.2001</v>
+        <v>22.2329</v>
       </c>
       <c t="n" r="F18">
-        <v>11.8672</v>
+        <v>12.0369</v>
       </c>
       <c t="n" r="G18">
-        <v>55.8535</v>
+        <v>55.9269</v>
       </c>
     </row>
     <row r="19">
@@ -742,19 +742,19 @@
         </is>
       </c>
       <c t="n" r="C19">
-        <v>3.7485</v>
+        <v>3.9059</v>
       </c>
       <c t="n" r="D19">
-        <v>10.3786</v>
+        <v>10.4356</v>
       </c>
       <c t="n" r="E19">
-        <v>22.1976</v>
+        <v>22.2304</v>
       </c>
       <c t="n" r="F19">
-        <v>11.8659</v>
+        <v>12.0356</v>
       </c>
       <c t="n" r="G19">
-        <v>55.8455</v>
+        <v>55.9190</v>
       </c>
     </row>
     <row r="20">
@@ -769,22 +769,22 @@
         </is>
       </c>
       <c t="n" r="C20">
-        <v>0.2578</v>
+        <v>0.2903</v>
       </c>
       <c t="n" r="D20">
-        <v>0.8077</v>
+        <v>0.8376</v>
       </c>
       <c t="n" r="E20">
-        <v>1.3233</v>
+        <v>1.3696</v>
       </c>
       <c t="n" r="F20">
-        <v>0.8907</v>
+        <v>0.9233</v>
       </c>
       <c t="n" r="G20">
-        <v>55.1749</v>
+        <v>55.2325</v>
       </c>
       <c t="n" r="H20">
-        <v>410.2755</v>
+        <v>410.4407</v>
       </c>
     </row>
     <row r="21">
@@ -799,76 +799,76 @@
         </is>
       </c>
       <c t="n" r="C21">
-        <v>-0.0294</v>
+        <v>-0.0135</v>
       </c>
       <c t="n" r="D21">
-        <v>6.4413</v>
+        <v>6.4339</v>
       </c>
       <c t="n" r="E21">
-        <v>19.5817</v>
+        <v>19.5481</v>
       </c>
       <c t="n" r="F21">
-        <v>6.7981</v>
+        <v>6.8150</v>
       </c>
       <c t="n" r="G21">
-        <v>54.8295</v>
+        <v>54.7130</v>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">BRE</t>
+          <t xml:space="preserve">OYK</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ÇEŞME GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C22">
-        <v>5.8655</v>
+        <v>-0.2023</v>
       </c>
       <c t="n" r="D22">
-        <v>23.6185</v>
+        <v>-0.2035</v>
       </c>
       <c t="n" r="E22">
-        <v>28.1429</v>
+        <v>55.3903</v>
       </c>
       <c t="n" r="F22">
-        <v>29.2965</v>
+        <v>-0.2326</v>
       </c>
       <c t="n" r="G22">
-        <v>54.4696</v>
+        <v>54.4094</v>
+      </c>
+      <c t="n" r="H22">
+        <v>172.5228</v>
       </c>
     </row>
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">OYK</t>
+          <t xml:space="preserve">BRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ÇEŞME GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C23">
-        <v>-0.1974</v>
+        <v>5.9224</v>
       </c>
       <c t="n" r="D23">
-        <v>-0.2277</v>
+        <v>23.6492</v>
       </c>
       <c t="n" r="E23">
-        <v>55.3983</v>
+        <v>28.2303</v>
       </c>
       <c t="n" r="F23">
-        <v>-0.2276</v>
+        <v>29.3660</v>
       </c>
       <c t="n" r="G23">
-        <v>54.4175</v>
-      </c>
-      <c t="n" r="H23">
-        <v>172.5362</v>
+        <v>54.2687</v>
       </c>
     </row>
     <row r="24">
@@ -883,19 +883,19 @@
         </is>
       </c>
       <c t="n" r="C24">
-        <v>4.2614</v>
+        <v>4.3927</v>
       </c>
       <c t="n" r="D24">
-        <v>12.4414</v>
+        <v>10.9170</v>
       </c>
       <c t="n" r="E24">
-        <v>22.7164</v>
+        <v>22.7414</v>
       </c>
       <c t="n" r="F24">
-        <v>14.2214</v>
+        <v>14.3653</v>
       </c>
       <c t="n" r="G24">
-        <v>52.9474</v>
+        <v>52.9607</v>
       </c>
     </row>
     <row r="25">
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c t="n" r="C25">
-        <v>-0.2549</v>
+        <v>-0.2624</v>
       </c>
       <c t="n" r="D25">
-        <v>-1.4334</v>
+        <v>-1.4321</v>
       </c>
       <c t="n" r="E25">
-        <v>28.4783</v>
+        <v>28.4793</v>
       </c>
       <c t="n" r="F25">
-        <v>-1.6953</v>
+        <v>-1.7027</v>
       </c>
       <c t="n" r="G25">
-        <v>49.0209</v>
+        <v>49.0620</v>
       </c>
       <c t="n" r="H25">
-        <v>168.2097</v>
+        <v>168.1896</v>
       </c>
       <c t="n" r="I25">
-        <v>1143.7179</v>
+        <v>1143.6244</v>
       </c>
     </row>
     <row r="26">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c t="n" r="C26">
-        <v>5.2470</v>
+        <v>5.2877</v>
       </c>
       <c t="n" r="D26">
-        <v>12.1236</v>
+        <v>12.0685</v>
       </c>
       <c t="n" r="E26">
-        <v>21.4125</v>
+        <v>21.3333</v>
       </c>
       <c t="n" r="F26">
-        <v>13.3868</v>
+        <v>13.4306</v>
       </c>
       <c t="n" r="G26">
-        <v>48.4177</v>
+        <v>48.3497</v>
       </c>
     </row>
     <row r="27">
@@ -970,25 +970,25 @@
         </is>
       </c>
       <c t="n" r="C27">
-        <v>-0.3224</v>
+        <v>-0.3299</v>
       </c>
       <c t="n" r="D27">
-        <v>-0.4400</v>
+        <v>-0.4354</v>
       </c>
       <c t="n" r="E27">
-        <v>16.0243</v>
+        <v>16.0248</v>
       </c>
       <c t="n" r="F27">
-        <v>-0.6099</v>
+        <v>-0.6174</v>
       </c>
       <c t="n" r="G27">
-        <v>48.0917</v>
+        <v>48.1076</v>
       </c>
       <c t="n" r="H27">
-        <v>196.8592</v>
+        <v>196.8368</v>
       </c>
       <c t="n" r="I27">
-        <v>1322.6018</v>
+        <v>1322.4948</v>
       </c>
     </row>
     <row r="28">
@@ -1003,76 +1003,76 @@
         </is>
       </c>
       <c t="n" r="C28">
-        <v>0.4648</v>
+        <v>0.4808</v>
       </c>
       <c t="n" r="D28">
-        <v>6.3053</v>
+        <v>6.3091</v>
       </c>
       <c t="n" r="E28">
-        <v>43.8100</v>
+        <v>43.8098</v>
       </c>
       <c t="n" r="F28">
-        <v>5.9789</v>
+        <v>5.9958</v>
       </c>
       <c t="n" r="G28">
-        <v>45.3199</v>
+        <v>45.3622</v>
       </c>
       <c t="n" r="H28">
-        <v>461.9253</v>
+        <v>462.0146</v>
       </c>
     </row>
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">YYF</t>
+          <t xml:space="preserve">TGI</t>
         </is>
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C29">
-        <v>3.2293</v>
+        <v>1.4416</v>
       </c>
       <c t="n" r="D29">
-        <v>8.8464</v>
+        <v>5.0275</v>
       </c>
       <c t="n" r="E29">
-        <v>19.1909</v>
+        <v>22.3913</v>
       </c>
       <c t="n" r="F29">
-        <v>10.3354</v>
+        <v>5.5950</v>
       </c>
       <c t="n" r="G29">
-        <v>44.5413</v>
+        <v>44.5726</v>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">TGI</t>
+          <t xml:space="preserve">YYF</t>
         </is>
       </c>
       <c t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C30">
-        <v>1.3492</v>
+        <v>3.3626</v>
       </c>
       <c t="n" r="D30">
-        <v>5.0639</v>
+        <v>8.8912</v>
       </c>
       <c t="n" r="E30">
-        <v>23.9206</v>
+        <v>19.2211</v>
       </c>
       <c t="n" r="F30">
-        <v>5.4988</v>
+        <v>10.4779</v>
       </c>
       <c t="n" r="G30">
-        <v>44.3240</v>
+        <v>44.5592</v>
       </c>
     </row>
     <row r="31">
@@ -1087,19 +1087,19 @@
         </is>
       </c>
       <c t="n" r="C31">
-        <v>-1.0515</v>
+        <v>-1.0357</v>
       </c>
       <c t="n" r="D31">
-        <v>0.4793</v>
+        <v>0.4830</v>
       </c>
       <c t="n" r="E31">
-        <v>29.4095</v>
+        <v>29.4118</v>
       </c>
       <c t="n" r="F31">
-        <v>1.6003</v>
+        <v>1.6165</v>
       </c>
       <c t="n" r="G31">
-        <v>44.1598</v>
+        <v>44.1762</v>
       </c>
     </row>
     <row r="32">
@@ -1114,19 +1114,19 @@
         </is>
       </c>
       <c t="n" r="C32">
-        <v>2.1967</v>
+        <v>2.2262</v>
       </c>
       <c t="n" r="D32">
-        <v>4.9212</v>
+        <v>3.7681</v>
       </c>
       <c t="n" r="E32">
-        <v>24.7670</v>
+        <v>24.7072</v>
       </c>
       <c t="n" r="F32">
-        <v>8.7512</v>
+        <v>8.7827</v>
       </c>
       <c t="n" r="G32">
-        <v>42.3891</v>
+        <v>42.2320</v>
       </c>
     </row>
     <row r="33">
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c t="n" r="C33">
-        <v>-0.0210</v>
+        <v>-0.0209</v>
       </c>
       <c t="n" r="D33">
-        <v>0.2470</v>
+        <v>0.2593</v>
       </c>
       <c t="n" r="E33">
-        <v>27.7403</v>
+        <v>27.5230</v>
       </c>
       <c t="n" r="F33">
-        <v>0.3204</v>
+        <v>0.3206</v>
       </c>
       <c t="n" r="G33">
-        <v>41.7825</v>
+        <v>41.8789</v>
       </c>
     </row>
     <row r="34">
@@ -1168,25 +1168,25 @@
         </is>
       </c>
       <c t="n" r="C34">
-        <v>0.1605</v>
+        <v>0.1587</v>
       </c>
       <c t="n" r="D34">
-        <v>0.5340</v>
+        <v>0.5345</v>
       </c>
       <c t="n" r="E34">
-        <v>38.6429</v>
+        <v>38.6427</v>
       </c>
       <c t="n" r="F34">
-        <v>0.7333</v>
+        <v>0.7315</v>
       </c>
       <c t="n" r="G34">
-        <v>41.7431</v>
+        <v>41.7473</v>
       </c>
       <c t="n" r="H34">
-        <v>241.8867</v>
+        <v>241.8806</v>
       </c>
       <c t="n" r="I34">
-        <v>848.0395</v>
+        <v>848.0227</v>
       </c>
     </row>
     <row r="35">
@@ -1201,25 +1201,25 @@
         </is>
       </c>
       <c t="n" r="C35">
-        <v>-0.0784</v>
+        <v>-0.0792</v>
       </c>
       <c t="n" r="D35">
-        <v>-0.3341</v>
+        <v>-0.3340</v>
       </c>
       <c t="n" r="E35">
-        <v>42.2751</v>
+        <v>42.2748</v>
       </c>
       <c t="n" r="F35">
-        <v>-0.4986</v>
+        <v>-0.4995</v>
       </c>
       <c t="n" r="G35">
-        <v>41.6633</v>
+        <v>41.6786</v>
       </c>
       <c t="n" r="H35">
-        <v>212.9996</v>
+        <v>212.9968</v>
       </c>
       <c t="n" r="I35">
-        <v>723.3385</v>
+        <v>723.9338</v>
       </c>
     </row>
     <row r="36">
@@ -1234,22 +1234,22 @@
         </is>
       </c>
       <c t="n" r="C36">
-        <v>0.1535</v>
+        <v>0.1472</v>
       </c>
       <c t="n" r="D36">
-        <v>0.0135</v>
+        <v>0.0129</v>
       </c>
       <c t="n" r="E36">
-        <v>41.1467</v>
+        <v>41.1480</v>
       </c>
       <c t="n" r="F36">
-        <v>0.2917</v>
+        <v>0.2853</v>
       </c>
       <c t="n" r="G36">
-        <v>41.4623</v>
+        <v>41.4633</v>
       </c>
       <c t="n" r="H36">
-        <v>251.9383</v>
+        <v>251.9159</v>
       </c>
     </row>
     <row r="37">
@@ -1264,25 +1264,25 @@
         </is>
       </c>
       <c t="n" r="C37">
-        <v>0.5530</v>
+        <v>0.5657</v>
       </c>
       <c t="n" r="D37">
-        <v>1.5452</v>
+        <v>1.5465</v>
       </c>
       <c t="n" r="E37">
-        <v>28.9772</v>
+        <v>28.9764</v>
       </c>
       <c t="n" r="F37">
-        <v>1.5084</v>
+        <v>1.5212</v>
       </c>
       <c t="n" r="G37">
-        <v>40.7973</v>
+        <v>40.7900</v>
       </c>
       <c t="n" r="H37">
-        <v>172.2282</v>
+        <v>172.2624</v>
       </c>
       <c t="n" r="I37">
-        <v>400.4321</v>
+        <v>400.4949</v>
       </c>
     </row>
     <row r="38">
@@ -1297,25 +1297,25 @@
         </is>
       </c>
       <c t="n" r="C38">
-        <v>0.4609</v>
+        <v>0.4725</v>
       </c>
       <c t="n" r="D38">
-        <v>1.7486</v>
+        <v>1.7563</v>
       </c>
       <c t="n" r="E38">
-        <v>16.2012</v>
+        <v>16.1777</v>
       </c>
       <c t="n" r="F38">
-        <v>2.0195</v>
+        <v>2.0313</v>
       </c>
       <c t="n" r="G38">
-        <v>40.2528</v>
+        <v>40.2539</v>
       </c>
       <c t="n" r="H38">
-        <v>295.3139</v>
+        <v>295.3594</v>
       </c>
       <c t="n" r="I38">
-        <v>916.2844</v>
+        <v>916.2804</v>
       </c>
     </row>
     <row r="39">
@@ -1330,148 +1330,148 @@
         </is>
       </c>
       <c t="n" r="C39">
-        <v>1.4809</v>
+        <v>1.5115</v>
       </c>
       <c t="n" r="D39">
-        <v>4.4272</v>
+        <v>4.4417</v>
       </c>
       <c t="n" r="E39">
-        <v>14.5111</v>
+        <v>14.5132</v>
       </c>
       <c t="n" r="F39">
-        <v>3.4822</v>
+        <v>3.5134</v>
       </c>
       <c t="n" r="G39">
-        <v>39.8793</v>
+        <v>39.9065</v>
       </c>
       <c t="n" r="H39">
-        <v>141.4796</v>
+        <v>141.5523</v>
       </c>
       <c t="n" r="I39">
-        <v>260.3882</v>
+        <v>260.4879</v>
       </c>
     </row>
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">RGO</t>
+          <t xml:space="preserve">RG4</t>
         </is>
       </c>
       <c t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. GÖKSU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C40">
-        <v>0.6933</v>
+        <v>0.9009</v>
       </c>
       <c t="n" r="D40">
-        <v>2.0372</v>
+        <v>5.5432</v>
       </c>
       <c t="n" r="E40">
-        <v>31.1440</v>
+        <v>34.9050</v>
       </c>
       <c t="n" r="F40">
-        <v>2.6653</v>
+        <v>13.3790</v>
       </c>
       <c t="n" r="G40">
-        <v>38.6921</v>
+        <v>39.1797</v>
+      </c>
+      <c t="n" r="H40">
+        <v>840.4288</v>
       </c>
     </row>
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">YD2</t>
+          <t xml:space="preserve">RGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALZAMİL KİRA GETİRİLİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. GÖKSU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C41">
-        <v>-1.2889</v>
+        <v>0.6992</v>
       </c>
       <c t="n" r="D41">
-        <v>-0.9279</v>
+        <v>2.0430</v>
       </c>
       <c t="n" r="E41">
-        <v>23.8410</v>
+        <v>31.1477</v>
       </c>
       <c t="n" r="F41">
-        <v>-0.5195</v>
+        <v>2.6713</v>
       </c>
       <c t="n" r="G41">
-        <v>38.3745</v>
-      </c>
-      <c t="n" r="H41">
-        <v>326.8208</v>
-      </c>
-      <c t="n" r="I41">
-        <v>713.2516</v>
+        <v>38.6765</v>
       </c>
     </row>
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">IKG</t>
+          <t xml:space="preserve">YD2</t>
         </is>
       </c>
       <c t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALZAMİL KİRA GETİRİLİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C42">
-        <v>1.3904</v>
+        <v>-1.2948</v>
       </c>
       <c t="n" r="D42">
-        <v>4.1735</v>
+        <v>-0.9276</v>
       </c>
       <c t="n" r="E42">
-        <v>13.8696</v>
+        <v>26.0488</v>
       </c>
       <c t="n" r="F42">
-        <v>4.7524</v>
+        <v>-0.5254</v>
       </c>
       <c t="n" r="G42">
-        <v>37.4575</v>
+        <v>38.3862</v>
       </c>
       <c t="n" r="H42">
-        <v>179.3659</v>
+        <v>326.7953</v>
       </c>
       <c t="n" r="I42">
-        <v>415.4173</v>
+        <v>713.2030</v>
       </c>
     </row>
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">RG4</t>
+          <t xml:space="preserve">IKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C43">
-        <v>-0.6252</v>
+        <v>1.4758</v>
       </c>
       <c t="n" r="D43">
-        <v>3.9451</v>
+        <v>4.1740</v>
       </c>
       <c t="n" r="E43">
-        <v>32.8739</v>
+        <v>13.9114</v>
       </c>
       <c t="n" r="F43">
-        <v>11.6642</v>
+        <v>4.8406</v>
       </c>
       <c t="n" r="G43">
-        <v>37.1170</v>
+        <v>37.4817</v>
       </c>
       <c t="n" r="H43">
-        <v>826.2060</v>
+        <v>179.6011</v>
+      </c>
+      <c t="n" r="I43">
+        <v>415.6494</v>
       </c>
     </row>
     <row r="44">
@@ -1486,19 +1486,19 @@
         </is>
       </c>
       <c t="n" r="C44">
-        <v>2.7705</v>
+        <v>2.8614</v>
       </c>
       <c t="n" r="D44">
-        <v>7.0161</v>
+        <v>7.0419</v>
       </c>
       <c t="n" r="E44">
-        <v>15.3130</v>
+        <v>15.3162</v>
       </c>
       <c t="n" r="F44">
-        <v>8.2592</v>
+        <v>8.3550</v>
       </c>
       <c t="n" r="G44">
-        <v>35.8490</v>
+        <v>35.8256</v>
       </c>
     </row>
     <row r="45">
@@ -1513,25 +1513,25 @@
         </is>
       </c>
       <c t="n" r="C45">
-        <v>-0.0774</v>
+        <v>-0.0780</v>
       </c>
       <c t="n" r="D45">
-        <v>-0.4221</v>
+        <v>-0.4220</v>
       </c>
       <c t="n" r="E45">
-        <v>32.6747</v>
+        <v>32.6748</v>
       </c>
       <c t="n" r="F45">
-        <v>-0.4739</v>
+        <v>-0.4745</v>
       </c>
       <c t="n" r="G45">
-        <v>35.5503</v>
+        <v>35.5651</v>
       </c>
       <c t="n" r="H45">
-        <v>243.3410</v>
+        <v>243.3390</v>
       </c>
       <c t="n" r="I45">
-        <v>921.6639</v>
+        <v>921.6593</v>
       </c>
     </row>
     <row r="46">
@@ -1546,19 +1546,19 @@
         </is>
       </c>
       <c t="n" r="C46">
-        <v>1.9159</v>
+        <v>1.2663</v>
       </c>
       <c t="n" r="D46">
-        <v>-1.7477</v>
+        <v>-3.2651</v>
       </c>
       <c t="n" r="E46">
-        <v>15.7780</v>
+        <v>12.6633</v>
       </c>
       <c t="n" r="F46">
-        <v>4.6171</v>
+        <v>3.9502</v>
       </c>
       <c t="n" r="G46">
-        <v>35.2007</v>
+        <v>35.3651</v>
       </c>
     </row>
     <row r="47">
@@ -1573,22 +1573,22 @@
         </is>
       </c>
       <c t="n" r="C47">
-        <v>0.4870</v>
+        <v>0.5225</v>
       </c>
       <c t="n" r="D47">
-        <v>1.8100</v>
+        <v>1.8066</v>
       </c>
       <c t="n" r="E47">
-        <v>26.8803</v>
+        <v>26.8985</v>
       </c>
       <c t="n" r="F47">
-        <v>2.1621</v>
+        <v>2.1981</v>
       </c>
       <c t="n" r="G47">
-        <v>34.8309</v>
+        <v>34.8507</v>
       </c>
       <c t="n" r="H47">
-        <v>575.2487</v>
+        <v>575.4866</v>
       </c>
     </row>
     <row r="48">
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c t="n" r="C48">
-        <v>-0.0224</v>
+        <v>-0.0227</v>
       </c>
       <c t="n" r="D48">
-        <v>-0.1093</v>
+        <v>-0.1091</v>
       </c>
       <c t="n" r="E48">
-        <v>34.0428</v>
+        <v>34.0426</v>
       </c>
       <c t="n" r="F48">
-        <v>-0.1143</v>
+        <v>-0.1146</v>
       </c>
       <c t="n" r="G48">
-        <v>34.5353</v>
+        <v>34.5358</v>
       </c>
     </row>
     <row r="49">
@@ -1630,19 +1630,19 @@
         </is>
       </c>
       <c t="n" r="C49">
-        <v>0.5285</v>
+        <v>0.5321</v>
       </c>
       <c t="n" r="D49">
-        <v>1.5285</v>
+        <v>1.5474</v>
       </c>
       <c t="n" r="E49">
-        <v>28.4869</v>
+        <v>28.4866</v>
       </c>
       <c t="n" r="F49">
-        <v>1.5125</v>
+        <v>1.5162</v>
       </c>
       <c t="n" r="G49">
-        <v>33.8528</v>
+        <v>33.8580</v>
       </c>
     </row>
     <row r="50">
@@ -1657,22 +1657,22 @@
         </is>
       </c>
       <c t="n" r="C50">
-        <v>0.2682</v>
+        <v>0.2669</v>
       </c>
       <c t="n" r="D50">
-        <v>0.7665</v>
+        <v>0.7670</v>
       </c>
       <c t="n" r="E50">
-        <v>31.5208</v>
+        <v>31.5218</v>
       </c>
       <c t="n" r="F50">
-        <v>1.1074</v>
+        <v>1.1060</v>
       </c>
       <c t="n" r="G50">
-        <v>33.0089</v>
+        <v>33.0211</v>
       </c>
       <c t="n" r="H50">
-        <v>316.3629</v>
+        <v>316.3573</v>
       </c>
     </row>
     <row r="51">
@@ -1687,22 +1687,22 @@
         </is>
       </c>
       <c t="n" r="C51">
-        <v>0.4448</v>
+        <v>0.4447</v>
       </c>
       <c t="n" r="D51">
-        <v>0.4842</v>
+        <v>0.4847</v>
       </c>
       <c t="n" r="E51">
-        <v>10.6838</v>
+        <v>10.4440</v>
       </c>
       <c t="n" r="F51">
-        <v>0.1187</v>
+        <v>0.1185</v>
       </c>
       <c t="n" r="G51">
-        <v>32.2818</v>
+        <v>32.2867</v>
       </c>
       <c t="n" r="H51">
-        <v>302.6305</v>
+        <v>302.6300</v>
       </c>
     </row>
     <row r="52">
@@ -1720,22 +1720,22 @@
         <v>-0.0082</v>
       </c>
       <c t="n" r="D52">
-        <v>-0.2014</v>
+        <v>-0.1987</v>
       </c>
       <c t="n" r="E52">
-        <v>32.8664</v>
+        <v>32.8701</v>
       </c>
       <c t="n" r="F52">
-        <v>-2.9933</v>
+        <v>-2.9932</v>
       </c>
       <c t="n" r="G52">
-        <v>31.6679</v>
+        <v>31.7311</v>
       </c>
       <c t="n" r="H52">
-        <v>214.8774</v>
+        <v>214.8775</v>
       </c>
       <c t="n" r="I52">
-        <v>684.3906</v>
+        <v>684.3908</v>
       </c>
     </row>
     <row r="53">
@@ -1750,19 +1750,19 @@
         </is>
       </c>
       <c t="n" r="C53">
-        <v>2.6472</v>
+        <v>2.7484</v>
       </c>
       <c t="n" r="D53">
-        <v>4.9499</v>
+        <v>4.9842</v>
       </c>
       <c t="n" r="E53">
-        <v>12.4041</v>
+        <v>12.4251</v>
       </c>
       <c t="n" r="F53">
-        <v>6.5683</v>
+        <v>6.6733</v>
       </c>
       <c t="n" r="G53">
-        <v>31.4821</v>
+        <v>31.5234</v>
       </c>
     </row>
     <row r="54">
@@ -1777,25 +1777,25 @@
         </is>
       </c>
       <c t="n" r="C54">
-        <v>0.1933</v>
+        <v>0.2063</v>
       </c>
       <c t="n" r="D54">
-        <v>-0.5509</v>
+        <v>-0.5541</v>
       </c>
       <c t="n" r="E54">
-        <v>31.2305</v>
+        <v>31.2576</v>
       </c>
       <c t="n" r="F54">
-        <v>0.0708</v>
+        <v>0.0838</v>
       </c>
       <c t="n" r="G54">
-        <v>31.2550</v>
+        <v>31.2918</v>
       </c>
       <c t="n" r="H54">
-        <v>683.9051</v>
+        <v>684.0070</v>
       </c>
       <c t="n" r="I54">
-        <v>1727.9606</v>
+        <v>1728.1066</v>
       </c>
     </row>
     <row r="55">
@@ -1810,106 +1810,106 @@
         </is>
       </c>
       <c t="n" r="C55">
-        <v>-0.0026</v>
+        <v>0.0002</v>
       </c>
       <c t="n" r="D55">
-        <v>0.0398</v>
+        <v>0.0437</v>
       </c>
       <c t="n" r="E55">
-        <v>29.1979</v>
+        <v>28.9037</v>
       </c>
       <c t="n" r="F55">
-        <v>0.2675</v>
+        <v>0.2703</v>
       </c>
       <c t="n" r="G55">
-        <v>31.2183</v>
+        <v>31.2241</v>
       </c>
     </row>
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">ITG</t>
+          <t xml:space="preserve">TUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. QUASAR İSTANBUL TİCARİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C56">
-        <v>0.2117</v>
+        <v>1.7446</v>
       </c>
       <c t="n" r="D56">
-        <v>1.0852</v>
+        <v>2.9176</v>
       </c>
       <c t="n" r="E56">
-        <v>12.9971</v>
+        <v>10.7062</v>
       </c>
       <c t="n" r="F56">
-        <v>1.3427</v>
+        <v>3.6002</v>
       </c>
       <c t="n" r="G56">
-        <v>30.8888</v>
-      </c>
-      <c t="n" r="H56">
-        <v>156.4625</v>
-      </c>
-      <c t="n" r="I56">
-        <v>486.1972</v>
+        <v>31.1544</v>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">FT1</t>
+          <t xml:space="preserve">ITG</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. QUASAR İSTANBUL TİCARİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C57">
-        <v>0.1108</v>
+        <v>0.2266</v>
       </c>
       <c t="n" r="D57">
-        <v>0.2046</v>
+        <v>1.1000</v>
       </c>
       <c t="n" r="E57">
-        <v>5.4323</v>
+        <v>13.0135</v>
       </c>
       <c t="n" r="F57">
-        <v>0.2335</v>
+        <v>1.3577</v>
       </c>
       <c t="n" r="G57">
-        <v>30.8558</v>
+        <v>30.8928</v>
+      </c>
+      <c t="n" r="H57">
+        <v>156.5005</v>
+      </c>
+      <c t="n" r="I57">
+        <v>486.3049</v>
       </c>
     </row>
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">TUG</t>
+          <t xml:space="preserve">FT1</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C58">
-        <v>1.6981</v>
+        <v>0.1167</v>
       </c>
       <c t="n" r="D58">
-        <v>3.0403</v>
+        <v>0.2083</v>
       </c>
       <c t="n" r="E58">
-        <v>39.5913</v>
+        <v>5.3195</v>
       </c>
       <c t="n" r="F58">
-        <v>3.5528</v>
+        <v>0.2393</v>
       </c>
       <c t="n" r="G58">
-        <v>30.8199</v>
+        <v>30.7424</v>
       </c>
     </row>
     <row r="59">
@@ -1924,19 +1924,19 @@
         </is>
       </c>
       <c t="n" r="C59">
-        <v>1.4902</v>
+        <v>1.5498</v>
       </c>
       <c t="n" r="D59">
-        <v>3.8134</v>
+        <v>3.8597</v>
       </c>
       <c t="n" r="E59">
-        <v>12.8687</v>
+        <v>12.9207</v>
       </c>
       <c t="n" r="F59">
-        <v>3.8423</v>
+        <v>3.9033</v>
       </c>
       <c t="n" r="G59">
-        <v>30.7050</v>
+        <v>30.6414</v>
       </c>
     </row>
     <row r="60">
@@ -1951,25 +1951,25 @@
         </is>
       </c>
       <c t="n" r="C60">
-        <v>0.0703</v>
+        <v>0.0773</v>
       </c>
       <c t="n" r="D60">
-        <v>0.8767</v>
+        <v>0.8884</v>
       </c>
       <c t="n" r="E60">
-        <v>27.7138</v>
+        <v>27.7164</v>
       </c>
       <c t="n" r="F60">
-        <v>-5.9664</v>
+        <v>-5.9599</v>
       </c>
       <c t="n" r="G60">
-        <v>30.0095</v>
+        <v>30.0285</v>
       </c>
       <c t="n" r="H60">
-        <v>172.0164</v>
+        <v>172.0354</v>
       </c>
       <c t="n" r="I60">
-        <v>827.9675</v>
+        <v>828.0323</v>
       </c>
     </row>
     <row r="61">
@@ -1984,79 +1984,79 @@
         </is>
       </c>
       <c t="n" r="C61">
-        <v>0.2309</v>
+        <v>0.2344</v>
       </c>
       <c t="n" r="D61">
-        <v>0.7698</v>
+        <v>0.7720</v>
       </c>
       <c t="n" r="E61">
-        <v>27.8871</v>
+        <v>-1.0645</v>
       </c>
       <c t="n" r="F61">
-        <v>1.0631</v>
+        <v>1.0666</v>
       </c>
       <c t="n" r="G61">
-        <v>29.6533</v>
+        <v>29.6583</v>
       </c>
     </row>
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">AG6</t>
+          <t xml:space="preserve">GF2</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C62">
-        <v>0.1277</v>
+        <v>-1.1117</v>
       </c>
       <c t="n" r="D62">
-        <v>0.2799</v>
+        <v>5.0673</v>
       </c>
       <c t="n" r="E62">
-        <v>28.6761</v>
+        <v>16.5335</v>
       </c>
       <c t="n" r="F62">
-        <v>0.3374</v>
+        <v>6.3359</v>
       </c>
       <c t="n" r="G62">
-        <v>29.1447</v>
-      </c>
-      <c t="n" r="H62">
-        <v>231.8186</v>
-      </c>
-      <c t="n" r="I62">
-        <v>353.6600</v>
+        <v>29.4195</v>
       </c>
     </row>
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">GF2</t>
+          <t xml:space="preserve">AG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C63">
-        <v>-1.3897</v>
+        <v>0.1278</v>
       </c>
       <c t="n" r="D63">
-        <v>4.9207</v>
+        <v>0.3605</v>
       </c>
       <c t="n" r="E63">
-        <v>16.3126</v>
+        <v>28.6683</v>
       </c>
       <c t="n" r="F63">
-        <v>6.0371</v>
+        <v>0.3375</v>
       </c>
       <c t="n" r="G63">
-        <v>29.1309</v>
+        <v>29.1367</v>
+      </c>
+      <c t="n" r="H63">
+        <v>231.8189</v>
+      </c>
+      <c t="n" r="I63">
+        <v>353.6605</v>
       </c>
     </row>
     <row r="64">
@@ -2071,19 +2071,19 @@
         </is>
       </c>
       <c t="n" r="C64">
-        <v>0.3534</v>
+        <v>0.3529</v>
       </c>
       <c t="n" r="D64">
-        <v>0.7213</v>
+        <v>0.7027</v>
       </c>
       <c t="n" r="E64">
-        <v>26.7208</v>
+        <v>26.7295</v>
       </c>
       <c t="n" r="F64">
-        <v>2.4652</v>
+        <v>2.4647</v>
       </c>
       <c t="n" r="G64">
-        <v>28.8128</v>
+        <v>28.7789</v>
       </c>
     </row>
     <row r="65">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c t="n" r="C65">
-        <v>-0.0182</v>
+        <v>-0.0183</v>
       </c>
       <c t="n" r="D65">
         <v>-0.0587</v>
@@ -2107,10 +2107,10 @@
         <v>28.1661</v>
       </c>
       <c t="n" r="F65">
-        <v>-0.0775</v>
+        <v>-0.0776</v>
       </c>
       <c t="n" r="G65">
-        <v>27.9999</v>
+        <v>28.0136</v>
       </c>
     </row>
     <row r="66">
@@ -2125,304 +2125,304 @@
         </is>
       </c>
       <c t="n" r="C66">
-        <v>0.5103</v>
+        <v>0.5090</v>
       </c>
       <c t="n" r="D66">
-        <v>-1.3974</v>
+        <v>-1.3613</v>
       </c>
       <c t="n" r="E66">
-        <v>25.4636</v>
+        <v>25.4615</v>
       </c>
       <c t="n" r="F66">
-        <v>-20.3852</v>
+        <v>-20.3862</v>
       </c>
       <c t="n" r="G66">
-        <v>27.2124</v>
+        <v>27.2175</v>
       </c>
       <c t="n" r="H66">
-        <v>242.8301</v>
+        <v>242.8256</v>
       </c>
       <c t="n" r="I66">
-        <v>1974.1136</v>
+        <v>1974.0868</v>
       </c>
     </row>
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">UKA</t>
+          <t xml:space="preserve">RP7</t>
         </is>
       </c>
       <c t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. KONUT ALFA KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. TURESİF GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C67">
-        <v>1.6412</v>
+        <v>-2.2928</v>
       </c>
       <c t="n" r="D67">
-        <v>4.0697</v>
+        <v>-1.1784</v>
       </c>
       <c t="n" r="E67">
-        <v>16.1231</v>
+        <v>25.5677</v>
       </c>
       <c t="n" r="F67">
-        <v>4.2624</v>
+        <v>-0.3169</v>
       </c>
       <c t="n" r="G67">
-        <v>27.2070</v>
+        <v>26.1290</v>
       </c>
       <c t="n" r="H67">
-        <v>134.6370</v>
+        <v>49.1221</v>
       </c>
       <c t="n" r="I67">
-        <v>634865.8160</v>
+        <v>980.8419</v>
       </c>
     </row>
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">RP7</t>
+          <t xml:space="preserve">UNC</t>
         </is>
       </c>
       <c t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. TURESİF GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C68">
-        <v>-2.2901</v>
+        <v>0.4237</v>
       </c>
       <c t="n" r="D68">
-        <v>-1.1737</v>
+        <v>1.7880</v>
       </c>
       <c t="n" r="E68">
-        <v>25.5706</v>
+        <v>8.7390</v>
       </c>
       <c t="n" r="F68">
-        <v>-0.3142</v>
+        <v>1.7384</v>
       </c>
       <c t="n" r="G68">
-        <v>26.1252</v>
+        <v>25.8338</v>
       </c>
       <c t="n" r="H68">
-        <v>49.1261</v>
-      </c>
-      <c t="n" r="I68">
-        <v>980.8711</v>
+        <v>76.5555</v>
       </c>
     </row>
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">UNC</t>
+          <t xml:space="preserve">NUY</t>
         </is>
       </c>
       <c t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C69">
-        <v>0.4252</v>
+        <v>-2.2596</v>
       </c>
       <c t="n" r="D69">
-        <v>1.7858</v>
+        <v>0.0540</v>
       </c>
       <c t="n" r="E69">
-        <v>8.7402</v>
+        <v>17.0676</v>
       </c>
       <c t="n" r="F69">
-        <v>1.7400</v>
+        <v>0.9928</v>
       </c>
       <c t="n" r="G69">
-        <v>25.8615</v>
-      </c>
-      <c t="n" r="H69">
-        <v>76.5582</v>
+        <v>25.8214</v>
       </c>
     </row>
     <row r="70">
       <c t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">NUY</t>
+          <t xml:space="preserve">IDG</t>
         </is>
       </c>
       <c t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C70">
-        <v>-2.2812</v>
+        <v>0.2968</v>
       </c>
       <c t="n" r="D70">
-        <v>0.0538</v>
+        <v>2.7197</v>
       </c>
       <c t="n" r="E70">
-        <v>17.0685</v>
+        <v>16.6172</v>
       </c>
       <c t="n" r="F70">
-        <v>0.9705</v>
+        <v>4.1153</v>
       </c>
       <c t="n" r="G70">
-        <v>25.8178</v>
+        <v>25.8197</v>
+      </c>
+      <c t="n" r="H70">
+        <v>217.5628</v>
+      </c>
+      <c t="n" r="I70">
+        <v>496.5295</v>
       </c>
     </row>
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">IDG</t>
+          <t xml:space="preserve">AG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. METROPOL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C71">
-        <v>0.2742</v>
+        <v>4.2164</v>
       </c>
       <c t="n" r="D71">
-        <v>2.7163</v>
+        <v>4.9755</v>
       </c>
       <c t="n" r="E71">
-        <v>16.5918</v>
+        <v>14.2769</v>
       </c>
       <c t="n" r="F71">
-        <v>4.0919</v>
+        <v>1.0041</v>
       </c>
       <c t="n" r="G71">
-        <v>25.8105</v>
+        <v>25.3690</v>
       </c>
       <c t="n" r="H71">
-        <v>217.4913</v>
+        <v>331.4125</v>
       </c>
       <c t="n" r="I71">
-        <v>496.3803</v>
+        <v>836.6347</v>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">AG7</t>
+          <t xml:space="preserve">NUZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. METROPOL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C72">
-        <v>4.2449</v>
+        <v>1.2812</v>
       </c>
       <c t="n" r="D72">
-        <v>4.9991</v>
+        <v>3.5636</v>
       </c>
       <c t="n" r="E72">
-        <v>14.3031</v>
+        <v>-0.4795</v>
       </c>
       <c t="n" r="F72">
-        <v>1.0317</v>
+        <v>3.9649</v>
       </c>
       <c t="n" r="G72">
-        <v>25.4134</v>
+        <v>25.2488</v>
       </c>
       <c t="n" r="H72">
-        <v>331.5304</v>
-      </c>
-      <c t="n" r="I72">
-        <v>836.8908</v>
+        <v>161.6189</v>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">NUZ</t>
+          <t xml:space="preserve">IVB</t>
         </is>
       </c>
       <c t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ SANAYİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C73">
-        <v>1.2338</v>
+        <v>0.3977</v>
       </c>
       <c t="n" r="D73">
-        <v>3.5435</v>
+        <v>-0.1074</v>
       </c>
       <c t="n" r="E73">
-        <v>-0.5179</v>
+        <v>23.2022</v>
       </c>
       <c t="n" r="F73">
-        <v>3.9162</v>
+        <v>-0.1196</v>
       </c>
       <c t="n" r="G73">
-        <v>25.2447</v>
-      </c>
-      <c t="n" r="H73">
-        <v>161.4964</v>
+        <v>24.9217</v>
       </c>
     </row>
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">IVB</t>
+          <t xml:space="preserve">ZUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ SANAYİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C74">
-        <v>0.3986</v>
+        <v>-0.0942</v>
       </c>
       <c t="n" r="D74">
-        <v>-0.1141</v>
+        <v>-0.3015</v>
       </c>
       <c t="n" r="E74">
-        <v>23.1971</v>
+        <v>25.3038</v>
       </c>
       <c t="n" r="F74">
-        <v>-0.1187</v>
+        <v>-0.0143</v>
       </c>
       <c t="n" r="G74">
-        <v>24.9209</v>
+        <v>24.8233</v>
+      </c>
+      <c t="n" r="H74">
+        <v>199.1958</v>
+      </c>
+      <c t="n" r="I74">
+        <v>400.1090</v>
       </c>
     </row>
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">ZUG</t>
+          <t xml:space="preserve">UKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. KONUT ALFA KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C75">
-        <v>-0.0927</v>
+        <v>1.7298</v>
       </c>
       <c t="n" r="D75">
-        <v>-0.2271</v>
+        <v>4.1458</v>
       </c>
       <c t="n" r="E75">
-        <v>25.3036</v>
+        <v>16.2124</v>
       </c>
       <c t="n" r="F75">
-        <v>-0.0128</v>
+        <v>4.3532</v>
       </c>
       <c t="n" r="G75">
-        <v>24.8238</v>
+        <v>24.7429</v>
       </c>
       <c t="n" r="H75">
-        <v>199.2004</v>
+        <v>134.8414</v>
       </c>
       <c t="n" r="I75">
-        <v>400.1177</v>
+        <v>635418.9018</v>
       </c>
     </row>
     <row r="76">
@@ -2437,22 +2437,22 @@
         </is>
       </c>
       <c t="n" r="C76">
-        <v>-2.2949</v>
+        <v>-2.3824</v>
       </c>
       <c t="n" r="D76">
-        <v>-2.1705</v>
+        <v>-2.2648</v>
       </c>
       <c t="n" r="E76">
-        <v>8.0738</v>
+        <v>8.0266</v>
       </c>
       <c t="n" r="F76">
-        <v>-2.6221</v>
+        <v>-2.7092</v>
       </c>
       <c t="n" r="G76">
-        <v>24.7842</v>
+        <v>24.6115</v>
       </c>
       <c t="n" r="H76">
-        <v>148.9886</v>
+        <v>148.7657</v>
       </c>
     </row>
     <row r="77">
@@ -2467,25 +2467,25 @@
         </is>
       </c>
       <c t="n" r="C77">
-        <v>-2.6530</v>
+        <v>-2.6568</v>
       </c>
       <c t="n" r="D77">
-        <v>5.5911</v>
+        <v>5.5918</v>
       </c>
       <c t="n" r="E77">
-        <v>24.7643</v>
+        <v>24.7794</v>
       </c>
       <c t="n" r="F77">
-        <v>-1.5813</v>
+        <v>-1.5851</v>
       </c>
       <c t="n" r="G77">
-        <v>23.7132</v>
+        <v>23.7078</v>
       </c>
       <c t="n" r="H77">
-        <v>253.3243</v>
+        <v>253.3108</v>
       </c>
       <c t="n" r="I77">
-        <v>781.4171</v>
+        <v>781.0074</v>
       </c>
     </row>
     <row r="78">
@@ -2500,25 +2500,25 @@
         </is>
       </c>
       <c t="n" r="C78">
-        <v>6.6994</v>
+        <v>6.7104</v>
       </c>
       <c t="n" r="D78">
-        <v>8.4335</v>
+        <v>8.5107</v>
       </c>
       <c t="n" r="E78">
-        <v>16.2060</v>
+        <v>16.1464</v>
       </c>
       <c t="n" r="F78">
-        <v>6.9111</v>
+        <v>6.9221</v>
       </c>
       <c t="n" r="G78">
-        <v>23.0808</v>
+        <v>23.0966</v>
       </c>
       <c t="n" r="H78">
-        <v>244.2187</v>
+        <v>244.2541</v>
       </c>
       <c t="n" r="I78">
-        <v>780.8700</v>
+        <v>780.9606</v>
       </c>
     </row>
     <row r="79">
@@ -2533,22 +2533,22 @@
         </is>
       </c>
       <c t="n" r="C79">
-        <v>-0.1049</v>
+        <v>-0.1065</v>
       </c>
       <c t="n" r="D79">
-        <v>-0.6136</v>
+        <v>-0.6153</v>
       </c>
       <c t="n" r="E79">
-        <v>23.0877</v>
+        <v>23.0859</v>
       </c>
       <c t="n" r="F79">
-        <v>-0.7267</v>
+        <v>-0.7284</v>
       </c>
       <c t="n" r="G79">
-        <v>21.8532</v>
+        <v>21.8622</v>
       </c>
       <c t="n" r="H79">
-        <v>171.1644</v>
+        <v>171.1599</v>
       </c>
     </row>
     <row r="80">
@@ -2563,25 +2563,25 @@
         </is>
       </c>
       <c t="n" r="C80">
-        <v>0.3886</v>
+        <v>0.3930</v>
       </c>
       <c t="n" r="D80">
-        <v>0.9984</v>
+        <v>1.0046</v>
       </c>
       <c t="n" r="E80">
-        <v>3.8473</v>
+        <v>3.8387</v>
       </c>
       <c t="n" r="F80">
-        <v>1.3799</v>
+        <v>1.3844</v>
       </c>
       <c t="n" r="G80">
-        <v>21.4929</v>
+        <v>21.4795</v>
       </c>
       <c t="n" r="H80">
-        <v>264.3103</v>
+        <v>264.3263</v>
       </c>
       <c t="n" r="I80">
-        <v>795.7346</v>
+        <v>795.6992</v>
       </c>
     </row>
     <row r="81">
@@ -2596,22 +2596,22 @@
         </is>
       </c>
       <c t="n" r="C81">
-        <v>0.9354</v>
+        <v>0.9617</v>
       </c>
       <c t="n" r="D81">
-        <v>1.6193</v>
+        <v>2.7346</v>
       </c>
       <c t="n" r="E81">
-        <v>12.1500</v>
+        <v>12.0841</v>
       </c>
       <c t="n" r="F81">
-        <v>1.7335</v>
+        <v>1.7600</v>
       </c>
       <c t="n" r="G81">
-        <v>21.4575</v>
+        <v>21.3691</v>
       </c>
       <c t="n" r="H81">
-        <v>76.9137</v>
+        <v>76.9598</v>
       </c>
     </row>
     <row r="82">
@@ -2626,22 +2626,22 @@
         </is>
       </c>
       <c t="n" r="C82">
-        <v>-0.1031</v>
+        <v>-0.1059</v>
       </c>
       <c t="n" r="D82">
-        <v>-0.3084</v>
+        <v>-0.3085</v>
       </c>
       <c t="n" r="E82">
-        <v>22.0979</v>
+        <v>22.0980</v>
       </c>
       <c t="n" r="F82">
-        <v>-2.4716</v>
+        <v>-2.4743</v>
       </c>
       <c t="n" r="G82">
-        <v>21.2792</v>
+        <v>21.2902</v>
       </c>
       <c t="n" r="H82">
-        <v>47.2009</v>
+        <v>47.1968</v>
       </c>
     </row>
     <row r="83">
@@ -2656,25 +2656,25 @@
         </is>
       </c>
       <c t="n" r="C83">
-        <v>0.2728</v>
+        <v>0.2739</v>
       </c>
       <c t="n" r="D83">
-        <v>1.0238</v>
+        <v>0.9968</v>
       </c>
       <c t="n" r="E83">
-        <v>5.6494</v>
+        <v>5.6505</v>
       </c>
       <c t="n" r="F83">
-        <v>1.1132</v>
+        <v>1.1143</v>
       </c>
       <c t="n" r="G83">
-        <v>20.9107</v>
+        <v>20.9122</v>
       </c>
       <c t="n" r="H83">
-        <v>221.0087</v>
+        <v>221.0123</v>
       </c>
       <c t="n" r="I83">
-        <v>989.6862</v>
+        <v>989.7155</v>
       </c>
     </row>
     <row r="84">
@@ -2689,25 +2689,25 @@
         </is>
       </c>
       <c t="n" r="C84">
-        <v>0.7885</v>
+        <v>0.5484</v>
       </c>
       <c t="n" r="D84">
-        <v>1.0634</v>
+        <v>0.8263</v>
       </c>
       <c t="n" r="E84">
-        <v>17.5768</v>
+        <v>17.2972</v>
       </c>
       <c t="n" r="F84">
-        <v>1.2580</v>
+        <v>1.0168</v>
       </c>
       <c t="n" r="G84">
-        <v>20.8075</v>
+        <v>20.5652</v>
       </c>
       <c t="n" r="H84">
-        <v>175.0248</v>
+        <v>174.3699</v>
       </c>
       <c t="n" r="I84">
-        <v>1195.6200</v>
+        <v>1193.5298</v>
       </c>
     </row>
     <row r="85">
@@ -2722,22 +2722,22 @@
         </is>
       </c>
       <c t="n" r="C85">
-        <v>-1.6197</v>
+        <v>-1.6160</v>
       </c>
       <c t="n" r="D85">
-        <v>0.0453</v>
+        <v>0.0491</v>
       </c>
       <c t="n" r="E85">
-        <v>16.6135</v>
+        <v>16.6180</v>
       </c>
       <c t="n" r="F85">
-        <v>0.5053</v>
+        <v>0.5091</v>
       </c>
       <c t="n" r="G85">
-        <v>20.2404</v>
+        <v>20.2465</v>
       </c>
       <c t="n" r="H85">
-        <v>368.1196</v>
+        <v>368.1373</v>
       </c>
     </row>
     <row r="86">
@@ -2752,25 +2752,25 @@
         </is>
       </c>
       <c t="n" r="C86">
-        <v>-0.4950</v>
+        <v>-0.4325</v>
       </c>
       <c t="n" r="D86">
-        <v>1.3001</v>
+        <v>1.3799</v>
       </c>
       <c t="n" r="E86">
-        <v>15.3902</v>
+        <v>15.4405</v>
       </c>
       <c t="n" r="F86">
-        <v>-2.8843</v>
+        <v>-2.8233</v>
       </c>
       <c t="n" r="G86">
-        <v>19.6445</v>
+        <v>19.7382</v>
       </c>
       <c t="n" r="H86">
-        <v>150.0638</v>
+        <v>150.2208</v>
       </c>
       <c t="n" r="I86">
-        <v>418.3589</v>
+        <v>418.6844</v>
       </c>
     </row>
     <row r="87">
@@ -2785,22 +2785,22 @@
         </is>
       </c>
       <c t="n" r="C87">
-        <v>0.5004</v>
+        <v>0.5108</v>
       </c>
       <c t="n" r="D87">
-        <v>1.2128</v>
+        <v>1.2172</v>
       </c>
       <c t="n" r="E87">
-        <v>11.5283</v>
+        <v>11.5395</v>
       </c>
       <c t="n" r="F87">
-        <v>-0.8078</v>
+        <v>-0.7977</v>
       </c>
       <c t="n" r="G87">
-        <v>19.6408</v>
+        <v>19.6471</v>
       </c>
       <c t="n" r="H87">
-        <v>151.9274</v>
+        <v>151.9533</v>
       </c>
     </row>
     <row r="88">
@@ -2815,25 +2815,25 @@
         </is>
       </c>
       <c t="n" r="C88">
-        <v>0.1048</v>
+        <v>0.1071</v>
       </c>
       <c t="n" r="D88">
-        <v>-0.0931</v>
+        <v>-0.0754</v>
       </c>
       <c t="n" r="E88">
-        <v>15.4462</v>
+        <v>15.4429</v>
       </c>
       <c t="n" r="F88">
-        <v>0.4192</v>
+        <v>0.4215</v>
       </c>
       <c t="n" r="G88">
-        <v>19.4105</v>
+        <v>19.4128</v>
       </c>
       <c t="n" r="H88">
-        <v>116.2943</v>
+        <v>116.2992</v>
       </c>
       <c t="n" r="I88">
-        <v>1160.1015</v>
+        <v>1160.1302</v>
       </c>
     </row>
     <row r="89">
@@ -2848,22 +2848,22 @@
         </is>
       </c>
       <c t="n" r="C89">
-        <v>-0.2391</v>
+        <v>-0.2383</v>
       </c>
       <c t="n" r="D89">
-        <v>0.2570</v>
+        <v>-0.1641</v>
       </c>
       <c t="n" r="E89">
-        <v>19.1448</v>
+        <v>19.1445</v>
       </c>
       <c t="n" r="F89">
-        <v>-0.0409</v>
+        <v>-0.0400</v>
       </c>
       <c t="n" r="G89">
-        <v>18.8359</v>
+        <v>18.8354</v>
       </c>
       <c t="n" r="H89">
-        <v>1431.5943</v>
+        <v>1431.6073</v>
       </c>
     </row>
     <row r="90">
@@ -2878,25 +2878,25 @@
         </is>
       </c>
       <c t="n" r="C90">
-        <v>2.0897</v>
+        <v>1.8041</v>
       </c>
       <c t="n" r="D90">
-        <v>2.4119</v>
+        <v>2.1739</v>
       </c>
       <c t="n" r="E90">
-        <v>17.1136</v>
+        <v>16.9159</v>
       </c>
       <c t="n" r="F90">
-        <v>2.6055</v>
+        <v>2.3185</v>
       </c>
       <c t="n" r="G90">
-        <v>18.3510</v>
+        <v>18.0184</v>
       </c>
       <c t="n" r="H90">
-        <v>144.3757</v>
+        <v>143.6922</v>
       </c>
       <c t="n" r="I90">
-        <v>450.4790</v>
+        <v>448.9734</v>
       </c>
     </row>
     <row r="91">
@@ -2911,25 +2911,25 @@
         </is>
       </c>
       <c t="n" r="C91">
-        <v>-0.5997</v>
+        <v>-0.6045</v>
       </c>
       <c t="n" r="D91">
-        <v>-0.4666</v>
+        <v>-0.5457</v>
       </c>
       <c t="n" r="E91">
-        <v>11.1794</v>
+        <v>11.1795</v>
       </c>
       <c t="n" r="F91">
-        <v>-0.5859</v>
+        <v>-0.5908</v>
       </c>
       <c t="n" r="G91">
-        <v>17.9869</v>
+        <v>17.9937</v>
       </c>
       <c t="n" r="H91">
-        <v>245.6469</v>
+        <v>245.6300</v>
       </c>
       <c t="n" r="I91">
-        <v>1005.3864</v>
+        <v>1005.3322</v>
       </c>
     </row>
     <row r="92">
@@ -2944,22 +2944,22 @@
         </is>
       </c>
       <c t="n" r="C92">
-        <v>-1.5360</v>
+        <v>-1.5358</v>
       </c>
       <c t="n" r="D92">
-        <v>-1.0571</v>
+        <v>-1.0582</v>
       </c>
       <c t="n" r="E92">
-        <v>25.6607</v>
+        <v>25.6593</v>
       </c>
       <c t="n" r="F92">
-        <v>-0.8532</v>
+        <v>-0.8531</v>
       </c>
       <c t="n" r="G92">
-        <v>17.8162</v>
+        <v>17.8192</v>
       </c>
       <c t="n" r="H92">
-        <v>215.9928</v>
+        <v>215.9932</v>
       </c>
     </row>
     <row r="93">
@@ -2974,22 +2974,22 @@
         </is>
       </c>
       <c t="n" r="C93">
-        <v>-0.1295</v>
+        <v>-0.1339</v>
       </c>
       <c t="n" r="D93">
-        <v>-0.3930</v>
+        <v>-0.3933</v>
       </c>
       <c t="n" r="E93">
         <v>26.9057</v>
       </c>
       <c t="n" r="F93">
-        <v>-0.4471</v>
+        <v>-0.4516</v>
       </c>
       <c t="n" r="G93">
-        <v>17.7032</v>
+        <v>17.7029</v>
       </c>
       <c t="n" r="H93">
-        <v>775.8840</v>
+        <v>775.8450</v>
       </c>
     </row>
     <row r="94">
@@ -3004,25 +3004,25 @@
         </is>
       </c>
       <c t="n" r="C94">
-        <v>-0.7145</v>
+        <v>-0.7203</v>
       </c>
       <c t="n" r="D94">
-        <v>-2.0850</v>
+        <v>-2.0853</v>
       </c>
       <c t="n" r="E94">
-        <v>11.7790</v>
+        <v>11.7778</v>
       </c>
       <c t="n" r="F94">
-        <v>-2.2726</v>
+        <v>-2.2783</v>
       </c>
       <c t="n" r="G94">
-        <v>17.0927</v>
+        <v>17.1057</v>
       </c>
       <c t="n" r="H94">
-        <v>148.4761</v>
+        <v>148.4616</v>
       </c>
       <c t="n" r="I94">
-        <v>674.7821</v>
+        <v>674.7369</v>
       </c>
     </row>
     <row r="95">
@@ -3040,7 +3040,7 @@
         <v>-0.2508</v>
       </c>
       <c t="n" r="D95">
-        <v>-0.2529</v>
+        <v>-0.2508</v>
       </c>
       <c t="n" r="E95">
         <v>5.3810</v>
@@ -3049,7 +3049,7 @@
         <v>-0.5036</v>
       </c>
       <c t="n" r="G95">
-        <v>16.9180</v>
+        <v>16.9179</v>
       </c>
     </row>
     <row r="96">
@@ -3064,25 +3064,25 @@
         </is>
       </c>
       <c t="n" r="C96">
-        <v>-0.2044</v>
+        <v>-0.2045</v>
       </c>
       <c t="n" r="D96">
-        <v>0.9085</v>
+        <v>0.5860</v>
       </c>
       <c t="n" r="E96">
-        <v>6.1938</v>
+        <v>6.1909</v>
       </c>
       <c t="n" r="F96">
-        <v>-0.6836</v>
+        <v>-0.6837</v>
       </c>
       <c t="n" r="G96">
-        <v>16.7667</v>
+        <v>16.7654</v>
       </c>
       <c t="n" r="H96">
-        <v>320.7575</v>
+        <v>320.7571</v>
       </c>
       <c t="n" r="I96">
-        <v>1601.1264</v>
+        <v>1601.1248</v>
       </c>
     </row>
     <row r="97">
@@ -3097,22 +3097,22 @@
         </is>
       </c>
       <c t="n" r="C97">
-        <v>-0.0087</v>
+        <v>-0.0088</v>
       </c>
       <c t="n" r="D97">
         <v>-0.0462</v>
       </c>
       <c t="n" r="E97">
-        <v>16.1309</v>
+        <v>15.5086</v>
       </c>
       <c t="n" r="F97">
         <v>-0.0458</v>
       </c>
       <c t="n" r="G97">
-        <v>16.0179</v>
+        <v>16.0178</v>
       </c>
       <c t="n" r="H97">
-        <v>580.1472</v>
+        <v>580.1468</v>
       </c>
     </row>
     <row r="98">
@@ -3127,25 +3127,25 @@
         </is>
       </c>
       <c t="n" r="C98">
-        <v>0.2706</v>
+        <v>0.3009</v>
       </c>
       <c t="n" r="D98">
-        <v>-0.4092</v>
+        <v>-0.3815</v>
       </c>
       <c t="n" r="E98">
-        <v>2.2601</v>
+        <v>2.3233</v>
       </c>
       <c t="n" r="F98">
-        <v>0.1282</v>
+        <v>0.1584</v>
       </c>
       <c t="n" r="G98">
-        <v>15.8312</v>
+        <v>15.7879</v>
       </c>
       <c t="n" r="H98">
-        <v>0.5737</v>
+        <v>0.6041</v>
       </c>
       <c t="n" r="I98">
-        <v>58.2283</v>
+        <v>58.2760</v>
       </c>
     </row>
     <row r="99">
@@ -3160,22 +3160,22 @@
         </is>
       </c>
       <c t="n" r="C99">
-        <v>-0.1827</v>
+        <v>-0.0777</v>
       </c>
       <c t="n" r="D99">
-        <v>2.5631</v>
+        <v>2.5530</v>
       </c>
       <c t="n" r="E99">
-        <v>15.5029</v>
+        <v>15.6048</v>
       </c>
       <c t="n" r="F99">
-        <v>3.4045</v>
+        <v>3.5133</v>
       </c>
       <c t="n" r="G99">
-        <v>15.1874</v>
+        <v>15.3195</v>
       </c>
       <c t="n" r="H99">
-        <v>187.5946</v>
+        <v>187.8970</v>
       </c>
     </row>
     <row r="100">
@@ -3190,241 +3190,241 @@
         </is>
       </c>
       <c t="n" r="C100">
-        <v>-0.2231</v>
+        <v>-0.2294</v>
       </c>
       <c t="n" r="D100">
         <v>-0.6075</v>
       </c>
       <c t="n" r="E100">
-        <v>16.6331</v>
+        <v>16.6333</v>
       </c>
       <c t="n" r="F100">
-        <v>-0.6946</v>
+        <v>-0.7009</v>
       </c>
       <c t="n" r="G100">
-        <v>14.9597</v>
+        <v>14.9605</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">FRG</t>
+          <t xml:space="preserve">AZ2</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C101">
-        <v>5.6764</v>
+        <v>-0.1186</v>
       </c>
       <c t="n" r="D101">
-        <v>3.9710</v>
+        <v>1.6128</v>
       </c>
       <c t="n" r="E101">
-        <v>15.9068</v>
+        <v>4.8691</v>
       </c>
       <c t="n" r="F101">
-        <v>5.8241</v>
+        <v>1.1829</v>
       </c>
       <c t="n" r="G101">
-        <v>14.9491</v>
+        <v>14.3545</v>
       </c>
       <c t="n" r="H101">
-        <v>95.3320</v>
+        <v>265.9108</v>
       </c>
       <c t="n" r="I101">
-        <v>448.0886</v>
+        <v>1193.2903</v>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">RP4</t>
+          <t xml:space="preserve">FRG</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C102">
-        <v>4.5694</v>
+        <v>4.8590</v>
       </c>
       <c t="n" r="D102">
-        <v>-4.3926</v>
+        <v>3.2624</v>
       </c>
       <c t="n" r="E102">
-        <v>11.2718</v>
+        <v>15.3377</v>
       </c>
       <c t="n" r="F102">
-        <v>-3.5627</v>
+        <v>5.0056</v>
       </c>
       <c t="n" r="G102">
-        <v>14.5458</v>
+        <v>13.9839</v>
       </c>
       <c t="n" r="H102">
-        <v>111.7179</v>
+        <v>93.8211</v>
       </c>
       <c t="n" r="I102">
-        <v>367.7609</v>
+        <v>443.7072</v>
       </c>
     </row>
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">AZ2</t>
+          <t xml:space="preserve">RAS</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C103">
-        <v>-0.1437</v>
+        <v>-0.1516</v>
       </c>
       <c t="n" r="D103">
-        <v>1.5765</v>
+        <v>0.5157</v>
       </c>
       <c t="n" r="E103">
-        <v>4.8481</v>
+        <v>12.6827</v>
       </c>
       <c t="n" r="F103">
-        <v>1.1575</v>
+        <v>1.1712</v>
       </c>
       <c t="n" r="G103">
-        <v>14.3090</v>
+        <v>13.9442</v>
       </c>
       <c t="n" r="H103">
-        <v>265.8190</v>
+        <v>260.6703</v>
       </c>
       <c t="n" r="I103">
-        <v>1192.9656</v>
+        <v>474.3482</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">RAS</t>
+          <t xml:space="preserve">NG4</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C104">
-        <v>-0.1286</v>
+        <v>0.2363</v>
       </c>
       <c t="n" r="D104">
-        <v>0.5707</v>
+        <v>-0.0223</v>
       </c>
       <c t="n" r="E104">
-        <v>12.7061</v>
+        <v>13.7559</v>
       </c>
       <c t="n" r="F104">
-        <v>1.1945</v>
+        <v>-0.9373</v>
       </c>
       <c t="n" r="G104">
-        <v>13.9869</v>
+        <v>13.7282</v>
       </c>
       <c t="n" r="H104">
-        <v>260.7534</v>
-      </c>
-      <c t="n" r="I104">
-        <v>474.1199</v>
+        <v>225.1336</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">NG4</t>
+          <t xml:space="preserve">RP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C105">
-        <v>0.2375</v>
+        <v>3.8329</v>
       </c>
       <c t="n" r="D105">
-        <v>-0.0218</v>
+        <v>-5.0161</v>
       </c>
       <c t="n" r="E105">
-        <v>13.7570</v>
+        <v>10.7305</v>
       </c>
       <c t="n" r="F105">
-        <v>-0.9360</v>
+        <v>-4.2420</v>
       </c>
       <c t="n" r="G105">
-        <v>13.7397</v>
+        <v>13.5663</v>
       </c>
       <c t="n" r="H105">
-        <v>225.1377</v>
+        <v>110.2266</v>
+      </c>
+      <c t="n" r="I105">
+        <v>364.7137</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">ZVE</t>
+          <t xml:space="preserve">RKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. NEF GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C106">
-        <v>0.0358</v>
+        <v>-0.0550</v>
       </c>
       <c t="n" r="D106">
-        <v>0.2018</v>
+        <v>-0.3437</v>
       </c>
       <c t="n" r="E106">
-        <v>-0.9860</v>
+        <v>13.7144</v>
       </c>
       <c t="n" r="F106">
-        <v>0.1944</v>
+        <v>-0.5431</v>
       </c>
       <c t="n" r="G106">
-        <v>13.0455</v>
+        <v>13.0495</v>
       </c>
       <c t="n" r="H106">
-        <v>124.6410</v>
+        <v>493.5670</v>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">RKG</t>
+          <t xml:space="preserve">ZVE</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. NEF GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C107">
-        <v>-0.0540</v>
+        <v>-0.0520</v>
       </c>
       <c t="n" r="D107">
-        <v>-0.3436</v>
+        <v>0.1176</v>
       </c>
       <c t="n" r="E107">
-        <v>13.7143</v>
+        <v>-1.0681</v>
       </c>
       <c t="n" r="F107">
-        <v>-0.5422</v>
+        <v>0.1064</v>
       </c>
       <c t="n" r="G107">
-        <v>13.0373</v>
+        <v>12.9470</v>
       </c>
       <c t="n" r="H107">
-        <v>493.5727</v>
+        <v>124.4438</v>
       </c>
     </row>
     <row r="108">
@@ -3439,19 +3439,19 @@
         </is>
       </c>
       <c t="n" r="C108">
-        <v>0.0513</v>
+        <v>0.0817</v>
       </c>
       <c t="n" r="D108">
-        <v>2.3651</v>
+        <v>2.2896</v>
       </c>
       <c t="n" r="E108">
-        <v>3.7758</v>
+        <v>3.6465</v>
       </c>
       <c t="n" r="F108">
-        <v>2.4442</v>
+        <v>2.4754</v>
       </c>
       <c t="n" r="G108">
-        <v>12.7803</v>
+        <v>12.8084</v>
       </c>
     </row>
     <row r="109">
@@ -3466,25 +3466,25 @@
         </is>
       </c>
       <c t="n" r="C109">
-        <v>-0.3203</v>
+        <v>-0.3219</v>
       </c>
       <c t="n" r="D109">
-        <v>1.0477</v>
+        <v>0.6197</v>
       </c>
       <c t="n" r="E109">
-        <v>8.8973</v>
+        <v>8.8903</v>
       </c>
       <c t="n" r="F109">
-        <v>-1.1206</v>
+        <v>-1.1222</v>
       </c>
       <c t="n" r="G109">
-        <v>12.4321</v>
+        <v>12.4171</v>
       </c>
       <c t="n" r="H109">
-        <v>201.5374</v>
+        <v>201.5325</v>
       </c>
       <c t="n" r="I109">
-        <v>576.4262</v>
+        <v>576.4153</v>
       </c>
     </row>
     <row r="110">
@@ -3499,22 +3499,22 @@
         </is>
       </c>
       <c t="n" r="C110">
-        <v>0.0776</v>
+        <v>0.0644</v>
       </c>
       <c t="n" r="D110">
-        <v>0.7893</v>
+        <v>0.7484</v>
       </c>
       <c t="n" r="E110">
-        <v>9.8483</v>
+        <v>9.8355</v>
       </c>
       <c t="n" r="F110">
-        <v>0.7710</v>
+        <v>0.7577</v>
       </c>
       <c t="n" r="G110">
-        <v>12.3494</v>
+        <v>12.2962</v>
       </c>
       <c t="n" r="H110">
-        <v>-18.5995</v>
+        <v>-18.6102</v>
       </c>
     </row>
     <row r="111">
@@ -3529,19 +3529,19 @@
         </is>
       </c>
       <c t="n" r="C111">
-        <v>0.7978</v>
+        <v>0.8212</v>
       </c>
       <c t="n" r="D111">
-        <v>2.4673</v>
+        <v>2.1750</v>
       </c>
       <c t="n" r="E111">
-        <v>11.8439</v>
+        <v>11.8679</v>
       </c>
       <c t="n" r="F111">
-        <v>3.2866</v>
+        <v>3.3105</v>
       </c>
       <c t="n" r="G111">
-        <v>12.2868</v>
+        <v>11.2708</v>
       </c>
     </row>
     <row r="112">
@@ -3556,22 +3556,22 @@
         </is>
       </c>
       <c t="n" r="C112">
-        <v>0.0386</v>
+        <v>0.0414</v>
       </c>
       <c t="n" r="D112">
-        <v>0.4043</v>
+        <v>0.4072</v>
       </c>
       <c t="n" r="E112">
-        <v>27.6667</v>
+        <v>27.6735</v>
       </c>
       <c t="n" r="F112">
-        <v>0.3223</v>
+        <v>0.3251</v>
       </c>
       <c t="n" r="G112">
-        <v>11.3779</v>
+        <v>10.5070</v>
       </c>
       <c t="n" r="H112">
-        <v>134.4985</v>
+        <v>134.5052</v>
       </c>
     </row>
     <row r="113">
@@ -3586,103 +3586,103 @@
         </is>
       </c>
       <c t="n" r="C113">
-        <v>-1.5831</v>
+        <v>-1.5880</v>
       </c>
       <c t="n" r="D113">
-        <v>-5.1426</v>
+        <v>-5.1495</v>
       </c>
       <c t="n" r="E113">
-        <v>33.3022</v>
+        <v>33.2931</v>
       </c>
       <c t="n" r="F113">
-        <v>-5.2001</v>
+        <v>-5.2048</v>
       </c>
       <c t="n" r="G113">
-        <v>10.4922</v>
+        <v>10.4960</v>
       </c>
       <c t="n" r="H113">
-        <v>400.5816</v>
+        <v>400.5566</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">HDU</t>
+          <t xml:space="preserve">NBA</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C114">
-        <v>-0.0729</v>
+        <v>-29.3103</v>
       </c>
       <c t="n" r="D114">
-        <v>-0.2028</v>
+        <v>-32.9237</v>
       </c>
       <c t="n" r="E114">
-        <v>10.8904</v>
+        <v>1680.6698</v>
       </c>
       <c t="n" r="F114">
-        <v>-0.2247</v>
+        <v>-33.0544</v>
       </c>
       <c t="n" r="G114">
-        <v>10.4031</v>
+        <v>10.4182</v>
       </c>
     </row>
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">IN9</t>
+          <t xml:space="preserve">HDU</t>
         </is>
       </c>
       <c t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. NEFES EGE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C115">
-        <v>-0.3237</v>
+        <v>-0.0748</v>
       </c>
       <c t="n" r="D115">
-        <v>-1.2039</v>
+        <v>-0.1836</v>
       </c>
       <c t="n" r="E115">
-        <v>12.3998</v>
+        <v>10.8899</v>
       </c>
       <c t="n" r="F115">
-        <v>-1.3293</v>
+        <v>-0.2266</v>
       </c>
       <c t="n" r="G115">
-        <v>10.3061</v>
+        <v>10.4012</v>
       </c>
     </row>
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">NBA</t>
+          <t xml:space="preserve">IN9</t>
         </is>
       </c>
       <c t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. NEFES EGE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C116">
-        <v>-29.2969</v>
+        <v>-0.3384</v>
       </c>
       <c t="n" r="D116">
-        <v>-32.9203</v>
+        <v>-1.1970</v>
       </c>
       <c t="n" r="E116">
-        <v>1660.2416</v>
+        <v>12.3999</v>
       </c>
       <c t="n" r="F116">
-        <v>-33.0417</v>
+        <v>-1.3438</v>
       </c>
       <c t="n" r="G116">
-        <v>10.0141</v>
+        <v>10.3035</v>
       </c>
     </row>
     <row r="117">
@@ -3697,25 +3697,25 @@
         </is>
       </c>
       <c t="n" r="C117">
-        <v>0.3058</v>
+        <v>0.3043</v>
       </c>
       <c t="n" r="D117">
-        <v>0.5164</v>
+        <v>0.4967</v>
       </c>
       <c t="n" r="E117">
-        <v>2.1630</v>
+        <v>2.1858</v>
       </c>
       <c t="n" r="F117">
-        <v>1.1211</v>
+        <v>1.1195</v>
       </c>
       <c t="n" r="G117">
-        <v>9.5741</v>
+        <v>9.5689</v>
       </c>
       <c t="n" r="H117">
-        <v>129.2901</v>
+        <v>129.2866</v>
       </c>
       <c t="n" r="I117">
-        <v>423.2283</v>
+        <v>423.7863</v>
       </c>
     </row>
     <row r="118">
@@ -3730,19 +3730,19 @@
         </is>
       </c>
       <c t="n" r="C118">
-        <v>0.4487</v>
+        <v>0.4532</v>
       </c>
       <c t="n" r="D118">
-        <v>1.6727</v>
+        <v>1.6751</v>
       </c>
       <c t="n" r="E118">
-        <v>6.5715</v>
+        <v>6.5762</v>
       </c>
       <c t="n" r="F118">
-        <v>1.2296</v>
+        <v>1.2341</v>
       </c>
       <c t="n" r="G118">
-        <v>9.2548</v>
+        <v>9.1919</v>
       </c>
     </row>
     <row r="119">
@@ -3757,19 +3757,19 @@
         </is>
       </c>
       <c t="n" r="C119">
-        <v>-0.0914</v>
+        <v>-0.0919</v>
       </c>
       <c t="n" r="D119">
-        <v>-0.1569</v>
+        <v>-0.1566</v>
       </c>
       <c t="n" r="E119">
         <v>9.2482</v>
       </c>
       <c t="n" r="F119">
-        <v>-0.1294</v>
+        <v>-0.1299</v>
       </c>
       <c t="n" r="G119">
-        <v>9.0068</v>
+        <v>9.0252</v>
       </c>
     </row>
     <row r="120">
@@ -3784,22 +3784,22 @@
         </is>
       </c>
       <c t="n" r="C120">
-        <v>0.2283</v>
+        <v>0.2271</v>
       </c>
       <c t="n" r="D120">
-        <v>1.7073</v>
+        <v>1.7071</v>
       </c>
       <c t="n" r="E120">
-        <v>8.3451</v>
+        <v>8.3448</v>
       </c>
       <c t="n" r="F120">
-        <v>1.6565</v>
+        <v>1.6553</v>
       </c>
       <c t="n" r="G120">
-        <v>8.9247</v>
+        <v>8.9313</v>
       </c>
       <c t="n" r="H120">
-        <v>125.0666</v>
+        <v>125.0640</v>
       </c>
     </row>
     <row r="121">
@@ -3814,22 +3814,22 @@
         </is>
       </c>
       <c t="n" r="C121">
-        <v>-0.0921</v>
+        <v>-0.0940</v>
       </c>
       <c t="n" r="D121">
-        <v>-0.2429</v>
+        <v>-0.2431</v>
       </c>
       <c t="n" r="E121">
-        <v>9.0311</v>
+        <v>9.0312</v>
       </c>
       <c t="n" r="F121">
-        <v>-0.1720</v>
+        <v>-0.1739</v>
       </c>
       <c t="n" r="G121">
-        <v>8.8606</v>
+        <v>8.8622</v>
       </c>
       <c t="n" r="H121">
-        <v>253.3588</v>
+        <v>253.3521</v>
       </c>
     </row>
     <row r="122">
@@ -3844,22 +3844,22 @@
         </is>
       </c>
       <c t="n" r="C122">
-        <v>0.1948</v>
+        <v>0.1927</v>
       </c>
       <c t="n" r="D122">
-        <v>0.4628</v>
+        <v>0.4627</v>
       </c>
       <c t="n" r="E122">
-        <v>3.9879</v>
+        <v>3.9950</v>
       </c>
       <c t="n" r="F122">
-        <v>0.5539</v>
+        <v>0.5519</v>
       </c>
       <c t="n" r="G122">
-        <v>8.6229</v>
+        <v>8.6342</v>
       </c>
       <c t="n" r="H122">
-        <v>244.7903</v>
+        <v>244.7833</v>
       </c>
     </row>
     <row r="123">
@@ -3874,19 +3874,19 @@
         </is>
       </c>
       <c t="n" r="C123">
-        <v>0.3970</v>
+        <v>0.3934</v>
       </c>
       <c t="n" r="D123">
-        <v>-1.8938</v>
+        <v>-1.8963</v>
       </c>
       <c t="n" r="E123">
-        <v>7.5511</v>
+        <v>7.5487</v>
       </c>
       <c t="n" r="F123">
-        <v>-1.4157</v>
+        <v>-1.4192</v>
       </c>
       <c t="n" r="G123">
-        <v>8.4609</v>
+        <v>8.4598</v>
       </c>
     </row>
     <row r="124">
@@ -3901,19 +3901,19 @@
         </is>
       </c>
       <c t="n" r="C124">
-        <v>-0.5061</v>
+        <v>-0.5108</v>
       </c>
       <c t="n" r="D124">
-        <v>-0.7019</v>
+        <v>-0.7027</v>
       </c>
       <c t="n" r="E124">
-        <v>8.8954</v>
+        <v>8.8935</v>
       </c>
       <c t="n" r="F124">
-        <v>-0.4632</v>
+        <v>-0.4679</v>
       </c>
       <c t="n" r="G124">
-        <v>8.3793</v>
+        <v>8.3771</v>
       </c>
     </row>
     <row r="125">
@@ -3928,22 +3928,22 @@
         </is>
       </c>
       <c t="n" r="C125">
-        <v>0.4565</v>
+        <v>0.4644</v>
       </c>
       <c t="n" r="D125">
-        <v>0.5736</v>
+        <v>0.5822</v>
       </c>
       <c t="n" r="E125">
-        <v>7.0960</v>
+        <v>7.1057</v>
       </c>
       <c t="n" r="F125">
-        <v>0.6546</v>
+        <v>0.6625</v>
       </c>
       <c t="n" r="G125">
-        <v>7.7475</v>
+        <v>7.7710</v>
       </c>
       <c t="n" r="H125">
-        <v>113.5683</v>
+        <v>113.5850</v>
       </c>
     </row>
     <row r="126">
@@ -3958,22 +3958,22 @@
         </is>
       </c>
       <c t="n" r="C126">
-        <v>-0.3529</v>
+        <v>-0.3530</v>
       </c>
       <c t="n" r="D126">
-        <v>-0.2362</v>
+        <v>-0.2347</v>
       </c>
       <c t="n" r="E126">
-        <v>12.1039</v>
+        <v>12.1118</v>
       </c>
       <c t="n" r="F126">
-        <v>-0.9742</v>
+        <v>-0.9744</v>
       </c>
       <c t="n" r="G126">
-        <v>7.6390</v>
+        <v>7.6391</v>
       </c>
       <c t="n" r="H126">
-        <v>213.9096</v>
+        <v>213.9092</v>
       </c>
     </row>
     <row r="127">
@@ -3988,22 +3988,22 @@
         </is>
       </c>
       <c t="n" r="C127">
-        <v>1.2619</v>
+        <v>1.2719</v>
       </c>
       <c t="n" r="D127">
-        <v>0.7981</v>
+        <v>0.8096</v>
       </c>
       <c t="n" r="E127">
-        <v>6.5156</v>
+        <v>6.5346</v>
       </c>
       <c t="n" r="F127">
-        <v>0.7187</v>
+        <v>0.7286</v>
       </c>
       <c t="n" r="G127">
-        <v>6.5870</v>
+        <v>6.5994</v>
       </c>
       <c t="n" r="H127">
-        <v>160.5678</v>
+        <v>160.5936</v>
       </c>
     </row>
     <row r="128">
@@ -4021,7 +4021,7 @@
         <v>-0.3717</v>
       </c>
       <c t="n" r="D128">
-        <v>-0.4051</v>
+        <v>-0.3841</v>
       </c>
       <c t="n" r="E128">
         <v>7.2274</v>
@@ -4048,22 +4048,22 @@
         </is>
       </c>
       <c t="n" r="C129">
-        <v>-0.0498</v>
+        <v>-0.0510</v>
       </c>
       <c t="n" r="D129">
         <v>-0.1440</v>
       </c>
       <c t="n" r="E129">
-        <v>6.6187</v>
+        <v>6.6184</v>
       </c>
       <c t="n" r="F129">
-        <v>-0.1717</v>
+        <v>-0.1729</v>
       </c>
       <c t="n" r="G129">
-        <v>6.3421</v>
+        <v>6.3486</v>
       </c>
       <c t="n" r="H129">
-        <v>305.8122</v>
+        <v>305.8073</v>
       </c>
     </row>
     <row r="130">
@@ -4078,22 +4078,22 @@
         </is>
       </c>
       <c t="n" r="C130">
-        <v>0.1718</v>
+        <v>0.1914</v>
       </c>
       <c t="n" r="D130">
-        <v>1.0062</v>
+        <v>1.0075</v>
       </c>
       <c t="n" r="E130">
-        <v>13.5607</v>
+        <v>13.5758</v>
       </c>
       <c t="n" r="F130">
-        <v>1.2799</v>
+        <v>1.2997</v>
       </c>
       <c t="n" r="G130">
-        <v>5.8143</v>
+        <v>5.8434</v>
       </c>
       <c t="n" r="H130">
-        <v>195.4184</v>
+        <v>195.4761</v>
       </c>
     </row>
     <row r="131">
@@ -4108,19 +4108,19 @@
         </is>
       </c>
       <c t="n" r="C131">
-        <v>-0.0652</v>
+        <v>-0.0642</v>
       </c>
       <c t="n" r="D131">
-        <v>-0.1788</v>
+        <v>-0.1775</v>
       </c>
       <c t="n" r="E131">
-        <v>8.3426</v>
+        <v>8.3552</v>
       </c>
       <c t="n" r="F131">
-        <v>2.1403</v>
+        <v>2.1413</v>
       </c>
       <c t="n" r="G131">
-        <v>5.3166</v>
+        <v>5.3301</v>
       </c>
     </row>
     <row r="132">
@@ -4135,22 +4135,22 @@
         </is>
       </c>
       <c t="n" r="C132">
-        <v>0.3183</v>
+        <v>0.3199</v>
       </c>
       <c t="n" r="D132">
-        <v>1.1235</v>
+        <v>1.1249</v>
       </c>
       <c t="n" r="E132">
-        <v>11.5029</v>
+        <v>11.0293</v>
       </c>
       <c t="n" r="F132">
-        <v>1.1042</v>
+        <v>1.1058</v>
       </c>
       <c t="n" r="G132">
-        <v>5.2217</v>
+        <v>5.2177</v>
       </c>
       <c t="n" r="H132">
-        <v>153.4289</v>
+        <v>153.4329</v>
       </c>
     </row>
     <row r="133">
@@ -4165,22 +4165,22 @@
         </is>
       </c>
       <c t="n" r="C133">
-        <v>1.2167</v>
+        <v>1.2672</v>
       </c>
       <c t="n" r="D133">
-        <v>3.7254</v>
+        <v>3.7304</v>
       </c>
       <c t="n" r="E133">
-        <v>9.5774</v>
+        <v>9.6433</v>
       </c>
       <c t="n" r="F133">
-        <v>4.4018</v>
+        <v>4.4539</v>
       </c>
       <c t="n" r="G133">
-        <v>4.9859</v>
+        <v>5.0493</v>
       </c>
       <c t="n" r="H133">
-        <v>89.8582</v>
+        <v>89.9529</v>
       </c>
     </row>
     <row r="134">
@@ -4195,19 +4195,19 @@
         </is>
       </c>
       <c t="n" r="C134">
-        <v>0.1642</v>
+        <v>0.1660</v>
       </c>
       <c t="n" r="D134">
-        <v>-10.4818</v>
+        <v>-10.4920</v>
       </c>
       <c t="n" r="E134">
-        <v>0.3363</v>
+        <v>0.3246</v>
       </c>
       <c t="n" r="F134">
-        <v>-10.4751</v>
+        <v>-10.4735</v>
       </c>
       <c t="n" r="G134">
-        <v>4.7834</v>
+        <v>4.7751</v>
       </c>
     </row>
     <row r="135">
@@ -4222,82 +4222,82 @@
         </is>
       </c>
       <c t="n" r="C135">
-        <v>-0.2245</v>
+        <v>-0.2317</v>
       </c>
       <c t="n" r="D135">
-        <v>-0.6782</v>
+        <v>-0.6588</v>
       </c>
       <c t="n" r="E135">
-        <v>5.9027</v>
+        <v>5.9030</v>
       </c>
       <c t="n" r="F135">
-        <v>-0.7698</v>
+        <v>-0.7769</v>
       </c>
       <c t="n" r="G135">
-        <v>4.4807</v>
+        <v>4.4800</v>
       </c>
       <c t="n" r="H135">
-        <v>113.8958</v>
+        <v>113.8804</v>
       </c>
     </row>
     <row r="136">
       <c t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">OO1</t>
+          <t xml:space="preserve">ORX</t>
         </is>
       </c>
       <c t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C136">
-        <v>-0.6071</v>
+        <v>0.0533</v>
       </c>
       <c t="n" r="D136">
-        <v>-2.3262</v>
+        <v>-0.6425</v>
       </c>
       <c t="n" r="E136">
-        <v>-14.9058</v>
+        <v>1.0633</v>
       </c>
       <c t="n" r="F136">
-        <v>-2.5566</v>
+        <v>-0.5765</v>
       </c>
       <c t="n" r="G136">
-        <v>3.9935</v>
+        <v>4.1246</v>
+      </c>
+      <c t="n" r="H136">
+        <v>89.2554</v>
+      </c>
+      <c t="n" r="I136">
+        <v>58.4834</v>
       </c>
     </row>
     <row r="137">
       <c t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">ORX</t>
+          <t xml:space="preserve">OO1</t>
         </is>
       </c>
       <c t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C137">
-        <v>-0.0067</v>
+        <v>-0.6103</v>
       </c>
       <c t="n" r="D137">
-        <v>-0.7020</v>
+        <v>-2.3171</v>
       </c>
       <c t="n" r="E137">
-        <v>0.8875</v>
+        <v>-14.9031</v>
       </c>
       <c t="n" r="F137">
-        <v>-0.6362</v>
+        <v>-2.5598</v>
       </c>
       <c t="n" r="G137">
-        <v>3.9540</v>
-      </c>
-      <c t="n" r="H137">
-        <v>89.1418</v>
-      </c>
-      <c t="n" r="I137">
-        <v>58.3883</v>
+        <v>3.9937</v>
       </c>
     </row>
     <row r="138">
@@ -4312,22 +4312,22 @@
         </is>
       </c>
       <c t="n" r="C138">
-        <v>-0.2534</v>
+        <v>-0.2591</v>
       </c>
       <c t="n" r="D138">
-        <v>-0.8515</v>
+        <v>-0.8160</v>
       </c>
       <c t="n" r="E138">
-        <v>0.6743</v>
+        <v>0.6747</v>
       </c>
       <c t="n" r="F138">
-        <v>-0.9731</v>
+        <v>-0.9788</v>
       </c>
       <c t="n" r="G138">
-        <v>3.4695</v>
+        <v>3.4824</v>
       </c>
       <c t="n" r="H138">
-        <v>169.6079</v>
+        <v>169.5925</v>
       </c>
     </row>
     <row r="139">
@@ -4342,19 +4342,19 @@
         </is>
       </c>
       <c t="n" r="C139">
-        <v>-0.6837</v>
+        <v>-0.6898</v>
       </c>
       <c t="n" r="D139">
-        <v>-1.5296</v>
+        <v>-1.5348</v>
       </c>
       <c t="n" r="E139">
-        <v>100.5450</v>
+        <v>100.3370</v>
       </c>
       <c t="n" r="F139">
-        <v>-2.1179</v>
+        <v>-2.1238</v>
       </c>
       <c t="n" r="G139">
-        <v>3.3765</v>
+        <v>3.2553</v>
       </c>
     </row>
     <row r="140">
@@ -4369,22 +4369,22 @@
         </is>
       </c>
       <c t="n" r="C140">
-        <v>-0.0943</v>
+        <v>-0.0964</v>
       </c>
       <c t="n" r="D140">
-        <v>-0.2737</v>
+        <v>-0.2727</v>
       </c>
       <c t="n" r="E140">
-        <v>9.4862</v>
+        <v>9.4848</v>
       </c>
       <c t="n" r="F140">
-        <v>-0.3423</v>
+        <v>-0.3443</v>
       </c>
       <c t="n" r="G140">
-        <v>3.1531</v>
+        <v>3.1534</v>
       </c>
       <c t="n" r="H140">
-        <v>121.8628</v>
+        <v>121.8582</v>
       </c>
     </row>
     <row r="141">
@@ -4399,22 +4399,22 @@
         </is>
       </c>
       <c t="n" r="C141">
-        <v>-0.1882</v>
+        <v>-0.1860</v>
       </c>
       <c t="n" r="D141">
-        <v>-0.4236</v>
+        <v>-0.4162</v>
       </c>
       <c t="n" r="E141">
-        <v>16.4452</v>
+        <v>16.4472</v>
       </c>
       <c t="n" r="F141">
-        <v>-0.5865</v>
+        <v>-0.5843</v>
       </c>
       <c t="n" r="G141">
-        <v>2.9929</v>
+        <v>2.9951</v>
       </c>
       <c t="n" r="H141">
-        <v>266.7169</v>
+        <v>266.7247</v>
       </c>
     </row>
     <row r="142">
@@ -4429,22 +4429,22 @@
         </is>
       </c>
       <c t="n" r="C142">
-        <v>1.1196</v>
+        <v>1.1450</v>
       </c>
       <c t="n" r="D142">
-        <v>0.1492</v>
+        <v>1.0248</v>
       </c>
       <c t="n" r="E142">
-        <v>4.9859</v>
+        <v>5.0034</v>
       </c>
       <c t="n" r="F142">
-        <v>-0.7529</v>
+        <v>-0.7280</v>
       </c>
       <c t="n" r="G142">
-        <v>2.8819</v>
+        <v>2.8749</v>
       </c>
       <c t="n" r="H142">
-        <v>265.9642</v>
+        <v>266.0562</v>
       </c>
     </row>
     <row r="143">
@@ -4459,19 +4459,19 @@
         </is>
       </c>
       <c t="n" r="C143">
-        <v>0.6606</v>
+        <v>0.6625</v>
       </c>
       <c t="n" r="D143">
-        <v>-1.9155</v>
+        <v>-1.9165</v>
       </c>
       <c t="n" r="E143">
-        <v>1.9000</v>
+        <v>1.9015</v>
       </c>
       <c t="n" r="F143">
-        <v>-1.2025</v>
+        <v>-1.2007</v>
       </c>
       <c t="n" r="G143">
-        <v>2.5327</v>
+        <v>2.5358</v>
       </c>
     </row>
     <row r="144">
@@ -4486,22 +4486,22 @@
         </is>
       </c>
       <c t="n" r="C144">
-        <v>-0.0079</v>
+        <v>-0.0082</v>
       </c>
       <c t="n" r="D144">
-        <v>-0.3706</v>
+        <v>-0.3223</v>
       </c>
       <c t="n" r="E144">
-        <v>7.8591</v>
+        <v>7.8596</v>
       </c>
       <c t="n" r="F144">
-        <v>-0.3738</v>
+        <v>-0.3740</v>
       </c>
       <c t="n" r="G144">
-        <v>2.2653</v>
+        <v>2.2608</v>
       </c>
       <c t="n" r="H144">
-        <v>131.0070</v>
+        <v>131.0065</v>
       </c>
     </row>
     <row r="145">
@@ -4516,19 +4516,19 @@
         </is>
       </c>
       <c t="n" r="C145">
-        <v>-1.9891</v>
+        <v>-1.9881</v>
       </c>
       <c t="n" r="D145">
-        <v>-1.5848</v>
+        <v>-1.6828</v>
       </c>
       <c t="n" r="E145">
-        <v>3.6843</v>
+        <v>3.6848</v>
       </c>
       <c t="n" r="F145">
-        <v>-1.5803</v>
+        <v>-1.5793</v>
       </c>
       <c t="n" r="G145">
-        <v>1.0925</v>
+        <v>1.0922</v>
       </c>
     </row>
     <row r="146">
@@ -4543,61 +4543,61 @@
         </is>
       </c>
       <c t="n" r="C146">
-        <v>-0.1324</v>
+        <v>-0.1292</v>
       </c>
       <c t="n" r="D146">
-        <v>-1.7581</v>
+        <v>-1.7591</v>
       </c>
       <c t="n" r="E146">
-        <v>2.1513</v>
+        <v>2.1545</v>
       </c>
       <c t="n" r="F146">
-        <v>-1.6391</v>
+        <v>-1.6360</v>
       </c>
       <c t="n" r="G146">
-        <v>1.0259</v>
+        <v>1.0379</v>
       </c>
       <c t="n" r="H146">
-        <v>70.5197</v>
+        <v>70.5251</v>
       </c>
     </row>
     <row r="147">
       <c t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">BKA</t>
+          <t xml:space="preserve">RF3</t>
         </is>
       </c>
       <c t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ANKA GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C147">
+        <v>-0.1405</v>
       </c>
       <c t="n" r="D147">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="E147">
-        <v>0.0000</v>
+        <v>-0.6473</v>
       </c>
       <c t="n" r="F147">
-        <v>0.0000</v>
+        <v>-0.8817</v>
       </c>
       <c t="n" r="G147">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="H147">
-        <v>0.0000</v>
+        <v>0.1342</v>
       </c>
     </row>
     <row r="148">
       <c t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">HP5</t>
+          <t xml:space="preserve">BKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ANKA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="D148">
+        <v>0.0000</v>
       </c>
       <c t="n" r="E148">
         <v>0.0000</v>
@@ -4608,16 +4608,19 @@
       <c t="n" r="G148">
         <v>0.0000</v>
       </c>
+      <c t="n" r="H148">
+        <v>0.0000</v>
+      </c>
     </row>
     <row r="149">
       <c t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">HP4</t>
+          <t xml:space="preserve">HP5</t>
         </is>
       </c>
       <c t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ MASTERTÜRK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="E149">
@@ -4633,19 +4636,13 @@
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">NGA</t>
+          <t xml:space="preserve">HP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C150">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="D150">
-        <v>0.0000</v>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ MASTERTÜRK GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="E150">
         <v>0.0000</v>
@@ -4660,13 +4657,16 @@
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">NFA</t>
+          <t xml:space="preserve">NGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C151">
+        <v>0.0000</v>
       </c>
       <c t="n" r="D151">
         <v>0.0000</v>
@@ -4684,12 +4684,12 @@
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">RF1</t>
+          <t xml:space="preserve">NFA</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D152">
@@ -4708,13 +4708,22 @@
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">RDO</t>
+          <t xml:space="preserve">RF1</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN OTEL GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="D153">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="E153">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="F153">
+        <v>0.0000</v>
       </c>
       <c t="n" r="G153">
         <v>0.0000</v>
@@ -4723,12 +4732,12 @@
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">RMK</t>
+          <t xml:space="preserve">RDO</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EMLAK KATILIM YENİ EVİM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN OTEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G154">
@@ -4738,12 +4747,12 @@
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">RF2</t>
+          <t xml:space="preserve">RMK</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EMLAK KATILIM YENİ EVİM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G155">
@@ -4753,12 +4762,12 @@
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">RSM</t>
+          <t xml:space="preserve">RF2</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SMART PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G156">
@@ -4768,12 +4777,12 @@
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">RSO</t>
+          <t xml:space="preserve">RSM</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SONNE PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SMART PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G157">
@@ -4783,12 +4792,12 @@
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">RTO</t>
+          <t xml:space="preserve">RSO</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TOROS PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SONNE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G158">
@@ -4798,12 +4807,12 @@
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">RGN</t>
+          <t xml:space="preserve">RTO</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TOROS PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G159">
@@ -4813,25 +4822,16 @@
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">RF3</t>
+          <t xml:space="preserve">RGN</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C160">
-        <v>-0.1365</v>
-      </c>
-      <c t="n" r="D160">
-        <v>-0.6466</v>
-      </c>
-      <c t="n" r="F160">
-        <v>-0.8777</v>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="G160">
-        <v>-0.4032</v>
+        <v>0.0000</v>
       </c>
     </row>
     <row r="161">
@@ -4846,25 +4846,25 @@
         </is>
       </c>
       <c t="n" r="C161">
-        <v>2.1761</v>
+        <v>2.1741</v>
       </c>
       <c t="n" r="D161">
-        <v>8.7817</v>
+        <v>8.7683</v>
       </c>
       <c t="n" r="E161">
-        <v>17.3563</v>
+        <v>17.3419</v>
       </c>
       <c t="n" r="F161">
-        <v>8.9363</v>
+        <v>8.9341</v>
       </c>
       <c t="n" r="G161">
-        <v>-0.5654</v>
+        <v>-0.5687</v>
       </c>
       <c t="n" r="H161">
-        <v>153.0514</v>
+        <v>153.0464</v>
       </c>
       <c t="n" r="I161">
-        <v>495.9045</v>
+        <v>495.8967</v>
       </c>
     </row>
     <row r="162">
@@ -4879,19 +4879,19 @@
         </is>
       </c>
       <c t="n" r="C162">
-        <v>-0.2583</v>
+        <v>-0.2672</v>
       </c>
       <c t="n" r="D162">
-        <v>-0.7645</v>
+        <v>-0.7660</v>
       </c>
       <c t="n" r="E162">
-        <v>-0.2625</v>
+        <v>-0.2641</v>
       </c>
       <c t="n" r="F162">
-        <v>-0.8541</v>
+        <v>-0.8629</v>
       </c>
       <c t="n" r="G162">
-        <v>-1.5858</v>
+        <v>-1.5876</v>
       </c>
     </row>
     <row r="163">
@@ -4906,22 +4906,22 @@
         </is>
       </c>
       <c t="n" r="C163">
-        <v>8.7644</v>
+        <v>8.9334</v>
       </c>
       <c t="n" r="D163">
-        <v>9.1403</v>
+        <v>8.9413</v>
       </c>
       <c t="n" r="E163">
-        <v>3.4521</v>
+        <v>3.6057</v>
       </c>
       <c t="n" r="F163">
-        <v>7.4955</v>
+        <v>7.6625</v>
       </c>
       <c t="n" r="G163">
-        <v>-5.2960</v>
+        <v>-5.2463</v>
       </c>
       <c t="n" r="H163">
-        <v>99.1849</v>
+        <v>99.4944</v>
       </c>
     </row>
     <row r="164">
@@ -4936,19 +4936,19 @@
         </is>
       </c>
       <c t="n" r="C164">
-        <v>-2.2540</v>
+        <v>-2.2598</v>
       </c>
       <c t="n" r="D164">
-        <v>-10.0888</v>
+        <v>-10.0843</v>
       </c>
       <c t="n" r="E164">
-        <v>-11.8505</v>
+        <v>-11.8526</v>
       </c>
       <c t="n" r="F164">
-        <v>-10.2459</v>
+        <v>-10.2513</v>
       </c>
       <c t="n" r="G164">
-        <v>-7.4618</v>
+        <v>-7.4642</v>
       </c>
     </row>
     <row r="165">
@@ -4963,19 +4963,19 @@
         </is>
       </c>
       <c t="n" r="C165">
-        <v>0.3866</v>
+        <v>0.3872</v>
       </c>
       <c t="n" r="D165">
-        <v>-0.5683</v>
+        <v>-0.5688</v>
       </c>
       <c t="n" r="E165">
-        <v>2.4273</v>
+        <v>2.4281</v>
       </c>
       <c t="n" r="F165">
-        <v>-0.2967</v>
+        <v>-0.2961</v>
       </c>
       <c t="n" r="G165">
-        <v>-11.4602</v>
+        <v>-11.4589</v>
       </c>
     </row>
     <row r="166">
@@ -4990,19 +4990,19 @@
         </is>
       </c>
       <c t="n" r="C166">
-        <v>0.1897</v>
+        <v>0.1969</v>
       </c>
       <c t="n" r="D166">
-        <v>4.2860</v>
+        <v>4.3477</v>
       </c>
       <c t="n" r="E166">
-        <v>4.7670</v>
+        <v>4.7756</v>
       </c>
       <c t="n" r="F166">
-        <v>4.0814</v>
+        <v>4.0889</v>
       </c>
       <c t="n" r="G166">
-        <v>-13.4158</v>
+        <v>-13.3993</v>
       </c>
     </row>
     <row r="167">
@@ -5017,22 +5017,22 @@
         </is>
       </c>
       <c t="n" r="C167">
-        <v>-0.0360</v>
+        <v>-0.0368</v>
       </c>
       <c t="n" r="D167">
-        <v>-0.1083</v>
+        <v>-0.1085</v>
       </c>
       <c t="n" r="E167">
-        <v>-17.3196</v>
+        <v>-17.3159</v>
       </c>
       <c t="n" r="F167">
-        <v>-0.1304</v>
+        <v>-0.1313</v>
       </c>
       <c t="n" r="G167">
-        <v>-13.9668</v>
+        <v>-13.9672</v>
       </c>
       <c t="n" r="H167">
-        <v>196.4797</v>
+        <v>196.4771</v>
       </c>
     </row>
     <row r="168">
@@ -5047,292 +5047,292 @@
         </is>
       </c>
       <c t="n" r="C168">
-        <v>-0.5609</v>
+        <v>-0.5729</v>
       </c>
       <c t="n" r="D168">
-        <v>-1.5655</v>
+        <v>-1.5635</v>
       </c>
       <c t="n" r="E168">
-        <v>-17.3547</v>
+        <v>-17.3543</v>
       </c>
       <c t="n" r="F168">
-        <v>-1.7555</v>
+        <v>-1.7673</v>
       </c>
       <c t="n" r="G168">
-        <v>-18.5329</v>
+        <v>-18.5116</v>
       </c>
       <c t="n" r="H168">
-        <v>-2.9706</v>
+        <v>-2.9822</v>
       </c>
     </row>
     <row r="169">
       <c t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">YG3</t>
+          <t xml:space="preserve">RG8</t>
         </is>
       </c>
       <c t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. MERİÇ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C169">
-        <v>-0.2961</v>
+        <v>0.1627</v>
       </c>
       <c t="n" r="D169">
-        <v>-0.8455</v>
+        <v>-0.5614</v>
       </c>
       <c t="n" r="E169">
-        <v>-23.3503</v>
+        <v>-17.8953</v>
       </c>
       <c t="n" r="F169">
-        <v>-0.9591</v>
+        <v>-0.0319</v>
       </c>
       <c t="n" r="G169">
-        <v>-24.4787</v>
+        <v>-18.7478</v>
       </c>
       <c t="n" r="H169">
-        <v>350.3201</v>
+        <v>91.4276</v>
       </c>
     </row>
     <row r="170">
       <c t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">REO</t>
+          <t xml:space="preserve">YG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C170">
-        <v>-0.0160</v>
+        <v>-0.3034</v>
       </c>
       <c t="n" r="D170">
-        <v>-0.0526</v>
+        <v>-0.8456</v>
       </c>
       <c t="n" r="E170">
-        <v>-0.0857</v>
+        <v>-23.3505</v>
       </c>
       <c t="n" r="F170">
-        <v>-0.0611</v>
+        <v>-0.9664</v>
       </c>
       <c t="n" r="G170">
-        <v>-24.5123</v>
+        <v>-24.4673</v>
+      </c>
+      <c t="n" r="H170">
+        <v>350.2869</v>
       </c>
     </row>
     <row r="171">
       <c t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">AZ7</t>
+          <t xml:space="preserve">REO</t>
         </is>
       </c>
       <c t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C171">
-        <v>-0.0799</v>
+        <v>-0.0160</v>
       </c>
       <c t="n" r="D171">
-        <v>-0.2706</v>
+        <v>-0.0526</v>
       </c>
       <c t="n" r="E171">
-        <v>-50.6351</v>
+        <v>-0.0857</v>
       </c>
       <c t="n" r="F171">
-        <v>-1.0427</v>
+        <v>-0.0611</v>
       </c>
       <c t="n" r="G171">
-        <v>-30.3407</v>
-      </c>
-      <c t="n" r="H171">
-        <v>71.0477</v>
-      </c>
-      <c t="n" r="I171">
-        <v>785.2236</v>
+        <v>-24.5056</v>
       </c>
     </row>
     <row r="172">
       <c t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">YG5</t>
+          <t xml:space="preserve">AZ7</t>
         </is>
       </c>
       <c t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FULYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C172">
-        <v>-0.6669</v>
+        <v>-0.0806</v>
       </c>
       <c t="n" r="D172">
-        <v>-1.7460</v>
+        <v>-0.2705</v>
       </c>
       <c t="n" r="E172">
-        <v>-30.4542</v>
+        <v>-50.6662</v>
       </c>
       <c t="n" r="F172">
-        <v>-1.9029</v>
+        <v>-1.0433</v>
       </c>
       <c t="n" r="G172">
-        <v>-30.8345</v>
+        <v>-30.3288</v>
       </c>
       <c t="n" r="H172">
-        <v>102.9685</v>
+        <v>71.0466</v>
+      </c>
+      <c t="n" r="I172">
+        <v>785.2178</v>
       </c>
     </row>
     <row r="173">
       <c t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">RG8</t>
+          <t xml:space="preserve">YG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. MERİÇ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FULYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C173">
-        <v>0.1793</v>
+        <v>-0.6801</v>
       </c>
       <c t="n" r="D173">
-        <v>-0.5372</v>
+        <v>-1.7494</v>
       </c>
       <c t="n" r="E173">
-        <v>-17.8833</v>
+        <v>-30.4553</v>
       </c>
       <c t="n" r="F173">
-        <v>-0.0154</v>
+        <v>-1.9159</v>
       </c>
       <c t="n" r="G173">
-        <v>-40.4956</v>
+        <v>-30.8144</v>
       </c>
       <c t="n" r="H173">
-        <v>91.4592</v>
+        <v>102.9416</v>
       </c>
     </row>
     <row r="174">
       <c t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">NG3</t>
+          <t xml:space="preserve">NGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C174">
-        <v>-0.2029</v>
+        <v>3.2132</v>
       </c>
       <c t="n" r="D174">
-        <v>-3.4713</v>
+        <v>10.5198</v>
       </c>
       <c t="n" r="E174">
-        <v>5.0972</v>
+        <v>15.7405</v>
       </c>
       <c t="n" r="F174">
-        <v>-7.3278</v>
+        <v>11.9144</v>
       </c>
       <c t="n" r="G174">
-        <v>-40.9147</v>
-      </c>
-      <c t="n" r="H174">
-        <v>113.6834</v>
+        <v>-33.3142</v>
       </c>
     </row>
     <row r="175">
       <c t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">UG2</t>
+          <t xml:space="preserve">NG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">ÜNLÜ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C175">
-        <v>-0.4457</v>
+        <v>-0.2068</v>
       </c>
       <c t="n" r="D175">
-        <v>-18.4531</v>
+        <v>-3.4717</v>
       </c>
       <c t="n" r="E175">
-        <v>-40.7955</v>
+        <v>5.0948</v>
       </c>
       <c t="n" r="F175">
-        <v>-52.0240</v>
+        <v>-7.3314</v>
       </c>
       <c t="n" r="G175">
-        <v>-41.7118</v>
+        <v>-40.9102</v>
       </c>
       <c t="n" r="H175">
-        <v>-2.7176</v>
-      </c>
-      <c t="n" r="I175">
-        <v>217.4015</v>
+        <v>113.6751</v>
       </c>
     </row>
     <row r="176">
       <c t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">NH3</t>
+          <t xml:space="preserve">UG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY  YÖNETİMİ A.Ş TÜRKAZ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ÜNLÜ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C176">
-        <v>-4.1269</v>
+        <v>-0.4437</v>
       </c>
       <c t="n" r="D176">
-        <v>-23.7561</v>
+        <v>-18.4724</v>
       </c>
       <c t="n" r="E176">
-        <v>-21.1829</v>
+        <v>-40.7932</v>
       </c>
       <c t="n" r="F176">
-        <v>-26.0828</v>
+        <v>-52.0230</v>
       </c>
       <c t="n" r="G176">
-        <v>-43.1308</v>
+        <v>-41.7097</v>
       </c>
       <c t="n" r="H176">
-        <v>40.5794</v>
+        <v>-2.7156</v>
+      </c>
+      <c t="n" r="I176">
+        <v>217.4079</v>
       </c>
     </row>
     <row r="177">
       <c t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">NGO</t>
+          <t xml:space="preserve">NH3</t>
         </is>
       </c>
       <c t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY  YÖNETİMİ A.Ş TÜRKAZ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C177">
-        <v>3.1090</v>
+        <v>-4.1287</v>
       </c>
       <c t="n" r="D177">
-        <v>13.0128</v>
+        <v>-23.7561</v>
       </c>
       <c t="n" r="E177">
-        <v>15.7960</v>
+        <v>-23.0512</v>
       </c>
       <c t="n" r="F177">
-        <v>11.8015</v>
+        <v>-26.0841</v>
       </c>
       <c t="n" r="G177">
-        <v>-43.6593</v>
+        <v>-43.1306</v>
+      </c>
+      <c t="n" r="H177">
+        <v>40.5768</v>
       </c>
     </row>
     <row r="178">
@@ -5347,19 +5347,19 @@
         </is>
       </c>
       <c t="n" r="C178">
-        <v>-82.7493</v>
+        <v>-82.7622</v>
       </c>
       <c t="n" r="D178">
-        <v>-83.9147</v>
+        <v>-83.9256</v>
       </c>
       <c t="n" r="E178">
-        <v>-76.2513</v>
+        <v>-76.2674</v>
       </c>
       <c t="n" r="F178">
-        <v>-83.9307</v>
+        <v>-83.9428</v>
       </c>
       <c t="n" r="G178">
-        <v>-55.7174</v>
+        <v>-55.5259</v>
       </c>
     </row>
     <row r="179">
@@ -5374,25 +5374,25 @@
         </is>
       </c>
       <c t="n" r="C179">
-        <v>2.8397</v>
+        <v>3.4918</v>
       </c>
       <c t="n" r="D179">
-        <v>6.5514</v>
+        <v>7.2202</v>
       </c>
       <c t="n" r="E179">
-        <v>-10.0383</v>
+        <v>-9.8764</v>
       </c>
       <c t="n" r="F179">
-        <v>-13.8495</v>
+        <v>-13.3033</v>
       </c>
       <c t="n" r="G179">
-        <v>-59.4409</v>
+        <v>-59.1857</v>
       </c>
       <c t="n" r="H179">
-        <v>-20.9417</v>
+        <v>-20.4404</v>
       </c>
       <c t="n" r="I179">
-        <v>330.1898</v>
+        <v>332.8853</v>
       </c>
     </row>
     <row r="180">
@@ -5407,19 +5407,19 @@
         </is>
       </c>
       <c t="n" r="C180">
-        <v>-14.7392</v>
+        <v>-14.9060</v>
       </c>
       <c t="n" r="D180">
-        <v>-30.2450</v>
+        <v>-30.3810</v>
       </c>
       <c t="n" r="E180">
-        <v>455.3639</v>
+        <v>468.4551</v>
       </c>
       <c t="n" r="F180">
-        <v>-30.2617</v>
+        <v>-30.3981</v>
       </c>
       <c t="n" r="G180">
-        <v>-63.4704</v>
+        <v>-63.2657</v>
       </c>
     </row>
     <row r="181">
@@ -5434,25 +5434,25 @@
         </is>
       </c>
       <c t="n" r="C181">
-        <v>-22.8052</v>
+        <v>-22.4190</v>
       </c>
       <c t="n" r="D181">
-        <v>-77.0899</v>
+        <v>-76.9723</v>
       </c>
       <c t="n" r="E181">
-        <v>-75.9150</v>
+        <v>-75.7922</v>
       </c>
       <c t="n" r="F181">
-        <v>-77.1268</v>
+        <v>-77.0124</v>
       </c>
       <c t="n" r="G181">
-        <v>-67.5249</v>
+        <v>-67.3198</v>
       </c>
       <c t="n" r="H181">
-        <v>-84.9749</v>
+        <v>-84.8997</v>
       </c>
       <c t="n" r="I181">
-        <v>-45.1150</v>
+        <v>-44.8404</v>
       </c>
     </row>
     <row r="182">
@@ -5467,25 +5467,25 @@
         </is>
       </c>
       <c t="n" r="C182">
-        <v>-2.7621</v>
+        <v>-2.7671</v>
       </c>
       <c t="n" r="D182">
-        <v>11.8139</v>
+        <v>11.7026</v>
       </c>
       <c t="n" r="E182">
-        <v>-65.5597</v>
+        <v>-65.5242</v>
       </c>
       <c t="n" r="F182">
-        <v>55.1400</v>
+        <v>55.1320</v>
       </c>
       <c t="n" r="G182">
-        <v>-67.5942</v>
+        <v>-67.6024</v>
       </c>
       <c t="n" r="H182">
-        <v>-68.8743</v>
+        <v>-68.8759</v>
       </c>
       <c t="n" r="I182">
-        <v>-16.2808</v>
+        <v>-16.2882</v>
       </c>
     </row>
     <row r="183">
@@ -5512,7 +5512,7 @@
         <v>-93.9130</v>
       </c>
       <c t="n" r="G183">
-        <v>-98.9811</v>
+        <v>-99.0291</v>
       </c>
       <c t="n" r="H183">
         <v>-99.9998</v>
@@ -5530,22 +5530,22 @@
         </is>
       </c>
       <c t="n" r="C184">
-        <v>-98.9063</v>
+        <v>-98.9142</v>
       </c>
       <c t="n" r="D184">
-        <v>-99.1386</v>
+        <v>-99.1449</v>
       </c>
       <c t="n" r="E184">
-        <v>-99.0855</v>
+        <v>-99.0921</v>
       </c>
       <c t="n" r="F184">
-        <v>-99.1462</v>
+        <v>-99.1524</v>
       </c>
       <c t="n" r="G184">
-        <v>-99.1814</v>
+        <v>-99.1872</v>
       </c>
       <c t="n" r="H184">
-        <v>-98.6004</v>
+        <v>-98.6105</v>
       </c>
     </row>
     <row r="185">
@@ -5608,13 +5608,13 @@
         </is>
       </c>
       <c t="n" r="C189">
-        <v>1.1611</v>
+        <v>1.2398</v>
       </c>
       <c t="n" r="D189">
-        <v>3.0983</v>
+        <v>3.1675</v>
       </c>
       <c t="n" r="F189">
-        <v>3.7960</v>
+        <v>3.8767</v>
       </c>
     </row>
     <row r="190">
@@ -5653,13 +5653,13 @@
         </is>
       </c>
       <c t="n" r="C192">
-        <v>-16.9701</v>
+        <v>-17.5524</v>
       </c>
       <c t="n" r="D192">
-        <v>-38.3130</v>
+        <v>-38.5014</v>
       </c>
       <c t="n" r="F192">
-        <v>-41.1190</v>
+        <v>-41.5320</v>
       </c>
     </row>
     <row r="193">
@@ -5674,13 +5674,13 @@
         </is>
       </c>
       <c t="n" r="C193">
-        <v>-10.0726</v>
+        <v>-9.9212</v>
       </c>
       <c t="n" r="D193">
-        <v>-63.1112</v>
+        <v>-63.1041</v>
       </c>
       <c t="n" r="F193">
-        <v>-28.4110</v>
+        <v>-28.2905</v>
       </c>
     </row>
     <row r="194">
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c t="n" r="C195">
-        <v>1.1444</v>
+        <v>1.1425</v>
       </c>
     </row>
     <row r="196">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c t="n" r="C196">
-        <v>0.8297</v>
+        <v>0.8292</v>
       </c>
       <c t="n" r="D196">
-        <v>1.4820</v>
+        <v>1.4821</v>
       </c>
       <c t="n" r="F196">
-        <v>1.8868</v>
+        <v>1.8863</v>
       </c>
     </row>
     <row r="197">
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c t="n" r="C203">
-        <v>1.4880</v>
+        <v>1.5370</v>
       </c>
       <c t="n" r="D203">
-        <v>2.1132</v>
+        <v>2.3321</v>
       </c>
     </row>
     <row r="204">
@@ -5833,16 +5833,16 @@
         </is>
       </c>
       <c t="n" r="C204">
-        <v>1.8628</v>
+        <v>1.9543</v>
       </c>
       <c t="n" r="D204">
-        <v>418.9450</v>
+        <v>418.3609</v>
       </c>
       <c t="n" r="E204">
-        <v>460.7399</v>
+        <v>460.7230</v>
       </c>
       <c t="n" r="F204">
-        <v>424.5459</v>
+        <v>425.0171</v>
       </c>
     </row>
     <row r="205">
@@ -5857,16 +5857,16 @@
         </is>
       </c>
       <c t="n" r="C205">
-        <v>12.1116</v>
+        <v>12.1159</v>
       </c>
       <c t="n" r="D205">
-        <v>44.4641</v>
+        <v>44.3261</v>
       </c>
       <c t="n" r="E205">
-        <v>59.0411</v>
+        <v>58.8701</v>
       </c>
       <c t="n" r="F205">
-        <v>46.4899</v>
+        <v>46.4956</v>
       </c>
     </row>
     <row r="206">
@@ -5893,16 +5893,16 @@
         </is>
       </c>
       <c t="n" r="C207">
-        <v>-0.0461</v>
+        <v>-0.0472</v>
       </c>
       <c t="n" r="D207">
-        <v>-0.1100</v>
+        <v>-0.1101</v>
       </c>
       <c t="n" r="E207">
-        <v>19.3977</v>
+        <v>19.3949</v>
       </c>
       <c t="n" r="F207">
-        <v>-0.1376</v>
+        <v>-0.1386</v>
       </c>
     </row>
     <row r="208">
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c t="n" r="C208">
-        <v>-0.0186</v>
+        <v>-0.0155</v>
       </c>
     </row>
     <row r="209">
@@ -5944,16 +5944,16 @@
         </is>
       </c>
       <c t="n" r="C210">
-        <v>3.2544</v>
+        <v>3.3780</v>
       </c>
       <c t="n" r="D210">
-        <v>9.0593</v>
+        <v>9.0812</v>
       </c>
       <c t="n" r="E210">
-        <v>19.5462</v>
+        <v>19.5666</v>
       </c>
       <c t="n" r="F210">
-        <v>10.6007</v>
+        <v>10.7331</v>
       </c>
     </row>
     <row r="211">
@@ -5980,13 +5980,13 @@
         </is>
       </c>
       <c t="n" r="C212">
-        <v>-0.1081</v>
+        <v>-0.1080</v>
       </c>
       <c t="n" r="D212">
-        <v>-0.3217</v>
+        <v>-0.3216</v>
       </c>
       <c t="n" r="F212">
-        <v>-0.3296</v>
+        <v>-0.3295</v>
       </c>
     </row>
     <row r="213">
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c t="n" r="C213">
-        <v>-0.9368</v>
+        <v>-0.9670</v>
       </c>
       <c t="n" r="D213">
-        <v>6.7243</v>
+        <v>6.7217</v>
       </c>
     </row>
     <row r="214">
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c t="n" r="C214">
-        <v>-0.1307</v>
+        <v>-0.0853</v>
       </c>
     </row>
     <row r="215">
@@ -6034,16 +6034,16 @@
         </is>
       </c>
       <c t="n" r="C215">
-        <v>-0.0360</v>
+        <v>-0.0371</v>
       </c>
       <c t="n" r="D215">
-        <v>-0.0990</v>
+        <v>-0.0991</v>
       </c>
       <c t="n" r="E215">
-        <v>12.7747</v>
+        <v>12.7802</v>
       </c>
       <c t="n" r="F215">
-        <v>-0.1140</v>
+        <v>-0.1150</v>
       </c>
     </row>
     <row r="216">
@@ -6058,16 +6058,16 @@
         </is>
       </c>
       <c t="n" r="C216">
-        <v>0.7992</v>
+        <v>0.7985</v>
       </c>
       <c t="n" r="D216">
-        <v>3.1140</v>
+        <v>2.7869</v>
       </c>
       <c t="n" r="E216">
-        <v>12.5299</v>
+        <v>12.5284</v>
       </c>
       <c t="n" r="F216">
-        <v>3.1065</v>
+        <v>3.1058</v>
       </c>
     </row>
     <row r="217">
@@ -6082,16 +6082,16 @@
         </is>
       </c>
       <c t="n" r="C217">
-        <v>-87.9737</v>
+        <v>-89.4236</v>
       </c>
       <c t="n" r="D217">
-        <v>-99.8766</v>
+        <v>-99.8918</v>
       </c>
       <c t="n" r="E217">
-        <v>-99.9897</v>
+        <v>-99.9903</v>
       </c>
       <c t="n" r="F217">
-        <v>-99.9796</v>
+        <v>-99.9820</v>
       </c>
     </row>
     <row r="218">
@@ -6130,16 +6130,16 @@
         </is>
       </c>
       <c t="n" r="C220">
-        <v>0.3803</v>
+        <v>0.1076</v>
       </c>
       <c t="n" r="D220">
-        <v>0.4005</v>
+        <v>0.1167</v>
       </c>
       <c t="n" r="E220">
-        <v>36.6576</v>
+        <v>36.2613</v>
       </c>
       <c t="n" r="F220">
-        <v>0.5531</v>
+        <v>0.2800</v>
       </c>
     </row>
     <row r="221">
@@ -6238,16 +6238,16 @@
         </is>
       </c>
       <c t="n" r="C228">
-        <v>5.5784</v>
+        <v>5.6357</v>
       </c>
       <c t="n" r="D228">
-        <v>7.9254</v>
+        <v>5.7304</v>
       </c>
       <c t="n" r="E228">
-        <v>16.4845</v>
+        <v>16.4523</v>
       </c>
       <c t="n" r="F228">
-        <v>11.3188</v>
+        <v>11.3792</v>
       </c>
     </row>
     <row r="229">
@@ -6286,16 +6286,16 @@
         </is>
       </c>
       <c t="n" r="C231">
-        <v>0.9522</v>
+        <v>1.1740</v>
       </c>
       <c t="n" r="D231">
-        <v>4.9498</v>
+        <v>5.1042</v>
       </c>
       <c t="n" r="E231">
-        <v>13.6359</v>
+        <v>13.7796</v>
       </c>
       <c t="n" r="F231">
-        <v>6.3613</v>
+        <v>6.5950</v>
       </c>
     </row>
     <row r="232">
@@ -6310,16 +6310,16 @@
         </is>
       </c>
       <c t="n" r="C232">
-        <v>3.1368</v>
+        <v>3.2553</v>
       </c>
       <c t="n" r="D232">
-        <v>9.5185</v>
+        <v>9.5332</v>
       </c>
       <c t="n" r="E232">
-        <v>20.6639</v>
+        <v>20.6839</v>
       </c>
       <c t="n" r="F232">
-        <v>10.9878</v>
+        <v>11.1153</v>
       </c>
     </row>
     <row r="233">
@@ -6334,16 +6334,16 @@
         </is>
       </c>
       <c t="n" r="C233">
-        <v>0.7604</v>
+        <v>0.9775</v>
       </c>
       <c t="n" r="D233">
-        <v>1.2630</v>
+        <v>1.4492</v>
       </c>
       <c t="n" r="E233">
-        <v>3.9331</v>
+        <v>4.1955</v>
       </c>
       <c t="n" r="F233">
-        <v>1.7634</v>
+        <v>1.9827</v>
       </c>
     </row>
     <row r="234">
@@ -6370,16 +6370,16 @@
         </is>
       </c>
       <c t="n" r="C235">
-        <v>1.0394</v>
+        <v>1.2613</v>
       </c>
       <c t="n" r="D235">
-        <v>5.0406</v>
+        <v>5.1949</v>
       </c>
       <c t="n" r="E235">
-        <v>13.7342</v>
+        <v>13.8778</v>
       </c>
       <c t="n" r="F235">
-        <v>6.4532</v>
+        <v>6.6870</v>
       </c>
     </row>
     <row r="236">
@@ -6430,13 +6430,13 @@
         </is>
       </c>
       <c t="n" r="C239">
-        <v>-1.8580</v>
+        <v>-1.8714</v>
       </c>
       <c t="n" r="D239">
-        <v>-82.0821</v>
+        <v>-81.8401</v>
       </c>
       <c t="n" r="F239">
-        <v>-84.7294</v>
+        <v>-84.7315</v>
       </c>
     </row>
     <row r="240">
@@ -6475,16 +6475,16 @@
         </is>
       </c>
       <c t="n" r="C242">
-        <v>-0.0517</v>
+        <v>-0.0533</v>
       </c>
       <c t="n" r="D242">
-        <v>-0.1439</v>
+        <v>-0.1435</v>
       </c>
       <c t="n" r="E242">
         <v>30.4730</v>
       </c>
       <c t="n" r="F242">
-        <v>-0.1684</v>
+        <v>-0.1700</v>
       </c>
     </row>
     <row r="243">
@@ -6499,16 +6499,16 @@
         </is>
       </c>
       <c t="n" r="C243">
-        <v>-0.0740</v>
+        <v>-0.0761</v>
       </c>
       <c t="n" r="D243">
-        <v>-0.2368</v>
+        <v>-0.2365</v>
       </c>
       <c t="n" r="E243">
-        <v>1624.8544</v>
+        <v>1624.7756</v>
       </c>
       <c t="n" r="F243">
-        <v>-0.2614</v>
+        <v>-0.2635</v>
       </c>
     </row>
     <row r="244">
@@ -6559,13 +6559,13 @@
         </is>
       </c>
       <c t="n" r="C247">
-        <v>-5.5249</v>
+        <v>-5.7159</v>
       </c>
       <c t="n" r="D247">
-        <v>-15.2772</v>
+        <v>-15.3085</v>
       </c>
       <c t="n" r="F247">
-        <v>-16.8203</v>
+        <v>-16.9884</v>
       </c>
     </row>
     <row r="248">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c t="n" r="C248">
-        <v>-5.8945</v>
+        <v>-6.0310</v>
       </c>
       <c t="n" r="D248">
-        <v>-15.7472</v>
+        <v>-15.7450</v>
       </c>
       <c t="n" r="E248">
-        <v>-23.9768</v>
+        <v>-24.1657</v>
       </c>
       <c t="n" r="F248">
-        <v>-17.1542</v>
+        <v>-17.2743</v>
       </c>
     </row>
     <row r="249">
@@ -6688,16 +6688,16 @@
         </is>
       </c>
       <c t="n" r="C256">
-        <v>-87.0180</v>
+        <v>-87.0401</v>
       </c>
       <c t="n" r="D256">
-        <v>-88.4845</v>
+        <v>-88.5033</v>
       </c>
       <c t="n" r="E256">
-        <v>-74.9807</v>
+        <v>-75.0215</v>
       </c>
       <c t="n" r="F256">
-        <v>-88.4955</v>
+        <v>-88.5151</v>
       </c>
     </row>
     <row r="257">
@@ -6712,13 +6712,13 @@
         </is>
       </c>
       <c t="n" r="C257">
-        <v>-1.4537</v>
+        <v>-1.5023</v>
       </c>
       <c t="n" r="D257">
-        <v>-13.1964</v>
+        <v>-13.2332</v>
       </c>
       <c t="n" r="F257">
-        <v>-13.2843</v>
+        <v>-13.3271</v>
       </c>
     </row>
     <row r="258">
@@ -6733,16 +6733,16 @@
         </is>
       </c>
       <c t="n" r="C258">
-        <v>-5.9369</v>
+        <v>-5.9444</v>
       </c>
       <c t="n" r="D258">
         <v>-6.4678</v>
       </c>
       <c t="n" r="E258">
-        <v>-9.3600</v>
+        <v>-9.3634</v>
       </c>
       <c t="n" r="F258">
-        <v>-4.5606</v>
+        <v>-4.5682</v>
       </c>
     </row>
     <row r="259">
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c t="n" r="C260">
-        <v>3.2647</v>
+        <v>3.3986</v>
       </c>
     </row>
     <row r="261">
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c t="n" r="C261">
-        <v>0.1300</v>
+        <v>0.1274</v>
       </c>
     </row>
     <row r="262">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c t="n" r="C264">
-        <v>80.6243</v>
+        <v>80.6249</v>
       </c>
     </row>
     <row r="265">
@@ -6850,13 +6850,13 @@
         </is>
       </c>
       <c t="n" r="C266">
-        <v>2.5175</v>
+        <v>2.5952</v>
       </c>
       <c t="n" r="D266">
-        <v>6.9813</v>
+        <v>6.9804</v>
       </c>
       <c t="n" r="F266">
-        <v>8.1779</v>
+        <v>8.2600</v>
       </c>
     </row>
     <row r="267">
@@ -6871,13 +6871,13 @@
         </is>
       </c>
       <c t="n" r="C267">
-        <v>2.5197</v>
+        <v>2.5975</v>
       </c>
       <c t="n" r="D267">
-        <v>6.9607</v>
+        <v>6.9599</v>
       </c>
       <c t="n" r="F267">
-        <v>8.1575</v>
+        <v>8.2397</v>
       </c>
     </row>
     <row r="268">
@@ -6904,16 +6904,16 @@
         </is>
       </c>
       <c t="n" r="C269">
-        <v>-30.3786</v>
+        <v>-30.3782</v>
       </c>
       <c t="n" r="D269">
-        <v>-27.8370</v>
+        <v>-27.8811</v>
       </c>
       <c t="n" r="E269">
-        <v>-23.5361</v>
+        <v>-23.6171</v>
       </c>
       <c t="n" r="F269">
-        <v>-27.2025</v>
+        <v>-27.2020</v>
       </c>
     </row>
     <row r="270">
@@ -6940,16 +6940,16 @@
         </is>
       </c>
       <c t="n" r="C271">
-        <v>-0.4779</v>
+        <v>-0.4889</v>
       </c>
       <c t="n" r="D271">
-        <v>28.4483</v>
+        <v>28.4047</v>
       </c>
       <c t="n" r="E271">
-        <v>-33.1418</v>
+        <v>-33.0204</v>
       </c>
       <c t="n" r="F271">
-        <v>95.8071</v>
+        <v>95.7856</v>
       </c>
     </row>
     <row r="272">
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c t="n" r="C272">
-        <v>21.7143</v>
+        <v>28.0639</v>
       </c>
     </row>
     <row r="273">
@@ -6979,13 +6979,13 @@
         </is>
       </c>
       <c t="n" r="C273">
-        <v>-0.3409</v>
+        <v>-0.3504</v>
       </c>
       <c t="n" r="D273">
-        <v>-1.0573</v>
+        <v>-1.0231</v>
       </c>
       <c t="n" r="F273">
-        <v>-2.2867</v>
+        <v>-2.2959</v>
       </c>
     </row>
     <row r="274">
@@ -7000,16 +7000,16 @@
         </is>
       </c>
       <c t="n" r="C274">
-        <v>-74.0296</v>
+        <v>-74.0280</v>
       </c>
       <c t="n" r="D274">
-        <v>-86.2078</v>
+        <v>-86.1757</v>
       </c>
       <c t="n" r="E274">
-        <v>-41.3398</v>
+        <v>-40.7826</v>
       </c>
       <c t="n" r="F274">
-        <v>137.2591</v>
+        <v>137.2743</v>
       </c>
     </row>
     <row r="275">
@@ -7048,13 +7048,13 @@
         </is>
       </c>
       <c t="n" r="C277">
-        <v>-0.0559</v>
+        <v>-0.0570</v>
       </c>
       <c t="n" r="D277">
-        <v>-10.5141</v>
+        <v>-10.5767</v>
       </c>
       <c t="n" r="F277">
-        <v>-9.7088</v>
+        <v>-9.7098</v>
       </c>
     </row>
     <row r="278">
@@ -7081,16 +7081,16 @@
         </is>
       </c>
       <c t="n" r="C279">
-        <v>3.2794</v>
+        <v>3.3693</v>
       </c>
       <c t="n" r="D279">
-        <v>-61.1064</v>
+        <v>-60.8474</v>
       </c>
       <c t="n" r="E279">
-        <v>-99.0862</v>
+        <v>-99.0583</v>
       </c>
       <c t="n" r="F279">
-        <v>-98.1715</v>
+        <v>-98.1699</v>
       </c>
     </row>
     <row r="280">
@@ -7123,7 +7123,7 @@
         <v>0.9074</v>
       </c>
       <c t="n" r="E281">
-        <v>-97.6087</v>
+        <v>-97.4381</v>
       </c>
       <c t="n" r="F281">
         <v>0.8311</v>
@@ -7165,16 +7165,16 @@
         </is>
       </c>
       <c t="n" r="C284">
-        <v>-0.4660</v>
+        <v>-0.4762</v>
       </c>
       <c t="n" r="D284">
-        <v>-29.8303</v>
+        <v>-29.8280</v>
       </c>
       <c t="n" r="E284">
-        <v>4985.8554</v>
+        <v>5020.1110</v>
       </c>
       <c t="n" r="F284">
-        <v>12086.3719</v>
+        <v>12085.1221</v>
       </c>
     </row>
     <row r="285">
@@ -7189,13 +7189,13 @@
         </is>
       </c>
       <c t="n" r="C285">
-        <v>-0.0224</v>
+        <v>-0.0274</v>
       </c>
       <c t="n" r="D285">
-        <v>-0.0636</v>
+        <v>-0.0672</v>
       </c>
       <c t="n" r="F285">
-        <v>-0.0123</v>
+        <v>-0.0173</v>
       </c>
     </row>
     <row r="286">
@@ -7246,7 +7246,7 @@
         </is>
       </c>
       <c t="n" r="C289">
-        <v>-74.3251</v>
+        <v>-74.5861</v>
       </c>
     </row>
     <row r="290">
@@ -7273,16 +7273,16 @@
         </is>
       </c>
       <c t="n" r="C291">
-        <v>0.7347</v>
+        <v>0.7328</v>
       </c>
       <c t="n" r="D291">
-        <v>2.7212</v>
+        <v>2.6979</v>
       </c>
       <c t="n" r="E291">
-        <v>10.3562</v>
+        <v>10.3280</v>
       </c>
       <c t="n" r="F291">
-        <v>3.1466</v>
+        <v>3.1448</v>
       </c>
     </row>
     <row r="292">
@@ -7309,16 +7309,16 @@
         </is>
       </c>
       <c t="n" r="C293">
-        <v>-26.4321</v>
+        <v>-26.3940</v>
       </c>
       <c t="n" r="D293">
-        <v>-57.3951</v>
+        <v>-57.4130</v>
       </c>
       <c t="n" r="E293">
-        <v>-57.3245</v>
+        <v>-57.3066</v>
       </c>
       <c t="n" r="F293">
-        <v>-56.8338</v>
+        <v>-56.8114</v>
       </c>
     </row>
     <row r="294">
@@ -7429,16 +7429,16 @@
         </is>
       </c>
       <c t="n" r="C300">
-        <v>3.6643</v>
+        <v>3.7865</v>
       </c>
       <c t="n" r="D300">
-        <v>10.2752</v>
+        <v>10.2744</v>
       </c>
       <c t="n" r="E300">
-        <v>21.2294</v>
+        <v>21.2542</v>
       </c>
       <c t="n" r="F300">
-        <v>12.0652</v>
+        <v>12.1973</v>
       </c>
     </row>
     <row r="301">
@@ -7453,13 +7453,13 @@
         </is>
       </c>
       <c t="n" r="C301">
-        <v>3.5776</v>
+        <v>3.6965</v>
       </c>
       <c t="n" r="D301">
-        <v>9.4798</v>
+        <v>9.4734</v>
       </c>
       <c t="n" r="F301">
-        <v>11.2732</v>
+        <v>11.4010</v>
       </c>
     </row>
     <row r="302">
@@ -7486,13 +7486,13 @@
         </is>
       </c>
       <c t="n" r="C303">
-        <v>4.1660</v>
+        <v>4.3246</v>
       </c>
       <c t="n" r="D303">
-        <v>11.8232</v>
+        <v>11.8559</v>
       </c>
       <c t="n" r="F303">
-        <v>13.8384</v>
+        <v>14.0116</v>
       </c>
     </row>
     <row r="304">
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c t="n" r="C304">
-        <v>-70.7076</v>
+        <v>-71.6965</v>
       </c>
     </row>
     <row r="305">
@@ -7522,10 +7522,10 @@
         </is>
       </c>
       <c t="n" r="C305">
-        <v>-0.0071</v>
+        <v>-0.0050</v>
       </c>
       <c t="n" r="D305">
-        <v>-0.8837</v>
+        <v>-0.8776</v>
       </c>
     </row>
     <row r="306">
@@ -7540,16 +7540,16 @@
         </is>
       </c>
       <c t="n" r="C306">
-        <v>1.1474</v>
+        <v>1.2289</v>
       </c>
       <c t="n" r="D306">
-        <v>6.0803</v>
+        <v>6.0814</v>
       </c>
       <c t="n" r="E306">
-        <v>14.5300</v>
+        <v>14.5201</v>
       </c>
       <c t="n" r="F306">
-        <v>7.1916</v>
+        <v>7.2779</v>
       </c>
     </row>
     <row r="307">
@@ -7588,16 +7588,16 @@
         </is>
       </c>
       <c t="n" r="C309">
-        <v>1.9942</v>
+        <v>2.0330</v>
       </c>
       <c t="n" r="D309">
-        <v>3.8541</v>
+        <v>3.7959</v>
       </c>
       <c t="n" r="E309">
-        <v>12.2201</v>
+        <v>12.1836</v>
       </c>
       <c t="n" r="F309">
-        <v>5.2080</v>
+        <v>5.2480</v>
       </c>
     </row>
     <row r="310">
@@ -7636,16 +7636,16 @@
         </is>
       </c>
       <c t="n" r="C312">
-        <v>-0.0762</v>
+        <v>-0.0778</v>
       </c>
       <c t="n" r="D312">
-        <v>-0.2179</v>
+        <v>-0.2181</v>
       </c>
       <c t="n" r="E312">
-        <v>0.6045</v>
+        <v>0.6046</v>
       </c>
       <c t="n" r="F312">
-        <v>-0.2426</v>
+        <v>-0.2442</v>
       </c>
     </row>
     <row r="313">
@@ -7684,13 +7684,16 @@
         </is>
       </c>
       <c t="n" r="C315">
-        <v>-0.0537</v>
+        <v>-0.0548</v>
       </c>
       <c t="n" r="D315">
-        <v>-0.1474</v>
+        <v>-0.1475</v>
+      </c>
+      <c t="n" r="E315">
+        <v>2.6117</v>
       </c>
       <c t="n" r="F315">
-        <v>-0.1669</v>
+        <v>-0.1679</v>
       </c>
     </row>
     <row r="316">
@@ -7717,16 +7720,16 @@
         </is>
       </c>
       <c t="n" r="C317">
-        <v>-0.1568</v>
+        <v>-0.1592</v>
       </c>
       <c t="n" r="D317">
         <v>-0.3507</v>
       </c>
       <c t="n" r="E317">
-        <v>3.0281</v>
+        <v>3.0278</v>
       </c>
       <c t="n" r="F317">
-        <v>-0.3845</v>
+        <v>-0.3869</v>
       </c>
     </row>
     <row r="318">
@@ -7741,7 +7744,7 @@
         </is>
       </c>
       <c t="n" r="C318">
-        <v>-0.1290</v>
+        <v>-0.1336</v>
       </c>
     </row>
     <row r="319">
@@ -7810,13 +7813,13 @@
         </is>
       </c>
       <c t="n" r="C323">
-        <v>-0.1162</v>
+        <v>-0.1126</v>
       </c>
       <c t="n" r="D323">
-        <v>-0.1495</v>
+        <v>-0.1472</v>
       </c>
       <c t="n" r="F323">
-        <v>-0.1308</v>
+        <v>-0.1272</v>
       </c>
     </row>
     <row r="324">
@@ -7855,7 +7858,7 @@
         </is>
       </c>
       <c t="n" r="C326">
-        <v>2.8818</v>
+        <v>2.9850</v>
       </c>
     </row>
     <row r="327">
@@ -7870,16 +7873,16 @@
         </is>
       </c>
       <c t="n" r="C327">
-        <v>0.0000</v>
+        <v>0.1274</v>
       </c>
       <c t="n" r="D327">
         <v>0.0212</v>
       </c>
       <c t="n" r="E327">
-        <v>-0.1272</v>
+        <v>0.0000</v>
       </c>
       <c t="n" r="F327">
-        <v>-0.0212</v>
+        <v>0.1061</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
@@ -280,22 +280,22 @@
         </is>
       </c>
       <c t="n" r="C3">
-        <v>38.7018</v>
+        <v>26.8601</v>
       </c>
       <c t="n" r="D3">
-        <v>664.8302</v>
+        <v>665.8372</v>
       </c>
       <c t="n" r="E3">
-        <v>691.4450</v>
+        <v>692.4037</v>
       </c>
       <c t="n" r="F3">
-        <v>659.3993</v>
+        <v>660.2958</v>
       </c>
       <c t="n" r="G3">
-        <v>616.4683</v>
+        <v>614.0943</v>
       </c>
       <c t="n" r="H3">
-        <v>769.8537</v>
+        <v>770.8807</v>
       </c>
     </row>
     <row r="4">
@@ -310,19 +310,19 @@
         </is>
       </c>
       <c t="n" r="C4">
-        <v>16.4394</v>
+        <v>16.3595</v>
       </c>
       <c t="n" r="D4">
-        <v>20.4024</v>
+        <v>20.3966</v>
       </c>
       <c t="n" r="E4">
-        <v>249.9272</v>
+        <v>249.8548</v>
       </c>
       <c t="n" r="F4">
-        <v>21.0611</v>
+        <v>21.0922</v>
       </c>
       <c t="n" r="G4">
-        <v>373.7437</v>
+        <v>373.9360</v>
       </c>
     </row>
     <row r="5">
@@ -337,19 +337,19 @@
         </is>
       </c>
       <c t="n" r="C5">
-        <v>0.9345</v>
+        <v>0.9121</v>
       </c>
       <c t="n" r="D5">
-        <v>2.6432</v>
+        <v>2.6493</v>
       </c>
       <c t="n" r="E5">
-        <v>27.7320</v>
+        <v>27.7362</v>
       </c>
       <c t="n" r="F5">
-        <v>3.3779</v>
+        <v>3.3878</v>
       </c>
       <c t="n" r="G5">
-        <v>362.4812</v>
+        <v>361.9765</v>
       </c>
     </row>
     <row r="6">
@@ -364,22 +364,22 @@
         </is>
       </c>
       <c t="n" r="C6">
-        <v>-0.4364</v>
+        <v>-0.4237</v>
       </c>
       <c t="n" r="D6">
-        <v>43.1989</v>
+        <v>43.1449</v>
       </c>
       <c t="n" r="E6">
-        <v>52.7670</v>
+        <v>52.7735</v>
       </c>
       <c t="n" r="F6">
-        <v>42.2891</v>
+        <v>42.2875</v>
       </c>
       <c t="n" r="G6">
-        <v>240.0814</v>
+        <v>240.0924</v>
       </c>
       <c t="n" r="H6">
-        <v>332.7502</v>
+        <v>332.7452</v>
       </c>
     </row>
     <row r="7">
@@ -394,22 +394,22 @@
         </is>
       </c>
       <c t="n" r="C7">
-        <v>-0.0191</v>
+        <v>-0.0190</v>
       </c>
       <c t="n" r="D7">
-        <v>-0.0488</v>
+        <v>-0.0481</v>
       </c>
       <c t="n" r="E7">
-        <v>192.5058</v>
+        <v>192.5060</v>
       </c>
       <c t="n" r="F7">
-        <v>-0.0586</v>
+        <v>-0.0590</v>
       </c>
       <c t="n" r="G7">
-        <v>191.4475</v>
+        <v>191.4476</v>
       </c>
       <c t="n" r="H7">
-        <v>166673.6393</v>
+        <v>166673.0297</v>
       </c>
     </row>
     <row r="8">
@@ -424,19 +424,19 @@
         </is>
       </c>
       <c t="n" r="C8">
-        <v>-0.0159</v>
+        <v>-0.0288</v>
       </c>
       <c t="n" r="D8">
-        <v>4.0109</v>
+        <v>4.0237</v>
       </c>
       <c t="n" r="E8">
-        <v>3.9844</v>
+        <v>3.9845</v>
       </c>
       <c t="n" r="F8">
-        <v>4.0206</v>
+        <v>4.0212</v>
       </c>
       <c t="n" r="G8">
-        <v>152.7232</v>
+        <v>152.7407</v>
       </c>
     </row>
     <row r="9">
@@ -451,19 +451,19 @@
         </is>
       </c>
       <c t="n" r="C9">
-        <v>0.7325</v>
+        <v>0.7166</v>
       </c>
       <c t="n" r="D9">
-        <v>1.0499</v>
+        <v>1.0644</v>
       </c>
       <c t="n" r="E9">
-        <v>141.4734</v>
+        <v>141.4649</v>
       </c>
       <c t="n" r="F9">
         <v>1.5291</v>
       </c>
       <c t="n" r="G9">
-        <v>143.3596</v>
+        <v>143.2885</v>
       </c>
     </row>
     <row r="10">
@@ -478,22 +478,22 @@
         </is>
       </c>
       <c t="n" r="C10">
-        <v>65.7361</v>
+        <v>65.7066</v>
       </c>
       <c t="n" r="D10">
-        <v>68.1865</v>
+        <v>68.1813</v>
       </c>
       <c t="n" r="E10">
-        <v>69.7758</v>
+        <v>69.7796</v>
       </c>
       <c t="n" r="F10">
-        <v>55.1316</v>
+        <v>55.1377</v>
       </c>
       <c t="n" r="G10">
-        <v>88.2606</v>
+        <v>88.2491</v>
       </c>
       <c t="n" r="H10">
-        <v>114.9058</v>
+        <v>114.9143</v>
       </c>
     </row>
     <row r="11">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c t="n" r="C11">
-        <v>1.8259</v>
+        <v>1.7777</v>
       </c>
       <c t="n" r="D11">
-        <v>33.7495</v>
+        <v>2.2804</v>
       </c>
       <c t="n" r="E11">
-        <v>76.8015</v>
+        <v>76.8130</v>
       </c>
       <c t="n" r="F11">
-        <v>33.7875</v>
+        <v>33.8000</v>
       </c>
       <c t="n" r="G11">
-        <v>82.7451</v>
+        <v>82.7581</v>
       </c>
       <c t="n" r="H11">
-        <v>299.3430</v>
+        <v>299.3805</v>
       </c>
       <c t="n" r="I11">
-        <v>1680.0745</v>
+        <v>1679.9848</v>
       </c>
     </row>
     <row r="12">
@@ -541,25 +541,25 @@
         </is>
       </c>
       <c t="n" r="C12">
-        <v>0.2698</v>
+        <v>0.2309</v>
       </c>
       <c t="n" r="D12">
-        <v>1.4034</v>
+        <v>1.4164</v>
       </c>
       <c t="n" r="E12">
-        <v>38.7401</v>
+        <v>38.6514</v>
       </c>
       <c t="n" r="F12">
-        <v>1.3126</v>
+        <v>1.3326</v>
       </c>
       <c t="n" r="G12">
-        <v>61.7123</v>
+        <v>61.6004</v>
       </c>
       <c t="n" r="H12">
-        <v>327.7286</v>
+        <v>327.8133</v>
       </c>
       <c t="n" r="I12">
-        <v>1093.8276</v>
+        <v>1094.0639</v>
       </c>
     </row>
     <row r="13">
@@ -574,22 +574,22 @@
         </is>
       </c>
       <c t="n" r="C13">
-        <v>-0.1948</v>
+        <v>-0.1953</v>
       </c>
       <c t="n" r="D13">
-        <v>-0.3572</v>
+        <v>-0.3492</v>
       </c>
       <c t="n" r="E13">
-        <v>19.9559</v>
+        <v>19.9445</v>
       </c>
       <c t="n" r="F13">
-        <v>-1.0410</v>
+        <v>-1.0431</v>
       </c>
       <c t="n" r="G13">
-        <v>61.6167</v>
+        <v>61.5713</v>
       </c>
       <c t="n" r="H13">
-        <v>687.3906</v>
+        <v>687.3739</v>
       </c>
     </row>
     <row r="14">
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c t="n" r="C14">
-        <v>3.8245</v>
+        <v>3.6470</v>
       </c>
       <c t="n" r="D14">
-        <v>10.2394</v>
+        <v>10.2754</v>
       </c>
       <c t="n" r="E14">
-        <v>27.7532</v>
+        <v>27.7879</v>
       </c>
       <c t="n" r="F14">
-        <v>11.2696</v>
+        <v>11.4196</v>
       </c>
       <c t="n" r="G14">
-        <v>58.6638</v>
+        <v>58.6588</v>
       </c>
     </row>
     <row r="15">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c t="n" r="C15">
-        <v>-0.1202</v>
+        <v>-0.1201</v>
       </c>
       <c t="n" r="D15">
-        <v>0.2721</v>
+        <v>0.2780</v>
       </c>
       <c t="n" r="E15">
-        <v>60.0178</v>
+        <v>60.0176</v>
       </c>
       <c t="n" r="F15">
-        <v>-4.4541</v>
+        <v>-4.4567</v>
       </c>
       <c t="n" r="G15">
-        <v>58.6156</v>
+        <v>58.6151</v>
       </c>
     </row>
     <row r="16">
@@ -658,19 +658,19 @@
         </is>
       </c>
       <c t="n" r="C16">
-        <v>3.5632</v>
+        <v>3.3464</v>
       </c>
       <c t="n" r="D16">
-        <v>14.5468</v>
+        <v>10.0000</v>
       </c>
       <c t="n" r="E16">
-        <v>26.5859</v>
+        <v>26.5560</v>
       </c>
       <c t="n" r="F16">
-        <v>18.1194</v>
+        <v>18.2159</v>
       </c>
       <c t="n" r="G16">
-        <v>57.5859</v>
+        <v>57.5298</v>
       </c>
     </row>
     <row r="17">
@@ -685,22 +685,22 @@
         </is>
       </c>
       <c t="n" r="C17">
-        <v>0.7467</v>
+        <v>0.7418</v>
       </c>
       <c t="n" r="D17">
-        <v>1.9341</v>
+        <v>1.9401</v>
       </c>
       <c t="n" r="E17">
-        <v>51.3594</v>
+        <v>51.3653</v>
       </c>
       <c t="n" r="F17">
-        <v>48.1886</v>
+        <v>48.1999</v>
       </c>
       <c t="n" r="G17">
-        <v>56.0158</v>
+        <v>56.1296</v>
       </c>
       <c t="n" r="H17">
-        <v>463.8363</v>
+        <v>463.8794</v>
       </c>
     </row>
     <row r="18">
@@ -715,19 +715,19 @@
         </is>
       </c>
       <c t="n" r="C18">
-        <v>3.9062</v>
+        <v>3.7926</v>
       </c>
       <c t="n" r="D18">
-        <v>10.4367</v>
+        <v>10.5008</v>
       </c>
       <c t="n" r="E18">
-        <v>22.2329</v>
+        <v>22.2864</v>
       </c>
       <c t="n" r="F18">
-        <v>12.0369</v>
+        <v>12.2196</v>
       </c>
       <c t="n" r="G18">
-        <v>55.9269</v>
+        <v>56.0013</v>
       </c>
     </row>
     <row r="19">
@@ -742,19 +742,19 @@
         </is>
       </c>
       <c t="n" r="C19">
-        <v>3.9059</v>
+        <v>3.7922</v>
       </c>
       <c t="n" r="D19">
-        <v>10.4356</v>
+        <v>10.4997</v>
       </c>
       <c t="n" r="E19">
-        <v>22.2304</v>
+        <v>22.2839</v>
       </c>
       <c t="n" r="F19">
-        <v>12.0356</v>
+        <v>12.2182</v>
       </c>
       <c t="n" r="G19">
-        <v>55.9190</v>
+        <v>55.9933</v>
       </c>
     </row>
     <row r="20">
@@ -769,22 +769,22 @@
         </is>
       </c>
       <c t="n" r="C20">
-        <v>0.2903</v>
+        <v>0.3123</v>
       </c>
       <c t="n" r="D20">
-        <v>0.8376</v>
+        <v>0.8794</v>
       </c>
       <c t="n" r="E20">
-        <v>1.3696</v>
+        <v>1.4049</v>
       </c>
       <c t="n" r="F20">
-        <v>0.9233</v>
+        <v>0.9557</v>
       </c>
       <c t="n" r="G20">
-        <v>55.2325</v>
+        <v>55.2876</v>
       </c>
       <c t="n" r="H20">
-        <v>410.4407</v>
+        <v>410.6042</v>
       </c>
     </row>
     <row r="21">
@@ -799,19 +799,19 @@
         </is>
       </c>
       <c t="n" r="C21">
-        <v>-0.0135</v>
+        <v>-0.0371</v>
       </c>
       <c t="n" r="D21">
-        <v>6.4339</v>
+        <v>6.4447</v>
       </c>
       <c t="n" r="E21">
-        <v>19.5481</v>
+        <v>19.5144</v>
       </c>
       <c t="n" r="F21">
-        <v>6.8150</v>
+        <v>6.8316</v>
       </c>
       <c t="n" r="G21">
-        <v>54.7130</v>
+        <v>54.5931</v>
       </c>
     </row>
     <row r="22">
@@ -826,22 +826,22 @@
         </is>
       </c>
       <c t="n" r="C22">
-        <v>-0.2023</v>
+        <v>-0.2025</v>
       </c>
       <c t="n" r="D22">
         <v>-0.2035</v>
       </c>
       <c t="n" r="E22">
-        <v>55.3903</v>
+        <v>55.3901</v>
       </c>
       <c t="n" r="F22">
-        <v>-0.2326</v>
+        <v>-0.2325</v>
       </c>
       <c t="n" r="G22">
-        <v>54.4094</v>
+        <v>54.4091</v>
       </c>
       <c t="n" r="H22">
-        <v>172.5228</v>
+        <v>172.5230</v>
       </c>
     </row>
     <row r="23">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c t="n" r="C23">
-        <v>5.9224</v>
+        <v>4.8469</v>
       </c>
       <c t="n" r="D23">
-        <v>23.6492</v>
+        <v>21.2746</v>
       </c>
       <c t="n" r="E23">
-        <v>28.2303</v>
+        <v>28.3121</v>
       </c>
       <c t="n" r="F23">
-        <v>29.3660</v>
+        <v>29.4366</v>
       </c>
       <c t="n" r="G23">
-        <v>54.2687</v>
+        <v>54.0584</v>
       </c>
     </row>
     <row r="24">
@@ -883,277 +883,277 @@
         </is>
       </c>
       <c t="n" r="C24">
-        <v>4.3927</v>
+        <v>3.7728</v>
       </c>
       <c t="n" r="D24">
-        <v>10.9170</v>
+        <v>5.4273</v>
       </c>
       <c t="n" r="E24">
-        <v>22.7414</v>
+        <v>22.3522</v>
       </c>
       <c t="n" r="F24">
-        <v>14.3653</v>
+        <v>14.1231</v>
       </c>
       <c t="n" r="G24">
-        <v>52.9607</v>
+        <v>52.4576</v>
       </c>
     </row>
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">YD7</t>
+          <t xml:space="preserve">IGJ</t>
         </is>
       </c>
       <c t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.KARDELEN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C25">
-        <v>-0.2624</v>
+        <v>0.0783</v>
       </c>
       <c t="n" r="D25">
-        <v>-1.4321</v>
+        <v>0.1302</v>
       </c>
       <c t="n" r="E25">
-        <v>28.4793</v>
+        <v>36.2521</v>
       </c>
       <c t="n" r="F25">
-        <v>-1.7027</v>
+        <v>0.2923</v>
       </c>
       <c t="n" r="G25">
-        <v>49.0620</v>
-      </c>
-      <c t="n" r="H25">
-        <v>168.1896</v>
-      </c>
-      <c t="n" r="I25">
-        <v>1143.6244</v>
+        <v>51.5190</v>
       </c>
     </row>
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">RAA</t>
+          <t xml:space="preserve">YD7</t>
         </is>
       </c>
       <c t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. AVRUPA-ANADOLU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.KARDELEN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C26">
-        <v>5.2877</v>
+        <v>-0.2585</v>
       </c>
       <c t="n" r="D26">
-        <v>12.0685</v>
+        <v>-1.4220</v>
       </c>
       <c t="n" r="E26">
-        <v>21.3333</v>
+        <v>28.4799</v>
       </c>
       <c t="n" r="F26">
-        <v>13.4306</v>
+        <v>-1.7104</v>
       </c>
       <c t="n" r="G26">
-        <v>48.3497</v>
+        <v>49.0671</v>
+      </c>
+      <c t="n" r="H26">
+        <v>168.1687</v>
+      </c>
+      <c t="n" r="I26">
+        <v>1143.5276</v>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">YD5</t>
+          <t xml:space="preserve">RAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. AVRUPA-ANADOLU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C27">
-        <v>-0.3299</v>
+        <v>5.1548</v>
       </c>
       <c t="n" r="D27">
-        <v>-0.4354</v>
+        <v>11.9820</v>
       </c>
       <c t="n" r="E27">
-        <v>16.0248</v>
+        <v>21.2494</v>
       </c>
       <c t="n" r="F27">
-        <v>-0.6174</v>
+        <v>13.4701</v>
       </c>
       <c t="n" r="G27">
-        <v>48.1076</v>
-      </c>
-      <c t="n" r="H27">
-        <v>196.8368</v>
-      </c>
-      <c t="n" r="I27">
-        <v>1322.4948</v>
+        <v>48.2441</v>
       </c>
     </row>
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">NG7</t>
+          <t xml:space="preserve">YD5</t>
         </is>
       </c>
       <c t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C28">
-        <v>0.4808</v>
+        <v>-0.3114</v>
       </c>
       <c t="n" r="D28">
-        <v>6.3091</v>
+        <v>-0.4266</v>
       </c>
       <c t="n" r="E28">
-        <v>43.8098</v>
+        <v>16.0250</v>
       </c>
       <c t="n" r="F28">
-        <v>5.9958</v>
+        <v>-0.6251</v>
       </c>
       <c t="n" r="G28">
-        <v>45.3622</v>
+        <v>48.1189</v>
       </c>
       <c t="n" r="H28">
-        <v>462.0146</v>
+        <v>196.8139</v>
+      </c>
+      <c t="n" r="I28">
+        <v>1322.3848</v>
       </c>
     </row>
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">TGI</t>
+          <t xml:space="preserve">NG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C29">
-        <v>1.4416</v>
+        <v>0.4399</v>
       </c>
       <c t="n" r="D29">
-        <v>5.0275</v>
+        <v>6.3955</v>
       </c>
       <c t="n" r="E29">
-        <v>22.3913</v>
+        <v>43.7950</v>
       </c>
       <c t="n" r="F29">
-        <v>5.5950</v>
+        <v>6.0018</v>
       </c>
       <c t="n" r="G29">
-        <v>44.5726</v>
+        <v>45.3631</v>
+      </c>
+      <c t="n" r="H29">
+        <v>462.0464</v>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">YYF</t>
+          <t xml:space="preserve">TGI</t>
         </is>
       </c>
       <c t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C30">
-        <v>3.3626</v>
+        <v>1.5992</v>
       </c>
       <c t="n" r="D30">
-        <v>8.8912</v>
+        <v>5.0109</v>
       </c>
       <c t="n" r="E30">
-        <v>19.2211</v>
+        <v>21.9992</v>
       </c>
       <c t="n" r="F30">
-        <v>10.4779</v>
+        <v>5.6219</v>
       </c>
       <c t="n" r="G30">
-        <v>44.5592</v>
+        <v>45.3039</v>
       </c>
     </row>
     <row r="31">
       <c t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">ZGG</t>
+          <t xml:space="preserve">YYF</t>
         </is>
       </c>
       <c t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BGF KATILIM ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C31">
-        <v>-1.0357</v>
+        <v>3.2880</v>
       </c>
       <c t="n" r="D31">
-        <v>0.4830</v>
+        <v>8.9639</v>
       </c>
       <c t="n" r="E31">
-        <v>29.4118</v>
+        <v>19.2711</v>
       </c>
       <c t="n" r="F31">
-        <v>1.6165</v>
+        <v>10.6432</v>
       </c>
       <c t="n" r="G31">
-        <v>44.1762</v>
+        <v>44.6044</v>
       </c>
     </row>
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">ZGU</t>
+          <t xml:space="preserve">ZGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BGF KATILIM ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C32">
-        <v>2.2262</v>
+        <v>0.1858</v>
       </c>
       <c t="n" r="D32">
-        <v>3.7681</v>
+        <v>-0.4535</v>
       </c>
       <c t="n" r="E32">
-        <v>24.7072</v>
+        <v>29.4117</v>
       </c>
       <c t="n" r="F32">
-        <v>8.7827</v>
+        <v>1.6321</v>
       </c>
       <c t="n" r="G32">
-        <v>42.2320</v>
+        <v>44.1840</v>
       </c>
     </row>
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">ORV</t>
+          <t xml:space="preserve">ZGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AVRASYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C33">
-        <v>-0.0209</v>
+        <v>1.8896</v>
       </c>
       <c t="n" r="D33">
-        <v>0.2593</v>
+        <v>2.5920</v>
       </c>
       <c t="n" r="E33">
-        <v>27.5230</v>
+        <v>24.8284</v>
       </c>
       <c t="n" r="F33">
-        <v>0.3206</v>
+        <v>8.4279</v>
       </c>
       <c t="n" r="G33">
-        <v>41.8789</v>
+        <v>42.1900</v>
       </c>
     </row>
     <row r="34">
@@ -1168,481 +1168,481 @@
         </is>
       </c>
       <c t="n" r="C34">
-        <v>0.1587</v>
+        <v>0.1572</v>
       </c>
       <c t="n" r="D34">
-        <v>0.5345</v>
+        <v>0.5463</v>
       </c>
       <c t="n" r="E34">
-        <v>38.6427</v>
+        <v>38.6423</v>
       </c>
       <c t="n" r="F34">
-        <v>0.7315</v>
+        <v>0.7286</v>
       </c>
       <c t="n" r="G34">
-        <v>41.7473</v>
+        <v>41.7498</v>
       </c>
       <c t="n" r="H34">
-        <v>241.8806</v>
+        <v>241.8709</v>
       </c>
       <c t="n" r="I34">
-        <v>848.0227</v>
+        <v>847.9956</v>
       </c>
     </row>
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">RG3</t>
+          <t xml:space="preserve">ORV</t>
         </is>
       </c>
       <c t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TRAKYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AVRASYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C35">
-        <v>-0.0792</v>
+        <v>-0.2280</v>
       </c>
       <c t="n" r="D35">
-        <v>-0.3340</v>
+        <v>-0.0226</v>
       </c>
       <c t="n" r="E35">
-        <v>42.2748</v>
+        <v>27.2694</v>
       </c>
       <c t="n" r="F35">
-        <v>-0.4995</v>
+        <v>0.1142</v>
       </c>
       <c t="n" r="G35">
-        <v>41.6786</v>
-      </c>
-      <c t="n" r="H35">
-        <v>212.9968</v>
-      </c>
-      <c t="n" r="I35">
-        <v>723.9338</v>
+        <v>41.7094</v>
       </c>
     </row>
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">KGG</t>
+          <t xml:space="preserve">RG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TRAKYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C36">
-        <v>0.1472</v>
+        <v>-0.0792</v>
       </c>
       <c t="n" r="D36">
-        <v>0.0129</v>
+        <v>-0.3323</v>
       </c>
       <c t="n" r="E36">
-        <v>41.1480</v>
+        <v>42.2744</v>
       </c>
       <c t="n" r="F36">
-        <v>0.2853</v>
+        <v>-0.5004</v>
       </c>
       <c t="n" r="G36">
-        <v>41.4633</v>
+        <v>41.6786</v>
       </c>
       <c t="n" r="H36">
-        <v>251.9159</v>
+        <v>212.9940</v>
+      </c>
+      <c t="n" r="I36">
+        <v>723.2328</v>
       </c>
     </row>
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">MPG</t>
+          <t xml:space="preserve">KGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM (TL) FONU</t>
+          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C37">
-        <v>0.5657</v>
+        <v>0.1468</v>
       </c>
       <c t="n" r="D37">
-        <v>1.5465</v>
+        <v>0.0247</v>
       </c>
       <c t="n" r="E37">
-        <v>28.9764</v>
+        <v>41.1493</v>
       </c>
       <c t="n" r="F37">
-        <v>1.5212</v>
+        <v>0.2791</v>
       </c>
       <c t="n" r="G37">
-        <v>40.7900</v>
+        <v>41.4643</v>
       </c>
       <c t="n" r="H37">
-        <v>172.2624</v>
-      </c>
-      <c t="n" r="I37">
-        <v>400.4949</v>
+        <v>251.8940</v>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">ISZ</t>
+          <t xml:space="preserve">MPG</t>
         </is>
       </c>
       <c t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM (TL) FONU</t>
         </is>
       </c>
       <c t="n" r="C38">
-        <v>0.4725</v>
+        <v>0.5518</v>
       </c>
       <c t="n" r="D38">
-        <v>1.7563</v>
+        <v>1.5389</v>
       </c>
       <c t="n" r="E38">
-        <v>16.1777</v>
+        <v>28.9759</v>
       </c>
       <c t="n" r="F38">
-        <v>2.0313</v>
+        <v>1.5342</v>
       </c>
       <c t="n" r="G38">
-        <v>40.2539</v>
+        <v>40.7827</v>
       </c>
       <c t="n" r="H38">
-        <v>295.3594</v>
+        <v>172.2973</v>
       </c>
       <c t="n" r="I38">
-        <v>916.2804</v>
+        <v>400.5591</v>
       </c>
     </row>
     <row r="39">
       <c t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">IIY</t>
+          <t xml:space="preserve">ISZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ  GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C39">
-        <v>1.5115</v>
+        <v>0.4527</v>
       </c>
       <c t="n" r="D39">
-        <v>4.4417</v>
+        <v>1.7188</v>
       </c>
       <c t="n" r="E39">
-        <v>14.5132</v>
+        <v>16.1825</v>
       </c>
       <c t="n" r="F39">
-        <v>3.5134</v>
+        <v>2.0444</v>
       </c>
       <c t="n" r="G39">
-        <v>39.9065</v>
+        <v>40.2618</v>
       </c>
       <c t="n" r="H39">
-        <v>141.5523</v>
+        <v>295.4102</v>
       </c>
       <c t="n" r="I39">
-        <v>260.4879</v>
+        <v>916.1180</v>
       </c>
     </row>
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">RG4</t>
+          <t xml:space="preserve">IIY</t>
         </is>
       </c>
       <c t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ  GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C40">
-        <v>0.9009</v>
+        <v>1.4956</v>
       </c>
       <c t="n" r="D40">
-        <v>5.5432</v>
+        <v>4.4659</v>
       </c>
       <c t="n" r="E40">
-        <v>34.9050</v>
+        <v>14.5215</v>
       </c>
       <c t="n" r="F40">
-        <v>13.3790</v>
+        <v>3.5517</v>
       </c>
       <c t="n" r="G40">
-        <v>39.1797</v>
+        <v>39.9466</v>
       </c>
       <c t="n" r="H40">
-        <v>840.4288</v>
+        <v>141.6417</v>
+      </c>
+      <c t="n" r="I40">
+        <v>260.6183</v>
       </c>
     </row>
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">RGO</t>
+          <t xml:space="preserve">RG4</t>
         </is>
       </c>
       <c t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. GÖKSU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C41">
-        <v>0.6992</v>
+        <v>0.0585</v>
       </c>
       <c t="n" r="D41">
-        <v>2.0430</v>
+        <v>5.5519</v>
       </c>
       <c t="n" r="E41">
-        <v>31.1477</v>
+        <v>34.9214</v>
       </c>
       <c t="n" r="F41">
-        <v>2.6713</v>
+        <v>13.3780</v>
       </c>
       <c t="n" r="G41">
-        <v>38.6765</v>
+        <v>39.1813</v>
+      </c>
+      <c t="n" r="H41">
+        <v>840.4208</v>
       </c>
     </row>
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">YD2</t>
+          <t xml:space="preserve">RGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALZAMİL KİRA GETİRİLİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. GÖKSU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C42">
-        <v>-1.2948</v>
+        <v>0.6988</v>
       </c>
       <c t="n" r="D42">
-        <v>-0.9276</v>
+        <v>2.0570</v>
       </c>
       <c t="n" r="E42">
-        <v>26.0488</v>
+        <v>30.9973</v>
       </c>
       <c t="n" r="F42">
-        <v>-0.5254</v>
+        <v>2.6779</v>
       </c>
       <c t="n" r="G42">
-        <v>38.3862</v>
-      </c>
-      <c t="n" r="H42">
-        <v>326.7953</v>
-      </c>
-      <c t="n" r="I42">
-        <v>713.2030</v>
+        <v>38.6392</v>
       </c>
     </row>
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">IKG</t>
+          <t xml:space="preserve">YD2</t>
         </is>
       </c>
       <c t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALZAMİL KİRA GETİRİLİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C43">
-        <v>1.4758</v>
+        <v>0.1743</v>
       </c>
       <c t="n" r="D43">
-        <v>4.1740</v>
+        <v>-0.9158</v>
       </c>
       <c t="n" r="E43">
-        <v>13.9114</v>
+        <v>26.0490</v>
       </c>
       <c t="n" r="F43">
-        <v>4.8406</v>
+        <v>-0.5314</v>
       </c>
       <c t="n" r="G43">
-        <v>37.4817</v>
+        <v>38.3870</v>
       </c>
       <c t="n" r="H43">
-        <v>179.6011</v>
+        <v>326.7696</v>
       </c>
       <c t="n" r="I43">
-        <v>415.6494</v>
+        <v>713.1541</v>
       </c>
     </row>
     <row r="44">
       <c t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">DIG</t>
+          <t xml:space="preserve">IKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C44">
-        <v>2.8614</v>
+        <v>1.4499</v>
       </c>
       <c t="n" r="D44">
-        <v>7.0419</v>
+        <v>4.0769</v>
       </c>
       <c t="n" r="E44">
-        <v>15.3162</v>
+        <v>13.9003</v>
       </c>
       <c t="n" r="F44">
-        <v>8.3550</v>
+        <v>4.8805</v>
       </c>
       <c t="n" r="G44">
-        <v>35.8256</v>
+        <v>37.4649</v>
+      </c>
+      <c t="n" r="H44">
+        <v>179.7077</v>
+      </c>
+      <c t="n" r="I44">
+        <v>415.2882</v>
       </c>
     </row>
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">RP1</t>
+          <t xml:space="preserve">FNR</t>
         </is>
       </c>
       <c t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NOVADA URFA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C45">
-        <v>-0.0780</v>
+        <v>1.8954</v>
       </c>
       <c t="n" r="D45">
-        <v>-0.4220</v>
+        <v>-3.5150</v>
       </c>
       <c t="n" r="E45">
-        <v>32.6748</v>
+        <v>12.7535</v>
       </c>
       <c t="n" r="F45">
-        <v>-0.4745</v>
+        <v>2.7331</v>
       </c>
       <c t="n" r="G45">
-        <v>35.5651</v>
-      </c>
-      <c t="n" r="H45">
-        <v>243.3390</v>
-      </c>
-      <c t="n" r="I45">
-        <v>921.6593</v>
+        <v>36.4797</v>
       </c>
     </row>
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">FNR</t>
+          <t xml:space="preserve">DIG</t>
         </is>
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C46">
-        <v>1.2663</v>
+        <v>2.6555</v>
       </c>
       <c t="n" r="D46">
-        <v>-3.2651</v>
+        <v>7.1034</v>
       </c>
       <c t="n" r="E46">
-        <v>12.6633</v>
+        <v>15.3222</v>
       </c>
       <c t="n" r="F46">
-        <v>3.9502</v>
+        <v>8.4513</v>
       </c>
       <c t="n" r="G46">
-        <v>35.3651</v>
+        <v>35.8034</v>
       </c>
     </row>
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">NNP</t>
+          <t xml:space="preserve">RP1</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AVANTAJ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NOVADA URFA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C47">
-        <v>0.5225</v>
+        <v>0.7267</v>
       </c>
       <c t="n" r="D47">
-        <v>1.8066</v>
+        <v>-0.4204</v>
       </c>
       <c t="n" r="E47">
-        <v>26.8985</v>
+        <v>32.6750</v>
       </c>
       <c t="n" r="F47">
-        <v>2.1981</v>
+        <v>-0.4751</v>
       </c>
       <c t="n" r="G47">
-        <v>34.8507</v>
+        <v>35.5652</v>
       </c>
       <c t="n" r="H47">
-        <v>575.4866</v>
+        <v>243.3369</v>
+      </c>
+      <c t="n" r="I47">
+        <v>921.6733</v>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">RGK</t>
+          <t xml:space="preserve">NNP</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AVANTAJ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C48">
-        <v>-0.0227</v>
+        <v>0.5373</v>
       </c>
       <c t="n" r="D48">
-        <v>-0.1091</v>
+        <v>1.8263</v>
       </c>
       <c t="n" r="E48">
-        <v>34.0426</v>
+        <v>26.8428</v>
       </c>
       <c t="n" r="F48">
-        <v>-0.1146</v>
+        <v>2.2291</v>
       </c>
       <c t="n" r="G48">
-        <v>34.5358</v>
+        <v>34.8617</v>
+      </c>
+      <c t="n" r="H48">
+        <v>575.6918</v>
       </c>
     </row>
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">FNI</t>
+          <t xml:space="preserve">RGK</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C49">
-        <v>0.5321</v>
+        <v>-0.0238</v>
       </c>
       <c t="n" r="D49">
-        <v>1.5474</v>
+        <v>-0.1064</v>
       </c>
       <c t="n" r="E49">
-        <v>28.4866</v>
+        <v>34.0422</v>
       </c>
       <c t="n" r="F49">
-        <v>1.5162</v>
+        <v>-0.1148</v>
       </c>
       <c t="n" r="G49">
-        <v>33.8580</v>
+        <v>34.5360</v>
       </c>
     </row>
     <row r="50">
@@ -1657,22 +1657,22 @@
         </is>
       </c>
       <c t="n" r="C50">
-        <v>0.2669</v>
+        <v>0.2648</v>
       </c>
       <c t="n" r="D50">
-        <v>0.7670</v>
+        <v>0.7756</v>
       </c>
       <c t="n" r="E50">
-        <v>31.5218</v>
+        <v>31.5228</v>
       </c>
       <c t="n" r="F50">
-        <v>1.1060</v>
+        <v>1.1046</v>
       </c>
       <c t="n" r="G50">
-        <v>33.0211</v>
+        <v>33.0224</v>
       </c>
       <c t="n" r="H50">
-        <v>316.3573</v>
+        <v>316.3517</v>
       </c>
     </row>
     <row r="51">
@@ -1687,22 +1687,22 @@
         </is>
       </c>
       <c t="n" r="C51">
-        <v>0.4447</v>
+        <v>0.1039</v>
       </c>
       <c t="n" r="D51">
-        <v>0.4847</v>
+        <v>0.4855</v>
       </c>
       <c t="n" r="E51">
         <v>10.4440</v>
       </c>
       <c t="n" r="F51">
-        <v>0.1185</v>
+        <v>0.1184</v>
       </c>
       <c t="n" r="G51">
-        <v>32.2867</v>
+        <v>32.2871</v>
       </c>
       <c t="n" r="H51">
-        <v>302.6300</v>
+        <v>302.6295</v>
       </c>
     </row>
     <row r="52">
@@ -1717,139 +1717,139 @@
         </is>
       </c>
       <c t="n" r="C52">
-        <v>-0.0082</v>
+        <v>-0.0074</v>
       </c>
       <c t="n" r="D52">
-        <v>-0.1987</v>
+        <v>-0.1903</v>
       </c>
       <c t="n" r="E52">
-        <v>32.8701</v>
+        <v>32.8738</v>
       </c>
       <c t="n" r="F52">
         <v>-2.9932</v>
       </c>
       <c t="n" r="G52">
-        <v>31.7311</v>
+        <v>31.7347</v>
       </c>
       <c t="n" r="H52">
         <v>214.8775</v>
       </c>
       <c t="n" r="I52">
-        <v>684.3908</v>
+        <v>684.3909</v>
       </c>
     </row>
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">HRE</t>
+          <t xml:space="preserve">UCG</t>
         </is>
       </c>
       <c t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C53">
-        <v>2.7484</v>
+        <v>0.2136</v>
       </c>
       <c t="n" r="D53">
-        <v>4.9842</v>
+        <v>-0.5499</v>
       </c>
       <c t="n" r="E53">
-        <v>12.4251</v>
+        <v>31.2840</v>
       </c>
       <c t="n" r="F53">
-        <v>6.6733</v>
+        <v>0.0865</v>
       </c>
       <c t="n" r="G53">
-        <v>31.5234</v>
+        <v>31.5267</v>
+      </c>
+      <c t="n" r="H53">
+        <v>684.0282</v>
+      </c>
+      <c t="n" r="I53">
+        <v>1727.9586</v>
       </c>
     </row>
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">UCG</t>
+          <t xml:space="preserve">FNI</t>
         </is>
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C54">
-        <v>0.2063</v>
+        <v>-1.3398</v>
       </c>
       <c t="n" r="D54">
-        <v>-0.5541</v>
+        <v>-0.3385</v>
       </c>
       <c t="n" r="E54">
-        <v>31.2576</v>
+        <v>26.0922</v>
       </c>
       <c t="n" r="F54">
-        <v>0.0838</v>
+        <v>-0.3718</v>
       </c>
       <c t="n" r="G54">
-        <v>31.2918</v>
-      </c>
-      <c t="n" r="H54">
-        <v>684.0070</v>
-      </c>
-      <c t="n" r="I54">
-        <v>1728.1066</v>
+        <v>31.3834</v>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">GF1</t>
+          <t xml:space="preserve">TUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C55">
-        <v>0.0002</v>
+        <v>1.5560</v>
       </c>
       <c t="n" r="D55">
-        <v>0.0437</v>
+        <v>2.4362</v>
       </c>
       <c t="n" r="E55">
-        <v>28.9037</v>
+        <v>10.7089</v>
       </c>
       <c t="n" r="F55">
-        <v>0.2703</v>
+        <v>3.5765</v>
       </c>
       <c t="n" r="G55">
-        <v>31.2241</v>
+        <v>31.3608</v>
       </c>
     </row>
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">TUG</t>
+          <t xml:space="preserve">GF1</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C56">
-        <v>1.7446</v>
+        <v>-0.0009</v>
       </c>
       <c t="n" r="D56">
-        <v>2.9176</v>
+        <v>0.0542</v>
       </c>
       <c t="n" r="E56">
-        <v>10.7062</v>
+        <v>28.9011</v>
       </c>
       <c t="n" r="F56">
-        <v>3.6002</v>
+        <v>0.2724</v>
       </c>
       <c t="n" r="G56">
-        <v>31.1544</v>
+        <v>31.1940</v>
       </c>
     </row>
     <row r="57">
@@ -1864,79 +1864,79 @@
         </is>
       </c>
       <c t="n" r="C57">
-        <v>0.2266</v>
+        <v>0.2287</v>
       </c>
       <c t="n" r="D57">
-        <v>1.1000</v>
+        <v>1.1108</v>
       </c>
       <c t="n" r="E57">
-        <v>13.0135</v>
+        <v>13.0167</v>
       </c>
       <c t="n" r="F57">
-        <v>1.3577</v>
+        <v>1.3633</v>
       </c>
       <c t="n" r="G57">
-        <v>30.8928</v>
+        <v>30.8849</v>
       </c>
       <c t="n" r="H57">
-        <v>156.5005</v>
+        <v>156.5147</v>
       </c>
       <c t="n" r="I57">
-        <v>486.3049</v>
+        <v>486.4056</v>
       </c>
     </row>
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">FT1</t>
+          <t xml:space="preserve">IRG</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C58">
-        <v>0.1167</v>
+        <v>1.5230</v>
       </c>
       <c t="n" r="D58">
-        <v>0.2083</v>
+        <v>3.8909</v>
       </c>
       <c t="n" r="E58">
-        <v>5.3195</v>
+        <v>12.9697</v>
       </c>
       <c t="n" r="F58">
-        <v>0.2393</v>
+        <v>3.9621</v>
       </c>
       <c t="n" r="G58">
-        <v>30.7424</v>
+        <v>30.7040</v>
       </c>
     </row>
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">IRG</t>
+          <t xml:space="preserve">FT1</t>
         </is>
       </c>
       <c t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C59">
-        <v>1.5498</v>
+        <v>0.1088</v>
       </c>
       <c t="n" r="D59">
-        <v>3.8597</v>
+        <v>0.2221</v>
       </c>
       <c t="n" r="E59">
-        <v>12.9207</v>
+        <v>5.2132</v>
       </c>
       <c t="n" r="F59">
-        <v>3.9033</v>
+        <v>0.2460</v>
       </c>
       <c t="n" r="G59">
-        <v>30.6414</v>
+        <v>30.6168</v>
       </c>
     </row>
     <row r="60">
@@ -1951,52 +1951,52 @@
         </is>
       </c>
       <c t="n" r="C60">
-        <v>0.0773</v>
+        <v>0.0986</v>
       </c>
       <c t="n" r="D60">
-        <v>0.8884</v>
+        <v>0.9087</v>
       </c>
       <c t="n" r="E60">
-        <v>27.7164</v>
+        <v>27.6975</v>
       </c>
       <c t="n" r="F60">
-        <v>-5.9599</v>
+        <v>-5.9553</v>
       </c>
       <c t="n" r="G60">
-        <v>30.0285</v>
+        <v>30.0286</v>
       </c>
       <c t="n" r="H60">
-        <v>172.0354</v>
+        <v>172.0487</v>
       </c>
       <c t="n" r="I60">
-        <v>828.0323</v>
+        <v>828.0775</v>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">ROG</t>
+          <t xml:space="preserve">HRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C61">
-        <v>0.2344</v>
+        <v>1.4109</v>
       </c>
       <c t="n" r="D61">
-        <v>0.7720</v>
+        <v>3.7444</v>
       </c>
       <c t="n" r="E61">
-        <v>-1.0645</v>
+        <v>11.0818</v>
       </c>
       <c t="n" r="F61">
-        <v>1.0666</v>
+        <v>5.4813</v>
       </c>
       <c t="n" r="G61">
-        <v>29.6583</v>
+        <v>29.9519</v>
       </c>
     </row>
     <row r="62">
@@ -2011,607 +2011,604 @@
         </is>
       </c>
       <c t="n" r="C62">
-        <v>-1.1117</v>
+        <v>-0.5580</v>
       </c>
       <c t="n" r="D62">
-        <v>5.0673</v>
+        <v>5.2569</v>
       </c>
       <c t="n" r="E62">
-        <v>16.5335</v>
+        <v>16.6383</v>
       </c>
       <c t="n" r="F62">
-        <v>6.3359</v>
+        <v>6.5152</v>
       </c>
       <c t="n" r="G62">
-        <v>29.4195</v>
+        <v>29.7510</v>
       </c>
     </row>
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">AG6</t>
+          <t xml:space="preserve">ROG</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C63">
-        <v>0.1278</v>
+        <v>0.2296</v>
       </c>
       <c t="n" r="D63">
-        <v>0.3605</v>
+        <v>0.7773</v>
       </c>
       <c t="n" r="E63">
-        <v>28.6683</v>
+        <v>-1.0616</v>
       </c>
       <c t="n" r="F63">
-        <v>0.3375</v>
+        <v>1.0703</v>
       </c>
       <c t="n" r="G63">
-        <v>29.1367</v>
-      </c>
-      <c t="n" r="H63">
-        <v>231.8189</v>
-      </c>
-      <c t="n" r="I63">
-        <v>353.6605</v>
+        <v>29.6632</v>
       </c>
     </row>
     <row r="64">
       <c t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">IUL</t>
+          <t xml:space="preserve">AG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İNAN 3 ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C64">
-        <v>0.3529</v>
+        <v>0.1179</v>
       </c>
       <c t="n" r="D64">
-        <v>0.7027</v>
+        <v>0.3609</v>
       </c>
       <c t="n" r="E64">
-        <v>26.7295</v>
+        <v>28.6669</v>
       </c>
       <c t="n" r="F64">
-        <v>2.4647</v>
+        <v>0.3427</v>
       </c>
       <c t="n" r="G64">
-        <v>28.7789</v>
+        <v>29.1351</v>
+      </c>
+      <c t="n" r="H64">
+        <v>231.8359</v>
+      </c>
+      <c t="n" r="I64">
+        <v>353.6836</v>
       </c>
     </row>
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">RMO</t>
+          <t xml:space="preserve">IUL</t>
         </is>
       </c>
       <c t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. MONO PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İNAN 3 ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C65">
-        <v>-0.0183</v>
+        <v>0.3119</v>
       </c>
       <c t="n" r="D65">
-        <v>-0.0587</v>
+        <v>0.6442</v>
       </c>
       <c t="n" r="E65">
-        <v>28.1661</v>
+        <v>26.6982</v>
       </c>
       <c t="n" r="F65">
-        <v>-0.0776</v>
+        <v>2.4387</v>
       </c>
       <c t="n" r="G65">
-        <v>28.0136</v>
+        <v>28.7384</v>
       </c>
     </row>
     <row r="66">
       <c t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">OFG</t>
+          <t xml:space="preserve">RMO</t>
         </is>
       </c>
       <c t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. FORM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. MONO PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C66">
-        <v>0.5090</v>
+        <v>-0.0183</v>
       </c>
       <c t="n" r="D66">
-        <v>-1.3613</v>
+        <v>-0.0586</v>
       </c>
       <c t="n" r="E66">
-        <v>25.4615</v>
+        <v>28.1661</v>
       </c>
       <c t="n" r="F66">
-        <v>-20.3862</v>
+        <v>-0.0777</v>
       </c>
       <c t="n" r="G66">
-        <v>27.2175</v>
-      </c>
-      <c t="n" r="H66">
-        <v>242.8256</v>
-      </c>
-      <c t="n" r="I66">
-        <v>1974.0868</v>
+        <v>28.0134</v>
       </c>
     </row>
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">RP7</t>
+          <t xml:space="preserve">UKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. TURESİF GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. KONUT ALFA KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C67">
-        <v>-2.2928</v>
+        <v>1.5273</v>
       </c>
       <c t="n" r="D67">
-        <v>-1.1784</v>
+        <v>4.1590</v>
       </c>
       <c t="n" r="E67">
-        <v>25.5677</v>
+        <v>16.2291</v>
       </c>
       <c t="n" r="F67">
-        <v>-0.3169</v>
+        <v>4.3788</v>
       </c>
       <c t="n" r="G67">
-        <v>26.1290</v>
+        <v>27.7929</v>
       </c>
       <c t="n" r="H67">
-        <v>49.1221</v>
+        <v>134.8991</v>
       </c>
       <c t="n" r="I67">
-        <v>980.8419</v>
+        <v>635575.0232</v>
       </c>
     </row>
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">UNC</t>
+          <t xml:space="preserve">OFG</t>
         </is>
       </c>
       <c t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. FORM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C68">
-        <v>0.4237</v>
+        <v>0.5054</v>
       </c>
       <c t="n" r="D68">
-        <v>1.7880</v>
+        <v>-1.3496</v>
       </c>
       <c t="n" r="E68">
-        <v>8.7390</v>
+        <v>25.3930</v>
       </c>
       <c t="n" r="F68">
-        <v>1.7384</v>
+        <v>-20.3872</v>
       </c>
       <c t="n" r="G68">
-        <v>25.8338</v>
+        <v>27.2299</v>
       </c>
       <c t="n" r="H68">
-        <v>76.5555</v>
+        <v>242.8212</v>
+      </c>
+      <c t="n" r="I68">
+        <v>1974.0601</v>
       </c>
     </row>
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">NUY</t>
+          <t xml:space="preserve">IDG</t>
         </is>
       </c>
       <c t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C69">
-        <v>-2.2596</v>
+        <v>0.9803</v>
       </c>
       <c t="n" r="D69">
-        <v>0.0540</v>
+        <v>3.4492</v>
       </c>
       <c t="n" r="E69">
-        <v>17.0676</v>
+        <v>17.4518</v>
       </c>
       <c t="n" r="F69">
-        <v>0.9928</v>
+        <v>4.8818</v>
       </c>
       <c t="n" r="G69">
-        <v>25.8214</v>
+        <v>26.7226</v>
+      </c>
+      <c t="n" r="H69">
+        <v>219.9005</v>
+      </c>
+      <c t="n" r="I69">
+        <v>501.7437</v>
       </c>
     </row>
     <row r="70">
       <c t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">IDG</t>
+          <t xml:space="preserve">RP7</t>
         </is>
       </c>
       <c t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. TURESİF GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C70">
-        <v>0.2968</v>
+        <v>-2.3018</v>
       </c>
       <c t="n" r="D70">
-        <v>2.7197</v>
+        <v>-1.1787</v>
       </c>
       <c t="n" r="E70">
-        <v>16.6172</v>
+        <v>25.5642</v>
       </c>
       <c t="n" r="F70">
-        <v>4.1153</v>
+        <v>-0.3200</v>
       </c>
       <c t="n" r="G70">
-        <v>25.8197</v>
+        <v>26.1253</v>
       </c>
       <c t="n" r="H70">
-        <v>217.5628</v>
+        <v>49.1174</v>
       </c>
       <c t="n" r="I70">
-        <v>496.5295</v>
+        <v>980.8078</v>
       </c>
     </row>
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">AG7</t>
+          <t xml:space="preserve">NUY</t>
         </is>
       </c>
       <c t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. METROPOL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C71">
-        <v>4.2164</v>
+        <v>-2.3162</v>
       </c>
       <c t="n" r="D71">
-        <v>4.9755</v>
+        <v>0.0602</v>
       </c>
       <c t="n" r="E71">
-        <v>14.2769</v>
+        <v>17.0667</v>
       </c>
       <c t="n" r="F71">
-        <v>1.0041</v>
+        <v>1.0151</v>
       </c>
       <c t="n" r="G71">
-        <v>25.3690</v>
-      </c>
-      <c t="n" r="H71">
-        <v>331.4125</v>
-      </c>
-      <c t="n" r="I71">
-        <v>836.6347</v>
+        <v>25.8253</v>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">NUZ</t>
+          <t xml:space="preserve">UNC</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C72">
-        <v>1.2812</v>
+        <v>0.4176</v>
       </c>
       <c t="n" r="D72">
-        <v>3.5636</v>
+        <v>1.8032</v>
       </c>
       <c t="n" r="E72">
-        <v>-0.4795</v>
+        <v>8.7373</v>
       </c>
       <c t="n" r="F72">
-        <v>3.9649</v>
+        <v>1.7377</v>
       </c>
       <c t="n" r="G72">
-        <v>25.2488</v>
+        <v>25.8251</v>
       </c>
       <c t="n" r="H72">
-        <v>161.6189</v>
+        <v>76.5544</v>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">IVB</t>
+          <t xml:space="preserve">AG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ SANAYİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. METROPOL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C73">
-        <v>0.3977</v>
+        <v>4.2487</v>
       </c>
       <c t="n" r="D73">
-        <v>-0.1074</v>
+        <v>4.9747</v>
       </c>
       <c t="n" r="E73">
-        <v>23.2022</v>
+        <v>14.2790</v>
       </c>
       <c t="n" r="F73">
-        <v>-0.1196</v>
+        <v>1.0222</v>
       </c>
       <c t="n" r="G73">
-        <v>24.9217</v>
+        <v>25.3836</v>
+      </c>
+      <c t="n" r="H73">
+        <v>331.4897</v>
+      </c>
+      <c t="n" r="I73">
+        <v>836.8025</v>
       </c>
     </row>
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">ZUG</t>
+          <t xml:space="preserve">NUZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C74">
-        <v>-0.0942</v>
+        <v>1.3007</v>
       </c>
       <c t="n" r="D74">
-        <v>-0.3015</v>
+        <v>3.6512</v>
       </c>
       <c t="n" r="E74">
-        <v>25.3038</v>
+        <v>-0.3829</v>
       </c>
       <c t="n" r="F74">
-        <v>-0.0143</v>
+        <v>4.0740</v>
       </c>
       <c t="n" r="G74">
-        <v>24.8233</v>
+        <v>25.3603</v>
       </c>
       <c t="n" r="H74">
-        <v>199.1958</v>
-      </c>
-      <c t="n" r="I74">
-        <v>400.1090</v>
+        <v>161.8937</v>
       </c>
     </row>
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">UKA</t>
+          <t xml:space="preserve">ZUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. KONUT ALFA KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C75">
-        <v>1.7298</v>
+        <v>-0.1382</v>
       </c>
       <c t="n" r="D75">
-        <v>4.1458</v>
+        <v>-0.2993</v>
       </c>
       <c t="n" r="E75">
-        <v>16.2124</v>
+        <v>25.3040</v>
       </c>
       <c t="n" r="F75">
-        <v>4.3532</v>
+        <v>-0.0159</v>
       </c>
       <c t="n" r="G75">
-        <v>24.7429</v>
+        <v>25.2635</v>
       </c>
       <c t="n" r="H75">
-        <v>134.8414</v>
+        <v>199.1912</v>
       </c>
       <c t="n" r="I75">
-        <v>635418.9018</v>
+        <v>400.1168</v>
       </c>
     </row>
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">RG6</t>
+          <t xml:space="preserve">IVB</t>
         </is>
       </c>
       <c t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İZMİR TARİHİ KEMERALTI GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ SANAYİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C76">
-        <v>-2.3824</v>
+        <v>0.3970</v>
       </c>
       <c t="n" r="D76">
-        <v>-2.2648</v>
+        <v>-0.0946</v>
       </c>
       <c t="n" r="E76">
-        <v>8.0266</v>
+        <v>23.1983</v>
       </c>
       <c t="n" r="F76">
-        <v>-2.7092</v>
+        <v>-0.1202</v>
       </c>
       <c t="n" r="G76">
-        <v>24.6115</v>
-      </c>
-      <c t="n" r="H76">
-        <v>148.7657</v>
+        <v>24.9231</v>
       </c>
     </row>
     <row r="77">
       <c t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">RP3</t>
+          <t xml:space="preserve">RG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRUPA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İZMİR TARİHİ KEMERALTI GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C77">
-        <v>-2.6568</v>
+        <v>-2.4337</v>
       </c>
       <c t="n" r="D77">
-        <v>5.5918</v>
+        <v>-2.3037</v>
       </c>
       <c t="n" r="E77">
-        <v>24.7794</v>
+        <v>7.9988</v>
       </c>
       <c t="n" r="F77">
-        <v>-1.5851</v>
+        <v>-2.7617</v>
       </c>
       <c t="n" r="G77">
-        <v>23.7078</v>
+        <v>24.5522</v>
       </c>
       <c t="n" r="H77">
-        <v>253.3108</v>
-      </c>
-      <c t="n" r="I77">
-        <v>781.0074</v>
+        <v>148.6315</v>
       </c>
     </row>
     <row r="78">
       <c t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">AG5</t>
+          <t xml:space="preserve">RP3</t>
         </is>
       </c>
       <c t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DÜKKAN GAYRIMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRUPA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C78">
-        <v>6.7104</v>
+        <v>-1.2427</v>
       </c>
       <c t="n" r="D78">
-        <v>8.5107</v>
+        <v>5.5796</v>
       </c>
       <c t="n" r="E78">
-        <v>16.1464</v>
+        <v>24.7728</v>
       </c>
       <c t="n" r="F78">
-        <v>6.9221</v>
+        <v>-1.5872</v>
       </c>
       <c t="n" r="G78">
-        <v>23.0966</v>
+        <v>23.6883</v>
       </c>
       <c t="n" r="H78">
-        <v>244.2541</v>
+        <v>253.3030</v>
       </c>
       <c t="n" r="I78">
-        <v>780.9606</v>
+        <v>780.7712</v>
       </c>
     </row>
     <row r="79">
       <c t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">RG2</t>
+          <t xml:space="preserve">AG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DÜKKAN GAYRIMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C79">
-        <v>-0.1065</v>
+        <v>6.5619</v>
       </c>
       <c t="n" r="D79">
-        <v>-0.6153</v>
+        <v>8.4398</v>
       </c>
       <c t="n" r="E79">
-        <v>23.0859</v>
+        <v>16.1570</v>
       </c>
       <c t="n" r="F79">
-        <v>-0.7284</v>
+        <v>6.9360</v>
       </c>
       <c t="n" r="G79">
-        <v>21.8622</v>
+        <v>23.1964</v>
       </c>
       <c t="n" r="H79">
-        <v>171.1599</v>
+        <v>244.2988</v>
+      </c>
+      <c t="n" r="I79">
+        <v>781.0748</v>
       </c>
     </row>
     <row r="80">
       <c t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">BGY</t>
+          <t xml:space="preserve">RG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C80">
-        <v>0.3930</v>
+        <v>-0.1069</v>
       </c>
       <c t="n" r="D80">
-        <v>1.0046</v>
+        <v>-0.6140</v>
       </c>
       <c t="n" r="E80">
-        <v>3.8387</v>
+        <v>23.0853</v>
       </c>
       <c t="n" r="F80">
-        <v>1.3844</v>
+        <v>-0.7297</v>
       </c>
       <c t="n" r="G80">
-        <v>21.4795</v>
+        <v>21.8601</v>
       </c>
       <c t="n" r="H80">
-        <v>264.3263</v>
-      </c>
-      <c t="n" r="I80">
-        <v>795.6992</v>
+        <v>171.1564</v>
       </c>
     </row>
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">GGF</t>
+          <t xml:space="preserve">BGY</t>
         </is>
       </c>
       <c t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C81">
-        <v>0.9617</v>
+        <v>0.3783</v>
       </c>
       <c t="n" r="D81">
-        <v>2.7346</v>
+        <v>1.0183</v>
       </c>
       <c t="n" r="E81">
-        <v>12.0841</v>
+        <v>3.8298</v>
       </c>
       <c t="n" r="F81">
-        <v>1.7600</v>
+        <v>1.3892</v>
       </c>
       <c t="n" r="G81">
-        <v>21.3691</v>
+        <v>21.4663</v>
       </c>
       <c t="n" r="H81">
-        <v>76.9598</v>
+        <v>264.3435</v>
+      </c>
+      <c t="n" r="I81">
+        <v>795.5700</v>
       </c>
     </row>
     <row r="82">
@@ -2626,1180 +2623,1180 @@
         </is>
       </c>
       <c t="n" r="C82">
-        <v>-0.1059</v>
+        <v>-0.1058</v>
       </c>
       <c t="n" r="D82">
-        <v>-0.3085</v>
+        <v>-0.3026</v>
       </c>
       <c t="n" r="E82">
         <v>22.0980</v>
       </c>
       <c t="n" r="F82">
-        <v>-2.4743</v>
+        <v>-2.4769</v>
       </c>
       <c t="n" r="G82">
-        <v>21.2902</v>
+        <v>21.2904</v>
       </c>
       <c t="n" r="H82">
-        <v>47.1968</v>
+        <v>47.1929</v>
       </c>
     </row>
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">OGM</t>
+          <t xml:space="preserve">GGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C83">
-        <v>0.2739</v>
+        <v>0.8684</v>
       </c>
       <c t="n" r="D83">
-        <v>0.9968</v>
+        <v>2.7619</v>
       </c>
       <c t="n" r="E83">
-        <v>5.6505</v>
+        <v>12.1104</v>
       </c>
       <c t="n" r="F83">
-        <v>1.1143</v>
+        <v>1.7753</v>
       </c>
       <c t="n" r="G83">
-        <v>20.9122</v>
+        <v>21.2380</v>
       </c>
       <c t="n" r="H83">
-        <v>221.0123</v>
-      </c>
-      <c t="n" r="I83">
-        <v>989.7155</v>
+        <v>76.9864</v>
       </c>
     </row>
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">RP9</t>
+          <t xml:space="preserve">OGM</t>
         </is>
       </c>
       <c t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NEVA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C84">
-        <v>0.5484</v>
+        <v>0.2761</v>
       </c>
       <c t="n" r="D84">
-        <v>0.8263</v>
+        <v>0.9378</v>
       </c>
       <c t="n" r="E84">
-        <v>17.2972</v>
+        <v>5.6597</v>
       </c>
       <c t="n" r="F84">
-        <v>1.0168</v>
+        <v>1.1222</v>
       </c>
       <c t="n" r="G84">
-        <v>20.5652</v>
+        <v>20.9218</v>
       </c>
       <c t="n" r="H84">
-        <v>174.3699</v>
+        <v>221.0375</v>
       </c>
       <c t="n" r="I84">
-        <v>1193.5298</v>
+        <v>989.8699</v>
       </c>
     </row>
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">RR4</t>
+          <t xml:space="preserve">RP9</t>
         </is>
       </c>
       <c t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ATAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NEVA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C85">
-        <v>-1.6160</v>
+        <v>0.3867</v>
       </c>
       <c t="n" r="D85">
-        <v>0.0491</v>
+        <v>0.8316</v>
       </c>
       <c t="n" r="E85">
-        <v>16.6180</v>
+        <v>17.3064</v>
       </c>
       <c t="n" r="F85">
-        <v>0.5091</v>
+        <v>1.0238</v>
       </c>
       <c t="n" r="G85">
-        <v>20.2465</v>
+        <v>20.5962</v>
       </c>
       <c t="n" r="H85">
-        <v>368.1373</v>
+        <v>174.3889</v>
+      </c>
+      <c t="n" r="I85">
+        <v>1191.9020</v>
       </c>
     </row>
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">AZ6</t>
+          <t xml:space="preserve">RR4</t>
         </is>
       </c>
       <c t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ATAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C86">
-        <v>-0.4325</v>
+        <v>-1.6186</v>
       </c>
       <c t="n" r="D86">
-        <v>1.3799</v>
+        <v>-0.1963</v>
       </c>
       <c t="n" r="E86">
-        <v>15.4405</v>
+        <v>16.6162</v>
       </c>
       <c t="n" r="F86">
-        <v>-2.8233</v>
+        <v>0.5133</v>
       </c>
       <c t="n" r="G86">
-        <v>19.7382</v>
+        <v>20.2454</v>
       </c>
       <c t="n" r="H86">
-        <v>150.2208</v>
-      </c>
-      <c t="n" r="I86">
-        <v>418.6844</v>
+        <v>368.1567</v>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">MGA</t>
+          <t xml:space="preserve">AZ6</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C87">
-        <v>0.5108</v>
+        <v>-0.2607</v>
       </c>
       <c t="n" r="D87">
-        <v>1.2172</v>
+        <v>1.4807</v>
       </c>
       <c t="n" r="E87">
-        <v>11.5395</v>
+        <v>15.3261</v>
       </c>
       <c t="n" r="F87">
-        <v>-0.7977</v>
+        <v>-2.7909</v>
       </c>
       <c t="n" r="G87">
-        <v>19.6471</v>
+        <v>19.7343</v>
       </c>
       <c t="n" r="H87">
-        <v>151.9533</v>
+        <v>150.3044</v>
+      </c>
+      <c t="n" r="I87">
+        <v>418.8575</v>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">OG2</t>
+          <t xml:space="preserve">MGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.UFUK KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C88">
-        <v>0.1071</v>
+        <v>0.5036</v>
       </c>
       <c t="n" r="D88">
-        <v>-0.0754</v>
+        <v>1.2196</v>
       </c>
       <c t="n" r="E88">
-        <v>15.4429</v>
+        <v>11.5542</v>
       </c>
       <c t="n" r="F88">
-        <v>0.4215</v>
+        <v>-0.7844</v>
       </c>
       <c t="n" r="G88">
-        <v>19.4128</v>
+        <v>19.6569</v>
       </c>
       <c t="n" r="H88">
-        <v>116.2992</v>
-      </c>
-      <c t="n" r="I88">
-        <v>1160.1302</v>
+        <v>151.9869</v>
       </c>
     </row>
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">PGB</t>
+          <t xml:space="preserve">OG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.UFUK KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C89">
-        <v>-0.2383</v>
+        <v>0.0862</v>
       </c>
       <c t="n" r="D89">
-        <v>-0.1641</v>
+        <v>-0.0919</v>
       </c>
       <c t="n" r="E89">
-        <v>19.1445</v>
+        <v>15.4218</v>
       </c>
       <c t="n" r="F89">
-        <v>-0.0400</v>
+        <v>0.4029</v>
       </c>
       <c t="n" r="G89">
-        <v>18.8354</v>
+        <v>19.3880</v>
       </c>
       <c t="n" r="H89">
-        <v>1431.6073</v>
+        <v>116.2591</v>
+      </c>
+      <c t="n" r="I89">
+        <v>1159.8965</v>
       </c>
     </row>
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">RP2</t>
+          <t xml:space="preserve">PGB</t>
         </is>
       </c>
       <c t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C90">
-        <v>1.8041</v>
+        <v>-0.2453</v>
       </c>
       <c t="n" r="D90">
-        <v>2.1739</v>
+        <v>-0.1643</v>
       </c>
       <c t="n" r="E90">
-        <v>16.9159</v>
+        <v>19.1443</v>
       </c>
       <c t="n" r="F90">
-        <v>2.3185</v>
+        <v>-0.0392</v>
       </c>
       <c t="n" r="G90">
-        <v>18.0184</v>
+        <v>18.8349</v>
       </c>
       <c t="n" r="H90">
-        <v>143.6922</v>
-      </c>
-      <c t="n" r="I90">
-        <v>448.9734</v>
+        <v>1431.6202</v>
       </c>
     </row>
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">YD4</t>
+          <t xml:space="preserve">RP2</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C91">
-        <v>-0.6045</v>
+        <v>1.4733</v>
       </c>
       <c t="n" r="D91">
-        <v>-0.5457</v>
+        <v>2.2097</v>
       </c>
       <c t="n" r="E91">
-        <v>11.1795</v>
+        <v>16.9981</v>
       </c>
       <c t="n" r="F91">
-        <v>-0.5908</v>
+        <v>2.4226</v>
       </c>
       <c t="n" r="G91">
-        <v>17.9937</v>
+        <v>18.1204</v>
       </c>
       <c t="n" r="H91">
-        <v>245.6300</v>
+        <v>143.9400</v>
       </c>
       <c t="n" r="I91">
-        <v>1005.3322</v>
+        <v>449.4496</v>
       </c>
     </row>
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">NMC</t>
+          <t xml:space="preserve">YD4</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. M CHARM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C92">
-        <v>-1.5358</v>
+        <v>-0.6039</v>
       </c>
       <c t="n" r="D92">
-        <v>-1.0582</v>
+        <v>-0.5369</v>
       </c>
       <c t="n" r="E92">
-        <v>25.6593</v>
+        <v>11.1795</v>
       </c>
       <c t="n" r="F92">
-        <v>-0.8531</v>
+        <v>-0.5957</v>
       </c>
       <c t="n" r="G92">
-        <v>17.8192</v>
+        <v>17.9938</v>
       </c>
       <c t="n" r="H92">
-        <v>215.9932</v>
+        <v>245.6130</v>
+      </c>
+      <c t="n" r="I92">
+        <v>1013.8893</v>
       </c>
     </row>
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">NUF</t>
+          <t xml:space="preserve">NMC</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. D VİZYON GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. M CHARM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C93">
-        <v>-0.1339</v>
+        <v>-1.5460</v>
       </c>
       <c t="n" r="D93">
-        <v>-0.3933</v>
+        <v>-1.0543</v>
       </c>
       <c t="n" r="E93">
-        <v>26.9057</v>
+        <v>25.6639</v>
       </c>
       <c t="n" r="F93">
-        <v>-0.4516</v>
+        <v>-0.8530</v>
       </c>
       <c t="n" r="G93">
-        <v>17.7029</v>
+        <v>17.8222</v>
       </c>
       <c t="n" r="H93">
-        <v>775.8450</v>
+        <v>215.9936</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">YD3</t>
+          <t xml:space="preserve">NUF</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. D VİZYON GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C94">
-        <v>-0.7203</v>
+        <v>-0.1340</v>
       </c>
       <c t="n" r="D94">
-        <v>-2.0853</v>
+        <v>-0.3854</v>
       </c>
       <c t="n" r="E94">
-        <v>11.7778</v>
+        <v>26.9057</v>
       </c>
       <c t="n" r="F94">
-        <v>-2.2783</v>
+        <v>-0.4560</v>
       </c>
       <c t="n" r="G94">
-        <v>17.1057</v>
+        <v>17.7026</v>
       </c>
       <c t="n" r="H94">
-        <v>148.4616</v>
-      </c>
-      <c t="n" r="I94">
-        <v>674.7369</v>
+        <v>775.8060</v>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">ABZ</t>
+          <t xml:space="preserve">YD3</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C95">
-        <v>-0.2508</v>
+        <v>-0.7661</v>
       </c>
       <c t="n" r="D95">
-        <v>-0.2508</v>
+        <v>-2.1104</v>
       </c>
       <c t="n" r="E95">
-        <v>5.3810</v>
+        <v>11.7757</v>
       </c>
       <c t="n" r="F95">
-        <v>-0.5036</v>
+        <v>-2.2850</v>
       </c>
       <c t="n" r="G95">
-        <v>16.9179</v>
+        <v>17.1112</v>
+      </c>
+      <c t="n" r="H95">
+        <v>148.4446</v>
+      </c>
+      <c t="n" r="I95">
+        <v>654.3624</v>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">OYZ</t>
+          <t xml:space="preserve">ABZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş.BEREKET KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C96">
-        <v>-0.2045</v>
+        <v>-0.2509</v>
       </c>
       <c t="n" r="D96">
-        <v>0.5860</v>
+        <v>-0.2508</v>
       </c>
       <c t="n" r="E96">
-        <v>6.1909</v>
+        <v>5.3809</v>
       </c>
       <c t="n" r="F96">
-        <v>-0.6837</v>
+        <v>-0.5035</v>
       </c>
       <c t="n" r="G96">
-        <v>16.7654</v>
-      </c>
-      <c t="n" r="H96">
-        <v>320.7571</v>
-      </c>
-      <c t="n" r="I96">
-        <v>1601.1248</v>
+        <v>16.9177</v>
       </c>
     </row>
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">PKA</t>
+          <t xml:space="preserve">OYZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş V METROWAY KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş.BEREKET KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C97">
-        <v>-0.0088</v>
+        <v>-0.2125</v>
       </c>
       <c t="n" r="D97">
-        <v>-0.0462</v>
+        <v>0.5873</v>
       </c>
       <c t="n" r="E97">
-        <v>15.5086</v>
+        <v>6.1930</v>
       </c>
       <c t="n" r="F97">
-        <v>-0.0458</v>
+        <v>-0.6792</v>
       </c>
       <c t="n" r="G97">
-        <v>16.0178</v>
+        <v>16.7695</v>
       </c>
       <c t="n" r="H97">
-        <v>580.1468</v>
+        <v>320.7764</v>
+      </c>
+      <c t="n" r="I97">
+        <v>1601.2029</v>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">OGI</t>
+          <t xml:space="preserve">PKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş V METROWAY KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C98">
-        <v>0.3009</v>
+        <v>-0.0007</v>
       </c>
       <c t="n" r="D98">
-        <v>-0.3815</v>
+        <v>-0.0400</v>
       </c>
       <c t="n" r="E98">
-        <v>2.3233</v>
+        <v>15.5054</v>
       </c>
       <c t="n" r="F98">
-        <v>0.1584</v>
+        <v>-0.0459</v>
       </c>
       <c t="n" r="G98">
-        <v>15.7879</v>
+        <v>16.0178</v>
       </c>
       <c t="n" r="H98">
-        <v>0.6041</v>
-      </c>
-      <c t="n" r="I98">
-        <v>58.2760</v>
+        <v>580.1464</v>
       </c>
     </row>
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">NUE</t>
+          <t xml:space="preserve">OGI</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. EGÇ KONUT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C99">
-        <v>-0.0777</v>
+        <v>0.2718</v>
       </c>
       <c t="n" r="D99">
-        <v>2.5530</v>
+        <v>-0.6899</v>
       </c>
       <c t="n" r="E99">
-        <v>15.6048</v>
+        <v>2.3348</v>
       </c>
       <c t="n" r="F99">
-        <v>3.5133</v>
+        <v>0.1953</v>
       </c>
       <c t="n" r="G99">
-        <v>15.3195</v>
+        <v>15.7834</v>
       </c>
       <c t="n" r="H99">
-        <v>187.8970</v>
+        <v>0.6411</v>
+      </c>
+      <c t="n" r="I99">
+        <v>58.3343</v>
       </c>
     </row>
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">NUS</t>
+          <t xml:space="preserve">NUE</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ALTINCI KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. EGÇ KONUT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C100">
-        <v>-0.2294</v>
+        <v>0.1716</v>
       </c>
       <c t="n" r="D100">
-        <v>-0.6075</v>
+        <v>2.6387</v>
       </c>
       <c t="n" r="E100">
-        <v>16.6333</v>
+        <v>15.4465</v>
       </c>
       <c t="n" r="F100">
-        <v>-0.7009</v>
+        <v>3.5929</v>
       </c>
       <c t="n" r="G100">
-        <v>14.9605</v>
+        <v>15.3364</v>
+      </c>
+      <c t="n" r="H100">
+        <v>188.1184</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">AZ2</t>
+          <t xml:space="preserve">NUS</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ALTINCI KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C101">
-        <v>-0.1186</v>
+        <v>-0.2296</v>
       </c>
       <c t="n" r="D101">
-        <v>1.6128</v>
+        <v>-0.5952</v>
       </c>
       <c t="n" r="E101">
-        <v>4.8691</v>
+        <v>16.6335</v>
       </c>
       <c t="n" r="F101">
-        <v>1.1829</v>
+        <v>-0.7072</v>
       </c>
       <c t="n" r="G101">
-        <v>14.3545</v>
-      </c>
-      <c t="n" r="H101">
-        <v>265.9108</v>
-      </c>
-      <c t="n" r="I101">
-        <v>1193.2903</v>
+        <v>14.9611</v>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">FRG</t>
+          <t xml:space="preserve">AZ2</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C102">
-        <v>4.8590</v>
+        <v>-0.0357</v>
       </c>
       <c t="n" r="D102">
-        <v>3.2624</v>
+        <v>1.6635</v>
       </c>
       <c t="n" r="E102">
-        <v>15.3377</v>
+        <v>4.8223</v>
       </c>
       <c t="n" r="F102">
-        <v>5.0056</v>
+        <v>1.1954</v>
       </c>
       <c t="n" r="G102">
-        <v>13.9839</v>
+        <v>14.3508</v>
       </c>
       <c t="n" r="H102">
-        <v>93.8211</v>
+        <v>265.9559</v>
       </c>
       <c t="n" r="I102">
-        <v>443.7072</v>
+        <v>1193.4495</v>
       </c>
     </row>
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">RAS</t>
+          <t xml:space="preserve">FRG</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C103">
-        <v>-0.1516</v>
+        <v>3.8722</v>
       </c>
       <c t="n" r="D103">
-        <v>0.5157</v>
+        <v>3.2183</v>
       </c>
       <c t="n" r="E103">
-        <v>12.6827</v>
+        <v>15.5820</v>
       </c>
       <c t="n" r="F103">
-        <v>1.1712</v>
+        <v>5.2265</v>
       </c>
       <c t="n" r="G103">
-        <v>13.9442</v>
+        <v>14.1588</v>
       </c>
       <c t="n" r="H103">
-        <v>260.6703</v>
+        <v>94.2289</v>
       </c>
       <c t="n" r="I103">
-        <v>474.3482</v>
+        <v>444.5144</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">NG4</t>
+          <t xml:space="preserve">RAS</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C104">
-        <v>0.2363</v>
+        <v>-0.1290</v>
       </c>
       <c t="n" r="D104">
-        <v>-0.0223</v>
+        <v>0.5556</v>
       </c>
       <c t="n" r="E104">
-        <v>13.7559</v>
+        <v>12.7476</v>
       </c>
       <c t="n" r="F104">
-        <v>-0.9373</v>
+        <v>1.2165</v>
       </c>
       <c t="n" r="G104">
-        <v>13.7282</v>
+        <v>13.9857</v>
       </c>
       <c t="n" r="H104">
-        <v>225.1336</v>
+        <v>260.8319</v>
+      </c>
+      <c t="n" r="I104">
+        <v>474.6193</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">RP4</t>
+          <t xml:space="preserve">NG4</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C105">
-        <v>3.8329</v>
+        <v>0.1100</v>
       </c>
       <c t="n" r="D105">
-        <v>-5.0161</v>
+        <v>-0.0193</v>
       </c>
       <c t="n" r="E105">
-        <v>10.7305</v>
+        <v>13.7738</v>
       </c>
       <c t="n" r="F105">
-        <v>-4.2420</v>
+        <v>-0.9385</v>
       </c>
       <c t="n" r="G105">
-        <v>13.5663</v>
+        <v>13.7253</v>
       </c>
       <c t="n" r="H105">
-        <v>110.2266</v>
-      </c>
-      <c t="n" r="I105">
-        <v>364.7137</v>
+        <v>225.1295</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">RKG</t>
+          <t xml:space="preserve">RP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. NEF GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C106">
-        <v>-0.0550</v>
+        <v>3.1528</v>
       </c>
       <c t="n" r="D106">
-        <v>-0.3437</v>
+        <v>-5.0642</v>
       </c>
       <c t="n" r="E106">
-        <v>13.7144</v>
+        <v>10.7816</v>
       </c>
       <c t="n" r="F106">
-        <v>-0.5431</v>
+        <v>-4.1882</v>
       </c>
       <c t="n" r="G106">
-        <v>13.0495</v>
+        <v>13.5923</v>
       </c>
       <c t="n" r="H106">
-        <v>493.5670</v>
+        <v>110.3447</v>
+      </c>
+      <c t="n" r="I106">
+        <v>363.5625</v>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">ZVE</t>
+          <t xml:space="preserve">RKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. NEF GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C107">
-        <v>-0.0520</v>
+        <v>-0.0550</v>
       </c>
       <c t="n" r="D107">
-        <v>0.1176</v>
+        <v>-0.3419</v>
       </c>
       <c t="n" r="E107">
-        <v>-1.0681</v>
+        <v>13.7144</v>
       </c>
       <c t="n" r="F107">
-        <v>0.1064</v>
+        <v>-0.5441</v>
       </c>
       <c t="n" r="G107">
-        <v>12.9470</v>
+        <v>13.0495</v>
       </c>
       <c t="n" r="H107">
-        <v>124.4438</v>
+        <v>493.5613</v>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">ILN</t>
+          <t xml:space="preserve">ZVE</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. FOLKART BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C108">
-        <v>0.0817</v>
+        <v>-0.0491</v>
       </c>
       <c t="n" r="D108">
-        <v>2.2896</v>
+        <v>0.0620</v>
       </c>
       <c t="n" r="E108">
-        <v>3.6465</v>
+        <v>-1.1257</v>
       </c>
       <c t="n" r="F108">
-        <v>2.4754</v>
+        <v>0.0484</v>
       </c>
       <c t="n" r="G108">
-        <v>12.8084</v>
+        <v>12.8852</v>
+      </c>
+      <c t="n" r="H108">
+        <v>124.3137</v>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">OYE</t>
+          <t xml:space="preserve">ILN</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALTINCI KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. FOLKART BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C109">
-        <v>-0.3219</v>
+        <v>0.0791</v>
       </c>
       <c t="n" r="D109">
-        <v>0.6197</v>
+        <v>2.2912</v>
       </c>
       <c t="n" r="E109">
-        <v>8.8903</v>
+        <v>3.6376</v>
       </c>
       <c t="n" r="F109">
-        <v>-1.1222</v>
+        <v>2.4716</v>
       </c>
       <c t="n" r="G109">
-        <v>12.4171</v>
-      </c>
-      <c t="n" r="H109">
-        <v>201.5325</v>
-      </c>
-      <c t="n" r="I109">
-        <v>576.4153</v>
+        <v>12.7981</v>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">YG7</t>
+          <t xml:space="preserve">OYE</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALTINCI KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C110">
-        <v>0.0644</v>
+        <v>-0.3298</v>
       </c>
       <c t="n" r="D110">
-        <v>0.7484</v>
+        <v>0.6244</v>
       </c>
       <c t="n" r="E110">
-        <v>9.8355</v>
+        <v>8.8880</v>
       </c>
       <c t="n" r="F110">
-        <v>0.7577</v>
+        <v>-1.1195</v>
       </c>
       <c t="n" r="G110">
-        <v>12.2962</v>
+        <v>12.4074</v>
       </c>
       <c t="n" r="H110">
-        <v>-18.6102</v>
+        <v>201.5409</v>
+      </c>
+      <c t="n" r="I110">
+        <v>576.4341</v>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">NH2</t>
+          <t xml:space="preserve">YG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş CORNERSTONE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C111">
-        <v>0.8212</v>
+        <v>0.0644</v>
       </c>
       <c t="n" r="D111">
-        <v>2.1750</v>
+        <v>0.7602</v>
       </c>
       <c t="n" r="E111">
-        <v>11.8679</v>
+        <v>9.8288</v>
       </c>
       <c t="n" r="F111">
-        <v>3.3105</v>
+        <v>0.7498</v>
       </c>
       <c t="n" r="G111">
-        <v>11.2708</v>
+        <v>12.2456</v>
+      </c>
+      <c t="n" r="H111">
+        <v>-18.6166</v>
       </c>
     </row>
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">NUA</t>
+          <t xml:space="preserve">NH2</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. FORTİS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş CORNERSTONE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C112">
-        <v>0.0414</v>
+        <v>0.7550</v>
       </c>
       <c t="n" r="D112">
-        <v>0.4072</v>
+        <v>1.5073</v>
       </c>
       <c t="n" r="E112">
-        <v>27.6735</v>
+        <v>4.2489</v>
       </c>
       <c t="n" r="F112">
-        <v>0.3251</v>
+        <v>3.3398</v>
       </c>
       <c t="n" r="G112">
-        <v>10.5070</v>
-      </c>
-      <c t="n" r="H112">
-        <v>134.5052</v>
+        <v>11.1844</v>
       </c>
     </row>
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">NYD</t>
+          <t xml:space="preserve">NBA</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİLGE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C113">
-        <v>-1.5880</v>
+        <v>-29.6328</v>
       </c>
       <c t="n" r="D113">
-        <v>-5.1495</v>
+        <v>-32.9079</v>
       </c>
       <c t="n" r="E113">
-        <v>33.2931</v>
+        <v>1701.5923</v>
       </c>
       <c t="n" r="F113">
-        <v>-5.2048</v>
+        <v>-33.0669</v>
       </c>
       <c t="n" r="G113">
-        <v>10.4960</v>
-      </c>
-      <c t="n" r="H113">
-        <v>400.5566</v>
+        <v>10.8281</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">NBA</t>
+          <t xml:space="preserve">NYD</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİLGE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C114">
-        <v>-29.3103</v>
+        <v>-1.6295</v>
       </c>
       <c t="n" r="D114">
-        <v>-32.9237</v>
+        <v>-5.1301</v>
       </c>
       <c t="n" r="E114">
-        <v>1680.6698</v>
+        <v>33.2840</v>
       </c>
       <c t="n" r="F114">
-        <v>-33.0544</v>
+        <v>-5.2095</v>
       </c>
       <c t="n" r="G114">
-        <v>10.4182</v>
+        <v>10.4981</v>
+      </c>
+      <c t="n" r="H114">
+        <v>400.5320</v>
       </c>
     </row>
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">HDU</t>
+          <t xml:space="preserve">NUA</t>
         </is>
       </c>
       <c t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. FORTİS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C115">
-        <v>-0.0748</v>
+        <v>0.0218</v>
       </c>
       <c t="n" r="D115">
-        <v>-0.1836</v>
+        <v>0.4025</v>
       </c>
       <c t="n" r="E115">
-        <v>10.8899</v>
+        <v>27.6687</v>
       </c>
       <c t="n" r="F115">
-        <v>-0.2266</v>
+        <v>0.3144</v>
       </c>
       <c t="n" r="G115">
-        <v>10.4012</v>
+        <v>10.4934</v>
+      </c>
+      <c t="n" r="H115">
+        <v>134.4802</v>
       </c>
     </row>
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">IN9</t>
+          <t xml:space="preserve">HDU</t>
         </is>
       </c>
       <c t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. NEFES EGE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C116">
-        <v>-0.3384</v>
+        <v>-0.0752</v>
       </c>
       <c t="n" r="D116">
-        <v>-1.1970</v>
+        <v>-0.1796</v>
       </c>
       <c t="n" r="E116">
-        <v>12.3999</v>
+        <v>10.8895</v>
       </c>
       <c t="n" r="F116">
-        <v>-1.3438</v>
+        <v>-0.2286</v>
       </c>
       <c t="n" r="G116">
-        <v>10.3035</v>
+        <v>10.3990</v>
       </c>
     </row>
     <row r="117">
       <c t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">ERP</t>
+          <t xml:space="preserve">IN9</t>
         </is>
       </c>
       <c t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">QİNVEST PORTFÖY YÖNETİMİ A.Ş. RE PİE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. NEFES EGE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C117">
-        <v>0.3043</v>
+        <v>-0.3367</v>
       </c>
       <c t="n" r="D117">
-        <v>0.4967</v>
+        <v>-1.0606</v>
       </c>
       <c t="n" r="E117">
-        <v>2.1858</v>
+        <v>12.4001</v>
       </c>
       <c t="n" r="F117">
-        <v>1.1195</v>
+        <v>-1.3545</v>
       </c>
       <c t="n" r="G117">
-        <v>9.5689</v>
-      </c>
-      <c t="n" r="H117">
-        <v>129.2866</v>
-      </c>
-      <c t="n" r="I117">
-        <v>423.7863</v>
+        <v>10.3015</v>
       </c>
     </row>
     <row r="118">
       <c t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">RBG</t>
+          <t xml:space="preserve">ERP</t>
         </is>
       </c>
       <c t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">QİNVEST PORTFÖY YÖNETİMİ A.Ş. RE PİE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C118">
-        <v>0.4532</v>
+        <v>0.2981</v>
       </c>
       <c t="n" r="D118">
-        <v>1.6751</v>
+        <v>0.4165</v>
       </c>
       <c t="n" r="E118">
-        <v>6.5762</v>
+        <v>2.2218</v>
       </c>
       <c t="n" r="F118">
-        <v>1.2341</v>
+        <v>1.1193</v>
       </c>
       <c t="n" r="G118">
-        <v>9.1919</v>
+        <v>9.5678</v>
+      </c>
+      <c t="n" r="H118">
+        <v>129.2860</v>
+      </c>
+      <c t="n" r="I118">
+        <v>423.7006</v>
       </c>
     </row>
     <row r="119">
       <c t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">YG8</t>
+          <t xml:space="preserve">RBG</t>
         </is>
       </c>
       <c t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LALE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C119">
-        <v>-0.0919</v>
+        <v>0.4508</v>
       </c>
       <c t="n" r="D119">
-        <v>-0.1566</v>
+        <v>1.6811</v>
       </c>
       <c t="n" r="E119">
-        <v>9.2482</v>
+        <v>6.5833</v>
       </c>
       <c t="n" r="F119">
-        <v>-0.1299</v>
+        <v>1.2415</v>
       </c>
       <c t="n" r="G119">
-        <v>9.0252</v>
+        <v>9.1298</v>
       </c>
     </row>
     <row r="120">
       <c t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">RG9</t>
+          <t xml:space="preserve">YG8</t>
         </is>
       </c>
       <c t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN AVM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LALE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C120">
-        <v>0.2271</v>
+        <v>-0.0919</v>
       </c>
       <c t="n" r="D120">
-        <v>1.7071</v>
+        <v>-0.1557</v>
       </c>
       <c t="n" r="E120">
-        <v>8.3448</v>
+        <v>9.2434</v>
       </c>
       <c t="n" r="F120">
-        <v>1.6553</v>
+        <v>-0.1304</v>
       </c>
       <c t="n" r="G120">
-        <v>8.9313</v>
-      </c>
-      <c t="n" r="H120">
-        <v>125.0640</v>
+        <v>9.0343</v>
       </c>
     </row>
     <row r="121">
@@ -3814,136 +3811,136 @@
         </is>
       </c>
       <c t="n" r="C121">
-        <v>-0.0940</v>
+        <v>0.0346</v>
       </c>
       <c t="n" r="D121">
-        <v>-0.2431</v>
+        <v>-0.1096</v>
       </c>
       <c t="n" r="E121">
-        <v>9.0312</v>
+        <v>9.1721</v>
       </c>
       <c t="n" r="F121">
-        <v>-0.1739</v>
+        <v>-0.0469</v>
       </c>
       <c t="n" r="G121">
-        <v>8.8622</v>
+        <v>9.0042</v>
       </c>
       <c t="n" r="H121">
-        <v>253.3521</v>
+        <v>253.8019</v>
       </c>
     </row>
     <row r="122">
       <c t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">NH4</t>
+          <t xml:space="preserve">RG9</t>
         </is>
       </c>
       <c t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN AVM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C122">
-        <v>0.1927</v>
+        <v>0.2270</v>
       </c>
       <c t="n" r="D122">
-        <v>0.4627</v>
+        <v>1.7091</v>
       </c>
       <c t="n" r="E122">
-        <v>3.9950</v>
+        <v>8.3444</v>
       </c>
       <c t="n" r="F122">
-        <v>0.5519</v>
+        <v>1.6540</v>
       </c>
       <c t="n" r="G122">
-        <v>8.6342</v>
+        <v>8.9312</v>
       </c>
       <c t="n" r="H122">
-        <v>244.7833</v>
+        <v>125.0612</v>
       </c>
     </row>
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">NUI</t>
+          <t xml:space="preserve">NH4</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. TİCARİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C123">
-        <v>0.3934</v>
+        <v>0.1901</v>
       </c>
       <c t="n" r="D123">
-        <v>-1.8963</v>
+        <v>0.4696</v>
       </c>
       <c t="n" r="E123">
-        <v>7.5487</v>
+        <v>3.9955</v>
       </c>
       <c t="n" r="F123">
-        <v>-1.4192</v>
+        <v>0.5510</v>
       </c>
       <c t="n" r="G123">
-        <v>8.4598</v>
+        <v>8.6270</v>
+      </c>
+      <c t="n" r="H123">
+        <v>244.7802</v>
       </c>
     </row>
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">NRY</t>
+          <t xml:space="preserve">NUI</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ROYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. TİCARİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C124">
-        <v>-0.5108</v>
+        <v>0.3939</v>
       </c>
       <c t="n" r="D124">
-        <v>-0.7027</v>
+        <v>-1.8912</v>
       </c>
       <c t="n" r="E124">
-        <v>8.8935</v>
+        <v>7.5465</v>
       </c>
       <c t="n" r="F124">
-        <v>-0.4679</v>
+        <v>-1.4228</v>
       </c>
       <c t="n" r="G124">
-        <v>8.3771</v>
+        <v>8.4587</v>
       </c>
     </row>
     <row r="125">
       <c t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">OCH</t>
+          <t xml:space="preserve">NRY</t>
         </is>
       </c>
       <c t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. OC HEDEF GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ROYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C125">
-        <v>0.4644</v>
+        <v>-0.5119</v>
       </c>
       <c t="n" r="D125">
-        <v>0.5822</v>
+        <v>-0.6835</v>
       </c>
       <c t="n" r="E125">
-        <v>7.1057</v>
+        <v>8.8923</v>
       </c>
       <c t="n" r="F125">
-        <v>0.6625</v>
+        <v>-0.4721</v>
       </c>
       <c t="n" r="G125">
-        <v>7.7710</v>
-      </c>
-      <c t="n" r="H125">
-        <v>113.5850</v>
+        <v>8.3753</v>
       </c>
     </row>
     <row r="126">
@@ -3958,22 +3955,22 @@
         </is>
       </c>
       <c t="n" r="C126">
-        <v>-0.3530</v>
+        <v>-0.3527</v>
       </c>
       <c t="n" r="D126">
-        <v>-0.2347</v>
+        <v>-0.2293</v>
       </c>
       <c t="n" r="E126">
-        <v>12.1118</v>
+        <v>12.1098</v>
       </c>
       <c t="n" r="F126">
-        <v>-0.9744</v>
+        <v>-0.9748</v>
       </c>
       <c t="n" r="G126">
-        <v>7.6391</v>
+        <v>7.6336</v>
       </c>
       <c t="n" r="H126">
-        <v>213.9092</v>
+        <v>213.9079</v>
       </c>
     </row>
     <row r="127">
@@ -3988,139 +3985,142 @@
         </is>
       </c>
       <c t="n" r="C127">
-        <v>1.2719</v>
+        <v>1.2541</v>
       </c>
       <c t="n" r="D127">
-        <v>0.8096</v>
+        <v>0.8244</v>
       </c>
       <c t="n" r="E127">
-        <v>6.5346</v>
+        <v>6.5472</v>
       </c>
       <c t="n" r="F127">
-        <v>0.7286</v>
+        <v>0.7390</v>
       </c>
       <c t="n" r="G127">
-        <v>6.5994</v>
+        <v>6.6122</v>
       </c>
       <c t="n" r="H127">
-        <v>160.5936</v>
+        <v>160.6203</v>
       </c>
     </row>
     <row r="128">
       <c t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">RTM</t>
+          <t xml:space="preserve">OCH</t>
         </is>
       </c>
       <c t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. TM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. OC HEDEF GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C128">
-        <v>-0.3717</v>
+        <v>-0.6872</v>
       </c>
       <c t="n" r="D128">
-        <v>-0.3841</v>
+        <v>-0.5413</v>
       </c>
       <c t="n" r="E128">
-        <v>7.2274</v>
+        <v>5.9065</v>
       </c>
       <c t="n" r="F128">
-        <v>-0.3807</v>
+        <v>-0.4658</v>
       </c>
       <c t="n" r="G128">
-        <v>6.5283</v>
+        <v>6.5664</v>
       </c>
       <c t="n" r="H128">
-        <v>233.4040</v>
+        <v>111.1909</v>
       </c>
     </row>
     <row r="129">
       <c t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">RG5</t>
+          <t xml:space="preserve">RTM</t>
         </is>
       </c>
       <c t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DİCLE PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. TM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C129">
-        <v>-0.0510</v>
+        <v>-0.3717</v>
       </c>
       <c t="n" r="D129">
-        <v>-0.1440</v>
+        <v>-0.3841</v>
       </c>
       <c t="n" r="E129">
-        <v>6.6184</v>
+        <v>7.2274</v>
       </c>
       <c t="n" r="F129">
-        <v>-0.1729</v>
+        <v>-0.3807</v>
       </c>
       <c t="n" r="G129">
-        <v>6.3486</v>
+        <v>6.5282</v>
       </c>
       <c t="n" r="H129">
-        <v>305.8073</v>
+        <v>233.4040</v>
       </c>
     </row>
     <row r="130">
       <c t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">NUT</t>
+          <t xml:space="preserve">RG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. NUROL TOWER GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DİCLE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C130">
-        <v>0.1914</v>
+        <v>-0.0510</v>
       </c>
       <c t="n" r="D130">
-        <v>1.0075</v>
+        <v>-0.1416</v>
       </c>
       <c t="n" r="E130">
-        <v>13.5758</v>
+        <v>6.6182</v>
       </c>
       <c t="n" r="F130">
-        <v>1.2997</v>
+        <v>-0.1741</v>
       </c>
       <c t="n" r="G130">
-        <v>5.8434</v>
+        <v>6.3483</v>
       </c>
       <c t="n" r="H130">
-        <v>195.4761</v>
+        <v>305.8025</v>
       </c>
     </row>
     <row r="131">
       <c t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">NUP</t>
+          <t xml:space="preserve">NUT</t>
         </is>
       </c>
       <c t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. NUROL TOWER GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C131">
-        <v>-0.0642</v>
+        <v>0.2717</v>
       </c>
       <c t="n" r="D131">
-        <v>-0.1775</v>
+        <v>1.0259</v>
       </c>
       <c t="n" r="E131">
-        <v>8.3552</v>
+        <v>13.5555</v>
       </c>
       <c t="n" r="F131">
-        <v>2.1413</v>
+        <v>1.3160</v>
       </c>
       <c t="n" r="G131">
-        <v>5.3301</v>
+        <v>5.8550</v>
+      </c>
+      <c t="n" r="H131">
+        <v>195.5235</v>
       </c>
     </row>
     <row r="132">
@@ -4135,226 +4135,226 @@
         </is>
       </c>
       <c t="n" r="C132">
-        <v>0.3199</v>
+        <v>0.7058</v>
       </c>
       <c t="n" r="D132">
-        <v>1.1249</v>
+        <v>1.2885</v>
       </c>
       <c t="n" r="E132">
-        <v>11.0293</v>
+        <v>11.4611</v>
       </c>
       <c t="n" r="F132">
-        <v>1.1058</v>
+        <v>1.4977</v>
       </c>
       <c t="n" r="G132">
-        <v>5.2177</v>
+        <v>5.6201</v>
       </c>
       <c t="n" r="H132">
-        <v>153.4329</v>
+        <v>154.4152</v>
       </c>
     </row>
     <row r="133">
       <c t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">NH5</t>
+          <t xml:space="preserve">NUP</t>
         </is>
       </c>
       <c t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C133">
-        <v>1.2672</v>
+        <v>-0.0552</v>
       </c>
       <c t="n" r="D133">
-        <v>3.7304</v>
+        <v>-0.1761</v>
       </c>
       <c t="n" r="E133">
-        <v>9.6433</v>
+        <v>8.3552</v>
       </c>
       <c t="n" r="F133">
-        <v>4.4539</v>
+        <v>2.1409</v>
       </c>
       <c t="n" r="G133">
-        <v>5.0493</v>
-      </c>
-      <c t="n" r="H133">
-        <v>89.9529</v>
+        <v>5.3324</v>
       </c>
     </row>
     <row r="134">
       <c t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">NUL</t>
+          <t xml:space="preserve">NH5</t>
         </is>
       </c>
       <c t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İGC GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C134">
-        <v>0.1660</v>
+        <v>1.1580</v>
       </c>
       <c t="n" r="D134">
-        <v>-10.4920</v>
+        <v>3.7616</v>
       </c>
       <c t="n" r="E134">
-        <v>0.3246</v>
+        <v>9.7093</v>
       </c>
       <c t="n" r="F134">
-        <v>-10.4735</v>
+        <v>4.5061</v>
       </c>
       <c t="n" r="G134">
-        <v>4.7751</v>
+        <v>5.1124</v>
+      </c>
+      <c t="n" r="H134">
+        <v>90.0479</v>
       </c>
     </row>
     <row r="135">
       <c t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">HP1</t>
+          <t xml:space="preserve">NUL</t>
         </is>
       </c>
       <c t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İGC GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C135">
-        <v>-0.2317</v>
+        <v>0.1613</v>
       </c>
       <c t="n" r="D135">
-        <v>-0.6588</v>
+        <v>-10.5001</v>
       </c>
       <c t="n" r="E135">
-        <v>5.9030</v>
+        <v>0.3120</v>
       </c>
       <c t="n" r="F135">
-        <v>-0.7769</v>
+        <v>-10.4726</v>
       </c>
       <c t="n" r="G135">
-        <v>4.4800</v>
-      </c>
-      <c t="n" r="H135">
-        <v>113.8804</v>
+        <v>4.7810</v>
       </c>
     </row>
     <row r="136">
       <c t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">ORX</t>
+          <t xml:space="preserve">HP1</t>
         </is>
       </c>
       <c t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C136">
-        <v>0.0533</v>
+        <v>-0.2315</v>
       </c>
       <c t="n" r="D136">
-        <v>-0.6425</v>
+        <v>-0.6443</v>
       </c>
       <c t="n" r="E136">
-        <v>1.0633</v>
+        <v>5.9032</v>
       </c>
       <c t="n" r="F136">
-        <v>-0.5765</v>
+        <v>-0.7840</v>
       </c>
       <c t="n" r="G136">
-        <v>4.1246</v>
+        <v>4.4794</v>
       </c>
       <c t="n" r="H136">
-        <v>89.2554</v>
-      </c>
-      <c t="n" r="I136">
-        <v>58.4834</v>
+        <v>113.8651</v>
       </c>
     </row>
     <row r="137">
       <c t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">OO1</t>
+          <t xml:space="preserve">ORX</t>
         </is>
       </c>
       <c t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C137">
-        <v>-0.6103</v>
+        <v>-0.1967</v>
       </c>
       <c t="n" r="D137">
-        <v>-2.3171</v>
+        <v>-0.7679</v>
       </c>
       <c t="n" r="E137">
-        <v>-14.9031</v>
+        <v>0.8519</v>
       </c>
       <c t="n" r="F137">
-        <v>-2.5598</v>
+        <v>-0.7373</v>
       </c>
       <c t="n" r="G137">
-        <v>3.9937</v>
+        <v>4.0603</v>
+      </c>
+      <c t="n" r="H137">
+        <v>88.9494</v>
+      </c>
+      <c t="n" r="I137">
+        <v>58.2272</v>
       </c>
     </row>
     <row r="138">
       <c t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">RG7</t>
+          <t xml:space="preserve">OO1</t>
         </is>
       </c>
       <c t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş DOWNTOWN OFİS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C138">
-        <v>-0.2591</v>
+        <v>-0.6082</v>
       </c>
       <c t="n" r="D138">
-        <v>-0.8160</v>
+        <v>-2.3178</v>
       </c>
       <c t="n" r="E138">
-        <v>0.6747</v>
+        <v>-14.9118</v>
       </c>
       <c t="n" r="F138">
-        <v>-0.9788</v>
+        <v>-2.5762</v>
       </c>
       <c t="n" r="G138">
-        <v>3.4824</v>
-      </c>
-      <c t="n" r="H138">
-        <v>169.5925</v>
+        <v>3.9798</v>
       </c>
     </row>
     <row r="139">
       <c t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">NFE</t>
+          <t xml:space="preserve">RG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş DOWNTOWN OFİS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C139">
-        <v>-0.6898</v>
+        <v>-0.2666</v>
       </c>
       <c t="n" r="D139">
-        <v>-1.5348</v>
+        <v>-0.7971</v>
       </c>
       <c t="n" r="E139">
-        <v>100.3370</v>
+        <v>0.6749</v>
       </c>
       <c t="n" r="F139">
-        <v>-2.1238</v>
+        <v>-0.9844</v>
       </c>
       <c t="n" r="G139">
-        <v>3.2553</v>
+        <v>3.4819</v>
+      </c>
+      <c t="n" r="H139">
+        <v>169.5772</v>
       </c>
     </row>
     <row r="140">
@@ -4369,259 +4369,262 @@
         </is>
       </c>
       <c t="n" r="C140">
-        <v>-0.0964</v>
+        <v>-0.0974</v>
       </c>
       <c t="n" r="D140">
-        <v>-0.2727</v>
+        <v>-0.2643</v>
       </c>
       <c t="n" r="E140">
-        <v>9.4848</v>
+        <v>9.4879</v>
       </c>
       <c t="n" r="F140">
-        <v>-0.3443</v>
+        <v>-0.3464</v>
       </c>
       <c t="n" r="G140">
-        <v>3.1534</v>
+        <v>3.1538</v>
       </c>
       <c t="n" r="H140">
-        <v>121.8582</v>
+        <v>121.8537</v>
       </c>
     </row>
     <row r="141">
       <c t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">PG2</t>
+          <t xml:space="preserve">NFE</t>
         </is>
       </c>
       <c t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C141">
-        <v>-0.1860</v>
+        <v>-0.6931</v>
       </c>
       <c t="n" r="D141">
-        <v>-0.4162</v>
+        <v>-1.5239</v>
       </c>
       <c t="n" r="E141">
-        <v>16.4472</v>
+        <v>100.0832</v>
       </c>
       <c t="n" r="F141">
-        <v>-0.5843</v>
+        <v>-2.1297</v>
       </c>
       <c t="n" r="G141">
-        <v>2.9951</v>
-      </c>
-      <c t="n" r="H141">
-        <v>266.7247</v>
+        <v>3.1332</v>
       </c>
     </row>
     <row r="142">
       <c t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">NG6</t>
+          <t xml:space="preserve">PG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C142">
-        <v>1.1450</v>
+        <v>-0.1905</v>
       </c>
       <c t="n" r="D142">
-        <v>1.0248</v>
+        <v>-0.4143</v>
       </c>
       <c t="n" r="E142">
-        <v>5.0034</v>
+        <v>16.4492</v>
       </c>
       <c t="n" r="F142">
-        <v>-0.7280</v>
+        <v>-0.5822</v>
       </c>
       <c t="n" r="G142">
-        <v>2.8749</v>
+        <v>2.9973</v>
       </c>
       <c t="n" r="H142">
-        <v>266.0562</v>
+        <v>266.7326</v>
       </c>
     </row>
     <row r="143">
       <c t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">RBU</t>
+          <t xml:space="preserve">NG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C143">
-        <v>0.6625</v>
+        <v>1.1519</v>
       </c>
       <c t="n" r="D143">
-        <v>-1.9165</v>
+        <v>1.4077</v>
       </c>
       <c t="n" r="E143">
-        <v>1.9015</v>
+        <v>5.0002</v>
       </c>
       <c t="n" r="F143">
-        <v>-1.2007</v>
+        <v>-0.7228</v>
       </c>
       <c t="n" r="G143">
-        <v>2.5358</v>
+        <v>2.8685</v>
+      </c>
+      <c t="n" r="H143">
+        <v>266.0754</v>
       </c>
     </row>
     <row r="144">
       <c t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">NUC</t>
+          <t xml:space="preserve">RBU</t>
         </is>
       </c>
       <c t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. CHARM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C144">
-        <v>-0.0082</v>
+        <v>0.6628</v>
       </c>
       <c t="n" r="D144">
-        <v>-0.3223</v>
+        <v>-1.9153</v>
       </c>
       <c t="n" r="E144">
-        <v>7.8596</v>
+        <v>1.9039</v>
       </c>
       <c t="n" r="F144">
-        <v>-0.3740</v>
+        <v>-1.1981</v>
       </c>
       <c t="n" r="G144">
-        <v>2.2608</v>
-      </c>
-      <c t="n" r="H144">
-        <v>131.0065</v>
+        <v>2.5393</v>
       </c>
     </row>
     <row r="145">
       <c t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">AHR</t>
+          <t xml:space="preserve">NUC</t>
         </is>
       </c>
       <c t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ONUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. CHARM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C145">
-        <v>-1.9881</v>
+        <v>-0.0102</v>
       </c>
       <c t="n" r="D145">
-        <v>-1.6828</v>
+        <v>-0.3133</v>
       </c>
       <c t="n" r="E145">
-        <v>3.6848</v>
+        <v>7.8859</v>
       </c>
       <c t="n" r="F145">
-        <v>-1.5793</v>
+        <v>-0.3751</v>
       </c>
       <c t="n" r="G145">
-        <v>1.0922</v>
+        <v>2.2556</v>
+      </c>
+      <c t="n" r="H145">
+        <v>131.0038</v>
       </c>
     </row>
     <row r="146">
       <c t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">OKG</t>
+          <t xml:space="preserve">AHR</t>
         </is>
       </c>
       <c t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. EMLAK JET GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ONUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C146">
-        <v>-0.1292</v>
+        <v>-1.9900</v>
       </c>
       <c t="n" r="D146">
-        <v>-1.7591</v>
+        <v>-1.6825</v>
       </c>
       <c t="n" r="E146">
-        <v>2.1545</v>
+        <v>3.6854</v>
       </c>
       <c t="n" r="F146">
-        <v>-1.6360</v>
+        <v>-1.5784</v>
       </c>
       <c t="n" r="G146">
-        <v>1.0379</v>
-      </c>
-      <c t="n" r="H146">
-        <v>70.5251</v>
+        <v>1.0919</v>
       </c>
     </row>
     <row r="147">
       <c t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">RF3</t>
+          <t xml:space="preserve">OKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. EMLAK JET GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C147">
-        <v>-0.1405</v>
+        <v>-0.1461</v>
       </c>
       <c t="n" r="D147">
-        <v>-0.6473</v>
+        <v>-0.6607</v>
+      </c>
+      <c t="n" r="E147">
+        <v>2.1563</v>
       </c>
       <c t="n" r="F147">
-        <v>-0.8817</v>
+        <v>-1.6329</v>
       </c>
       <c t="n" r="G147">
-        <v>0.1342</v>
+        <v>1.0326</v>
+      </c>
+      <c t="n" r="H147">
+        <v>70.5305</v>
       </c>
     </row>
     <row r="148">
       <c t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">BKA</t>
+          <t xml:space="preserve">RF3</t>
         </is>
       </c>
       <c t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ANKA GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C148">
+        <v>-0.1937</v>
       </c>
       <c t="n" r="D148">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="E148">
-        <v>0.0000</v>
+        <v>-0.6913</v>
       </c>
       <c t="n" r="F148">
-        <v>0.0000</v>
+        <v>-0.9374</v>
       </c>
       <c t="n" r="G148">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="H148">
-        <v>0.0000</v>
+        <v>0.0270</v>
       </c>
     </row>
     <row r="149">
       <c t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">HP5</t>
+          <t xml:space="preserve">BKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ANKA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="D149">
+        <v>0.0000</v>
       </c>
       <c t="n" r="E149">
         <v>0.0000</v>
@@ -4632,16 +4635,19 @@
       <c t="n" r="G149">
         <v>0.0000</v>
       </c>
+      <c t="n" r="H149">
+        <v>0.0000</v>
+      </c>
     </row>
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">HP4</t>
+          <t xml:space="preserve">HP5</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ MASTERTÜRK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="E150">
@@ -4657,19 +4663,13 @@
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">NGA</t>
+          <t xml:space="preserve">HP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C151">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="D151">
-        <v>0.0000</v>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ MASTERTÜRK GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="E151">
         <v>0.0000</v>
@@ -4684,13 +4684,16 @@
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">NFA</t>
+          <t xml:space="preserve">NGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C152">
+        <v>0.0000</v>
       </c>
       <c t="n" r="D152">
         <v>0.0000</v>
@@ -4708,12 +4711,12 @@
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">RF1</t>
+          <t xml:space="preserve">NFA</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D153">
@@ -4732,13 +4735,22 @@
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">RDO</t>
+          <t xml:space="preserve">RF1</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN OTEL GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="D154">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="E154">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="F154">
+        <v>0.0000</v>
       </c>
       <c t="n" r="G154">
         <v>0.0000</v>
@@ -4747,12 +4759,12 @@
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">RMK</t>
+          <t xml:space="preserve">RDO</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EMLAK KATILIM YENİ EVİM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN OTEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G155">
@@ -4762,12 +4774,12 @@
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">RF2</t>
+          <t xml:space="preserve">RMK</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EMLAK KATILIM YENİ EVİM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G156">
@@ -4777,12 +4789,12 @@
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">RSM</t>
+          <t xml:space="preserve">RF2</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SMART PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G157">
@@ -4792,12 +4804,12 @@
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">RSO</t>
+          <t xml:space="preserve">RSM</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SONNE PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SMART PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G158">
@@ -4807,12 +4819,12 @@
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">RTO</t>
+          <t xml:space="preserve">RSO</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TOROS PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SONNE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G159">
@@ -4822,12 +4834,12 @@
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">RGN</t>
+          <t xml:space="preserve">RTO</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TOROS PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G160">
@@ -4837,589 +4849,577 @@
     <row r="161">
       <c t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">IIG</t>
+          <t xml:space="preserve">RGN</t>
         </is>
       </c>
       <c t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C161">
-        <v>2.1741</v>
-      </c>
-      <c t="n" r="D161">
-        <v>8.7683</v>
-      </c>
-      <c t="n" r="E161">
-        <v>17.3419</v>
-      </c>
-      <c t="n" r="F161">
-        <v>8.9341</v>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="G161">
-        <v>-0.5687</v>
-      </c>
-      <c t="n" r="H161">
-        <v>153.0464</v>
-      </c>
-      <c t="n" r="I161">
-        <v>495.8967</v>
+        <v>0.0000</v>
       </c>
     </row>
     <row r="162">
       <c t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">NUN</t>
+          <t xml:space="preserve">IIG</t>
         </is>
       </c>
       <c t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. KELEŞOĞLU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C162">
-        <v>-0.2672</v>
+        <v>2.1483</v>
       </c>
       <c t="n" r="D162">
-        <v>-0.7660</v>
+        <v>8.7752</v>
       </c>
       <c t="n" r="E162">
-        <v>-0.2641</v>
+        <v>17.4239</v>
       </c>
       <c t="n" r="F162">
-        <v>-0.8629</v>
+        <v>8.9445</v>
       </c>
       <c t="n" r="G162">
-        <v>-1.5876</v>
+        <v>-0.5607</v>
+      </c>
+      <c t="n" r="H162">
+        <v>153.0705</v>
+      </c>
+      <c t="n" r="I162">
+        <v>495.9748</v>
       </c>
     </row>
     <row r="163">
       <c t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">ZPV</t>
+          <t xml:space="preserve">NUN</t>
         </is>
       </c>
       <c t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. KELEŞOĞLU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C163">
-        <v>8.9334</v>
+        <v>-0.2674</v>
       </c>
       <c t="n" r="D163">
-        <v>8.9413</v>
+        <v>-0.7530</v>
       </c>
       <c t="n" r="E163">
-        <v>3.6057</v>
+        <v>-0.2657</v>
       </c>
       <c t="n" r="F163">
-        <v>7.6625</v>
+        <v>-0.8717</v>
       </c>
       <c t="n" r="G163">
-        <v>-5.2463</v>
-      </c>
-      <c t="n" r="H163">
-        <v>99.4944</v>
+        <v>-1.5893</v>
       </c>
     </row>
     <row r="164">
       <c t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">OO2</t>
+          <t xml:space="preserve">ZPV</t>
         </is>
       </c>
       <c t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
         </is>
       </c>
       <c t="n" r="C164">
-        <v>-2.2598</v>
+        <v>8.4215</v>
       </c>
       <c t="n" r="D164">
-        <v>-10.0843</v>
+        <v>8.4422</v>
       </c>
       <c t="n" r="E164">
-        <v>-11.8526</v>
+        <v>3.1174</v>
       </c>
       <c t="n" r="F164">
-        <v>-10.2513</v>
+        <v>7.1636</v>
       </c>
       <c t="n" r="G164">
-        <v>-7.4642</v>
+        <v>-5.7828</v>
+      </c>
+      <c t="n" r="H164">
+        <v>98.5700</v>
       </c>
     </row>
     <row r="165">
       <c t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">RYZ</t>
+          <t xml:space="preserve">OO2</t>
         </is>
       </c>
       <c t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C165">
-        <v>0.3872</v>
+        <v>-2.2629</v>
       </c>
       <c t="n" r="D165">
-        <v>-0.5688</v>
+        <v>-10.0672</v>
       </c>
       <c t="n" r="E165">
-        <v>2.4281</v>
+        <v>-11.8740</v>
       </c>
       <c t="n" r="F165">
-        <v>-0.2961</v>
+        <v>-10.2760</v>
       </c>
       <c t="n" r="G165">
-        <v>-11.4589</v>
+        <v>-7.4864</v>
       </c>
     </row>
     <row r="166">
       <c t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">RSH</t>
+          <t xml:space="preserve">RYZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SEYHAN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C166">
-        <v>0.1969</v>
+        <v>0.3874</v>
       </c>
       <c t="n" r="D166">
-        <v>4.3477</v>
+        <v>-0.5676</v>
       </c>
       <c t="n" r="E166">
-        <v>4.7756</v>
+        <v>2.4295</v>
       </c>
       <c t="n" r="F166">
-        <v>4.0889</v>
+        <v>-0.2951</v>
       </c>
       <c t="n" r="G166">
-        <v>-13.3993</v>
+        <v>-11.4573</v>
       </c>
     </row>
     <row r="167">
       <c t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">ZVD</t>
+          <t xml:space="preserve">RSH</t>
         </is>
       </c>
       <c t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SEYHAN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C167">
-        <v>-0.0368</v>
+        <v>0.1816</v>
       </c>
       <c t="n" r="D167">
-        <v>-0.1085</v>
+        <v>4.3586</v>
       </c>
       <c t="n" r="E167">
-        <v>-17.3159</v>
+        <v>4.7842</v>
       </c>
       <c t="n" r="F167">
-        <v>-0.1313</v>
+        <v>4.0964</v>
       </c>
       <c t="n" r="G167">
-        <v>-13.9672</v>
-      </c>
-      <c t="n" r="H167">
-        <v>196.4771</v>
+        <v>-13.3922</v>
       </c>
     </row>
     <row r="168">
       <c t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">YG6</t>
+          <t xml:space="preserve">ZVD</t>
         </is>
       </c>
       <c t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MANOLYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C168">
-        <v>-0.5729</v>
+        <v>-0.0369</v>
       </c>
       <c t="n" r="D168">
-        <v>-1.5635</v>
+        <v>-0.1070</v>
       </c>
       <c t="n" r="E168">
-        <v>-17.3543</v>
+        <v>-17.3162</v>
       </c>
       <c t="n" r="F168">
-        <v>-1.7673</v>
+        <v>-0.1321</v>
       </c>
       <c t="n" r="G168">
-        <v>-18.5116</v>
+        <v>-13.9675</v>
       </c>
       <c t="n" r="H168">
-        <v>-2.9822</v>
+        <v>196.4747</v>
       </c>
     </row>
     <row r="169">
       <c t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">RG8</t>
+          <t xml:space="preserve">YG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. MERİÇ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MANOLYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C169">
-        <v>0.1627</v>
+        <v>-0.5572</v>
       </c>
       <c t="n" r="D169">
-        <v>-0.5614</v>
+        <v>-1.5514</v>
       </c>
       <c t="n" r="E169">
-        <v>-17.8953</v>
+        <v>-17.3545</v>
       </c>
       <c t="n" r="F169">
-        <v>-0.0319</v>
+        <v>-1.7795</v>
       </c>
       <c t="n" r="G169">
-        <v>-18.7478</v>
+        <v>-18.4998</v>
       </c>
       <c t="n" r="H169">
-        <v>91.4276</v>
+        <v>-2.9943</v>
       </c>
     </row>
     <row r="170">
       <c t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">YG3</t>
+          <t xml:space="preserve">RG8</t>
         </is>
       </c>
       <c t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. MERİÇ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C170">
-        <v>-0.3034</v>
+        <v>0.1560</v>
       </c>
       <c t="n" r="D170">
-        <v>-0.8456</v>
+        <v>-0.5686</v>
       </c>
       <c t="n" r="E170">
-        <v>-23.3505</v>
+        <v>-17.9097</v>
       </c>
       <c t="n" r="F170">
-        <v>-0.9664</v>
+        <v>-0.0514</v>
       </c>
       <c t="n" r="G170">
-        <v>-24.4673</v>
+        <v>-18.7629</v>
       </c>
       <c t="n" r="H170">
-        <v>350.2869</v>
+        <v>91.3901</v>
       </c>
     </row>
     <row r="171">
       <c t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">REO</t>
+          <t xml:space="preserve">YG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C171">
-        <v>-0.0160</v>
+        <v>-0.3033</v>
       </c>
       <c t="n" r="D171">
-        <v>-0.0526</v>
+        <v>-0.8311</v>
       </c>
       <c t="n" r="E171">
-        <v>-0.0857</v>
+        <v>-23.3507</v>
       </c>
       <c t="n" r="F171">
-        <v>-0.0611</v>
+        <v>-0.9738</v>
       </c>
       <c t="n" r="G171">
-        <v>-24.5056</v>
+        <v>-24.4679</v>
+      </c>
+      <c t="n" r="H171">
+        <v>350.2536</v>
       </c>
     </row>
     <row r="172">
       <c t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">AZ7</t>
+          <t xml:space="preserve">REO</t>
         </is>
       </c>
       <c t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C172">
-        <v>-0.0806</v>
+        <v>-0.0160</v>
       </c>
       <c t="n" r="D172">
-        <v>-0.2705</v>
+        <v>-0.0526</v>
       </c>
       <c t="n" r="E172">
-        <v>-50.6662</v>
+        <v>-0.0858</v>
       </c>
       <c t="n" r="F172">
-        <v>-1.0433</v>
+        <v>-0.0611</v>
       </c>
       <c t="n" r="G172">
-        <v>-30.3288</v>
-      </c>
-      <c t="n" r="H172">
-        <v>71.0466</v>
-      </c>
-      <c t="n" r="I172">
-        <v>785.2178</v>
+        <v>-24.5048</v>
       </c>
     </row>
     <row r="173">
       <c t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">YG5</t>
+          <t xml:space="preserve">NGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FULYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C173">
-        <v>-0.6801</v>
+        <v>3.0055</v>
       </c>
       <c t="n" r="D173">
-        <v>-1.7494</v>
+        <v>8.9224</v>
       </c>
       <c t="n" r="E173">
-        <v>-30.4553</v>
+        <v>15.8018</v>
       </c>
       <c t="n" r="F173">
-        <v>-1.9159</v>
+        <v>12.0277</v>
       </c>
       <c t="n" r="G173">
-        <v>-30.8144</v>
-      </c>
-      <c t="n" r="H173">
-        <v>102.9416</v>
+        <v>-27.4095</v>
       </c>
     </row>
     <row r="174">
       <c t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">NGO</t>
+          <t xml:space="preserve">AZ7</t>
         </is>
       </c>
       <c t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C174">
-        <v>3.2132</v>
+        <v>-0.0841</v>
       </c>
       <c t="n" r="D174">
-        <v>10.5198</v>
+        <v>-0.2646</v>
       </c>
       <c t="n" r="E174">
-        <v>15.7405</v>
+        <v>-50.6990</v>
       </c>
       <c t="n" r="F174">
-        <v>11.9144</v>
+        <v>-1.0441</v>
       </c>
       <c t="n" r="G174">
-        <v>-33.3142</v>
+        <v>-30.3272</v>
+      </c>
+      <c t="n" r="H174">
+        <v>71.0452</v>
+      </c>
+      <c t="n" r="I174">
+        <v>785.2110</v>
       </c>
     </row>
     <row r="175">
       <c t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">NG3</t>
+          <t xml:space="preserve">YG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FULYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C175">
-        <v>-0.2068</v>
+        <v>-0.6689</v>
       </c>
       <c t="n" r="D175">
-        <v>-3.4717</v>
+        <v>-1.7385</v>
       </c>
       <c t="n" r="E175">
-        <v>5.0948</v>
+        <v>-30.4556</v>
       </c>
       <c t="n" r="F175">
-        <v>-7.3314</v>
+        <v>-1.9278</v>
       </c>
       <c t="n" r="G175">
-        <v>-40.9102</v>
+        <v>-30.8139</v>
       </c>
       <c t="n" r="H175">
-        <v>113.6751</v>
+        <v>102.9169</v>
       </c>
     </row>
     <row r="176">
       <c t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">UG2</t>
+          <t xml:space="preserve">NG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">ÜNLÜ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C176">
-        <v>-0.4437</v>
+        <v>-0.2068</v>
       </c>
       <c t="n" r="D176">
-        <v>-18.4724</v>
+        <v>-3.4590</v>
       </c>
       <c t="n" r="E176">
-        <v>-40.7932</v>
+        <v>5.0924</v>
       </c>
       <c t="n" r="F176">
-        <v>-52.0230</v>
+        <v>-7.3350</v>
       </c>
       <c t="n" r="G176">
-        <v>-41.7097</v>
+        <v>-40.9108</v>
       </c>
       <c t="n" r="H176">
-        <v>-2.7156</v>
-      </c>
-      <c t="n" r="I176">
-        <v>217.4079</v>
+        <v>113.6668</v>
       </c>
     </row>
     <row r="177">
       <c t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">NH3</t>
+          <t xml:space="preserve">UG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY  YÖNETİMİ A.Ş TÜRKAZ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ÜNLÜ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C177">
-        <v>-4.1287</v>
+        <v>-0.4420</v>
       </c>
       <c t="n" r="D177">
-        <v>-23.7561</v>
+        <v>-18.5518</v>
       </c>
       <c t="n" r="E177">
-        <v>-23.0512</v>
+        <v>-40.7908</v>
       </c>
       <c t="n" r="F177">
-        <v>-26.0841</v>
+        <v>-52.0220</v>
       </c>
       <c t="n" r="G177">
-        <v>-43.1306</v>
+        <v>-41.7084</v>
       </c>
       <c t="n" r="H177">
-        <v>40.5768</v>
+        <v>-2.7136</v>
+      </c>
+      <c t="n" r="I177">
+        <v>217.4144</v>
       </c>
     </row>
     <row r="178">
       <c t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">IY1</t>
+          <t xml:space="preserve">NH3</t>
         </is>
       </c>
       <c t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. V STATÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY  YÖNETİMİ A.Ş TÜRKAZ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C178">
-        <v>-82.7622</v>
+        <v>-0.2346</v>
       </c>
       <c t="n" r="D178">
-        <v>-83.9256</v>
+        <v>-23.7506</v>
       </c>
       <c t="n" r="E178">
-        <v>-76.2674</v>
+        <v>-23.0525</v>
       </c>
       <c t="n" r="F178">
-        <v>-83.9428</v>
+        <v>-26.0856</v>
       </c>
       <c t="n" r="G178">
-        <v>-55.5259</v>
+        <v>-43.1306</v>
+      </c>
+      <c t="n" r="H178">
+        <v>40.5741</v>
       </c>
     </row>
     <row r="179">
       <c t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">RG1</t>
+          <t xml:space="preserve">IY1</t>
         </is>
       </c>
       <c t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. YILDIZ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. V STATÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C179">
-        <v>3.4918</v>
+        <v>-82.0340</v>
       </c>
       <c t="n" r="D179">
-        <v>7.2202</v>
+        <v>-83.9343</v>
       </c>
       <c t="n" r="E179">
-        <v>-9.8764</v>
+        <v>-76.2836</v>
       </c>
       <c t="n" r="F179">
-        <v>-13.3033</v>
+        <v>-83.9548</v>
       </c>
       <c t="n" r="G179">
-        <v>-59.1857</v>
-      </c>
-      <c t="n" r="H179">
-        <v>-20.4404</v>
-      </c>
-      <c t="n" r="I179">
-        <v>332.8853</v>
+        <v>-54.8384</v>
       </c>
     </row>
     <row r="180">
       <c t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">GF3</t>
+          <t xml:space="preserve">RG1</t>
         </is>
       </c>
       <c t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. YILDIZ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C180">
-        <v>-14.9060</v>
+        <v>4.0732</v>
       </c>
       <c t="n" r="D180">
-        <v>-30.3810</v>
+        <v>7.4057</v>
       </c>
       <c t="n" r="E180">
-        <v>468.4551</v>
+        <v>-10.7678</v>
       </c>
       <c t="n" r="F180">
-        <v>-30.3981</v>
+        <v>-13.0532</v>
       </c>
       <c t="n" r="G180">
-        <v>-63.2657</v>
+        <v>-59.0689</v>
+      </c>
+      <c t="n" r="H180">
+        <v>-20.2109</v>
+      </c>
+      <c t="n" r="I180">
+        <v>334.1298</v>
       </c>
     </row>
     <row r="181">
@@ -5434,25 +5434,25 @@
         </is>
       </c>
       <c t="n" r="C181">
-        <v>-22.4190</v>
+        <v>-23.6104</v>
       </c>
       <c t="n" r="D181">
-        <v>-76.9723</v>
+        <v>-76.9761</v>
       </c>
       <c t="n" r="E181">
-        <v>-75.7922</v>
+        <v>-75.7943</v>
       </c>
       <c t="n" r="F181">
-        <v>-77.0124</v>
+        <v>-77.0165</v>
       </c>
       <c t="n" r="G181">
-        <v>-67.3198</v>
+        <v>-67.3160</v>
       </c>
       <c t="n" r="H181">
-        <v>-84.8997</v>
+        <v>-84.9025</v>
       </c>
       <c t="n" r="I181">
-        <v>-44.8404</v>
+        <v>-44.8504</v>
       </c>
     </row>
     <row r="182">
@@ -5467,679 +5467,682 @@
         </is>
       </c>
       <c t="n" r="C182">
-        <v>-2.7671</v>
+        <v>-2.6070</v>
       </c>
       <c t="n" r="D182">
-        <v>11.7026</v>
+        <v>11.4095</v>
       </c>
       <c t="n" r="E182">
-        <v>-65.5242</v>
+        <v>-65.5168</v>
       </c>
       <c t="n" r="F182">
-        <v>55.1320</v>
+        <v>55.1049</v>
       </c>
       <c t="n" r="G182">
-        <v>-67.6024</v>
+        <v>-67.5844</v>
       </c>
       <c t="n" r="H182">
-        <v>-68.8759</v>
+        <v>-68.8814</v>
       </c>
       <c t="n" r="I182">
-        <v>-16.2882</v>
+        <v>-16.3018</v>
       </c>
     </row>
     <row r="183">
       <c t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">YG2</t>
+          <t xml:space="preserve">GF3</t>
         </is>
       </c>
       <c t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYÇİÇEĞİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C183">
-        <v>-87.7193</v>
+        <v>-26.7131</v>
       </c>
       <c t="n" r="D183">
-        <v>-98.7931</v>
+        <v>-40.0275</v>
       </c>
       <c t="n" r="E183">
-        <v>-96.2567</v>
+        <v>402.6300</v>
       </c>
       <c t="n" r="F183">
-        <v>-93.9130</v>
+        <v>-40.0429</v>
       </c>
       <c t="n" r="G183">
-        <v>-99.0291</v>
-      </c>
-      <c t="n" r="H183">
-        <v>-99.9998</v>
+        <v>-68.1195</v>
       </c>
     </row>
     <row r="184">
       <c t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">MMG</t>
+          <t xml:space="preserve">YG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MEYDAN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYÇİÇEĞİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C184">
-        <v>-98.9142</v>
+        <v>-87.7193</v>
       </c>
       <c t="n" r="D184">
-        <v>-99.1449</v>
+        <v>-98.7931</v>
       </c>
       <c t="n" r="E184">
-        <v>-99.0921</v>
+        <v>-96.2567</v>
       </c>
       <c t="n" r="F184">
-        <v>-99.1524</v>
+        <v>-93.9130</v>
       </c>
       <c t="n" r="G184">
-        <v>-99.1872</v>
+        <v>-99.0291</v>
       </c>
       <c t="n" r="H184">
-        <v>-98.6105</v>
+        <v>-99.9998</v>
       </c>
     </row>
     <row r="185">
       <c t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">SGF</t>
+          <t xml:space="preserve">MMG</t>
         </is>
       </c>
       <c t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. SOFAZ ÖZEL GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MEYDAN GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C185">
+        <v>-98.9092</v>
+      </c>
+      <c t="n" r="D185">
+        <v>-99.1376</v>
+      </c>
+      <c t="n" r="E185">
+        <v>-99.0846</v>
+      </c>
+      <c t="n" r="F185">
+        <v>-99.1453</v>
+      </c>
+      <c t="n" r="G185">
+        <v>-99.1803</v>
+      </c>
+      <c t="n" r="H185">
+        <v>-98.5989</v>
       </c>
     </row>
     <row r="186">
       <c t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">NKB</t>
+          <t xml:space="preserve">SGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV BEŞİKTAŞ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. SOFAZ ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">NEV</t>
+          <t xml:space="preserve">NKB</t>
         </is>
       </c>
       <c t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV KADIKÖY KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV BEŞİKTAŞ KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">NKE</t>
+          <t xml:space="preserve">NEV</t>
         </is>
       </c>
       <c t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV KADIKÖY KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">MUG</t>
+          <t xml:space="preserve">NKE</t>
         </is>
       </c>
       <c t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C189">
-        <v>1.2398</v>
-      </c>
-      <c t="n" r="D189">
-        <v>3.1675</v>
-      </c>
-      <c t="n" r="F189">
-        <v>3.8767</v>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. NKOLAY EV KATILIM GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="190">
       <c t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">BGV</t>
+          <t xml:space="preserve">MUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C190">
+        <v>1.2794</v>
+      </c>
+      <c t="n" r="D190">
+        <v>3.2435</v>
+      </c>
+      <c t="n" r="F190">
+        <v>3.9615</v>
       </c>
     </row>
     <row r="191">
       <c t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">BGA</t>
+          <t xml:space="preserve">BGV</t>
         </is>
       </c>
       <c t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">ALLBATROSS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">AB2</t>
+          <t xml:space="preserve">BGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">ALLBATROSS PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C192">
-        <v>-17.5524</v>
-      </c>
-      <c t="n" r="D192">
-        <v>-38.5014</v>
-      </c>
-      <c t="n" r="F192">
-        <v>-41.5320</v>
+          <t xml:space="preserve">ALLBATROSS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="193">
       <c t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">AY2</t>
+          <t xml:space="preserve">AB2</t>
         </is>
       </c>
       <c t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ARVA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALLBATROSS PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C193">
-        <v>-9.9212</v>
+        <v>-17.8664</v>
       </c>
       <c t="n" r="D193">
-        <v>-63.1041</v>
+        <v>-38.0485</v>
       </c>
       <c t="n" r="F193">
-        <v>-28.2905</v>
+        <v>-41.9450</v>
       </c>
     </row>
     <row r="194">
       <c t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">BGO</t>
+          <t xml:space="preserve">AY2</t>
         </is>
       </c>
       <c t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BAHAR GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ARVA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C194">
+        <v>-10.0897</v>
+      </c>
+      <c t="n" r="D194">
+        <v>-63.0951</v>
+      </c>
+      <c t="n" r="F194">
+        <v>-28.1658</v>
       </c>
     </row>
     <row r="195">
       <c t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">TLG</t>
+          <t xml:space="preserve">BGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C195">
-        <v>1.1425</v>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BAHAR GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="196">
       <c t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">AY1</t>
+          <t xml:space="preserve">TLG</t>
         </is>
       </c>
       <c t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BMS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C196">
-        <v>0.8292</v>
-      </c>
-      <c t="n" r="D196">
-        <v>1.4821</v>
-      </c>
-      <c t="n" r="F196">
-        <v>1.8863</v>
+        <v>1.5983</v>
       </c>
     </row>
     <row r="197">
       <c t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">DGR</t>
+          <t xml:space="preserve">AY1</t>
         </is>
       </c>
       <c t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞRUL GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BMS GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C197">
+        <v>0.8272</v>
+      </c>
+      <c t="n" r="D197">
+        <v>2.0024</v>
+      </c>
+      <c t="n" r="F197">
+        <v>1.8871</v>
       </c>
     </row>
     <row r="198">
       <c t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">DRO</t>
+          <t xml:space="preserve">DGR</t>
         </is>
       </c>
       <c t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞRUL PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞRUL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">AN4</t>
+          <t xml:space="preserve">DRO</t>
         </is>
       </c>
       <c t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞRUL PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">TG2</t>
+          <t xml:space="preserve">AN4</t>
         </is>
       </c>
       <c t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">TUP</t>
+          <t xml:space="preserve">TG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. TÜRKEL BİRDALLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">UGP</t>
+          <t xml:space="preserve">TUP</t>
         </is>
       </c>
       <c t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. TÜRKEL BİRDALLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">NGC</t>
+          <t xml:space="preserve">UGP</t>
         </is>
       </c>
       <c t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">ANATOLİA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MG HARBOUR GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C203">
-        <v>1.5370</v>
-      </c>
-      <c t="n" r="D203">
-        <v>2.3321</v>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="204">
       <c t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">GYU</t>
+          <t xml:space="preserve">NGC</t>
         </is>
       </c>
       <c t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLİA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MG HARBOUR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C204">
-        <v>1.9543</v>
+        <v>1.3626</v>
       </c>
       <c t="n" r="D204">
-        <v>418.3609</v>
-      </c>
-      <c t="n" r="E204">
-        <v>460.7230</v>
-      </c>
-      <c t="n" r="F204">
-        <v>425.0171</v>
+        <v>3.0980</v>
       </c>
     </row>
     <row r="205">
       <c t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">DGG</t>
+          <t xml:space="preserve">GYU</t>
         </is>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C205">
-        <v>12.1159</v>
+        <v>1.8740</v>
       </c>
       <c t="n" r="D205">
-        <v>44.3261</v>
+        <v>418.3414</v>
       </c>
       <c t="n" r="E205">
-        <v>58.8701</v>
+        <v>460.7232</v>
       </c>
       <c t="n" r="F205">
-        <v>46.4956</v>
+        <v>425.4831</v>
       </c>
     </row>
     <row r="206">
       <c t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">OGN</t>
+          <t xml:space="preserve">DGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C206">
+        <v>12.0463</v>
+      </c>
+      <c t="n" r="D206">
+        <v>44.2053</v>
+      </c>
+      <c t="n" r="E206">
+        <v>58.7087</v>
+      </c>
+      <c t="n" r="F206">
+        <v>46.5038</v>
       </c>
     </row>
     <row r="207">
       <c t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">SGG</t>
+          <t xml:space="preserve">OGN</t>
         </is>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C207">
-        <v>-0.0472</v>
-      </c>
-      <c t="n" r="D207">
-        <v>-0.1101</v>
-      </c>
-      <c t="n" r="E207">
-        <v>19.3949</v>
-      </c>
-      <c t="n" r="F207">
-        <v>-0.1386</v>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="208">
       <c t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">YGG</t>
+          <t xml:space="preserve">SGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C208">
-        <v>-0.0155</v>
+        <v>-0.0476</v>
+      </c>
+      <c t="n" r="D208">
+        <v>-0.1076</v>
+      </c>
+      <c t="n" r="E208">
+        <v>19.3921</v>
+      </c>
+      <c t="n" r="F208">
+        <v>-0.1397</v>
       </c>
     </row>
     <row r="209">
       <c t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">BGU</t>
+          <t xml:space="preserve">YGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C209">
+        <v>-0.0180</v>
       </c>
     </row>
     <row r="210">
       <c t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">ON3</t>
+          <t xml:space="preserve">BGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C210">
-        <v>3.3780</v>
-      </c>
-      <c t="n" r="D210">
-        <v>9.0812</v>
-      </c>
-      <c t="n" r="E210">
-        <v>19.5666</v>
-      </c>
-      <c t="n" r="F210">
-        <v>10.7331</v>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="211">
       <c t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">RZ1</t>
+          <t xml:space="preserve">ON3</t>
         </is>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C211">
+        <v>3.1791</v>
+      </c>
+      <c t="n" r="D211">
+        <v>9.0955</v>
+      </c>
+      <c t="n" r="E211">
+        <v>19.5721</v>
+      </c>
+      <c t="n" r="F211">
+        <v>10.8584</v>
       </c>
     </row>
     <row r="212">
       <c t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">ONU</t>
+          <t xml:space="preserve">RZ1</t>
         </is>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C212">
-        <v>-0.1080</v>
-      </c>
-      <c t="n" r="D212">
-        <v>-0.3216</v>
-      </c>
-      <c t="n" r="F212">
-        <v>-0.3295</v>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="213">
       <c t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">BAK</t>
+          <t xml:space="preserve">ONU</t>
         </is>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BAKIRCI PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C213">
-        <v>-0.9670</v>
+        <v>-0.1077</v>
       </c>
       <c t="n" r="D213">
-        <v>6.7217</v>
+        <v>-0.3216</v>
+      </c>
+      <c t="n" r="F213">
+        <v>-0.3294</v>
       </c>
     </row>
     <row r="214">
       <c t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">BLM</t>
+          <t xml:space="preserve">BAK</t>
         </is>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BALMUMCU PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BAKIRCI PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C214">
-        <v>-0.0853</v>
+        <v>-0.9668</v>
+      </c>
+      <c t="n" r="D214">
+        <v>6.7817</v>
       </c>
     </row>
     <row r="215">
       <c t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">BNE</t>
+          <t xml:space="preserve">BLM</t>
         </is>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BENESTA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BALMUMCU PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C215">
-        <v>-0.0371</v>
-      </c>
-      <c t="n" r="D215">
-        <v>-0.0991</v>
-      </c>
-      <c t="n" r="E215">
-        <v>12.7802</v>
-      </c>
-      <c t="n" r="F215">
-        <v>-0.1150</v>
+        <v>-0.0795</v>
       </c>
     </row>
     <row r="216">
       <c t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">BN2</t>
+          <t xml:space="preserve">BNE</t>
         </is>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BENESTA-2 PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BENESTA PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C216">
-        <v>0.7985</v>
+        <v>-0.0371</v>
       </c>
       <c t="n" r="D216">
-        <v>2.7869</v>
+        <v>-0.0972</v>
       </c>
       <c t="n" r="E216">
-        <v>12.5284</v>
+        <v>12.7800</v>
       </c>
       <c t="n" r="F216">
-        <v>3.1058</v>
+        <v>-0.1161</v>
       </c>
     </row>
     <row r="217">
       <c t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">GTR</t>
+          <t xml:space="preserve">BN2</t>
         </is>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. GÖKTÜRK-3 PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. BENESTA-2 PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C217">
-        <v>-89.4236</v>
+        <v>0.7976</v>
       </c>
       <c t="n" r="D217">
-        <v>-99.8918</v>
+        <v>2.7868</v>
       </c>
       <c t="n" r="E217">
-        <v>-99.9903</v>
+        <v>12.5214</v>
       </c>
       <c t="n" r="F217">
-        <v>-99.9820</v>
+        <v>3.1051</v>
       </c>
     </row>
     <row r="218">
       <c t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">BRP</t>
+          <t xml:space="preserve">GTR</t>
         </is>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. GÖKTÜRK-3 PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C218">
+        <v>-90.7942</v>
+      </c>
+      <c t="n" r="D218">
+        <v>-99.9055</v>
+      </c>
+      <c t="n" r="E218">
+        <v>-99.9914</v>
+      </c>
+      <c t="n" r="F218">
+        <v>-99.9843</v>
       </c>
     </row>
     <row r="219">
       <c t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">ZDR</t>
+          <t xml:space="preserve">BRP</t>
         </is>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">IGJ</t>
+          <t xml:space="preserve">ZDR</t>
         </is>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C220">
-        <v>0.1076</v>
-      </c>
-      <c t="n" r="D220">
-        <v>0.1167</v>
-      </c>
-      <c t="n" r="E220">
-        <v>36.2613</v>
-      </c>
-      <c t="n" r="F220">
-        <v>0.2800</v>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="221">
@@ -6238,16 +6241,16 @@
         </is>
       </c>
       <c t="n" r="C228">
-        <v>5.6357</v>
+        <v>5.4685</v>
       </c>
       <c t="n" r="D228">
-        <v>5.7304</v>
+        <v>0.3344</v>
       </c>
       <c t="n" r="E228">
-        <v>16.4523</v>
+        <v>15.8346</v>
       </c>
       <c t="n" r="F228">
-        <v>11.3792</v>
+        <v>10.7607</v>
       </c>
     </row>
     <row r="229">
@@ -6286,16 +6289,16 @@
         </is>
       </c>
       <c t="n" r="C231">
-        <v>1.1740</v>
+        <v>0.9524</v>
       </c>
       <c t="n" r="D231">
-        <v>5.1042</v>
+        <v>5.1779</v>
       </c>
       <c t="n" r="E231">
-        <v>13.7796</v>
+        <v>13.8089</v>
       </c>
       <c t="n" r="F231">
-        <v>6.5950</v>
+        <v>6.7219</v>
       </c>
     </row>
     <row r="232">
@@ -6310,16 +6313,16 @@
         </is>
       </c>
       <c t="n" r="C232">
-        <v>3.2553</v>
+        <v>3.2309</v>
       </c>
       <c t="n" r="D232">
-        <v>9.5332</v>
+        <v>9.3349</v>
       </c>
       <c t="n" r="E232">
-        <v>20.6839</v>
+        <v>20.6913</v>
       </c>
       <c t="n" r="F232">
-        <v>11.1153</v>
+        <v>11.2313</v>
       </c>
     </row>
     <row r="233">
@@ -6334,16 +6337,16 @@
         </is>
       </c>
       <c t="n" r="C233">
-        <v>0.9775</v>
+        <v>0.9284</v>
       </c>
       <c t="n" r="D233">
-        <v>1.4492</v>
+        <v>1.6015</v>
       </c>
       <c t="n" r="E233">
-        <v>4.1955</v>
+        <v>3.9764</v>
       </c>
       <c t="n" r="F233">
-        <v>1.9827</v>
+        <v>1.9664</v>
       </c>
     </row>
     <row r="234">
@@ -6370,16 +6373,16 @@
         </is>
       </c>
       <c t="n" r="C235">
-        <v>1.2613</v>
+        <v>1.0394</v>
       </c>
       <c t="n" r="D235">
-        <v>5.1949</v>
+        <v>5.2686</v>
       </c>
       <c t="n" r="E235">
-        <v>13.8778</v>
+        <v>13.9070</v>
       </c>
       <c t="n" r="F235">
-        <v>6.6870</v>
+        <v>6.8139</v>
       </c>
     </row>
     <row r="236">
@@ -6430,13 +6433,13 @@
         </is>
       </c>
       <c t="n" r="C239">
-        <v>-1.8714</v>
+        <v>-1.8164</v>
       </c>
       <c t="n" r="D239">
-        <v>-81.8401</v>
+        <v>-81.0644</v>
       </c>
       <c t="n" r="F239">
-        <v>-84.7315</v>
+        <v>-84.7334</v>
       </c>
     </row>
     <row r="240">
@@ -6475,16 +6478,16 @@
         </is>
       </c>
       <c t="n" r="C242">
-        <v>-0.0533</v>
+        <v>-0.0534</v>
       </c>
       <c t="n" r="D242">
-        <v>-0.1435</v>
+        <v>-0.1394</v>
       </c>
       <c t="n" r="E242">
-        <v>30.4730</v>
+        <v>30.4727</v>
       </c>
       <c t="n" r="F242">
-        <v>-0.1700</v>
+        <v>-0.1716</v>
       </c>
     </row>
     <row r="243">
@@ -6499,16 +6502,16 @@
         </is>
       </c>
       <c t="n" r="C243">
-        <v>-0.0761</v>
+        <v>-0.0874</v>
       </c>
       <c t="n" r="D243">
-        <v>-0.2365</v>
+        <v>-0.2191</v>
       </c>
       <c t="n" r="E243">
-        <v>1624.7756</v>
+        <v>1624.7266</v>
       </c>
       <c t="n" r="F243">
-        <v>-0.2635</v>
+        <v>-0.2656</v>
       </c>
     </row>
     <row r="244">
@@ -6559,13 +6562,13 @@
         </is>
       </c>
       <c t="n" r="C247">
-        <v>-5.7159</v>
+        <v>-5.9494</v>
       </c>
       <c t="n" r="D247">
-        <v>-15.3085</v>
+        <v>-14.8888</v>
       </c>
       <c t="n" r="F247">
-        <v>-16.9884</v>
+        <v>-17.1567</v>
       </c>
     </row>
     <row r="248">
@@ -6580,16 +6583,16 @@
         </is>
       </c>
       <c t="n" r="C248">
-        <v>-6.0310</v>
+        <v>-6.1543</v>
       </c>
       <c t="n" r="D248">
-        <v>-15.7450</v>
+        <v>-15.3276</v>
       </c>
       <c t="n" r="E248">
-        <v>-24.1657</v>
+        <v>-24.3582</v>
       </c>
       <c t="n" r="F248">
-        <v>-17.2743</v>
+        <v>-17.3879</v>
       </c>
     </row>
     <row r="249">
@@ -6688,16 +6691,16 @@
         </is>
       </c>
       <c t="n" r="C256">
-        <v>-87.0401</v>
+        <v>-86.0218</v>
       </c>
       <c t="n" r="D256">
-        <v>-88.5033</v>
+        <v>-88.5205</v>
       </c>
       <c t="n" r="E256">
-        <v>-75.0215</v>
+        <v>-75.0623</v>
       </c>
       <c t="n" r="F256">
-        <v>-88.5151</v>
+        <v>-88.5346</v>
       </c>
     </row>
     <row r="257">
@@ -6712,13 +6715,13 @@
         </is>
       </c>
       <c t="n" r="C257">
-        <v>-1.5023</v>
+        <v>-1.5029</v>
       </c>
       <c t="n" r="D257">
-        <v>-13.2332</v>
+        <v>-13.2578</v>
       </c>
       <c t="n" r="F257">
-        <v>-13.3271</v>
+        <v>-13.3699</v>
       </c>
     </row>
     <row r="258">
@@ -6733,16 +6736,16 @@
         </is>
       </c>
       <c t="n" r="C258">
-        <v>-5.9444</v>
+        <v>-5.9461</v>
       </c>
       <c t="n" r="D258">
-        <v>-6.4678</v>
+        <v>-6.4506</v>
       </c>
       <c t="n" r="E258">
-        <v>-9.3634</v>
+        <v>-9.3087</v>
       </c>
       <c t="n" r="F258">
-        <v>-4.5682</v>
+        <v>-4.5758</v>
       </c>
     </row>
     <row r="259">
@@ -6769,7 +6772,7 @@
         </is>
       </c>
       <c t="n" r="C260">
-        <v>3.3986</v>
+        <v>3.3239</v>
       </c>
     </row>
     <row r="261">
@@ -6784,7 +6787,7 @@
         </is>
       </c>
       <c t="n" r="C261">
-        <v>0.1274</v>
+        <v>-0.0951</v>
       </c>
     </row>
     <row r="262">
@@ -6823,7 +6826,7 @@
         </is>
       </c>
       <c t="n" r="C264">
-        <v>80.6249</v>
+        <v>80.2997</v>
       </c>
     </row>
     <row r="265">
@@ -6850,13 +6853,13 @@
         </is>
       </c>
       <c t="n" r="C266">
-        <v>2.5952</v>
+        <v>1.1333</v>
       </c>
       <c t="n" r="D266">
-        <v>6.9804</v>
+        <v>5.6990</v>
       </c>
       <c t="n" r="F266">
-        <v>8.2600</v>
+        <v>7.0011</v>
       </c>
     </row>
     <row r="267">
@@ -6871,13 +6874,13 @@
         </is>
       </c>
       <c t="n" r="C267">
-        <v>2.5975</v>
+        <v>1.0872</v>
       </c>
       <c t="n" r="D267">
-        <v>6.9599</v>
+        <v>5.6281</v>
       </c>
       <c t="n" r="F267">
-        <v>8.2397</v>
+        <v>6.9299</v>
       </c>
     </row>
     <row r="268">
@@ -6904,16 +6907,16 @@
         </is>
       </c>
       <c t="n" r="C269">
-        <v>-30.3782</v>
+        <v>-30.5196</v>
       </c>
       <c t="n" r="D269">
-        <v>-27.8811</v>
+        <v>-27.9137</v>
       </c>
       <c t="n" r="E269">
-        <v>-23.6171</v>
+        <v>-23.6951</v>
       </c>
       <c t="n" r="F269">
-        <v>-27.2020</v>
+        <v>-27.2013</v>
       </c>
     </row>
     <row r="270">
@@ -6940,16 +6943,16 @@
         </is>
       </c>
       <c t="n" r="C271">
-        <v>-0.4889</v>
+        <v>-0.4858</v>
       </c>
       <c t="n" r="D271">
-        <v>28.4047</v>
+        <v>-1.4272</v>
       </c>
       <c t="n" r="E271">
-        <v>-33.0204</v>
+        <v>-32.8953</v>
       </c>
       <c t="n" r="F271">
-        <v>95.7856</v>
+        <v>95.7660</v>
       </c>
     </row>
     <row r="272">
@@ -6964,7 +6967,7 @@
         </is>
       </c>
       <c t="n" r="C272">
-        <v>28.0639</v>
+        <v>28.5666</v>
       </c>
     </row>
     <row r="273">
@@ -6982,10 +6985,10 @@
         <v>-0.3504</v>
       </c>
       <c t="n" r="D273">
-        <v>-1.0231</v>
+        <v>-0.9014</v>
       </c>
       <c t="n" r="F273">
-        <v>-2.2959</v>
+        <v>-2.3052</v>
       </c>
     </row>
     <row r="274">
@@ -7000,16 +7003,16 @@
         </is>
       </c>
       <c t="n" r="C274">
-        <v>-74.0280</v>
+        <v>-74.1573</v>
       </c>
       <c t="n" r="D274">
-        <v>-86.1757</v>
+        <v>-86.0146</v>
       </c>
       <c t="n" r="E274">
-        <v>-40.7826</v>
+        <v>-40.2198</v>
       </c>
       <c t="n" r="F274">
-        <v>137.2743</v>
+        <v>137.2746</v>
       </c>
     </row>
     <row r="275">
@@ -7048,13 +7051,13 @@
         </is>
       </c>
       <c t="n" r="C277">
-        <v>-0.0570</v>
+        <v>-0.0648</v>
       </c>
       <c t="n" r="D277">
-        <v>-10.5767</v>
+        <v>-10.6300</v>
       </c>
       <c t="n" r="F277">
-        <v>-9.7098</v>
+        <v>-9.7109</v>
       </c>
     </row>
     <row r="278">
@@ -7081,16 +7084,16 @@
         </is>
       </c>
       <c t="n" r="C279">
-        <v>3.3693</v>
+        <v>3.1810</v>
       </c>
       <c t="n" r="D279">
-        <v>-60.8474</v>
+        <v>-59.4114</v>
       </c>
       <c t="n" r="E279">
-        <v>-99.0583</v>
+        <v>-99.0287</v>
       </c>
       <c t="n" r="F279">
-        <v>-98.1699</v>
+        <v>-98.1683</v>
       </c>
     </row>
     <row r="280">
@@ -7123,7 +7126,7 @@
         <v>0.9074</v>
       </c>
       <c t="n" r="E281">
-        <v>-97.4381</v>
+        <v>-97.2413</v>
       </c>
       <c t="n" r="F281">
         <v>0.8311</v>
@@ -7165,16 +7168,16 @@
         </is>
       </c>
       <c t="n" r="C284">
-        <v>-0.4762</v>
+        <v>-0.4877</v>
       </c>
       <c t="n" r="D284">
-        <v>-29.8280</v>
+        <v>-29.8208</v>
       </c>
       <c t="n" r="E284">
-        <v>5020.1110</v>
+        <v>5127.3903</v>
       </c>
       <c t="n" r="F284">
-        <v>12085.1221</v>
+        <v>12081.2452</v>
       </c>
     </row>
     <row r="285">
@@ -7189,13 +7192,13 @@
         </is>
       </c>
       <c t="n" r="C285">
-        <v>-0.0274</v>
+        <v>-0.0320</v>
       </c>
       <c t="n" r="D285">
-        <v>-0.0672</v>
+        <v>-0.0524</v>
       </c>
       <c t="n" r="F285">
-        <v>-0.0173</v>
+        <v>-0.0149</v>
       </c>
     </row>
     <row r="286">
@@ -7246,7 +7249,7 @@
         </is>
       </c>
       <c t="n" r="C289">
-        <v>-74.5861</v>
+        <v>-74.7812</v>
       </c>
     </row>
     <row r="290">
@@ -7273,16 +7276,16 @@
         </is>
       </c>
       <c t="n" r="C291">
-        <v>0.7328</v>
+        <v>0.5962</v>
       </c>
       <c t="n" r="D291">
-        <v>2.6979</v>
+        <v>2.6877</v>
       </c>
       <c t="n" r="E291">
-        <v>10.3280</v>
+        <v>10.3020</v>
       </c>
       <c t="n" r="F291">
-        <v>3.1448</v>
+        <v>3.1429</v>
       </c>
     </row>
     <row r="292">
@@ -7309,16 +7312,16 @@
         </is>
       </c>
       <c t="n" r="C293">
-        <v>-26.3940</v>
+        <v>-26.6958</v>
       </c>
       <c t="n" r="D293">
-        <v>-57.4130</v>
+        <v>-57.5327</v>
       </c>
       <c t="n" r="E293">
-        <v>-57.3066</v>
+        <v>-57.3908</v>
       </c>
       <c t="n" r="F293">
-        <v>-56.8114</v>
+        <v>-56.8921</v>
       </c>
     </row>
     <row r="294">
@@ -7429,16 +7432,16 @@
         </is>
       </c>
       <c t="n" r="C300">
-        <v>3.7865</v>
+        <v>3.5287</v>
       </c>
       <c t="n" r="D300">
-        <v>10.2744</v>
+        <v>10.2863</v>
       </c>
       <c t="n" r="E300">
-        <v>21.2542</v>
+        <v>21.2785</v>
       </c>
       <c t="n" r="F300">
-        <v>12.1973</v>
+        <v>12.3291</v>
       </c>
     </row>
     <row r="301">
@@ -7453,13 +7456,13 @@
         </is>
       </c>
       <c t="n" r="C301">
-        <v>3.6965</v>
+        <v>3.4389</v>
       </c>
       <c t="n" r="D301">
-        <v>9.4734</v>
+        <v>9.4795</v>
       </c>
       <c t="n" r="F301">
-        <v>11.4010</v>
+        <v>11.5330</v>
       </c>
     </row>
     <row r="302">
@@ -7486,13 +7489,13 @@
         </is>
       </c>
       <c t="n" r="C303">
-        <v>4.3246</v>
+        <v>4.1429</v>
       </c>
       <c t="n" r="D303">
-        <v>11.8559</v>
+        <v>11.8996</v>
       </c>
       <c t="n" r="F303">
-        <v>14.0116</v>
+        <v>14.1960</v>
       </c>
     </row>
     <row r="304">
@@ -7507,7 +7510,7 @@
         </is>
       </c>
       <c t="n" r="C304">
-        <v>-71.6965</v>
+        <v>-72.5167</v>
       </c>
     </row>
     <row r="305">
@@ -7522,10 +7525,10 @@
         </is>
       </c>
       <c t="n" r="C305">
-        <v>-0.0050</v>
+        <v>-0.0222</v>
       </c>
       <c t="n" r="D305">
-        <v>-0.8776</v>
+        <v>-0.8703</v>
       </c>
     </row>
     <row r="306">
@@ -7540,16 +7543,16 @@
         </is>
       </c>
       <c t="n" r="C306">
-        <v>1.2289</v>
+        <v>1.2005</v>
       </c>
       <c t="n" r="D306">
-        <v>6.0814</v>
+        <v>5.9469</v>
       </c>
       <c t="n" r="E306">
-        <v>14.5201</v>
+        <v>14.5062</v>
       </c>
       <c t="n" r="F306">
-        <v>7.2779</v>
+        <v>7.3671</v>
       </c>
     </row>
     <row r="307">
@@ -7588,16 +7591,16 @@
         </is>
       </c>
       <c t="n" r="C309">
-        <v>2.0330</v>
+        <v>1.8411</v>
       </c>
       <c t="n" r="D309">
-        <v>3.7959</v>
+        <v>3.7493</v>
       </c>
       <c t="n" r="E309">
-        <v>12.1836</v>
+        <v>12.1138</v>
       </c>
       <c t="n" r="F309">
-        <v>5.2480</v>
+        <v>5.2864</v>
       </c>
     </row>
     <row r="310">
@@ -7636,16 +7639,16 @@
         </is>
       </c>
       <c t="n" r="C312">
-        <v>-0.0778</v>
+        <v>-0.0825</v>
       </c>
       <c t="n" r="D312">
-        <v>-0.2181</v>
+        <v>-0.2103</v>
       </c>
       <c t="n" r="E312">
-        <v>0.6046</v>
+        <v>0.6039</v>
       </c>
       <c t="n" r="F312">
-        <v>-0.2442</v>
+        <v>-0.2458</v>
       </c>
     </row>
     <row r="313">
@@ -7684,16 +7687,16 @@
         </is>
       </c>
       <c t="n" r="C315">
-        <v>-0.0548</v>
+        <v>-0.0573</v>
       </c>
       <c t="n" r="D315">
-        <v>-0.1475</v>
+        <v>-0.1429</v>
       </c>
       <c t="n" r="E315">
-        <v>2.6117</v>
+        <v>2.5242</v>
       </c>
       <c t="n" r="F315">
-        <v>-0.1679</v>
+        <v>-0.1689</v>
       </c>
     </row>
     <row r="316">
@@ -7720,16 +7723,16 @@
         </is>
       </c>
       <c t="n" r="C317">
-        <v>-0.1592</v>
+        <v>-0.1593</v>
       </c>
       <c t="n" r="D317">
-        <v>-0.3507</v>
+        <v>-0.3460</v>
       </c>
       <c t="n" r="E317">
-        <v>3.0278</v>
+        <v>3.0274</v>
       </c>
       <c t="n" r="F317">
-        <v>-0.3869</v>
+        <v>-0.3893</v>
       </c>
     </row>
     <row r="318">
@@ -7744,7 +7747,7 @@
         </is>
       </c>
       <c t="n" r="C318">
-        <v>-0.1336</v>
+        <v>-0.1337</v>
       </c>
     </row>
     <row r="319">
@@ -7813,13 +7816,13 @@
         </is>
       </c>
       <c t="n" r="C323">
-        <v>-0.1126</v>
+        <v>-0.1215</v>
       </c>
       <c t="n" r="D323">
-        <v>-0.1472</v>
+        <v>-0.1366</v>
       </c>
       <c t="n" r="F323">
-        <v>-0.1272</v>
+        <v>-0.1231</v>
       </c>
     </row>
     <row r="324">
@@ -7858,7 +7861,7 @@
         </is>
       </c>
       <c t="n" r="C326">
-        <v>2.9850</v>
+        <v>2.9831</v>
       </c>
     </row>
     <row r="327">
@@ -7873,16 +7876,16 @@
         </is>
       </c>
       <c t="n" r="C327">
-        <v>0.1274</v>
+        <v>0.1062</v>
       </c>
       <c t="n" r="D327">
-        <v>0.0212</v>
+        <v>0.0000</v>
       </c>
       <c t="n" r="E327">
         <v>0.0000</v>
       </c>
       <c t="n" r="F327">
-        <v>0.1061</v>
+        <v>0.0849</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
@@ -280,22 +280,22 @@
         </is>
       </c>
       <c t="n" r="C3">
-        <v>26.8601</v>
+        <v>21.4221</v>
       </c>
       <c t="n" r="D3">
-        <v>665.8372</v>
+        <v>666.6126</v>
       </c>
       <c t="n" r="E3">
-        <v>692.4037</v>
+        <v>693.3031</v>
       </c>
       <c t="n" r="F3">
-        <v>660.2958</v>
+        <v>661.0468</v>
       </c>
       <c t="n" r="G3">
-        <v>614.0943</v>
+        <v>618.7322</v>
       </c>
       <c t="n" r="H3">
-        <v>770.8807</v>
+        <v>769.9907</v>
       </c>
     </row>
     <row r="4">
@@ -310,19 +310,19 @@
         </is>
       </c>
       <c t="n" r="C4">
-        <v>16.3595</v>
+        <v>16.1998</v>
       </c>
       <c t="n" r="D4">
-        <v>20.3966</v>
+        <v>20.4063</v>
       </c>
       <c t="n" r="E4">
-        <v>249.8548</v>
+        <v>249.5133</v>
       </c>
       <c t="n" r="F4">
-        <v>21.0922</v>
+        <v>21.1760</v>
       </c>
       <c t="n" r="G4">
-        <v>373.9360</v>
+        <v>372.9468</v>
       </c>
     </row>
     <row r="5">
@@ -337,19 +337,19 @@
         </is>
       </c>
       <c t="n" r="C5">
-        <v>0.9121</v>
+        <v>0.8944</v>
       </c>
       <c t="n" r="D5">
-        <v>2.6493</v>
+        <v>2.6309</v>
       </c>
       <c t="n" r="E5">
-        <v>27.7362</v>
+        <v>27.7408</v>
       </c>
       <c t="n" r="F5">
-        <v>3.3878</v>
+        <v>3.3942</v>
       </c>
       <c t="n" r="G5">
-        <v>361.9765</v>
+        <v>361.0086</v>
       </c>
     </row>
     <row r="6">
@@ -364,22 +364,22 @@
         </is>
       </c>
       <c t="n" r="C6">
-        <v>-0.4237</v>
+        <v>-0.3978</v>
       </c>
       <c t="n" r="D6">
-        <v>43.1449</v>
+        <v>43.1297</v>
       </c>
       <c t="n" r="E6">
-        <v>52.7735</v>
+        <v>52.7785</v>
       </c>
       <c t="n" r="F6">
-        <v>42.2875</v>
+        <v>42.2834</v>
       </c>
       <c t="n" r="G6">
-        <v>240.0924</v>
+        <v>240.1406</v>
       </c>
       <c t="n" r="H6">
-        <v>332.7452</v>
+        <v>332.7833</v>
       </c>
     </row>
     <row r="7">
@@ -394,22 +394,22 @@
         </is>
       </c>
       <c t="n" r="C7">
-        <v>-0.0190</v>
+        <v>-0.0178</v>
       </c>
       <c t="n" r="D7">
-        <v>-0.0481</v>
+        <v>-0.0487</v>
       </c>
       <c t="n" r="E7">
-        <v>192.5060</v>
+        <v>192.5067</v>
       </c>
       <c t="n" r="F7">
-        <v>-0.0590</v>
+        <v>-0.0600</v>
       </c>
       <c t="n" r="G7">
-        <v>191.4476</v>
+        <v>191.4496</v>
       </c>
       <c t="n" r="H7">
-        <v>166673.0297</v>
+        <v>167559.8662</v>
       </c>
     </row>
     <row r="8">
@@ -424,19 +424,19 @@
         </is>
       </c>
       <c t="n" r="C8">
-        <v>-0.0288</v>
+        <v>-0.0236</v>
       </c>
       <c t="n" r="D8">
-        <v>4.0237</v>
+        <v>3.9961</v>
       </c>
       <c t="n" r="E8">
-        <v>3.9845</v>
+        <v>3.9662</v>
       </c>
       <c t="n" r="F8">
-        <v>4.0212</v>
+        <v>4.0092</v>
       </c>
       <c t="n" r="G8">
-        <v>152.7407</v>
+        <v>152.7771</v>
       </c>
     </row>
     <row r="9">
@@ -451,19 +451,19 @@
         </is>
       </c>
       <c t="n" r="C9">
-        <v>0.7166</v>
+        <v>0.7250</v>
       </c>
       <c t="n" r="D9">
-        <v>1.0644</v>
+        <v>1.0302</v>
       </c>
       <c t="n" r="E9">
-        <v>141.4649</v>
+        <v>138.0454</v>
       </c>
       <c t="n" r="F9">
-        <v>1.5291</v>
+        <v>1.5147</v>
       </c>
       <c t="n" r="G9">
-        <v>143.2885</v>
+        <v>143.1764</v>
       </c>
     </row>
     <row r="10">
@@ -478,22 +478,22 @@
         </is>
       </c>
       <c t="n" r="C10">
-        <v>65.7066</v>
+        <v>65.6756</v>
       </c>
       <c t="n" r="D10">
-        <v>68.1813</v>
+        <v>68.1525</v>
       </c>
       <c t="n" r="E10">
-        <v>69.7796</v>
+        <v>69.7829</v>
       </c>
       <c t="n" r="F10">
-        <v>55.1377</v>
+        <v>55.1437</v>
       </c>
       <c t="n" r="G10">
-        <v>88.2491</v>
+        <v>89.8580</v>
       </c>
       <c t="n" r="H10">
-        <v>114.9143</v>
+        <v>114.9439</v>
       </c>
     </row>
     <row r="11">
@@ -508,142 +508,142 @@
         </is>
       </c>
       <c t="n" r="C11">
-        <v>1.7777</v>
+        <v>1.6764</v>
       </c>
       <c t="n" r="D11">
-        <v>2.2804</v>
+        <v>2.1812</v>
       </c>
       <c t="n" r="E11">
-        <v>76.8130</v>
+        <v>76.7665</v>
       </c>
       <c t="n" r="F11">
-        <v>33.8000</v>
+        <v>33.7759</v>
       </c>
       <c t="n" r="G11">
-        <v>82.7581</v>
+        <v>82.7379</v>
       </c>
       <c t="n" r="H11">
-        <v>299.3805</v>
+        <v>299.0342</v>
       </c>
       <c t="n" r="I11">
-        <v>1679.9848</v>
+        <v>1679.0140</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">VVF</t>
+          <t xml:space="preserve">NFG</t>
         </is>
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C12">
-        <v>0.2309</v>
+        <v>-0.1895</v>
       </c>
       <c t="n" r="D12">
-        <v>1.4164</v>
+        <v>-0.3545</v>
       </c>
       <c t="n" r="E12">
-        <v>38.6514</v>
+        <v>19.9333</v>
       </c>
       <c t="n" r="F12">
-        <v>1.3326</v>
+        <v>-1.0494</v>
       </c>
       <c t="n" r="G12">
-        <v>61.6004</v>
+        <v>61.5836</v>
       </c>
       <c t="n" r="H12">
-        <v>327.8133</v>
-      </c>
-      <c t="n" r="I12">
-        <v>1094.0639</v>
+        <v>689.8607</v>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">NFG</t>
+          <t xml:space="preserve">VVF</t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C13">
-        <v>-0.1953</v>
+        <v>0.1974</v>
       </c>
       <c t="n" r="D13">
-        <v>-0.3492</v>
+        <v>1.3982</v>
       </c>
       <c t="n" r="E13">
-        <v>19.9445</v>
+        <v>38.5630</v>
       </c>
       <c t="n" r="F13">
-        <v>-1.0431</v>
+        <v>1.3509</v>
       </c>
       <c t="n" r="G13">
-        <v>61.5713</v>
+        <v>61.3523</v>
       </c>
       <c t="n" r="H13">
-        <v>687.3739</v>
+        <v>327.8888</v>
+      </c>
+      <c t="n" r="I13">
+        <v>1094.2792</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">TNG</t>
+          <t xml:space="preserve">AR9</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TUNA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C14">
-        <v>3.6470</v>
+        <v>-0.1115</v>
       </c>
       <c t="n" r="D14">
-        <v>10.2754</v>
+        <v>0.2723</v>
       </c>
       <c t="n" r="E14">
-        <v>27.7879</v>
+        <v>60.0175</v>
       </c>
       <c t="n" r="F14">
-        <v>11.4196</v>
+        <v>-4.4647</v>
       </c>
       <c t="n" r="G14">
-        <v>58.6588</v>
+        <v>58.6185</v>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">AR9</t>
+          <t xml:space="preserve">TNG</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TUNA PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C15">
-        <v>-0.1201</v>
+        <v>3.4602</v>
       </c>
       <c t="n" r="D15">
-        <v>0.2780</v>
+        <v>10.1782</v>
       </c>
       <c t="n" r="E15">
-        <v>60.0176</v>
+        <v>27.9019</v>
       </c>
       <c t="n" r="F15">
-        <v>-4.4567</v>
+        <v>11.6387</v>
       </c>
       <c t="n" r="G15">
-        <v>58.6151</v>
+        <v>58.5935</v>
       </c>
     </row>
     <row r="16">
@@ -658,19 +658,19 @@
         </is>
       </c>
       <c t="n" r="C16">
-        <v>3.3464</v>
+        <v>3.0933</v>
       </c>
       <c t="n" r="D16">
-        <v>10.0000</v>
+        <v>9.6802</v>
       </c>
       <c t="n" r="E16">
-        <v>26.5560</v>
+        <v>26.4823</v>
       </c>
       <c t="n" r="F16">
-        <v>18.2159</v>
+        <v>18.2686</v>
       </c>
       <c t="n" r="G16">
-        <v>57.5298</v>
+        <v>57.2333</v>
       </c>
     </row>
     <row r="17">
@@ -685,133 +685,133 @@
         </is>
       </c>
       <c t="n" r="C17">
-        <v>0.7418</v>
+        <v>0.6819</v>
       </c>
       <c t="n" r="D17">
-        <v>1.9401</v>
+        <v>1.9337</v>
       </c>
       <c t="n" r="E17">
-        <v>51.3653</v>
+        <v>50.3775</v>
       </c>
       <c t="n" r="F17">
-        <v>48.1999</v>
+        <v>48.2089</v>
       </c>
       <c t="n" r="G17">
-        <v>56.1296</v>
+        <v>56.1345</v>
       </c>
       <c t="n" r="H17">
-        <v>463.8794</v>
+        <v>462.1595</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">VBI</t>
+          <t xml:space="preserve">BRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C18">
-        <v>3.7926</v>
+        <v>6.2877</v>
       </c>
       <c t="n" r="D18">
-        <v>10.5008</v>
+        <v>22.9262</v>
       </c>
       <c t="n" r="E18">
-        <v>22.2864</v>
+        <v>30.2778</v>
       </c>
       <c t="n" r="F18">
-        <v>12.2196</v>
+        <v>31.3827</v>
       </c>
       <c t="n" r="G18">
-        <v>56.0013</v>
+        <v>56.0880</v>
       </c>
     </row>
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">VIK</t>
+          <t xml:space="preserve">VBI</t>
         </is>
       </c>
       <c t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C19">
-        <v>3.7922</v>
+        <v>3.4858</v>
       </c>
       <c t="n" r="D19">
-        <v>10.4997</v>
+        <v>10.2789</v>
       </c>
       <c t="n" r="E19">
-        <v>22.2839</v>
+        <v>22.3022</v>
       </c>
       <c t="n" r="F19">
-        <v>12.2182</v>
+        <v>12.3619</v>
       </c>
       <c t="n" r="G19">
-        <v>55.9933</v>
+        <v>55.6781</v>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">OGC</t>
+          <t xml:space="preserve">VIK</t>
         </is>
       </c>
       <c t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÇATI KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C20">
-        <v>0.3123</v>
+        <v>3.4855</v>
       </c>
       <c t="n" r="D20">
-        <v>0.8794</v>
+        <v>10.2779</v>
       </c>
       <c t="n" r="E20">
-        <v>1.4049</v>
+        <v>22.2998</v>
       </c>
       <c t="n" r="F20">
-        <v>0.9557</v>
+        <v>12.3606</v>
       </c>
       <c t="n" r="G20">
-        <v>55.2876</v>
-      </c>
-      <c t="n" r="H20">
-        <v>410.6042</v>
+        <v>55.6704</v>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">RGF</t>
+          <t xml:space="preserve">OGC</t>
         </is>
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. TSL PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÇATI KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C21">
-        <v>-0.0371</v>
+        <v>0.3668</v>
       </c>
       <c t="n" r="D21">
-        <v>6.4447</v>
+        <v>0.8949</v>
       </c>
       <c t="n" r="E21">
-        <v>19.5144</v>
+        <v>1.4338</v>
       </c>
       <c t="n" r="F21">
-        <v>6.8316</v>
+        <v>0.9810</v>
       </c>
       <c t="n" r="G21">
-        <v>54.5931</v>
+        <v>55.3624</v>
+      </c>
+      <c t="n" r="H21">
+        <v>410.7320</v>
       </c>
     </row>
     <row r="22">
@@ -826,76 +826,76 @@
         </is>
       </c>
       <c t="n" r="C22">
-        <v>-0.2025</v>
+        <v>-0.2027</v>
       </c>
       <c t="n" r="D22">
-        <v>-0.2035</v>
+        <v>-0.2037</v>
       </c>
       <c t="n" r="E22">
-        <v>55.3901</v>
+        <v>55.3899</v>
       </c>
       <c t="n" r="F22">
-        <v>-0.2325</v>
+        <v>-0.2324</v>
       </c>
       <c t="n" r="G22">
-        <v>54.4091</v>
+        <v>54.4083</v>
       </c>
       <c t="n" r="H22">
-        <v>172.5230</v>
+        <v>172.5091</v>
       </c>
     </row>
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">BRE</t>
+          <t xml:space="preserve">NO1</t>
         </is>
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C23">
-        <v>4.8469</v>
+        <v>4.9457</v>
       </c>
       <c t="n" r="D23">
-        <v>21.2746</v>
+        <v>6.5394</v>
       </c>
       <c t="n" r="E23">
-        <v>28.3121</v>
+        <v>23.8809</v>
       </c>
       <c t="n" r="F23">
-        <v>29.4366</v>
+        <v>15.6687</v>
       </c>
       <c t="n" r="G23">
-        <v>54.0584</v>
+        <v>54.1613</v>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">NO1</t>
+          <t xml:space="preserve">RGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. TSL PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C24">
-        <v>3.7728</v>
+        <v>-0.0340</v>
       </c>
       <c t="n" r="D24">
-        <v>5.4273</v>
+        <v>6.3473</v>
       </c>
       <c t="n" r="E24">
-        <v>22.3522</v>
+        <v>19.4816</v>
       </c>
       <c t="n" r="F24">
-        <v>14.1231</v>
+        <v>6.8291</v>
       </c>
       <c t="n" r="G24">
-        <v>52.4576</v>
+        <v>53.9497</v>
       </c>
     </row>
     <row r="25">
@@ -910,19 +910,19 @@
         </is>
       </c>
       <c t="n" r="C25">
-        <v>0.0783</v>
+        <v>0.0431</v>
       </c>
       <c t="n" r="D25">
-        <v>0.1302</v>
+        <v>0.0676</v>
       </c>
       <c t="n" r="E25">
-        <v>36.2521</v>
+        <v>36.2240</v>
       </c>
       <c t="n" r="F25">
-        <v>0.2923</v>
+        <v>0.2766</v>
       </c>
       <c t="n" r="G25">
-        <v>51.5190</v>
+        <v>51.1363</v>
       </c>
     </row>
     <row r="26">
@@ -937,85 +937,85 @@
         </is>
       </c>
       <c t="n" r="C26">
-        <v>-0.2585</v>
+        <v>-0.2324</v>
       </c>
       <c t="n" r="D26">
-        <v>-1.4220</v>
+        <v>-1.4329</v>
       </c>
       <c t="n" r="E26">
-        <v>28.4799</v>
+        <v>28.4810</v>
       </c>
       <c t="n" r="F26">
-        <v>-1.7104</v>
+        <v>-1.7320</v>
       </c>
       <c t="n" r="G26">
-        <v>49.0671</v>
+        <v>49.0908</v>
       </c>
       <c t="n" r="H26">
-        <v>168.1687</v>
+        <v>168.1969</v>
       </c>
       <c t="n" r="I26">
-        <v>1143.5276</v>
+        <v>1143.2547</v>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">RAA</t>
+          <t xml:space="preserve">YD5</t>
         </is>
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. AVRUPA-ANADOLU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C27">
-        <v>5.1548</v>
+        <v>-0.2738</v>
       </c>
       <c t="n" r="D27">
-        <v>11.9820</v>
+        <v>-0.4395</v>
       </c>
       <c t="n" r="E27">
-        <v>21.2494</v>
+        <v>16.0251</v>
       </c>
       <c t="n" r="F27">
-        <v>13.4701</v>
+        <v>-0.6451</v>
       </c>
       <c t="n" r="G27">
-        <v>48.2441</v>
+        <v>48.1367</v>
+      </c>
+      <c t="n" r="H27">
+        <v>196.8714</v>
+      </c>
+      <c t="n" r="I27">
+        <v>1322.0985</v>
       </c>
     </row>
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">YD5</t>
+          <t xml:space="preserve">RAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. AVRUPA-ANADOLU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C28">
-        <v>-0.3114</v>
+        <v>4.8246</v>
       </c>
       <c t="n" r="D28">
-        <v>-0.4266</v>
+        <v>11.8166</v>
       </c>
       <c t="n" r="E28">
-        <v>16.0250</v>
+        <v>20.9541</v>
       </c>
       <c t="n" r="F28">
-        <v>-0.6251</v>
+        <v>13.5390</v>
       </c>
       <c t="n" r="G28">
-        <v>48.1189</v>
-      </c>
-      <c t="n" r="H28">
-        <v>196.8139</v>
-      </c>
-      <c t="n" r="I28">
-        <v>1322.3848</v>
+        <v>47.9863</v>
       </c>
     </row>
     <row r="29">
@@ -1030,223 +1030,223 @@
         </is>
       </c>
       <c t="n" r="C29">
-        <v>0.4399</v>
+        <v>0.3987</v>
       </c>
       <c t="n" r="D29">
-        <v>6.3955</v>
+        <v>6.3302</v>
       </c>
       <c t="n" r="E29">
-        <v>43.7950</v>
+        <v>43.7316</v>
       </c>
       <c t="n" r="F29">
-        <v>6.0018</v>
+        <v>5.9695</v>
       </c>
       <c t="n" r="G29">
-        <v>45.3631</v>
+        <v>45.4449</v>
       </c>
       <c t="n" r="H29">
-        <v>462.0464</v>
+        <v>464.9724</v>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">TGI</t>
+          <t xml:space="preserve">ZGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C30">
-        <v>1.5992</v>
+        <v>2.9841</v>
       </c>
       <c t="n" r="D30">
-        <v>5.0109</v>
+        <v>3.4656</v>
       </c>
       <c t="n" r="E30">
-        <v>21.9992</v>
+        <v>26.4310</v>
       </c>
       <c t="n" r="F30">
-        <v>5.6219</v>
+        <v>9.6325</v>
       </c>
       <c t="n" r="G30">
-        <v>45.3039</v>
+        <v>44.3435</v>
       </c>
     </row>
     <row r="31">
       <c t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">YYF</t>
+          <t xml:space="preserve">ZGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BGF KATILIM ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C31">
-        <v>3.2880</v>
+        <v>0.1921</v>
       </c>
       <c t="n" r="D31">
-        <v>8.9639</v>
+        <v>-0.4840</v>
       </c>
       <c t="n" r="E31">
-        <v>19.2711</v>
+        <v>29.4138</v>
       </c>
       <c t="n" r="F31">
-        <v>10.6432</v>
+        <v>1.6453</v>
       </c>
       <c t="n" r="G31">
-        <v>44.6044</v>
+        <v>44.1956</v>
       </c>
     </row>
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">ZGG</t>
+          <t xml:space="preserve">YYF</t>
         </is>
       </c>
       <c t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BGF KATILIM ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C32">
-        <v>0.1858</v>
+        <v>3.0430</v>
       </c>
       <c t="n" r="D32">
-        <v>-0.4535</v>
+        <v>8.7606</v>
       </c>
       <c t="n" r="E32">
-        <v>29.4117</v>
+        <v>19.2872</v>
       </c>
       <c t="n" r="F32">
-        <v>1.6321</v>
+        <v>10.7656</v>
       </c>
       <c t="n" r="G32">
-        <v>44.1840</v>
+        <v>44.0869</v>
       </c>
     </row>
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">ZGU</t>
+          <t xml:space="preserve">FNR</t>
         </is>
       </c>
       <c t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C33">
-        <v>1.8896</v>
+        <v>2.3096</v>
       </c>
       <c t="n" r="D33">
-        <v>2.5920</v>
+        <v>-0.9661</v>
       </c>
       <c t="n" r="E33">
-        <v>24.8284</v>
+        <v>18.6537</v>
       </c>
       <c t="n" r="F33">
-        <v>8.4279</v>
+        <v>5.3862</v>
       </c>
       <c t="n" r="G33">
-        <v>42.1900</v>
+        <v>42.1689</v>
       </c>
     </row>
     <row r="34">
       <c t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">KGB</t>
+          <t xml:space="preserve">ORV</t>
         </is>
       </c>
       <c t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AVRASYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C34">
-        <v>0.1572</v>
+        <v>-0.2375</v>
       </c>
       <c t="n" r="D34">
-        <v>0.5463</v>
+        <v>-0.1671</v>
       </c>
       <c t="n" r="E34">
-        <v>38.6423</v>
+        <v>27.3217</v>
       </c>
       <c t="n" r="F34">
-        <v>0.7286</v>
+        <v>0.1149</v>
       </c>
       <c t="n" r="G34">
-        <v>41.7498</v>
-      </c>
-      <c t="n" r="H34">
-        <v>241.8709</v>
-      </c>
-      <c t="n" r="I34">
-        <v>847.9956</v>
+        <v>41.6972</v>
       </c>
     </row>
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">ORV</t>
+          <t xml:space="preserve">RG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AVRASYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TRAKYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C35">
-        <v>-0.2280</v>
+        <v>-0.0766</v>
       </c>
       <c t="n" r="D35">
-        <v>-0.0226</v>
+        <v>-0.3341</v>
       </c>
       <c t="n" r="E35">
-        <v>27.2694</v>
+        <v>42.2740</v>
       </c>
       <c t="n" r="F35">
-        <v>0.1142</v>
+        <v>-0.5031</v>
       </c>
       <c t="n" r="G35">
-        <v>41.7094</v>
+        <v>41.6799</v>
+      </c>
+      <c t="n" r="H35">
+        <v>213.3044</v>
+      </c>
+      <c t="n" r="I35">
+        <v>723.2954</v>
       </c>
     </row>
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">RG3</t>
+          <t xml:space="preserve">KGB</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TRAKYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C36">
-        <v>-0.0792</v>
+        <v>0.1705</v>
       </c>
       <c t="n" r="D36">
-        <v>-0.3323</v>
+        <v>0.5235</v>
       </c>
       <c t="n" r="E36">
-        <v>42.2744</v>
+        <v>38.6409</v>
       </c>
       <c t="n" r="F36">
-        <v>-0.5004</v>
+        <v>0.7113</v>
       </c>
       <c t="n" r="G36">
-        <v>41.6786</v>
+        <v>41.6711</v>
       </c>
       <c t="n" r="H36">
-        <v>212.9940</v>
+        <v>241.8800</v>
       </c>
       <c t="n" r="I36">
-        <v>723.2328</v>
+        <v>847.8326</v>
       </c>
     </row>
     <row r="37">
@@ -1261,22 +1261,22 @@
         </is>
       </c>
       <c t="n" r="C37">
-        <v>0.1468</v>
+        <v>0.1663</v>
       </c>
       <c t="n" r="D37">
-        <v>0.0247</v>
+        <v>0.0092</v>
       </c>
       <c t="n" r="E37">
-        <v>41.1493</v>
+        <v>41.1528</v>
       </c>
       <c t="n" r="F37">
-        <v>0.2791</v>
+        <v>0.2591</v>
       </c>
       <c t="n" r="G37">
-        <v>41.4643</v>
+        <v>41.4463</v>
       </c>
       <c t="n" r="H37">
-        <v>251.8940</v>
+        <v>251.8837</v>
       </c>
     </row>
     <row r="38">
@@ -1291,25 +1291,25 @@
         </is>
       </c>
       <c t="n" r="C38">
-        <v>0.5518</v>
+        <v>0.5034</v>
       </c>
       <c t="n" r="D38">
-        <v>1.5389</v>
+        <v>1.5177</v>
       </c>
       <c t="n" r="E38">
-        <v>28.9759</v>
+        <v>28.9496</v>
       </c>
       <c t="n" r="F38">
-        <v>1.5342</v>
+        <v>1.5382</v>
       </c>
       <c t="n" r="G38">
-        <v>40.7827</v>
+        <v>40.7167</v>
       </c>
       <c t="n" r="H38">
-        <v>172.2973</v>
+        <v>172.3067</v>
       </c>
       <c t="n" r="I38">
-        <v>400.5591</v>
+        <v>400.5791</v>
       </c>
     </row>
     <row r="39">
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c t="n" r="C39">
-        <v>0.4527</v>
+        <v>0.4376</v>
       </c>
       <c t="n" r="D39">
-        <v>1.7188</v>
+        <v>1.6867</v>
       </c>
       <c t="n" r="E39">
-        <v>16.1825</v>
+        <v>16.1884</v>
       </c>
       <c t="n" r="F39">
-        <v>2.0444</v>
+        <v>2.0483</v>
       </c>
       <c t="n" r="G39">
-        <v>40.2618</v>
+        <v>40.2174</v>
       </c>
       <c t="n" r="H39">
-        <v>295.4102</v>
+        <v>295.3568</v>
       </c>
       <c t="n" r="I39">
-        <v>916.1180</v>
+        <v>915.9538</v>
       </c>
     </row>
     <row r="40">
@@ -1357,25 +1357,25 @@
         </is>
       </c>
       <c t="n" r="C40">
-        <v>1.4956</v>
+        <v>1.0627</v>
       </c>
       <c t="n" r="D40">
-        <v>4.4659</v>
+        <v>4.4558</v>
       </c>
       <c t="n" r="E40">
-        <v>14.5215</v>
+        <v>14.5476</v>
       </c>
       <c t="n" r="F40">
-        <v>3.5517</v>
+        <v>3.5918</v>
       </c>
       <c t="n" r="G40">
-        <v>39.9466</v>
+        <v>40.0259</v>
       </c>
       <c t="n" r="H40">
-        <v>141.6417</v>
+        <v>141.3024</v>
       </c>
       <c t="n" r="I40">
-        <v>260.6183</v>
+        <v>260.7764</v>
       </c>
     </row>
     <row r="41">
@@ -1390,22 +1390,22 @@
         </is>
       </c>
       <c t="n" r="C41">
-        <v>0.0585</v>
+        <v>0.8523</v>
       </c>
       <c t="n" r="D41">
-        <v>5.5519</v>
+        <v>5.5393</v>
       </c>
       <c t="n" r="E41">
-        <v>34.9214</v>
+        <v>34.9147</v>
       </c>
       <c t="n" r="F41">
-        <v>13.3780</v>
+        <v>13.3698</v>
       </c>
       <c t="n" r="G41">
-        <v>39.1813</v>
+        <v>39.1962</v>
       </c>
       <c t="n" r="H41">
-        <v>840.4208</v>
+        <v>842.8873</v>
       </c>
     </row>
     <row r="42">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c t="n" r="C42">
-        <v>0.6988</v>
+        <v>0.6995</v>
       </c>
       <c t="n" r="D42">
-        <v>2.0570</v>
+        <v>2.1079</v>
       </c>
       <c t="n" r="E42">
-        <v>30.9973</v>
+        <v>30.9270</v>
       </c>
       <c t="n" r="F42">
-        <v>2.6779</v>
+        <v>2.6848</v>
       </c>
       <c t="n" r="G42">
-        <v>38.6392</v>
+        <v>38.6111</v>
       </c>
     </row>
     <row r="43">
@@ -1447,25 +1447,25 @@
         </is>
       </c>
       <c t="n" r="C43">
-        <v>0.1743</v>
+        <v>0.1928</v>
       </c>
       <c t="n" r="D43">
-        <v>-0.9158</v>
+        <v>-0.9306</v>
       </c>
       <c t="n" r="E43">
-        <v>26.0490</v>
+        <v>26.0491</v>
       </c>
       <c t="n" r="F43">
-        <v>-0.5314</v>
+        <v>-0.5496</v>
       </c>
       <c t="n" r="G43">
-        <v>38.3870</v>
+        <v>38.3964</v>
       </c>
       <c t="n" r="H43">
-        <v>326.7696</v>
+        <v>326.7369</v>
       </c>
       <c t="n" r="I43">
-        <v>713.1541</v>
+        <v>713.0053</v>
       </c>
     </row>
     <row r="44">
@@ -1480,112 +1480,112 @@
         </is>
       </c>
       <c t="n" r="C44">
-        <v>1.4499</v>
+        <v>1.3165</v>
       </c>
       <c t="n" r="D44">
-        <v>4.0769</v>
+        <v>4.1784</v>
       </c>
       <c t="n" r="E44">
-        <v>13.9003</v>
+        <v>13.8978</v>
       </c>
       <c t="n" r="F44">
-        <v>4.8805</v>
+        <v>5.0291</v>
       </c>
       <c t="n" r="G44">
-        <v>37.4649</v>
+        <v>37.4447</v>
       </c>
       <c t="n" r="H44">
-        <v>179.7077</v>
+        <v>179.8663</v>
       </c>
       <c t="n" r="I44">
-        <v>415.2882</v>
+        <v>415.8104</v>
       </c>
     </row>
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">FNR</t>
+          <t xml:space="preserve">TGI</t>
         </is>
       </c>
       <c t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C45">
-        <v>1.8954</v>
+        <v>1.6234</v>
       </c>
       <c t="n" r="D45">
-        <v>-3.5150</v>
+        <v>5.1354</v>
       </c>
       <c t="n" r="E45">
-        <v>12.7535</v>
+        <v>22.1425</v>
       </c>
       <c t="n" r="F45">
-        <v>2.7331</v>
+        <v>5.7936</v>
       </c>
       <c t="n" r="G45">
-        <v>36.4797</v>
+        <v>36.2587</v>
       </c>
     </row>
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">DIG</t>
+          <t xml:space="preserve">RP1</t>
         </is>
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NOVADA URFA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C46">
-        <v>2.6555</v>
+        <v>0.7287</v>
       </c>
       <c t="n" r="D46">
-        <v>7.1034</v>
+        <v>-0.4218</v>
       </c>
       <c t="n" r="E46">
-        <v>15.3222</v>
+        <v>32.6751</v>
       </c>
       <c t="n" r="F46">
-        <v>8.4513</v>
+        <v>-0.4771</v>
       </c>
       <c t="n" r="G46">
-        <v>35.8034</v>
+        <v>35.5664</v>
+      </c>
+      <c t="n" r="H46">
+        <v>244.2912</v>
+      </c>
+      <c t="n" r="I46">
+        <v>921.6458</v>
       </c>
     </row>
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">RP1</t>
+          <t xml:space="preserve">DIG</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NOVADA URFA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C47">
-        <v>0.7267</v>
+        <v>2.5206</v>
       </c>
       <c t="n" r="D47">
-        <v>-0.4204</v>
+        <v>6.8428</v>
       </c>
       <c t="n" r="E47">
-        <v>32.6750</v>
+        <v>15.3333</v>
       </c>
       <c t="n" r="F47">
-        <v>-0.4751</v>
+        <v>8.4990</v>
       </c>
       <c t="n" r="G47">
-        <v>35.5652</v>
-      </c>
-      <c t="n" r="H47">
-        <v>243.3369</v>
-      </c>
-      <c t="n" r="I47">
-        <v>921.6733</v>
+        <v>35.2864</v>
       </c>
     </row>
     <row r="48">
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c t="n" r="C48">
-        <v>0.5373</v>
+        <v>0.5367</v>
       </c>
       <c t="n" r="D48">
-        <v>1.8263</v>
+        <v>1.8006</v>
       </c>
       <c t="n" r="E48">
-        <v>26.8428</v>
+        <v>26.8196</v>
       </c>
       <c t="n" r="F48">
-        <v>2.2291</v>
+        <v>2.2672</v>
       </c>
       <c t="n" r="G48">
-        <v>34.8617</v>
+        <v>34.8681</v>
       </c>
       <c t="n" r="H48">
-        <v>575.6918</v>
+        <v>576.0369</v>
       </c>
     </row>
     <row r="49">
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c t="n" r="C49">
-        <v>-0.0238</v>
+        <v>-0.0219</v>
       </c>
       <c t="n" r="D49">
-        <v>-0.1064</v>
+        <v>-0.1104</v>
       </c>
       <c t="n" r="E49">
-        <v>34.0422</v>
+        <v>34.0418</v>
       </c>
       <c t="n" r="F49">
-        <v>-0.1148</v>
+        <v>-0.1177</v>
       </c>
       <c t="n" r="G49">
         <v>34.5360</v>
@@ -1648,268 +1648,268 @@
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">NG2</t>
+          <t xml:space="preserve">TUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C50">
-        <v>0.2648</v>
+        <v>1.9226</v>
       </c>
       <c t="n" r="D50">
-        <v>0.7756</v>
+        <v>2.9722</v>
       </c>
       <c t="n" r="E50">
-        <v>31.5228</v>
+        <v>11.3360</v>
       </c>
       <c t="n" r="F50">
-        <v>1.1046</v>
+        <v>4.2160</v>
       </c>
       <c t="n" r="G50">
-        <v>33.0224</v>
-      </c>
-      <c t="n" r="H50">
-        <v>316.3517</v>
+        <v>33.6574</v>
       </c>
     </row>
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">YG1</t>
+          <t xml:space="preserve">IRG</t>
         </is>
       </c>
       <c t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LOTUS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C51">
-        <v>0.1039</v>
+        <v>0.8985</v>
       </c>
       <c t="n" r="D51">
-        <v>0.4855</v>
+        <v>3.8053</v>
       </c>
       <c t="n" r="E51">
-        <v>10.4440</v>
+        <v>12.9919</v>
       </c>
       <c t="n" r="F51">
-        <v>0.1184</v>
+        <v>3.9893</v>
       </c>
       <c t="n" r="G51">
-        <v>32.2871</v>
-      </c>
-      <c t="n" r="H51">
-        <v>302.6295</v>
+        <v>33.6365</v>
       </c>
     </row>
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">AZ3</t>
+          <t xml:space="preserve">NG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C52">
-        <v>-0.0074</v>
+        <v>0.2708</v>
       </c>
       <c t="n" r="D52">
-        <v>-0.1903</v>
+        <v>0.7691</v>
       </c>
       <c t="n" r="E52">
-        <v>32.8738</v>
+        <v>31.5237</v>
       </c>
       <c t="n" r="F52">
-        <v>-2.9932</v>
+        <v>1.0979</v>
       </c>
       <c t="n" r="G52">
-        <v>31.7347</v>
+        <v>33.0269</v>
       </c>
       <c t="n" r="H52">
-        <v>214.8775</v>
-      </c>
-      <c t="n" r="I52">
-        <v>684.3909</v>
+        <v>316.5859</v>
       </c>
     </row>
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">UCG</t>
+          <t xml:space="preserve">YG1</t>
         </is>
       </c>
       <c t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LOTUS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C53">
-        <v>0.2136</v>
+        <v>0.1681</v>
       </c>
       <c t="n" r="D53">
-        <v>-0.5499</v>
+        <v>0.4848</v>
       </c>
       <c t="n" r="E53">
-        <v>31.2840</v>
+        <v>10.4440</v>
       </c>
       <c t="n" r="F53">
-        <v>0.0865</v>
+        <v>0.1176</v>
       </c>
       <c t="n" r="G53">
-        <v>31.5267</v>
+        <v>32.2875</v>
       </c>
       <c t="n" r="H53">
-        <v>684.0282</v>
-      </c>
-      <c t="n" r="I53">
-        <v>1727.9586</v>
+        <v>302.6300</v>
       </c>
     </row>
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">FNI</t>
+          <t xml:space="preserve">AZ3</t>
         </is>
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C54">
-        <v>-1.3398</v>
+        <v>-0.0075</v>
       </c>
       <c t="n" r="D54">
-        <v>-0.3385</v>
+        <v>-0.1879</v>
       </c>
       <c t="n" r="E54">
-        <v>26.0922</v>
+        <v>32.8852</v>
       </c>
       <c t="n" r="F54">
-        <v>-0.3718</v>
+        <v>-2.9932</v>
       </c>
       <c t="n" r="G54">
-        <v>31.3834</v>
+        <v>31.7496</v>
+      </c>
+      <c t="n" r="H54">
+        <v>214.9001</v>
+      </c>
+      <c t="n" r="I54">
+        <v>684.3911</v>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">TUG</t>
+          <t xml:space="preserve">UCG</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C55">
-        <v>1.5560</v>
+        <v>0.2242</v>
       </c>
       <c t="n" r="D55">
-        <v>2.4362</v>
+        <v>-0.5499</v>
       </c>
       <c t="n" r="E55">
-        <v>10.7089</v>
+        <v>31.3179</v>
       </c>
       <c t="n" r="F55">
-        <v>3.5765</v>
+        <v>0.0885</v>
       </c>
       <c t="n" r="G55">
-        <v>31.3608</v>
+        <v>31.5472</v>
+      </c>
+      <c t="n" r="H55">
+        <v>683.3077</v>
+      </c>
+      <c t="n" r="I55">
+        <v>1727.7203</v>
       </c>
     </row>
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">GF1</t>
+          <t xml:space="preserve">FNI</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C56">
-        <v>-0.0009</v>
+        <v>-1.3411</v>
       </c>
       <c t="n" r="D56">
-        <v>0.0542</v>
+        <v>-0.3420</v>
       </c>
       <c t="n" r="E56">
-        <v>28.9011</v>
+        <v>26.0870</v>
       </c>
       <c t="n" r="F56">
-        <v>0.2724</v>
+        <v>-0.3748</v>
       </c>
       <c t="n" r="G56">
-        <v>31.1940</v>
+        <v>31.3832</v>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">ITG</t>
+          <t xml:space="preserve">GF1</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. QUASAR İSTANBUL TİCARİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C57">
-        <v>0.2287</v>
+        <v>0.0021</v>
       </c>
       <c t="n" r="D57">
-        <v>1.1108</v>
+        <v>0.0366</v>
       </c>
       <c t="n" r="E57">
-        <v>13.0167</v>
+        <v>28.9023</v>
       </c>
       <c t="n" r="F57">
-        <v>1.3633</v>
+        <v>0.2625</v>
       </c>
       <c t="n" r="G57">
-        <v>30.8849</v>
-      </c>
-      <c t="n" r="H57">
-        <v>156.5147</v>
-      </c>
-      <c t="n" r="I57">
-        <v>486.4056</v>
+        <v>31.1962</v>
       </c>
     </row>
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">IRG</t>
+          <t xml:space="preserve">ITG</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. QUASAR İSTANBUL TİCARİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C58">
-        <v>1.5230</v>
+        <v>0.2329</v>
       </c>
       <c t="n" r="D58">
-        <v>3.8909</v>
+        <v>1.1051</v>
       </c>
       <c t="n" r="E58">
-        <v>12.9697</v>
+        <v>13.0198</v>
       </c>
       <c t="n" r="F58">
-        <v>3.9621</v>
+        <v>1.3653</v>
       </c>
       <c t="n" r="G58">
-        <v>30.7040</v>
+        <v>30.8794</v>
+      </c>
+      <c t="n" r="H58">
+        <v>156.5411</v>
+      </c>
+      <c t="n" r="I58">
+        <v>486.5781</v>
       </c>
     </row>
     <row r="59">
@@ -1924,19 +1924,19 @@
         </is>
       </c>
       <c t="n" r="C59">
-        <v>0.1088</v>
+        <v>0.1031</v>
       </c>
       <c t="n" r="D59">
-        <v>0.2221</v>
+        <v>0.1972</v>
       </c>
       <c t="n" r="E59">
-        <v>5.2132</v>
+        <v>5.1096</v>
       </c>
       <c t="n" r="F59">
-        <v>0.2460</v>
+        <v>0.2393</v>
       </c>
       <c t="n" r="G59">
-        <v>30.6168</v>
+        <v>30.2270</v>
       </c>
     </row>
     <row r="60">
@@ -1951,79 +1951,79 @@
         </is>
       </c>
       <c t="n" r="C60">
-        <v>0.0986</v>
+        <v>0.1222</v>
       </c>
       <c t="n" r="D60">
-        <v>0.9087</v>
+        <v>0.8937</v>
       </c>
       <c t="n" r="E60">
-        <v>27.6975</v>
+        <v>27.6723</v>
       </c>
       <c t="n" r="F60">
-        <v>-5.9553</v>
+        <v>-5.9603</v>
       </c>
       <c t="n" r="G60">
-        <v>30.0286</v>
+        <v>29.9905</v>
       </c>
       <c t="n" r="H60">
-        <v>172.0487</v>
+        <v>172.0121</v>
       </c>
       <c t="n" r="I60">
-        <v>828.0775</v>
+        <v>828.0276</v>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">HRE</t>
+          <t xml:space="preserve">GF2</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C61">
-        <v>1.4109</v>
+        <v>-0.0224</v>
       </c>
       <c t="n" r="D61">
-        <v>3.7444</v>
+        <v>4.9953</v>
       </c>
       <c t="n" r="E61">
-        <v>11.0818</v>
+        <v>16.5577</v>
       </c>
       <c t="n" r="F61">
-        <v>5.4813</v>
+        <v>6.5392</v>
       </c>
       <c t="n" r="G61">
-        <v>29.9519</v>
+        <v>29.7990</v>
       </c>
     </row>
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">GF2</t>
+          <t xml:space="preserve">HRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C62">
-        <v>-0.5580</v>
+        <v>1.2104</v>
       </c>
       <c t="n" r="D62">
-        <v>5.2569</v>
+        <v>3.5959</v>
       </c>
       <c t="n" r="E62">
-        <v>16.6383</v>
+        <v>11.0823</v>
       </c>
       <c t="n" r="F62">
-        <v>6.5152</v>
+        <v>5.5611</v>
       </c>
       <c t="n" r="G62">
-        <v>29.7510</v>
+        <v>29.7912</v>
       </c>
     </row>
     <row r="63">
@@ -2038,205 +2038,199 @@
         </is>
       </c>
       <c t="n" r="C63">
-        <v>0.2296</v>
+        <v>0.2265</v>
       </c>
       <c t="n" r="D63">
-        <v>0.7773</v>
+        <v>0.7705</v>
       </c>
       <c t="n" r="E63">
-        <v>-1.0616</v>
+        <v>-1.0592</v>
       </c>
       <c t="n" r="F63">
-        <v>1.0703</v>
+        <v>1.0707</v>
       </c>
       <c t="n" r="G63">
-        <v>29.6632</v>
+        <v>29.6661</v>
       </c>
     </row>
     <row r="64">
       <c t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">AG6</t>
+          <t xml:space="preserve">HVG</t>
         </is>
       </c>
       <c t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C64">
-        <v>0.1179</v>
+        <v>-0.0486</v>
       </c>
       <c t="n" r="D64">
-        <v>0.3609</v>
+        <v>-0.1423</v>
       </c>
       <c t="n" r="E64">
-        <v>28.6669</v>
+        <v>30.4725</v>
       </c>
       <c t="n" r="F64">
-        <v>0.3427</v>
+        <v>-0.1764</v>
       </c>
       <c t="n" r="G64">
-        <v>29.1351</v>
-      </c>
-      <c t="n" r="H64">
-        <v>231.8359</v>
-      </c>
-      <c t="n" r="I64">
-        <v>353.6836</v>
+        <v>29.4751</v>
       </c>
     </row>
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">IUL</t>
+          <t xml:space="preserve">AG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İNAN 3 ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C65">
-        <v>0.3119</v>
+        <v>0.1079</v>
       </c>
       <c t="n" r="D65">
-        <v>0.6442</v>
+        <v>0.3519</v>
       </c>
       <c t="n" r="E65">
-        <v>26.6982</v>
+        <v>28.6655</v>
       </c>
       <c t="n" r="F65">
-        <v>2.4387</v>
+        <v>0.3478</v>
       </c>
       <c t="n" r="G65">
-        <v>28.7384</v>
+        <v>29.1250</v>
+      </c>
+      <c t="n" r="H65">
+        <v>230.8954</v>
+      </c>
+      <c t="n" r="I65">
+        <v>353.7068</v>
       </c>
     </row>
     <row r="66">
       <c t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">RMO</t>
+          <t xml:space="preserve">IUL</t>
         </is>
       </c>
       <c t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. MONO PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İNAN 3 ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C66">
-        <v>-0.0183</v>
+        <v>0.3658</v>
       </c>
       <c t="n" r="D66">
-        <v>-0.0586</v>
+        <v>0.6660</v>
       </c>
       <c t="n" r="E66">
-        <v>28.1661</v>
+        <v>26.7967</v>
       </c>
       <c t="n" r="F66">
-        <v>-0.0777</v>
+        <v>2.4832</v>
       </c>
       <c t="n" r="G66">
-        <v>28.0134</v>
+        <v>28.7788</v>
       </c>
     </row>
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">UKA</t>
+          <t xml:space="preserve">RMO</t>
         </is>
       </c>
       <c t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. KONUT ALFA KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. MONO PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C67">
-        <v>1.5273</v>
+        <v>-0.0180</v>
       </c>
       <c t="n" r="D67">
-        <v>4.1590</v>
+        <v>-0.0587</v>
       </c>
       <c t="n" r="E67">
-        <v>16.2291</v>
+        <v>28.1661</v>
       </c>
       <c t="n" r="F67">
-        <v>4.3788</v>
+        <v>-0.0779</v>
       </c>
       <c t="n" r="G67">
-        <v>27.7929</v>
-      </c>
-      <c t="n" r="H67">
-        <v>134.8991</v>
-      </c>
-      <c t="n" r="I67">
-        <v>635575.0232</v>
+        <v>28.0133</v>
       </c>
     </row>
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">OFG</t>
+          <t xml:space="preserve">UKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. FORM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. KONUT ALFA KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C68">
-        <v>0.5054</v>
+        <v>1.1809</v>
       </c>
       <c t="n" r="D68">
-        <v>-1.3496</v>
+        <v>4.1438</v>
       </c>
       <c t="n" r="E68">
-        <v>25.3930</v>
+        <v>16.2252</v>
       </c>
       <c t="n" r="F68">
-        <v>-20.3872</v>
+        <v>4.4070</v>
       </c>
       <c t="n" r="G68">
-        <v>27.2299</v>
+        <v>27.7923</v>
       </c>
       <c t="n" r="H68">
-        <v>242.8212</v>
+        <v>130.7065</v>
       </c>
       <c t="n" r="I68">
-        <v>1974.0601</v>
+        <v>635746.3872</v>
       </c>
     </row>
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">IDG</t>
+          <t xml:space="preserve">OFG</t>
         </is>
       </c>
       <c t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. FORM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C69">
-        <v>0.9803</v>
+        <v>0.5594</v>
       </c>
       <c t="n" r="D69">
-        <v>3.4492</v>
+        <v>-1.3612</v>
       </c>
       <c t="n" r="E69">
-        <v>17.4518</v>
+        <v>25.3436</v>
       </c>
       <c t="n" r="F69">
-        <v>4.8818</v>
+        <v>-20.3950</v>
       </c>
       <c t="n" r="G69">
-        <v>26.7226</v>
+        <v>27.1675</v>
       </c>
       <c t="n" r="H69">
-        <v>219.9005</v>
+        <v>242.8761</v>
       </c>
       <c t="n" r="I69">
-        <v>501.7437</v>
+        <v>1973.8580</v>
       </c>
     </row>
     <row r="70">
@@ -2251,115 +2245,124 @@
         </is>
       </c>
       <c t="n" r="C70">
-        <v>-2.3018</v>
+        <v>0.7943</v>
       </c>
       <c t="n" r="D70">
-        <v>-1.1787</v>
+        <v>-1.1850</v>
       </c>
       <c t="n" r="E70">
-        <v>25.5642</v>
+        <v>25.5319</v>
       </c>
       <c t="n" r="F70">
-        <v>-0.3200</v>
+        <v>-0.3222</v>
       </c>
       <c t="n" r="G70">
-        <v>26.1253</v>
+        <v>26.1280</v>
       </c>
       <c t="n" r="H70">
-        <v>49.1174</v>
+        <v>49.1217</v>
       </c>
       <c t="n" r="I70">
-        <v>980.8078</v>
+        <v>980.7843</v>
       </c>
     </row>
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">NUY</t>
+          <t xml:space="preserve">IDG</t>
         </is>
       </c>
       <c t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C71">
-        <v>-2.3162</v>
+        <v>1.1791</v>
       </c>
       <c t="n" r="D71">
-        <v>0.0602</v>
+        <v>3.3567</v>
       </c>
       <c t="n" r="E71">
-        <v>17.0667</v>
+        <v>17.4605</v>
       </c>
       <c t="n" r="F71">
-        <v>1.0151</v>
+        <v>4.9159</v>
       </c>
       <c t="n" r="G71">
-        <v>25.8253</v>
+        <v>25.7502</v>
+      </c>
+      <c t="n" r="H71">
+        <v>220.4609</v>
+      </c>
+      <c t="n" r="I71">
+        <v>501.9490</v>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">UNC</t>
+          <t xml:space="preserve">AG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. METROPOL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C72">
-        <v>0.4176</v>
+        <v>4.1205</v>
       </c>
       <c t="n" r="D72">
-        <v>1.8032</v>
+        <v>4.9614</v>
       </c>
       <c t="n" r="E72">
-        <v>8.7373</v>
+        <v>14.3083</v>
       </c>
       <c t="n" r="F72">
-        <v>1.7377</v>
+        <v>1.0219</v>
       </c>
       <c t="n" r="G72">
-        <v>25.8251</v>
+        <v>25.4490</v>
       </c>
       <c t="n" r="H72">
-        <v>76.5544</v>
+        <v>331.4009</v>
+      </c>
+      <c t="n" r="I72">
+        <v>836.7997</v>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">AG7</t>
+          <t xml:space="preserve">ZUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. METROPOL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C73">
-        <v>4.2487</v>
+        <v>-0.0786</v>
       </c>
       <c t="n" r="D73">
-        <v>4.9747</v>
+        <v>-0.2394</v>
       </c>
       <c t="n" r="E73">
-        <v>14.2790</v>
+        <v>25.3553</v>
       </c>
       <c t="n" r="F73">
-        <v>1.0222</v>
+        <v>0.0438</v>
       </c>
       <c t="n" r="G73">
-        <v>25.3836</v>
+        <v>25.3299</v>
       </c>
       <c t="n" r="H73">
-        <v>331.4897</v>
+        <v>200.1532</v>
       </c>
       <c t="n" r="I73">
-        <v>836.8025</v>
+        <v>400.3929</v>
       </c>
     </row>
     <row r="74">
@@ -2374,82 +2377,76 @@
         </is>
       </c>
       <c t="n" r="C74">
-        <v>1.3007</v>
+        <v>1.2158</v>
       </c>
       <c t="n" r="D74">
-        <v>3.6512</v>
+        <v>3.5773</v>
       </c>
       <c t="n" r="E74">
-        <v>-0.3829</v>
+        <v>-0.3595</v>
       </c>
       <c t="n" r="F74">
-        <v>4.0740</v>
+        <v>4.1045</v>
       </c>
       <c t="n" r="G74">
-        <v>25.3603</v>
+        <v>25.2834</v>
       </c>
       <c t="n" r="H74">
-        <v>161.8937</v>
+        <v>161.9940</v>
       </c>
     </row>
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">ZUG</t>
+          <t xml:space="preserve">IVB</t>
         </is>
       </c>
       <c t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ SANAYİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C75">
-        <v>-0.1382</v>
+        <v>0.4026</v>
       </c>
       <c t="n" r="D75">
-        <v>-0.2993</v>
+        <v>-0.1037</v>
       </c>
       <c t="n" r="E75">
-        <v>25.3040</v>
+        <v>23.1990</v>
       </c>
       <c t="n" r="F75">
-        <v>-0.0159</v>
+        <v>-0.1268</v>
       </c>
       <c t="n" r="G75">
-        <v>25.2635</v>
-      </c>
-      <c t="n" r="H75">
-        <v>199.1912</v>
-      </c>
-      <c t="n" r="I75">
-        <v>400.1168</v>
+        <v>24.9260</v>
       </c>
     </row>
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">IVB</t>
+          <t xml:space="preserve">NUY</t>
         </is>
       </c>
       <c t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ SANAYİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C76">
-        <v>0.3970</v>
+        <v>-2.3642</v>
       </c>
       <c t="n" r="D76">
-        <v>-0.0946</v>
+        <v>0.0036</v>
       </c>
       <c t="n" r="E76">
-        <v>23.1983</v>
+        <v>17.0680</v>
       </c>
       <c t="n" r="F76">
-        <v>-0.1202</v>
+        <v>1.0304</v>
       </c>
       <c t="n" r="G76">
-        <v>24.9231</v>
+        <v>24.9242</v>
       </c>
     </row>
     <row r="77">
@@ -2464,22 +2461,22 @@
         </is>
       </c>
       <c t="n" r="C77">
-        <v>-2.4337</v>
+        <v>-2.5794</v>
       </c>
       <c t="n" r="D77">
-        <v>-2.3037</v>
+        <v>-2.3165</v>
       </c>
       <c t="n" r="E77">
-        <v>7.9988</v>
+        <v>8.0147</v>
       </c>
       <c t="n" r="F77">
-        <v>-2.7617</v>
+        <v>-2.7562</v>
       </c>
       <c t="n" r="G77">
-        <v>24.5522</v>
+        <v>24.6169</v>
       </c>
       <c t="n" r="H77">
-        <v>148.6315</v>
+        <v>148.4729</v>
       </c>
     </row>
     <row r="78">
@@ -2494,25 +2491,25 @@
         </is>
       </c>
       <c t="n" r="C78">
-        <v>-1.2427</v>
+        <v>-1.2902</v>
       </c>
       <c t="n" r="D78">
-        <v>5.5796</v>
+        <v>5.5708</v>
       </c>
       <c t="n" r="E78">
-        <v>24.7728</v>
+        <v>24.7734</v>
       </c>
       <c t="n" r="F78">
-        <v>-1.5872</v>
+        <v>-1.6021</v>
       </c>
       <c t="n" r="G78">
-        <v>23.6883</v>
+        <v>23.7146</v>
       </c>
       <c t="n" r="H78">
-        <v>253.3030</v>
+        <v>253.2568</v>
       </c>
       <c t="n" r="I78">
-        <v>780.7712</v>
+        <v>781.2924</v>
       </c>
     </row>
     <row r="79">
@@ -2527,25 +2524,25 @@
         </is>
       </c>
       <c t="n" r="C79">
-        <v>6.5619</v>
+        <v>6.5250</v>
       </c>
       <c t="n" r="D79">
-        <v>8.4398</v>
+        <v>8.1731</v>
       </c>
       <c t="n" r="E79">
-        <v>16.1570</v>
+        <v>16.2075</v>
       </c>
       <c t="n" r="F79">
-        <v>6.9360</v>
+        <v>6.9081</v>
       </c>
       <c t="n" r="G79">
-        <v>23.1964</v>
+        <v>23.0710</v>
       </c>
       <c t="n" r="H79">
-        <v>244.2988</v>
+        <v>244.1181</v>
       </c>
       <c t="n" r="I79">
-        <v>781.0748</v>
+        <v>780.8448</v>
       </c>
     </row>
     <row r="80">
@@ -2560,22 +2557,22 @@
         </is>
       </c>
       <c t="n" r="C80">
-        <v>-0.1069</v>
+        <v>-0.1087</v>
       </c>
       <c t="n" r="D80">
-        <v>-0.6140</v>
+        <v>-0.6151</v>
       </c>
       <c t="n" r="E80">
-        <v>23.0853</v>
+        <v>23.0854</v>
       </c>
       <c t="n" r="F80">
-        <v>-0.7297</v>
+        <v>-0.7318</v>
       </c>
       <c t="n" r="G80">
-        <v>21.8601</v>
+        <v>21.8603</v>
       </c>
       <c t="n" r="H80">
-        <v>171.1564</v>
+        <v>171.1401</v>
       </c>
     </row>
     <row r="81">
@@ -2590,85 +2587,85 @@
         </is>
       </c>
       <c t="n" r="C81">
-        <v>0.3783</v>
+        <v>0.3796</v>
       </c>
       <c t="n" r="D81">
-        <v>1.0183</v>
+        <v>0.9944</v>
       </c>
       <c t="n" r="E81">
-        <v>3.8298</v>
+        <v>3.8191</v>
       </c>
       <c t="n" r="F81">
-        <v>1.3892</v>
+        <v>1.3835</v>
       </c>
       <c t="n" r="G81">
-        <v>21.4663</v>
+        <v>21.4583</v>
       </c>
       <c t="n" r="H81">
-        <v>264.3435</v>
+        <v>264.4139</v>
       </c>
       <c t="n" r="I81">
-        <v>795.5700</v>
+        <v>794.3956</v>
       </c>
     </row>
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">ZG6</t>
+          <t xml:space="preserve">GGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C82">
-        <v>-0.1058</v>
+        <v>1.0357</v>
       </c>
       <c t="n" r="D82">
-        <v>-0.3026</v>
+        <v>2.7901</v>
       </c>
       <c t="n" r="E82">
-        <v>22.0980</v>
+        <v>12.2367</v>
       </c>
       <c t="n" r="F82">
-        <v>-2.4769</v>
+        <v>1.9251</v>
       </c>
       <c t="n" r="G82">
-        <v>21.2904</v>
+        <v>21.4084</v>
       </c>
       <c t="n" r="H82">
-        <v>47.1929</v>
+        <v>81.8403</v>
       </c>
     </row>
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">GGF</t>
+          <t xml:space="preserve">ZG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C83">
-        <v>0.8684</v>
+        <v>-0.0976</v>
       </c>
       <c t="n" r="D83">
-        <v>2.7619</v>
+        <v>-0.3085</v>
       </c>
       <c t="n" r="E83">
-        <v>12.1104</v>
+        <v>23.5572</v>
       </c>
       <c t="n" r="F83">
-        <v>1.7753</v>
+        <v>-2.4852</v>
       </c>
       <c t="n" r="G83">
-        <v>21.2380</v>
+        <v>21.2934</v>
       </c>
       <c t="n" r="H83">
-        <v>76.9864</v>
+        <v>46.5400</v>
       </c>
     </row>
     <row r="84">
@@ -2683,25 +2680,25 @@
         </is>
       </c>
       <c t="n" r="C84">
-        <v>0.2761</v>
+        <v>0.2720</v>
       </c>
       <c t="n" r="D84">
-        <v>0.9378</v>
+        <v>0.9442</v>
       </c>
       <c t="n" r="E84">
-        <v>5.6597</v>
+        <v>5.6632</v>
       </c>
       <c t="n" r="F84">
-        <v>1.1222</v>
+        <v>1.1273</v>
       </c>
       <c t="n" r="G84">
-        <v>20.9218</v>
+        <v>20.9282</v>
       </c>
       <c t="n" r="H84">
-        <v>221.0375</v>
+        <v>221.0866</v>
       </c>
       <c t="n" r="I84">
-        <v>989.8699</v>
+        <v>989.9694</v>
       </c>
     </row>
     <row r="85">
@@ -2716,25 +2713,25 @@
         </is>
       </c>
       <c t="n" r="C85">
-        <v>0.3867</v>
+        <v>0.4684</v>
       </c>
       <c t="n" r="D85">
-        <v>0.8316</v>
+        <v>0.8041</v>
       </c>
       <c t="n" r="E85">
-        <v>17.3064</v>
+        <v>17.2625</v>
       </c>
       <c t="n" r="F85">
-        <v>1.0238</v>
+        <v>1.0194</v>
       </c>
       <c t="n" r="G85">
-        <v>20.5962</v>
+        <v>20.5690</v>
       </c>
       <c t="n" r="H85">
-        <v>174.3889</v>
+        <v>174.2688</v>
       </c>
       <c t="n" r="I85">
-        <v>1191.9020</v>
+        <v>1191.8348</v>
       </c>
     </row>
     <row r="86">
@@ -2749,22 +2746,22 @@
         </is>
       </c>
       <c t="n" r="C86">
-        <v>-1.6186</v>
+        <v>-1.6282</v>
       </c>
       <c t="n" r="D86">
-        <v>-0.1963</v>
+        <v>-0.2085</v>
       </c>
       <c t="n" r="E86">
-        <v>16.6162</v>
+        <v>16.6110</v>
       </c>
       <c t="n" r="F86">
-        <v>0.5133</v>
+        <v>0.5127</v>
       </c>
       <c t="n" r="G86">
-        <v>20.2454</v>
+        <v>20.2506</v>
       </c>
       <c t="n" r="H86">
-        <v>368.1567</v>
+        <v>368.9459</v>
       </c>
     </row>
     <row r="87">
@@ -2779,88 +2776,88 @@
         </is>
       </c>
       <c t="n" r="C87">
-        <v>-0.2607</v>
+        <v>-0.1564</v>
       </c>
       <c t="n" r="D87">
-        <v>1.4807</v>
+        <v>1.4180</v>
       </c>
       <c t="n" r="E87">
-        <v>15.3261</v>
+        <v>15.1922</v>
       </c>
       <c t="n" r="F87">
-        <v>-2.7909</v>
+        <v>-2.7913</v>
       </c>
       <c t="n" r="G87">
-        <v>19.7343</v>
+        <v>19.5083</v>
       </c>
       <c t="n" r="H87">
-        <v>150.3044</v>
+        <v>150.2471</v>
       </c>
       <c t="n" r="I87">
-        <v>418.8575</v>
+        <v>418.8552</v>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">MGA</t>
+          <t xml:space="preserve">OG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.UFUK KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C88">
-        <v>0.5036</v>
+        <v>0.0920</v>
       </c>
       <c t="n" r="D88">
-        <v>1.2196</v>
+        <v>-0.0863</v>
       </c>
       <c t="n" r="E88">
-        <v>11.5542</v>
+        <v>15.4324</v>
       </c>
       <c t="n" r="F88">
-        <v>-0.7844</v>
+        <v>0.4107</v>
       </c>
       <c t="n" r="G88">
-        <v>19.6569</v>
+        <v>19.4001</v>
       </c>
       <c t="n" r="H88">
-        <v>151.9869</v>
+        <v>116.2931</v>
+      </c>
+      <c t="n" r="I88">
+        <v>1159.9466</v>
       </c>
     </row>
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">OG2</t>
+          <t xml:space="preserve">MGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.UFUK KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C89">
-        <v>0.0862</v>
+        <v>0.4845</v>
       </c>
       <c t="n" r="D89">
-        <v>-0.0919</v>
+        <v>1.1979</v>
       </c>
       <c t="n" r="E89">
-        <v>15.4218</v>
+        <v>11.5565</v>
       </c>
       <c t="n" r="F89">
-        <v>0.4029</v>
+        <v>-0.7777</v>
       </c>
       <c t="n" r="G89">
-        <v>19.3880</v>
+        <v>19.1109</v>
       </c>
       <c t="n" r="H89">
-        <v>116.2591</v>
-      </c>
-      <c t="n" r="I89">
-        <v>1159.8965</v>
+        <v>152.0051</v>
       </c>
     </row>
     <row r="90">
@@ -2875,208 +2872,211 @@
         </is>
       </c>
       <c t="n" r="C90">
-        <v>-0.2453</v>
+        <v>-0.2706</v>
       </c>
       <c t="n" r="D90">
-        <v>-0.1643</v>
+        <v>-0.1661</v>
       </c>
       <c t="n" r="E90">
-        <v>19.1443</v>
+        <v>19.1440</v>
       </c>
       <c t="n" r="F90">
-        <v>-0.0392</v>
+        <v>-0.0382</v>
       </c>
       <c t="n" r="G90">
-        <v>18.8349</v>
+        <v>18.8331</v>
       </c>
       <c t="n" r="H90">
-        <v>1431.6202</v>
+        <v>1439.9375</v>
       </c>
     </row>
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">RP2</t>
+          <t xml:space="preserve">UNC</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C91">
-        <v>1.4733</v>
+        <v>0.4695</v>
       </c>
       <c t="n" r="D91">
-        <v>2.2097</v>
+        <v>1.7898</v>
       </c>
       <c t="n" r="E91">
-        <v>16.9981</v>
+        <v>8.7350</v>
       </c>
       <c t="n" r="F91">
-        <v>2.4226</v>
+        <v>1.7247</v>
       </c>
       <c t="n" r="G91">
-        <v>18.1204</v>
+        <v>18.0508</v>
       </c>
       <c t="n" r="H91">
-        <v>143.9400</v>
-      </c>
-      <c t="n" r="I91">
-        <v>449.4496</v>
+        <v>76.1548</v>
       </c>
     </row>
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">YD4</t>
+          <t xml:space="preserve">RP2</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C92">
-        <v>-0.6039</v>
+        <v>0.9059</v>
       </c>
       <c t="n" r="D92">
-        <v>-0.5369</v>
+        <v>2.1848</v>
       </c>
       <c t="n" r="E92">
-        <v>11.1795</v>
+        <v>16.9188</v>
       </c>
       <c t="n" r="F92">
-        <v>-0.5957</v>
+        <v>2.3327</v>
       </c>
       <c t="n" r="G92">
-        <v>17.9938</v>
+        <v>18.0030</v>
       </c>
       <c t="n" r="H92">
-        <v>245.6130</v>
+        <v>143.7135</v>
       </c>
       <c t="n" r="I92">
-        <v>1013.8893</v>
+        <v>448.9044</v>
       </c>
     </row>
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">NMC</t>
+          <t xml:space="preserve">YD4</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. M CHARM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C93">
-        <v>-1.5460</v>
+        <v>-0.2006</v>
       </c>
       <c t="n" r="D93">
-        <v>-1.0543</v>
+        <v>-0.5496</v>
       </c>
       <c t="n" r="E93">
-        <v>25.6639</v>
+        <v>11.1796</v>
       </c>
       <c t="n" r="F93">
-        <v>-0.8530</v>
+        <v>-0.6103</v>
       </c>
       <c t="n" r="G93">
-        <v>17.8222</v>
+        <v>18.0001</v>
       </c>
       <c t="n" r="H93">
-        <v>215.9936</v>
+        <v>245.6155</v>
+      </c>
+      <c t="n" r="I93">
+        <v>1013.7248</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">NUF</t>
+          <t xml:space="preserve">NMC</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. D VİZYON GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. M CHARM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C94">
-        <v>-0.1340</v>
+        <v>-1.5485</v>
       </c>
       <c t="n" r="D94">
-        <v>-0.3854</v>
+        <v>-1.0683</v>
       </c>
       <c t="n" r="E94">
-        <v>26.9057</v>
+        <v>25.6645</v>
       </c>
       <c t="n" r="F94">
-        <v>-0.4560</v>
+        <v>-0.8582</v>
       </c>
       <c t="n" r="G94">
-        <v>17.7026</v>
+        <v>17.8276</v>
       </c>
       <c t="n" r="H94">
-        <v>775.8060</v>
+        <v>215.9562</v>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">YD3</t>
+          <t xml:space="preserve">NUF</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. D VİZYON GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C95">
-        <v>-0.7661</v>
+        <v>-0.1208</v>
       </c>
       <c t="n" r="D95">
-        <v>-2.1104</v>
+        <v>-0.3945</v>
       </c>
       <c t="n" r="E95">
-        <v>11.7757</v>
+        <v>26.9058</v>
       </c>
       <c t="n" r="F95">
-        <v>-2.2850</v>
+        <v>-0.4691</v>
       </c>
       <c t="n" r="G95">
-        <v>17.1112</v>
+        <v>17.7069</v>
       </c>
       <c t="n" r="H95">
-        <v>148.4446</v>
-      </c>
-      <c t="n" r="I95">
-        <v>654.3624</v>
+        <v>775.4533</v>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">ABZ</t>
+          <t xml:space="preserve">YD3</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C96">
-        <v>-0.2509</v>
+        <v>-0.3048</v>
       </c>
       <c t="n" r="D96">
-        <v>-0.2508</v>
+        <v>-2.1258</v>
       </c>
       <c t="n" r="E96">
-        <v>5.3809</v>
+        <v>11.7730</v>
       </c>
       <c t="n" r="F96">
-        <v>-0.5035</v>
+        <v>-2.3041</v>
       </c>
       <c t="n" r="G96">
-        <v>16.9177</v>
+        <v>17.1204</v>
+      </c>
+      <c t="n" r="H96">
+        <v>148.4721</v>
+      </c>
+      <c t="n" r="I96">
+        <v>654.2145</v>
       </c>
     </row>
     <row r="97">
@@ -3091,685 +3091,679 @@
         </is>
       </c>
       <c t="n" r="C97">
-        <v>-0.2125</v>
+        <v>-0.2205</v>
       </c>
       <c t="n" r="D97">
-        <v>0.5873</v>
+        <v>0.5817</v>
       </c>
       <c t="n" r="E97">
-        <v>6.1930</v>
+        <v>6.1951</v>
       </c>
       <c t="n" r="F97">
-        <v>-0.6792</v>
+        <v>-0.6746</v>
       </c>
       <c t="n" r="G97">
-        <v>16.7695</v>
+        <v>16.9350</v>
       </c>
       <c t="n" r="H97">
-        <v>320.7764</v>
+        <v>320.7155</v>
       </c>
       <c t="n" r="I97">
-        <v>1601.2029</v>
+        <v>1601.2809</v>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">PKA</t>
+          <t xml:space="preserve">ABZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş V METROWAY KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C98">
-        <v>-0.0007</v>
+        <v>-0.2509</v>
       </c>
       <c t="n" r="D98">
-        <v>-0.0400</v>
+        <v>-0.2509</v>
       </c>
       <c t="n" r="E98">
-        <v>15.5054</v>
+        <v>5.3809</v>
       </c>
       <c t="n" r="F98">
-        <v>-0.0459</v>
+        <v>-0.5035</v>
       </c>
       <c t="n" r="G98">
-        <v>16.0178</v>
-      </c>
-      <c t="n" r="H98">
-        <v>580.1464</v>
+        <v>16.9175</v>
       </c>
     </row>
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">OGI</t>
+          <t xml:space="preserve">PKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş V METROWAY KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C99">
-        <v>0.2718</v>
+        <v>-0.0007</v>
       </c>
       <c t="n" r="D99">
-        <v>-0.6899</v>
+        <v>-0.0402</v>
       </c>
       <c t="n" r="E99">
-        <v>2.3348</v>
+        <v>16.1308</v>
       </c>
       <c t="n" r="F99">
-        <v>0.1953</v>
+        <v>-0.0460</v>
       </c>
       <c t="n" r="G99">
-        <v>15.7834</v>
+        <v>16.0176</v>
       </c>
       <c t="n" r="H99">
-        <v>0.6411</v>
-      </c>
-      <c t="n" r="I99">
-        <v>58.3343</v>
+        <v>580.1220</v>
       </c>
     </row>
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">NUE</t>
+          <t xml:space="preserve">OGI</t>
         </is>
       </c>
       <c t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. EGÇ KONUT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C100">
-        <v>0.1716</v>
+        <v>0.9070</v>
       </c>
       <c t="n" r="D100">
-        <v>2.6387</v>
+        <v>-0.7659</v>
       </c>
       <c t="n" r="E100">
-        <v>15.4465</v>
+        <v>2.3364</v>
       </c>
       <c t="n" r="F100">
-        <v>3.5929</v>
+        <v>0.2291</v>
       </c>
       <c t="n" r="G100">
-        <v>15.3364</v>
+        <v>15.6113</v>
       </c>
       <c t="n" r="H100">
-        <v>188.1184</v>
+        <v>0.7238</v>
+      </c>
+      <c t="n" r="I100">
+        <v>58.8643</v>
       </c>
     </row>
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">NUS</t>
+          <t xml:space="preserve">NUE</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ALTINCI KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. EGÇ KONUT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C101">
-        <v>-0.2296</v>
+        <v>0.3030</v>
       </c>
       <c t="n" r="D101">
-        <v>-0.5952</v>
+        <v>2.6184</v>
       </c>
       <c t="n" r="E101">
-        <v>16.6335</v>
+        <v>15.3095</v>
       </c>
       <c t="n" r="F101">
-        <v>-0.7072</v>
+        <v>3.6281</v>
       </c>
       <c t="n" r="G101">
-        <v>14.9611</v>
+        <v>15.0489</v>
+      </c>
+      <c t="n" r="H101">
+        <v>188.0601</v>
       </c>
     </row>
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">AZ2</t>
+          <t xml:space="preserve">NUS</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ALTINCI KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C102">
-        <v>-0.0357</v>
+        <v>-0.2107</v>
       </c>
       <c t="n" r="D102">
-        <v>1.6635</v>
+        <v>-0.6080</v>
       </c>
       <c t="n" r="E102">
-        <v>4.8223</v>
+        <v>16.6344</v>
       </c>
       <c t="n" r="F102">
-        <v>1.1954</v>
+        <v>-0.7263</v>
       </c>
       <c t="n" r="G102">
-        <v>14.3508</v>
-      </c>
-      <c t="n" r="H102">
-        <v>265.9559</v>
-      </c>
-      <c t="n" r="I102">
-        <v>1193.4495</v>
+        <v>14.9711</v>
       </c>
     </row>
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">FRG</t>
+          <t xml:space="preserve">AZ2</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C103">
-        <v>3.8722</v>
+        <v>0.0209</v>
       </c>
       <c t="n" r="D103">
-        <v>3.2183</v>
+        <v>1.6329</v>
       </c>
       <c t="n" r="E103">
-        <v>15.5820</v>
+        <v>4.7669</v>
       </c>
       <c t="n" r="F103">
-        <v>5.2265</v>
+        <v>1.1882</v>
       </c>
       <c t="n" r="G103">
-        <v>14.1588</v>
+        <v>14.2502</v>
       </c>
       <c t="n" r="H103">
-        <v>94.2289</v>
+        <v>265.9118</v>
       </c>
       <c t="n" r="I103">
-        <v>444.5144</v>
+        <v>1193.3583</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">RAS</t>
+          <t xml:space="preserve">FRG</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C104">
-        <v>-0.1290</v>
+        <v>2.1225</v>
       </c>
       <c t="n" r="D104">
-        <v>0.5556</v>
+        <v>3.1821</v>
       </c>
       <c t="n" r="E104">
-        <v>12.7476</v>
+        <v>15.3658</v>
       </c>
       <c t="n" r="F104">
-        <v>1.2165</v>
+        <v>5.0493</v>
       </c>
       <c t="n" r="G104">
-        <v>13.9857</v>
+        <v>13.8697</v>
       </c>
       <c t="n" r="H104">
-        <v>260.8319</v>
+        <v>93.9807</v>
       </c>
       <c t="n" r="I104">
-        <v>474.6193</v>
+        <v>443.4196</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">NG4</t>
+          <t xml:space="preserve">RAS</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C105">
-        <v>0.1100</v>
+        <v>-0.1336</v>
       </c>
       <c t="n" r="D105">
-        <v>-0.0193</v>
+        <v>0.3678</v>
       </c>
       <c t="n" r="E105">
-        <v>13.7738</v>
+        <v>12.5817</v>
       </c>
       <c t="n" r="F105">
-        <v>-0.9385</v>
+        <v>1.2221</v>
       </c>
       <c t="n" r="G105">
-        <v>13.7253</v>
+        <v>13.8557</v>
       </c>
       <c t="n" r="H105">
-        <v>225.1295</v>
+        <v>262.8896</v>
+      </c>
+      <c t="n" r="I105">
+        <v>474.6495</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">RP4</t>
+          <t xml:space="preserve">NG4</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C106">
-        <v>3.1528</v>
+        <v>0.0142</v>
       </c>
       <c t="n" r="D106">
-        <v>-5.0642</v>
+        <v>-0.0237</v>
       </c>
       <c t="n" r="E106">
-        <v>10.7816</v>
+        <v>13.7728</v>
       </c>
       <c t="n" r="F106">
-        <v>-4.1882</v>
+        <v>-0.9424</v>
       </c>
       <c t="n" r="G106">
-        <v>13.5923</v>
+        <v>13.7187</v>
       </c>
       <c t="n" r="H106">
-        <v>110.3447</v>
-      </c>
-      <c t="n" r="I106">
-        <v>363.5625</v>
+        <v>226.6298</v>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">RKG</t>
+          <t xml:space="preserve">RP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. NEF GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C107">
-        <v>-0.0550</v>
+        <v>1.7806</v>
       </c>
       <c t="n" r="D107">
-        <v>-0.3419</v>
+        <v>-5.0798</v>
       </c>
       <c t="n" r="E107">
-        <v>13.7144</v>
+        <v>10.6882</v>
       </c>
       <c t="n" r="F107">
-        <v>-0.5441</v>
+        <v>-4.2651</v>
       </c>
       <c t="n" r="G107">
-        <v>13.0495</v>
+        <v>13.5102</v>
       </c>
       <c t="n" r="H107">
-        <v>493.5613</v>
+        <v>110.2052</v>
+      </c>
+      <c t="n" r="I107">
+        <v>362.1929</v>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">ZVE</t>
+          <t xml:space="preserve">ILN</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. FOLKART BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C108">
-        <v>-0.0491</v>
+        <v>0.0282</v>
       </c>
       <c t="n" r="D108">
-        <v>0.0620</v>
+        <v>2.2792</v>
       </c>
       <c t="n" r="E108">
-        <v>-1.1257</v>
+        <v>3.6237</v>
       </c>
       <c t="n" r="F108">
-        <v>0.0484</v>
+        <v>2.4593</v>
       </c>
       <c t="n" r="G108">
-        <v>12.8852</v>
-      </c>
-      <c t="n" r="H108">
-        <v>124.3137</v>
+        <v>13.3912</v>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">ILN</t>
+          <t xml:space="preserve">RKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. FOLKART BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. NEF GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C109">
-        <v>0.0791</v>
+        <v>-0.0521</v>
       </c>
       <c t="n" r="D109">
-        <v>2.2912</v>
+        <v>-0.3441</v>
       </c>
       <c t="n" r="E109">
-        <v>3.6376</v>
+        <v>13.7144</v>
       </c>
       <c t="n" r="F109">
-        <v>2.4716</v>
+        <v>-0.5469</v>
       </c>
       <c t="n" r="G109">
-        <v>12.7981</v>
+        <v>13.0506</v>
+      </c>
+      <c t="n" r="H109">
+        <v>493.6903</v>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">OYE</t>
+          <t xml:space="preserve">ZVE</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALTINCI KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C110">
-        <v>-0.3298</v>
+        <v>-0.0463</v>
       </c>
       <c t="n" r="D110">
-        <v>0.6244</v>
+        <v>0.0616</v>
       </c>
       <c t="n" r="E110">
-        <v>8.8880</v>
+        <v>-1.0756</v>
       </c>
       <c t="n" r="F110">
-        <v>-1.1195</v>
+        <v>0.0508</v>
       </c>
       <c t="n" r="G110">
-        <v>12.4074</v>
+        <v>12.8910</v>
       </c>
       <c t="n" r="H110">
-        <v>201.5409</v>
-      </c>
-      <c t="n" r="I110">
-        <v>576.4341</v>
+        <v>124.3664</v>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">YG7</t>
+          <t xml:space="preserve">NBA</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C111">
-        <v>0.0644</v>
+        <v>-29.5729</v>
       </c>
       <c t="n" r="D111">
-        <v>0.7602</v>
+        <v>-33.0174</v>
       </c>
       <c t="n" r="E111">
-        <v>9.8288</v>
+        <v>1768.1377</v>
       </c>
       <c t="n" r="F111">
-        <v>0.7498</v>
+        <v>-33.1855</v>
       </c>
       <c t="n" r="G111">
-        <v>12.2456</v>
-      </c>
-      <c t="n" r="H111">
-        <v>-18.6166</v>
+        <v>12.6854</v>
       </c>
     </row>
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">NH2</t>
+          <t xml:space="preserve">OYE</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş CORNERSTONE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALTINCI KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C112">
-        <v>0.7550</v>
+        <v>-0.3316</v>
       </c>
       <c t="n" r="D112">
-        <v>1.5073</v>
+        <v>0.6162</v>
       </c>
       <c t="n" r="E112">
-        <v>4.2489</v>
+        <v>8.8858</v>
       </c>
       <c t="n" r="F112">
-        <v>3.3398</v>
+        <v>-1.1168</v>
       </c>
       <c t="n" r="G112">
-        <v>11.1844</v>
+        <v>12.6077</v>
+      </c>
+      <c t="n" r="H112">
+        <v>201.5328</v>
+      </c>
+      <c t="n" r="I112">
+        <v>576.4525</v>
       </c>
     </row>
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">NBA</t>
+          <t xml:space="preserve">YG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C113">
-        <v>-29.6328</v>
+        <v>0.1300</v>
       </c>
       <c t="n" r="D113">
-        <v>-32.9079</v>
+        <v>0.7819</v>
       </c>
       <c t="n" r="E113">
-        <v>1701.5923</v>
+        <v>9.8665</v>
       </c>
       <c t="n" r="F113">
-        <v>-33.0669</v>
+        <v>0.7678</v>
       </c>
       <c t="n" r="G113">
-        <v>10.8281</v>
+        <v>12.2003</v>
+      </c>
+      <c t="n" r="H113">
+        <v>-18.5257</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">NYD</t>
+          <t xml:space="preserve">NGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİLGE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C114">
-        <v>-1.6295</v>
+        <v>2.8119</v>
       </c>
       <c t="n" r="D114">
-        <v>-5.1301</v>
+        <v>8.6929</v>
       </c>
       <c t="n" r="E114">
-        <v>33.2840</v>
+        <v>15.8199</v>
       </c>
       <c t="n" r="F114">
-        <v>-5.2095</v>
+        <v>12.1318</v>
       </c>
       <c t="n" r="G114">
-        <v>10.4981</v>
-      </c>
-      <c t="n" r="H114">
-        <v>400.5320</v>
+        <v>11.6066</v>
       </c>
     </row>
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">NUA</t>
+          <t xml:space="preserve">NH2</t>
         </is>
       </c>
       <c t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. FORTİS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş CORNERSTONE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C115">
-        <v>0.0218</v>
+        <v>0.7223</v>
       </c>
       <c t="n" r="D115">
-        <v>0.4025</v>
+        <v>1.3929</v>
       </c>
       <c t="n" r="E115">
-        <v>27.6687</v>
+        <v>4.2582</v>
       </c>
       <c t="n" r="F115">
-        <v>0.3144</v>
+        <v>3.3421</v>
       </c>
       <c t="n" r="G115">
-        <v>10.4934</v>
-      </c>
-      <c t="n" r="H115">
-        <v>134.4802</v>
+        <v>11.0205</v>
       </c>
     </row>
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">HDU</t>
+          <t xml:space="preserve">NYD</t>
         </is>
       </c>
       <c t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİLGE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C116">
-        <v>-0.0752</v>
+        <v>-1.6623</v>
       </c>
       <c t="n" r="D116">
-        <v>-0.1796</v>
+        <v>-5.1788</v>
       </c>
       <c t="n" r="E116">
-        <v>10.8895</v>
+        <v>33.2551</v>
       </c>
       <c t="n" r="F116">
-        <v>-0.2286</v>
+        <v>-5.2449</v>
       </c>
       <c t="n" r="G116">
-        <v>10.3990</v>
+        <v>10.4975</v>
+      </c>
+      <c t="n" r="H116">
+        <v>399.2742</v>
       </c>
     </row>
     <row r="117">
       <c t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">IN9</t>
+          <t xml:space="preserve">NUA</t>
         </is>
       </c>
       <c t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. NEFES EGE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. FORTİS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C117">
-        <v>-0.3367</v>
+        <v>0.0215</v>
       </c>
       <c t="n" r="D117">
-        <v>-1.0606</v>
+        <v>0.3915</v>
       </c>
       <c t="n" r="E117">
-        <v>12.4001</v>
+        <v>27.6721</v>
       </c>
       <c t="n" r="F117">
-        <v>-1.3545</v>
+        <v>0.3088</v>
       </c>
       <c t="n" r="G117">
-        <v>10.3015</v>
+        <v>10.4898</v>
+      </c>
+      <c t="n" r="H117">
+        <v>134.4973</v>
       </c>
     </row>
     <row r="118">
       <c t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">ERP</t>
+          <t xml:space="preserve">HDU</t>
         </is>
       </c>
       <c t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">QİNVEST PORTFÖY YÖNETİMİ A.Ş. RE PİE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C118">
-        <v>0.2981</v>
+        <v>-0.0697</v>
       </c>
       <c t="n" r="D118">
-        <v>0.4165</v>
+        <v>-0.1848</v>
       </c>
       <c t="n" r="E118">
-        <v>2.2218</v>
+        <v>10.8894</v>
       </c>
       <c t="n" r="F118">
-        <v>1.1193</v>
+        <v>-0.2348</v>
       </c>
       <c t="n" r="G118">
-        <v>9.5678</v>
-      </c>
-      <c t="n" r="H118">
-        <v>129.2860</v>
-      </c>
-      <c t="n" r="I118">
-        <v>423.7006</v>
+        <v>10.3940</v>
       </c>
     </row>
     <row r="119">
       <c t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">RBG</t>
+          <t xml:space="preserve">IN9</t>
         </is>
       </c>
       <c t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. NEFES EGE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C119">
-        <v>0.4508</v>
+        <v>-0.3069</v>
       </c>
       <c t="n" r="D119">
-        <v>1.6811</v>
+        <v>-1.0789</v>
       </c>
       <c t="n" r="E119">
-        <v>6.5833</v>
+        <v>12.4000</v>
       </c>
       <c t="n" r="F119">
-        <v>1.2415</v>
+        <v>-1.3873</v>
       </c>
       <c t="n" r="G119">
-        <v>9.1298</v>
+        <v>10.3102</v>
       </c>
     </row>
     <row r="120">
@@ -3784,49 +3778,52 @@
         </is>
       </c>
       <c t="n" r="C120">
-        <v>-0.0919</v>
+        <v>0.4401</v>
       </c>
       <c t="n" r="D120">
-        <v>-0.1557</v>
+        <v>0.3737</v>
       </c>
       <c t="n" r="E120">
-        <v>9.2434</v>
+        <v>9.8238</v>
       </c>
       <c t="n" r="F120">
-        <v>-0.1304</v>
+        <v>0.3987</v>
       </c>
       <c t="n" r="G120">
-        <v>9.0343</v>
+        <v>9.6496</v>
       </c>
     </row>
     <row r="121">
       <c t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">NAG</t>
+          <t xml:space="preserve">ERP</t>
         </is>
       </c>
       <c t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AKS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">QİNVEST PORTFÖY YÖNETİMİ A.Ş. RE PİE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C121">
-        <v>0.0346</v>
+        <v>0.1571</v>
       </c>
       <c t="n" r="D121">
-        <v>-0.1096</v>
+        <v>0.4062</v>
       </c>
       <c t="n" r="E121">
-        <v>9.1721</v>
+        <v>2.1667</v>
       </c>
       <c t="n" r="F121">
-        <v>-0.0469</v>
+        <v>1.1112</v>
       </c>
       <c t="n" r="G121">
-        <v>9.0042</v>
+        <v>9.5751</v>
       </c>
       <c t="n" r="H121">
-        <v>253.8019</v>
+        <v>129.3061</v>
+      </c>
+      <c t="n" r="I121">
+        <v>423.2320</v>
       </c>
     </row>
     <row r="122">
@@ -3841,835 +3838,847 @@
         </is>
       </c>
       <c t="n" r="C122">
-        <v>0.2270</v>
+        <v>0.6829</v>
       </c>
       <c t="n" r="D122">
-        <v>1.7091</v>
+        <v>2.0047</v>
       </c>
       <c t="n" r="E122">
-        <v>8.3444</v>
+        <v>8.6613</v>
       </c>
       <c t="n" r="F122">
-        <v>1.6540</v>
+        <v>1.9484</v>
       </c>
       <c t="n" r="G122">
-        <v>8.9312</v>
+        <v>9.2516</v>
       </c>
       <c t="n" r="H122">
-        <v>125.0612</v>
+        <v>127.7635</v>
       </c>
     </row>
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">NH4</t>
+          <t xml:space="preserve">NAG</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AKS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C123">
-        <v>0.1901</v>
+        <v>0.0403</v>
       </c>
       <c t="n" r="D123">
-        <v>0.4696</v>
+        <v>-0.1158</v>
       </c>
       <c t="n" r="E123">
-        <v>3.9955</v>
+        <v>9.1729</v>
       </c>
       <c t="n" r="F123">
-        <v>0.5510</v>
+        <v>-0.0534</v>
       </c>
       <c t="n" r="G123">
-        <v>8.6270</v>
+        <v>9.0111</v>
       </c>
       <c t="n" r="H123">
-        <v>244.7802</v>
+        <v>253.8059</v>
       </c>
     </row>
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">NUI</t>
+          <t xml:space="preserve">RBG</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. TİCARİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C124">
-        <v>0.3939</v>
+        <v>0.4402</v>
       </c>
       <c t="n" r="D124">
-        <v>-1.8912</v>
+        <v>1.6735</v>
       </c>
       <c t="n" r="E124">
-        <v>7.5465</v>
+        <v>6.5909</v>
       </c>
       <c t="n" r="F124">
-        <v>-1.4228</v>
+        <v>1.2450</v>
       </c>
       <c t="n" r="G124">
-        <v>8.4587</v>
+        <v>9.0084</v>
       </c>
     </row>
     <row r="125">
       <c t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">NRY</t>
+          <t xml:space="preserve">NH4</t>
         </is>
       </c>
       <c t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ROYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C125">
-        <v>-0.5119</v>
+        <v>0.1919</v>
       </c>
       <c t="n" r="D125">
-        <v>-0.6835</v>
+        <v>0.4719</v>
       </c>
       <c t="n" r="E125">
-        <v>8.8923</v>
+        <v>3.9958</v>
       </c>
       <c t="n" r="F125">
-        <v>-0.4721</v>
+        <v>0.5457</v>
       </c>
       <c t="n" r="G125">
-        <v>8.3753</v>
+        <v>8.6310</v>
+      </c>
+      <c t="n" r="H125">
+        <v>244.3893</v>
       </c>
     </row>
     <row r="126">
       <c t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">NG5</t>
+          <t xml:space="preserve">NUI</t>
         </is>
       </c>
       <c t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. TİCARİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C126">
-        <v>-0.3527</v>
+        <v>0.3909</v>
       </c>
       <c t="n" r="D126">
-        <v>-0.2293</v>
+        <v>-1.9219</v>
       </c>
       <c t="n" r="E126">
-        <v>12.1098</v>
+        <v>7.5288</v>
       </c>
       <c t="n" r="F126">
-        <v>-0.9748</v>
+        <v>-1.4484</v>
       </c>
       <c t="n" r="G126">
-        <v>7.6336</v>
-      </c>
-      <c t="n" r="H126">
-        <v>213.9079</v>
+        <v>8.4431</v>
       </c>
     </row>
     <row r="127">
       <c t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">GJS</t>
+          <t xml:space="preserve">NRY</t>
         </is>
       </c>
       <c t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. SAĞLAM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ROYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C127">
-        <v>1.2541</v>
+        <v>-0.4976</v>
       </c>
       <c t="n" r="D127">
-        <v>0.8244</v>
+        <v>-0.6582</v>
       </c>
       <c t="n" r="E127">
-        <v>6.5472</v>
+        <v>8.8891</v>
       </c>
       <c t="n" r="F127">
-        <v>0.7390</v>
+        <v>-0.4888</v>
       </c>
       <c t="n" r="G127">
-        <v>6.6122</v>
-      </c>
-      <c t="n" r="H127">
-        <v>160.6203</v>
+        <v>8.3743</v>
       </c>
     </row>
     <row r="128">
       <c t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">OCH</t>
+          <t xml:space="preserve">NG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. OC HEDEF GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C128">
-        <v>-0.6872</v>
+        <v>-0.3494</v>
       </c>
       <c t="n" r="D128">
-        <v>-0.5413</v>
+        <v>-0.2307</v>
       </c>
       <c t="n" r="E128">
-        <v>5.9065</v>
+        <v>12.1060</v>
       </c>
       <c t="n" r="F128">
-        <v>-0.4658</v>
+        <v>-0.9808</v>
       </c>
       <c t="n" r="G128">
-        <v>6.5664</v>
+        <v>7.6172</v>
       </c>
       <c t="n" r="H128">
-        <v>111.1909</v>
+        <v>209.8109</v>
       </c>
     </row>
     <row r="129">
       <c t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">RTM</t>
+          <t xml:space="preserve">GJS</t>
         </is>
       </c>
       <c t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. TM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. SAĞLAM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C129">
-        <v>-0.3717</v>
+        <v>1.2459</v>
       </c>
       <c t="n" r="D129">
-        <v>-0.3841</v>
+        <v>0.8321</v>
       </c>
       <c t="n" r="E129">
-        <v>7.2274</v>
+        <v>6.5712</v>
       </c>
       <c t="n" r="F129">
-        <v>-0.3807</v>
+        <v>0.7455</v>
       </c>
       <c t="n" r="G129">
-        <v>6.5282</v>
+        <v>6.6265</v>
       </c>
       <c t="n" r="H129">
-        <v>233.4040</v>
+        <v>160.6960</v>
       </c>
     </row>
     <row r="130">
       <c t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">RG5</t>
+          <t xml:space="preserve">OCH</t>
         </is>
       </c>
       <c t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DİCLE PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. OC HEDEF GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C130">
-        <v>-0.0510</v>
+        <v>-0.7034</v>
       </c>
       <c t="n" r="D130">
-        <v>-0.1416</v>
+        <v>-0.5408</v>
       </c>
       <c t="n" r="E130">
-        <v>6.6182</v>
+        <v>5.9123</v>
       </c>
       <c t="n" r="F130">
-        <v>-0.1741</v>
+        <v>-0.4647</v>
       </c>
       <c t="n" r="G130">
-        <v>6.3483</v>
+        <v>6.5804</v>
       </c>
       <c t="n" r="H130">
-        <v>305.8025</v>
+        <v>110.5810</v>
       </c>
     </row>
     <row r="131">
       <c t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">NUT</t>
+          <t xml:space="preserve">RTM</t>
         </is>
       </c>
       <c t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. NUROL TOWER GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. TM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C131">
-        <v>0.2717</v>
+        <v>-0.3744</v>
       </c>
       <c t="n" r="D131">
-        <v>1.0259</v>
+        <v>-0.3841</v>
       </c>
       <c t="n" r="E131">
-        <v>13.5555</v>
+        <v>7.2274</v>
       </c>
       <c t="n" r="F131">
-        <v>1.3160</v>
+        <v>-0.3807</v>
       </c>
       <c t="n" r="G131">
-        <v>5.8550</v>
+        <v>6.5278</v>
       </c>
       <c t="n" r="H131">
-        <v>195.5235</v>
+        <v>233.3712</v>
       </c>
     </row>
     <row r="132">
       <c t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">ERS</t>
+          <t xml:space="preserve">RG5</t>
         </is>
       </c>
       <c t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DİCLE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C132">
-        <v>0.7058</v>
+        <v>-0.0474</v>
       </c>
       <c t="n" r="D132">
-        <v>1.2885</v>
+        <v>-0.1440</v>
       </c>
       <c t="n" r="E132">
-        <v>11.4611</v>
+        <v>6.6175</v>
       </c>
       <c t="n" r="F132">
-        <v>1.4977</v>
+        <v>-0.1777</v>
       </c>
       <c t="n" r="G132">
-        <v>5.6201</v>
+        <v>6.3487</v>
       </c>
       <c t="n" r="H132">
-        <v>154.4152</v>
+        <v>305.8260</v>
       </c>
     </row>
     <row r="133">
       <c t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">NUP</t>
+          <t xml:space="preserve">NUT</t>
         </is>
       </c>
       <c t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. NUROL TOWER GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C133">
-        <v>-0.0552</v>
+        <v>0.2869</v>
       </c>
       <c t="n" r="D133">
-        <v>-0.1761</v>
+        <v>1.0154</v>
       </c>
       <c t="n" r="E133">
-        <v>8.3552</v>
+        <v>13.5368</v>
       </c>
       <c t="n" r="F133">
-        <v>2.1409</v>
+        <v>1.3195</v>
       </c>
       <c t="n" r="G133">
-        <v>5.3324</v>
+        <v>5.8074</v>
+      </c>
+      <c t="n" r="H133">
+        <v>195.5274</v>
       </c>
     </row>
     <row r="134">
       <c t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">NH5</t>
+          <t xml:space="preserve">ERS</t>
         </is>
       </c>
       <c t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C134">
-        <v>1.1580</v>
+        <v>0.3271</v>
       </c>
       <c t="n" r="D134">
-        <v>3.7616</v>
+        <v>1.2897</v>
       </c>
       <c t="n" r="E134">
-        <v>9.7093</v>
+        <v>11.4667</v>
       </c>
       <c t="n" r="F134">
-        <v>4.5061</v>
+        <v>1.4978</v>
       </c>
       <c t="n" r="G134">
-        <v>5.1124</v>
+        <v>5.6191</v>
       </c>
       <c t="n" r="H134">
-        <v>90.0479</v>
+        <v>154.3959</v>
       </c>
     </row>
     <row r="135">
       <c t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">NUL</t>
+          <t xml:space="preserve">NUP</t>
         </is>
       </c>
       <c t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İGC GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C135">
-        <v>0.1613</v>
+        <v>-0.0452</v>
       </c>
       <c t="n" r="D135">
-        <v>-10.5001</v>
+        <v>-0.1771</v>
       </c>
       <c t="n" r="E135">
-        <v>0.3120</v>
+        <v>8.3571</v>
       </c>
       <c t="n" r="F135">
-        <v>-10.4726</v>
+        <v>2.1375</v>
       </c>
       <c t="n" r="G135">
-        <v>4.7810</v>
+        <v>5.3162</v>
       </c>
     </row>
     <row r="136">
       <c t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">HP1</t>
+          <t xml:space="preserve">NH5</t>
         </is>
       </c>
       <c t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C136">
-        <v>-0.2315</v>
+        <v>1.0712</v>
       </c>
       <c t="n" r="D136">
-        <v>-0.6443</v>
+        <v>3.6420</v>
       </c>
       <c t="n" r="E136">
-        <v>5.9032</v>
+        <v>9.7821</v>
       </c>
       <c t="n" r="F136">
-        <v>-0.7840</v>
+        <v>4.5434</v>
       </c>
       <c t="n" r="G136">
-        <v>4.4794</v>
+        <v>5.1923</v>
       </c>
       <c t="n" r="H136">
-        <v>113.8651</v>
+        <v>90.1210</v>
       </c>
     </row>
     <row r="137">
       <c t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">ORX</t>
+          <t xml:space="preserve">NUL</t>
         </is>
       </c>
       <c t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İGC GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C137">
-        <v>-0.1967</v>
+        <v>0.1599</v>
       </c>
       <c t="n" r="D137">
-        <v>-0.7679</v>
+        <v>-10.5401</v>
       </c>
       <c t="n" r="E137">
-        <v>0.8519</v>
+        <v>0.3031</v>
       </c>
       <c t="n" r="F137">
-        <v>-0.7373</v>
+        <v>-10.4742</v>
       </c>
       <c t="n" r="G137">
-        <v>4.0603</v>
-      </c>
-      <c t="n" r="H137">
-        <v>88.9494</v>
-      </c>
-      <c t="n" r="I137">
-        <v>58.2272</v>
+        <v>4.7664</v>
       </c>
     </row>
     <row r="138">
       <c t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">OO1</t>
+          <t xml:space="preserve">HP1</t>
         </is>
       </c>
       <c t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C138">
-        <v>-0.6082</v>
+        <v>-0.2093</v>
       </c>
       <c t="n" r="D138">
-        <v>-2.3178</v>
+        <v>-0.6595</v>
       </c>
       <c t="n" r="E138">
-        <v>-14.9118</v>
+        <v>5.9037</v>
       </c>
       <c t="n" r="F138">
-        <v>-2.5762</v>
+        <v>-0.8058</v>
       </c>
       <c t="n" r="G138">
-        <v>3.9798</v>
+        <v>4.4839</v>
+      </c>
+      <c t="n" r="H138">
+        <v>113.3187</v>
       </c>
     </row>
     <row r="139">
       <c t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">RG7</t>
+          <t xml:space="preserve">ORX</t>
         </is>
       </c>
       <c t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş DOWNTOWN OFİS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C139">
-        <v>-0.2666</v>
+        <v>-0.1605</v>
       </c>
       <c t="n" r="D139">
-        <v>-0.7971</v>
+        <v>-0.9442</v>
       </c>
       <c t="n" r="E139">
-        <v>0.6749</v>
+        <v>0.8434</v>
       </c>
       <c t="n" r="F139">
-        <v>-0.9844</v>
+        <v>-0.7542</v>
       </c>
       <c t="n" r="G139">
-        <v>3.4819</v>
+        <v>4.1920</v>
       </c>
       <c t="n" r="H139">
-        <v>169.5772</v>
+        <v>89.0709</v>
+      </c>
+      <c t="n" r="I139">
+        <v>58.2002</v>
       </c>
     </row>
     <row r="140">
       <c t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">NUK</t>
+          <t xml:space="preserve">OO1</t>
         </is>
       </c>
       <c t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C140">
-        <v>-0.0974</v>
+        <v>-0.5574</v>
       </c>
       <c t="n" r="D140">
-        <v>-0.2643</v>
+        <v>-1.6663</v>
       </c>
       <c t="n" r="E140">
-        <v>9.4879</v>
+        <v>-14.9489</v>
       </c>
       <c t="n" r="F140">
-        <v>-0.3464</v>
+        <v>-2.6370</v>
       </c>
       <c t="n" r="G140">
-        <v>3.1538</v>
-      </c>
-      <c t="n" r="H140">
-        <v>121.8537</v>
+        <v>3.9291</v>
       </c>
     </row>
     <row r="141">
       <c t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">NFE</t>
+          <t xml:space="preserve">RG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş DOWNTOWN OFİS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C141">
-        <v>-0.6931</v>
+        <v>-0.2141</v>
       </c>
       <c t="n" r="D141">
-        <v>-1.5239</v>
+        <v>-0.7772</v>
       </c>
       <c t="n" r="E141">
-        <v>100.0832</v>
+        <v>0.7069</v>
       </c>
       <c t="n" r="F141">
-        <v>-2.1297</v>
+        <v>-0.9703</v>
       </c>
       <c t="n" r="G141">
-        <v>3.1332</v>
+        <v>3.5230</v>
+      </c>
+      <c t="n" r="H141">
+        <v>171.0405</v>
       </c>
     </row>
     <row r="142">
       <c t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">PG2</t>
+          <t xml:space="preserve">NUK</t>
         </is>
       </c>
       <c t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C142">
-        <v>-0.1905</v>
+        <v>-0.0915</v>
       </c>
       <c t="n" r="D142">
-        <v>-0.4143</v>
+        <v>-0.2693</v>
       </c>
       <c t="n" r="E142">
-        <v>16.4492</v>
+        <v>9.4856</v>
       </c>
       <c t="n" r="F142">
-        <v>-0.5822</v>
+        <v>-0.3531</v>
       </c>
       <c t="n" r="G142">
-        <v>2.9973</v>
+        <v>3.1568</v>
       </c>
       <c t="n" r="H142">
-        <v>266.7326</v>
+        <v>132.8767</v>
       </c>
     </row>
     <row r="143">
       <c t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">NG6</t>
+          <t xml:space="preserve">PG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C143">
-        <v>1.1519</v>
+        <v>-0.1949</v>
       </c>
       <c t="n" r="D143">
-        <v>1.4077</v>
+        <v>-0.4130</v>
       </c>
       <c t="n" r="E143">
-        <v>5.0002</v>
+        <v>16.4512</v>
       </c>
       <c t="n" r="F143">
-        <v>-0.7228</v>
+        <v>-0.5801</v>
       </c>
       <c t="n" r="G143">
-        <v>2.8685</v>
+        <v>2.9995</v>
       </c>
       <c t="n" r="H143">
-        <v>266.0754</v>
+        <v>269.3076</v>
       </c>
     </row>
     <row r="144">
       <c t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">RBU</t>
+          <t xml:space="preserve">NG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C144">
-        <v>0.6628</v>
+        <v>1.2694</v>
       </c>
       <c t="n" r="D144">
-        <v>-1.9153</v>
+        <v>1.4287</v>
       </c>
       <c t="n" r="E144">
-        <v>1.9039</v>
+        <v>5.0718</v>
       </c>
       <c t="n" r="F144">
-        <v>-1.1981</v>
+        <v>-0.6486</v>
       </c>
       <c t="n" r="G144">
-        <v>2.5393</v>
+        <v>2.9258</v>
+      </c>
+      <c t="n" r="H144">
+        <v>266.3492</v>
       </c>
     </row>
     <row r="145">
       <c t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">NUC</t>
+          <t xml:space="preserve">NFE</t>
         </is>
       </c>
       <c t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. CHARM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C145">
-        <v>-0.0102</v>
+        <v>-0.6769</v>
       </c>
       <c t="n" r="D145">
-        <v>-0.3133</v>
+        <v>-1.5461</v>
       </c>
       <c t="n" r="E145">
-        <v>7.8859</v>
+        <v>99.8614</v>
       </c>
       <c t="n" r="F145">
-        <v>-0.3751</v>
+        <v>-2.1486</v>
       </c>
       <c t="n" r="G145">
-        <v>2.2556</v>
-      </c>
-      <c t="n" r="H145">
-        <v>131.0038</v>
+        <v>2.9162</v>
       </c>
     </row>
     <row r="146">
       <c t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">AHR</t>
+          <t xml:space="preserve">RBU</t>
         </is>
       </c>
       <c t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ONUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C146">
-        <v>-1.9900</v>
+        <v>0.6623</v>
       </c>
       <c t="n" r="D146">
-        <v>-1.6825</v>
+        <v>-1.9250</v>
       </c>
       <c t="n" r="E146">
-        <v>3.6854</v>
+        <v>1.9063</v>
       </c>
       <c t="n" r="F146">
-        <v>-1.5784</v>
+        <v>-1.1978</v>
       </c>
       <c t="n" r="G146">
-        <v>1.0919</v>
+        <v>2.5500</v>
       </c>
     </row>
     <row r="147">
       <c t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">OKG</t>
+          <t xml:space="preserve">NUC</t>
         </is>
       </c>
       <c t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. EMLAK JET GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. CHARM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C147">
-        <v>-0.1461</v>
+        <v>-0.0068</v>
       </c>
       <c t="n" r="D147">
-        <v>-0.6607</v>
+        <v>-0.3313</v>
       </c>
       <c t="n" r="E147">
-        <v>2.1563</v>
+        <v>7.8846</v>
       </c>
       <c t="n" r="F147">
-        <v>-1.6329</v>
+        <v>-0.3828</v>
       </c>
       <c t="n" r="G147">
-        <v>1.0326</v>
+        <v>2.2624</v>
       </c>
       <c t="n" r="H147">
-        <v>70.5305</v>
+        <v>130.9874</v>
       </c>
     </row>
     <row r="148">
       <c t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">RF3</t>
+          <t xml:space="preserve">AHR</t>
         </is>
       </c>
       <c t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ONUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C148">
-        <v>-0.1937</v>
+        <v>-1.9919</v>
       </c>
       <c t="n" r="D148">
-        <v>-0.6913</v>
+        <v>-1.6834</v>
+      </c>
+      <c t="n" r="E148">
+        <v>3.6859</v>
       </c>
       <c t="n" r="F148">
-        <v>-0.9374</v>
+        <v>-1.5774</v>
       </c>
       <c t="n" r="G148">
-        <v>0.0270</v>
+        <v>1.0904</v>
       </c>
     </row>
     <row r="149">
       <c t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">BKA</t>
+          <t xml:space="preserve">OKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ANKA GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. EMLAK JET GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C149">
+        <v>-0.1462</v>
       </c>
       <c t="n" r="D149">
-        <v>0.0000</v>
+        <v>-0.6889</v>
       </c>
       <c t="n" r="E149">
-        <v>0.0000</v>
+        <v>2.1592</v>
       </c>
       <c t="n" r="F149">
-        <v>0.0000</v>
+        <v>-1.6406</v>
       </c>
       <c t="n" r="G149">
-        <v>0.0000</v>
+        <v>1.0524</v>
       </c>
       <c t="n" r="H149">
-        <v>0.0000</v>
+        <v>70.7214</v>
       </c>
     </row>
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">HP5</t>
+          <t xml:space="preserve">RF3</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="E150">
-        <v>0.0000</v>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C150">
+        <v>-0.1788</v>
+      </c>
+      <c t="n" r="D150">
+        <v>-0.7025</v>
       </c>
       <c t="n" r="F150">
-        <v>0.0000</v>
+        <v>-0.9499</v>
       </c>
       <c t="n" r="G150">
-        <v>0.0000</v>
+        <v>0.0928</v>
       </c>
     </row>
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">HP4</t>
+          <t xml:space="preserve">BKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ MASTERTÜRK GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ANKA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="D151">
+        <v>0.0000</v>
       </c>
       <c t="n" r="E151">
         <v>0.0000</v>
@@ -4680,23 +4689,20 @@
       <c t="n" r="G151">
         <v>0.0000</v>
       </c>
+      <c t="n" r="H151">
+        <v>0.0000</v>
+      </c>
     </row>
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">NGA</t>
+          <t xml:space="preserve">HP5</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C152">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="D152">
-        <v>0.0000</v>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="E152">
         <v>0.0000</v>
@@ -4711,16 +4717,13 @@
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">NFA</t>
+          <t xml:space="preserve">HP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="D153">
-        <v>0.0000</v>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ MASTERTÜRK GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="E153">
         <v>0.0000</v>
@@ -4735,13 +4738,16 @@
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">RF1</t>
+          <t xml:space="preserve">NGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C154">
+        <v>0.0000</v>
       </c>
       <c t="n" r="D154">
         <v>0.0000</v>
@@ -4759,13 +4765,22 @@
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">RDO</t>
+          <t xml:space="preserve">NFA</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN OTEL GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="D155">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="E155">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="F155">
+        <v>0.0000</v>
       </c>
       <c t="n" r="G155">
         <v>0.0000</v>
@@ -4774,13 +4789,22 @@
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">RMK</t>
+          <t xml:space="preserve">RF1</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EMLAK KATILIM YENİ EVİM GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="D156">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="E156">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="F156">
+        <v>0.0000</v>
       </c>
       <c t="n" r="G156">
         <v>0.0000</v>
@@ -4789,12 +4813,12 @@
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">RF2</t>
+          <t xml:space="preserve">RDO</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN OTEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G157">
@@ -4804,12 +4828,12 @@
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">RSM</t>
+          <t xml:space="preserve">RMK</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SMART PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EMLAK KATILIM YENİ EVİM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G158">
@@ -4819,12 +4843,12 @@
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">RSO</t>
+          <t xml:space="preserve">RF2</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SONNE PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G159">
@@ -4834,12 +4858,12 @@
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">RTO</t>
+          <t xml:space="preserve">RSM</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TOROS PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SMART PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G160">
@@ -4849,12 +4873,12 @@
     <row r="161">
       <c t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">RGN</t>
+          <t xml:space="preserve">RSO</t>
         </is>
       </c>
       <c t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SONNE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G161">
@@ -4864,346 +4888,334 @@
     <row r="162">
       <c t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">IIG</t>
+          <t xml:space="preserve">RTO</t>
         </is>
       </c>
       <c t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C162">
-        <v>2.1483</v>
-      </c>
-      <c t="n" r="D162">
-        <v>8.7752</v>
-      </c>
-      <c t="n" r="E162">
-        <v>17.4239</v>
-      </c>
-      <c t="n" r="F162">
-        <v>8.9445</v>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TOROS PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="G162">
-        <v>-0.5607</v>
-      </c>
-      <c t="n" r="H162">
-        <v>153.0705</v>
-      </c>
-      <c t="n" r="I162">
-        <v>495.9748</v>
+        <v>0.0000</v>
       </c>
     </row>
     <row r="163">
       <c t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">NUN</t>
+          <t xml:space="preserve">IIG</t>
         </is>
       </c>
       <c t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. KELEŞOĞLU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C163">
-        <v>-0.2674</v>
+        <v>0.2975</v>
       </c>
       <c t="n" r="D163">
-        <v>-0.7530</v>
+        <v>8.7463</v>
       </c>
       <c t="n" r="E163">
-        <v>-0.2657</v>
+        <v>17.1696</v>
       </c>
       <c t="n" r="F163">
-        <v>-0.8717</v>
+        <v>9.0349</v>
       </c>
       <c t="n" r="G163">
-        <v>-1.5893</v>
+        <v>-0.4726</v>
+      </c>
+      <c t="n" r="H163">
+        <v>153.2588</v>
+      </c>
+      <c t="n" r="I163">
+        <v>496.4624</v>
       </c>
     </row>
     <row r="164">
       <c t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">ZPV</t>
+          <t xml:space="preserve">NUN</t>
         </is>
       </c>
       <c t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. KELEŞOĞLU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C164">
-        <v>8.4215</v>
+        <v>-0.2421</v>
       </c>
       <c t="n" r="D164">
-        <v>8.4422</v>
+        <v>-0.7722</v>
       </c>
       <c t="n" r="E164">
-        <v>3.1174</v>
+        <v>-0.2703</v>
       </c>
       <c t="n" r="F164">
-        <v>7.1636</v>
+        <v>-0.8981</v>
       </c>
       <c t="n" r="G164">
-        <v>-5.7828</v>
-      </c>
-      <c t="n" r="H164">
-        <v>98.5700</v>
+        <v>-1.5876</v>
       </c>
     </row>
     <row r="165">
       <c t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">OO2</t>
+          <t xml:space="preserve">ZPV</t>
         </is>
       </c>
       <c t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
         </is>
       </c>
       <c t="n" r="C165">
-        <v>-2.2629</v>
+        <v>6.7287</v>
       </c>
       <c t="n" r="D165">
-        <v>-10.0672</v>
+        <v>6.3763</v>
       </c>
       <c t="n" r="E165">
-        <v>-11.8740</v>
+        <v>1.6688</v>
       </c>
       <c t="n" r="F165">
-        <v>-10.2760</v>
+        <v>5.6605</v>
       </c>
       <c t="n" r="G165">
-        <v>-7.4864</v>
+        <v>-7.4594</v>
+      </c>
+      <c t="n" r="H165">
+        <v>95.2654</v>
       </c>
     </row>
     <row r="166">
       <c t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">RYZ</t>
+          <t xml:space="preserve">OO2</t>
         </is>
       </c>
       <c t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C166">
-        <v>0.3874</v>
+        <v>-2.2006</v>
       </c>
       <c t="n" r="D166">
-        <v>-0.5676</v>
+        <v>-7.6220</v>
       </c>
       <c t="n" r="E166">
-        <v>2.4295</v>
+        <v>-11.9397</v>
       </c>
       <c t="n" r="F166">
-        <v>-0.2951</v>
+        <v>-10.3500</v>
       </c>
       <c t="n" r="G166">
-        <v>-11.4573</v>
+        <v>-7.5501</v>
       </c>
     </row>
     <row r="167">
       <c t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">RSH</t>
+          <t xml:space="preserve">RYZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SEYHAN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C167">
-        <v>0.1816</v>
+        <v>0.3881</v>
       </c>
       <c t="n" r="D167">
-        <v>4.3586</v>
+        <v>-0.5729</v>
       </c>
       <c t="n" r="E167">
-        <v>4.7842</v>
+        <v>2.4307</v>
       </c>
       <c t="n" r="F167">
-        <v>4.0964</v>
+        <v>-0.2959</v>
       </c>
       <c t="n" r="G167">
-        <v>-13.3922</v>
+        <v>-11.4533</v>
       </c>
     </row>
     <row r="168">
       <c t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">ZVD</t>
+          <t xml:space="preserve">RSH</t>
         </is>
       </c>
       <c t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SEYHAN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C168">
-        <v>-0.0369</v>
+        <v>0.1693</v>
       </c>
       <c t="n" r="D168">
-        <v>-0.1070</v>
+        <v>4.3540</v>
       </c>
       <c t="n" r="E168">
-        <v>-17.3162</v>
+        <v>4.7927</v>
       </c>
       <c t="n" r="F168">
-        <v>-0.1321</v>
+        <v>4.1016</v>
       </c>
       <c t="n" r="G168">
-        <v>-13.9675</v>
-      </c>
-      <c t="n" r="H168">
-        <v>196.4747</v>
+        <v>-13.3843</v>
       </c>
     </row>
     <row r="169">
       <c t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">YG6</t>
+          <t xml:space="preserve">ZVD</t>
         </is>
       </c>
       <c t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MANOLYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C169">
-        <v>-0.5572</v>
+        <v>-0.0348</v>
       </c>
       <c t="n" r="D169">
-        <v>-1.5514</v>
+        <v>-0.1091</v>
       </c>
       <c t="n" r="E169">
-        <v>-17.3545</v>
+        <v>-17.3171</v>
       </c>
       <c t="n" r="F169">
-        <v>-1.7795</v>
+        <v>-0.1348</v>
       </c>
       <c t="n" r="G169">
-        <v>-18.4998</v>
+        <v>-13.9674</v>
       </c>
       <c t="n" r="H169">
-        <v>-2.9943</v>
+        <v>196.3034</v>
       </c>
     </row>
     <row r="170">
       <c t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">RG8</t>
+          <t xml:space="preserve">YG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. MERİÇ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MANOLYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C170">
-        <v>0.1560</v>
+        <v>-0.5139</v>
       </c>
       <c t="n" r="D170">
-        <v>-0.5686</v>
+        <v>-1.5530</v>
       </c>
       <c t="n" r="E170">
-        <v>-17.9097</v>
+        <v>-17.3549</v>
       </c>
       <c t="n" r="F170">
-        <v>-0.0514</v>
+        <v>-1.8041</v>
       </c>
       <c t="n" r="G170">
-        <v>-18.7629</v>
+        <v>-18.4915</v>
       </c>
       <c t="n" r="H170">
-        <v>91.3901</v>
+        <v>-2.9532</v>
       </c>
     </row>
     <row r="171">
       <c t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">YG3</t>
+          <t xml:space="preserve">RG8</t>
         </is>
       </c>
       <c t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. MERİÇ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C171">
-        <v>-0.3033</v>
+        <v>0.1133</v>
       </c>
       <c t="n" r="D171">
-        <v>-0.8311</v>
+        <v>-0.5744</v>
       </c>
       <c t="n" r="E171">
-        <v>-23.3507</v>
+        <v>-17.9089</v>
       </c>
       <c t="n" r="F171">
-        <v>-0.9738</v>
+        <v>-0.0539</v>
       </c>
       <c t="n" r="G171">
-        <v>-24.4679</v>
+        <v>-18.7606</v>
       </c>
       <c t="n" r="H171">
-        <v>350.2536</v>
+        <v>91.3713</v>
       </c>
     </row>
     <row r="172">
       <c t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">REO</t>
+          <t xml:space="preserve">YG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C172">
-        <v>-0.0160</v>
+        <v>-0.2813</v>
       </c>
       <c t="n" r="D172">
-        <v>-0.0526</v>
+        <v>-0.8458</v>
       </c>
       <c t="n" r="E172">
-        <v>-0.0858</v>
+        <v>-23.3514</v>
       </c>
       <c t="n" r="F172">
-        <v>-0.0611</v>
+        <v>-0.9957</v>
       </c>
       <c t="n" r="G172">
-        <v>-24.5048</v>
+        <v>-24.4645</v>
+      </c>
+      <c t="n" r="H172">
+        <v>350.2507</v>
       </c>
     </row>
     <row r="173">
       <c t="inlineStr" r="A173">
         <is>
-          <t xml:space="preserve">NGO</t>
+          <t xml:space="preserve">REO</t>
         </is>
       </c>
       <c t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C173">
-        <v>3.0055</v>
+        <v>-0.0160</v>
       </c>
       <c t="n" r="D173">
-        <v>8.9224</v>
+        <v>-0.0526</v>
       </c>
       <c t="n" r="E173">
-        <v>15.8018</v>
+        <v>-0.0859</v>
       </c>
       <c t="n" r="F173">
-        <v>12.0277</v>
+        <v>-0.0611</v>
       </c>
       <c t="n" r="G173">
-        <v>-27.4095</v>
+        <v>-24.5005</v>
       </c>
     </row>
     <row r="174">
@@ -5218,25 +5230,25 @@
         </is>
       </c>
       <c t="n" r="C174">
-        <v>-0.0841</v>
+        <v>-0.0790</v>
       </c>
       <c t="n" r="D174">
-        <v>-0.2646</v>
+        <v>-0.2747</v>
       </c>
       <c t="n" r="E174">
-        <v>-50.6990</v>
+        <v>-50.7321</v>
       </c>
       <c t="n" r="F174">
-        <v>-1.0441</v>
+        <v>-1.0505</v>
       </c>
       <c t="n" r="G174">
-        <v>-30.3272</v>
+        <v>-30.3229</v>
       </c>
       <c t="n" r="H174">
-        <v>71.0452</v>
+        <v>71.0482</v>
       </c>
       <c t="n" r="I174">
-        <v>785.2110</v>
+        <v>785.1535</v>
       </c>
     </row>
     <row r="175">
@@ -5251,22 +5263,22 @@
         </is>
       </c>
       <c t="n" r="C175">
-        <v>-0.6689</v>
+        <v>-0.6398</v>
       </c>
       <c t="n" r="D175">
-        <v>-1.7385</v>
+        <v>-1.7419</v>
       </c>
       <c t="n" r="E175">
-        <v>-30.4556</v>
+        <v>-30.4559</v>
       </c>
       <c t="n" r="F175">
-        <v>-1.9278</v>
+        <v>-1.9517</v>
       </c>
       <c t="n" r="G175">
-        <v>-30.8139</v>
+        <v>-30.8235</v>
       </c>
       <c t="n" r="H175">
-        <v>102.9169</v>
+        <v>102.9259</v>
       </c>
     </row>
     <row r="176">
@@ -5281,22 +5293,22 @@
         </is>
       </c>
       <c t="n" r="C176">
-        <v>-0.2068</v>
+        <v>-0.1954</v>
       </c>
       <c t="n" r="D176">
-        <v>-3.4590</v>
+        <v>-3.4675</v>
       </c>
       <c t="n" r="E176">
-        <v>5.0924</v>
+        <v>5.0890</v>
       </c>
       <c t="n" r="F176">
-        <v>-7.3350</v>
+        <v>-7.3457</v>
       </c>
       <c t="n" r="G176">
-        <v>-40.9108</v>
+        <v>-40.9111</v>
       </c>
       <c t="n" r="H176">
-        <v>113.6668</v>
+        <v>113.6524</v>
       </c>
     </row>
     <row r="177">
@@ -5311,25 +5323,25 @@
         </is>
       </c>
       <c t="n" r="C177">
-        <v>-0.4420</v>
+        <v>-0.4541</v>
       </c>
       <c t="n" r="D177">
-        <v>-18.5518</v>
+        <v>-18.5577</v>
       </c>
       <c t="n" r="E177">
-        <v>-40.7908</v>
+        <v>-40.7806</v>
       </c>
       <c t="n" r="F177">
-        <v>-52.0220</v>
+        <v>-52.0184</v>
       </c>
       <c t="n" r="G177">
-        <v>-41.7084</v>
+        <v>-41.6898</v>
       </c>
       <c t="n" r="H177">
-        <v>-2.7136</v>
+        <v>-2.6072</v>
       </c>
       <c t="n" r="I177">
-        <v>217.4144</v>
+        <v>217.4383</v>
       </c>
     </row>
     <row r="178">
@@ -5344,22 +5356,22 @@
         </is>
       </c>
       <c t="n" r="C178">
-        <v>-0.2346</v>
+        <v>-0.1431</v>
       </c>
       <c t="n" r="D178">
-        <v>-23.7506</v>
+        <v>-23.7558</v>
       </c>
       <c t="n" r="E178">
-        <v>-23.0525</v>
+        <v>-23.0544</v>
       </c>
       <c t="n" r="F178">
-        <v>-26.0856</v>
+        <v>-26.0910</v>
       </c>
       <c t="n" r="G178">
-        <v>-43.1306</v>
+        <v>-43.1301</v>
       </c>
       <c t="n" r="H178">
-        <v>40.5741</v>
+        <v>40.5694</v>
       </c>
     </row>
     <row r="179">
@@ -5374,19 +5386,19 @@
         </is>
       </c>
       <c t="n" r="C179">
-        <v>-82.0340</v>
+        <v>-82.0537</v>
       </c>
       <c t="n" r="D179">
-        <v>-83.9343</v>
+        <v>-83.9676</v>
       </c>
       <c t="n" r="E179">
-        <v>-76.2836</v>
+        <v>-76.3320</v>
       </c>
       <c t="n" r="F179">
-        <v>-83.9548</v>
+        <v>-83.9910</v>
       </c>
       <c t="n" r="G179">
-        <v>-54.8384</v>
+        <v>-54.5990</v>
       </c>
     </row>
     <row r="180">
@@ -5401,118 +5413,118 @@
         </is>
       </c>
       <c t="n" r="C180">
-        <v>4.0732</v>
+        <v>4.1329</v>
       </c>
       <c t="n" r="D180">
-        <v>7.4057</v>
+        <v>7.0247</v>
       </c>
       <c t="n" r="E180">
-        <v>-10.7678</v>
+        <v>-9.9771</v>
       </c>
       <c t="n" r="F180">
-        <v>-13.0532</v>
+        <v>-12.8320</v>
       </c>
       <c t="n" r="G180">
-        <v>-59.0689</v>
+        <v>-58.9620</v>
       </c>
       <c t="n" r="H180">
-        <v>-20.2109</v>
+        <v>-20.0122</v>
       </c>
       <c t="n" r="I180">
-        <v>334.1298</v>
+        <v>335.1301</v>
       </c>
     </row>
     <row r="181">
       <c t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">YD1</t>
+          <t xml:space="preserve">RP5</t>
         </is>
       </c>
       <c t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş.MİLENYUM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C181">
-        <v>-23.6104</v>
+        <v>-1.2914</v>
       </c>
       <c t="n" r="D181">
-        <v>-76.9761</v>
+        <v>35.8306</v>
       </c>
       <c t="n" r="E181">
-        <v>-75.7943</v>
+        <v>-63.4906</v>
       </c>
       <c t="n" r="F181">
-        <v>-77.0165</v>
+        <v>55.0695</v>
       </c>
       <c t="n" r="G181">
-        <v>-67.3160</v>
+        <v>-66.2324</v>
       </c>
       <c t="n" r="H181">
-        <v>-84.9025</v>
+        <v>-68.8958</v>
       </c>
       <c t="n" r="I181">
-        <v>-44.8504</v>
+        <v>-16.3292</v>
       </c>
     </row>
     <row r="182">
       <c t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">RP5</t>
+          <t xml:space="preserve">GF3</t>
         </is>
       </c>
       <c t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş.MİLENYUM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C182">
-        <v>-2.6070</v>
+        <v>-26.5669</v>
       </c>
       <c t="n" r="D182">
-        <v>11.4095</v>
+        <v>-40.5795</v>
       </c>
       <c t="n" r="E182">
-        <v>-65.5168</v>
+        <v>444.0308</v>
       </c>
       <c t="n" r="F182">
-        <v>55.1049</v>
+        <v>-40.6016</v>
       </c>
       <c t="n" r="G182">
-        <v>-67.5844</v>
-      </c>
-      <c t="n" r="H182">
-        <v>-68.8814</v>
-      </c>
-      <c t="n" r="I182">
-        <v>-16.3018</v>
+        <v>-67.0972</v>
       </c>
     </row>
     <row r="183">
       <c t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">GF3</t>
+          <t xml:space="preserve">YD1</t>
         </is>
       </c>
       <c t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C183">
-        <v>-26.7131</v>
+        <v>-24.7717</v>
       </c>
       <c t="n" r="D183">
-        <v>-40.0275</v>
+        <v>-76.9662</v>
       </c>
       <c t="n" r="E183">
-        <v>402.6300</v>
+        <v>-75.7923</v>
       </c>
       <c t="n" r="F183">
-        <v>-40.0429</v>
+        <v>-77.0187</v>
       </c>
       <c t="n" r="G183">
-        <v>-68.1195</v>
+        <v>-67.3201</v>
+      </c>
+      <c t="n" r="H183">
+        <v>-84.9017</v>
+      </c>
+      <c t="n" r="I183">
+        <v>-44.8555</v>
       </c>
     </row>
     <row r="184">
@@ -5530,7 +5542,7 @@
         <v>-87.7193</v>
       </c>
       <c t="n" r="D184">
-        <v>-98.7931</v>
+        <v>-93.9130</v>
       </c>
       <c t="n" r="E184">
         <v>-96.2567</v>
@@ -5557,22 +5569,22 @@
         </is>
       </c>
       <c t="n" r="C185">
-        <v>-98.9092</v>
+        <v>-98.9038</v>
       </c>
       <c t="n" r="D185">
-        <v>-99.1376</v>
+        <v>-99.1307</v>
       </c>
       <c t="n" r="E185">
-        <v>-99.0846</v>
+        <v>-99.0769</v>
       </c>
       <c t="n" r="F185">
-        <v>-99.1453</v>
+        <v>-99.1382</v>
       </c>
       <c t="n" r="G185">
-        <v>-99.1803</v>
+        <v>-99.1732</v>
       </c>
       <c t="n" r="H185">
-        <v>-98.5989</v>
+        <v>-98.5904</v>
       </c>
     </row>
     <row r="186">
@@ -5635,13 +5647,13 @@
         </is>
       </c>
       <c t="n" r="C190">
-        <v>1.2794</v>
+        <v>1.4645</v>
       </c>
       <c t="n" r="D190">
-        <v>3.2435</v>
+        <v>3.4366</v>
       </c>
       <c t="n" r="F190">
-        <v>3.9615</v>
+        <v>4.1998</v>
       </c>
     </row>
     <row r="191">
@@ -5680,13 +5692,13 @@
         </is>
       </c>
       <c t="n" r="C193">
-        <v>-17.8664</v>
+        <v>-16.6727</v>
       </c>
       <c t="n" r="D193">
-        <v>-38.0485</v>
+        <v>-39.4426</v>
       </c>
       <c t="n" r="F193">
-        <v>-41.9450</v>
+        <v>-43.3399</v>
       </c>
     </row>
     <row r="194">
@@ -5701,13 +5713,13 @@
         </is>
       </c>
       <c t="n" r="C194">
-        <v>-10.0897</v>
+        <v>-10.3321</v>
       </c>
       <c t="n" r="D194">
-        <v>-63.0951</v>
+        <v>-63.2151</v>
       </c>
       <c t="n" r="F194">
-        <v>-28.1658</v>
+        <v>-28.0572</v>
       </c>
     </row>
     <row r="195">
@@ -5734,7 +5746,7 @@
         </is>
       </c>
       <c t="n" r="C196">
-        <v>1.5983</v>
+        <v>1.6064</v>
       </c>
     </row>
     <row r="197">
@@ -5749,13 +5761,13 @@
         </is>
       </c>
       <c t="n" r="C197">
-        <v>0.8272</v>
+        <v>0.8126</v>
       </c>
       <c t="n" r="D197">
-        <v>2.0024</v>
+        <v>1.9988</v>
       </c>
       <c t="n" r="F197">
-        <v>1.8871</v>
+        <v>1.8854</v>
       </c>
     </row>
     <row r="198">
@@ -5842,10 +5854,10 @@
         </is>
       </c>
       <c t="n" r="C204">
-        <v>1.3626</v>
+        <v>0.3719</v>
       </c>
       <c t="n" r="D204">
-        <v>3.0980</v>
+        <v>2.1031</v>
       </c>
     </row>
     <row r="205">
@@ -5860,16 +5872,16 @@
         </is>
       </c>
       <c t="n" r="C205">
-        <v>1.8740</v>
+        <v>1.7261</v>
       </c>
       <c t="n" r="D205">
-        <v>418.3414</v>
+        <v>417.0733</v>
       </c>
       <c t="n" r="E205">
-        <v>460.7232</v>
+        <v>460.8613</v>
       </c>
       <c t="n" r="F205">
-        <v>425.4831</v>
+        <v>425.8669</v>
       </c>
     </row>
     <row r="206">
@@ -5884,16 +5896,16 @@
         </is>
       </c>
       <c t="n" r="C206">
-        <v>12.0463</v>
+        <v>11.9295</v>
       </c>
       <c t="n" r="D206">
-        <v>44.2053</v>
+        <v>43.7518</v>
       </c>
       <c t="n" r="E206">
-        <v>58.7087</v>
+        <v>58.5430</v>
       </c>
       <c t="n" r="F206">
-        <v>46.5038</v>
+        <v>46.5044</v>
       </c>
     </row>
     <row r="207">
@@ -5920,16 +5932,16 @@
         </is>
       </c>
       <c t="n" r="C208">
-        <v>-0.0476</v>
+        <v>-0.0445</v>
       </c>
       <c t="n" r="D208">
-        <v>-0.1076</v>
+        <v>-0.1108</v>
       </c>
       <c t="n" r="E208">
-        <v>19.3921</v>
+        <v>19.3887</v>
       </c>
       <c t="n" r="F208">
-        <v>-0.1397</v>
+        <v>-0.1434</v>
       </c>
     </row>
     <row r="209">
@@ -5944,7 +5956,7 @@
         </is>
       </c>
       <c t="n" r="C209">
-        <v>-0.0180</v>
+        <v>-0.0245</v>
       </c>
     </row>
     <row r="210">
@@ -5971,16 +5983,16 @@
         </is>
       </c>
       <c t="n" r="C211">
-        <v>3.1791</v>
+        <v>2.9905</v>
       </c>
       <c t="n" r="D211">
-        <v>9.0955</v>
+        <v>8.9054</v>
       </c>
       <c t="n" r="E211">
-        <v>19.5721</v>
+        <v>19.5911</v>
       </c>
       <c t="n" r="F211">
-        <v>10.8584</v>
+        <v>10.9968</v>
       </c>
     </row>
     <row r="212">
@@ -6007,10 +6019,10 @@
         </is>
       </c>
       <c t="n" r="C213">
-        <v>-0.1077</v>
+        <v>-0.1078</v>
       </c>
       <c t="n" r="D213">
-        <v>-0.3216</v>
+        <v>-0.3218</v>
       </c>
       <c t="n" r="F213">
         <v>-0.3294</v>
@@ -6028,10 +6040,10 @@
         </is>
       </c>
       <c t="n" r="C214">
-        <v>-0.9668</v>
+        <v>-0.8886</v>
       </c>
       <c t="n" r="D214">
-        <v>6.7817</v>
+        <v>6.7103</v>
       </c>
     </row>
     <row r="215">
@@ -6046,7 +6058,7 @@
         </is>
       </c>
       <c t="n" r="C215">
-        <v>-0.0795</v>
+        <v>-0.2600</v>
       </c>
     </row>
     <row r="216">
@@ -6061,16 +6073,16 @@
         </is>
       </c>
       <c t="n" r="C216">
-        <v>-0.0371</v>
+        <v>-0.0342</v>
       </c>
       <c t="n" r="D216">
-        <v>-0.0972</v>
+        <v>-0.0995</v>
       </c>
       <c t="n" r="E216">
-        <v>12.7800</v>
+        <v>12.7794</v>
       </c>
       <c t="n" r="F216">
-        <v>-0.1161</v>
+        <v>-0.1194</v>
       </c>
     </row>
     <row r="217">
@@ -6085,16 +6097,16 @@
         </is>
       </c>
       <c t="n" r="C217">
-        <v>0.7976</v>
+        <v>-0.0084</v>
       </c>
       <c t="n" r="D217">
-        <v>2.7868</v>
+        <v>2.7802</v>
       </c>
       <c t="n" r="E217">
-        <v>12.5214</v>
+        <v>12.5153</v>
       </c>
       <c t="n" r="F217">
-        <v>3.1051</v>
+        <v>3.1037</v>
       </c>
     </row>
     <row r="218">
@@ -6109,16 +6121,16 @@
         </is>
       </c>
       <c t="n" r="C218">
-        <v>-90.7942</v>
+        <v>-95.2551</v>
       </c>
       <c t="n" r="D218">
-        <v>-99.9055</v>
+        <v>-99.9518</v>
       </c>
       <c t="n" r="E218">
-        <v>-99.9914</v>
+        <v>-99.9955</v>
       </c>
       <c t="n" r="F218">
-        <v>-99.9843</v>
+        <v>-99.9919</v>
       </c>
     </row>
     <row r="219">
@@ -6241,16 +6253,16 @@
         </is>
       </c>
       <c t="n" r="C228">
-        <v>5.4685</v>
+        <v>10.1256</v>
       </c>
       <c t="n" r="D228">
-        <v>0.3344</v>
+        <v>4.5594</v>
       </c>
       <c t="n" r="E228">
-        <v>15.8346</v>
+        <v>21.2201</v>
       </c>
       <c t="n" r="F228">
-        <v>10.7607</v>
+        <v>16.0164</v>
       </c>
     </row>
     <row r="229">
@@ -6289,16 +6301,16 @@
         </is>
       </c>
       <c t="n" r="C231">
-        <v>0.9524</v>
+        <v>0.8756</v>
       </c>
       <c t="n" r="D231">
-        <v>5.1779</v>
+        <v>4.9950</v>
       </c>
       <c t="n" r="E231">
-        <v>13.8089</v>
+        <v>13.8603</v>
       </c>
       <c t="n" r="F231">
-        <v>6.7219</v>
+        <v>6.8363</v>
       </c>
     </row>
     <row r="232">
@@ -6313,16 +6325,16 @@
         </is>
       </c>
       <c t="n" r="C232">
-        <v>3.2309</v>
+        <v>2.9299</v>
       </c>
       <c t="n" r="D232">
-        <v>9.3349</v>
+        <v>9.5130</v>
       </c>
       <c t="n" r="E232">
-        <v>20.6913</v>
+        <v>20.9450</v>
       </c>
       <c t="n" r="F232">
-        <v>11.2313</v>
+        <v>11.5511</v>
       </c>
     </row>
     <row r="233">
@@ -6337,16 +6349,16 @@
         </is>
       </c>
       <c t="n" r="C233">
-        <v>0.9284</v>
+        <v>1.0898</v>
       </c>
       <c t="n" r="D233">
-        <v>1.6015</v>
+        <v>1.3543</v>
       </c>
       <c t="n" r="E233">
-        <v>3.9764</v>
+        <v>3.9078</v>
       </c>
       <c t="n" r="F233">
-        <v>1.9664</v>
+        <v>1.9769</v>
       </c>
     </row>
     <row r="234">
@@ -6373,16 +6385,16 @@
         </is>
       </c>
       <c t="n" r="C235">
-        <v>1.0394</v>
+        <v>0.9625</v>
       </c>
       <c t="n" r="D235">
-        <v>5.2686</v>
+        <v>5.0854</v>
       </c>
       <c t="n" r="E235">
-        <v>13.9070</v>
+        <v>13.9583</v>
       </c>
       <c t="n" r="F235">
-        <v>6.8139</v>
+        <v>6.9282</v>
       </c>
     </row>
     <row r="236">
@@ -6433,13 +6445,13 @@
         </is>
       </c>
       <c t="n" r="C239">
-        <v>-1.8164</v>
+        <v>-1.4486</v>
       </c>
       <c t="n" r="D239">
-        <v>-81.0644</v>
+        <v>-80.7985</v>
       </c>
       <c t="n" r="F239">
-        <v>-84.7334</v>
+        <v>-84.7394</v>
       </c>
     </row>
     <row r="240">
@@ -6469,1422 +6481,1386 @@
     <row r="242">
       <c t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">HVG</t>
+          <t xml:space="preserve">HGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C242">
-        <v>-0.0534</v>
+        <v>-0.0748</v>
       </c>
       <c t="n" r="D242">
-        <v>-0.1394</v>
+        <v>-0.2469</v>
       </c>
       <c t="n" r="E242">
-        <v>30.4727</v>
+        <v>1628.0437</v>
       </c>
       <c t="n" r="F242">
-        <v>-0.1716</v>
+        <v>-0.2840</v>
       </c>
     </row>
     <row r="243">
       <c t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">HGG</t>
+          <t xml:space="preserve">HV2</t>
         </is>
       </c>
       <c t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C243">
-        <v>-0.0874</v>
-      </c>
-      <c t="n" r="D243">
-        <v>-0.2191</v>
-      </c>
-      <c t="n" r="E243">
-        <v>1624.7266</v>
-      </c>
-      <c t="n" r="F243">
-        <v>-0.2656</v>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="244">
       <c t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">HV2</t>
+          <t xml:space="preserve">HG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">HG2</t>
+          <t xml:space="preserve">HVY</t>
         </is>
       </c>
       <c t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YENİ UFUKLAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">HVY</t>
+          <t xml:space="preserve">HLN</t>
         </is>
       </c>
       <c t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YENİ UFUKLAR GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C246">
+        <v>-5.3652</v>
+      </c>
+      <c t="n" r="D246">
+        <v>-15.6301</v>
+      </c>
+      <c t="n" r="F246">
+        <v>-17.8511</v>
       </c>
     </row>
     <row r="247">
       <c t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">HLN</t>
+          <t xml:space="preserve">HMP</t>
         </is>
       </c>
       <c t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C247">
-        <v>-5.9494</v>
+        <v>-5.6975</v>
       </c>
       <c t="n" r="D247">
-        <v>-14.8888</v>
+        <v>-16.0311</v>
+      </c>
+      <c t="n" r="E247">
+        <v>-24.9807</v>
       </c>
       <c t="n" r="F247">
-        <v>-17.1567</v>
+        <v>-18.0174</v>
       </c>
     </row>
     <row r="248">
       <c t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">HMP</t>
+          <t xml:space="preserve">HIK</t>
         </is>
       </c>
       <c t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C248">
-        <v>-6.1543</v>
-      </c>
-      <c t="n" r="D248">
-        <v>-15.3276</v>
-      </c>
-      <c t="n" r="E248">
-        <v>-24.3582</v>
-      </c>
-      <c t="n" r="F248">
-        <v>-17.3879</v>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="249">
       <c t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">HIK</t>
+          <t xml:space="preserve">HG8</t>
         </is>
       </c>
       <c t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">HG8</t>
+          <t xml:space="preserve">HMA</t>
         </is>
       </c>
       <c t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">HMA</t>
+          <t xml:space="preserve">IRJ</t>
         </is>
       </c>
       <c t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">IRJ</t>
+          <t xml:space="preserve">BRY</t>
         </is>
       </c>
       <c t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BORYAL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">BRY</t>
+          <t xml:space="preserve">IDT</t>
         </is>
       </c>
       <c t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BORYAL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. GELİŞİM TRAKYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">IDT</t>
+          <t xml:space="preserve">IE1</t>
         </is>
       </c>
       <c t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. GELİŞİM TRAKYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">IE1</t>
+          <t xml:space="preserve">IY3</t>
         </is>
       </c>
       <c t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C255">
+        <v>-86.0685</v>
+      </c>
+      <c t="n" r="D255">
+        <v>-88.5763</v>
+      </c>
+      <c t="n" r="E255">
+        <v>-75.1848</v>
+      </c>
+      <c t="n" r="F255">
+        <v>-88.5933</v>
       </c>
     </row>
     <row r="256">
       <c t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">IY3</t>
+          <t xml:space="preserve">IY2</t>
         </is>
       </c>
       <c t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C256">
-        <v>-86.0218</v>
+        <v>-1.3604</v>
       </c>
       <c t="n" r="D256">
-        <v>-88.5205</v>
-      </c>
-      <c t="n" r="E256">
-        <v>-75.0623</v>
+        <v>-13.3484</v>
       </c>
       <c t="n" r="F256">
-        <v>-88.5346</v>
+        <v>-13.4982</v>
       </c>
     </row>
     <row r="257">
       <c t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">IY2</t>
+          <t xml:space="preserve">VMG</t>
         </is>
       </c>
       <c t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">İSRA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C257">
-        <v>-1.5029</v>
+        <v>-5.8159</v>
       </c>
       <c t="n" r="D257">
-        <v>-13.2578</v>
+        <v>-6.4686</v>
+      </c>
+      <c t="n" r="E257">
+        <v>-9.3143</v>
       </c>
       <c t="n" r="F257">
-        <v>-13.3699</v>
+        <v>-4.5993</v>
       </c>
     </row>
     <row r="258">
       <c t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">VMG</t>
+          <t xml:space="preserve">VMP</t>
         </is>
       </c>
       <c t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C258">
-        <v>-5.9461</v>
-      </c>
-      <c t="n" r="D258">
-        <v>-6.4506</v>
-      </c>
-      <c t="n" r="E258">
-        <v>-9.3087</v>
-      </c>
-      <c t="n" r="F258">
-        <v>-4.5758</v>
+          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="259">
       <c t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">VMP</t>
+          <t xml:space="preserve">KPE</t>
         </is>
       </c>
       <c t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. KAR PAYI ÖDEYEN GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C259">
+        <v>3.0773</v>
       </c>
     </row>
     <row r="260">
       <c t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">KPE</t>
+          <t xml:space="preserve">RIN</t>
         </is>
       </c>
       <c t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. KAR PAYI ÖDEYEN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. RİNNOVA PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C260">
-        <v>3.3239</v>
+        <v>-0.0782</v>
       </c>
     </row>
     <row r="261">
       <c t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">RIN</t>
+          <t xml:space="preserve">ITO</t>
         </is>
       </c>
       <c t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. RİNNOVA PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C261">
-        <v>-0.0951</v>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. T-FON PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="262">
       <c t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">ITO</t>
+          <t xml:space="preserve">UNO</t>
         </is>
       </c>
       <c t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. T-FON PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. UNİCON PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">UNO</t>
+          <t xml:space="preserve">YAL</t>
         </is>
       </c>
       <c t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. UNİCON PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C263">
+        <v>8.9013</v>
       </c>
     </row>
     <row r="264">
       <c t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">YAL</t>
+          <t xml:space="preserve">YLP</t>
         </is>
       </c>
       <c t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C264">
-        <v>80.2997</v>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="265">
       <c t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">YLP</t>
+          <t xml:space="preserve">KBN</t>
         </is>
       </c>
       <c t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C265">
+        <v>0.9229</v>
+      </c>
+      <c t="n" r="D265">
+        <v>5.3759</v>
+      </c>
+      <c t="n" r="F265">
+        <v>6.9627</v>
       </c>
     </row>
     <row r="266">
       <c t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">KBN</t>
+          <t xml:space="preserve">KKR</t>
         </is>
       </c>
       <c t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C266">
-        <v>1.1333</v>
+        <v>0.8678</v>
       </c>
       <c t="n" r="D266">
-        <v>5.6990</v>
+        <v>5.2960</v>
       </c>
       <c t="n" r="F266">
-        <v>7.0011</v>
+        <v>6.8822</v>
       </c>
     </row>
     <row r="267">
       <c t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">KKR</t>
+          <t xml:space="preserve">MDG</t>
         </is>
       </c>
       <c t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">KUVEYT TÜRK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C267">
-        <v>1.0872</v>
-      </c>
-      <c t="n" r="D267">
-        <v>5.6281</v>
-      </c>
-      <c t="n" r="F267">
-        <v>6.9299</v>
+          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="268">
       <c t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">MDG</t>
+          <t xml:space="preserve">NAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">MAQASİD GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DOĞAN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C268">
+        <v>-29.4004</v>
+      </c>
+      <c t="n" r="D268">
+        <v>-28.0677</v>
+      </c>
+      <c t="n" r="E268">
+        <v>-23.7384</v>
+      </c>
+      <c t="n" r="F268">
+        <v>-27.2141</v>
       </c>
     </row>
     <row r="269">
       <c t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">NAA</t>
+          <t xml:space="preserve">NGB</t>
         </is>
       </c>
       <c t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTINCI PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C269">
-        <v>-30.5196</v>
-      </c>
-      <c t="n" r="D269">
-        <v>-27.9137</v>
-      </c>
-      <c t="n" r="E269">
-        <v>-23.6951</v>
-      </c>
-      <c t="n" r="F269">
-        <v>-27.2013</v>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="270">
       <c t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">NGB</t>
+          <t xml:space="preserve">NBR</t>
         </is>
       </c>
       <c t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C270">
+        <v>-0.4371</v>
+      </c>
+      <c t="n" r="D270">
+        <v>-1.4505</v>
+      </c>
+      <c t="n" r="E270">
+        <v>-32.3293</v>
+      </c>
+      <c t="n" r="F270">
+        <v>95.7068</v>
       </c>
     </row>
     <row r="271">
       <c t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">NBR</t>
+          <t xml:space="preserve">NGD</t>
         </is>
       </c>
       <c t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C271">
-        <v>-0.4858</v>
-      </c>
-      <c t="n" r="D271">
-        <v>-1.4272</v>
-      </c>
-      <c t="n" r="E271">
-        <v>-32.8953</v>
-      </c>
-      <c t="n" r="F271">
-        <v>95.7660</v>
+        <v>33.7609</v>
       </c>
     </row>
     <row r="272">
       <c t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">NGD</t>
+          <t xml:space="preserve">GNC</t>
         </is>
       </c>
       <c t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. GNC KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C272">
-        <v>28.5666</v>
+        <v>-0.3219</v>
+      </c>
+      <c t="n" r="D272">
+        <v>-0.8859</v>
+      </c>
+      <c t="n" r="F272">
+        <v>-2.3331</v>
       </c>
     </row>
     <row r="273">
       <c t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">GNC</t>
+          <t xml:space="preserve">NIK</t>
         </is>
       </c>
       <c t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. GNC KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C273">
-        <v>-0.3504</v>
+        <v>-77.3787</v>
       </c>
       <c t="n" r="D273">
-        <v>-0.9014</v>
+        <v>-87.8722</v>
+      </c>
+      <c t="n" r="E273">
+        <v>-45.8616</v>
       </c>
       <c t="n" r="F273">
-        <v>-2.3052</v>
+        <v>106.2584</v>
       </c>
     </row>
     <row r="274">
       <c t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">NIK</t>
+          <t xml:space="preserve">NGR</t>
         </is>
       </c>
       <c t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C274">
-        <v>-74.1573</v>
-      </c>
-      <c t="n" r="D274">
-        <v>-86.0146</v>
-      </c>
-      <c t="n" r="E274">
-        <v>-40.2198</v>
-      </c>
-      <c t="n" r="F274">
-        <v>137.2746</v>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. RİVA PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="275">
       <c t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">NGR</t>
+          <t xml:space="preserve">NGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. RİVA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">NGU</t>
+          <t xml:space="preserve">NBP</t>
         </is>
       </c>
       <c t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">NATURA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C276">
+        <v>-0.0573</v>
+      </c>
+      <c t="n" r="D276">
+        <v>-10.8353</v>
+      </c>
+      <c t="n" r="F276">
+        <v>-9.7212</v>
       </c>
     </row>
     <row r="277">
       <c t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">NBP</t>
+          <t xml:space="preserve">NP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C277">
-        <v>-0.0648</v>
-      </c>
-      <c t="n" r="D277">
-        <v>-10.6300</v>
-      </c>
-      <c t="n" r="F277">
-        <v>-9.7109</v>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="278">
       <c t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">NP4</t>
+          <t xml:space="preserve">NKN</t>
         </is>
       </c>
       <c t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C278">
+        <v>2.9924</v>
+      </c>
+      <c t="n" r="D278">
+        <v>-59.0990</v>
+      </c>
+      <c t="n" r="E278">
+        <v>-98.9263</v>
+      </c>
+      <c t="n" r="F278">
+        <v>-98.1659</v>
       </c>
     </row>
     <row r="279">
       <c t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">NKN</t>
+          <t xml:space="preserve">MAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C279">
-        <v>3.1810</v>
-      </c>
-      <c t="n" r="D279">
-        <v>-59.4114</v>
-      </c>
-      <c t="n" r="E279">
-        <v>-99.0287</v>
-      </c>
-      <c t="n" r="F279">
-        <v>-98.1683</v>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. MAANAA LEVENT PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="280">
       <c t="inlineStr" r="A280">
         <is>
-          <t xml:space="preserve">MAA</t>
+          <t xml:space="preserve">NGM</t>
         </is>
       </c>
       <c t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. MAANAA LEVENT PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C280">
+        <v>-0.2988</v>
+      </c>
+      <c t="n" r="D280">
+        <v>0.8692</v>
+      </c>
+      <c t="n" r="E280">
+        <v>-96.4050</v>
+      </c>
+      <c t="n" r="F280">
+        <v>0.8311</v>
       </c>
     </row>
     <row r="281">
       <c t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">NGM</t>
+          <t xml:space="preserve">NP5</t>
         </is>
       </c>
       <c t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C281">
-        <v>-0.2988</v>
-      </c>
-      <c t="n" r="D281">
-        <v>0.9074</v>
-      </c>
-      <c t="n" r="E281">
-        <v>-97.2413</v>
-      </c>
-      <c t="n" r="F281">
-        <v>0.8311</v>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="282">
       <c t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">NP5</t>
+          <t xml:space="preserve">ND4</t>
         </is>
       </c>
       <c t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">ND4</t>
+          <t xml:space="preserve">NIP</t>
         </is>
       </c>
       <c t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C283">
+        <v>-6.2990</v>
+      </c>
+      <c t="n" r="D283">
+        <v>-33.9867</v>
+      </c>
+      <c t="n" r="E283">
+        <v>4935.5467</v>
+      </c>
+      <c t="n" r="F283">
+        <v>11356.7496</v>
       </c>
     </row>
     <row r="284">
       <c t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">NIP</t>
+          <t xml:space="preserve">NPO</t>
         </is>
       </c>
       <c t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C284">
-        <v>-0.4877</v>
+        <v>-0.0180</v>
       </c>
       <c t="n" r="D284">
-        <v>-29.8208</v>
-      </c>
-      <c t="n" r="E284">
-        <v>5127.3903</v>
+        <v>-0.0680</v>
       </c>
       <c t="n" r="F284">
-        <v>12081.2452</v>
+        <v>-0.0237</v>
       </c>
     </row>
     <row r="285">
       <c t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">NPO</t>
+          <t xml:space="preserve">NR3</t>
         </is>
       </c>
       <c t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONİKİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C285">
-        <v>-0.0320</v>
-      </c>
-      <c t="n" r="D285">
-        <v>-0.0524</v>
-      </c>
-      <c t="n" r="F285">
-        <v>-0.0149</v>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="286">
       <c t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">NR3</t>
+          <t xml:space="preserve">NU3</t>
         </is>
       </c>
       <c t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">NU3</t>
+          <t xml:space="preserve">OG4</t>
         </is>
       </c>
       <c t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">OG4</t>
+          <t xml:space="preserve">OGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C288">
+        <v>-28.1577</v>
       </c>
     </row>
     <row r="289">
       <c t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">OGG</t>
+          <t xml:space="preserve">OLN</t>
         </is>
       </c>
       <c t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C289">
-        <v>-74.7812</v>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="290">
       <c t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">OLN</t>
+          <t xml:space="preserve">FGY</t>
         </is>
       </c>
       <c t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ALTINCI GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C290">
+        <v>0.4850</v>
+      </c>
+      <c t="n" r="D290">
+        <v>2.5671</v>
+      </c>
+      <c t="n" r="E290">
+        <v>10.2739</v>
+      </c>
+      <c t="n" r="F290">
+        <v>3.1249</v>
       </c>
     </row>
     <row r="291">
       <c t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">FGY</t>
+          <t xml:space="preserve">BCP</t>
         </is>
       </c>
       <c t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C291">
-        <v>0.5962</v>
-      </c>
-      <c t="n" r="D291">
-        <v>2.6877</v>
-      </c>
-      <c t="n" r="E291">
-        <v>10.3020</v>
-      </c>
-      <c t="n" r="F291">
-        <v>3.1429</v>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="292">
       <c t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">BCP</t>
+          <t xml:space="preserve">GF4</t>
         </is>
       </c>
       <c t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C292">
+        <v>-26.7876</v>
+      </c>
+      <c t="n" r="D292">
+        <v>-57.7434</v>
+      </c>
+      <c t="n" r="E292">
+        <v>-57.4681</v>
+      </c>
+      <c t="n" r="F292">
+        <v>-56.9607</v>
       </c>
     </row>
     <row r="293">
       <c t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">GF4</t>
+          <t xml:space="preserve">OGK</t>
         </is>
       </c>
       <c t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C293">
-        <v>-26.6958</v>
-      </c>
-      <c t="n" r="D293">
-        <v>-57.5327</v>
-      </c>
-      <c t="n" r="E293">
-        <v>-57.3908</v>
-      </c>
-      <c t="n" r="F293">
-        <v>-56.8921</v>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. GENYAP KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="294">
       <c t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">OGK</t>
+          <t xml:space="preserve">BP2</t>
         </is>
       </c>
       <c t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. GENYAP KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">BP2</t>
+          <t xml:space="preserve">ORF</t>
         </is>
       </c>
       <c t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AGREGA PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C295">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="D295">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="E295">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="F295">
+        <v>0.0000</v>
       </c>
     </row>
     <row r="296">
       <c t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">ORF</t>
+          <t xml:space="preserve">OAZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AGREGA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYYILDIZ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C296">
-        <v>-0.0050</v>
+        <v>0.0000</v>
       </c>
       <c t="n" r="D296">
-        <v>-0.0050</v>
+        <v>0.0000</v>
       </c>
       <c t="n" r="E296">
-        <v>-0.0050</v>
+        <v>0.0000</v>
       </c>
       <c t="n" r="F296">
-        <v>-0.0050</v>
+        <v>0.0000</v>
       </c>
     </row>
     <row r="297">
       <c t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">OAZ</t>
+          <t xml:space="preserve">OO4</t>
         </is>
       </c>
       <c t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYYILDIZ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C297">
-        <v>-0.0050</v>
-      </c>
-      <c t="n" r="D297">
-        <v>-0.0050</v>
-      </c>
-      <c t="n" r="E297">
-        <v>-0.0050</v>
-      </c>
-      <c t="n" r="F297">
-        <v>-0.0050</v>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="298">
       <c t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">OO4</t>
+          <t xml:space="preserve">OO3</t>
         </is>
       </c>
       <c t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">OO3</t>
+          <t xml:space="preserve">BCI</t>
         </is>
       </c>
       <c t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C299">
+        <v>3.3016</v>
+      </c>
+      <c t="n" r="D299">
+        <v>9.9905</v>
+      </c>
+      <c t="n" r="E299">
+        <v>21.0490</v>
+      </c>
+      <c t="n" r="F299">
+        <v>12.4447</v>
       </c>
     </row>
     <row r="300">
       <c t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">BCI</t>
+          <t xml:space="preserve">PGN</t>
         </is>
       </c>
       <c t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C300">
-        <v>3.5287</v>
+        <v>3.2076</v>
       </c>
       <c t="n" r="D300">
-        <v>10.2863</v>
-      </c>
-      <c t="n" r="E300">
-        <v>21.2785</v>
+        <v>9.1881</v>
       </c>
       <c t="n" r="F300">
-        <v>12.3291</v>
+        <v>11.6520</v>
       </c>
     </row>
     <row r="301">
       <c t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">PGN</t>
+          <t xml:space="preserve">DDG</t>
         </is>
       </c>
       <c t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C301">
-        <v>3.4389</v>
-      </c>
-      <c t="n" r="D301">
-        <v>9.4795</v>
-      </c>
-      <c t="n" r="F301">
-        <v>11.5330</v>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="302">
       <c t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">DDG</t>
+          <t xml:space="preserve">KCI</t>
         </is>
       </c>
       <c t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C302">
+        <v>3.8178</v>
+      </c>
+      <c t="n" r="D302">
+        <v>11.6007</v>
+      </c>
+      <c t="n" r="F302">
+        <v>14.3393</v>
       </c>
     </row>
     <row r="303">
       <c t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">KCI</t>
+          <t xml:space="preserve">UUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C303">
-        <v>4.1429</v>
-      </c>
-      <c t="n" r="D303">
-        <v>11.8996</v>
-      </c>
-      <c t="n" r="F303">
-        <v>14.1960</v>
+        <v>-74.1352</v>
       </c>
     </row>
     <row r="304">
       <c t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">UUG</t>
+          <t xml:space="preserve">GY2</t>
         </is>
       </c>
       <c t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">QINVEST PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C304">
-        <v>-72.5167</v>
+        <v>-0.0277</v>
+      </c>
+      <c t="n" r="D304">
+        <v>-0.9002</v>
       </c>
     </row>
     <row r="305">
       <c t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">GY2</t>
+          <t xml:space="preserve">GM1</t>
         </is>
       </c>
       <c t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">QINVEST PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">QİNVEST PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C305">
-        <v>-0.0222</v>
+        <v>0.7848</v>
       </c>
       <c t="n" r="D305">
-        <v>-0.8703</v>
+        <v>5.8841</v>
+      </c>
+      <c t="n" r="E305">
+        <v>14.4945</v>
+      </c>
+      <c t="n" r="F305">
+        <v>7.4039</v>
       </c>
     </row>
     <row r="306">
       <c t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">GM1</t>
+          <t xml:space="preserve">RI5</t>
         </is>
       </c>
       <c t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">QİNVEST PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C306">
-        <v>1.2005</v>
-      </c>
-      <c t="n" r="D306">
-        <v>5.9469</v>
-      </c>
-      <c t="n" r="E306">
-        <v>14.5062</v>
-      </c>
-      <c t="n" r="F306">
-        <v>7.3671</v>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="307">
       <c t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">RI5</t>
+          <t xml:space="preserve">RE5</t>
         </is>
       </c>
       <c t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">RE5</t>
+          <t xml:space="preserve">RKP</t>
         </is>
       </c>
       <c t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C308">
+        <v>1.8269</v>
+      </c>
+      <c t="n" r="D308">
+        <v>3.3822</v>
+      </c>
+      <c t="n" r="E308">
+        <v>11.9289</v>
+      </c>
+      <c t="n" r="F308">
+        <v>5.2171</v>
       </c>
     </row>
     <row r="309">
       <c t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">RKP</t>
+          <t xml:space="preserve">RI4</t>
         </is>
       </c>
       <c t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C309">
-        <v>1.8411</v>
-      </c>
-      <c t="n" r="D309">
-        <v>3.7493</v>
-      </c>
-      <c t="n" r="E309">
-        <v>12.1138</v>
-      </c>
-      <c t="n" r="F309">
-        <v>5.2864</v>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="310">
       <c t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">RI4</t>
+          <t xml:space="preserve">RE4</t>
         </is>
       </c>
       <c t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">RE4</t>
+          <t xml:space="preserve">EPG</t>
         </is>
       </c>
       <c t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C311">
+        <v>-0.0754</v>
+      </c>
+      <c t="n" r="D311">
+        <v>-0.2234</v>
+      </c>
+      <c t="n" r="E311">
+        <v>0.6031</v>
+      </c>
+      <c t="n" r="F311">
+        <v>-0.2553</v>
       </c>
     </row>
     <row r="312">
       <c t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">EPG</t>
+          <t xml:space="preserve">RE2</t>
         </is>
       </c>
       <c t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C312">
-        <v>-0.0825</v>
-      </c>
-      <c t="n" r="D312">
-        <v>-0.2103</v>
-      </c>
-      <c t="n" r="E312">
-        <v>0.6039</v>
-      </c>
-      <c t="n" r="F312">
-        <v>-0.2458</v>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="313">
       <c t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">RE2</t>
+          <t xml:space="preserve">RIP</t>
         </is>
       </c>
       <c t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İSTANBUL PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">RIP</t>
+          <t xml:space="preserve">RE3</t>
         </is>
       </c>
       <c t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İSTANBUL PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C314">
+        <v>-0.0530</v>
+      </c>
+      <c t="n" r="D314">
+        <v>-0.1503</v>
+      </c>
+      <c t="n" r="E314">
+        <v>2.2272</v>
+      </c>
+      <c t="n" r="F314">
+        <v>-0.1746</v>
       </c>
     </row>
     <row r="315">
       <c t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">RE3</t>
+          <t xml:space="preserve">REI</t>
         </is>
       </c>
       <c t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C315">
-        <v>-0.0573</v>
-      </c>
-      <c t="n" r="D315">
-        <v>-0.1429</v>
-      </c>
-      <c t="n" r="E315">
-        <v>2.5242</v>
-      </c>
-      <c t="n" r="F315">
-        <v>-0.1689</v>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="316">
       <c t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">REI</t>
+          <t xml:space="preserve">RNG</t>
         </is>
       </c>
       <c t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C316">
+        <v>-0.1521</v>
+      </c>
+      <c t="n" r="D316">
+        <v>-0.3508</v>
+      </c>
+      <c t="n" r="E316">
+        <v>3.0271</v>
+      </c>
+      <c t="n" r="F316">
+        <v>-0.3965</v>
       </c>
     </row>
     <row r="317">
       <c t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">RNG</t>
+          <t xml:space="preserve">ROR</t>
         </is>
       </c>
       <c t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C317">
-        <v>-0.1593</v>
-      </c>
-      <c t="n" r="D317">
-        <v>-0.3460</v>
-      </c>
-      <c t="n" r="E317">
-        <v>3.0274</v>
-      </c>
-      <c t="n" r="F317">
-        <v>-0.3893</v>
+        <v>-0.1313</v>
       </c>
     </row>
     <row r="318">
       <c t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">ROR</t>
+          <t xml:space="preserve">RGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C318">
-        <v>-0.1337</v>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="319">
       <c t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">RGU</t>
+          <t xml:space="preserve">RZB</t>
         </is>
       </c>
       <c t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. SEBA CENTER GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="E319">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="F319">
+        <v>0.0000</v>
       </c>
     </row>
     <row r="320">
       <c t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">RZB</t>
+          <t xml:space="preserve">SEB</t>
         </is>
       </c>
       <c t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. SEBA CENTER GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="E320">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="F320">
-        <v>0.0000</v>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. SEBA CENTER PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="321">
       <c t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">SEB</t>
+          <t xml:space="preserve">TCE</t>
         </is>
       </c>
       <c t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. SEBA CENTER PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">TACİRLER PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C321">
+        <v>-0.1232</v>
+      </c>
+      <c t="n" r="D321">
+        <v>-0.1207</v>
+      </c>
+      <c t="n" r="F321">
+        <v>-0.1324</v>
       </c>
     </row>
     <row r="322">
       <c t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">RTR</t>
+          <t xml:space="preserve">TN1</t>
         </is>
       </c>
       <c t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. TRAKYA GELİŞİM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">TCE</t>
+          <t xml:space="preserve">TUC</t>
         </is>
       </c>
       <c t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">TACİRLER PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C323">
-        <v>-0.1215</v>
-      </c>
-      <c t="n" r="D323">
-        <v>-0.1366</v>
-      </c>
-      <c t="n" r="F323">
-        <v>-0.1231</v>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="324">
       <c t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">TN1</t>
+          <t xml:space="preserve">ZEP</t>
         </is>
       </c>
       <c t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. EMLAK KONUT GELİR PAYLAŞIMI BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C324">
+        <v>2.7199</v>
       </c>
     </row>
     <row r="325">
       <c t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">TUC</t>
+          <t xml:space="preserve">YOR</t>
         </is>
       </c>
       <c t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c t="inlineStr" r="A326">
-        <is>
-          <t xml:space="preserve">ZEP</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B326">
-        <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. EMLAK KONUT GELİR PAYLAŞIMI BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C326">
-        <v>2.9831</v>
-      </c>
-    </row>
-    <row r="327">
-      <c t="inlineStr" r="A327">
-        <is>
-          <t xml:space="preserve">YOR</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B327">
-        <is>
           <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ORKİDE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
-      <c t="n" r="C327">
-        <v>0.1062</v>
-      </c>
-      <c t="n" r="D327">
+      <c t="n" r="C325">
+        <v>0.1274</v>
+      </c>
+      <c t="n" r="D325">
         <v>0.0000</v>
       </c>
-      <c t="n" r="E327">
+      <c t="n" r="E325">
         <v>0.0000</v>
       </c>
-      <c t="n" r="F327">
+      <c t="n" r="F325">
         <v>0.0849</v>
       </c>
     </row>

--- a/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
@@ -280,22 +280,22 @@
         </is>
       </c>
       <c t="n" r="C3">
-        <v>21.4221</v>
+        <v>21.7498</v>
       </c>
       <c t="n" r="D3">
-        <v>666.6126</v>
+        <v>668.6347</v>
       </c>
       <c t="n" r="E3">
-        <v>693.3031</v>
+        <v>695.4256</v>
       </c>
       <c t="n" r="F3">
-        <v>661.0468</v>
+        <v>663.1006</v>
       </c>
       <c t="n" r="G3">
-        <v>618.7322</v>
+        <v>620.6718</v>
       </c>
       <c t="n" r="H3">
-        <v>769.9907</v>
+        <v>773.0548</v>
       </c>
     </row>
     <row r="4">
@@ -310,19 +310,19 @@
         </is>
       </c>
       <c t="n" r="C4">
-        <v>16.1998</v>
+        <v>16.2385</v>
       </c>
       <c t="n" r="D4">
-        <v>20.4063</v>
+        <v>20.4563</v>
       </c>
       <c t="n" r="E4">
-        <v>249.5133</v>
+        <v>248.8586</v>
       </c>
       <c t="n" r="F4">
-        <v>21.1760</v>
+        <v>21.2164</v>
       </c>
       <c t="n" r="G4">
-        <v>372.9468</v>
+        <v>373.1043</v>
       </c>
     </row>
     <row r="5">
@@ -337,19 +337,19 @@
         </is>
       </c>
       <c t="n" r="C5">
-        <v>0.8944</v>
+        <v>0.9267</v>
       </c>
       <c t="n" r="D5">
-        <v>2.6309</v>
+        <v>2.6564</v>
       </c>
       <c t="n" r="E5">
-        <v>27.7408</v>
+        <v>27.7535</v>
       </c>
       <c t="n" r="F5">
-        <v>3.3942</v>
+        <v>3.4273</v>
       </c>
       <c t="n" r="G5">
-        <v>361.0086</v>
+        <v>361.1561</v>
       </c>
     </row>
     <row r="6">
@@ -364,22 +364,22 @@
         </is>
       </c>
       <c t="n" r="C6">
-        <v>-0.3978</v>
+        <v>-0.4119</v>
       </c>
       <c t="n" r="D6">
-        <v>43.1297</v>
+        <v>36.6221</v>
       </c>
       <c t="n" r="E6">
-        <v>52.7785</v>
+        <v>52.7806</v>
       </c>
       <c t="n" r="F6">
-        <v>42.2834</v>
+        <v>42.2634</v>
       </c>
       <c t="n" r="G6">
-        <v>240.1406</v>
+        <v>240.0926</v>
       </c>
       <c t="n" r="H6">
-        <v>332.7833</v>
+        <v>332.7889</v>
       </c>
     </row>
     <row r="7">
@@ -394,22 +394,22 @@
         </is>
       </c>
       <c t="n" r="C7">
-        <v>-0.0178</v>
+        <v>-0.0182</v>
       </c>
       <c t="n" r="D7">
         <v>-0.0487</v>
       </c>
       <c t="n" r="E7">
-        <v>192.5067</v>
+        <v>192.5068</v>
       </c>
       <c t="n" r="F7">
-        <v>-0.0600</v>
+        <v>-0.0603</v>
       </c>
       <c t="n" r="G7">
-        <v>191.4496</v>
+        <v>191.4485</v>
       </c>
       <c t="n" r="H7">
-        <v>167559.8662</v>
+        <v>167657.3709</v>
       </c>
     </row>
     <row r="8">
@@ -424,19 +424,19 @@
         </is>
       </c>
       <c t="n" r="C8">
-        <v>-0.0236</v>
+        <v>-0.0096</v>
       </c>
       <c t="n" r="D8">
-        <v>3.9961</v>
+        <v>4.0097</v>
       </c>
       <c t="n" r="E8">
-        <v>3.9662</v>
+        <v>3.9661</v>
       </c>
       <c t="n" r="F8">
-        <v>4.0092</v>
+        <v>4.0238</v>
       </c>
       <c t="n" r="G8">
-        <v>152.7771</v>
+        <v>152.8126</v>
       </c>
     </row>
     <row r="9">
@@ -451,19 +451,19 @@
         </is>
       </c>
       <c t="n" r="C9">
-        <v>0.7250</v>
+        <v>0.7420</v>
       </c>
       <c t="n" r="D9">
-        <v>1.0302</v>
+        <v>1.0458</v>
       </c>
       <c t="n" r="E9">
-        <v>138.0454</v>
+        <v>137.9872</v>
       </c>
       <c t="n" r="F9">
-        <v>1.5147</v>
+        <v>1.5317</v>
       </c>
       <c t="n" r="G9">
-        <v>143.1764</v>
+        <v>143.2172</v>
       </c>
     </row>
     <row r="10">
@@ -478,22 +478,22 @@
         </is>
       </c>
       <c t="n" r="C10">
-        <v>65.6756</v>
+        <v>65.6944</v>
       </c>
       <c t="n" r="D10">
-        <v>68.1525</v>
+        <v>68.1007</v>
       </c>
       <c t="n" r="E10">
-        <v>69.7829</v>
+        <v>69.7947</v>
       </c>
       <c t="n" r="F10">
-        <v>55.1437</v>
+        <v>55.1612</v>
       </c>
       <c t="n" r="G10">
-        <v>89.8580</v>
+        <v>89.8795</v>
       </c>
       <c t="n" r="H10">
-        <v>114.9439</v>
+        <v>114.9666</v>
       </c>
     </row>
     <row r="11">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c t="n" r="C11">
-        <v>1.6764</v>
+        <v>1.7292</v>
       </c>
       <c t="n" r="D11">
-        <v>2.1812</v>
+        <v>2.2249</v>
       </c>
       <c t="n" r="E11">
-        <v>76.7665</v>
+        <v>76.8535</v>
       </c>
       <c t="n" r="F11">
-        <v>33.7759</v>
+        <v>33.8454</v>
       </c>
       <c t="n" r="G11">
-        <v>82.7379</v>
+        <v>82.8329</v>
       </c>
       <c t="n" r="H11">
-        <v>299.0342</v>
+        <v>299.2993</v>
       </c>
       <c t="n" r="I11">
-        <v>1679.0140</v>
+        <v>1679.7710</v>
       </c>
     </row>
     <row r="12">
@@ -541,22 +541,22 @@
         </is>
       </c>
       <c t="n" r="C12">
-        <v>-0.1895</v>
+        <v>-0.1916</v>
       </c>
       <c t="n" r="D12">
-        <v>-0.3545</v>
+        <v>-0.3550</v>
       </c>
       <c t="n" r="E12">
-        <v>19.9333</v>
+        <v>19.9025</v>
       </c>
       <c t="n" r="F12">
-        <v>-1.0494</v>
+        <v>-1.0515</v>
       </c>
       <c t="n" r="G12">
-        <v>61.5836</v>
+        <v>61.5802</v>
       </c>
       <c t="n" r="H12">
-        <v>689.8607</v>
+        <v>695.6510</v>
       </c>
     </row>
     <row r="13">
@@ -571,163 +571,163 @@
         </is>
       </c>
       <c t="n" r="C13">
-        <v>0.1974</v>
+        <v>0.2566</v>
       </c>
       <c t="n" r="D13">
-        <v>1.3982</v>
+        <v>1.4263</v>
       </c>
       <c t="n" r="E13">
-        <v>38.5630</v>
+        <v>38.2906</v>
       </c>
       <c t="n" r="F13">
-        <v>1.3509</v>
+        <v>1.4108</v>
       </c>
       <c t="n" r="G13">
-        <v>61.3523</v>
+        <v>61.4477</v>
       </c>
       <c t="n" r="H13">
-        <v>327.8888</v>
+        <v>328.1439</v>
       </c>
       <c t="n" r="I13">
-        <v>1094.2792</v>
+        <v>1094.9855</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">AR9</t>
+          <t xml:space="preserve">TNG</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TUNA PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C14">
-        <v>-0.1115</v>
+        <v>3.7154</v>
       </c>
       <c t="n" r="D14">
-        <v>0.2723</v>
+        <v>10.3315</v>
       </c>
       <c t="n" r="E14">
-        <v>60.0175</v>
+        <v>27.7986</v>
       </c>
       <c t="n" r="F14">
-        <v>-4.4647</v>
+        <v>11.9141</v>
       </c>
       <c t="n" r="G14">
-        <v>58.6185</v>
+        <v>58.9848</v>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">TNG</t>
+          <t xml:space="preserve">AR9</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TUNA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C15">
-        <v>3.4602</v>
+        <v>-0.1145</v>
       </c>
       <c t="n" r="D15">
-        <v>10.1782</v>
+        <v>0.2722</v>
       </c>
       <c t="n" r="E15">
-        <v>27.9019</v>
+        <v>60.0161</v>
       </c>
       <c t="n" r="F15">
-        <v>11.6387</v>
+        <v>-4.4675</v>
       </c>
       <c t="n" r="G15">
-        <v>58.5935</v>
+        <v>58.6139</v>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">NG8</t>
+          <t xml:space="preserve">BRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C16">
-        <v>3.0933</v>
+        <v>7.8470</v>
       </c>
       <c t="n" r="D16">
-        <v>9.6802</v>
+        <v>24.6782</v>
       </c>
       <c t="n" r="E16">
-        <v>26.4823</v>
+        <v>32.2012</v>
       </c>
       <c t="n" r="F16">
-        <v>18.2686</v>
+        <v>33.3102</v>
       </c>
       <c t="n" r="G16">
-        <v>57.2333</v>
+        <v>58.3780</v>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">HP2</t>
+          <t xml:space="preserve">NG8</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C17">
-        <v>0.6819</v>
+        <v>3.3845</v>
       </c>
       <c t="n" r="D17">
-        <v>1.9337</v>
+        <v>10.1592</v>
       </c>
       <c t="n" r="E17">
-        <v>50.3775</v>
+        <v>26.4050</v>
       </c>
       <c t="n" r="F17">
-        <v>48.2089</v>
+        <v>18.6028</v>
       </c>
       <c t="n" r="G17">
-        <v>56.1345</v>
-      </c>
-      <c t="n" r="H17">
-        <v>462.1595</v>
+        <v>57.6776</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">BRE</t>
+          <t xml:space="preserve">HP2</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C18">
-        <v>6.2877</v>
+        <v>0.7476</v>
       </c>
       <c t="n" r="D18">
-        <v>22.9262</v>
+        <v>1.9962</v>
       </c>
       <c t="n" r="E18">
-        <v>30.2778</v>
+        <v>50.4560</v>
       </c>
       <c t="n" r="F18">
-        <v>31.3827</v>
+        <v>48.3057</v>
       </c>
       <c t="n" r="G18">
-        <v>56.0880</v>
+        <v>56.2365</v>
+      </c>
+      <c t="n" r="H18">
+        <v>462.5771</v>
       </c>
     </row>
     <row r="19">
@@ -742,19 +742,19 @@
         </is>
       </c>
       <c t="n" r="C19">
-        <v>3.4858</v>
+        <v>3.8224</v>
       </c>
       <c t="n" r="D19">
-        <v>10.2789</v>
+        <v>10.5150</v>
       </c>
       <c t="n" r="E19">
-        <v>22.3022</v>
+        <v>22.2773</v>
       </c>
       <c t="n" r="F19">
-        <v>12.3619</v>
+        <v>12.7274</v>
       </c>
       <c t="n" r="G19">
-        <v>55.6781</v>
+        <v>56.1845</v>
       </c>
     </row>
     <row r="20">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c t="n" r="C20">
-        <v>3.4855</v>
+        <v>3.8221</v>
       </c>
       <c t="n" r="D20">
-        <v>10.2779</v>
+        <v>10.5141</v>
       </c>
       <c t="n" r="E20">
-        <v>22.2998</v>
+        <v>22.2748</v>
       </c>
       <c t="n" r="F20">
-        <v>12.3606</v>
+        <v>12.7261</v>
       </c>
       <c t="n" r="G20">
-        <v>55.6704</v>
+        <v>56.1767</v>
       </c>
     </row>
     <row r="21">
@@ -796,22 +796,22 @@
         </is>
       </c>
       <c t="n" r="C21">
-        <v>0.3668</v>
+        <v>0.3739</v>
       </c>
       <c t="n" r="D21">
-        <v>0.8949</v>
+        <v>0.9047</v>
       </c>
       <c t="n" r="E21">
-        <v>1.4338</v>
+        <v>1.4417</v>
       </c>
       <c t="n" r="F21">
-        <v>0.9810</v>
+        <v>0.9881</v>
       </c>
       <c t="n" r="G21">
-        <v>55.3624</v>
+        <v>55.3734</v>
       </c>
       <c t="n" r="H21">
-        <v>410.7320</v>
+        <v>410.7683</v>
       </c>
     </row>
     <row r="22">
@@ -826,76 +826,76 @@
         </is>
       </c>
       <c t="n" r="C22">
-        <v>-0.2027</v>
+        <v>-0.2025</v>
       </c>
       <c t="n" r="D22">
-        <v>-0.2037</v>
+        <v>-0.2154</v>
       </c>
       <c t="n" r="E22">
-        <v>55.3899</v>
+        <v>55.3897</v>
       </c>
       <c t="n" r="F22">
-        <v>-0.2324</v>
+        <v>-0.2322</v>
       </c>
       <c t="n" r="G22">
-        <v>54.4083</v>
+        <v>54.4087</v>
       </c>
       <c t="n" r="H22">
-        <v>172.5091</v>
+        <v>172.5012</v>
       </c>
     </row>
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">NO1</t>
+          <t xml:space="preserve">RGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. TSL PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C23">
-        <v>4.9457</v>
+        <v>0.0307</v>
       </c>
       <c t="n" r="D23">
-        <v>6.5394</v>
+        <v>6.3910</v>
       </c>
       <c t="n" r="E23">
-        <v>23.8809</v>
+        <v>19.3793</v>
       </c>
       <c t="n" r="F23">
-        <v>15.6687</v>
+        <v>6.8982</v>
       </c>
       <c t="n" r="G23">
-        <v>54.1613</v>
+        <v>54.0494</v>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">RGF</t>
+          <t xml:space="preserve">NO1</t>
         </is>
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. TSL PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C24">
-        <v>-0.0340</v>
+        <v>4.5689</v>
       </c>
       <c t="n" r="D24">
-        <v>6.3473</v>
+        <v>7.2146</v>
       </c>
       <c t="n" r="E24">
-        <v>19.4816</v>
+        <v>23.0130</v>
       </c>
       <c t="n" r="F24">
-        <v>6.8291</v>
+        <v>15.2533</v>
       </c>
       <c t="n" r="G24">
-        <v>53.9497</v>
+        <v>53.6077</v>
       </c>
     </row>
     <row r="25">
@@ -910,19 +910,19 @@
         </is>
       </c>
       <c t="n" r="C25">
-        <v>0.0431</v>
+        <v>0.0453</v>
       </c>
       <c t="n" r="D25">
-        <v>0.0676</v>
+        <v>0.0554</v>
       </c>
       <c t="n" r="E25">
-        <v>36.2240</v>
+        <v>36.1353</v>
       </c>
       <c t="n" r="F25">
-        <v>0.2766</v>
+        <v>0.2788</v>
       </c>
       <c t="n" r="G25">
-        <v>51.1363</v>
+        <v>51.1397</v>
       </c>
     </row>
     <row r="26">
@@ -937,85 +937,85 @@
         </is>
       </c>
       <c t="n" r="C26">
-        <v>-0.2324</v>
+        <v>0.9345</v>
       </c>
       <c t="n" r="D26">
-        <v>-1.4329</v>
+        <v>-0.2744</v>
       </c>
       <c t="n" r="E26">
-        <v>28.4810</v>
+        <v>29.9954</v>
       </c>
       <c t="n" r="F26">
-        <v>-1.7320</v>
+        <v>-0.5826</v>
       </c>
       <c t="n" r="G26">
-        <v>49.0908</v>
+        <v>50.8345</v>
       </c>
       <c t="n" r="H26">
-        <v>168.1969</v>
+        <v>171.4219</v>
       </c>
       <c t="n" r="I26">
-        <v>1143.2547</v>
+        <v>1157.7954</v>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">YD5</t>
+          <t xml:space="preserve">RAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. AVRUPA-ANADOLU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C27">
-        <v>-0.2738</v>
+        <v>4.9385</v>
       </c>
       <c t="n" r="D27">
-        <v>-0.4395</v>
+        <v>11.8391</v>
       </c>
       <c t="n" r="E27">
-        <v>16.0251</v>
+        <v>20.9565</v>
       </c>
       <c t="n" r="F27">
-        <v>-0.6451</v>
+        <v>13.6622</v>
       </c>
       <c t="n" r="G27">
-        <v>48.1367</v>
-      </c>
-      <c t="n" r="H27">
-        <v>196.8714</v>
-      </c>
-      <c t="n" r="I27">
-        <v>1322.0985</v>
+        <v>48.1470</v>
       </c>
     </row>
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">RAA</t>
+          <t xml:space="preserve">YD5</t>
         </is>
       </c>
       <c t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. AVRUPA-ANADOLU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C28">
-        <v>4.8246</v>
+        <v>-0.2878</v>
       </c>
       <c t="n" r="D28">
-        <v>11.8166</v>
+        <v>-0.4484</v>
       </c>
       <c t="n" r="E28">
-        <v>20.9541</v>
+        <v>16.0200</v>
       </c>
       <c t="n" r="F28">
-        <v>13.5390</v>
+        <v>-0.6590</v>
       </c>
       <c t="n" r="G28">
-        <v>47.9863</v>
+        <v>48.1160</v>
+      </c>
+      <c t="n" r="H28">
+        <v>196.9798</v>
+      </c>
+      <c t="n" r="I28">
+        <v>1321.8995</v>
       </c>
     </row>
     <row r="29">
@@ -1030,49 +1030,49 @@
         </is>
       </c>
       <c t="n" r="C29">
-        <v>0.3987</v>
+        <v>0.4208</v>
       </c>
       <c t="n" r="D29">
-        <v>6.3302</v>
+        <v>6.3395</v>
       </c>
       <c t="n" r="E29">
-        <v>43.7316</v>
+        <v>43.6925</v>
       </c>
       <c t="n" r="F29">
-        <v>5.9695</v>
+        <v>5.9928</v>
       </c>
       <c t="n" r="G29">
-        <v>45.4449</v>
+        <v>45.4769</v>
       </c>
       <c t="n" r="H29">
-        <v>464.9724</v>
+        <v>465.0755</v>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">ZGU</t>
+          <t xml:space="preserve">YYF</t>
         </is>
       </c>
       <c t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C30">
-        <v>2.9841</v>
+        <v>3.3578</v>
       </c>
       <c t="n" r="D30">
-        <v>3.4656</v>
+        <v>8.9841</v>
       </c>
       <c t="n" r="E30">
-        <v>26.4310</v>
+        <v>19.2774</v>
       </c>
       <c t="n" r="F30">
-        <v>9.6325</v>
+        <v>11.1039</v>
       </c>
       <c t="n" r="G30">
-        <v>44.3435</v>
+        <v>44.5270</v>
       </c>
     </row>
     <row r="31">
@@ -1087,229 +1087,229 @@
         </is>
       </c>
       <c t="n" r="C31">
-        <v>0.1921</v>
+        <v>0.2415</v>
       </c>
       <c t="n" r="D31">
-        <v>-0.4840</v>
+        <v>-0.4488</v>
       </c>
       <c t="n" r="E31">
-        <v>29.4138</v>
+        <v>29.4152</v>
       </c>
       <c t="n" r="F31">
-        <v>1.6453</v>
+        <v>1.6954</v>
       </c>
       <c t="n" r="G31">
-        <v>44.1956</v>
+        <v>44.2666</v>
       </c>
     </row>
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">YYF</t>
+          <t xml:space="preserve">ZGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C32">
-        <v>3.0430</v>
+        <v>2.6391</v>
       </c>
       <c t="n" r="D32">
-        <v>8.7606</v>
+        <v>3.6843</v>
       </c>
       <c t="n" r="E32">
-        <v>19.2872</v>
+        <v>25.1787</v>
       </c>
       <c t="n" r="F32">
-        <v>10.7656</v>
+        <v>9.2652</v>
       </c>
       <c t="n" r="G32">
-        <v>44.0869</v>
+        <v>43.8600</v>
       </c>
     </row>
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">FNR</t>
+          <t xml:space="preserve">ORV</t>
         </is>
       </c>
       <c t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AVRASYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C33">
-        <v>2.3096</v>
+        <v>-0.2453</v>
       </c>
       <c t="n" r="D33">
-        <v>-0.9661</v>
+        <v>-0.4075</v>
       </c>
       <c t="n" r="E33">
-        <v>18.6537</v>
+        <v>27.3337</v>
       </c>
       <c t="n" r="F33">
-        <v>5.3862</v>
+        <v>0.1070</v>
       </c>
       <c t="n" r="G33">
-        <v>42.1689</v>
+        <v>41.6860</v>
       </c>
     </row>
     <row r="34">
       <c t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">ORV</t>
+          <t xml:space="preserve">RG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AVRASYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TRAKYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C34">
-        <v>-0.2375</v>
+        <v>-0.0775</v>
       </c>
       <c t="n" r="D34">
-        <v>-0.1671</v>
+        <v>-0.3341</v>
       </c>
       <c t="n" r="E34">
-        <v>27.3217</v>
+        <v>42.2728</v>
       </c>
       <c t="n" r="F34">
-        <v>0.1149</v>
+        <v>-0.5040</v>
       </c>
       <c t="n" r="G34">
-        <v>41.6972</v>
+        <v>41.6786</v>
+      </c>
+      <c t="n" r="H34">
+        <v>213.3103</v>
+      </c>
+      <c t="n" r="I34">
+        <v>720.5567</v>
       </c>
     </row>
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">RG3</t>
+          <t xml:space="preserve">KGB</t>
         </is>
       </c>
       <c t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TRAKYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C35">
-        <v>-0.0766</v>
+        <v>0.1750</v>
       </c>
       <c t="n" r="D35">
-        <v>-0.3341</v>
+        <v>0.5302</v>
       </c>
       <c t="n" r="E35">
-        <v>42.2740</v>
+        <v>38.6392</v>
       </c>
       <c t="n" r="F35">
-        <v>-0.5031</v>
+        <v>0.7159</v>
       </c>
       <c t="n" r="G35">
-        <v>41.6799</v>
+        <v>41.6775</v>
       </c>
       <c t="n" r="H35">
-        <v>213.3044</v>
+        <v>241.9868</v>
       </c>
       <c t="n" r="I35">
-        <v>723.2954</v>
+        <v>847.8751</v>
       </c>
     </row>
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">KGB</t>
+          <t xml:space="preserve">KGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C36">
-        <v>0.1705</v>
+        <v>0.1618</v>
       </c>
       <c t="n" r="D36">
-        <v>0.5235</v>
+        <v>0.0102</v>
       </c>
       <c t="n" r="E36">
-        <v>38.6409</v>
+        <v>41.1551</v>
       </c>
       <c t="n" r="F36">
-        <v>0.7113</v>
+        <v>0.2546</v>
       </c>
       <c t="n" r="G36">
-        <v>41.6711</v>
+        <v>41.4399</v>
       </c>
       <c t="n" r="H36">
-        <v>241.8800</v>
-      </c>
-      <c t="n" r="I36">
-        <v>847.8326</v>
+        <v>251.9588</v>
       </c>
     </row>
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">KGG</t>
+          <t xml:space="preserve">MPG</t>
         </is>
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM (TL) FONU</t>
         </is>
       </c>
       <c t="n" r="C37">
-        <v>0.1663</v>
+        <v>0.5314</v>
       </c>
       <c t="n" r="D37">
-        <v>0.0092</v>
+        <v>1.5345</v>
       </c>
       <c t="n" r="E37">
-        <v>41.1528</v>
+        <v>28.9881</v>
       </c>
       <c t="n" r="F37">
-        <v>0.2591</v>
+        <v>1.5666</v>
       </c>
       <c t="n" r="G37">
-        <v>41.4463</v>
+        <v>40.7560</v>
       </c>
       <c t="n" r="H37">
-        <v>251.8837</v>
+        <v>172.3896</v>
+      </c>
+      <c t="n" r="I37">
+        <v>400.7189</v>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">MPG</t>
+          <t xml:space="preserve">FNR</t>
         </is>
       </c>
       <c t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM (TL) FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C38">
-        <v>0.5034</v>
+        <v>1.1261</v>
       </c>
       <c t="n" r="D38">
-        <v>1.5177</v>
+        <v>-3.0780</v>
       </c>
       <c t="n" r="E38">
-        <v>28.9496</v>
+        <v>16.0658</v>
       </c>
       <c t="n" r="F38">
-        <v>1.5382</v>
+        <v>4.1671</v>
       </c>
       <c t="n" r="G38">
-        <v>40.7167</v>
-      </c>
-      <c t="n" r="H38">
-        <v>172.3067</v>
-      </c>
-      <c t="n" r="I38">
-        <v>400.5791</v>
+        <v>40.5243</v>
       </c>
     </row>
     <row r="39">
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c t="n" r="C39">
-        <v>0.4376</v>
+        <v>0.4681</v>
       </c>
       <c t="n" r="D39">
-        <v>1.6867</v>
+        <v>1.6215</v>
       </c>
       <c t="n" r="E39">
-        <v>16.1884</v>
+        <v>16.1824</v>
       </c>
       <c t="n" r="F39">
-        <v>2.0483</v>
+        <v>2.0794</v>
       </c>
       <c t="n" r="G39">
-        <v>40.2174</v>
+        <v>40.2601</v>
       </c>
       <c t="n" r="H39">
-        <v>295.3568</v>
+        <v>295.3129</v>
       </c>
       <c t="n" r="I39">
-        <v>915.9538</v>
+        <v>916.1386</v>
       </c>
     </row>
     <row r="40">
@@ -1357,25 +1357,25 @@
         </is>
       </c>
       <c t="n" r="C40">
-        <v>1.0627</v>
+        <v>1.0662</v>
       </c>
       <c t="n" r="D40">
-        <v>4.4558</v>
+        <v>4.4127</v>
       </c>
       <c t="n" r="E40">
-        <v>14.5476</v>
+        <v>14.4081</v>
       </c>
       <c t="n" r="F40">
-        <v>3.5918</v>
+        <v>3.5954</v>
       </c>
       <c t="n" r="G40">
-        <v>40.0259</v>
+        <v>40.0308</v>
       </c>
       <c t="n" r="H40">
-        <v>141.3024</v>
+        <v>141.2385</v>
       </c>
       <c t="n" r="I40">
-        <v>260.7764</v>
+        <v>260.7794</v>
       </c>
     </row>
     <row r="41">
@@ -1390,22 +1390,22 @@
         </is>
       </c>
       <c t="n" r="C41">
-        <v>0.8523</v>
+        <v>0.8373</v>
       </c>
       <c t="n" r="D41">
-        <v>5.5393</v>
+        <v>5.5339</v>
       </c>
       <c t="n" r="E41">
-        <v>34.9147</v>
+        <v>34.9036</v>
       </c>
       <c t="n" r="F41">
-        <v>13.3698</v>
+        <v>13.3530</v>
       </c>
       <c t="n" r="G41">
-        <v>39.1962</v>
+        <v>39.1756</v>
       </c>
       <c t="n" r="H41">
-        <v>842.8873</v>
+        <v>840.9152</v>
       </c>
     </row>
     <row r="42">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c t="n" r="C42">
-        <v>0.6995</v>
+        <v>0.7083</v>
       </c>
       <c t="n" r="D42">
-        <v>2.1079</v>
+        <v>2.1166</v>
       </c>
       <c t="n" r="E42">
-        <v>30.9270</v>
+        <v>30.9239</v>
       </c>
       <c t="n" r="F42">
-        <v>2.6848</v>
+        <v>2.6938</v>
       </c>
       <c t="n" r="G42">
-        <v>38.6111</v>
+        <v>38.6231</v>
       </c>
     </row>
     <row r="43">
@@ -1447,25 +1447,25 @@
         </is>
       </c>
       <c t="n" r="C43">
-        <v>0.1928</v>
+        <v>0.1870</v>
       </c>
       <c t="n" r="D43">
-        <v>-0.9306</v>
+        <v>-0.9312</v>
       </c>
       <c t="n" r="E43">
-        <v>26.0491</v>
+        <v>26.0495</v>
       </c>
       <c t="n" r="F43">
-        <v>-0.5496</v>
+        <v>-0.5554</v>
       </c>
       <c t="n" r="G43">
-        <v>38.3964</v>
+        <v>38.3884</v>
       </c>
       <c t="n" r="H43">
-        <v>326.7369</v>
+        <v>326.8080</v>
       </c>
       <c t="n" r="I43">
-        <v>713.0053</v>
+        <v>712.9582</v>
       </c>
     </row>
     <row r="44">
@@ -1480,25 +1480,25 @@
         </is>
       </c>
       <c t="n" r="C44">
-        <v>1.3165</v>
+        <v>1.3722</v>
       </c>
       <c t="n" r="D44">
-        <v>4.1784</v>
+        <v>4.1810</v>
       </c>
       <c t="n" r="E44">
-        <v>13.8978</v>
+        <v>13.8970</v>
       </c>
       <c t="n" r="F44">
-        <v>5.0291</v>
+        <v>5.0869</v>
       </c>
       <c t="n" r="G44">
-        <v>37.4447</v>
+        <v>37.5203</v>
       </c>
       <c t="n" r="H44">
-        <v>179.8663</v>
+        <v>179.8312</v>
       </c>
       <c t="n" r="I44">
-        <v>415.8104</v>
+        <v>415.9149</v>
       </c>
     </row>
     <row r="45">
@@ -1513,79 +1513,79 @@
         </is>
       </c>
       <c t="n" r="C45">
-        <v>1.6234</v>
+        <v>1.5845</v>
       </c>
       <c t="n" r="D45">
-        <v>5.1354</v>
+        <v>5.1549</v>
       </c>
       <c t="n" r="E45">
-        <v>22.1425</v>
+        <v>21.4665</v>
       </c>
       <c t="n" r="F45">
-        <v>5.7936</v>
+        <v>5.7530</v>
       </c>
       <c t="n" r="G45">
-        <v>36.2587</v>
+        <v>36.2064</v>
       </c>
     </row>
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">RP1</t>
+          <t xml:space="preserve">DIG</t>
         </is>
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NOVADA URFA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C46">
-        <v>0.7287</v>
+        <v>2.8389</v>
       </c>
       <c t="n" r="D46">
-        <v>-0.4218</v>
+        <v>7.0887</v>
       </c>
       <c t="n" r="E46">
-        <v>32.6751</v>
+        <v>15.3438</v>
       </c>
       <c t="n" r="F46">
-        <v>-0.4771</v>
+        <v>8.8358</v>
       </c>
       <c t="n" r="G46">
-        <v>35.5664</v>
-      </c>
-      <c t="n" r="H46">
-        <v>244.2912</v>
-      </c>
-      <c t="n" r="I46">
-        <v>921.6458</v>
+        <v>35.7064</v>
       </c>
     </row>
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">DIG</t>
+          <t xml:space="preserve">RP1</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">DENİZ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NOVADA URFA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C47">
-        <v>2.5206</v>
+        <v>0.7284</v>
       </c>
       <c t="n" r="D47">
-        <v>6.8428</v>
+        <v>-0.4214</v>
       </c>
       <c t="n" r="E47">
-        <v>15.3333</v>
+        <v>32.6756</v>
       </c>
       <c t="n" r="F47">
-        <v>8.4990</v>
+        <v>-0.4775</v>
       </c>
       <c t="n" r="G47">
-        <v>35.2864</v>
+        <v>35.5659</v>
+      </c>
+      <c t="n" r="H47">
+        <v>244.3034</v>
+      </c>
+      <c t="n" r="I47">
+        <v>921.6512</v>
       </c>
     </row>
     <row r="48">
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c t="n" r="C48">
-        <v>0.5367</v>
+        <v>0.5979</v>
       </c>
       <c t="n" r="D48">
-        <v>1.8006</v>
+        <v>1.8390</v>
       </c>
       <c t="n" r="E48">
-        <v>26.8196</v>
+        <v>26.6041</v>
       </c>
       <c t="n" r="F48">
-        <v>2.2672</v>
+        <v>2.3295</v>
       </c>
       <c t="n" r="G48">
-        <v>34.8681</v>
+        <v>34.9502</v>
       </c>
       <c t="n" r="H48">
-        <v>576.0369</v>
+        <v>576.5823</v>
       </c>
     </row>
     <row r="49">
@@ -1630,73 +1630,73 @@
         </is>
       </c>
       <c t="n" r="C49">
-        <v>-0.0219</v>
+        <v>-0.0211</v>
       </c>
       <c t="n" r="D49">
-        <v>-0.1104</v>
+        <v>-0.1092</v>
       </c>
       <c t="n" r="E49">
-        <v>34.0418</v>
+        <v>34.0399</v>
       </c>
       <c t="n" r="F49">
-        <v>-0.1177</v>
+        <v>-0.1169</v>
       </c>
       <c t="n" r="G49">
-        <v>34.5360</v>
+        <v>34.5370</v>
       </c>
     </row>
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">TUG</t>
+          <t xml:space="preserve">IRG</t>
         </is>
       </c>
       <c t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C50">
-        <v>1.9226</v>
+        <v>0.9908</v>
       </c>
       <c t="n" r="D50">
-        <v>2.9722</v>
+        <v>3.8633</v>
       </c>
       <c t="n" r="E50">
-        <v>11.3360</v>
+        <v>13.0458</v>
       </c>
       <c t="n" r="F50">
-        <v>4.2160</v>
+        <v>4.0844</v>
       </c>
       <c t="n" r="G50">
-        <v>33.6574</v>
+        <v>33.7588</v>
       </c>
     </row>
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">IRG</t>
+          <t xml:space="preserve">TUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C51">
-        <v>0.8985</v>
+        <v>1.7605</v>
       </c>
       <c t="n" r="D51">
-        <v>3.8053</v>
+        <v>2.8806</v>
       </c>
       <c t="n" r="E51">
-        <v>12.9919</v>
+        <v>11.0184</v>
       </c>
       <c t="n" r="F51">
-        <v>3.9893</v>
+        <v>4.0502</v>
       </c>
       <c t="n" r="G51">
-        <v>33.6365</v>
+        <v>33.4447</v>
       </c>
     </row>
     <row r="52">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c t="n" r="C52">
-        <v>0.2708</v>
+        <v>0.2719</v>
       </c>
       <c t="n" r="D52">
-        <v>0.7691</v>
+        <v>0.7721</v>
       </c>
       <c t="n" r="E52">
-        <v>31.5237</v>
+        <v>31.5265</v>
       </c>
       <c t="n" r="F52">
-        <v>1.0979</v>
+        <v>1.0989</v>
       </c>
       <c t="n" r="G52">
-        <v>33.0269</v>
+        <v>33.0283</v>
       </c>
       <c t="n" r="H52">
-        <v>316.5859</v>
+        <v>316.3872</v>
       </c>
     </row>
     <row r="53">
@@ -1741,22 +1741,22 @@
         </is>
       </c>
       <c t="n" r="C53">
-        <v>0.1681</v>
+        <v>0.0925</v>
       </c>
       <c t="n" r="D53">
-        <v>0.4848</v>
+        <v>0.0691</v>
       </c>
       <c t="n" r="E53">
-        <v>10.4440</v>
+        <v>10.3601</v>
       </c>
       <c t="n" r="F53">
-        <v>0.1176</v>
+        <v>0.0419</v>
       </c>
       <c t="n" r="G53">
-        <v>32.2875</v>
+        <v>32.1875</v>
       </c>
       <c t="n" r="H53">
-        <v>302.6300</v>
+        <v>302.3311</v>
       </c>
     </row>
     <row r="54">
@@ -1771,25 +1771,25 @@
         </is>
       </c>
       <c t="n" r="C54">
-        <v>-0.0075</v>
+        <v>-0.0086</v>
       </c>
       <c t="n" r="D54">
-        <v>-0.1879</v>
+        <v>-0.1864</v>
       </c>
       <c t="n" r="E54">
-        <v>32.8852</v>
+        <v>32.8872</v>
       </c>
       <c t="n" r="F54">
-        <v>-2.9932</v>
+        <v>-2.9943</v>
       </c>
       <c t="n" r="G54">
-        <v>31.7496</v>
+        <v>31.7481</v>
       </c>
       <c t="n" r="H54">
-        <v>214.9001</v>
+        <v>214.9335</v>
       </c>
       <c t="n" r="I54">
-        <v>684.3911</v>
+        <v>684.3822</v>
       </c>
     </row>
     <row r="55">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c t="n" r="C55">
-        <v>0.2242</v>
+        <v>0.2199</v>
       </c>
       <c t="n" r="D55">
-        <v>-0.5499</v>
+        <v>-0.5501</v>
       </c>
       <c t="n" r="E55">
-        <v>31.3179</v>
+        <v>31.3017</v>
       </c>
       <c t="n" r="F55">
-        <v>0.0885</v>
+        <v>0.0842</v>
       </c>
       <c t="n" r="G55">
-        <v>31.5472</v>
+        <v>31.5415</v>
       </c>
       <c t="n" r="H55">
-        <v>683.3077</v>
+        <v>683.7499</v>
       </c>
       <c t="n" r="I55">
-        <v>1727.7203</v>
+        <v>1727.6559</v>
       </c>
     </row>
     <row r="56">
@@ -1837,19 +1837,19 @@
         </is>
       </c>
       <c t="n" r="C56">
-        <v>-1.3411</v>
+        <v>-1.3414</v>
       </c>
       <c t="n" r="D56">
-        <v>-0.3420</v>
+        <v>-0.3418</v>
       </c>
       <c t="n" r="E56">
-        <v>26.0870</v>
+        <v>26.0699</v>
       </c>
       <c t="n" r="F56">
-        <v>-0.3748</v>
+        <v>-0.3751</v>
       </c>
       <c t="n" r="G56">
-        <v>31.3832</v>
+        <v>31.3828</v>
       </c>
     </row>
     <row r="57">
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c t="n" r="C57">
-        <v>0.0021</v>
+        <v>0.0118</v>
       </c>
       <c t="n" r="D57">
-        <v>0.0366</v>
+        <v>0.0456</v>
       </c>
       <c t="n" r="E57">
-        <v>28.9023</v>
+        <v>28.9094</v>
       </c>
       <c t="n" r="F57">
-        <v>0.2625</v>
+        <v>0.2722</v>
       </c>
       <c t="n" r="G57">
-        <v>31.1962</v>
+        <v>31.2089</v>
       </c>
     </row>
     <row r="58">
@@ -1891,25 +1891,25 @@
         </is>
       </c>
       <c t="n" r="C58">
-        <v>0.2329</v>
+        <v>0.2406</v>
       </c>
       <c t="n" r="D58">
-        <v>1.1051</v>
+        <v>1.1121</v>
       </c>
       <c t="n" r="E58">
-        <v>13.0198</v>
+        <v>13.0213</v>
       </c>
       <c t="n" r="F58">
-        <v>1.3653</v>
+        <v>1.3731</v>
       </c>
       <c t="n" r="G58">
-        <v>30.8794</v>
+        <v>30.8894</v>
       </c>
       <c t="n" r="H58">
-        <v>156.5411</v>
+        <v>156.5747</v>
       </c>
       <c t="n" r="I58">
-        <v>486.5781</v>
+        <v>486.6446</v>
       </c>
     </row>
     <row r="59">
@@ -1924,106 +1924,106 @@
         </is>
       </c>
       <c t="n" r="C59">
-        <v>0.1031</v>
+        <v>0.1218</v>
       </c>
       <c t="n" r="D59">
-        <v>0.1972</v>
+        <v>0.2132</v>
       </c>
       <c t="n" r="E59">
-        <v>5.1096</v>
+        <v>4.7911</v>
       </c>
       <c t="n" r="F59">
-        <v>0.2393</v>
+        <v>0.2580</v>
       </c>
       <c t="n" r="G59">
-        <v>30.2270</v>
+        <v>30.2514</v>
       </c>
     </row>
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">AZ1</t>
+          <t xml:space="preserve">GF2</t>
         </is>
       </c>
       <c t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C60">
-        <v>0.1222</v>
+        <v>0.2692</v>
       </c>
       <c t="n" r="D60">
-        <v>0.8937</v>
+        <v>5.0788</v>
       </c>
       <c t="n" r="E60">
-        <v>27.6723</v>
+        <v>16.6232</v>
       </c>
       <c t="n" r="F60">
-        <v>-5.9603</v>
+        <v>6.8500</v>
       </c>
       <c t="n" r="G60">
-        <v>29.9905</v>
-      </c>
-      <c t="n" r="H60">
-        <v>172.0121</v>
-      </c>
-      <c t="n" r="I60">
-        <v>828.0276</v>
+        <v>30.1777</v>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">GF2</t>
+          <t xml:space="preserve">HRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C61">
-        <v>-0.0224</v>
+        <v>1.4323</v>
       </c>
       <c t="n" r="D61">
-        <v>4.9953</v>
+        <v>3.7587</v>
       </c>
       <c t="n" r="E61">
-        <v>16.5577</v>
+        <v>11.0590</v>
       </c>
       <c t="n" r="F61">
-        <v>6.5392</v>
+        <v>5.7925</v>
       </c>
       <c t="n" r="G61">
-        <v>29.7990</v>
+        <v>30.0758</v>
       </c>
     </row>
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">HRE</t>
+          <t xml:space="preserve">AZ1</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C62">
-        <v>1.2104</v>
+        <v>0.1302</v>
       </c>
       <c t="n" r="D62">
-        <v>3.5959</v>
+        <v>0.8993</v>
       </c>
       <c t="n" r="E62">
-        <v>11.0823</v>
+        <v>27.6029</v>
       </c>
       <c t="n" r="F62">
-        <v>5.5611</v>
+        <v>-5.9528</v>
       </c>
       <c t="n" r="G62">
-        <v>29.7912</v>
+        <v>30.0010</v>
+      </c>
+      <c t="n" r="H62">
+        <v>172.0448</v>
+      </c>
+      <c t="n" r="I62">
+        <v>828.1023</v>
       </c>
     </row>
     <row r="63">
@@ -2038,19 +2038,19 @@
         </is>
       </c>
       <c t="n" r="C63">
-        <v>0.2265</v>
+        <v>0.2359</v>
       </c>
       <c t="n" r="D63">
-        <v>0.7705</v>
+        <v>0.7785</v>
       </c>
       <c t="n" r="E63">
-        <v>-1.0592</v>
+        <v>-1.0546</v>
       </c>
       <c t="n" r="F63">
-        <v>1.0707</v>
+        <v>1.0802</v>
       </c>
       <c t="n" r="G63">
-        <v>29.6661</v>
+        <v>29.6782</v>
       </c>
     </row>
     <row r="64">
@@ -2065,19 +2065,19 @@
         </is>
       </c>
       <c t="n" r="C64">
-        <v>-0.0486</v>
+        <v>-0.0501</v>
       </c>
       <c t="n" r="D64">
-        <v>-0.1423</v>
+        <v>-0.1419</v>
       </c>
       <c t="n" r="E64">
-        <v>30.4725</v>
+        <v>30.4723</v>
       </c>
       <c t="n" r="F64">
-        <v>-0.1764</v>
+        <v>-0.1779</v>
       </c>
       <c t="n" r="G64">
-        <v>29.4751</v>
+        <v>29.4731</v>
       </c>
     </row>
     <row r="65">
@@ -2092,25 +2092,25 @@
         </is>
       </c>
       <c t="n" r="C65">
-        <v>0.1079</v>
+        <v>0.1232</v>
       </c>
       <c t="n" r="D65">
-        <v>0.3519</v>
+        <v>0.2855</v>
       </c>
       <c t="n" r="E65">
-        <v>28.6655</v>
+        <v>28.6633</v>
       </c>
       <c t="n" r="F65">
-        <v>0.3478</v>
+        <v>0.3631</v>
       </c>
       <c t="n" r="G65">
-        <v>29.1250</v>
+        <v>29.1448</v>
       </c>
       <c t="n" r="H65">
-        <v>230.8954</v>
+        <v>230.7145</v>
       </c>
       <c t="n" r="I65">
-        <v>353.7068</v>
+        <v>353.7763</v>
       </c>
     </row>
     <row r="66">
@@ -2125,19 +2125,19 @@
         </is>
       </c>
       <c t="n" r="C66">
-        <v>0.3658</v>
+        <v>0.3592</v>
       </c>
       <c t="n" r="D66">
-        <v>0.6660</v>
+        <v>0.6650</v>
       </c>
       <c t="n" r="E66">
-        <v>26.7967</v>
+        <v>26.8171</v>
       </c>
       <c t="n" r="F66">
-        <v>2.4832</v>
+        <v>2.4765</v>
       </c>
       <c t="n" r="G66">
-        <v>28.7788</v>
+        <v>28.7703</v>
       </c>
     </row>
     <row r="67">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c t="n" r="C67">
-        <v>-0.0180</v>
+        <v>-0.0181</v>
       </c>
       <c t="n" r="D67">
         <v>-0.0587</v>
@@ -2161,10 +2161,10 @@
         <v>28.1661</v>
       </c>
       <c t="n" r="F67">
-        <v>-0.0779</v>
+        <v>-0.0780</v>
       </c>
       <c t="n" r="G67">
-        <v>28.0133</v>
+        <v>28.0132</v>
       </c>
     </row>
     <row r="68">
@@ -2179,25 +2179,25 @@
         </is>
       </c>
       <c t="n" r="C68">
-        <v>1.1809</v>
+        <v>1.2429</v>
       </c>
       <c t="n" r="D68">
-        <v>4.1438</v>
+        <v>4.1851</v>
       </c>
       <c t="n" r="E68">
-        <v>16.2252</v>
+        <v>16.2844</v>
       </c>
       <c t="n" r="F68">
-        <v>4.4070</v>
+        <v>4.4709</v>
       </c>
       <c t="n" r="G68">
-        <v>27.7923</v>
+        <v>27.8706</v>
       </c>
       <c t="n" r="H68">
-        <v>130.7065</v>
+        <v>130.8951</v>
       </c>
       <c t="n" r="I68">
-        <v>635746.3872</v>
+        <v>636135.7774</v>
       </c>
     </row>
     <row r="69">
@@ -2212,25 +2212,25 @@
         </is>
       </c>
       <c t="n" r="C69">
-        <v>0.5594</v>
+        <v>0.5641</v>
       </c>
       <c t="n" r="D69">
-        <v>-1.3612</v>
+        <v>-1.5000</v>
       </c>
       <c t="n" r="E69">
-        <v>25.3436</v>
+        <v>24.6916</v>
       </c>
       <c t="n" r="F69">
-        <v>-20.3950</v>
+        <v>-20.3912</v>
       </c>
       <c t="n" r="G69">
-        <v>27.1675</v>
+        <v>27.1735</v>
       </c>
       <c t="n" r="H69">
-        <v>242.8761</v>
+        <v>242.9238</v>
       </c>
       <c t="n" r="I69">
-        <v>1973.8580</v>
+        <v>1973.9560</v>
       </c>
     </row>
     <row r="70">
@@ -2245,25 +2245,25 @@
         </is>
       </c>
       <c t="n" r="C70">
-        <v>0.7943</v>
+        <v>0.7951</v>
       </c>
       <c t="n" r="D70">
-        <v>-1.1850</v>
+        <v>-1.1822</v>
       </c>
       <c t="n" r="E70">
-        <v>25.5319</v>
+        <v>25.4290</v>
       </c>
       <c t="n" r="F70">
-        <v>-0.3222</v>
+        <v>-0.3214</v>
       </c>
       <c t="n" r="G70">
-        <v>26.1280</v>
+        <v>26.1290</v>
       </c>
       <c t="n" r="H70">
-        <v>49.1217</v>
+        <v>49.1317</v>
       </c>
       <c t="n" r="I70">
-        <v>980.7843</v>
+        <v>980.7928</v>
       </c>
     </row>
     <row r="71">
@@ -2278,175 +2278,175 @@
         </is>
       </c>
       <c t="n" r="C71">
-        <v>1.1791</v>
+        <v>1.2388</v>
       </c>
       <c t="n" r="D71">
-        <v>3.3567</v>
+        <v>3.3966</v>
       </c>
       <c t="n" r="E71">
-        <v>17.4605</v>
+        <v>17.4373</v>
       </c>
       <c t="n" r="F71">
-        <v>4.9159</v>
+        <v>4.9778</v>
       </c>
       <c t="n" r="G71">
-        <v>25.7502</v>
+        <v>25.8244</v>
       </c>
       <c t="n" r="H71">
-        <v>220.4609</v>
+        <v>220.6431</v>
       </c>
       <c t="n" r="I71">
-        <v>501.9490</v>
+        <v>502.3143</v>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">AG7</t>
+          <t xml:space="preserve">NUZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. METROPOL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C72">
-        <v>4.1205</v>
+        <v>1.4476</v>
       </c>
       <c t="n" r="D72">
-        <v>4.9614</v>
+        <v>3.7822</v>
       </c>
       <c t="n" r="E72">
-        <v>14.3083</v>
+        <v>-0.1559</v>
       </c>
       <c t="n" r="F72">
-        <v>1.0219</v>
+        <v>4.3429</v>
       </c>
       <c t="n" r="G72">
-        <v>25.4490</v>
+        <v>25.5703</v>
       </c>
       <c t="n" r="H72">
-        <v>331.4009</v>
-      </c>
-      <c t="n" r="I72">
-        <v>836.7997</v>
+        <v>162.6374</v>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">ZUG</t>
+          <t xml:space="preserve">AG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. METROPOL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C73">
-        <v>-0.0786</v>
+        <v>4.1314</v>
       </c>
       <c t="n" r="D73">
-        <v>-0.2394</v>
+        <v>4.9662</v>
       </c>
       <c t="n" r="E73">
-        <v>25.3553</v>
+        <v>14.3013</v>
       </c>
       <c t="n" r="F73">
-        <v>0.0438</v>
+        <v>1.0325</v>
       </c>
       <c t="n" r="G73">
-        <v>25.3299</v>
+        <v>25.4622</v>
       </c>
       <c t="n" r="H73">
-        <v>200.1532</v>
+        <v>331.4111</v>
       </c>
       <c t="n" r="I73">
-        <v>400.3929</v>
+        <v>836.8979</v>
       </c>
     </row>
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">NUZ</t>
+          <t xml:space="preserve">ZUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C74">
-        <v>1.2158</v>
+        <v>-0.0796</v>
       </c>
       <c t="n" r="D74">
-        <v>3.5773</v>
+        <v>-0.2328</v>
       </c>
       <c t="n" r="E74">
-        <v>-0.3595</v>
+        <v>25.3582</v>
       </c>
       <c t="n" r="F74">
-        <v>4.1045</v>
+        <v>0.0428</v>
       </c>
       <c t="n" r="G74">
-        <v>25.2834</v>
+        <v>25.3286</v>
       </c>
       <c t="n" r="H74">
-        <v>161.9940</v>
+        <v>200.1705</v>
+      </c>
+      <c t="n" r="I74">
+        <v>400.3860</v>
       </c>
     </row>
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">IVB</t>
+          <t xml:space="preserve">NUY</t>
         </is>
       </c>
       <c t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ SANAYİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C75">
-        <v>0.4026</v>
+        <v>-2.2929</v>
       </c>
       <c t="n" r="D75">
-        <v>-0.1037</v>
+        <v>0.0610</v>
       </c>
       <c t="n" r="E75">
-        <v>23.1990</v>
+        <v>17.0655</v>
       </c>
       <c t="n" r="F75">
-        <v>-0.1268</v>
+        <v>1.1042</v>
       </c>
       <c t="n" r="G75">
-        <v>24.9260</v>
+        <v>25.0155</v>
       </c>
     </row>
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">NUY</t>
+          <t xml:space="preserve">IVB</t>
         </is>
       </c>
       <c t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ SANAYİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C76">
-        <v>-2.3642</v>
+        <v>0.4051</v>
       </c>
       <c t="n" r="D76">
-        <v>0.0036</v>
+        <v>-0.1001</v>
       </c>
       <c t="n" r="E76">
-        <v>17.0680</v>
+        <v>23.1988</v>
       </c>
       <c t="n" r="F76">
-        <v>1.0304</v>
+        <v>-0.1244</v>
       </c>
       <c t="n" r="G76">
-        <v>24.9242</v>
+        <v>24.9290</v>
       </c>
     </row>
     <row r="77">
@@ -2461,22 +2461,22 @@
         </is>
       </c>
       <c t="n" r="C77">
-        <v>-2.5794</v>
+        <v>-2.5914</v>
       </c>
       <c t="n" r="D77">
-        <v>-2.3165</v>
+        <v>-2.3141</v>
       </c>
       <c t="n" r="E77">
-        <v>8.0147</v>
+        <v>8.0025</v>
       </c>
       <c t="n" r="F77">
-        <v>-2.7562</v>
+        <v>-2.7682</v>
       </c>
       <c t="n" r="G77">
-        <v>24.6169</v>
+        <v>24.6014</v>
       </c>
       <c t="n" r="H77">
-        <v>148.4729</v>
+        <v>148.1488</v>
       </c>
     </row>
     <row r="78">
@@ -2491,25 +2491,25 @@
         </is>
       </c>
       <c t="n" r="C78">
-        <v>-1.2902</v>
+        <v>-1.2818</v>
       </c>
       <c t="n" r="D78">
-        <v>5.5708</v>
+        <v>5.5867</v>
       </c>
       <c t="n" r="E78">
-        <v>24.7734</v>
+        <v>24.8246</v>
       </c>
       <c t="n" r="F78">
-        <v>-1.6021</v>
+        <v>-1.5937</v>
       </c>
       <c t="n" r="G78">
-        <v>23.7146</v>
+        <v>23.7251</v>
       </c>
       <c t="n" r="H78">
-        <v>253.2568</v>
+        <v>253.3076</v>
       </c>
       <c t="n" r="I78">
-        <v>781.2924</v>
+        <v>783.8526</v>
       </c>
     </row>
     <row r="79">
@@ -2524,25 +2524,25 @@
         </is>
       </c>
       <c t="n" r="C79">
-        <v>6.5250</v>
+        <v>6.5541</v>
       </c>
       <c t="n" r="D79">
-        <v>8.1731</v>
+        <v>8.2535</v>
       </c>
       <c t="n" r="E79">
-        <v>16.2075</v>
+        <v>16.1236</v>
       </c>
       <c t="n" r="F79">
-        <v>6.9081</v>
+        <v>6.9372</v>
       </c>
       <c t="n" r="G79">
-        <v>23.0710</v>
+        <v>23.1046</v>
       </c>
       <c t="n" r="H79">
-        <v>244.1181</v>
+        <v>244.1935</v>
       </c>
       <c t="n" r="I79">
-        <v>780.8448</v>
+        <v>781.0853</v>
       </c>
     </row>
     <row r="80">
@@ -2557,22 +2557,22 @@
         </is>
       </c>
       <c t="n" r="C80">
-        <v>-0.1087</v>
+        <v>-0.2523</v>
       </c>
       <c t="n" r="D80">
-        <v>-0.6151</v>
+        <v>-0.7591</v>
       </c>
       <c t="n" r="E80">
-        <v>23.0854</v>
+        <v>22.9089</v>
       </c>
       <c t="n" r="F80">
-        <v>-0.7318</v>
+        <v>-0.8744</v>
       </c>
       <c t="n" r="G80">
-        <v>21.8603</v>
+        <v>21.6852</v>
       </c>
       <c t="n" r="H80">
-        <v>171.1401</v>
+        <v>170.7615</v>
       </c>
     </row>
     <row r="81">
@@ -2587,25 +2587,25 @@
         </is>
       </c>
       <c t="n" r="C81">
-        <v>0.3796</v>
+        <v>0.4011</v>
       </c>
       <c t="n" r="D81">
-        <v>0.9944</v>
+        <v>1.0169</v>
       </c>
       <c t="n" r="E81">
-        <v>3.8191</v>
+        <v>3.8050</v>
       </c>
       <c t="n" r="F81">
-        <v>1.3835</v>
+        <v>1.4052</v>
       </c>
       <c t="n" r="G81">
-        <v>21.4583</v>
+        <v>21.4842</v>
       </c>
       <c t="n" r="H81">
-        <v>264.4139</v>
+        <v>264.5239</v>
       </c>
       <c t="n" r="I81">
-        <v>794.3956</v>
+        <v>794.5911</v>
       </c>
     </row>
     <row r="82">
@@ -2620,22 +2620,22 @@
         </is>
       </c>
       <c t="n" r="C82">
-        <v>1.0357</v>
+        <v>1.0863</v>
       </c>
       <c t="n" r="D82">
-        <v>2.7901</v>
+        <v>2.8664</v>
       </c>
       <c t="n" r="E82">
-        <v>12.2367</v>
+        <v>12.1106</v>
       </c>
       <c t="n" r="F82">
-        <v>1.9251</v>
+        <v>1.9761</v>
       </c>
       <c t="n" r="G82">
-        <v>21.4084</v>
+        <v>21.4692</v>
       </c>
       <c t="n" r="H82">
-        <v>81.8403</v>
+        <v>81.5246</v>
       </c>
     </row>
     <row r="83">
@@ -2650,22 +2650,22 @@
         </is>
       </c>
       <c t="n" r="C83">
-        <v>-0.0976</v>
+        <v>-0.0999</v>
       </c>
       <c t="n" r="D83">
-        <v>-0.3085</v>
+        <v>-0.3081</v>
       </c>
       <c t="n" r="E83">
-        <v>23.5572</v>
+        <v>23.5577</v>
       </c>
       <c t="n" r="F83">
-        <v>-2.4852</v>
+        <v>-2.4874</v>
       </c>
       <c t="n" r="G83">
-        <v>21.2934</v>
+        <v>21.2906</v>
       </c>
       <c t="n" r="H83">
-        <v>46.5400</v>
+        <v>46.6419</v>
       </c>
     </row>
     <row r="84">
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c t="n" r="C84">
-        <v>0.2720</v>
+        <v>0.2712</v>
       </c>
       <c t="n" r="D84">
-        <v>0.9442</v>
+        <v>0.9434</v>
       </c>
       <c t="n" r="E84">
-        <v>5.6632</v>
+        <v>5.6637</v>
       </c>
       <c t="n" r="F84">
-        <v>1.1273</v>
+        <v>1.1266</v>
       </c>
       <c t="n" r="G84">
-        <v>20.9282</v>
+        <v>20.9274</v>
       </c>
       <c t="n" r="H84">
-        <v>221.0866</v>
+        <v>221.1281</v>
       </c>
       <c t="n" r="I84">
-        <v>989.9694</v>
+        <v>989.9800</v>
       </c>
     </row>
     <row r="85">
@@ -2713,25 +2713,25 @@
         </is>
       </c>
       <c t="n" r="C85">
-        <v>0.4684</v>
+        <v>0.4690</v>
       </c>
       <c t="n" r="D85">
-        <v>0.8041</v>
+        <v>0.8361</v>
       </c>
       <c t="n" r="E85">
-        <v>17.2625</v>
+        <v>17.3040</v>
       </c>
       <c t="n" r="F85">
-        <v>1.0194</v>
+        <v>1.0200</v>
       </c>
       <c t="n" r="G85">
-        <v>20.5690</v>
+        <v>20.5698</v>
       </c>
       <c t="n" r="H85">
-        <v>174.2688</v>
+        <v>174.3996</v>
       </c>
       <c t="n" r="I85">
-        <v>1191.8348</v>
+        <v>1191.8516</v>
       </c>
     </row>
     <row r="86">
@@ -2746,22 +2746,22 @@
         </is>
       </c>
       <c t="n" r="C86">
-        <v>-1.6282</v>
+        <v>-1.6186</v>
       </c>
       <c t="n" r="D86">
-        <v>-0.2085</v>
+        <v>-0.2030</v>
       </c>
       <c t="n" r="E86">
-        <v>16.6110</v>
+        <v>16.6167</v>
       </c>
       <c t="n" r="F86">
-        <v>0.5127</v>
+        <v>0.5224</v>
       </c>
       <c t="n" r="G86">
-        <v>20.2506</v>
+        <v>20.2623</v>
       </c>
       <c t="n" r="H86">
-        <v>368.9459</v>
+        <v>368.8716</v>
       </c>
     </row>
     <row r="87">
@@ -2776,25 +2776,25 @@
         </is>
       </c>
       <c t="n" r="C87">
-        <v>-0.1564</v>
+        <v>-0.1180</v>
       </c>
       <c t="n" r="D87">
-        <v>1.4180</v>
+        <v>1.4374</v>
       </c>
       <c t="n" r="E87">
-        <v>15.1922</v>
+        <v>14.7951</v>
       </c>
       <c t="n" r="F87">
-        <v>-2.7913</v>
+        <v>-2.7540</v>
       </c>
       <c t="n" r="G87">
-        <v>19.5083</v>
+        <v>19.5542</v>
       </c>
       <c t="n" r="H87">
-        <v>150.2471</v>
+        <v>150.4107</v>
       </c>
       <c t="n" r="I87">
-        <v>418.8552</v>
+        <v>419.0545</v>
       </c>
     </row>
     <row r="88">
@@ -2809,25 +2809,25 @@
         </is>
       </c>
       <c t="n" r="C88">
-        <v>0.0920</v>
+        <v>0.0672</v>
       </c>
       <c t="n" r="D88">
-        <v>-0.0863</v>
+        <v>-0.1106</v>
       </c>
       <c t="n" r="E88">
-        <v>15.4324</v>
+        <v>15.2805</v>
       </c>
       <c t="n" r="F88">
-        <v>0.4107</v>
+        <v>0.3858</v>
       </c>
       <c t="n" r="G88">
-        <v>19.4001</v>
+        <v>19.3705</v>
       </c>
       <c t="n" r="H88">
-        <v>116.2931</v>
+        <v>116.2434</v>
       </c>
       <c t="n" r="I88">
-        <v>1159.9466</v>
+        <v>1159.6336</v>
       </c>
     </row>
     <row r="89">
@@ -2842,22 +2842,22 @@
         </is>
       </c>
       <c t="n" r="C89">
-        <v>0.4845</v>
+        <v>0.5089</v>
       </c>
       <c t="n" r="D89">
-        <v>1.1979</v>
+        <v>1.2150</v>
       </c>
       <c t="n" r="E89">
-        <v>11.5565</v>
+        <v>11.5818</v>
       </c>
       <c t="n" r="F89">
-        <v>-0.7777</v>
+        <v>-0.7536</v>
       </c>
       <c t="n" r="G89">
-        <v>19.1109</v>
+        <v>19.1398</v>
       </c>
       <c t="n" r="H89">
-        <v>152.0051</v>
+        <v>152.0693</v>
       </c>
     </row>
     <row r="90">
@@ -2872,22 +2872,22 @@
         </is>
       </c>
       <c t="n" r="C90">
-        <v>-0.2706</v>
+        <v>-0.2681</v>
       </c>
       <c t="n" r="D90">
-        <v>-0.1661</v>
+        <v>-0.1759</v>
       </c>
       <c t="n" r="E90">
-        <v>19.1440</v>
+        <v>19.1436</v>
       </c>
       <c t="n" r="F90">
-        <v>-0.0382</v>
+        <v>-0.0357</v>
       </c>
       <c t="n" r="G90">
-        <v>18.8331</v>
+        <v>18.8361</v>
       </c>
       <c t="n" r="H90">
-        <v>1439.9375</v>
+        <v>1436.5311</v>
       </c>
     </row>
     <row r="91">
@@ -2902,88 +2902,88 @@
         </is>
       </c>
       <c t="n" r="C91">
-        <v>0.4695</v>
+        <v>0.4775</v>
       </c>
       <c t="n" r="D91">
-        <v>1.7898</v>
+        <v>1.8007</v>
       </c>
       <c t="n" r="E91">
-        <v>8.7350</v>
+        <v>8.7288</v>
       </c>
       <c t="n" r="F91">
-        <v>1.7247</v>
+        <v>1.7328</v>
       </c>
       <c t="n" r="G91">
-        <v>18.0508</v>
+        <v>18.0601</v>
       </c>
       <c t="n" r="H91">
-        <v>76.1548</v>
+        <v>75.8050</v>
       </c>
     </row>
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">RP2</t>
+          <t xml:space="preserve">YD4</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C92">
-        <v>0.9059</v>
+        <v>-0.2059</v>
       </c>
       <c t="n" r="D92">
-        <v>2.1848</v>
+        <v>-0.5523</v>
       </c>
       <c t="n" r="E92">
-        <v>16.9188</v>
+        <v>11.1788</v>
       </c>
       <c t="n" r="F92">
-        <v>2.3327</v>
+        <v>-0.6157</v>
       </c>
       <c t="n" r="G92">
-        <v>18.0030</v>
+        <v>17.9938</v>
       </c>
       <c t="n" r="H92">
-        <v>143.7135</v>
+        <v>245.7115</v>
       </c>
       <c t="n" r="I92">
-        <v>448.9044</v>
+        <v>1013.6653</v>
       </c>
     </row>
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">YD4</t>
+          <t xml:space="preserve">RP2</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C93">
-        <v>-0.2006</v>
+        <v>0.8177</v>
       </c>
       <c t="n" r="D93">
-        <v>-0.5496</v>
+        <v>2.1305</v>
       </c>
       <c t="n" r="E93">
-        <v>11.1796</v>
+        <v>16.9972</v>
       </c>
       <c t="n" r="F93">
-        <v>-0.6103</v>
+        <v>2.2432</v>
       </c>
       <c t="n" r="G93">
-        <v>18.0001</v>
+        <v>17.8999</v>
       </c>
       <c t="n" r="H93">
-        <v>245.6155</v>
+        <v>143.5286</v>
       </c>
       <c t="n" r="I93">
-        <v>1013.7248</v>
+        <v>448.4695</v>
       </c>
     </row>
     <row r="94">
@@ -2998,22 +2998,22 @@
         </is>
       </c>
       <c t="n" r="C94">
-        <v>-1.5485</v>
+        <v>-1.5429</v>
       </c>
       <c t="n" r="D94">
-        <v>-1.0683</v>
+        <v>-1.0638</v>
       </c>
       <c t="n" r="E94">
-        <v>25.6645</v>
+        <v>25.6602</v>
       </c>
       <c t="n" r="F94">
-        <v>-0.8582</v>
+        <v>-0.8525</v>
       </c>
       <c t="n" r="G94">
-        <v>17.8276</v>
+        <v>17.8344</v>
       </c>
       <c t="n" r="H94">
-        <v>215.9562</v>
+        <v>215.9994</v>
       </c>
     </row>
     <row r="95">
@@ -3028,22 +3028,22 @@
         </is>
       </c>
       <c t="n" r="C95">
-        <v>-0.1208</v>
+        <v>-0.1248</v>
       </c>
       <c t="n" r="D95">
         <v>-0.3945</v>
       </c>
       <c t="n" r="E95">
-        <v>26.9058</v>
+        <v>26.9062</v>
       </c>
       <c t="n" r="F95">
-        <v>-0.4691</v>
+        <v>-0.4732</v>
       </c>
       <c t="n" r="G95">
-        <v>17.7069</v>
+        <v>17.7021</v>
       </c>
       <c t="n" r="H95">
-        <v>775.4533</v>
+        <v>775.5475</v>
       </c>
     </row>
     <row r="96">
@@ -3058,25 +3058,25 @@
         </is>
       </c>
       <c t="n" r="C96">
-        <v>-0.3048</v>
+        <v>-0.3125</v>
       </c>
       <c t="n" r="D96">
-        <v>-2.1258</v>
+        <v>-2.1292</v>
       </c>
       <c t="n" r="E96">
-        <v>11.7730</v>
+        <v>11.7668</v>
       </c>
       <c t="n" r="F96">
-        <v>-2.3041</v>
+        <v>-2.3117</v>
       </c>
       <c t="n" r="G96">
-        <v>17.1204</v>
+        <v>17.1114</v>
       </c>
       <c t="n" r="H96">
-        <v>148.4721</v>
+        <v>148.5625</v>
       </c>
       <c t="n" r="I96">
-        <v>654.2145</v>
+        <v>654.1563</v>
       </c>
     </row>
     <row r="97">
@@ -3091,25 +3091,25 @@
         </is>
       </c>
       <c t="n" r="C97">
-        <v>-0.2205</v>
+        <v>-0.2068</v>
       </c>
       <c t="n" r="D97">
-        <v>0.5817</v>
+        <v>0.5906</v>
       </c>
       <c t="n" r="E97">
-        <v>6.1951</v>
+        <v>6.2015</v>
       </c>
       <c t="n" r="F97">
-        <v>-0.6746</v>
+        <v>-0.6609</v>
       </c>
       <c t="n" r="G97">
-        <v>16.9350</v>
+        <v>16.9511</v>
       </c>
       <c t="n" r="H97">
-        <v>320.7155</v>
+        <v>320.7572</v>
       </c>
       <c t="n" r="I97">
-        <v>1601.2809</v>
+        <v>1601.5154</v>
       </c>
     </row>
     <row r="98">
@@ -3127,10 +3127,10 @@
         <v>-0.2509</v>
       </c>
       <c t="n" r="D98">
-        <v>-0.2509</v>
+        <v>-0.2529</v>
       </c>
       <c t="n" r="E98">
-        <v>5.3809</v>
+        <v>5.3807</v>
       </c>
       <c t="n" r="F98">
         <v>-0.5035</v>
@@ -3151,22 +3151,22 @@
         </is>
       </c>
       <c t="n" r="C99">
-        <v>-0.0007</v>
+        <v>-0.0008</v>
       </c>
       <c t="n" r="D99">
         <v>-0.0402</v>
       </c>
       <c t="n" r="E99">
-        <v>16.1308</v>
+        <v>16.1307</v>
       </c>
       <c t="n" r="F99">
-        <v>-0.0460</v>
+        <v>-0.0461</v>
       </c>
       <c t="n" r="G99">
-        <v>16.0176</v>
+        <v>16.0175</v>
       </c>
       <c t="n" r="H99">
-        <v>580.1220</v>
+        <v>580.0913</v>
       </c>
     </row>
     <row r="100">
@@ -3181,25 +3181,25 @@
         </is>
       </c>
       <c t="n" r="C100">
-        <v>0.9070</v>
+        <v>1.0002</v>
       </c>
       <c t="n" r="D100">
-        <v>-0.7659</v>
+        <v>-0.7210</v>
       </c>
       <c t="n" r="E100">
-        <v>2.3364</v>
+        <v>2.3756</v>
       </c>
       <c t="n" r="F100">
-        <v>0.2291</v>
+        <v>0.3217</v>
       </c>
       <c t="n" r="G100">
-        <v>15.6113</v>
+        <v>15.7181</v>
       </c>
       <c t="n" r="H100">
-        <v>0.7238</v>
+        <v>0.8698</v>
       </c>
       <c t="n" r="I100">
-        <v>58.8643</v>
+        <v>59.0111</v>
       </c>
     </row>
     <row r="101">
@@ -3214,22 +3214,22 @@
         </is>
       </c>
       <c t="n" r="C101">
-        <v>0.3030</v>
+        <v>0.3188</v>
       </c>
       <c t="n" r="D101">
-        <v>2.6184</v>
+        <v>2.5978</v>
       </c>
       <c t="n" r="E101">
-        <v>15.3095</v>
+        <v>14.5672</v>
       </c>
       <c t="n" r="F101">
-        <v>3.6281</v>
+        <v>3.6443</v>
       </c>
       <c t="n" r="G101">
-        <v>15.0489</v>
+        <v>15.0670</v>
       </c>
       <c t="n" r="H101">
-        <v>188.0601</v>
+        <v>188.0673</v>
       </c>
     </row>
     <row r="102">
@@ -3244,19 +3244,19 @@
         </is>
       </c>
       <c t="n" r="C102">
-        <v>-0.2107</v>
+        <v>-0.4049</v>
       </c>
       <c t="n" r="D102">
-        <v>-0.6080</v>
+        <v>-0.7951</v>
       </c>
       <c t="n" r="E102">
-        <v>16.6344</v>
+        <v>16.4151</v>
       </c>
       <c t="n" r="F102">
-        <v>-0.7263</v>
+        <v>-0.9194</v>
       </c>
       <c t="n" r="G102">
-        <v>14.9711</v>
+        <v>14.7474</v>
       </c>
     </row>
     <row r="103">
@@ -3271,181 +3271,181 @@
         </is>
       </c>
       <c t="n" r="C103">
-        <v>0.0209</v>
+        <v>0.0323</v>
       </c>
       <c t="n" r="D103">
-        <v>1.6329</v>
+        <v>1.6391</v>
       </c>
       <c t="n" r="E103">
-        <v>4.7669</v>
+        <v>4.6038</v>
       </c>
       <c t="n" r="F103">
-        <v>1.1882</v>
+        <v>1.1998</v>
       </c>
       <c t="n" r="G103">
-        <v>14.2502</v>
+        <v>14.2632</v>
       </c>
       <c t="n" r="H103">
-        <v>265.9118</v>
+        <v>266.1400</v>
       </c>
       <c t="n" r="I103">
-        <v>1193.3583</v>
+        <v>1193.5055</v>
       </c>
     </row>
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">FRG</t>
+          <t xml:space="preserve">RAS</t>
         </is>
       </c>
       <c t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C104">
-        <v>2.1225</v>
+        <v>-0.1325</v>
       </c>
       <c t="n" r="D104">
-        <v>3.1821</v>
+        <v>0.5000</v>
       </c>
       <c t="n" r="E104">
-        <v>15.3658</v>
+        <v>12.7220</v>
       </c>
       <c t="n" r="F104">
-        <v>5.0493</v>
+        <v>1.2232</v>
       </c>
       <c t="n" r="G104">
-        <v>13.8697</v>
+        <v>13.8569</v>
       </c>
       <c t="n" r="H104">
-        <v>93.9807</v>
+        <v>262.6318</v>
       </c>
       <c t="n" r="I104">
-        <v>443.4196</v>
+        <v>474.6542</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">RAS</t>
+          <t xml:space="preserve">NG4</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C105">
-        <v>-0.1336</v>
+        <v>0.0131</v>
       </c>
       <c t="n" r="D105">
-        <v>0.3678</v>
+        <v>-0.0239</v>
       </c>
       <c t="n" r="E105">
-        <v>12.5817</v>
+        <v>13.7695</v>
       </c>
       <c t="n" r="F105">
-        <v>1.2221</v>
+        <v>-0.9435</v>
       </c>
       <c t="n" r="G105">
-        <v>13.8557</v>
+        <v>13.7175</v>
       </c>
       <c t="n" r="H105">
-        <v>262.8896</v>
-      </c>
-      <c t="n" r="I105">
-        <v>474.6495</v>
+        <v>226.6165</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">NG4</t>
+          <t xml:space="preserve">FRG</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C106">
-        <v>0.0142</v>
+        <v>1.9180</v>
       </c>
       <c t="n" r="D106">
-        <v>-0.0237</v>
+        <v>3.0421</v>
       </c>
       <c t="n" r="E106">
-        <v>13.7728</v>
+        <v>15.5002</v>
       </c>
       <c t="n" r="F106">
-        <v>-0.9424</v>
+        <v>4.8389</v>
       </c>
       <c t="n" r="G106">
-        <v>13.7187</v>
+        <v>13.6416</v>
       </c>
       <c t="n" r="H106">
-        <v>226.6298</v>
+        <v>93.6226</v>
+      </c>
+      <c t="n" r="I106">
+        <v>442.2233</v>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">RP4</t>
+          <t xml:space="preserve">ILN</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. FOLKART BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C107">
-        <v>1.7806</v>
+        <v>0.0287</v>
       </c>
       <c t="n" r="D107">
-        <v>-5.0798</v>
+        <v>2.2688</v>
       </c>
       <c t="n" r="E107">
-        <v>10.6882</v>
+        <v>3.6058</v>
       </c>
       <c t="n" r="F107">
-        <v>-4.2651</v>
+        <v>2.4598</v>
       </c>
       <c t="n" r="G107">
-        <v>13.5102</v>
-      </c>
-      <c t="n" r="H107">
-        <v>110.2052</v>
-      </c>
-      <c t="n" r="I107">
-        <v>362.1929</v>
+        <v>13.3918</v>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">ILN</t>
+          <t xml:space="preserve">RP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. FOLKART BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C108">
-        <v>0.0282</v>
+        <v>1.5994</v>
       </c>
       <c t="n" r="D108">
-        <v>2.2792</v>
+        <v>-5.1784</v>
       </c>
       <c t="n" r="E108">
-        <v>3.6237</v>
+        <v>10.7665</v>
       </c>
       <c t="n" r="F108">
-        <v>2.4593</v>
+        <v>-4.4356</v>
       </c>
       <c t="n" r="G108">
-        <v>13.3912</v>
+        <v>13.3081</v>
+      </c>
+      <c t="n" r="H108">
+        <v>109.8841</v>
+      </c>
+      <c t="n" r="I108">
+        <v>361.0544</v>
       </c>
     </row>
     <row r="109">
@@ -3460,22 +3460,22 @@
         </is>
       </c>
       <c t="n" r="C109">
-        <v>-0.0521</v>
+        <v>-0.0530</v>
       </c>
       <c t="n" r="D109">
-        <v>-0.3441</v>
+        <v>-0.3442</v>
       </c>
       <c t="n" r="E109">
         <v>13.7144</v>
       </c>
       <c t="n" r="F109">
-        <v>-0.5469</v>
+        <v>-0.5479</v>
       </c>
       <c t="n" r="G109">
-        <v>13.0506</v>
+        <v>13.0495</v>
       </c>
       <c t="n" r="H109">
-        <v>493.6903</v>
+        <v>493.7480</v>
       </c>
     </row>
     <row r="110">
@@ -3490,22 +3490,22 @@
         </is>
       </c>
       <c t="n" r="C110">
-        <v>-0.0463</v>
+        <v>-0.0272</v>
       </c>
       <c t="n" r="D110">
-        <v>0.0616</v>
+        <v>0.1379</v>
       </c>
       <c t="n" r="E110">
-        <v>-1.0756</v>
+        <v>-1.0597</v>
       </c>
       <c t="n" r="F110">
-        <v>0.0508</v>
+        <v>0.0699</v>
       </c>
       <c t="n" r="G110">
-        <v>12.8910</v>
+        <v>12.9126</v>
       </c>
       <c t="n" r="H110">
-        <v>124.3664</v>
+        <v>124.4176</v>
       </c>
     </row>
     <row r="111">
@@ -3520,19 +3520,19 @@
         </is>
       </c>
       <c t="n" r="C111">
-        <v>-29.5729</v>
+        <v>-29.5788</v>
       </c>
       <c t="n" r="D111">
-        <v>-33.0174</v>
+        <v>-33.0137</v>
       </c>
       <c t="n" r="E111">
-        <v>1768.1377</v>
+        <v>1789.9965</v>
       </c>
       <c t="n" r="F111">
-        <v>-33.1855</v>
+        <v>-33.1912</v>
       </c>
       <c t="n" r="G111">
-        <v>12.6854</v>
+        <v>12.6759</v>
       </c>
     </row>
     <row r="112">
@@ -3547,25 +3547,25 @@
         </is>
       </c>
       <c t="n" r="C112">
-        <v>-0.3316</v>
+        <v>-0.3194</v>
       </c>
       <c t="n" r="D112">
-        <v>0.6162</v>
+        <v>0.6234</v>
       </c>
       <c t="n" r="E112">
-        <v>8.8858</v>
+        <v>8.8651</v>
       </c>
       <c t="n" r="F112">
-        <v>-1.1168</v>
+        <v>-1.1046</v>
       </c>
       <c t="n" r="G112">
-        <v>12.6077</v>
+        <v>12.6215</v>
       </c>
       <c t="n" r="H112">
-        <v>201.5328</v>
+        <v>201.5686</v>
       </c>
       <c t="n" r="I112">
-        <v>576.4525</v>
+        <v>576.5357</v>
       </c>
     </row>
     <row r="113">
@@ -3580,22 +3580,22 @@
         </is>
       </c>
       <c t="n" r="C113">
-        <v>0.1300</v>
+        <v>0.1377</v>
       </c>
       <c t="n" r="D113">
-        <v>0.7819</v>
+        <v>0.7964</v>
       </c>
       <c t="n" r="E113">
-        <v>9.8665</v>
+        <v>9.5916</v>
       </c>
       <c t="n" r="F113">
-        <v>0.7678</v>
+        <v>0.7755</v>
       </c>
       <c t="n" r="G113">
-        <v>12.2003</v>
+        <v>12.2090</v>
       </c>
       <c t="n" r="H113">
-        <v>-18.5257</v>
+        <v>-18.4589</v>
       </c>
     </row>
     <row r="114">
@@ -3610,19 +3610,19 @@
         </is>
       </c>
       <c t="n" r="C114">
-        <v>2.8119</v>
+        <v>3.1135</v>
       </c>
       <c t="n" r="D114">
-        <v>8.6929</v>
+        <v>9.0439</v>
       </c>
       <c t="n" r="E114">
-        <v>15.8199</v>
+        <v>15.8747</v>
       </c>
       <c t="n" r="F114">
-        <v>12.1318</v>
+        <v>12.4608</v>
       </c>
       <c t="n" r="G114">
-        <v>11.6066</v>
+        <v>11.9341</v>
       </c>
     </row>
     <row r="115">
@@ -3637,19 +3637,19 @@
         </is>
       </c>
       <c t="n" r="C115">
-        <v>0.7223</v>
+        <v>0.8140</v>
       </c>
       <c t="n" r="D115">
-        <v>1.3929</v>
+        <v>1.6692</v>
       </c>
       <c t="n" r="E115">
-        <v>4.2582</v>
+        <v>4.2883</v>
       </c>
       <c t="n" r="F115">
-        <v>3.3421</v>
+        <v>3.4361</v>
       </c>
       <c t="n" r="G115">
-        <v>11.0205</v>
+        <v>11.1215</v>
       </c>
     </row>
     <row r="116">
@@ -3664,22 +3664,22 @@
         </is>
       </c>
       <c t="n" r="C116">
-        <v>-1.6623</v>
+        <v>-1.6469</v>
       </c>
       <c t="n" r="D116">
-        <v>-5.1788</v>
+        <v>-5.1617</v>
       </c>
       <c t="n" r="E116">
-        <v>33.2551</v>
+        <v>33.2450</v>
       </c>
       <c t="n" r="F116">
-        <v>-5.2449</v>
+        <v>-5.2300</v>
       </c>
       <c t="n" r="G116">
-        <v>10.4975</v>
+        <v>10.5148</v>
       </c>
       <c t="n" r="H116">
-        <v>399.2742</v>
+        <v>399.3584</v>
       </c>
     </row>
     <row r="117">
@@ -3694,22 +3694,22 @@
         </is>
       </c>
       <c t="n" r="C117">
-        <v>0.0215</v>
+        <v>-0.0255</v>
       </c>
       <c t="n" r="D117">
-        <v>0.3915</v>
+        <v>0.3443</v>
       </c>
       <c t="n" r="E117">
-        <v>27.6721</v>
+        <v>27.6139</v>
       </c>
       <c t="n" r="F117">
-        <v>0.3088</v>
+        <v>0.2616</v>
       </c>
       <c t="n" r="G117">
-        <v>10.4898</v>
+        <v>10.4378</v>
       </c>
       <c t="n" r="H117">
-        <v>134.4973</v>
+        <v>134.4121</v>
       </c>
     </row>
     <row r="118">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c t="n" r="C118">
-        <v>-0.0697</v>
+        <v>-0.0714</v>
       </c>
       <c t="n" r="D118">
         <v>-0.1848</v>
       </c>
       <c t="n" r="E118">
-        <v>10.8894</v>
+        <v>10.8872</v>
       </c>
       <c t="n" r="F118">
-        <v>-0.2348</v>
+        <v>-0.2365</v>
       </c>
       <c t="n" r="G118">
-        <v>10.3940</v>
+        <v>10.3921</v>
       </c>
     </row>
     <row r="119">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c t="n" r="C119">
-        <v>-0.3069</v>
+        <v>-0.3169</v>
       </c>
       <c t="n" r="D119">
-        <v>-1.0789</v>
+        <v>-1.0713</v>
       </c>
       <c t="n" r="E119">
-        <v>12.4000</v>
+        <v>12.4010</v>
       </c>
       <c t="n" r="F119">
-        <v>-1.3873</v>
+        <v>-1.3972</v>
       </c>
       <c t="n" r="G119">
-        <v>10.3102</v>
+        <v>10.2991</v>
       </c>
     </row>
     <row r="120">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c t="n" r="C120">
-        <v>0.4401</v>
+        <v>0.4397</v>
       </c>
       <c t="n" r="D120">
         <v>0.3737</v>
@@ -3787,10 +3787,10 @@
         <v>9.8238</v>
       </c>
       <c t="n" r="F120">
-        <v>0.3987</v>
+        <v>0.3983</v>
       </c>
       <c t="n" r="G120">
-        <v>9.6496</v>
+        <v>9.6491</v>
       </c>
     </row>
     <row r="121">
@@ -3805,25 +3805,25 @@
         </is>
       </c>
       <c t="n" r="C121">
-        <v>0.1571</v>
+        <v>0.1605</v>
       </c>
       <c t="n" r="D121">
         <v>0.4062</v>
       </c>
       <c t="n" r="E121">
-        <v>2.1667</v>
+        <v>2.1481</v>
       </c>
       <c t="n" r="F121">
-        <v>1.1112</v>
+        <v>1.1147</v>
       </c>
       <c t="n" r="G121">
-        <v>9.5751</v>
+        <v>9.5789</v>
       </c>
       <c t="n" r="H121">
-        <v>129.3061</v>
+        <v>129.3094</v>
       </c>
       <c t="n" r="I121">
-        <v>423.2320</v>
+        <v>423.2328</v>
       </c>
     </row>
     <row r="122">
@@ -3838,79 +3838,79 @@
         </is>
       </c>
       <c t="n" r="C122">
-        <v>0.6829</v>
+        <v>0.6818</v>
       </c>
       <c t="n" r="D122">
-        <v>2.0047</v>
+        <v>2.0049</v>
       </c>
       <c t="n" r="E122">
-        <v>8.6613</v>
+        <v>8.6601</v>
       </c>
       <c t="n" r="F122">
-        <v>1.9484</v>
+        <v>1.9473</v>
       </c>
       <c t="n" r="G122">
-        <v>9.2516</v>
+        <v>9.2504</v>
       </c>
       <c t="n" r="H122">
-        <v>127.7635</v>
+        <v>127.7413</v>
       </c>
     </row>
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">NAG</t>
+          <t xml:space="preserve">RBG</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AKS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C123">
-        <v>0.0403</v>
+        <v>0.4543</v>
       </c>
       <c t="n" r="D123">
-        <v>-0.1158</v>
+        <v>1.6846</v>
       </c>
       <c t="n" r="E123">
-        <v>9.1729</v>
+        <v>6.5989</v>
       </c>
       <c t="n" r="F123">
-        <v>-0.0534</v>
+        <v>1.2592</v>
       </c>
       <c t="n" r="G123">
-        <v>9.0111</v>
-      </c>
-      <c t="n" r="H123">
-        <v>253.8059</v>
+        <v>9.0238</v>
       </c>
     </row>
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">RBG</t>
+          <t xml:space="preserve">NAG</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AKS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C124">
-        <v>0.4402</v>
+        <v>0.0390</v>
       </c>
       <c t="n" r="D124">
-        <v>1.6735</v>
+        <v>-0.1154</v>
       </c>
       <c t="n" r="E124">
-        <v>6.5909</v>
+        <v>9.1730</v>
       </c>
       <c t="n" r="F124">
-        <v>1.2450</v>
+        <v>-0.0547</v>
       </c>
       <c t="n" r="G124">
-        <v>9.0084</v>
+        <v>9.0097</v>
+      </c>
+      <c t="n" r="H124">
+        <v>253.8437</v>
       </c>
     </row>
     <row r="125">
@@ -3925,22 +3925,22 @@
         </is>
       </c>
       <c t="n" r="C125">
-        <v>0.1919</v>
+        <v>0.1892</v>
       </c>
       <c t="n" r="D125">
-        <v>0.4719</v>
+        <v>0.4678</v>
       </c>
       <c t="n" r="E125">
-        <v>3.9958</v>
+        <v>3.9939</v>
       </c>
       <c t="n" r="F125">
-        <v>0.5457</v>
+        <v>0.5430</v>
       </c>
       <c t="n" r="G125">
-        <v>8.6310</v>
+        <v>8.6281</v>
       </c>
       <c t="n" r="H125">
-        <v>244.3893</v>
+        <v>244.3516</v>
       </c>
     </row>
     <row r="126">
@@ -3955,19 +3955,19 @@
         </is>
       </c>
       <c t="n" r="C126">
-        <v>0.3909</v>
+        <v>0.3942</v>
       </c>
       <c t="n" r="D126">
-        <v>-1.9219</v>
+        <v>-1.9178</v>
       </c>
       <c t="n" r="E126">
-        <v>7.5288</v>
+        <v>7.5289</v>
       </c>
       <c t="n" r="F126">
-        <v>-1.4484</v>
+        <v>-1.4451</v>
       </c>
       <c t="n" r="G126">
-        <v>8.4431</v>
+        <v>8.4467</v>
       </c>
     </row>
     <row r="127">
@@ -3982,19 +3982,19 @@
         </is>
       </c>
       <c t="n" r="C127">
-        <v>-0.4976</v>
+        <v>-0.5002</v>
       </c>
       <c t="n" r="D127">
-        <v>-0.6582</v>
+        <v>-0.6566</v>
       </c>
       <c t="n" r="E127">
-        <v>8.8891</v>
+        <v>8.8845</v>
       </c>
       <c t="n" r="F127">
-        <v>-0.4888</v>
+        <v>-0.4915</v>
       </c>
       <c t="n" r="G127">
-        <v>8.3743</v>
+        <v>8.3714</v>
       </c>
     </row>
     <row r="128">
@@ -4009,22 +4009,22 @@
         </is>
       </c>
       <c t="n" r="C128">
-        <v>-0.3494</v>
+        <v>-0.3462</v>
       </c>
       <c t="n" r="D128">
-        <v>-0.2307</v>
+        <v>-0.2259</v>
       </c>
       <c t="n" r="E128">
-        <v>12.1060</v>
+        <v>12.1007</v>
       </c>
       <c t="n" r="F128">
-        <v>-0.9808</v>
+        <v>-0.9776</v>
       </c>
       <c t="n" r="G128">
-        <v>7.6172</v>
+        <v>7.6206</v>
       </c>
       <c t="n" r="H128">
-        <v>209.8109</v>
+        <v>209.1013</v>
       </c>
     </row>
     <row r="129">
@@ -4039,22 +4039,22 @@
         </is>
       </c>
       <c t="n" r="C129">
-        <v>1.2459</v>
+        <v>1.2815</v>
       </c>
       <c t="n" r="D129">
-        <v>0.8321</v>
+        <v>0.8690</v>
       </c>
       <c t="n" r="E129">
-        <v>6.5712</v>
+        <v>6.6102</v>
       </c>
       <c t="n" r="F129">
-        <v>0.7455</v>
+        <v>0.7809</v>
       </c>
       <c t="n" r="G129">
-        <v>6.6265</v>
+        <v>6.6640</v>
       </c>
       <c t="n" r="H129">
-        <v>160.6960</v>
+        <v>160.8044</v>
       </c>
     </row>
     <row r="130">
@@ -4069,22 +4069,22 @@
         </is>
       </c>
       <c t="n" r="C130">
-        <v>-0.7034</v>
+        <v>-0.6800</v>
       </c>
       <c t="n" r="D130">
-        <v>-0.5408</v>
+        <v>-0.5165</v>
       </c>
       <c t="n" r="E130">
-        <v>5.9123</v>
+        <v>5.9374</v>
       </c>
       <c t="n" r="F130">
-        <v>-0.4647</v>
+        <v>-0.4413</v>
       </c>
       <c t="n" r="G130">
-        <v>6.5804</v>
+        <v>6.6055</v>
       </c>
       <c t="n" r="H130">
-        <v>110.5810</v>
+        <v>110.6364</v>
       </c>
     </row>
     <row r="131">
@@ -4102,10 +4102,10 @@
         <v>-0.3744</v>
       </c>
       <c t="n" r="D131">
-        <v>-0.3841</v>
+        <v>-0.4051</v>
       </c>
       <c t="n" r="E131">
-        <v>7.2274</v>
+        <v>7.2278</v>
       </c>
       <c t="n" r="F131">
         <v>-0.3807</v>
@@ -4114,7 +4114,7 @@
         <v>6.5278</v>
       </c>
       <c t="n" r="H131">
-        <v>233.3712</v>
+        <v>233.3698</v>
       </c>
     </row>
     <row r="132">
@@ -4129,22 +4129,22 @@
         </is>
       </c>
       <c t="n" r="C132">
-        <v>-0.0474</v>
+        <v>-0.0486</v>
       </c>
       <c t="n" r="D132">
         <v>-0.1440</v>
       </c>
       <c t="n" r="E132">
-        <v>6.6175</v>
+        <v>6.6173</v>
       </c>
       <c t="n" r="F132">
-        <v>-0.1777</v>
+        <v>-0.1789</v>
       </c>
       <c t="n" r="G132">
-        <v>6.3487</v>
+        <v>6.3474</v>
       </c>
       <c t="n" r="H132">
-        <v>305.8260</v>
+        <v>305.8538</v>
       </c>
     </row>
     <row r="133">
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c t="n" r="C133">
-        <v>0.2869</v>
+        <v>0.2977</v>
       </c>
       <c t="n" r="D133">
-        <v>1.0154</v>
+        <v>1.0192</v>
       </c>
       <c t="n" r="E133">
-        <v>13.5368</v>
+        <v>13.4278</v>
       </c>
       <c t="n" r="F133">
-        <v>1.3195</v>
+        <v>1.3304</v>
       </c>
       <c t="n" r="G133">
-        <v>5.8074</v>
+        <v>5.8187</v>
       </c>
       <c t="n" r="H133">
-        <v>195.5274</v>
+        <v>195.5744</v>
       </c>
     </row>
     <row r="134">
@@ -4189,79 +4189,79 @@
         </is>
       </c>
       <c t="n" r="C134">
-        <v>0.3271</v>
+        <v>0.3320</v>
       </c>
       <c t="n" r="D134">
-        <v>1.2897</v>
+        <v>1.2953</v>
       </c>
       <c t="n" r="E134">
-        <v>11.4667</v>
+        <v>11.4735</v>
       </c>
       <c t="n" r="F134">
-        <v>1.4978</v>
+        <v>1.5028</v>
       </c>
       <c t="n" r="G134">
-        <v>5.6191</v>
+        <v>5.6243</v>
       </c>
       <c t="n" r="H134">
-        <v>154.3959</v>
+        <v>154.3323</v>
       </c>
     </row>
     <row r="135">
       <c t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">NUP</t>
+          <t xml:space="preserve">NH5</t>
         </is>
       </c>
       <c t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C135">
-        <v>-0.0452</v>
+        <v>1.2275</v>
       </c>
       <c t="n" r="D135">
-        <v>-0.1771</v>
+        <v>3.7551</v>
       </c>
       <c t="n" r="E135">
-        <v>8.3571</v>
+        <v>9.9631</v>
       </c>
       <c t="n" r="F135">
-        <v>2.1375</v>
+        <v>4.7050</v>
       </c>
       <c t="n" r="G135">
-        <v>5.3162</v>
+        <v>5.3550</v>
+      </c>
+      <c t="n" r="H135">
+        <v>90.4208</v>
       </c>
     </row>
     <row r="136">
       <c t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">NH5</t>
+          <t xml:space="preserve">NUP</t>
         </is>
       </c>
       <c t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C136">
-        <v>1.0712</v>
+        <v>-0.0420</v>
       </c>
       <c t="n" r="D136">
-        <v>3.6420</v>
+        <v>-0.1735</v>
       </c>
       <c t="n" r="E136">
-        <v>9.7821</v>
+        <v>8.3674</v>
       </c>
       <c t="n" r="F136">
-        <v>4.5434</v>
+        <v>2.1408</v>
       </c>
       <c t="n" r="G136">
-        <v>5.1923</v>
-      </c>
-      <c t="n" r="H136">
-        <v>90.1210</v>
+        <v>5.3196</v>
       </c>
     </row>
     <row r="137">
@@ -4276,19 +4276,19 @@
         </is>
       </c>
       <c t="n" r="C137">
-        <v>0.1599</v>
+        <v>0.1688</v>
       </c>
       <c t="n" r="D137">
-        <v>-10.5401</v>
+        <v>-10.5440</v>
       </c>
       <c t="n" r="E137">
-        <v>0.3031</v>
+        <v>0.2679</v>
       </c>
       <c t="n" r="F137">
-        <v>-10.4742</v>
+        <v>-10.4662</v>
       </c>
       <c t="n" r="G137">
-        <v>4.7664</v>
+        <v>4.7757</v>
       </c>
     </row>
     <row r="138">
@@ -4303,22 +4303,22 @@
         </is>
       </c>
       <c t="n" r="C138">
-        <v>-0.2093</v>
+        <v>-0.2161</v>
       </c>
       <c t="n" r="D138">
-        <v>-0.6595</v>
+        <v>-0.6592</v>
       </c>
       <c t="n" r="E138">
-        <v>5.9037</v>
+        <v>5.9040</v>
       </c>
       <c t="n" r="F138">
-        <v>-0.8058</v>
+        <v>-0.8125</v>
       </c>
       <c t="n" r="G138">
-        <v>4.4839</v>
+        <v>4.4768</v>
       </c>
       <c t="n" r="H138">
-        <v>113.3187</v>
+        <v>113.2899</v>
       </c>
     </row>
     <row r="139">
@@ -4333,25 +4333,25 @@
         </is>
       </c>
       <c t="n" r="C139">
-        <v>-0.1605</v>
+        <v>-0.0283</v>
       </c>
       <c t="n" r="D139">
-        <v>-0.9442</v>
+        <v>-0.7748</v>
       </c>
       <c t="n" r="E139">
-        <v>0.8434</v>
+        <v>0.9174</v>
       </c>
       <c t="n" r="F139">
-        <v>-0.7542</v>
+        <v>-0.6228</v>
       </c>
       <c t="n" r="G139">
-        <v>4.1920</v>
+        <v>4.3299</v>
       </c>
       <c t="n" r="H139">
-        <v>89.0709</v>
+        <v>89.3212</v>
       </c>
       <c t="n" r="I139">
-        <v>58.2002</v>
+        <v>58.4096</v>
       </c>
     </row>
     <row r="140">
@@ -4366,19 +4366,19 @@
         </is>
       </c>
       <c t="n" r="C140">
-        <v>-0.5574</v>
+        <v>-0.5782</v>
       </c>
       <c t="n" r="D140">
-        <v>-1.6663</v>
+        <v>-1.6683</v>
       </c>
       <c t="n" r="E140">
-        <v>-14.9489</v>
+        <v>-14.9608</v>
       </c>
       <c t="n" r="F140">
-        <v>-2.6370</v>
+        <v>-2.6574</v>
       </c>
       <c t="n" r="G140">
-        <v>3.9291</v>
+        <v>3.9073</v>
       </c>
     </row>
     <row r="141">
@@ -4393,22 +4393,22 @@
         </is>
       </c>
       <c t="n" r="C141">
-        <v>-0.2141</v>
+        <v>-0.2144</v>
       </c>
       <c t="n" r="D141">
-        <v>-0.7772</v>
+        <v>-0.7719</v>
       </c>
       <c t="n" r="E141">
-        <v>0.7069</v>
+        <v>0.7126</v>
       </c>
       <c t="n" r="F141">
-        <v>-0.9703</v>
+        <v>-0.9706</v>
       </c>
       <c t="n" r="G141">
-        <v>3.5230</v>
+        <v>3.5227</v>
       </c>
       <c t="n" r="H141">
-        <v>171.0405</v>
+        <v>171.0545</v>
       </c>
     </row>
     <row r="142">
@@ -4423,22 +4423,22 @@
         </is>
       </c>
       <c t="n" r="C142">
-        <v>-0.0915</v>
+        <v>-0.0929</v>
       </c>
       <c t="n" r="D142">
-        <v>-0.2693</v>
+        <v>-0.2677</v>
       </c>
       <c t="n" r="E142">
-        <v>9.4856</v>
+        <v>9.4824</v>
       </c>
       <c t="n" r="F142">
-        <v>-0.3531</v>
+        <v>-0.3545</v>
       </c>
       <c t="n" r="G142">
-        <v>3.1568</v>
+        <v>3.1554</v>
       </c>
       <c t="n" r="H142">
-        <v>132.8767</v>
+        <v>132.9031</v>
       </c>
     </row>
     <row r="143">
@@ -4453,22 +4453,22 @@
         </is>
       </c>
       <c t="n" r="C143">
-        <v>-0.1949</v>
+        <v>-0.1885</v>
       </c>
       <c t="n" r="D143">
-        <v>-0.4130</v>
+        <v>-0.4126</v>
       </c>
       <c t="n" r="E143">
-        <v>16.4512</v>
+        <v>16.4575</v>
       </c>
       <c t="n" r="F143">
-        <v>-0.5801</v>
+        <v>-0.5738</v>
       </c>
       <c t="n" r="G143">
-        <v>2.9995</v>
+        <v>3.0060</v>
       </c>
       <c t="n" r="H143">
-        <v>269.3076</v>
+        <v>268.5039</v>
       </c>
     </row>
     <row r="144">
@@ -4483,22 +4483,22 @@
         </is>
       </c>
       <c t="n" r="C144">
-        <v>1.2694</v>
+        <v>1.2554</v>
       </c>
       <c t="n" r="D144">
-        <v>1.4287</v>
+        <v>1.3917</v>
       </c>
       <c t="n" r="E144">
-        <v>5.0718</v>
+        <v>5.0289</v>
       </c>
       <c t="n" r="F144">
-        <v>-0.6486</v>
+        <v>-0.6623</v>
       </c>
       <c t="n" r="G144">
-        <v>2.9258</v>
+        <v>2.9116</v>
       </c>
       <c t="n" r="H144">
-        <v>266.3492</v>
+        <v>266.2984</v>
       </c>
     </row>
     <row r="145">
@@ -4513,19 +4513,19 @@
         </is>
       </c>
       <c t="n" r="C145">
-        <v>-0.6769</v>
+        <v>-0.6819</v>
       </c>
       <c t="n" r="D145">
-        <v>-1.5461</v>
+        <v>-1.5502</v>
       </c>
       <c t="n" r="E145">
-        <v>99.8614</v>
+        <v>99.2573</v>
       </c>
       <c t="n" r="F145">
-        <v>-2.1486</v>
+        <v>-2.1535</v>
       </c>
       <c t="n" r="G145">
-        <v>2.9162</v>
+        <v>2.9110</v>
       </c>
     </row>
     <row r="146">
@@ -4540,19 +4540,19 @@
         </is>
       </c>
       <c t="n" r="C146">
-        <v>0.6623</v>
+        <v>0.6678</v>
       </c>
       <c t="n" r="D146">
-        <v>-1.9250</v>
+        <v>-1.9225</v>
       </c>
       <c t="n" r="E146">
-        <v>1.9063</v>
+        <v>1.9086</v>
       </c>
       <c t="n" r="F146">
-        <v>-1.1978</v>
+        <v>-1.1923</v>
       </c>
       <c t="n" r="G146">
-        <v>2.5500</v>
+        <v>2.5556</v>
       </c>
     </row>
     <row r="147">
@@ -4567,22 +4567,22 @@
         </is>
       </c>
       <c t="n" r="C147">
-        <v>-0.0068</v>
+        <v>0.0012</v>
       </c>
       <c t="n" r="D147">
-        <v>-0.3313</v>
+        <v>-0.3226</v>
       </c>
       <c t="n" r="E147">
-        <v>7.8846</v>
+        <v>7.8820</v>
       </c>
       <c t="n" r="F147">
-        <v>-0.3828</v>
+        <v>-0.3749</v>
       </c>
       <c t="n" r="G147">
-        <v>2.2624</v>
+        <v>2.2706</v>
       </c>
       <c t="n" r="H147">
-        <v>130.9874</v>
+        <v>131.0189</v>
       </c>
     </row>
     <row r="148">
@@ -4597,19 +4597,19 @@
         </is>
       </c>
       <c t="n" r="C148">
-        <v>-1.9919</v>
+        <v>-1.9890</v>
       </c>
       <c t="n" r="D148">
-        <v>-1.6834</v>
+        <v>-1.7294</v>
       </c>
       <c t="n" r="E148">
-        <v>3.6859</v>
+        <v>3.6885</v>
       </c>
       <c t="n" r="F148">
-        <v>-1.5774</v>
+        <v>-1.5745</v>
       </c>
       <c t="n" r="G148">
-        <v>1.0904</v>
+        <v>1.0933</v>
       </c>
     </row>
     <row r="149">
@@ -4624,22 +4624,22 @@
         </is>
       </c>
       <c t="n" r="C149">
-        <v>-0.1462</v>
+        <v>-0.1248</v>
       </c>
       <c t="n" r="D149">
-        <v>-0.6889</v>
+        <v>-0.6709</v>
       </c>
       <c t="n" r="E149">
-        <v>2.1592</v>
+        <v>2.1695</v>
       </c>
       <c t="n" r="F149">
-        <v>-1.6406</v>
+        <v>-1.6195</v>
       </c>
       <c t="n" r="G149">
-        <v>1.0524</v>
+        <v>1.0741</v>
       </c>
       <c t="n" r="H149">
-        <v>70.7214</v>
+        <v>69.7759</v>
       </c>
     </row>
     <row r="150">
@@ -4654,16 +4654,16 @@
         </is>
       </c>
       <c t="n" r="C150">
-        <v>-0.1788</v>
+        <v>-0.1823</v>
       </c>
       <c t="n" r="D150">
-        <v>-0.7025</v>
+        <v>-0.7027</v>
       </c>
       <c t="n" r="F150">
-        <v>-0.9499</v>
+        <v>-0.9534</v>
       </c>
       <c t="n" r="G150">
-        <v>0.0928</v>
+        <v>0.0893</v>
       </c>
     </row>
     <row r="151">
@@ -4912,25 +4912,25 @@
         </is>
       </c>
       <c t="n" r="C163">
-        <v>0.2975</v>
+        <v>0.2551</v>
       </c>
       <c t="n" r="D163">
-        <v>8.7463</v>
+        <v>8.6869</v>
       </c>
       <c t="n" r="E163">
-        <v>17.1696</v>
+        <v>17.0852</v>
       </c>
       <c t="n" r="F163">
-        <v>9.0349</v>
+        <v>8.9887</v>
       </c>
       <c t="n" r="G163">
-        <v>-0.4726</v>
+        <v>-0.5147</v>
       </c>
       <c t="n" r="H163">
-        <v>153.2588</v>
+        <v>153.1449</v>
       </c>
       <c t="n" r="I163">
-        <v>496.4624</v>
+        <v>496.2134</v>
       </c>
     </row>
     <row r="164">
@@ -4945,76 +4945,76 @@
         </is>
       </c>
       <c t="n" r="C164">
-        <v>-0.2421</v>
+        <v>-0.2510</v>
       </c>
       <c t="n" r="D164">
-        <v>-0.7722</v>
+        <v>-0.7737</v>
       </c>
       <c t="n" r="E164">
-        <v>-0.2703</v>
+        <v>-0.2719</v>
       </c>
       <c t="n" r="F164">
-        <v>-0.8981</v>
+        <v>-0.9070</v>
       </c>
       <c t="n" r="G164">
-        <v>-1.5876</v>
+        <v>-1.5964</v>
       </c>
     </row>
     <row r="165">
       <c t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">ZPV</t>
+          <t xml:space="preserve">OO2</t>
         </is>
       </c>
       <c t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
+          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C165">
-        <v>6.7287</v>
+        <v>-2.2274</v>
       </c>
       <c t="n" r="D165">
-        <v>6.3763</v>
+        <v>-7.6270</v>
       </c>
       <c t="n" r="E165">
-        <v>1.6688</v>
+        <v>-11.9595</v>
       </c>
       <c t="n" r="F165">
-        <v>5.6605</v>
+        <v>-10.3745</v>
       </c>
       <c t="n" r="G165">
-        <v>-7.4594</v>
-      </c>
-      <c t="n" r="H165">
-        <v>95.2654</v>
+        <v>-7.5754</v>
       </c>
     </row>
     <row r="166">
       <c t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">OO2</t>
+          <t xml:space="preserve">ZPV</t>
         </is>
       </c>
       <c t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
         </is>
       </c>
       <c t="n" r="C166">
-        <v>-2.2006</v>
+        <v>5.7273</v>
       </c>
       <c t="n" r="D166">
-        <v>-7.6220</v>
+        <v>2.4592</v>
       </c>
       <c t="n" r="E166">
-        <v>-11.9397</v>
+        <v>0.6985</v>
       </c>
       <c t="n" r="F166">
-        <v>-10.3500</v>
+        <v>4.6691</v>
       </c>
       <c t="n" r="G166">
-        <v>-7.5501</v>
+        <v>-8.3277</v>
+      </c>
+      <c t="n" r="H166">
+        <v>93.3456</v>
       </c>
     </row>
     <row r="167">
@@ -5029,19 +5029,19 @@
         </is>
       </c>
       <c t="n" r="C167">
-        <v>0.3881</v>
+        <v>0.3905</v>
       </c>
       <c t="n" r="D167">
-        <v>-0.5729</v>
+        <v>-0.5716</v>
       </c>
       <c t="n" r="E167">
-        <v>2.4307</v>
+        <v>2.4323</v>
       </c>
       <c t="n" r="F167">
-        <v>-0.2959</v>
+        <v>-0.2936</v>
       </c>
       <c t="n" r="G167">
-        <v>-11.4533</v>
+        <v>-11.4512</v>
       </c>
     </row>
     <row r="168">
@@ -5056,19 +5056,19 @@
         </is>
       </c>
       <c t="n" r="C168">
-        <v>0.1693</v>
+        <v>0.1932</v>
       </c>
       <c t="n" r="D168">
-        <v>4.3540</v>
+        <v>4.3800</v>
       </c>
       <c t="n" r="E168">
-        <v>4.7927</v>
+        <v>4.8187</v>
       </c>
       <c t="n" r="F168">
-        <v>4.1016</v>
+        <v>4.1264</v>
       </c>
       <c t="n" r="G168">
-        <v>-13.3843</v>
+        <v>-13.3637</v>
       </c>
     </row>
     <row r="169">
@@ -5083,22 +5083,22 @@
         </is>
       </c>
       <c t="n" r="C169">
-        <v>-0.0348</v>
+        <v>-0.0356</v>
       </c>
       <c t="n" r="D169">
-        <v>-0.1091</v>
+        <v>-0.1093</v>
       </c>
       <c t="n" r="E169">
-        <v>-17.3171</v>
+        <v>-17.3178</v>
       </c>
       <c t="n" r="F169">
-        <v>-0.1348</v>
+        <v>-0.1356</v>
       </c>
       <c t="n" r="G169">
-        <v>-13.9674</v>
+        <v>-13.9681</v>
       </c>
       <c t="n" r="H169">
-        <v>196.3034</v>
+        <v>196.2719</v>
       </c>
     </row>
     <row r="170">
@@ -5113,22 +5113,22 @@
         </is>
       </c>
       <c t="n" r="C170">
-        <v>-0.5139</v>
+        <v>-0.5388</v>
       </c>
       <c t="n" r="D170">
-        <v>-1.5530</v>
+        <v>-1.5655</v>
       </c>
       <c t="n" r="E170">
-        <v>-17.3549</v>
+        <v>-17.3552</v>
       </c>
       <c t="n" r="F170">
-        <v>-1.8041</v>
+        <v>-1.8287</v>
       </c>
       <c t="n" r="G170">
-        <v>-18.4915</v>
+        <v>-18.5119</v>
       </c>
       <c t="n" r="H170">
-        <v>-2.9532</v>
+        <v>-2.9056</v>
       </c>
     </row>
     <row r="171">
@@ -5143,22 +5143,22 @@
         </is>
       </c>
       <c t="n" r="C171">
-        <v>0.1133</v>
+        <v>0.1064</v>
       </c>
       <c t="n" r="D171">
-        <v>-0.5744</v>
+        <v>-0.5639</v>
       </c>
       <c t="n" r="E171">
-        <v>-17.9089</v>
+        <v>-17.9133</v>
       </c>
       <c t="n" r="F171">
-        <v>-0.0539</v>
+        <v>-0.0608</v>
       </c>
       <c t="n" r="G171">
-        <v>-18.7606</v>
+        <v>-18.7662</v>
       </c>
       <c t="n" r="H171">
-        <v>91.3713</v>
+        <v>91.3537</v>
       </c>
     </row>
     <row r="172">
@@ -5173,22 +5173,22 @@
         </is>
       </c>
       <c t="n" r="C172">
-        <v>-0.2813</v>
+        <v>-0.2887</v>
       </c>
       <c t="n" r="D172">
-        <v>-0.8458</v>
+        <v>-0.8459</v>
       </c>
       <c t="n" r="E172">
-        <v>-23.3514</v>
+        <v>-23.3516</v>
       </c>
       <c t="n" r="F172">
-        <v>-0.9957</v>
+        <v>-1.0030</v>
       </c>
       <c t="n" r="G172">
-        <v>-24.4645</v>
+        <v>-24.4701</v>
       </c>
       <c t="n" r="H172">
-        <v>350.2507</v>
+        <v>350.3243</v>
       </c>
     </row>
     <row r="173">
@@ -5209,7 +5209,7 @@
         <v>-0.0526</v>
       </c>
       <c t="n" r="E173">
-        <v>-0.0859</v>
+        <v>-0.0861</v>
       </c>
       <c t="n" r="F173">
         <v>-0.0611</v>
@@ -5230,25 +5230,25 @@
         </is>
       </c>
       <c t="n" r="C174">
-        <v>-0.0790</v>
+        <v>-0.0793</v>
       </c>
       <c t="n" r="D174">
-        <v>-0.2747</v>
+        <v>-0.2743</v>
       </c>
       <c t="n" r="E174">
-        <v>-50.7321</v>
+        <v>-50.8301</v>
       </c>
       <c t="n" r="F174">
-        <v>-1.0505</v>
+        <v>-1.0508</v>
       </c>
       <c t="n" r="G174">
-        <v>-30.3229</v>
+        <v>-30.3231</v>
       </c>
       <c t="n" r="H174">
-        <v>71.0482</v>
+        <v>71.0695</v>
       </c>
       <c t="n" r="I174">
-        <v>785.1535</v>
+        <v>785.1506</v>
       </c>
     </row>
     <row r="175">
@@ -5263,22 +5263,22 @@
         </is>
       </c>
       <c t="n" r="C175">
-        <v>-0.6398</v>
+        <v>-0.6640</v>
       </c>
       <c t="n" r="D175">
-        <v>-1.7419</v>
+        <v>-1.7550</v>
       </c>
       <c t="n" r="E175">
-        <v>-30.4559</v>
+        <v>-30.4570</v>
       </c>
       <c t="n" r="F175">
-        <v>-1.9517</v>
+        <v>-1.9756</v>
       </c>
       <c t="n" r="G175">
-        <v>-30.8235</v>
+        <v>-30.8404</v>
       </c>
       <c t="n" r="H175">
-        <v>102.9259</v>
+        <v>102.9667</v>
       </c>
     </row>
     <row r="176">
@@ -5293,22 +5293,22 @@
         </is>
       </c>
       <c t="n" r="C176">
-        <v>-0.1954</v>
+        <v>-0.1993</v>
       </c>
       <c t="n" r="D176">
-        <v>-3.4675</v>
+        <v>-3.4679</v>
       </c>
       <c t="n" r="E176">
-        <v>5.0890</v>
+        <v>5.0829</v>
       </c>
       <c t="n" r="F176">
-        <v>-7.3457</v>
+        <v>-7.3493</v>
       </c>
       <c t="n" r="G176">
-        <v>-40.9111</v>
+        <v>-40.9134</v>
       </c>
       <c t="n" r="H176">
-        <v>113.6524</v>
+        <v>113.6578</v>
       </c>
     </row>
     <row r="177">
@@ -5323,25 +5323,25 @@
         </is>
       </c>
       <c t="n" r="C177">
-        <v>-0.4541</v>
+        <v>-0.4535</v>
       </c>
       <c t="n" r="D177">
-        <v>-18.5577</v>
+        <v>-18.5805</v>
       </c>
       <c t="n" r="E177">
-        <v>-40.7806</v>
+        <v>-40.7789</v>
       </c>
       <c t="n" r="F177">
-        <v>-52.0184</v>
+        <v>-52.0181</v>
       </c>
       <c t="n" r="G177">
-        <v>-41.6898</v>
+        <v>-41.6894</v>
       </c>
       <c t="n" r="H177">
-        <v>-2.6072</v>
+        <v>-2.5842</v>
       </c>
       <c t="n" r="I177">
-        <v>217.4383</v>
+        <v>217.4404</v>
       </c>
     </row>
     <row r="178">
@@ -5359,10 +5359,10 @@
         <v>-0.1431</v>
       </c>
       <c t="n" r="D178">
-        <v>-23.7558</v>
+        <v>-23.7544</v>
       </c>
       <c t="n" r="E178">
-        <v>-23.0544</v>
+        <v>-23.0577</v>
       </c>
       <c t="n" r="F178">
         <v>-26.0910</v>
@@ -5371,7 +5371,7 @@
         <v>-43.1301</v>
       </c>
       <c t="n" r="H178">
-        <v>40.5694</v>
+        <v>40.5781</v>
       </c>
     </row>
     <row r="179">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c t="n" r="C179">
-        <v>-82.0537</v>
+        <v>-82.0672</v>
       </c>
       <c t="n" r="D179">
-        <v>-83.9676</v>
+        <v>-83.9768</v>
       </c>
       <c t="n" r="E179">
-        <v>-76.3320</v>
+        <v>-76.3482</v>
       </c>
       <c t="n" r="F179">
-        <v>-83.9910</v>
+        <v>-84.0030</v>
       </c>
       <c t="n" r="G179">
-        <v>-54.5990</v>
+        <v>-54.6331</v>
       </c>
     </row>
     <row r="180">
@@ -5413,25 +5413,25 @@
         </is>
       </c>
       <c t="n" r="C180">
-        <v>4.1329</v>
+        <v>4.8453</v>
       </c>
       <c t="n" r="D180">
-        <v>7.0247</v>
+        <v>7.3039</v>
       </c>
       <c t="n" r="E180">
-        <v>-9.9771</v>
+        <v>-9.8290</v>
       </c>
       <c t="n" r="F180">
-        <v>-12.8320</v>
+        <v>-12.2357</v>
       </c>
       <c t="n" r="G180">
-        <v>-58.9620</v>
+        <v>-58.6812</v>
       </c>
       <c t="n" r="H180">
-        <v>-20.0122</v>
+        <v>-19.4641</v>
       </c>
       <c t="n" r="I180">
-        <v>335.1301</v>
+        <v>338.0764</v>
       </c>
     </row>
     <row r="181">
@@ -5446,25 +5446,25 @@
         </is>
       </c>
       <c t="n" r="C181">
-        <v>-1.2914</v>
+        <v>-1.2938</v>
       </c>
       <c t="n" r="D181">
-        <v>35.8306</v>
+        <v>37.1716</v>
       </c>
       <c t="n" r="E181">
-        <v>-63.4906</v>
+        <v>-63.4845</v>
       </c>
       <c t="n" r="F181">
-        <v>55.0695</v>
+        <v>55.0658</v>
       </c>
       <c t="n" r="G181">
-        <v>-66.2324</v>
+        <v>-66.2332</v>
       </c>
       <c t="n" r="H181">
-        <v>-68.8958</v>
+        <v>-68.8926</v>
       </c>
       <c t="n" r="I181">
-        <v>-16.3292</v>
+        <v>-16.3326</v>
       </c>
     </row>
     <row r="182">
@@ -5479,19 +5479,19 @@
         </is>
       </c>
       <c t="n" r="C182">
-        <v>-26.5669</v>
+        <v>-26.6546</v>
       </c>
       <c t="n" r="D182">
-        <v>-40.5795</v>
+        <v>-40.6434</v>
       </c>
       <c t="n" r="E182">
-        <v>444.0308</v>
+        <v>455.9669</v>
       </c>
       <c t="n" r="F182">
-        <v>-40.6016</v>
+        <v>-40.6725</v>
       </c>
       <c t="n" r="G182">
-        <v>-67.0972</v>
+        <v>-67.1365</v>
       </c>
     </row>
     <row r="183">
@@ -5506,25 +5506,25 @@
         </is>
       </c>
       <c t="n" r="C183">
-        <v>-24.7717</v>
+        <v>-24.7767</v>
       </c>
       <c t="n" r="D183">
-        <v>-76.9662</v>
+        <v>-76.9671</v>
       </c>
       <c t="n" r="E183">
-        <v>-75.7923</v>
+        <v>-75.7841</v>
       </c>
       <c t="n" r="F183">
-        <v>-77.0187</v>
+        <v>-77.0202</v>
       </c>
       <c t="n" r="G183">
-        <v>-67.3201</v>
+        <v>-67.3223</v>
       </c>
       <c t="n" r="H183">
-        <v>-84.9017</v>
+        <v>-84.8999</v>
       </c>
       <c t="n" r="I183">
-        <v>-44.8555</v>
+        <v>-44.8592</v>
       </c>
     </row>
     <row r="184">
@@ -5569,22 +5569,22 @@
         </is>
       </c>
       <c t="n" r="C185">
-        <v>-98.9038</v>
+        <v>-98.8766</v>
       </c>
       <c t="n" r="D185">
-        <v>-99.1307</v>
+        <v>-99.1091</v>
       </c>
       <c t="n" r="E185">
-        <v>-99.0769</v>
+        <v>-99.0544</v>
       </c>
       <c t="n" r="F185">
-        <v>-99.1382</v>
+        <v>-99.1168</v>
       </c>
       <c t="n" r="G185">
-        <v>-99.1732</v>
+        <v>-99.1527</v>
       </c>
       <c t="n" r="H185">
-        <v>-98.5904</v>
+        <v>-98.5554</v>
       </c>
     </row>
     <row r="186">
@@ -5647,13 +5647,13 @@
         </is>
       </c>
       <c t="n" r="C190">
-        <v>1.4645</v>
+        <v>1.5578</v>
       </c>
       <c t="n" r="D190">
-        <v>3.4366</v>
+        <v>3.5185</v>
       </c>
       <c t="n" r="F190">
-        <v>4.1998</v>
+        <v>4.2956</v>
       </c>
     </row>
     <row r="191">
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c t="n" r="C193">
-        <v>-16.6727</v>
+        <v>-17.0496</v>
       </c>
       <c t="n" r="D193">
-        <v>-39.4426</v>
+        <v>-39.4738</v>
       </c>
       <c t="n" r="F193">
-        <v>-43.3399</v>
+        <v>-43.5962</v>
       </c>
     </row>
     <row r="194">
@@ -5713,13 +5713,13 @@
         </is>
       </c>
       <c t="n" r="C194">
-        <v>-10.3321</v>
+        <v>-9.9376</v>
       </c>
       <c t="n" r="D194">
-        <v>-63.2151</v>
+        <v>-63.1119</v>
       </c>
       <c t="n" r="F194">
-        <v>-28.0572</v>
+        <v>-27.7406</v>
       </c>
     </row>
     <row r="195">
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c t="n" r="C196">
-        <v>1.6064</v>
+        <v>1.6073</v>
       </c>
     </row>
     <row r="197">
@@ -5761,13 +5761,13 @@
         </is>
       </c>
       <c t="n" r="C197">
-        <v>0.8126</v>
+        <v>0.8132</v>
       </c>
       <c t="n" r="D197">
-        <v>1.9988</v>
+        <v>1.9946</v>
       </c>
       <c t="n" r="F197">
-        <v>1.8854</v>
+        <v>1.8860</v>
       </c>
     </row>
     <row r="198">
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c t="n" r="C204">
-        <v>0.3719</v>
+        <v>0.5891</v>
       </c>
       <c t="n" r="D204">
-        <v>2.1031</v>
+        <v>2.4948</v>
       </c>
     </row>
     <row r="205">
@@ -5872,16 +5872,16 @@
         </is>
       </c>
       <c t="n" r="C205">
-        <v>1.7261</v>
+        <v>1.9286</v>
       </c>
       <c t="n" r="D205">
-        <v>417.0733</v>
+        <v>417.5734</v>
       </c>
       <c t="n" r="E205">
-        <v>460.8613</v>
+        <v>460.3801</v>
       </c>
       <c t="n" r="F205">
-        <v>425.8669</v>
+        <v>426.9139</v>
       </c>
     </row>
     <row r="206">
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c t="n" r="C206">
-        <v>11.9295</v>
+        <v>11.8744</v>
       </c>
       <c t="n" r="D206">
-        <v>43.7518</v>
+        <v>43.5363</v>
       </c>
       <c t="n" r="E206">
-        <v>58.5430</v>
+        <v>57.9499</v>
       </c>
       <c t="n" r="F206">
-        <v>46.5044</v>
+        <v>46.4322</v>
       </c>
     </row>
     <row r="207">
@@ -5932,16 +5932,16 @@
         </is>
       </c>
       <c t="n" r="C208">
-        <v>-0.0445</v>
+        <v>-0.0452</v>
       </c>
       <c t="n" r="D208">
-        <v>-0.1108</v>
+        <v>-0.1105</v>
       </c>
       <c t="n" r="E208">
-        <v>19.3887</v>
+        <v>19.3810</v>
       </c>
       <c t="n" r="F208">
-        <v>-0.1434</v>
+        <v>-0.1441</v>
       </c>
     </row>
     <row r="209">
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c t="n" r="C209">
-        <v>-0.0245</v>
+        <v>-0.0155</v>
       </c>
     </row>
     <row r="210">
@@ -5983,16 +5983,16 @@
         </is>
       </c>
       <c t="n" r="C211">
-        <v>2.9905</v>
+        <v>3.3300</v>
       </c>
       <c t="n" r="D211">
-        <v>8.9054</v>
+        <v>9.1541</v>
       </c>
       <c t="n" r="E211">
-        <v>19.5911</v>
+        <v>19.6049</v>
       </c>
       <c t="n" r="F211">
-        <v>10.9968</v>
+        <v>11.3627</v>
       </c>
     </row>
     <row r="212">
@@ -6019,13 +6019,13 @@
         </is>
       </c>
       <c t="n" r="C213">
-        <v>-0.1078</v>
+        <v>-0.1075</v>
       </c>
       <c t="n" r="D213">
-        <v>-0.3218</v>
+        <v>-0.3216</v>
       </c>
       <c t="n" r="F213">
-        <v>-0.3294</v>
+        <v>-0.3291</v>
       </c>
     </row>
     <row r="214">
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c t="n" r="C214">
-        <v>-0.8886</v>
+        <v>-0.9158</v>
       </c>
       <c t="n" r="D214">
-        <v>6.7103</v>
+        <v>6.7112</v>
       </c>
     </row>
     <row r="215">
@@ -6058,7 +6058,7 @@
         </is>
       </c>
       <c t="n" r="C215">
-        <v>-0.2600</v>
+        <v>-0.2094</v>
       </c>
     </row>
     <row r="216">
@@ -6073,16 +6073,16 @@
         </is>
       </c>
       <c t="n" r="C216">
-        <v>-0.0342</v>
+        <v>-0.0352</v>
       </c>
       <c t="n" r="D216">
-        <v>-0.0995</v>
+        <v>-0.0996</v>
       </c>
       <c t="n" r="E216">
-        <v>12.7794</v>
+        <v>12.7793</v>
       </c>
       <c t="n" r="F216">
-        <v>-0.1194</v>
+        <v>-0.1204</v>
       </c>
     </row>
     <row r="217">
@@ -6097,16 +6097,16 @@
         </is>
       </c>
       <c t="n" r="C217">
-        <v>-0.0084</v>
+        <v>-0.0086</v>
       </c>
       <c t="n" r="D217">
-        <v>2.7802</v>
+        <v>2.7789</v>
       </c>
       <c t="n" r="E217">
-        <v>12.5153</v>
+        <v>12.4946</v>
       </c>
       <c t="n" r="F217">
-        <v>3.1037</v>
+        <v>3.1035</v>
       </c>
     </row>
     <row r="218">
@@ -6121,16 +6121,16 @@
         </is>
       </c>
       <c t="n" r="C218">
-        <v>-95.2551</v>
+        <v>-96.4626</v>
       </c>
       <c t="n" r="D218">
-        <v>-99.9518</v>
+        <v>-99.9642</v>
       </c>
       <c t="n" r="E218">
-        <v>-99.9955</v>
+        <v>-99.9966</v>
       </c>
       <c t="n" r="F218">
-        <v>-99.9919</v>
+        <v>-99.9940</v>
       </c>
     </row>
     <row r="219">
@@ -6253,16 +6253,16 @@
         </is>
       </c>
       <c t="n" r="C228">
-        <v>10.1256</v>
+        <v>9.0264</v>
       </c>
       <c t="n" r="D228">
-        <v>4.5594</v>
+        <v>4.6562</v>
       </c>
       <c t="n" r="E228">
-        <v>21.2201</v>
+        <v>19.6239</v>
       </c>
       <c t="n" r="F228">
-        <v>16.0164</v>
+        <v>14.8585</v>
       </c>
     </row>
     <row r="229">
@@ -6301,16 +6301,16 @@
         </is>
       </c>
       <c t="n" r="C231">
-        <v>0.8756</v>
+        <v>1.1789</v>
       </c>
       <c t="n" r="D231">
-        <v>4.9950</v>
+        <v>5.2221</v>
       </c>
       <c t="n" r="E231">
-        <v>13.8603</v>
+        <v>13.8678</v>
       </c>
       <c t="n" r="F231">
-        <v>6.8363</v>
+        <v>7.1575</v>
       </c>
     </row>
     <row r="232">
@@ -6325,16 +6325,16 @@
         </is>
       </c>
       <c t="n" r="C232">
-        <v>2.9299</v>
+        <v>3.0568</v>
       </c>
       <c t="n" r="D232">
-        <v>9.5130</v>
+        <v>9.5355</v>
       </c>
       <c t="n" r="E232">
-        <v>20.9450</v>
+        <v>20.7331</v>
       </c>
       <c t="n" r="F232">
-        <v>11.5511</v>
+        <v>11.6886</v>
       </c>
     </row>
     <row r="233">
@@ -6349,16 +6349,16 @@
         </is>
       </c>
       <c t="n" r="C233">
-        <v>1.0898</v>
+        <v>1.3693</v>
       </c>
       <c t="n" r="D233">
-        <v>1.3543</v>
+        <v>1.6369</v>
       </c>
       <c t="n" r="E233">
-        <v>3.9078</v>
+        <v>4.0882</v>
       </c>
       <c t="n" r="F233">
-        <v>1.9769</v>
+        <v>2.2589</v>
       </c>
     </row>
     <row r="234">
@@ -6385,16 +6385,16 @@
         </is>
       </c>
       <c t="n" r="C235">
-        <v>0.9625</v>
+        <v>1.2658</v>
       </c>
       <c t="n" r="D235">
-        <v>5.0854</v>
+        <v>5.3124</v>
       </c>
       <c t="n" r="E235">
-        <v>13.9583</v>
+        <v>13.9655</v>
       </c>
       <c t="n" r="F235">
-        <v>6.9282</v>
+        <v>7.2495</v>
       </c>
     </row>
     <row r="236">
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c t="n" r="C239">
-        <v>-1.4486</v>
+        <v>-1.4611</v>
       </c>
       <c t="n" r="D239">
-        <v>-80.7985</v>
+        <v>-80.5190</v>
       </c>
       <c t="n" r="F239">
-        <v>-84.7394</v>
+        <v>-84.7413</v>
       </c>
     </row>
     <row r="240">
@@ -6490,16 +6490,16 @@
         </is>
       </c>
       <c t="n" r="C242">
-        <v>-0.0748</v>
+        <v>-0.0647</v>
       </c>
       <c t="n" r="D242">
-        <v>-0.2469</v>
+        <v>-0.2345</v>
       </c>
       <c t="n" r="E242">
-        <v>1628.0437</v>
+        <v>1624.4586</v>
       </c>
       <c t="n" r="F242">
-        <v>-0.2840</v>
+        <v>-0.2739</v>
       </c>
     </row>
     <row r="243">
@@ -6550,13 +6550,13 @@
         </is>
       </c>
       <c t="n" r="C246">
-        <v>-5.3652</v>
+        <v>-5.3447</v>
       </c>
       <c t="n" r="D246">
-        <v>-15.6301</v>
+        <v>-15.4653</v>
       </c>
       <c t="n" r="F246">
-        <v>-17.8511</v>
+        <v>-17.8333</v>
       </c>
     </row>
     <row r="247">
@@ -6571,16 +6571,16 @@
         </is>
       </c>
       <c t="n" r="C247">
-        <v>-5.6975</v>
+        <v>-5.6790</v>
       </c>
       <c t="n" r="D247">
-        <v>-16.0311</v>
+        <v>-15.9059</v>
       </c>
       <c t="n" r="E247">
-        <v>-24.9807</v>
+        <v>-25.2164</v>
       </c>
       <c t="n" r="F247">
-        <v>-18.0174</v>
+        <v>-18.0013</v>
       </c>
     </row>
     <row r="248">
@@ -6679,16 +6679,16 @@
         </is>
       </c>
       <c t="n" r="C255">
-        <v>-86.0685</v>
+        <v>-86.0924</v>
       </c>
       <c t="n" r="D255">
-        <v>-88.5763</v>
+        <v>-88.5930</v>
       </c>
       <c t="n" r="E255">
-        <v>-75.1848</v>
+        <v>-75.2257</v>
       </c>
       <c t="n" r="F255">
-        <v>-88.5933</v>
+        <v>-88.6129</v>
       </c>
     </row>
     <row r="256">
@@ -6703,13 +6703,16 @@
         </is>
       </c>
       <c t="n" r="C256">
-        <v>-1.3604</v>
+        <v>-1.4092</v>
       </c>
       <c t="n" r="D256">
-        <v>-13.3484</v>
+        <v>-13.3533</v>
+      </c>
+      <c t="n" r="E256">
+        <v>607.4662</v>
       </c>
       <c t="n" r="F256">
-        <v>-13.4982</v>
+        <v>-13.5410</v>
       </c>
     </row>
     <row r="257">
@@ -6724,16 +6727,16 @@
         </is>
       </c>
       <c t="n" r="C257">
-        <v>-5.8159</v>
+        <v>-5.8252</v>
       </c>
       <c t="n" r="D257">
-        <v>-6.4686</v>
+        <v>-6.4705</v>
       </c>
       <c t="n" r="E257">
-        <v>-9.3143</v>
+        <v>-9.3239</v>
       </c>
       <c t="n" r="F257">
-        <v>-4.5993</v>
+        <v>-4.6087</v>
       </c>
     </row>
     <row r="258">
@@ -6760,7 +6763,7 @@
         </is>
       </c>
       <c t="n" r="C259">
-        <v>3.0773</v>
+        <v>3.3931</v>
       </c>
     </row>
     <row r="260">
@@ -6775,7 +6778,7 @@
         </is>
       </c>
       <c t="n" r="C260">
-        <v>-0.0782</v>
+        <v>-0.0801</v>
       </c>
     </row>
     <row r="261">
@@ -6814,7 +6817,7 @@
         </is>
       </c>
       <c t="n" r="C263">
-        <v>8.9013</v>
+        <v>8.9159</v>
       </c>
     </row>
     <row r="264">
@@ -6841,13 +6844,13 @@
         </is>
       </c>
       <c t="n" r="C265">
-        <v>0.9229</v>
+        <v>1.1667</v>
       </c>
       <c t="n" r="D265">
-        <v>5.3759</v>
+        <v>5.5508</v>
       </c>
       <c t="n" r="F265">
-        <v>6.9627</v>
+        <v>7.2210</v>
       </c>
     </row>
     <row r="266">
@@ -6862,13 +6865,13 @@
         </is>
       </c>
       <c t="n" r="C266">
-        <v>0.8678</v>
+        <v>1.1087</v>
       </c>
       <c t="n" r="D266">
-        <v>5.2960</v>
+        <v>5.4680</v>
       </c>
       <c t="n" r="F266">
-        <v>6.8822</v>
+        <v>7.1375</v>
       </c>
     </row>
     <row r="267">
@@ -6895,16 +6898,16 @@
         </is>
       </c>
       <c t="n" r="C268">
-        <v>-29.4004</v>
+        <v>-29.3918</v>
       </c>
       <c t="n" r="D268">
-        <v>-28.0677</v>
+        <v>-28.1049</v>
       </c>
       <c t="n" r="E268">
-        <v>-23.7384</v>
+        <v>-23.9446</v>
       </c>
       <c t="n" r="F268">
-        <v>-27.2141</v>
+        <v>-27.2052</v>
       </c>
     </row>
     <row r="269">
@@ -6931,16 +6934,16 @@
         </is>
       </c>
       <c t="n" r="C270">
-        <v>-0.4371</v>
+        <v>-0.4468</v>
       </c>
       <c t="n" r="D270">
-        <v>-1.4505</v>
+        <v>-1.4532</v>
       </c>
       <c t="n" r="E270">
-        <v>-32.3293</v>
+        <v>-32.3712</v>
       </c>
       <c t="n" r="F270">
-        <v>95.7068</v>
+        <v>95.6879</v>
       </c>
     </row>
     <row r="271">
@@ -6955,7 +6958,7 @@
         </is>
       </c>
       <c t="n" r="C271">
-        <v>33.7609</v>
+        <v>34.1998</v>
       </c>
     </row>
     <row r="272">
@@ -6970,13 +6973,13 @@
         </is>
       </c>
       <c t="n" r="C272">
-        <v>-0.3219</v>
+        <v>-0.3314</v>
       </c>
       <c t="n" r="D272">
-        <v>-0.8859</v>
+        <v>-0.8515</v>
       </c>
       <c t="n" r="F272">
-        <v>-2.3331</v>
+        <v>-2.3424</v>
       </c>
     </row>
     <row r="273">
@@ -6991,16 +6994,16 @@
         </is>
       </c>
       <c t="n" r="C273">
-        <v>-77.3787</v>
+        <v>-77.5869</v>
       </c>
       <c t="n" r="D273">
-        <v>-87.8722</v>
+        <v>-87.9568</v>
       </c>
       <c t="n" r="E273">
-        <v>-45.8616</v>
+        <v>-46.4694</v>
       </c>
       <c t="n" r="F273">
-        <v>106.2584</v>
+        <v>104.3596</v>
       </c>
     </row>
     <row r="274">
@@ -7039,13 +7042,13 @@
         </is>
       </c>
       <c t="n" r="C276">
-        <v>-0.0573</v>
+        <v>-0.0512</v>
       </c>
       <c t="n" r="D276">
-        <v>-10.8353</v>
+        <v>-10.8914</v>
       </c>
       <c t="n" r="F276">
-        <v>-9.7212</v>
+        <v>-9.7157</v>
       </c>
     </row>
     <row r="277">
@@ -7072,16 +7075,16 @@
         </is>
       </c>
       <c t="n" r="C278">
-        <v>2.9924</v>
+        <v>3.2604</v>
       </c>
       <c t="n" r="D278">
-        <v>-59.0990</v>
+        <v>-58.7511</v>
       </c>
       <c t="n" r="E278">
-        <v>-98.9263</v>
+        <v>-98.8890</v>
       </c>
       <c t="n" r="F278">
-        <v>-98.1659</v>
+        <v>-98.1611</v>
       </c>
     </row>
     <row r="279">
@@ -7111,10 +7114,10 @@
         <v>-0.2988</v>
       </c>
       <c t="n" r="D280">
-        <v>0.8692</v>
+        <v>0.8311</v>
       </c>
       <c t="n" r="E280">
-        <v>-96.4050</v>
+        <v>-96.0178</v>
       </c>
       <c t="n" r="F280">
         <v>0.8311</v>
@@ -7156,16 +7159,16 @@
         </is>
       </c>
       <c t="n" r="C283">
-        <v>-6.2990</v>
+        <v>-6.3116</v>
       </c>
       <c t="n" r="D283">
-        <v>-33.9867</v>
+        <v>-22.6033</v>
       </c>
       <c t="n" r="E283">
-        <v>4935.5467</v>
+        <v>4957.6045</v>
       </c>
       <c t="n" r="F283">
-        <v>11356.7496</v>
+        <v>11355.2071</v>
       </c>
     </row>
     <row r="284">
@@ -7180,13 +7183,13 @@
         </is>
       </c>
       <c t="n" r="C284">
-        <v>-0.0180</v>
+        <v>0.0003</v>
       </c>
       <c t="n" r="D284">
-        <v>-0.0680</v>
+        <v>-0.0484</v>
       </c>
       <c t="n" r="F284">
-        <v>-0.0237</v>
+        <v>-0.0054</v>
       </c>
     </row>
     <row r="285">
@@ -7237,7 +7240,7 @@
         </is>
       </c>
       <c t="n" r="C288">
-        <v>-28.1577</v>
+        <v>-28.9269</v>
       </c>
     </row>
     <row r="289">
@@ -7264,16 +7267,16 @@
         </is>
       </c>
       <c t="n" r="C290">
-        <v>0.4850</v>
+        <v>0.4950</v>
       </c>
       <c t="n" r="D290">
-        <v>2.5671</v>
+        <v>2.5505</v>
       </c>
       <c t="n" r="E290">
-        <v>10.2739</v>
+        <v>10.1936</v>
       </c>
       <c t="n" r="F290">
-        <v>3.1249</v>
+        <v>3.1352</v>
       </c>
     </row>
     <row r="291">
@@ -7300,16 +7303,16 @@
         </is>
       </c>
       <c t="n" r="C292">
-        <v>-26.7876</v>
+        <v>-26.6108</v>
       </c>
       <c t="n" r="D292">
-        <v>-57.7434</v>
+        <v>-57.6853</v>
       </c>
       <c t="n" r="E292">
-        <v>-57.4681</v>
+        <v>-57.3752</v>
       </c>
       <c t="n" r="F292">
-        <v>-56.9607</v>
+        <v>-56.8568</v>
       </c>
     </row>
     <row r="293">
@@ -7399,468 +7402,456 @@
     <row r="298">
       <c t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">OO3</t>
+          <t xml:space="preserve">BCI</t>
         </is>
       </c>
       <c t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">OYAK PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C298">
+        <v>3.6767</v>
+      </c>
+      <c t="n" r="D298">
+        <v>10.2571</v>
+      </c>
+      <c t="n" r="E298">
+        <v>21.3702</v>
+      </c>
+      <c t="n" r="F298">
+        <v>12.8529</v>
       </c>
     </row>
     <row r="299">
       <c t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">BCI</t>
+          <t xml:space="preserve">PGN</t>
         </is>
       </c>
       <c t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C299">
-        <v>3.3016</v>
+        <v>3.1560</v>
       </c>
       <c t="n" r="D299">
-        <v>9.9905</v>
-      </c>
-      <c t="n" r="E299">
-        <v>21.0490</v>
+        <v>9.0005</v>
       </c>
       <c t="n" r="F299">
-        <v>12.4447</v>
+        <v>11.5963</v>
       </c>
     </row>
     <row r="300">
       <c t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">PGN</t>
+          <t xml:space="preserve">DDG</t>
         </is>
       </c>
       <c t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C300">
-        <v>3.2076</v>
-      </c>
-      <c t="n" r="D300">
-        <v>9.1881</v>
-      </c>
-      <c t="n" r="F300">
-        <v>11.6520</v>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="301">
       <c t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">DDG</t>
+          <t xml:space="preserve">KCI</t>
         </is>
       </c>
       <c t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C301">
+        <v>4.1757</v>
+      </c>
+      <c t="n" r="D301">
+        <v>11.8413</v>
+      </c>
+      <c t="n" r="F301">
+        <v>14.7335</v>
       </c>
     </row>
     <row r="302">
       <c t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">KCI</t>
+          <t xml:space="preserve">UUG</t>
         </is>
       </c>
       <c t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C302">
-        <v>3.8178</v>
-      </c>
-      <c t="n" r="D302">
-        <v>11.6007</v>
-      </c>
-      <c t="n" r="F302">
-        <v>14.3393</v>
+        <v>-73.7474</v>
       </c>
     </row>
     <row r="303">
       <c t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">UUG</t>
+          <t xml:space="preserve">GY2</t>
         </is>
       </c>
       <c t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">QINVEST PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C303">
-        <v>-74.1352</v>
+        <v>-0.0097</v>
+      </c>
+      <c t="n" r="D303">
+        <v>-0.8861</v>
       </c>
     </row>
     <row r="304">
       <c t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">GY2</t>
+          <t xml:space="preserve">GM1</t>
         </is>
       </c>
       <c t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">QINVEST PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">QİNVEST PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C304">
-        <v>-0.0277</v>
+        <v>1.0835</v>
       </c>
       <c t="n" r="D304">
-        <v>-0.9002</v>
+        <v>6.1134</v>
+      </c>
+      <c t="n" r="E304">
+        <v>14.4849</v>
+      </c>
+      <c t="n" r="F304">
+        <v>7.7223</v>
       </c>
     </row>
     <row r="305">
       <c t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">GM1</t>
+          <t xml:space="preserve">RI5</t>
         </is>
       </c>
       <c t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">QİNVEST PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C305">
-        <v>0.7848</v>
-      </c>
-      <c t="n" r="D305">
-        <v>5.8841</v>
-      </c>
-      <c t="n" r="E305">
-        <v>14.4945</v>
-      </c>
-      <c t="n" r="F305">
-        <v>7.4039</v>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="306">
       <c t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">RI5</t>
+          <t xml:space="preserve">RE5</t>
         </is>
       </c>
       <c t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">RE5</t>
+          <t xml:space="preserve">RKP</t>
         </is>
       </c>
       <c t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C307">
+        <v>2.0547</v>
+      </c>
+      <c t="n" r="D307">
+        <v>3.5173</v>
+      </c>
+      <c t="n" r="E307">
+        <v>11.8418</v>
+      </c>
+      <c t="n" r="F307">
+        <v>5.4524</v>
       </c>
     </row>
     <row r="308">
       <c t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">RKP</t>
+          <t xml:space="preserve">RI4</t>
         </is>
       </c>
       <c t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ KATILIM PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C308">
-        <v>1.8269</v>
-      </c>
-      <c t="n" r="D308">
-        <v>3.3822</v>
-      </c>
-      <c t="n" r="E308">
-        <v>11.9289</v>
-      </c>
-      <c t="n" r="F308">
-        <v>5.2171</v>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="309">
       <c t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">RI4</t>
+          <t xml:space="preserve">RE4</t>
         </is>
       </c>
       <c t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">RE4</t>
+          <t xml:space="preserve">EPG</t>
         </is>
       </c>
       <c t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C310">
+        <v>-0.0724</v>
+      </c>
+      <c t="n" r="D310">
+        <v>-0.2190</v>
+      </c>
+      <c t="n" r="E310">
+        <v>0.6009</v>
+      </c>
+      <c t="n" r="F310">
+        <v>-0.2522</v>
       </c>
     </row>
     <row r="311">
       <c t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">EPG</t>
+          <t xml:space="preserve">RE2</t>
         </is>
       </c>
       <c t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EFOR PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C311">
-        <v>-0.0754</v>
-      </c>
-      <c t="n" r="D311">
-        <v>-0.2234</v>
-      </c>
-      <c t="n" r="E311">
-        <v>0.6031</v>
-      </c>
-      <c t="n" r="F311">
-        <v>-0.2553</v>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="312">
       <c t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">RE2</t>
+          <t xml:space="preserve">RIP</t>
         </is>
       </c>
       <c t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İSTANBUL PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">RIP</t>
+          <t xml:space="preserve">RE3</t>
         </is>
       </c>
       <c t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İSTANBUL PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C313">
+        <v>-0.0516</v>
+      </c>
+      <c t="n" r="D313">
+        <v>-0.1479</v>
+      </c>
+      <c t="n" r="E313">
+        <v>2.0813</v>
+      </c>
+      <c t="n" r="F313">
+        <v>-0.1731</v>
       </c>
     </row>
     <row r="314">
       <c t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">RE3</t>
+          <t xml:space="preserve">REI</t>
         </is>
       </c>
       <c t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C314">
-        <v>-0.0530</v>
-      </c>
-      <c t="n" r="D314">
-        <v>-0.1503</v>
-      </c>
-      <c t="n" r="E314">
-        <v>2.2272</v>
-      </c>
-      <c t="n" r="F314">
-        <v>-0.1746</v>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="315">
       <c t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">REI</t>
+          <t xml:space="preserve">RNG</t>
         </is>
       </c>
       <c t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C315">
+        <v>-0.1545</v>
+      </c>
+      <c t="n" r="D315">
+        <v>-0.3508</v>
+      </c>
+      <c t="n" r="E315">
+        <v>3.0261</v>
+      </c>
+      <c t="n" r="F315">
+        <v>-0.3988</v>
       </c>
     </row>
     <row r="316">
       <c t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">RNG</t>
+          <t xml:space="preserve">ROR</t>
         </is>
       </c>
       <c t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C316">
-        <v>-0.1521</v>
-      </c>
-      <c t="n" r="D316">
-        <v>-0.3508</v>
-      </c>
-      <c t="n" r="E316">
-        <v>3.0271</v>
-      </c>
-      <c t="n" r="F316">
-        <v>-0.3965</v>
+        <v>-0.1321</v>
       </c>
     </row>
     <row r="317">
       <c t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">ROR</t>
+          <t xml:space="preserve">RGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C317">
-        <v>-0.1313</v>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="318">
       <c t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">RGU</t>
+          <t xml:space="preserve">RZB</t>
         </is>
       </c>
       <c t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ REGNUM PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. SEBA CENTER GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="E318">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="F318">
+        <v>0.0000</v>
       </c>
     </row>
     <row r="319">
       <c t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">RZB</t>
+          <t xml:space="preserve">SEB</t>
         </is>
       </c>
       <c t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. SEBA CENTER GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="E319">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="F319">
-        <v>0.0000</v>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. SEBA CENTER PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="320">
       <c t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">SEB</t>
+          <t xml:space="preserve">TCE</t>
         </is>
       </c>
       <c t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. SEBA CENTER PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">TACİRLER PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C320">
+        <v>-0.1090</v>
+      </c>
+      <c t="n" r="D320">
+        <v>-0.1090</v>
+      </c>
+      <c t="n" r="F320">
+        <v>-0.1183</v>
       </c>
     </row>
     <row r="321">
       <c t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">TCE</t>
+          <t xml:space="preserve">TN1</t>
         </is>
       </c>
       <c t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">TACİRLER PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C321">
-        <v>-0.1232</v>
-      </c>
-      <c t="n" r="D321">
-        <v>-0.1207</v>
-      </c>
-      <c t="n" r="F321">
-        <v>-0.1324</v>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
     </row>
     <row r="322">
       <c t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">TN1</t>
+          <t xml:space="preserve">TUC</t>
         </is>
       </c>
       <c t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">TUC</t>
+          <t xml:space="preserve">ZEP</t>
         </is>
       </c>
       <c t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. EMLAK KONUT GELİR PAYLAŞIMI BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C323">
+        <v>2.8273</v>
       </c>
     </row>
     <row r="324">
       <c t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">ZEP</t>
+          <t xml:space="preserve">YOR</t>
         </is>
       </c>
       <c t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. EMLAK KONUT GELİR PAYLAŞIMI BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ORKİDE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C324">
-        <v>2.7199</v>
-      </c>
-    </row>
-    <row r="325">
-      <c t="inlineStr" r="A325">
-        <is>
-          <t xml:space="preserve">YOR</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B325">
-        <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ORKİDE PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C325">
         <v>0.1274</v>
       </c>
-      <c t="n" r="D325">
+      <c t="n" r="D324">
         <v>0.0000</v>
       </c>
-      <c t="n" r="E325">
+      <c t="n" r="E324">
         <v>0.0000</v>
       </c>
-      <c t="n" r="F325">
+      <c t="n" r="F324">
         <v>0.0849</v>
       </c>
     </row>

--- a/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
@@ -280,22 +280,22 @@
         </is>
       </c>
       <c t="n" r="C3">
-        <v>21.7498</v>
+        <v>21.8477</v>
       </c>
       <c t="n" r="D3">
-        <v>668.6347</v>
+        <v>669.2501</v>
       </c>
       <c t="n" r="E3">
-        <v>695.4256</v>
+        <v>696.0894</v>
       </c>
       <c t="n" r="F3">
-        <v>663.1006</v>
+        <v>663.7140</v>
       </c>
       <c t="n" r="G3">
-        <v>620.6718</v>
+        <v>621.2344</v>
       </c>
       <c t="n" r="H3">
-        <v>773.0548</v>
+        <v>773.7566</v>
       </c>
     </row>
     <row r="4">
@@ -310,19 +310,19 @@
         </is>
       </c>
       <c t="n" r="C4">
-        <v>16.2385</v>
+        <v>16.2683</v>
       </c>
       <c t="n" r="D4">
-        <v>20.4563</v>
+        <v>20.4483</v>
       </c>
       <c t="n" r="E4">
-        <v>248.8586</v>
+        <v>248.4914</v>
       </c>
       <c t="n" r="F4">
-        <v>21.2164</v>
+        <v>21.2474</v>
       </c>
       <c t="n" r="G4">
-        <v>373.1043</v>
+        <v>372.1803</v>
       </c>
     </row>
     <row r="5">
@@ -337,19 +337,19 @@
         </is>
       </c>
       <c t="n" r="C5">
-        <v>0.9267</v>
+        <v>0.9364</v>
       </c>
       <c t="n" r="D5">
-        <v>2.6564</v>
+        <v>2.6591</v>
       </c>
       <c t="n" r="E5">
-        <v>27.7535</v>
+        <v>27.7596</v>
       </c>
       <c t="n" r="F5">
-        <v>3.4273</v>
+        <v>3.4373</v>
       </c>
       <c t="n" r="G5">
-        <v>361.1561</v>
+        <v>359.3357</v>
       </c>
     </row>
     <row r="6">
@@ -364,22 +364,22 @@
         </is>
       </c>
       <c t="n" r="C6">
-        <v>-0.4119</v>
+        <v>-0.3811</v>
       </c>
       <c t="n" r="D6">
-        <v>36.6221</v>
+        <v>36.6681</v>
       </c>
       <c t="n" r="E6">
-        <v>52.7806</v>
+        <v>52.8358</v>
       </c>
       <c t="n" r="F6">
-        <v>42.2634</v>
+        <v>42.3073</v>
       </c>
       <c t="n" r="G6">
-        <v>240.0926</v>
+        <v>240.2122</v>
       </c>
       <c t="n" r="H6">
-        <v>332.7889</v>
+        <v>332.9227</v>
       </c>
     </row>
     <row r="7">
@@ -394,22 +394,22 @@
         </is>
       </c>
       <c t="n" r="C7">
-        <v>-0.0182</v>
+        <v>-0.0185</v>
       </c>
       <c t="n" r="D7">
         <v>-0.0487</v>
       </c>
       <c t="n" r="E7">
-        <v>192.5068</v>
+        <v>192.5069</v>
       </c>
       <c t="n" r="F7">
-        <v>-0.0603</v>
+        <v>-0.0607</v>
       </c>
       <c t="n" r="G7">
-        <v>191.4485</v>
+        <v>191.4487</v>
       </c>
       <c t="n" r="H7">
-        <v>167657.3709</v>
+        <v>167656.7578</v>
       </c>
     </row>
     <row r="8">
@@ -424,19 +424,19 @@
         </is>
       </c>
       <c t="n" r="C8">
-        <v>-0.0096</v>
+        <v>-0.0089</v>
       </c>
       <c t="n" r="D8">
-        <v>4.0097</v>
+        <v>4.0094</v>
       </c>
       <c t="n" r="E8">
-        <v>3.9661</v>
+        <v>3.9662</v>
       </c>
       <c t="n" r="F8">
-        <v>4.0238</v>
+        <v>4.0244</v>
       </c>
       <c t="n" r="G8">
-        <v>152.8126</v>
+        <v>152.9178</v>
       </c>
     </row>
     <row r="9">
@@ -451,19 +451,19 @@
         </is>
       </c>
       <c t="n" r="C9">
-        <v>0.7420</v>
+        <v>0.7435</v>
       </c>
       <c t="n" r="D9">
-        <v>1.0458</v>
+        <v>1.0502</v>
       </c>
       <c t="n" r="E9">
-        <v>137.9872</v>
+        <v>137.9567</v>
       </c>
       <c t="n" r="F9">
-        <v>1.5317</v>
+        <v>1.5332</v>
       </c>
       <c t="n" r="G9">
-        <v>143.2172</v>
+        <v>142.9521</v>
       </c>
     </row>
     <row r="10">
@@ -478,22 +478,22 @@
         </is>
       </c>
       <c t="n" r="C10">
-        <v>65.6944</v>
+        <v>65.7009</v>
       </c>
       <c t="n" r="D10">
-        <v>68.1007</v>
+        <v>68.0954</v>
       </c>
       <c t="n" r="E10">
-        <v>69.7947</v>
+        <v>69.7978</v>
       </c>
       <c t="n" r="F10">
-        <v>55.1612</v>
+        <v>55.1673</v>
       </c>
       <c t="n" r="G10">
-        <v>89.8795</v>
+        <v>89.8288</v>
       </c>
       <c t="n" r="H10">
-        <v>114.9666</v>
+        <v>114.9751</v>
       </c>
     </row>
     <row r="11">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c t="n" r="C11">
-        <v>1.7292</v>
+        <v>1.7369</v>
       </c>
       <c t="n" r="D11">
-        <v>2.2249</v>
+        <v>2.2248</v>
       </c>
       <c t="n" r="E11">
-        <v>76.8535</v>
+        <v>76.8614</v>
       </c>
       <c t="n" r="F11">
-        <v>33.8454</v>
+        <v>33.8555</v>
       </c>
       <c t="n" r="G11">
-        <v>82.8329</v>
+        <v>82.8408</v>
       </c>
       <c t="n" r="H11">
-        <v>299.2993</v>
+        <v>299.3294</v>
       </c>
       <c t="n" r="I11">
-        <v>1679.7710</v>
+        <v>1679.7970</v>
       </c>
     </row>
     <row r="12">
@@ -541,22 +541,22 @@
         </is>
       </c>
       <c t="n" r="C12">
-        <v>-0.1916</v>
+        <v>-0.1937</v>
       </c>
       <c t="n" r="D12">
-        <v>-0.3550</v>
+        <v>-0.3554</v>
       </c>
       <c t="n" r="E12">
-        <v>19.9025</v>
+        <v>19.8906</v>
       </c>
       <c t="n" r="F12">
-        <v>-1.0515</v>
+        <v>-1.0536</v>
       </c>
       <c t="n" r="G12">
-        <v>61.5802</v>
+        <v>61.3409</v>
       </c>
       <c t="n" r="H12">
-        <v>695.6510</v>
+        <v>695.6341</v>
       </c>
     </row>
     <row r="13">
@@ -571,25 +571,25 @@
         </is>
       </c>
       <c t="n" r="C13">
-        <v>0.2566</v>
+        <v>0.2767</v>
       </c>
       <c t="n" r="D13">
-        <v>1.4263</v>
+        <v>1.4152</v>
       </c>
       <c t="n" r="E13">
-        <v>38.2906</v>
+        <v>38.2021</v>
       </c>
       <c t="n" r="F13">
-        <v>1.4108</v>
+        <v>1.4311</v>
       </c>
       <c t="n" r="G13">
-        <v>61.4477</v>
+        <v>61.0194</v>
       </c>
       <c t="n" r="H13">
-        <v>328.1439</v>
+        <v>328.2295</v>
       </c>
       <c t="n" r="I13">
-        <v>1094.9855</v>
+        <v>1095.2244</v>
       </c>
     </row>
     <row r="14">
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c t="n" r="C14">
-        <v>3.7154</v>
+        <v>3.8277</v>
       </c>
       <c t="n" r="D14">
-        <v>10.3315</v>
+        <v>10.3367</v>
       </c>
       <c t="n" r="E14">
-        <v>27.7986</v>
+        <v>27.7977</v>
       </c>
       <c t="n" r="F14">
-        <v>11.9141</v>
+        <v>12.0352</v>
       </c>
       <c t="n" r="G14">
-        <v>58.9848</v>
+        <v>58.6333</v>
       </c>
     </row>
     <row r="15">
@@ -631,73 +631,73 @@
         </is>
       </c>
       <c t="n" r="C15">
-        <v>-0.1145</v>
+        <v>-0.1171</v>
       </c>
       <c t="n" r="D15">
-        <v>0.2722</v>
+        <v>0.2724</v>
       </c>
       <c t="n" r="E15">
-        <v>60.0161</v>
+        <v>60.0160</v>
       </c>
       <c t="n" r="F15">
-        <v>-4.4675</v>
+        <v>-4.4700</v>
       </c>
       <c t="n" r="G15">
-        <v>58.6139</v>
+        <v>58.6119</v>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">BRE</t>
+          <t xml:space="preserve">NG8</t>
         </is>
       </c>
       <c t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C16">
-        <v>7.8470</v>
+        <v>3.4876</v>
       </c>
       <c t="n" r="D16">
-        <v>24.6782</v>
+        <v>8.9261</v>
       </c>
       <c t="n" r="E16">
-        <v>32.2012</v>
+        <v>26.3973</v>
       </c>
       <c t="n" r="F16">
-        <v>33.3102</v>
+        <v>18.7210</v>
       </c>
       <c t="n" r="G16">
-        <v>58.3780</v>
+        <v>57.2351</v>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">NG8</t>
+          <t xml:space="preserve">BRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DOKUZUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C17">
-        <v>3.3845</v>
+        <v>7.9052</v>
       </c>
       <c t="n" r="D17">
-        <v>10.1592</v>
+        <v>24.6928</v>
       </c>
       <c t="n" r="E17">
-        <v>26.4050</v>
+        <v>32.3636</v>
       </c>
       <c t="n" r="F17">
-        <v>18.6028</v>
+        <v>33.3821</v>
       </c>
       <c t="n" r="G17">
-        <v>57.6776</v>
+        <v>57.1862</v>
       </c>
     </row>
     <row r="18">
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c t="n" r="C18">
-        <v>0.7476</v>
+        <v>0.7534</v>
       </c>
       <c t="n" r="D18">
-        <v>1.9962</v>
+        <v>1.9985</v>
       </c>
       <c t="n" r="E18">
-        <v>50.4560</v>
+        <v>50.4590</v>
       </c>
       <c t="n" r="F18">
-        <v>48.3057</v>
+        <v>48.3142</v>
       </c>
       <c t="n" r="G18">
-        <v>56.2365</v>
+        <v>56.2349</v>
       </c>
       <c t="n" r="H18">
-        <v>462.5771</v>
+        <v>462.6094</v>
       </c>
     </row>
     <row r="19">
@@ -742,19 +742,19 @@
         </is>
       </c>
       <c t="n" r="C19">
-        <v>3.8224</v>
+        <v>3.9330</v>
       </c>
       <c t="n" r="D19">
-        <v>10.5150</v>
+        <v>10.5147</v>
       </c>
       <c t="n" r="E19">
-        <v>22.2773</v>
+        <v>22.2695</v>
       </c>
       <c t="n" r="F19">
-        <v>12.7274</v>
+        <v>12.8475</v>
       </c>
       <c t="n" r="G19">
-        <v>56.1845</v>
+        <v>55.6090</v>
       </c>
     </row>
     <row r="20">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c t="n" r="C20">
-        <v>3.8221</v>
+        <v>3.9327</v>
       </c>
       <c t="n" r="D20">
-        <v>10.5141</v>
+        <v>10.5138</v>
       </c>
       <c t="n" r="E20">
-        <v>22.2748</v>
+        <v>22.2671</v>
       </c>
       <c t="n" r="F20">
-        <v>12.7261</v>
+        <v>12.8462</v>
       </c>
       <c t="n" r="G20">
-        <v>56.1767</v>
+        <v>55.6013</v>
       </c>
     </row>
     <row r="21">
@@ -796,22 +796,22 @@
         </is>
       </c>
       <c t="n" r="C21">
-        <v>0.3739</v>
+        <v>0.3771</v>
       </c>
       <c t="n" r="D21">
-        <v>0.9047</v>
+        <v>0.9027</v>
       </c>
       <c t="n" r="E21">
-        <v>1.4417</v>
+        <v>1.4451</v>
       </c>
       <c t="n" r="F21">
-        <v>0.9881</v>
+        <v>0.9913</v>
       </c>
       <c t="n" r="G21">
-        <v>55.3734</v>
+        <v>55.3459</v>
       </c>
       <c t="n" r="H21">
-        <v>410.7683</v>
+        <v>410.7846</v>
       </c>
     </row>
     <row r="22">
@@ -826,22 +826,22 @@
         </is>
       </c>
       <c t="n" r="C22">
-        <v>-0.2025</v>
+        <v>-0.2024</v>
       </c>
       <c t="n" r="D22">
         <v>-0.2154</v>
       </c>
       <c t="n" r="E22">
-        <v>55.3897</v>
+        <v>55.3895</v>
       </c>
       <c t="n" r="F22">
-        <v>-0.2322</v>
+        <v>-0.2321</v>
       </c>
       <c t="n" r="G22">
-        <v>54.4087</v>
+        <v>54.4074</v>
       </c>
       <c t="n" r="H22">
-        <v>172.5012</v>
+        <v>172.5014</v>
       </c>
     </row>
     <row r="23">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c t="n" r="C23">
-        <v>0.0307</v>
+        <v>0.0463</v>
       </c>
       <c t="n" r="D23">
-        <v>6.3910</v>
+        <v>6.3825</v>
       </c>
       <c t="n" r="E23">
-        <v>19.3793</v>
+        <v>19.3452</v>
       </c>
       <c t="n" r="F23">
-        <v>6.8982</v>
+        <v>6.9149</v>
       </c>
       <c t="n" r="G23">
-        <v>54.0494</v>
+        <v>53.9847</v>
       </c>
     </row>
     <row r="24">
@@ -883,139 +883,139 @@
         </is>
       </c>
       <c t="n" r="C24">
-        <v>4.5689</v>
+        <v>4.1375</v>
       </c>
       <c t="n" r="D24">
-        <v>7.2146</v>
+        <v>5.5836</v>
       </c>
       <c t="n" r="E24">
-        <v>23.0130</v>
+        <v>22.3757</v>
       </c>
       <c t="n" r="F24">
-        <v>15.2533</v>
+        <v>14.7778</v>
       </c>
       <c t="n" r="G24">
-        <v>53.6077</v>
+        <v>52.3925</v>
       </c>
     </row>
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">IGJ</t>
+          <t xml:space="preserve">YD7</t>
         </is>
       </c>
       <c t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.KARDELEN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C25">
-        <v>0.0453</v>
+        <v>0.9279</v>
       </c>
       <c t="n" r="D25">
-        <v>0.0554</v>
+        <v>-0.2735</v>
       </c>
       <c t="n" r="E25">
-        <v>36.1353</v>
+        <v>29.9946</v>
       </c>
       <c t="n" r="F25">
-        <v>0.2788</v>
+        <v>-0.5892</v>
       </c>
       <c t="n" r="G25">
-        <v>51.1397</v>
+        <v>50.8447</v>
+      </c>
+      <c t="n" r="H25">
+        <v>171.4041</v>
+      </c>
+      <c t="n" r="I25">
+        <v>1157.7130</v>
       </c>
     </row>
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">YD7</t>
+          <t xml:space="preserve">IGJ</t>
         </is>
       </c>
       <c t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.KARDELEN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C26">
-        <v>0.9345</v>
+        <v>0.0480</v>
       </c>
       <c t="n" r="D26">
-        <v>-0.2744</v>
+        <v>0.0469</v>
       </c>
       <c t="n" r="E26">
-        <v>29.9954</v>
+        <v>36.1141</v>
       </c>
       <c t="n" r="F26">
-        <v>-0.5826</v>
+        <v>0.2815</v>
       </c>
       <c t="n" r="G26">
-        <v>50.8345</v>
-      </c>
-      <c t="n" r="H26">
-        <v>171.4219</v>
-      </c>
-      <c t="n" r="I26">
-        <v>1157.7954</v>
+        <v>50.5293</v>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">RAA</t>
+          <t xml:space="preserve">YD5</t>
         </is>
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. AVRUPA-ANADOLU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C27">
-        <v>4.9385</v>
+        <v>-0.0554</v>
       </c>
       <c t="n" r="D27">
-        <v>11.8391</v>
+        <v>-0.2090</v>
       </c>
       <c t="n" r="E27">
-        <v>20.9565</v>
+        <v>16.2954</v>
       </c>
       <c t="n" r="F27">
-        <v>13.6622</v>
+        <v>-0.4274</v>
       </c>
       <c t="n" r="G27">
-        <v>48.1470</v>
+        <v>48.4834</v>
+      </c>
+      <c t="n" r="H27">
+        <v>197.6721</v>
+      </c>
+      <c t="n" r="I27">
+        <v>1325.2140</v>
       </c>
     </row>
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">YD5</t>
+          <t xml:space="preserve">RAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. AVRUPA-ANADOLU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C28">
-        <v>-0.2878</v>
+        <v>4.9830</v>
       </c>
       <c t="n" r="D28">
-        <v>-0.4484</v>
+        <v>11.7877</v>
       </c>
       <c t="n" r="E28">
-        <v>16.0200</v>
+        <v>20.9032</v>
       </c>
       <c t="n" r="F28">
-        <v>-0.6590</v>
+        <v>13.7104</v>
       </c>
       <c t="n" r="G28">
-        <v>48.1160</v>
-      </c>
-      <c t="n" r="H28">
-        <v>196.9798</v>
-      </c>
-      <c t="n" r="I28">
-        <v>1321.8995</v>
+        <v>47.6495</v>
       </c>
     </row>
     <row r="29">
@@ -1030,22 +1030,22 @@
         </is>
       </c>
       <c t="n" r="C29">
-        <v>0.4208</v>
+        <v>0.4377</v>
       </c>
       <c t="n" r="D29">
-        <v>6.3395</v>
+        <v>6.3680</v>
       </c>
       <c t="n" r="E29">
-        <v>43.6925</v>
+        <v>43.6910</v>
       </c>
       <c t="n" r="F29">
-        <v>5.9928</v>
+        <v>6.0107</v>
       </c>
       <c t="n" r="G29">
-        <v>45.4769</v>
+        <v>45.4754</v>
       </c>
       <c t="n" r="H29">
-        <v>465.0755</v>
+        <v>465.1706</v>
       </c>
     </row>
     <row r="30">
@@ -1060,19 +1060,19 @@
         </is>
       </c>
       <c t="n" r="C30">
-        <v>3.3578</v>
+        <v>3.4647</v>
       </c>
       <c t="n" r="D30">
-        <v>8.9841</v>
+        <v>8.9959</v>
       </c>
       <c t="n" r="E30">
-        <v>19.2774</v>
+        <v>19.2787</v>
       </c>
       <c t="n" r="F30">
-        <v>11.1039</v>
+        <v>11.2189</v>
       </c>
       <c t="n" r="G30">
-        <v>44.5270</v>
+        <v>44.4887</v>
       </c>
     </row>
     <row r="31">
@@ -1087,19 +1087,19 @@
         </is>
       </c>
       <c t="n" r="C31">
-        <v>0.2415</v>
+        <v>0.2586</v>
       </c>
       <c t="n" r="D31">
-        <v>-0.4488</v>
+        <v>-0.4460</v>
       </c>
       <c t="n" r="E31">
-        <v>29.4152</v>
+        <v>29.4183</v>
       </c>
       <c t="n" r="F31">
-        <v>1.6954</v>
+        <v>1.7127</v>
       </c>
       <c t="n" r="G31">
-        <v>44.2666</v>
+        <v>44.2654</v>
       </c>
     </row>
     <row r="32">
@@ -1114,46 +1114,46 @@
         </is>
       </c>
       <c t="n" r="C32">
-        <v>2.6391</v>
+        <v>2.3298</v>
       </c>
       <c t="n" r="D32">
-        <v>3.6843</v>
+        <v>3.3552</v>
       </c>
       <c t="n" r="E32">
-        <v>25.1787</v>
+        <v>24.5088</v>
       </c>
       <c t="n" r="F32">
-        <v>9.2652</v>
+        <v>8.9360</v>
       </c>
       <c t="n" r="G32">
-        <v>43.8600</v>
+        <v>43.2903</v>
       </c>
     </row>
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">ORV</t>
+          <t xml:space="preserve">FNR</t>
         </is>
       </c>
       <c t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AVRASYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C33">
-        <v>-0.2453</v>
+        <v>2.6120</v>
       </c>
       <c t="n" r="D33">
-        <v>-0.4075</v>
+        <v>-0.3568</v>
       </c>
       <c t="n" r="E33">
-        <v>27.3337</v>
+        <v>16.3303</v>
       </c>
       <c t="n" r="F33">
-        <v>0.1070</v>
+        <v>5.6978</v>
       </c>
       <c t="n" r="G33">
-        <v>41.6860</v>
+        <v>42.9038</v>
       </c>
     </row>
     <row r="34">
@@ -1168,25 +1168,25 @@
         </is>
       </c>
       <c t="n" r="C34">
-        <v>-0.0775</v>
+        <v>-0.0784</v>
       </c>
       <c t="n" r="D34">
         <v>-0.3341</v>
       </c>
       <c t="n" r="E34">
-        <v>42.2728</v>
+        <v>42.2724</v>
       </c>
       <c t="n" r="F34">
-        <v>-0.5040</v>
+        <v>-0.5049</v>
       </c>
       <c t="n" r="G34">
         <v>41.6786</v>
       </c>
       <c t="n" r="H34">
-        <v>213.3103</v>
+        <v>213.3075</v>
       </c>
       <c t="n" r="I34">
-        <v>720.5567</v>
+        <v>718.2115</v>
       </c>
     </row>
     <row r="35">
@@ -1201,115 +1201,115 @@
         </is>
       </c>
       <c t="n" r="C35">
-        <v>0.1750</v>
+        <v>0.1747</v>
       </c>
       <c t="n" r="D35">
-        <v>0.5302</v>
+        <v>0.5318</v>
       </c>
       <c t="n" r="E35">
-        <v>38.6392</v>
+        <v>38.6427</v>
       </c>
       <c t="n" r="F35">
-        <v>0.7159</v>
+        <v>0.7156</v>
       </c>
       <c t="n" r="G35">
-        <v>41.6775</v>
+        <v>41.6747</v>
       </c>
       <c t="n" r="H35">
-        <v>241.9868</v>
+        <v>241.9860</v>
       </c>
       <c t="n" r="I35">
-        <v>847.8751</v>
+        <v>847.8730</v>
       </c>
     </row>
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">KGG</t>
+          <t xml:space="preserve">ORV</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AVRASYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C36">
-        <v>0.1618</v>
+        <v>-0.2471</v>
       </c>
       <c t="n" r="D36">
-        <v>0.0102</v>
+        <v>-0.5126</v>
       </c>
       <c t="n" r="E36">
-        <v>41.1551</v>
+        <v>27.2935</v>
       </c>
       <c t="n" r="F36">
-        <v>0.2546</v>
+        <v>0.1053</v>
       </c>
       <c t="n" r="G36">
-        <v>41.4399</v>
-      </c>
-      <c t="n" r="H36">
-        <v>251.9588</v>
+        <v>41.6709</v>
       </c>
     </row>
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">MPG</t>
+          <t xml:space="preserve">KGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM (TL) FONU</t>
+          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C37">
-        <v>0.5314</v>
+        <v>0.1558</v>
       </c>
       <c t="n" r="D37">
-        <v>1.5345</v>
+        <v>0.0095</v>
       </c>
       <c t="n" r="E37">
-        <v>28.9881</v>
+        <v>41.1567</v>
       </c>
       <c t="n" r="F37">
-        <v>1.5666</v>
+        <v>0.2485</v>
       </c>
       <c t="n" r="G37">
-        <v>40.7560</v>
+        <v>41.4373</v>
       </c>
       <c t="n" r="H37">
-        <v>172.3896</v>
-      </c>
-      <c t="n" r="I37">
-        <v>400.7189</v>
+        <v>251.9377</v>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">FNR</t>
+          <t xml:space="preserve">MPG</t>
         </is>
       </c>
       <c t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM (TL) FONU</t>
         </is>
       </c>
       <c t="n" r="C38">
-        <v>1.1261</v>
+        <v>0.5443</v>
       </c>
       <c t="n" r="D38">
-        <v>-3.0780</v>
+        <v>1.5363</v>
       </c>
       <c t="n" r="E38">
-        <v>16.0658</v>
+        <v>28.9879</v>
       </c>
       <c t="n" r="F38">
-        <v>4.1671</v>
+        <v>1.5796</v>
       </c>
       <c t="n" r="G38">
-        <v>40.5243</v>
+        <v>40.7192</v>
+      </c>
+      <c t="n" r="H38">
+        <v>172.4245</v>
+      </c>
+      <c t="n" r="I38">
+        <v>400.7830</v>
       </c>
     </row>
     <row r="39">
@@ -1324,148 +1324,148 @@
         </is>
       </c>
       <c t="n" r="C39">
-        <v>0.4681</v>
+        <v>0.4771</v>
       </c>
       <c t="n" r="D39">
-        <v>1.6215</v>
+        <v>1.6243</v>
       </c>
       <c t="n" r="E39">
-        <v>16.1824</v>
+        <v>16.1871</v>
       </c>
       <c t="n" r="F39">
-        <v>2.0794</v>
+        <v>2.0885</v>
       </c>
       <c t="n" r="G39">
-        <v>40.2601</v>
+        <v>40.2376</v>
       </c>
       <c t="n" r="H39">
-        <v>295.3129</v>
+        <v>295.3483</v>
       </c>
       <c t="n" r="I39">
-        <v>916.1386</v>
+        <v>916.1052</v>
       </c>
     </row>
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">IIY</t>
+          <t xml:space="preserve">RG4</t>
         </is>
       </c>
       <c t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ  GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C40">
-        <v>1.0662</v>
+        <v>0.8369</v>
       </c>
       <c t="n" r="D40">
-        <v>4.4127</v>
+        <v>5.5404</v>
       </c>
       <c t="n" r="E40">
-        <v>14.4081</v>
+        <v>34.9349</v>
       </c>
       <c t="n" r="F40">
-        <v>3.5954</v>
+        <v>13.3525</v>
       </c>
       <c t="n" r="G40">
-        <v>40.0308</v>
+        <v>39.1814</v>
       </c>
       <c t="n" r="H40">
-        <v>141.2385</v>
-      </c>
-      <c t="n" r="I40">
-        <v>260.7794</v>
+        <v>840.9113</v>
       </c>
     </row>
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">RG4</t>
+          <t xml:space="preserve">RGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. GÖKSU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C41">
-        <v>0.8373</v>
+        <v>0.6998</v>
       </c>
       <c t="n" r="D41">
-        <v>5.5339</v>
+        <v>2.1079</v>
       </c>
       <c t="n" r="E41">
-        <v>34.9036</v>
+        <v>30.8572</v>
       </c>
       <c t="n" r="F41">
-        <v>13.3530</v>
+        <v>2.6852</v>
       </c>
       <c t="n" r="G41">
-        <v>39.1756</v>
-      </c>
-      <c t="n" r="H41">
-        <v>840.9152</v>
+        <v>38.5009</v>
       </c>
     </row>
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">RGO</t>
+          <t xml:space="preserve">YD2</t>
         </is>
       </c>
       <c t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. GÖKSU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALZAMİL KİRA GETİRİLİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C42">
-        <v>0.7083</v>
+        <v>0.1810</v>
       </c>
       <c t="n" r="D42">
-        <v>2.1166</v>
+        <v>-0.9320</v>
       </c>
       <c t="n" r="E42">
-        <v>30.9239</v>
+        <v>26.0496</v>
       </c>
       <c t="n" r="F42">
-        <v>2.6938</v>
+        <v>-0.5614</v>
       </c>
       <c t="n" r="G42">
-        <v>38.6231</v>
+        <v>38.3873</v>
+      </c>
+      <c t="n" r="H42">
+        <v>326.7824</v>
+      </c>
+      <c t="n" r="I42">
+        <v>712.9093</v>
       </c>
     </row>
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">YD2</t>
+          <t xml:space="preserve">IIY</t>
         </is>
       </c>
       <c t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALZAMİL KİRA GETİRİLİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ  GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C43">
-        <v>0.1870</v>
+        <v>1.1364</v>
       </c>
       <c t="n" r="D43">
-        <v>-0.9312</v>
+        <v>4.4477</v>
       </c>
       <c t="n" r="E43">
-        <v>26.0495</v>
+        <v>14.4412</v>
       </c>
       <c t="n" r="F43">
-        <v>-0.5554</v>
+        <v>3.6673</v>
       </c>
       <c t="n" r="G43">
-        <v>38.3884</v>
+        <v>37.8756</v>
       </c>
       <c t="n" r="H43">
-        <v>326.8080</v>
+        <v>141.4059</v>
       </c>
       <c t="n" r="I43">
-        <v>712.9582</v>
+        <v>261.0203</v>
       </c>
     </row>
     <row r="44">
@@ -1480,25 +1480,25 @@
         </is>
       </c>
       <c t="n" r="C44">
-        <v>1.3722</v>
+        <v>1.4182</v>
       </c>
       <c t="n" r="D44">
-        <v>4.1810</v>
+        <v>4.1815</v>
       </c>
       <c t="n" r="E44">
-        <v>13.8970</v>
+        <v>13.8933</v>
       </c>
       <c t="n" r="F44">
-        <v>5.0869</v>
+        <v>5.1346</v>
       </c>
       <c t="n" r="G44">
-        <v>37.5203</v>
+        <v>37.4932</v>
       </c>
       <c t="n" r="H44">
-        <v>179.8312</v>
+        <v>179.9580</v>
       </c>
       <c t="n" r="I44">
-        <v>415.9149</v>
+        <v>415.9704</v>
       </c>
     </row>
     <row r="45">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c t="n" r="C45">
-        <v>1.5845</v>
+        <v>1.7752</v>
       </c>
       <c t="n" r="D45">
-        <v>5.1549</v>
+        <v>5.2929</v>
       </c>
       <c t="n" r="E45">
-        <v>21.4665</v>
+        <v>21.4233</v>
       </c>
       <c t="n" r="F45">
-        <v>5.7530</v>
+        <v>5.9516</v>
       </c>
       <c t="n" r="G45">
-        <v>36.2064</v>
+        <v>36.3903</v>
       </c>
     </row>
     <row r="46">
@@ -1540,19 +1540,19 @@
         </is>
       </c>
       <c t="n" r="C46">
-        <v>2.8389</v>
+        <v>2.9298</v>
       </c>
       <c t="n" r="D46">
-        <v>7.0887</v>
+        <v>7.0980</v>
       </c>
       <c t="n" r="E46">
-        <v>15.3438</v>
+        <v>15.3648</v>
       </c>
       <c t="n" r="F46">
-        <v>8.8358</v>
+        <v>8.9320</v>
       </c>
       <c t="n" r="G46">
-        <v>35.7064</v>
+        <v>35.6892</v>
       </c>
     </row>
     <row r="47">
@@ -1567,25 +1567,25 @@
         </is>
       </c>
       <c t="n" r="C47">
-        <v>0.7284</v>
+        <v>0.7277</v>
       </c>
       <c t="n" r="D47">
-        <v>-0.4214</v>
+        <v>-0.4213</v>
       </c>
       <c t="n" r="E47">
-        <v>32.6756</v>
+        <v>32.6757</v>
       </c>
       <c t="n" r="F47">
-        <v>-0.4775</v>
+        <v>-0.4781</v>
       </c>
       <c t="n" r="G47">
-        <v>35.5659</v>
+        <v>35.5660</v>
       </c>
       <c t="n" r="H47">
-        <v>244.3034</v>
+        <v>244.3013</v>
       </c>
       <c t="n" r="I47">
-        <v>921.6512</v>
+        <v>921.6480</v>
       </c>
     </row>
     <row r="48">
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c t="n" r="C48">
-        <v>0.5979</v>
+        <v>0.6300</v>
       </c>
       <c t="n" r="D48">
-        <v>1.8390</v>
+        <v>1.8050</v>
       </c>
       <c t="n" r="E48">
-        <v>26.6041</v>
+        <v>26.7380</v>
       </c>
       <c t="n" r="F48">
-        <v>2.3295</v>
+        <v>2.3621</v>
       </c>
       <c t="n" r="G48">
-        <v>34.9502</v>
+        <v>34.9270</v>
       </c>
       <c t="n" r="H48">
-        <v>576.5823</v>
+        <v>576.7979</v>
       </c>
     </row>
     <row r="49">
@@ -1630,19 +1630,19 @@
         </is>
       </c>
       <c t="n" r="C49">
-        <v>-0.0211</v>
+        <v>-0.0216</v>
       </c>
       <c t="n" r="D49">
-        <v>-0.1092</v>
+        <v>-0.1094</v>
       </c>
       <c t="n" r="E49">
-        <v>34.0399</v>
+        <v>34.0392</v>
       </c>
       <c t="n" r="F49">
-        <v>-0.1169</v>
+        <v>-0.1175</v>
       </c>
       <c t="n" r="G49">
-        <v>34.5370</v>
+        <v>34.5341</v>
       </c>
     </row>
     <row r="50">
@@ -1657,19 +1657,19 @@
         </is>
       </c>
       <c t="n" r="C50">
-        <v>0.9908</v>
+        <v>1.0300</v>
       </c>
       <c t="n" r="D50">
-        <v>3.8633</v>
+        <v>3.8694</v>
       </c>
       <c t="n" r="E50">
-        <v>13.0458</v>
+        <v>13.1326</v>
       </c>
       <c t="n" r="F50">
-        <v>4.0844</v>
+        <v>4.1249</v>
       </c>
       <c t="n" r="G50">
-        <v>33.7588</v>
+        <v>33.7705</v>
       </c>
     </row>
     <row r="51">
@@ -1684,19 +1684,19 @@
         </is>
       </c>
       <c t="n" r="C51">
-        <v>1.7605</v>
+        <v>1.5983</v>
       </c>
       <c t="n" r="D51">
-        <v>2.8806</v>
+        <v>2.5965</v>
       </c>
       <c t="n" r="E51">
-        <v>11.0184</v>
+        <v>10.7856</v>
       </c>
       <c t="n" r="F51">
-        <v>4.0502</v>
+        <v>3.8844</v>
       </c>
       <c t="n" r="G51">
-        <v>33.4447</v>
+        <v>33.0300</v>
       </c>
     </row>
     <row r="52">
@@ -1711,232 +1711,235 @@
         </is>
       </c>
       <c t="n" r="C52">
-        <v>0.2719</v>
+        <v>0.2705</v>
       </c>
       <c t="n" r="D52">
-        <v>0.7721</v>
+        <v>0.7726</v>
       </c>
       <c t="n" r="E52">
-        <v>31.5265</v>
+        <v>31.5275</v>
       </c>
       <c t="n" r="F52">
-        <v>1.0989</v>
+        <v>1.0976</v>
       </c>
       <c t="n" r="G52">
-        <v>33.0283</v>
+        <v>33.0286</v>
       </c>
       <c t="n" r="H52">
-        <v>316.3872</v>
+        <v>316.3817</v>
       </c>
     </row>
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">YG1</t>
+          <t xml:space="preserve">AZ3</t>
         </is>
       </c>
       <c t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LOTUS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C53">
-        <v>0.0925</v>
+        <v>-0.0040</v>
       </c>
       <c t="n" r="D53">
-        <v>0.0691</v>
+        <v>-0.1790</v>
       </c>
       <c t="n" r="E53">
-        <v>10.3601</v>
+        <v>32.8971</v>
       </c>
       <c t="n" r="F53">
-        <v>0.0419</v>
+        <v>-2.9898</v>
       </c>
       <c t="n" r="G53">
-        <v>32.1875</v>
+        <v>31.7576</v>
       </c>
       <c t="n" r="H53">
-        <v>302.3311</v>
+        <v>214.9481</v>
+      </c>
+      <c t="n" r="I53">
+        <v>684.4187</v>
       </c>
     </row>
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">AZ3</t>
+          <t xml:space="preserve">UCG</t>
         </is>
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C54">
-        <v>-0.0086</v>
+        <v>0.2211</v>
       </c>
       <c t="n" r="D54">
-        <v>-0.1864</v>
+        <v>-0.5353</v>
       </c>
       <c t="n" r="E54">
-        <v>32.8872</v>
+        <v>31.2861</v>
       </c>
       <c t="n" r="F54">
-        <v>-2.9943</v>
+        <v>0.0854</v>
       </c>
       <c t="n" r="G54">
-        <v>31.7481</v>
+        <v>31.5455</v>
       </c>
       <c t="n" r="H54">
-        <v>214.9335</v>
+        <v>683.7593</v>
       </c>
       <c t="n" r="I54">
-        <v>684.3822</v>
+        <v>1727.6635</v>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">UCG</t>
+          <t xml:space="preserve">FNI</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C55">
-        <v>0.2199</v>
+        <v>-1.3422</v>
       </c>
       <c t="n" r="D55">
-        <v>-0.5501</v>
+        <v>-0.3422</v>
       </c>
       <c t="n" r="E55">
-        <v>31.3017</v>
+        <v>26.0640</v>
       </c>
       <c t="n" r="F55">
-        <v>0.0842</v>
+        <v>-0.3759</v>
       </c>
       <c t="n" r="G55">
-        <v>31.5415</v>
-      </c>
-      <c t="n" r="H55">
-        <v>683.7499</v>
-      </c>
-      <c t="n" r="I55">
-        <v>1727.6559</v>
+        <v>31.3799</v>
       </c>
     </row>
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">FNI</t>
+          <t xml:space="preserve">GF1</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C56">
-        <v>-1.3414</v>
+        <v>0.0103</v>
       </c>
       <c t="n" r="D56">
-        <v>-0.3418</v>
+        <v>0.0454</v>
       </c>
       <c t="n" r="E56">
-        <v>26.0699</v>
+        <v>28.9032</v>
       </c>
       <c t="n" r="F56">
-        <v>-0.3751</v>
+        <v>0.2707</v>
       </c>
       <c t="n" r="G56">
-        <v>31.3828</v>
+        <v>31.2018</v>
       </c>
     </row>
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">GF1</t>
+          <t xml:space="preserve">ITG</t>
         </is>
       </c>
       <c t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. QUASAR İSTANBUL TİCARİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C57">
-        <v>0.0118</v>
+        <v>0.3308</v>
       </c>
       <c t="n" r="D57">
-        <v>0.0456</v>
+        <v>1.2026</v>
       </c>
       <c t="n" r="E57">
-        <v>28.9094</v>
+        <v>13.1220</v>
       </c>
       <c t="n" r="F57">
-        <v>0.2722</v>
+        <v>1.4643</v>
       </c>
       <c t="n" r="G57">
-        <v>31.2089</v>
+        <v>30.9793</v>
+      </c>
+      <c t="n" r="H57">
+        <v>156.8055</v>
+      </c>
+      <c t="n" r="I57">
+        <v>487.1943</v>
       </c>
     </row>
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">ITG</t>
+          <t xml:space="preserve">AZ1</t>
         </is>
       </c>
       <c t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. QUASAR İSTANBUL TİCARİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C58">
-        <v>0.2406</v>
+        <v>0.1291</v>
       </c>
       <c t="n" r="D58">
-        <v>1.1121</v>
+        <v>0.8783</v>
       </c>
       <c t="n" r="E58">
-        <v>13.0213</v>
+        <v>27.6042</v>
       </c>
       <c t="n" r="F58">
-        <v>1.3731</v>
+        <v>-5.9538</v>
       </c>
       <c t="n" r="G58">
-        <v>30.8894</v>
+        <v>29.9856</v>
       </c>
       <c t="n" r="H58">
-        <v>156.5747</v>
+        <v>172.0417</v>
       </c>
       <c t="n" r="I58">
-        <v>486.6446</v>
+        <v>828.0917</v>
       </c>
     </row>
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">FT1</t>
+          <t xml:space="preserve">HRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C59">
-        <v>0.1218</v>
+        <v>1.5053</v>
       </c>
       <c t="n" r="D59">
-        <v>0.2132</v>
+        <v>3.7619</v>
       </c>
       <c t="n" r="E59">
-        <v>4.7911</v>
+        <v>11.0528</v>
       </c>
       <c t="n" r="F59">
-        <v>0.2580</v>
+        <v>5.8687</v>
       </c>
       <c t="n" r="G59">
-        <v>30.2514</v>
+        <v>29.7644</v>
       </c>
     </row>
     <row r="60">
@@ -1951,166 +1954,160 @@
         </is>
       </c>
       <c t="n" r="C60">
-        <v>0.2692</v>
+        <v>0.1683</v>
       </c>
       <c t="n" r="D60">
-        <v>5.0788</v>
+        <v>4.2742</v>
       </c>
       <c t="n" r="E60">
-        <v>16.6232</v>
+        <v>16.3994</v>
       </c>
       <c t="n" r="F60">
-        <v>6.8500</v>
+        <v>6.7424</v>
       </c>
       <c t="n" r="G60">
-        <v>30.1777</v>
+        <v>29.7254</v>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">HRE</t>
+          <t xml:space="preserve">FT1</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C61">
-        <v>1.4323</v>
+        <v>0.1244</v>
       </c>
       <c t="n" r="D61">
-        <v>3.7587</v>
+        <v>0.2133</v>
       </c>
       <c t="n" r="E61">
-        <v>11.0590</v>
+        <v>4.6874</v>
       </c>
       <c t="n" r="F61">
-        <v>5.7925</v>
+        <v>0.2606</v>
       </c>
       <c t="n" r="G61">
-        <v>30.0758</v>
+        <v>29.6828</v>
       </c>
     </row>
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">AZ1</t>
+          <t xml:space="preserve">ROG</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C62">
-        <v>0.1302</v>
+        <v>0.2379</v>
       </c>
       <c t="n" r="D62">
-        <v>0.8993</v>
+        <v>0.7793</v>
       </c>
       <c t="n" r="E62">
-        <v>27.6029</v>
+        <v>-1.0531</v>
       </c>
       <c t="n" r="F62">
-        <v>-5.9528</v>
+        <v>1.0822</v>
       </c>
       <c t="n" r="G62">
-        <v>30.0010</v>
-      </c>
-      <c t="n" r="H62">
-        <v>172.0448</v>
-      </c>
-      <c t="n" r="I62">
-        <v>828.1023</v>
+        <v>29.6787</v>
       </c>
     </row>
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">ROG</t>
+          <t xml:space="preserve">NGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C63">
-        <v>0.2359</v>
+        <v>3.2185</v>
       </c>
       <c t="n" r="D63">
-        <v>0.7785</v>
+        <v>8.9462</v>
       </c>
       <c t="n" r="E63">
-        <v>-1.0546</v>
+        <v>15.9853</v>
       </c>
       <c t="n" r="F63">
-        <v>1.0802</v>
+        <v>12.5752</v>
       </c>
       <c t="n" r="G63">
-        <v>29.6782</v>
+        <v>29.5980</v>
       </c>
     </row>
     <row r="64">
       <c t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">HVG</t>
+          <t xml:space="preserve">AG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C64">
-        <v>-0.0501</v>
+        <v>0.1284</v>
       </c>
       <c t="n" r="D64">
-        <v>-0.1419</v>
+        <v>0.2858</v>
       </c>
       <c t="n" r="E64">
-        <v>30.4723</v>
+        <v>28.6619</v>
       </c>
       <c t="n" r="F64">
-        <v>-0.1779</v>
+        <v>0.3683</v>
       </c>
       <c t="n" r="G64">
-        <v>29.4731</v>
+        <v>29.1263</v>
+      </c>
+      <c t="n" r="H64">
+        <v>230.7314</v>
+      </c>
+      <c t="n" r="I64">
+        <v>353.7995</v>
       </c>
     </row>
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">AG6</t>
+          <t xml:space="preserve">HVG</t>
         </is>
       </c>
       <c t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HAN VARLIK GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C65">
-        <v>0.1232</v>
+        <v>-0.0517</v>
       </c>
       <c t="n" r="D65">
-        <v>0.2855</v>
+        <v>-0.1419</v>
       </c>
       <c t="n" r="E65">
-        <v>28.6633</v>
+        <v>30.4723</v>
       </c>
       <c t="n" r="F65">
-        <v>0.3631</v>
+        <v>-0.1794</v>
       </c>
       <c t="n" r="G65">
-        <v>29.1448</v>
-      </c>
-      <c t="n" r="H65">
-        <v>230.7145</v>
-      </c>
-      <c t="n" r="I65">
-        <v>353.7763</v>
+        <v>28.9968</v>
       </c>
     </row>
     <row r="66">
@@ -2125,19 +2122,19 @@
         </is>
       </c>
       <c t="n" r="C66">
-        <v>0.3592</v>
+        <v>0.3546</v>
       </c>
       <c t="n" r="D66">
-        <v>0.6650</v>
+        <v>0.6580</v>
       </c>
       <c t="n" r="E66">
-        <v>26.8171</v>
+        <v>26.7127</v>
       </c>
       <c t="n" r="F66">
-        <v>2.4765</v>
+        <v>2.4717</v>
       </c>
       <c t="n" r="G66">
-        <v>28.7703</v>
+        <v>28.7598</v>
       </c>
     </row>
     <row r="67">
@@ -2152,19 +2149,19 @@
         </is>
       </c>
       <c t="n" r="C67">
-        <v>-0.0181</v>
+        <v>-0.0182</v>
       </c>
       <c t="n" r="D67">
         <v>-0.0587</v>
       </c>
       <c t="n" r="E67">
-        <v>28.1661</v>
+        <v>28.1682</v>
       </c>
       <c t="n" r="F67">
         <v>-0.0780</v>
       </c>
       <c t="n" r="G67">
-        <v>28.0132</v>
+        <v>28.0128</v>
       </c>
     </row>
     <row r="68">
@@ -2179,25 +2176,25 @@
         </is>
       </c>
       <c t="n" r="C68">
-        <v>1.2429</v>
+        <v>1.2694</v>
       </c>
       <c t="n" r="D68">
-        <v>4.1851</v>
+        <v>4.1943</v>
       </c>
       <c t="n" r="E68">
-        <v>16.2844</v>
+        <v>16.3025</v>
       </c>
       <c t="n" r="F68">
-        <v>4.4709</v>
+        <v>4.4983</v>
       </c>
       <c t="n" r="G68">
-        <v>27.8706</v>
+        <v>27.8959</v>
       </c>
       <c t="n" r="H68">
-        <v>130.8951</v>
+        <v>130.9556</v>
       </c>
       <c t="n" r="I68">
-        <v>636135.7774</v>
+        <v>636302.5393</v>
       </c>
     </row>
     <row r="69">
@@ -2212,25 +2209,25 @@
         </is>
       </c>
       <c t="n" r="C69">
-        <v>0.5641</v>
+        <v>0.5629</v>
       </c>
       <c t="n" r="D69">
-        <v>-1.5000</v>
+        <v>-1.7699</v>
       </c>
       <c t="n" r="E69">
-        <v>24.6916</v>
+        <v>24.7468</v>
       </c>
       <c t="n" r="F69">
-        <v>-20.3912</v>
+        <v>-20.3922</v>
       </c>
       <c t="n" r="G69">
-        <v>27.1735</v>
+        <v>27.1789</v>
       </c>
       <c t="n" r="H69">
-        <v>242.9238</v>
+        <v>242.9197</v>
       </c>
       <c t="n" r="I69">
-        <v>1973.9560</v>
+        <v>1973.9311</v>
       </c>
     </row>
     <row r="70">
@@ -2248,16 +2245,16 @@
         <v>0.7951</v>
       </c>
       <c t="n" r="D70">
-        <v>-1.1822</v>
+        <v>-1.1819</v>
       </c>
       <c t="n" r="E70">
-        <v>25.4290</v>
+        <v>25.3975</v>
       </c>
       <c t="n" r="F70">
         <v>-0.3214</v>
       </c>
       <c t="n" r="G70">
-        <v>26.1290</v>
+        <v>26.1219</v>
       </c>
       <c t="n" r="H70">
         <v>49.1317</v>
@@ -2278,88 +2275,88 @@
         </is>
       </c>
       <c t="n" r="C71">
-        <v>1.2388</v>
+        <v>1.2617</v>
       </c>
       <c t="n" r="D71">
-        <v>3.3966</v>
+        <v>3.4002</v>
       </c>
       <c t="n" r="E71">
-        <v>17.4373</v>
+        <v>17.4396</v>
       </c>
       <c t="n" r="F71">
-        <v>4.9778</v>
+        <v>5.0015</v>
       </c>
       <c t="n" r="G71">
-        <v>25.8244</v>
+        <v>25.7885</v>
       </c>
       <c t="n" r="H71">
-        <v>220.6431</v>
+        <v>220.7156</v>
       </c>
       <c t="n" r="I71">
-        <v>502.3143</v>
+        <v>502.4595</v>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">NUZ</t>
+          <t xml:space="preserve">AG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. METROPOL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C72">
-        <v>1.4476</v>
+        <v>4.1313</v>
       </c>
       <c t="n" r="D72">
-        <v>3.7822</v>
+        <v>4.9276</v>
       </c>
       <c t="n" r="E72">
-        <v>-0.1559</v>
+        <v>14.2756</v>
       </c>
       <c t="n" r="F72">
-        <v>4.3429</v>
+        <v>1.0324</v>
       </c>
       <c t="n" r="G72">
-        <v>25.5703</v>
+        <v>25.4675</v>
       </c>
       <c t="n" r="H72">
-        <v>162.6374</v>
+        <v>331.4108</v>
+      </c>
+      <c t="n" r="I72">
+        <v>836.8971</v>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">AG7</t>
+          <t xml:space="preserve">NUZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. METROPOL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C73">
-        <v>4.1314</v>
+        <v>1.4798</v>
       </c>
       <c t="n" r="D73">
-        <v>4.9662</v>
+        <v>3.7841</v>
       </c>
       <c t="n" r="E73">
-        <v>14.3013</v>
+        <v>-0.1318</v>
       </c>
       <c t="n" r="F73">
-        <v>1.0325</v>
+        <v>4.3759</v>
       </c>
       <c t="n" r="G73">
-        <v>25.4622</v>
+        <v>25.4672</v>
       </c>
       <c t="n" r="H73">
-        <v>331.4111</v>
-      </c>
-      <c t="n" r="I73">
-        <v>836.8979</v>
+        <v>162.7206</v>
       </c>
     </row>
     <row r="74">
@@ -2374,25 +2371,25 @@
         </is>
       </c>
       <c t="n" r="C74">
-        <v>-0.0796</v>
+        <v>-0.0811</v>
       </c>
       <c t="n" r="D74">
-        <v>-0.2328</v>
+        <v>-0.2626</v>
       </c>
       <c t="n" r="E74">
-        <v>25.3582</v>
+        <v>25.3585</v>
       </c>
       <c t="n" r="F74">
-        <v>0.0428</v>
+        <v>0.0414</v>
       </c>
       <c t="n" r="G74">
-        <v>25.3286</v>
+        <v>25.3287</v>
       </c>
       <c t="n" r="H74">
-        <v>200.1705</v>
+        <v>200.1661</v>
       </c>
       <c t="n" r="I74">
-        <v>400.3860</v>
+        <v>400.3803</v>
       </c>
     </row>
     <row r="75">
@@ -2407,19 +2404,19 @@
         </is>
       </c>
       <c t="n" r="C75">
-        <v>-2.2929</v>
+        <v>-2.2705</v>
       </c>
       <c t="n" r="D75">
-        <v>0.0610</v>
+        <v>0.0612</v>
       </c>
       <c t="n" r="E75">
-        <v>17.0655</v>
+        <v>17.0705</v>
       </c>
       <c t="n" r="F75">
-        <v>1.1042</v>
+        <v>1.1275</v>
       </c>
       <c t="n" r="G75">
-        <v>25.0155</v>
+        <v>24.9729</v>
       </c>
     </row>
     <row r="76">
@@ -2434,19 +2431,19 @@
         </is>
       </c>
       <c t="n" r="C76">
-        <v>0.4051</v>
+        <v>0.4040</v>
       </c>
       <c t="n" r="D76">
-        <v>-0.1001</v>
+        <v>-0.0997</v>
       </c>
       <c t="n" r="E76">
-        <v>23.1988</v>
+        <v>23.1935</v>
       </c>
       <c t="n" r="F76">
-        <v>-0.1244</v>
+        <v>-0.1254</v>
       </c>
       <c t="n" r="G76">
-        <v>24.9290</v>
+        <v>24.9272</v>
       </c>
     </row>
     <row r="77">
@@ -2461,22 +2458,22 @@
         </is>
       </c>
       <c t="n" r="C77">
-        <v>-2.5914</v>
+        <v>-2.6067</v>
       </c>
       <c t="n" r="D77">
-        <v>-2.3141</v>
+        <v>-2.3274</v>
       </c>
       <c t="n" r="E77">
-        <v>8.0025</v>
+        <v>8.0189</v>
       </c>
       <c t="n" r="F77">
-        <v>-2.7682</v>
+        <v>-2.7835</v>
       </c>
       <c t="n" r="G77">
-        <v>24.6014</v>
+        <v>24.5422</v>
       </c>
       <c t="n" r="H77">
-        <v>148.1488</v>
+        <v>148.1098</v>
       </c>
     </row>
     <row r="78">
@@ -2491,25 +2488,25 @@
         </is>
       </c>
       <c t="n" r="C78">
-        <v>-1.2818</v>
+        <v>-1.2841</v>
       </c>
       <c t="n" r="D78">
-        <v>5.5867</v>
+        <v>5.5717</v>
       </c>
       <c t="n" r="E78">
-        <v>24.8246</v>
+        <v>24.8277</v>
       </c>
       <c t="n" r="F78">
-        <v>-1.5937</v>
+        <v>-1.5959</v>
       </c>
       <c t="n" r="G78">
-        <v>23.7251</v>
+        <v>23.6738</v>
       </c>
       <c t="n" r="H78">
-        <v>253.3076</v>
+        <v>253.2997</v>
       </c>
       <c t="n" r="I78">
-        <v>783.8526</v>
+        <v>783.9845</v>
       </c>
     </row>
     <row r="79">
@@ -2524,25 +2521,25 @@
         </is>
       </c>
       <c t="n" r="C79">
-        <v>6.5541</v>
+        <v>6.5790</v>
       </c>
       <c t="n" r="D79">
-        <v>8.2535</v>
+        <v>8.2565</v>
       </c>
       <c t="n" r="E79">
-        <v>16.1236</v>
+        <v>16.0730</v>
       </c>
       <c t="n" r="F79">
-        <v>6.9372</v>
+        <v>6.9623</v>
       </c>
       <c t="n" r="G79">
-        <v>23.1046</v>
+        <v>23.1284</v>
       </c>
       <c t="n" r="H79">
-        <v>244.1935</v>
+        <v>244.2741</v>
       </c>
       <c t="n" r="I79">
-        <v>781.0853</v>
+        <v>781.2917</v>
       </c>
     </row>
     <row r="80">
@@ -2557,22 +2554,22 @@
         </is>
       </c>
       <c t="n" r="C80">
-        <v>-0.2523</v>
+        <v>-0.2503</v>
       </c>
       <c t="n" r="D80">
-        <v>-0.7591</v>
+        <v>-0.7563</v>
       </c>
       <c t="n" r="E80">
-        <v>22.9089</v>
+        <v>22.9093</v>
       </c>
       <c t="n" r="F80">
-        <v>-0.8744</v>
+        <v>-0.8725</v>
       </c>
       <c t="n" r="G80">
-        <v>21.6852</v>
+        <v>21.6906</v>
       </c>
       <c t="n" r="H80">
-        <v>170.7615</v>
+        <v>170.7667</v>
       </c>
     </row>
     <row r="81">
@@ -2587,85 +2584,85 @@
         </is>
       </c>
       <c t="n" r="C81">
-        <v>0.4011</v>
+        <v>0.4043</v>
       </c>
       <c t="n" r="D81">
-        <v>1.0169</v>
+        <v>1.0179</v>
       </c>
       <c t="n" r="E81">
-        <v>3.8050</v>
+        <v>3.7945</v>
       </c>
       <c t="n" r="F81">
-        <v>1.4052</v>
+        <v>1.4084</v>
       </c>
       <c t="n" r="G81">
-        <v>21.4842</v>
+        <v>21.4339</v>
       </c>
       <c t="n" r="H81">
-        <v>264.5239</v>
+        <v>264.5354</v>
       </c>
       <c t="n" r="I81">
-        <v>794.5911</v>
+        <v>794.6134</v>
       </c>
     </row>
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">GGF</t>
+          <t xml:space="preserve">ZG6</t>
         </is>
       </c>
       <c t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C82">
-        <v>1.0863</v>
+        <v>-0.1025</v>
       </c>
       <c t="n" r="D82">
-        <v>2.8664</v>
+        <v>-0.3079</v>
       </c>
       <c t="n" r="E82">
-        <v>12.1106</v>
+        <v>23.5578</v>
       </c>
       <c t="n" r="F82">
-        <v>1.9761</v>
+        <v>-2.4900</v>
       </c>
       <c t="n" r="G82">
-        <v>21.4692</v>
+        <v>21.2900</v>
       </c>
       <c t="n" r="H82">
-        <v>81.5246</v>
+        <v>46.6381</v>
       </c>
     </row>
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">ZG6</t>
+          <t xml:space="preserve">GGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C83">
-        <v>-0.0999</v>
+        <v>1.1175</v>
       </c>
       <c t="n" r="D83">
-        <v>-0.3081</v>
+        <v>2.8360</v>
       </c>
       <c t="n" r="E83">
-        <v>23.5577</v>
+        <v>12.1051</v>
       </c>
       <c t="n" r="F83">
-        <v>-2.4874</v>
+        <v>2.0076</v>
       </c>
       <c t="n" r="G83">
-        <v>21.2906</v>
+        <v>21.2013</v>
       </c>
       <c t="n" r="H83">
-        <v>46.6419</v>
+        <v>81.5806</v>
       </c>
     </row>
     <row r="84">
@@ -2680,25 +2677,25 @@
         </is>
       </c>
       <c t="n" r="C84">
-        <v>0.2712</v>
+        <v>0.2722</v>
       </c>
       <c t="n" r="D84">
-        <v>0.9434</v>
+        <v>0.9443</v>
       </c>
       <c t="n" r="E84">
-        <v>5.6637</v>
+        <v>5.6646</v>
       </c>
       <c t="n" r="F84">
-        <v>1.1266</v>
+        <v>1.1275</v>
       </c>
       <c t="n" r="G84">
-        <v>20.9274</v>
+        <v>20.9285</v>
       </c>
       <c t="n" r="H84">
-        <v>221.1281</v>
+        <v>221.1313</v>
       </c>
       <c t="n" r="I84">
-        <v>989.9800</v>
+        <v>990.0077</v>
       </c>
     </row>
     <row r="85">
@@ -2713,25 +2710,25 @@
         </is>
       </c>
       <c t="n" r="C85">
-        <v>0.4690</v>
+        <v>0.4647</v>
       </c>
       <c t="n" r="D85">
-        <v>0.8361</v>
+        <v>0.8260</v>
       </c>
       <c t="n" r="E85">
-        <v>17.3040</v>
+        <v>17.2982</v>
       </c>
       <c t="n" r="F85">
-        <v>1.0200</v>
+        <v>1.0157</v>
       </c>
       <c t="n" r="G85">
-        <v>20.5698</v>
+        <v>20.6188</v>
       </c>
       <c t="n" r="H85">
-        <v>174.3996</v>
+        <v>174.3878</v>
       </c>
       <c t="n" r="I85">
-        <v>1191.8516</v>
+        <v>1191.4738</v>
       </c>
     </row>
     <row r="86">
@@ -2746,22 +2743,22 @@
         </is>
       </c>
       <c t="n" r="C86">
-        <v>-1.6186</v>
+        <v>-1.6157</v>
       </c>
       <c t="n" r="D86">
-        <v>-0.2030</v>
+        <v>-0.2041</v>
       </c>
       <c t="n" r="E86">
-        <v>16.6167</v>
+        <v>16.6177</v>
       </c>
       <c t="n" r="F86">
-        <v>0.5224</v>
+        <v>0.5254</v>
       </c>
       <c t="n" r="G86">
-        <v>20.2623</v>
+        <v>20.2492</v>
       </c>
       <c t="n" r="H86">
-        <v>368.8716</v>
+        <v>368.8855</v>
       </c>
     </row>
     <row r="87">
@@ -2776,25 +2773,25 @@
         </is>
       </c>
       <c t="n" r="C87">
-        <v>-0.1180</v>
+        <v>-0.1280</v>
       </c>
       <c t="n" r="D87">
-        <v>1.4374</v>
+        <v>1.2716</v>
       </c>
       <c t="n" r="E87">
-        <v>14.7951</v>
+        <v>14.8556</v>
       </c>
       <c t="n" r="F87">
-        <v>-2.7540</v>
+        <v>-2.7636</v>
       </c>
       <c t="n" r="G87">
-        <v>19.5542</v>
+        <v>19.4917</v>
       </c>
       <c t="n" r="H87">
-        <v>150.4107</v>
+        <v>150.3859</v>
       </c>
       <c t="n" r="I87">
-        <v>419.0545</v>
+        <v>419.0029</v>
       </c>
     </row>
     <row r="88">
@@ -2809,25 +2806,25 @@
         </is>
       </c>
       <c t="n" r="C88">
-        <v>0.0672</v>
+        <v>0.0689</v>
       </c>
       <c t="n" r="D88">
-        <v>-0.1106</v>
+        <v>-0.1084</v>
       </c>
       <c t="n" r="E88">
-        <v>15.2805</v>
+        <v>15.2832</v>
       </c>
       <c t="n" r="F88">
-        <v>0.3858</v>
+        <v>0.3875</v>
       </c>
       <c t="n" r="G88">
-        <v>19.3705</v>
+        <v>19.3693</v>
       </c>
       <c t="n" r="H88">
-        <v>116.2434</v>
+        <v>116.2470</v>
       </c>
       <c t="n" r="I88">
-        <v>1159.6336</v>
+        <v>1159.6547</v>
       </c>
     </row>
     <row r="89">
@@ -2842,22 +2839,22 @@
         </is>
       </c>
       <c t="n" r="C89">
-        <v>0.5089</v>
+        <v>0.5180</v>
       </c>
       <c t="n" r="D89">
-        <v>1.2150</v>
+        <v>1.2178</v>
       </c>
       <c t="n" r="E89">
-        <v>11.5818</v>
+        <v>11.5916</v>
       </c>
       <c t="n" r="F89">
-        <v>-0.7536</v>
+        <v>-0.7445</v>
       </c>
       <c t="n" r="G89">
-        <v>19.1398</v>
+        <v>19.0998</v>
       </c>
       <c t="n" r="H89">
-        <v>152.0693</v>
+        <v>152.0923</v>
       </c>
     </row>
     <row r="90">
@@ -2872,22 +2869,22 @@
         </is>
       </c>
       <c t="n" r="C90">
-        <v>-0.2681</v>
+        <v>-0.2673</v>
       </c>
       <c t="n" r="D90">
-        <v>-0.1759</v>
+        <v>-0.1760</v>
       </c>
       <c t="n" r="E90">
-        <v>19.1436</v>
+        <v>19.1434</v>
       </c>
       <c t="n" r="F90">
-        <v>-0.0357</v>
+        <v>-0.0348</v>
       </c>
       <c t="n" r="G90">
-        <v>18.8361</v>
+        <v>18.8328</v>
       </c>
       <c t="n" r="H90">
-        <v>1436.5311</v>
+        <v>1436.5442</v>
       </c>
     </row>
     <row r="91">
@@ -2902,22 +2899,22 @@
         </is>
       </c>
       <c t="n" r="C91">
-        <v>0.4775</v>
+        <v>0.4658</v>
       </c>
       <c t="n" r="D91">
-        <v>1.8007</v>
+        <v>1.7921</v>
       </c>
       <c t="n" r="E91">
-        <v>8.7288</v>
+        <v>8.7156</v>
       </c>
       <c t="n" r="F91">
-        <v>1.7328</v>
+        <v>1.7210</v>
       </c>
       <c t="n" r="G91">
-        <v>18.0601</v>
+        <v>18.0346</v>
       </c>
       <c t="n" r="H91">
-        <v>75.8050</v>
+        <v>75.7846</v>
       </c>
     </row>
     <row r="92">
@@ -2932,25 +2929,25 @@
         </is>
       </c>
       <c t="n" r="C92">
-        <v>-0.2059</v>
+        <v>-0.2103</v>
       </c>
       <c t="n" r="D92">
-        <v>-0.5523</v>
+        <v>-0.5535</v>
       </c>
       <c t="n" r="E92">
         <v>11.1788</v>
       </c>
       <c t="n" r="F92">
-        <v>-0.6157</v>
+        <v>-0.6201</v>
       </c>
       <c t="n" r="G92">
         <v>17.9938</v>
       </c>
       <c t="n" r="H92">
-        <v>245.7115</v>
+        <v>245.6962</v>
       </c>
       <c t="n" r="I92">
-        <v>1013.6653</v>
+        <v>1013.6160</v>
       </c>
     </row>
     <row r="93">
@@ -2965,25 +2962,25 @@
         </is>
       </c>
       <c t="n" r="C93">
-        <v>0.8177</v>
+        <v>0.7465</v>
       </c>
       <c t="n" r="D93">
-        <v>2.1305</v>
+        <v>1.7929</v>
       </c>
       <c t="n" r="E93">
-        <v>16.9972</v>
+        <v>16.8409</v>
       </c>
       <c t="n" r="F93">
-        <v>2.2432</v>
+        <v>2.1710</v>
       </c>
       <c t="n" r="G93">
-        <v>17.8999</v>
+        <v>17.9670</v>
       </c>
       <c t="n" r="H93">
-        <v>143.5286</v>
+        <v>143.3566</v>
       </c>
       <c t="n" r="I93">
-        <v>448.4695</v>
+        <v>448.2166</v>
       </c>
     </row>
     <row r="94">
@@ -2998,22 +2995,22 @@
         </is>
       </c>
       <c t="n" r="C94">
-        <v>-1.5429</v>
+        <v>-1.5427</v>
       </c>
       <c t="n" r="D94">
-        <v>-1.0638</v>
+        <v>-1.0650</v>
       </c>
       <c t="n" r="E94">
-        <v>25.6602</v>
+        <v>25.6597</v>
       </c>
       <c t="n" r="F94">
-        <v>-0.8525</v>
+        <v>-0.8523</v>
       </c>
       <c t="n" r="G94">
-        <v>17.8344</v>
+        <v>17.8368</v>
       </c>
       <c t="n" r="H94">
-        <v>215.9994</v>
+        <v>215.9999</v>
       </c>
     </row>
     <row r="95">
@@ -3028,22 +3025,22 @@
         </is>
       </c>
       <c t="n" r="C95">
-        <v>-0.1248</v>
+        <v>-0.1292</v>
       </c>
       <c t="n" r="D95">
-        <v>-0.3945</v>
+        <v>-0.3946</v>
       </c>
       <c t="n" r="E95">
-        <v>26.9062</v>
+        <v>26.9064</v>
       </c>
       <c t="n" r="F95">
-        <v>-0.4732</v>
+        <v>-0.4775</v>
       </c>
       <c t="n" r="G95">
-        <v>17.7021</v>
+        <v>17.7020</v>
       </c>
       <c t="n" r="H95">
-        <v>775.5475</v>
+        <v>775.5096</v>
       </c>
     </row>
     <row r="96">
@@ -3058,25 +3055,25 @@
         </is>
       </c>
       <c t="n" r="C96">
-        <v>-0.3125</v>
+        <v>-0.3195</v>
       </c>
       <c t="n" r="D96">
-        <v>-2.1292</v>
+        <v>-2.1316</v>
       </c>
       <c t="n" r="E96">
-        <v>11.7668</v>
+        <v>11.7644</v>
       </c>
       <c t="n" r="F96">
-        <v>-2.3117</v>
+        <v>-2.3186</v>
       </c>
       <c t="n" r="G96">
-        <v>17.1114</v>
+        <v>17.1613</v>
       </c>
       <c t="n" r="H96">
-        <v>148.5625</v>
+        <v>148.5449</v>
       </c>
       <c t="n" r="I96">
-        <v>654.1563</v>
+        <v>654.1030</v>
       </c>
     </row>
     <row r="97">
@@ -3091,25 +3088,25 @@
         </is>
       </c>
       <c t="n" r="C97">
-        <v>-0.2068</v>
+        <v>-0.2022</v>
       </c>
       <c t="n" r="D97">
-        <v>0.5906</v>
+        <v>0.6261</v>
       </c>
       <c t="n" r="E97">
-        <v>6.2015</v>
+        <v>6.2037</v>
       </c>
       <c t="n" r="F97">
-        <v>-0.6609</v>
+        <v>-0.6563</v>
       </c>
       <c t="n" r="G97">
-        <v>16.9511</v>
+        <v>16.9527</v>
       </c>
       <c t="n" r="H97">
-        <v>320.7572</v>
+        <v>320.7766</v>
       </c>
       <c t="n" r="I97">
-        <v>1601.5154</v>
+        <v>1601.5938</v>
       </c>
     </row>
     <row r="98">
@@ -3124,7 +3121,7 @@
         </is>
       </c>
       <c t="n" r="C98">
-        <v>-0.2509</v>
+        <v>-0.2508</v>
       </c>
       <c t="n" r="D98">
         <v>-0.2529</v>
@@ -3136,7 +3133,7 @@
         <v>-0.5035</v>
       </c>
       <c t="n" r="G98">
-        <v>16.9175</v>
+        <v>16.9171</v>
       </c>
     </row>
     <row r="99">
@@ -3154,19 +3151,19 @@
         <v>-0.0008</v>
       </c>
       <c t="n" r="D99">
-        <v>-0.0402</v>
+        <v>-0.0403</v>
       </c>
       <c t="n" r="E99">
         <v>16.1307</v>
       </c>
       <c t="n" r="F99">
-        <v>-0.0461</v>
+        <v>-0.0462</v>
       </c>
       <c t="n" r="G99">
-        <v>16.0175</v>
+        <v>16.0174</v>
       </c>
       <c t="n" r="H99">
-        <v>580.0913</v>
+        <v>580.0909</v>
       </c>
     </row>
     <row r="100">
@@ -3181,25 +3178,25 @@
         </is>
       </c>
       <c t="n" r="C100">
-        <v>1.0002</v>
+        <v>1.0019</v>
       </c>
       <c t="n" r="D100">
-        <v>-0.7210</v>
+        <v>-0.7528</v>
       </c>
       <c t="n" r="E100">
-        <v>2.3756</v>
+        <v>-0.2189</v>
       </c>
       <c t="n" r="F100">
-        <v>0.3217</v>
+        <v>0.3234</v>
       </c>
       <c t="n" r="G100">
-        <v>15.7181</v>
+        <v>15.6837</v>
       </c>
       <c t="n" r="H100">
-        <v>0.8698</v>
+        <v>0.8715</v>
       </c>
       <c t="n" r="I100">
-        <v>59.0111</v>
+        <v>59.0137</v>
       </c>
     </row>
     <row r="101">
@@ -3214,22 +3211,22 @@
         </is>
       </c>
       <c t="n" r="C101">
-        <v>0.3188</v>
+        <v>0.3578</v>
       </c>
       <c t="n" r="D101">
-        <v>2.5978</v>
+        <v>2.3991</v>
       </c>
       <c t="n" r="E101">
-        <v>14.5672</v>
+        <v>14.9621</v>
       </c>
       <c t="n" r="F101">
-        <v>3.6443</v>
+        <v>3.6846</v>
       </c>
       <c t="n" r="G101">
-        <v>15.0670</v>
+        <v>15.0775</v>
       </c>
       <c t="n" r="H101">
-        <v>188.0673</v>
+        <v>188.1793</v>
       </c>
     </row>
     <row r="102">
@@ -3244,19 +3241,19 @@
         </is>
       </c>
       <c t="n" r="C102">
-        <v>-0.4049</v>
+        <v>-0.4327</v>
       </c>
       <c t="n" r="D102">
-        <v>-0.7951</v>
+        <v>-0.8165</v>
       </c>
       <c t="n" r="E102">
-        <v>16.4151</v>
+        <v>16.3903</v>
       </c>
       <c t="n" r="F102">
-        <v>-0.9194</v>
+        <v>-0.9471</v>
       </c>
       <c t="n" r="G102">
-        <v>14.7474</v>
+        <v>14.7232</v>
       </c>
     </row>
     <row r="103">
@@ -3271,25 +3268,25 @@
         </is>
       </c>
       <c t="n" r="C103">
-        <v>0.0323</v>
+        <v>0.0237</v>
       </c>
       <c t="n" r="D103">
-        <v>1.6391</v>
+        <v>1.5594</v>
       </c>
       <c t="n" r="E103">
-        <v>4.6038</v>
+        <v>4.6288</v>
       </c>
       <c t="n" r="F103">
-        <v>1.1998</v>
+        <v>1.1911</v>
       </c>
       <c t="n" r="G103">
-        <v>14.2632</v>
+        <v>14.2367</v>
       </c>
       <c t="n" r="H103">
-        <v>266.1400</v>
+        <v>266.1086</v>
       </c>
       <c t="n" r="I103">
-        <v>1193.5055</v>
+        <v>1193.3946</v>
       </c>
     </row>
     <row r="104">
@@ -3304,88 +3301,88 @@
         </is>
       </c>
       <c t="n" r="C104">
-        <v>-0.1325</v>
+        <v>-0.1294</v>
       </c>
       <c t="n" r="D104">
-        <v>0.5000</v>
+        <v>0.5155</v>
       </c>
       <c t="n" r="E104">
-        <v>12.7220</v>
+        <v>12.7231</v>
       </c>
       <c t="n" r="F104">
-        <v>1.2232</v>
+        <v>1.2264</v>
       </c>
       <c t="n" r="G104">
-        <v>13.8569</v>
+        <v>13.9576</v>
       </c>
       <c t="n" r="H104">
-        <v>262.6318</v>
+        <v>262.6431</v>
       </c>
       <c t="n" r="I104">
-        <v>474.6542</v>
+        <v>474.6751</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">NG4</t>
+          <t xml:space="preserve">FRG</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C105">
-        <v>0.0131</v>
+        <v>1.7330</v>
       </c>
       <c t="n" r="D105">
-        <v>-0.0239</v>
+        <v>2.1226</v>
       </c>
       <c t="n" r="E105">
-        <v>13.7695</v>
+        <v>14.9717</v>
       </c>
       <c t="n" r="F105">
-        <v>-0.9435</v>
+        <v>4.6487</v>
       </c>
       <c t="n" r="G105">
-        <v>13.7175</v>
+        <v>13.7531</v>
       </c>
       <c t="n" r="H105">
-        <v>226.6165</v>
+        <v>93.2712</v>
+      </c>
+      <c t="n" r="I105">
+        <v>441.1140</v>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">FRG</t>
+          <t xml:space="preserve">NG4</t>
         </is>
       </c>
       <c t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C106">
-        <v>1.9180</v>
+        <v>0.0096</v>
       </c>
       <c t="n" r="D106">
-        <v>3.0421</v>
+        <v>0.1233</v>
       </c>
       <c t="n" r="E106">
-        <v>15.5002</v>
+        <v>13.7657</v>
       </c>
       <c t="n" r="F106">
-        <v>4.8389</v>
+        <v>-0.9470</v>
       </c>
       <c t="n" r="G106">
-        <v>13.6416</v>
+        <v>13.7073</v>
       </c>
       <c t="n" r="H106">
-        <v>93.6226</v>
-      </c>
-      <c t="n" r="I106">
-        <v>442.2233</v>
+        <v>226.6047</v>
       </c>
     </row>
     <row r="107">
@@ -3400,19 +3397,19 @@
         </is>
       </c>
       <c t="n" r="C107">
-        <v>0.0287</v>
+        <v>0.0277</v>
       </c>
       <c t="n" r="D107">
-        <v>2.2688</v>
+        <v>2.2693</v>
       </c>
       <c t="n" r="E107">
-        <v>3.6058</v>
+        <v>3.5999</v>
       </c>
       <c t="n" r="F107">
-        <v>2.4598</v>
+        <v>2.4588</v>
       </c>
       <c t="n" r="G107">
-        <v>13.3918</v>
+        <v>13.4129</v>
       </c>
     </row>
     <row r="108">
@@ -3427,25 +3424,25 @@
         </is>
       </c>
       <c t="n" r="C108">
-        <v>1.5994</v>
+        <v>1.4469</v>
       </c>
       <c t="n" r="D108">
-        <v>-5.1784</v>
+        <v>-5.7004</v>
       </c>
       <c t="n" r="E108">
-        <v>10.7665</v>
+        <v>10.5556</v>
       </c>
       <c t="n" r="F108">
-        <v>-4.4356</v>
+        <v>-4.5790</v>
       </c>
       <c t="n" r="G108">
-        <v>13.3081</v>
+        <v>13.2854</v>
       </c>
       <c t="n" r="H108">
-        <v>109.8841</v>
+        <v>109.5691</v>
       </c>
       <c t="n" r="I108">
-        <v>361.0544</v>
+        <v>359.9718</v>
       </c>
     </row>
     <row r="109">
@@ -3460,22 +3457,22 @@
         </is>
       </c>
       <c t="n" r="C109">
-        <v>-0.0530</v>
+        <v>-0.0540</v>
       </c>
       <c t="n" r="D109">
-        <v>-0.3442</v>
+        <v>-0.3443</v>
       </c>
       <c t="n" r="E109">
         <v>13.7144</v>
       </c>
       <c t="n" r="F109">
-        <v>-0.5479</v>
+        <v>-0.5489</v>
       </c>
       <c t="n" r="G109">
         <v>13.0495</v>
       </c>
       <c t="n" r="H109">
-        <v>493.7480</v>
+        <v>493.7423</v>
       </c>
     </row>
     <row r="110">
@@ -3490,22 +3487,22 @@
         </is>
       </c>
       <c t="n" r="C110">
-        <v>-0.0272</v>
+        <v>-0.0219</v>
       </c>
       <c t="n" r="D110">
-        <v>0.1379</v>
+        <v>0.1432</v>
       </c>
       <c t="n" r="E110">
-        <v>-1.0597</v>
+        <v>-1.0548</v>
       </c>
       <c t="n" r="F110">
-        <v>0.0699</v>
+        <v>0.0752</v>
       </c>
       <c t="n" r="G110">
-        <v>12.9126</v>
+        <v>12.9194</v>
       </c>
       <c t="n" r="H110">
-        <v>124.4176</v>
+        <v>124.4294</v>
       </c>
     </row>
     <row r="111">
@@ -3520,19 +3517,19 @@
         </is>
       </c>
       <c t="n" r="C111">
-        <v>-29.5788</v>
+        <v>-29.5926</v>
       </c>
       <c t="n" r="D111">
-        <v>-33.0137</v>
+        <v>-33.0173</v>
       </c>
       <c t="n" r="E111">
-        <v>1789.9965</v>
+        <v>1814.2098</v>
       </c>
       <c t="n" r="F111">
-        <v>-33.1912</v>
+        <v>-33.2042</v>
       </c>
       <c t="n" r="G111">
-        <v>12.6759</v>
+        <v>12.7660</v>
       </c>
     </row>
     <row r="112">
@@ -3547,25 +3544,25 @@
         </is>
       </c>
       <c t="n" r="C112">
-        <v>-0.3194</v>
+        <v>-0.3172</v>
       </c>
       <c t="n" r="D112">
-        <v>0.6234</v>
+        <v>0.6243</v>
       </c>
       <c t="n" r="E112">
-        <v>8.8651</v>
+        <v>8.8629</v>
       </c>
       <c t="n" r="F112">
-        <v>-1.1046</v>
+        <v>-1.1024</v>
       </c>
       <c t="n" r="G112">
-        <v>12.6215</v>
+        <v>12.5884</v>
       </c>
       <c t="n" r="H112">
-        <v>201.5686</v>
+        <v>201.5753</v>
       </c>
       <c t="n" r="I112">
-        <v>576.5357</v>
+        <v>576.5506</v>
       </c>
     </row>
     <row r="113">
@@ -3580,49 +3577,52 @@
         </is>
       </c>
       <c t="n" r="C113">
-        <v>0.1377</v>
+        <v>0.1366</v>
       </c>
       <c t="n" r="D113">
-        <v>0.7964</v>
+        <v>0.7670</v>
       </c>
       <c t="n" r="E113">
-        <v>9.5916</v>
+        <v>9.5924</v>
       </c>
       <c t="n" r="F113">
-        <v>0.7755</v>
+        <v>0.7744</v>
       </c>
       <c t="n" r="G113">
-        <v>12.2090</v>
+        <v>12.0639</v>
       </c>
       <c t="n" r="H113">
-        <v>-18.4589</v>
+        <v>-18.4598</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">NGO</t>
+          <t xml:space="preserve">YG1</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LOTUS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C114">
-        <v>3.1135</v>
+        <v>0.0924</v>
       </c>
       <c t="n" r="D114">
-        <v>9.0439</v>
+        <v>0.0692</v>
       </c>
       <c t="n" r="E114">
-        <v>15.8747</v>
+        <v>10.3602</v>
       </c>
       <c t="n" r="F114">
-        <v>12.4608</v>
+        <v>0.0418</v>
       </c>
       <c t="n" r="G114">
-        <v>11.9341</v>
+        <v>12.0458</v>
+      </c>
+      <c t="n" r="H114">
+        <v>302.3307</v>
       </c>
     </row>
     <row r="115">
@@ -3637,19 +3637,19 @@
         </is>
       </c>
       <c t="n" r="C115">
-        <v>0.8140</v>
+        <v>0.8404</v>
       </c>
       <c t="n" r="D115">
-        <v>1.6692</v>
+        <v>1.7172</v>
       </c>
       <c t="n" r="E115">
-        <v>4.2883</v>
+        <v>4.3044</v>
       </c>
       <c t="n" r="F115">
-        <v>3.4361</v>
+        <v>3.4633</v>
       </c>
       <c t="n" r="G115">
-        <v>11.1215</v>
+        <v>11.0688</v>
       </c>
     </row>
     <row r="116">
@@ -3664,22 +3664,22 @@
         </is>
       </c>
       <c t="n" r="C116">
-        <v>-1.6469</v>
+        <v>-1.6516</v>
       </c>
       <c t="n" r="D116">
-        <v>-5.1617</v>
+        <v>-5.1694</v>
       </c>
       <c t="n" r="E116">
-        <v>33.2450</v>
+        <v>33.2360</v>
       </c>
       <c t="n" r="F116">
-        <v>-5.2300</v>
+        <v>-5.2345</v>
       </c>
       <c t="n" r="G116">
-        <v>10.5148</v>
+        <v>10.5053</v>
       </c>
       <c t="n" r="H116">
-        <v>399.3584</v>
+        <v>399.3346</v>
       </c>
     </row>
     <row r="117">
@@ -3694,22 +3694,22 @@
         </is>
       </c>
       <c t="n" r="C117">
-        <v>-0.0255</v>
+        <v>-0.0227</v>
       </c>
       <c t="n" r="D117">
-        <v>0.3443</v>
+        <v>0.3472</v>
       </c>
       <c t="n" r="E117">
-        <v>27.6139</v>
+        <v>27.6205</v>
       </c>
       <c t="n" r="F117">
-        <v>0.2616</v>
+        <v>0.2644</v>
       </c>
       <c t="n" r="G117">
-        <v>10.4378</v>
+        <v>10.4293</v>
       </c>
       <c t="n" r="H117">
-        <v>134.4121</v>
+        <v>134.4185</v>
       </c>
     </row>
     <row r="118">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c t="n" r="C118">
-        <v>-0.0714</v>
+        <v>-0.0734</v>
       </c>
       <c t="n" r="D118">
-        <v>-0.1848</v>
+        <v>-0.1851</v>
       </c>
       <c t="n" r="E118">
-        <v>10.8872</v>
+        <v>10.8867</v>
       </c>
       <c t="n" r="F118">
-        <v>-0.2365</v>
+        <v>-0.2385</v>
       </c>
       <c t="n" r="G118">
-        <v>10.3921</v>
+        <v>10.3861</v>
       </c>
     </row>
     <row r="119">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c t="n" r="C119">
-        <v>-0.3169</v>
+        <v>-0.3427</v>
       </c>
       <c t="n" r="D119">
-        <v>-1.0713</v>
+        <v>-1.0793</v>
       </c>
       <c t="n" r="E119">
-        <v>12.4010</v>
+        <v>12.3843</v>
       </c>
       <c t="n" r="F119">
-        <v>-1.3972</v>
+        <v>-1.4228</v>
       </c>
       <c t="n" r="G119">
-        <v>10.2991</v>
+        <v>10.2772</v>
       </c>
     </row>
     <row r="120">
@@ -3778,19 +3778,19 @@
         </is>
       </c>
       <c t="n" r="C120">
-        <v>0.4397</v>
+        <v>0.4392</v>
       </c>
       <c t="n" r="D120">
-        <v>0.3737</v>
+        <v>0.3576</v>
       </c>
       <c t="n" r="E120">
-        <v>9.8238</v>
+        <v>10.3915</v>
       </c>
       <c t="n" r="F120">
-        <v>0.3983</v>
+        <v>0.3978</v>
       </c>
       <c t="n" r="G120">
-        <v>9.6491</v>
+        <v>9.6581</v>
       </c>
     </row>
     <row r="121">
@@ -3805,25 +3805,25 @@
         </is>
       </c>
       <c t="n" r="C121">
-        <v>0.1605</v>
+        <v>0.1643</v>
       </c>
       <c t="n" r="D121">
-        <v>0.4062</v>
+        <v>0.4103</v>
       </c>
       <c t="n" r="E121">
-        <v>2.1481</v>
+        <v>2.1606</v>
       </c>
       <c t="n" r="F121">
-        <v>1.1147</v>
+        <v>1.1185</v>
       </c>
       <c t="n" r="G121">
-        <v>9.5789</v>
+        <v>9.5754</v>
       </c>
       <c t="n" r="H121">
-        <v>129.3094</v>
+        <v>129.3180</v>
       </c>
       <c t="n" r="I121">
-        <v>423.2328</v>
+        <v>422.3719</v>
       </c>
     </row>
     <row r="122">
@@ -3838,79 +3838,79 @@
         </is>
       </c>
       <c t="n" r="C122">
-        <v>0.6818</v>
+        <v>0.6764</v>
       </c>
       <c t="n" r="D122">
-        <v>2.0049</v>
+        <v>2.0005</v>
       </c>
       <c t="n" r="E122">
-        <v>8.6601</v>
+        <v>8.6551</v>
       </c>
       <c t="n" r="F122">
-        <v>1.9473</v>
+        <v>1.9418</v>
       </c>
       <c t="n" r="G122">
-        <v>9.2504</v>
+        <v>9.2457</v>
       </c>
       <c t="n" r="H122">
-        <v>127.7413</v>
+        <v>127.7290</v>
       </c>
     </row>
     <row r="123">
       <c t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">RBG</t>
+          <t xml:space="preserve">NAG</t>
         </is>
       </c>
       <c t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AKS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C123">
-        <v>0.4543</v>
+        <v>0.0371</v>
       </c>
       <c t="n" r="D123">
-        <v>1.6846</v>
+        <v>-0.1157</v>
       </c>
       <c t="n" r="E123">
-        <v>6.5989</v>
+        <v>9.1730</v>
       </c>
       <c t="n" r="F123">
-        <v>1.2592</v>
+        <v>-0.0567</v>
       </c>
       <c t="n" r="G123">
-        <v>9.0238</v>
+        <v>9.0109</v>
+      </c>
+      <c t="n" r="H123">
+        <v>253.8367</v>
       </c>
     </row>
     <row r="124">
       <c t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">NAG</t>
+          <t xml:space="preserve">RBG</t>
         </is>
       </c>
       <c t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AKS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C124">
-        <v>0.0390</v>
+        <v>0.4586</v>
       </c>
       <c t="n" r="D124">
-        <v>-0.1154</v>
+        <v>1.6859</v>
       </c>
       <c t="n" r="E124">
-        <v>9.1730</v>
+        <v>6.6025</v>
       </c>
       <c t="n" r="F124">
-        <v>-0.0547</v>
+        <v>1.2635</v>
       </c>
       <c t="n" r="G124">
-        <v>9.0097</v>
-      </c>
-      <c t="n" r="H124">
-        <v>253.8437</v>
+        <v>8.7849</v>
       </c>
     </row>
     <row r="125">
@@ -3925,22 +3925,22 @@
         </is>
       </c>
       <c t="n" r="C125">
-        <v>0.1892</v>
+        <v>0.1886</v>
       </c>
       <c t="n" r="D125">
-        <v>0.4678</v>
+        <v>0.4695</v>
       </c>
       <c t="n" r="E125">
-        <v>3.9939</v>
+        <v>3.9956</v>
       </c>
       <c t="n" r="F125">
-        <v>0.5430</v>
+        <v>0.5424</v>
       </c>
       <c t="n" r="G125">
-        <v>8.6281</v>
+        <v>8.5982</v>
       </c>
       <c t="n" r="H125">
-        <v>244.3516</v>
+        <v>244.3494</v>
       </c>
     </row>
     <row r="126">
@@ -3955,19 +3955,19 @@
         </is>
       </c>
       <c t="n" r="C126">
-        <v>0.3942</v>
+        <v>0.3924</v>
       </c>
       <c t="n" r="D126">
-        <v>-1.9178</v>
+        <v>-1.9187</v>
       </c>
       <c t="n" r="E126">
-        <v>7.5289</v>
+        <v>7.5287</v>
       </c>
       <c t="n" r="F126">
-        <v>-1.4451</v>
+        <v>-1.4468</v>
       </c>
       <c t="n" r="G126">
-        <v>8.4467</v>
+        <v>8.4502</v>
       </c>
     </row>
     <row r="127">
@@ -3982,19 +3982,19 @@
         </is>
       </c>
       <c t="n" r="C127">
-        <v>-0.5002</v>
+        <v>-0.5051</v>
       </c>
       <c t="n" r="D127">
-        <v>-0.6566</v>
+        <v>-0.6578</v>
       </c>
       <c t="n" r="E127">
-        <v>8.8845</v>
+        <v>8.8824</v>
       </c>
       <c t="n" r="F127">
-        <v>-0.4915</v>
+        <v>-0.4964</v>
       </c>
       <c t="n" r="G127">
-        <v>8.3714</v>
+        <v>8.3615</v>
       </c>
     </row>
     <row r="128">
@@ -4012,16 +4012,16 @@
         <v>-0.3462</v>
       </c>
       <c t="n" r="D128">
-        <v>-0.2259</v>
+        <v>-0.2243</v>
       </c>
       <c t="n" r="E128">
-        <v>12.1007</v>
+        <v>12.1018</v>
       </c>
       <c t="n" r="F128">
         <v>-0.9776</v>
       </c>
       <c t="n" r="G128">
-        <v>7.6206</v>
+        <v>7.2824</v>
       </c>
       <c t="n" r="H128">
         <v>209.1013</v>
@@ -4039,22 +4039,22 @@
         </is>
       </c>
       <c t="n" r="C129">
-        <v>1.2815</v>
+        <v>1.2920</v>
       </c>
       <c t="n" r="D129">
-        <v>0.8690</v>
+        <v>0.8809</v>
       </c>
       <c t="n" r="E129">
-        <v>6.6102</v>
+        <v>6.6229</v>
       </c>
       <c t="n" r="F129">
-        <v>0.7809</v>
+        <v>0.7913</v>
       </c>
       <c t="n" r="G129">
-        <v>6.6640</v>
+        <v>6.6766</v>
       </c>
       <c t="n" r="H129">
-        <v>160.8044</v>
+        <v>160.8314</v>
       </c>
     </row>
     <row r="130">
@@ -4069,22 +4069,22 @@
         </is>
       </c>
       <c t="n" r="C130">
-        <v>-0.6800</v>
+        <v>-0.6730</v>
       </c>
       <c t="n" r="D130">
-        <v>-0.5165</v>
+        <v>-0.5086</v>
       </c>
       <c t="n" r="E130">
-        <v>5.9374</v>
+        <v>5.9462</v>
       </c>
       <c t="n" r="F130">
-        <v>-0.4413</v>
+        <v>-0.4343</v>
       </c>
       <c t="n" r="G130">
-        <v>6.6055</v>
+        <v>6.6165</v>
       </c>
       <c t="n" r="H130">
-        <v>110.6364</v>
+        <v>110.6512</v>
       </c>
     </row>
     <row r="131">
@@ -4111,7 +4111,7 @@
         <v>-0.3807</v>
       </c>
       <c t="n" r="G131">
-        <v>6.5278</v>
+        <v>6.5277</v>
       </c>
       <c t="n" r="H131">
         <v>233.3698</v>
@@ -4129,22 +4129,22 @@
         </is>
       </c>
       <c t="n" r="C132">
-        <v>-0.0486</v>
+        <v>-0.0498</v>
       </c>
       <c t="n" r="D132">
         <v>-0.1440</v>
       </c>
       <c t="n" r="E132">
-        <v>6.6173</v>
+        <v>6.6170</v>
       </c>
       <c t="n" r="F132">
-        <v>-0.1789</v>
+        <v>-0.1801</v>
       </c>
       <c t="n" r="G132">
-        <v>6.3474</v>
+        <v>6.3472</v>
       </c>
       <c t="n" r="H132">
-        <v>305.8538</v>
+        <v>305.8489</v>
       </c>
     </row>
     <row r="133">
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c t="n" r="C133">
-        <v>0.2977</v>
+        <v>0.3068</v>
       </c>
       <c t="n" r="D133">
-        <v>1.0192</v>
+        <v>0.9910</v>
       </c>
       <c t="n" r="E133">
-        <v>13.4278</v>
+        <v>13.4907</v>
       </c>
       <c t="n" r="F133">
-        <v>1.3304</v>
+        <v>1.3396</v>
       </c>
       <c t="n" r="G133">
-        <v>5.8187</v>
+        <v>5.8206</v>
       </c>
       <c t="n" r="H133">
-        <v>195.5744</v>
+        <v>195.6013</v>
       </c>
     </row>
     <row r="134">
@@ -4189,22 +4189,22 @@
         </is>
       </c>
       <c t="n" r="C134">
-        <v>0.3320</v>
+        <v>0.3332</v>
       </c>
       <c t="n" r="D134">
-        <v>1.2953</v>
+        <v>1.2966</v>
       </c>
       <c t="n" r="E134">
-        <v>11.4735</v>
+        <v>11.4763</v>
       </c>
       <c t="n" r="F134">
-        <v>1.5028</v>
+        <v>1.5040</v>
       </c>
       <c t="n" r="G134">
-        <v>5.6243</v>
+        <v>5.6038</v>
       </c>
       <c t="n" r="H134">
-        <v>154.3323</v>
+        <v>154.3353</v>
       </c>
     </row>
     <row r="135">
@@ -4219,22 +4219,22 @@
         </is>
       </c>
       <c t="n" r="C135">
-        <v>1.2275</v>
+        <v>1.2786</v>
       </c>
       <c t="n" r="D135">
-        <v>3.7551</v>
+        <v>3.7608</v>
       </c>
       <c t="n" r="E135">
-        <v>9.9631</v>
+        <v>10.0298</v>
       </c>
       <c t="n" r="F135">
-        <v>4.7050</v>
+        <v>4.7579</v>
       </c>
       <c t="n" r="G135">
-        <v>5.3550</v>
+        <v>5.4186</v>
       </c>
       <c t="n" r="H135">
-        <v>90.4208</v>
+        <v>90.5170</v>
       </c>
     </row>
     <row r="136">
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c t="n" r="C136">
-        <v>-0.0420</v>
+        <v>-0.0449</v>
       </c>
       <c t="n" r="D136">
-        <v>-0.1735</v>
+        <v>-0.1741</v>
       </c>
       <c t="n" r="E136">
-        <v>8.3674</v>
+        <v>8.3683</v>
       </c>
       <c t="n" r="F136">
-        <v>2.1408</v>
+        <v>2.1378</v>
       </c>
       <c t="n" r="G136">
-        <v>5.3196</v>
+        <v>5.3244</v>
       </c>
     </row>
     <row r="137">
@@ -4276,19 +4276,19 @@
         </is>
       </c>
       <c t="n" r="C137">
-        <v>0.1688</v>
+        <v>0.1684</v>
       </c>
       <c t="n" r="D137">
-        <v>-10.5440</v>
+        <v>-10.5563</v>
       </c>
       <c t="n" r="E137">
-        <v>0.2679</v>
+        <v>0.2566</v>
       </c>
       <c t="n" r="F137">
-        <v>-10.4662</v>
+        <v>-10.4666</v>
       </c>
       <c t="n" r="G137">
-        <v>4.7757</v>
+        <v>4.7354</v>
       </c>
     </row>
     <row r="138">
@@ -4303,22 +4303,22 @@
         </is>
       </c>
       <c t="n" r="C138">
-        <v>-0.2161</v>
+        <v>-0.2232</v>
       </c>
       <c t="n" r="D138">
-        <v>-0.6592</v>
+        <v>-0.6593</v>
       </c>
       <c t="n" r="E138">
-        <v>5.9040</v>
+        <v>5.9043</v>
       </c>
       <c t="n" r="F138">
-        <v>-0.8125</v>
+        <v>-0.8196</v>
       </c>
       <c t="n" r="G138">
-        <v>4.4768</v>
+        <v>4.4762</v>
       </c>
       <c t="n" r="H138">
-        <v>113.2899</v>
+        <v>113.2746</v>
       </c>
     </row>
     <row r="139">
@@ -4333,25 +4333,25 @@
         </is>
       </c>
       <c t="n" r="C139">
-        <v>-0.0283</v>
+        <v>-0.0314</v>
       </c>
       <c t="n" r="D139">
-        <v>-0.7748</v>
+        <v>-0.8558</v>
       </c>
       <c t="n" r="E139">
-        <v>0.9174</v>
+        <v>0.9661</v>
       </c>
       <c t="n" r="F139">
-        <v>-0.6228</v>
+        <v>-0.6259</v>
       </c>
       <c t="n" r="G139">
-        <v>4.3299</v>
+        <v>4.1739</v>
       </c>
       <c t="n" r="H139">
-        <v>89.3212</v>
+        <v>89.3154</v>
       </c>
       <c t="n" r="I139">
-        <v>58.4096</v>
+        <v>58.4047</v>
       </c>
     </row>
     <row r="140">
@@ -4366,19 +4366,19 @@
         </is>
       </c>
       <c t="n" r="C140">
-        <v>-0.5782</v>
+        <v>-0.5989</v>
       </c>
       <c t="n" r="D140">
-        <v>-1.6683</v>
+        <v>-1.6703</v>
       </c>
       <c t="n" r="E140">
-        <v>-14.9608</v>
+        <v>-14.9731</v>
       </c>
       <c t="n" r="F140">
-        <v>-2.6574</v>
+        <v>-2.6777</v>
       </c>
       <c t="n" r="G140">
-        <v>3.9073</v>
+        <v>3.8892</v>
       </c>
     </row>
     <row r="141">
@@ -4393,22 +4393,22 @@
         </is>
       </c>
       <c t="n" r="C141">
-        <v>-0.2144</v>
+        <v>-0.2200</v>
       </c>
       <c t="n" r="D141">
-        <v>-0.7719</v>
+        <v>-0.7718</v>
       </c>
       <c t="n" r="E141">
-        <v>0.7126</v>
+        <v>0.7128</v>
       </c>
       <c t="n" r="F141">
-        <v>-0.9706</v>
+        <v>-0.9762</v>
       </c>
       <c t="n" r="G141">
-        <v>3.5227</v>
+        <v>3.5200</v>
       </c>
       <c t="n" r="H141">
-        <v>171.0545</v>
+        <v>171.0391</v>
       </c>
     </row>
     <row r="142">
@@ -4423,22 +4423,22 @@
         </is>
       </c>
       <c t="n" r="C142">
-        <v>-0.0929</v>
+        <v>-0.0949</v>
       </c>
       <c t="n" r="D142">
-        <v>-0.2677</v>
+        <v>-0.2667</v>
       </c>
       <c t="n" r="E142">
-        <v>9.4824</v>
+        <v>9.4812</v>
       </c>
       <c t="n" r="F142">
-        <v>-0.3545</v>
+        <v>-0.3566</v>
       </c>
       <c t="n" r="G142">
-        <v>3.1554</v>
+        <v>3.1552</v>
       </c>
       <c t="n" r="H142">
-        <v>132.9031</v>
+        <v>132.8984</v>
       </c>
     </row>
     <row r="143">
@@ -4453,22 +4453,22 @@
         </is>
       </c>
       <c t="n" r="C143">
-        <v>-0.1885</v>
+        <v>-0.1864</v>
       </c>
       <c t="n" r="D143">
-        <v>-0.4126</v>
+        <v>-0.4107</v>
       </c>
       <c t="n" r="E143">
-        <v>16.4575</v>
+        <v>16.4595</v>
       </c>
       <c t="n" r="F143">
-        <v>-0.5738</v>
+        <v>-0.5716</v>
       </c>
       <c t="n" r="G143">
-        <v>3.0060</v>
+        <v>3.0082</v>
       </c>
       <c t="n" r="H143">
-        <v>268.5039</v>
+        <v>268.5118</v>
       </c>
     </row>
     <row r="144">
@@ -4483,76 +4483,76 @@
         </is>
       </c>
       <c t="n" r="C144">
-        <v>1.2554</v>
+        <v>1.2388</v>
       </c>
       <c t="n" r="D144">
-        <v>1.3917</v>
+        <v>1.3498</v>
       </c>
       <c t="n" r="E144">
-        <v>5.0289</v>
+        <v>5.0025</v>
       </c>
       <c t="n" r="F144">
-        <v>-0.6623</v>
+        <v>-0.6786</v>
       </c>
       <c t="n" r="G144">
-        <v>2.9116</v>
+        <v>2.8545</v>
       </c>
       <c t="n" r="H144">
-        <v>266.2984</v>
+        <v>266.2381</v>
       </c>
     </row>
     <row r="145">
       <c t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">NFE</t>
+          <t xml:space="preserve">RBU</t>
         </is>
       </c>
       <c t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C145">
-        <v>-0.6819</v>
+        <v>0.6693</v>
       </c>
       <c t="n" r="D145">
-        <v>-1.5502</v>
+        <v>-1.9239</v>
       </c>
       <c t="n" r="E145">
-        <v>99.2573</v>
+        <v>1.9097</v>
       </c>
       <c t="n" r="F145">
-        <v>-2.1535</v>
+        <v>-1.1910</v>
       </c>
       <c t="n" r="G145">
-        <v>2.9110</v>
+        <v>2.5579</v>
       </c>
     </row>
     <row r="146">
       <c t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">RBU</t>
+          <t xml:space="preserve">NFE</t>
         </is>
       </c>
       <c t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C146">
-        <v>0.6678</v>
+        <v>-0.6878</v>
       </c>
       <c t="n" r="D146">
-        <v>-1.9225</v>
+        <v>-1.5553</v>
       </c>
       <c t="n" r="E146">
-        <v>1.9086</v>
+        <v>99.0519</v>
       </c>
       <c t="n" r="F146">
-        <v>-1.1923</v>
+        <v>-2.1593</v>
       </c>
       <c t="n" r="G146">
-        <v>2.5556</v>
+        <v>2.5514</v>
       </c>
     </row>
     <row r="147">
@@ -4567,22 +4567,22 @@
         </is>
       </c>
       <c t="n" r="C147">
-        <v>0.0012</v>
+        <v>0.0004</v>
       </c>
       <c t="n" r="D147">
-        <v>-0.3226</v>
+        <v>-0.3224</v>
       </c>
       <c t="n" r="E147">
         <v>7.8820</v>
       </c>
       <c t="n" r="F147">
-        <v>-0.3749</v>
+        <v>-0.3756</v>
       </c>
       <c t="n" r="G147">
-        <v>2.2706</v>
+        <v>2.2540</v>
       </c>
       <c t="n" r="H147">
-        <v>131.0189</v>
+        <v>131.0172</v>
       </c>
     </row>
     <row r="148">
@@ -4597,19 +4597,19 @@
         </is>
       </c>
       <c t="n" r="C148">
-        <v>-1.9890</v>
+        <v>-1.9881</v>
       </c>
       <c t="n" r="D148">
-        <v>-1.7294</v>
+        <v>-1.7291</v>
       </c>
       <c t="n" r="E148">
-        <v>3.6885</v>
+        <v>3.6889</v>
       </c>
       <c t="n" r="F148">
-        <v>-1.5745</v>
+        <v>-1.5736</v>
       </c>
       <c t="n" r="G148">
-        <v>1.0933</v>
+        <v>1.0904</v>
       </c>
     </row>
     <row r="149">
@@ -4624,61 +4624,61 @@
         </is>
       </c>
       <c t="n" r="C149">
-        <v>-0.1248</v>
+        <v>-0.1198</v>
       </c>
       <c t="n" r="D149">
-        <v>-0.6709</v>
+        <v>-0.6694</v>
       </c>
       <c t="n" r="E149">
-        <v>2.1695</v>
+        <v>2.1738</v>
       </c>
       <c t="n" r="F149">
-        <v>-1.6195</v>
+        <v>-1.6146</v>
       </c>
       <c t="n" r="G149">
-        <v>1.0741</v>
+        <v>1.0824</v>
       </c>
       <c t="n" r="H149">
-        <v>69.7759</v>
+        <v>69.7845</v>
       </c>
     </row>
     <row r="150">
       <c t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">RF3</t>
+          <t xml:space="preserve">BKA</t>
         </is>
       </c>
       <c t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C150">
-        <v>-0.1823</v>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ANKA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="D150">
-        <v>-0.7027</v>
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="E150">
+        <v>0.0000</v>
       </c>
       <c t="n" r="F150">
-        <v>-0.9534</v>
+        <v>0.0000</v>
       </c>
       <c t="n" r="G150">
-        <v>0.0893</v>
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="H150">
+        <v>0.0000</v>
       </c>
     </row>
     <row r="151">
       <c t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">BKA</t>
+          <t xml:space="preserve">HP5</t>
         </is>
       </c>
       <c t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ANKA GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="D151">
-        <v>0.0000</v>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="E151">
         <v>0.0000</v>
@@ -4689,19 +4689,16 @@
       <c t="n" r="G151">
         <v>0.0000</v>
       </c>
-      <c t="n" r="H151">
-        <v>0.0000</v>
-      </c>
     </row>
     <row r="152">
       <c t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">HP5</t>
+          <t xml:space="preserve">HP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ MASTERTÜRK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="E152">
@@ -4717,13 +4714,19 @@
     <row r="153">
       <c t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">HP4</t>
+          <t xml:space="preserve">NGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ MASTERTÜRK GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C153">
+        <v>0.0000</v>
+      </c>
+      <c t="n" r="D153">
+        <v>0.0000</v>
       </c>
       <c t="n" r="E153">
         <v>0.0000</v>
@@ -4738,16 +4741,13 @@
     <row r="154">
       <c t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">NGA</t>
+          <t xml:space="preserve">NFA</t>
         </is>
       </c>
       <c t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">INVEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="C154">
-        <v>0.0000</v>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU PROJE GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="D154">
         <v>0.0000</v>
@@ -4765,12 +4765,12 @@
     <row r="155">
       <c t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">NFA</t>
+          <t xml:space="preserve">RF1</t>
         </is>
       </c>
       <c t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FENERCİOĞLU PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D155">
@@ -4789,22 +4789,13 @@
     <row r="156">
       <c t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">RF1</t>
+          <t xml:space="preserve">RDO</t>
         </is>
       </c>
       <c t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
-        </is>
-      </c>
-      <c t="n" r="D156">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="E156">
-        <v>0.0000</v>
-      </c>
-      <c t="n" r="F156">
-        <v>0.0000</v>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN OTEL GAYRİMENKUL YATIRIM FONU</t>
+        </is>
       </c>
       <c t="n" r="G156">
         <v>0.0000</v>
@@ -4813,12 +4804,12 @@
     <row r="157">
       <c t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">RDO</t>
+          <t xml:space="preserve">RMK</t>
         </is>
       </c>
       <c t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. DOWNTOWN OTEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EMLAK KATILIM YENİ EVİM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G157">
@@ -4828,12 +4819,12 @@
     <row r="158">
       <c t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">RMK</t>
+          <t xml:space="preserve">RF2</t>
         </is>
       </c>
       <c t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. EMLAK KATILIM YENİ EVİM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G158">
@@ -4843,12 +4834,12 @@
     <row r="159">
       <c t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">RF2</t>
+          <t xml:space="preserve">RSM</t>
         </is>
       </c>
       <c t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SMART PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G159">
@@ -4858,12 +4849,12 @@
     <row r="160">
       <c t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">RSM</t>
+          <t xml:space="preserve">RSO</t>
         </is>
       </c>
       <c t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SMART PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SONNE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G160">
@@ -4873,12 +4864,12 @@
     <row r="161">
       <c t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">RSO</t>
+          <t xml:space="preserve">RTO</t>
         </is>
       </c>
       <c t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SONNE PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TOROS PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="G161">
@@ -4888,16 +4879,25 @@
     <row r="162">
       <c t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">RTO</t>
+          <t xml:space="preserve">RF3</t>
         </is>
       </c>
       <c t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TOROS PROJE GAYRİMENKUL YATIRIM FONU</t>
-        </is>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="C162">
+        <v>-0.1863</v>
+      </c>
+      <c t="n" r="D162">
+        <v>-0.7035</v>
+      </c>
+      <c t="n" r="F162">
+        <v>-0.9574</v>
       </c>
       <c t="n" r="G162">
-        <v>0.0000</v>
+        <v>-0.1662</v>
       </c>
     </row>
     <row r="163">
@@ -4912,25 +4912,25 @@
         </is>
       </c>
       <c t="n" r="C163">
-        <v>0.2551</v>
+        <v>0.1915</v>
       </c>
       <c t="n" r="D163">
-        <v>8.6869</v>
+        <v>8.6893</v>
       </c>
       <c t="n" r="E163">
-        <v>17.0852</v>
+        <v>17.0000</v>
       </c>
       <c t="n" r="F163">
-        <v>8.9887</v>
+        <v>8.9196</v>
       </c>
       <c t="n" r="G163">
-        <v>-0.5147</v>
+        <v>-0.5832</v>
       </c>
       <c t="n" r="H163">
-        <v>153.1449</v>
+        <v>152.9843</v>
       </c>
       <c t="n" r="I163">
-        <v>496.2134</v>
+        <v>495.8387</v>
       </c>
     </row>
     <row r="164">
@@ -4945,19 +4945,19 @@
         </is>
       </c>
       <c t="n" r="C164">
-        <v>-0.2510</v>
+        <v>-0.2599</v>
       </c>
       <c t="n" r="D164">
-        <v>-0.7737</v>
+        <v>-0.7753</v>
       </c>
       <c t="n" r="E164">
-        <v>-0.2719</v>
+        <v>-0.2735</v>
       </c>
       <c t="n" r="F164">
-        <v>-0.9070</v>
+        <v>-0.9158</v>
       </c>
       <c t="n" r="G164">
-        <v>-1.5964</v>
+        <v>-1.5981</v>
       </c>
     </row>
     <row r="165">
@@ -4972,19 +4972,19 @@
         </is>
       </c>
       <c t="n" r="C165">
-        <v>-2.2274</v>
+        <v>-2.2539</v>
       </c>
       <c t="n" r="D165">
-        <v>-7.6270</v>
+        <v>-7.6342</v>
       </c>
       <c t="n" r="E165">
-        <v>-11.9595</v>
+        <v>-11.9808</v>
       </c>
       <c t="n" r="F165">
-        <v>-10.3745</v>
+        <v>-10.3989</v>
       </c>
       <c t="n" r="G165">
-        <v>-7.5754</v>
+        <v>-7.5973</v>
       </c>
     </row>
     <row r="166">
@@ -4999,22 +4999,22 @@
         </is>
       </c>
       <c t="n" r="C166">
-        <v>5.7273</v>
+        <v>6.2324</v>
       </c>
       <c t="n" r="D166">
-        <v>2.4592</v>
+        <v>3.7936</v>
       </c>
       <c t="n" r="E166">
-        <v>0.6985</v>
+        <v>1.8256</v>
       </c>
       <c t="n" r="F166">
-        <v>4.6691</v>
+        <v>5.1692</v>
       </c>
       <c t="n" r="G166">
-        <v>-8.3277</v>
+        <v>-8.0115</v>
       </c>
       <c t="n" r="H166">
-        <v>93.3456</v>
+        <v>94.2693</v>
       </c>
     </row>
     <row r="167">
@@ -5029,19 +5029,19 @@
         </is>
       </c>
       <c t="n" r="C167">
-        <v>0.3905</v>
+        <v>0.3908</v>
       </c>
       <c t="n" r="D167">
-        <v>-0.5716</v>
+        <v>-0.5723</v>
       </c>
       <c t="n" r="E167">
-        <v>2.4323</v>
+        <v>2.4330</v>
       </c>
       <c t="n" r="F167">
-        <v>-0.2936</v>
+        <v>-0.2932</v>
       </c>
       <c t="n" r="G167">
-        <v>-11.4512</v>
+        <v>-11.4502</v>
       </c>
     </row>
     <row r="168">
@@ -5056,19 +5056,19 @@
         </is>
       </c>
       <c t="n" r="C168">
-        <v>0.1932</v>
+        <v>0.1994</v>
       </c>
       <c t="n" r="D168">
-        <v>4.3800</v>
+        <v>4.3876</v>
       </c>
       <c t="n" r="E168">
-        <v>4.8187</v>
+        <v>4.8263</v>
       </c>
       <c t="n" r="F168">
-        <v>4.1264</v>
+        <v>4.1329</v>
       </c>
       <c t="n" r="G168">
-        <v>-13.3637</v>
+        <v>-13.3574</v>
       </c>
     </row>
     <row r="169">
@@ -5083,22 +5083,22 @@
         </is>
       </c>
       <c t="n" r="C169">
-        <v>-0.0356</v>
+        <v>-0.0364</v>
       </c>
       <c t="n" r="D169">
-        <v>-0.1093</v>
+        <v>-0.1094</v>
       </c>
       <c t="n" r="E169">
-        <v>-17.3178</v>
+        <v>-17.3181</v>
       </c>
       <c t="n" r="F169">
-        <v>-0.1356</v>
+        <v>-0.1364</v>
       </c>
       <c t="n" r="G169">
-        <v>-13.9681</v>
+        <v>-13.9692</v>
       </c>
       <c t="n" r="H169">
-        <v>196.2719</v>
+        <v>196.2695</v>
       </c>
     </row>
     <row r="170">
@@ -5113,22 +5113,22 @@
         </is>
       </c>
       <c t="n" r="C170">
-        <v>-0.5388</v>
+        <v>-0.5000</v>
       </c>
       <c t="n" r="D170">
-        <v>-1.5655</v>
+        <v>-1.5151</v>
       </c>
       <c t="n" r="E170">
-        <v>-17.3552</v>
+        <v>-17.3128</v>
       </c>
       <c t="n" r="F170">
-        <v>-1.8287</v>
+        <v>-1.7905</v>
       </c>
       <c t="n" r="G170">
-        <v>-18.5119</v>
+        <v>-18.4620</v>
       </c>
       <c t="n" r="H170">
-        <v>-2.9056</v>
+        <v>-2.8678</v>
       </c>
     </row>
     <row r="171">
@@ -5143,22 +5143,22 @@
         </is>
       </c>
       <c t="n" r="C171">
-        <v>0.1064</v>
+        <v>0.1066</v>
       </c>
       <c t="n" r="D171">
-        <v>-0.5639</v>
+        <v>-0.5574</v>
       </c>
       <c t="n" r="E171">
-        <v>-17.9133</v>
+        <v>-17.9113</v>
       </c>
       <c t="n" r="F171">
-        <v>-0.0608</v>
+        <v>-0.0606</v>
       </c>
       <c t="n" r="G171">
-        <v>-18.7662</v>
+        <v>-18.7669</v>
       </c>
       <c t="n" r="H171">
-        <v>91.3537</v>
+        <v>91.3540</v>
       </c>
     </row>
     <row r="172">
@@ -5173,22 +5173,22 @@
         </is>
       </c>
       <c t="n" r="C172">
-        <v>-0.2887</v>
+        <v>-0.2961</v>
       </c>
       <c t="n" r="D172">
-        <v>-0.8459</v>
+        <v>-0.8460</v>
       </c>
       <c t="n" r="E172">
-        <v>-23.3516</v>
+        <v>-23.3518</v>
       </c>
       <c t="n" r="F172">
-        <v>-1.0030</v>
+        <v>-1.0104</v>
       </c>
       <c t="n" r="G172">
-        <v>-24.4701</v>
+        <v>-24.4712</v>
       </c>
       <c t="n" r="H172">
-        <v>350.3243</v>
+        <v>350.2910</v>
       </c>
     </row>
     <row r="173">
@@ -5215,7 +5215,7 @@
         <v>-0.0611</v>
       </c>
       <c t="n" r="G173">
-        <v>-24.5005</v>
+        <v>-24.5006</v>
       </c>
     </row>
     <row r="174">
@@ -5230,25 +5230,25 @@
         </is>
       </c>
       <c t="n" r="C174">
-        <v>-0.0793</v>
+        <v>-0.0797</v>
       </c>
       <c t="n" r="D174">
-        <v>-0.2743</v>
+        <v>-0.2741</v>
       </c>
       <c t="n" r="E174">
-        <v>-50.8301</v>
+        <v>-50.8584</v>
       </c>
       <c t="n" r="F174">
-        <v>-1.0508</v>
+        <v>-1.0512</v>
       </c>
       <c t="n" r="G174">
-        <v>-30.3231</v>
+        <v>-30.3213</v>
       </c>
       <c t="n" r="H174">
-        <v>71.0695</v>
+        <v>71.0687</v>
       </c>
       <c t="n" r="I174">
-        <v>785.1506</v>
+        <v>785.1469</v>
       </c>
     </row>
     <row r="175">
@@ -5263,22 +5263,22 @@
         </is>
       </c>
       <c t="n" r="C175">
-        <v>-0.6640</v>
+        <v>-0.6761</v>
       </c>
       <c t="n" r="D175">
-        <v>-1.7550</v>
+        <v>-1.7562</v>
       </c>
       <c t="n" r="E175">
-        <v>-30.4570</v>
+        <v>-30.4572</v>
       </c>
       <c t="n" r="F175">
-        <v>-1.9756</v>
+        <v>-1.9875</v>
       </c>
       <c t="n" r="G175">
-        <v>-30.8404</v>
+        <v>-30.8591</v>
       </c>
       <c t="n" r="H175">
-        <v>102.9667</v>
+        <v>102.9420</v>
       </c>
     </row>
     <row r="176">
@@ -5293,22 +5293,22 @@
         </is>
       </c>
       <c t="n" r="C176">
-        <v>-0.1993</v>
+        <v>-0.2032</v>
       </c>
       <c t="n" r="D176">
-        <v>-3.4679</v>
+        <v>-3.4684</v>
       </c>
       <c t="n" r="E176">
-        <v>5.0829</v>
+        <v>5.0805</v>
       </c>
       <c t="n" r="F176">
-        <v>-7.3493</v>
+        <v>-7.3529</v>
       </c>
       <c t="n" r="G176">
-        <v>-40.9134</v>
+        <v>-40.9140</v>
       </c>
       <c t="n" r="H176">
-        <v>113.6578</v>
+        <v>113.6496</v>
       </c>
     </row>
     <row r="177">
@@ -5323,25 +5323,25 @@
         </is>
       </c>
       <c t="n" r="C177">
-        <v>-0.4535</v>
+        <v>-0.4562</v>
       </c>
       <c t="n" r="D177">
-        <v>-18.5805</v>
+        <v>-18.6061</v>
       </c>
       <c t="n" r="E177">
-        <v>-40.7789</v>
+        <v>-40.7793</v>
       </c>
       <c t="n" r="F177">
-        <v>-52.0181</v>
+        <v>-52.0194</v>
       </c>
       <c t="n" r="G177">
-        <v>-41.6894</v>
+        <v>-41.6931</v>
       </c>
       <c t="n" r="H177">
-        <v>-2.5842</v>
+        <v>-2.5869</v>
       </c>
       <c t="n" r="I177">
-        <v>217.4404</v>
+        <v>217.4316</v>
       </c>
     </row>
     <row r="178">
@@ -5356,22 +5356,22 @@
         </is>
       </c>
       <c t="n" r="C178">
-        <v>-0.1431</v>
+        <v>-0.1449</v>
       </c>
       <c t="n" r="D178">
-        <v>-23.7544</v>
+        <v>-23.7543</v>
       </c>
       <c t="n" r="E178">
-        <v>-23.0577</v>
+        <v>-23.0589</v>
       </c>
       <c t="n" r="F178">
-        <v>-26.0910</v>
+        <v>-26.0923</v>
       </c>
       <c t="n" r="G178">
-        <v>-43.1301</v>
+        <v>-43.1303</v>
       </c>
       <c t="n" r="H178">
-        <v>40.5781</v>
+        <v>40.5756</v>
       </c>
     </row>
     <row r="179">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c t="n" r="C179">
-        <v>-82.0672</v>
+        <v>-82.0808</v>
       </c>
       <c t="n" r="D179">
-        <v>-83.9768</v>
+        <v>-83.9860</v>
       </c>
       <c t="n" r="E179">
-        <v>-76.3482</v>
+        <v>-76.3643</v>
       </c>
       <c t="n" r="F179">
-        <v>-84.0030</v>
+        <v>-84.0151</v>
       </c>
       <c t="n" r="G179">
-        <v>-54.6331</v>
+        <v>-54.9490</v>
       </c>
     </row>
     <row r="180">
@@ -5413,25 +5413,25 @@
         </is>
       </c>
       <c t="n" r="C180">
-        <v>4.8453</v>
+        <v>4.4745</v>
       </c>
       <c t="n" r="D180">
-        <v>7.3039</v>
+        <v>7.1791</v>
       </c>
       <c t="n" r="E180">
-        <v>-9.8290</v>
+        <v>-10.1452</v>
       </c>
       <c t="n" r="F180">
-        <v>-12.2357</v>
+        <v>-12.5461</v>
       </c>
       <c t="n" r="G180">
-        <v>-58.6812</v>
+        <v>-58.8306</v>
       </c>
       <c t="n" r="H180">
-        <v>-19.4641</v>
+        <v>-19.7489</v>
       </c>
       <c t="n" r="I180">
-        <v>338.0764</v>
+        <v>336.5008</v>
       </c>
     </row>
     <row r="181">
@@ -5446,85 +5446,85 @@
         </is>
       </c>
       <c t="n" r="C181">
-        <v>-1.2938</v>
+        <v>-1.3057</v>
       </c>
       <c t="n" r="D181">
-        <v>37.1716</v>
+        <v>37.2208</v>
       </c>
       <c t="n" r="E181">
-        <v>-63.4845</v>
+        <v>-63.5001</v>
       </c>
       <c t="n" r="F181">
-        <v>55.0658</v>
+        <v>55.0471</v>
       </c>
       <c t="n" r="G181">
-        <v>-66.2332</v>
+        <v>-66.1619</v>
       </c>
       <c t="n" r="H181">
-        <v>-68.8926</v>
+        <v>-68.8963</v>
       </c>
       <c t="n" r="I181">
-        <v>-16.3326</v>
+        <v>-16.3364</v>
       </c>
     </row>
     <row r="182">
       <c t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">GF3</t>
+          <t xml:space="preserve">YD1</t>
         </is>
       </c>
       <c t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C182">
-        <v>-26.6546</v>
+        <v>-24.8495</v>
       </c>
       <c t="n" r="D182">
-        <v>-40.6434</v>
+        <v>-76.9875</v>
       </c>
       <c t="n" r="E182">
-        <v>455.9669</v>
+        <v>-75.8070</v>
       </c>
       <c t="n" r="F182">
-        <v>-40.6725</v>
+        <v>-77.0424</v>
       </c>
       <c t="n" r="G182">
-        <v>-67.1365</v>
+        <v>-67.2779</v>
+      </c>
+      <c t="n" r="H182">
+        <v>-84.9145</v>
+      </c>
+      <c t="n" r="I182">
+        <v>-44.9125</v>
       </c>
     </row>
     <row r="183">
       <c t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">YD1</t>
+          <t xml:space="preserve">GF3</t>
         </is>
       </c>
       <c t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C183">
-        <v>-24.7767</v>
+        <v>-44.9491</v>
       </c>
       <c t="n" r="D183">
-        <v>-76.9671</v>
+        <v>-55.4436</v>
       </c>
       <c t="n" r="E183">
-        <v>-75.7841</v>
+        <v>329.9094</v>
       </c>
       <c t="n" r="F183">
-        <v>-77.0202</v>
+        <v>-55.4706</v>
       </c>
       <c t="n" r="G183">
-        <v>-67.3223</v>
-      </c>
-      <c t="n" r="H183">
-        <v>-84.8999</v>
-      </c>
-      <c t="n" r="I183">
-        <v>-44.8592</v>
+        <v>-75.1606</v>
       </c>
     </row>
     <row r="184">
@@ -5551,7 +5551,7 @@
         <v>-93.9130</v>
       </c>
       <c t="n" r="G184">
-        <v>-99.0291</v>
+        <v>-91.7647</v>
       </c>
       <c t="n" r="H184">
         <v>-99.9998</v>
@@ -5569,22 +5569,22 @@
         </is>
       </c>
       <c t="n" r="C185">
-        <v>-98.8766</v>
+        <v>-98.8675</v>
       </c>
       <c t="n" r="D185">
-        <v>-99.1091</v>
+        <v>-99.1019</v>
       </c>
       <c t="n" r="E185">
-        <v>-99.0544</v>
+        <v>-99.0468</v>
       </c>
       <c t="n" r="F185">
-        <v>-99.1168</v>
+        <v>-99.1096</v>
       </c>
       <c t="n" r="G185">
-        <v>-99.1527</v>
+        <v>-99.1458</v>
       </c>
       <c t="n" r="H185">
-        <v>-98.5554</v>
+        <v>-98.5437</v>
       </c>
     </row>
     <row r="186">
@@ -5647,13 +5647,16 @@
         </is>
       </c>
       <c t="n" r="C190">
-        <v>1.5578</v>
+        <v>1.6395</v>
       </c>
       <c t="n" r="D190">
-        <v>3.5185</v>
+        <v>3.5891</v>
+      </c>
+      <c t="n" r="E190">
+        <v>33.6716</v>
       </c>
       <c t="n" r="F190">
-        <v>4.2956</v>
+        <v>4.3796</v>
       </c>
     </row>
     <row r="191">
@@ -5692,13 +5695,13 @@
         </is>
       </c>
       <c t="n" r="C193">
-        <v>-17.0496</v>
+        <v>-17.6562</v>
       </c>
       <c t="n" r="D193">
-        <v>-39.4738</v>
+        <v>-39.6736</v>
       </c>
       <c t="n" r="F193">
-        <v>-43.5962</v>
+        <v>-44.0086</v>
       </c>
     </row>
     <row r="194">
@@ -5713,13 +5716,13 @@
         </is>
       </c>
       <c t="n" r="C194">
-        <v>-9.9376</v>
+        <v>-9.8075</v>
       </c>
       <c t="n" r="D194">
-        <v>-63.1119</v>
+        <v>-63.1159</v>
       </c>
       <c t="n" r="F194">
-        <v>-27.7406</v>
+        <v>-27.6363</v>
       </c>
     </row>
     <row r="195">
@@ -5746,7 +5749,7 @@
         </is>
       </c>
       <c t="n" r="C196">
-        <v>1.6073</v>
+        <v>1.6041</v>
       </c>
     </row>
     <row r="197">
@@ -5761,13 +5764,13 @@
         </is>
       </c>
       <c t="n" r="C197">
-        <v>0.8132</v>
+        <v>0.8135</v>
       </c>
       <c t="n" r="D197">
-        <v>1.9946</v>
+        <v>1.9953</v>
       </c>
       <c t="n" r="F197">
-        <v>1.8860</v>
+        <v>1.8864</v>
       </c>
     </row>
     <row r="198">
@@ -5854,10 +5857,10 @@
         </is>
       </c>
       <c t="n" r="C204">
-        <v>0.5891</v>
+        <v>0.6228</v>
       </c>
       <c t="n" r="D204">
-        <v>2.4948</v>
+        <v>2.7001</v>
       </c>
     </row>
     <row r="205">
@@ -5872,16 +5875,16 @@
         </is>
       </c>
       <c t="n" r="C205">
-        <v>1.9286</v>
+        <v>1.9971</v>
       </c>
       <c t="n" r="D205">
-        <v>417.5734</v>
+        <v>417.3992</v>
       </c>
       <c t="n" r="E205">
-        <v>460.3801</v>
+        <v>460.2199</v>
       </c>
       <c t="n" r="F205">
-        <v>426.9139</v>
+        <v>427.2679</v>
       </c>
     </row>
     <row r="206">
@@ -5896,16 +5899,16 @@
         </is>
       </c>
       <c t="n" r="C206">
-        <v>11.8744</v>
+        <v>11.8776</v>
       </c>
       <c t="n" r="D206">
-        <v>43.5363</v>
+        <v>43.3977</v>
       </c>
       <c t="n" r="E206">
-        <v>57.9499</v>
+        <v>57.7743</v>
       </c>
       <c t="n" r="F206">
-        <v>46.4322</v>
+        <v>46.4364</v>
       </c>
     </row>
     <row r="207">
@@ -5932,16 +5935,16 @@
         </is>
       </c>
       <c t="n" r="C208">
-        <v>-0.0452</v>
+        <v>-0.0464</v>
       </c>
       <c t="n" r="D208">
-        <v>-0.1105</v>
+        <v>-0.1107</v>
       </c>
       <c t="n" r="E208">
-        <v>19.3810</v>
+        <v>19.3780</v>
       </c>
       <c t="n" r="F208">
-        <v>-0.1441</v>
+        <v>-0.1452</v>
       </c>
     </row>
     <row r="209">
@@ -5956,7 +5959,7 @@
         </is>
       </c>
       <c t="n" r="C209">
-        <v>-0.0155</v>
+        <v>-0.0131</v>
       </c>
     </row>
     <row r="210">
@@ -5983,16 +5986,16 @@
         </is>
       </c>
       <c t="n" r="C211">
-        <v>3.3300</v>
+        <v>3.4643</v>
       </c>
       <c t="n" r="D211">
-        <v>9.1541</v>
+        <v>9.1821</v>
       </c>
       <c t="n" r="E211">
-        <v>19.6049</v>
+        <v>19.6354</v>
       </c>
       <c t="n" r="F211">
-        <v>11.3627</v>
+        <v>11.5074</v>
       </c>
     </row>
     <row r="212">
@@ -6019,13 +6022,13 @@
         </is>
       </c>
       <c t="n" r="C213">
-        <v>-0.1075</v>
+        <v>-0.1074</v>
       </c>
       <c t="n" r="D213">
-        <v>-0.3216</v>
+        <v>-0.3215</v>
       </c>
       <c t="n" r="F213">
-        <v>-0.3291</v>
+        <v>-0.3290</v>
       </c>
     </row>
     <row r="214">
@@ -6040,10 +6043,10 @@
         </is>
       </c>
       <c t="n" r="C214">
-        <v>-0.9158</v>
+        <v>-0.9437</v>
       </c>
       <c t="n" r="D214">
-        <v>6.7112</v>
+        <v>6.7113</v>
       </c>
     </row>
     <row r="215">
@@ -6058,7 +6061,7 @@
         </is>
       </c>
       <c t="n" r="C215">
-        <v>-0.2094</v>
+        <v>-0.1586</v>
       </c>
     </row>
     <row r="216">
@@ -6073,16 +6076,16 @@
         </is>
       </c>
       <c t="n" r="C216">
-        <v>-0.0352</v>
+        <v>-0.0363</v>
       </c>
       <c t="n" r="D216">
-        <v>-0.0996</v>
+        <v>-0.0997</v>
       </c>
       <c t="n" r="E216">
-        <v>12.7793</v>
+        <v>12.7791</v>
       </c>
       <c t="n" r="F216">
-        <v>-0.1204</v>
+        <v>-0.1215</v>
       </c>
     </row>
     <row r="217">
@@ -6097,16 +6100,16 @@
         </is>
       </c>
       <c t="n" r="C217">
-        <v>-0.0086</v>
+        <v>-0.0088</v>
       </c>
       <c t="n" r="D217">
-        <v>2.7789</v>
+        <v>2.7775</v>
       </c>
       <c t="n" r="E217">
-        <v>12.4946</v>
+        <v>12.4879</v>
       </c>
       <c t="n" r="F217">
-        <v>3.1035</v>
+        <v>3.1033</v>
       </c>
     </row>
     <row r="218">
@@ -6121,16 +6124,16 @@
         </is>
       </c>
       <c t="n" r="C218">
-        <v>-96.4626</v>
+        <v>-97.7895</v>
       </c>
       <c t="n" r="D218">
-        <v>-99.9642</v>
+        <v>-99.9777</v>
       </c>
       <c t="n" r="E218">
-        <v>-99.9966</v>
+        <v>-99.9979</v>
       </c>
       <c t="n" r="F218">
-        <v>-99.9940</v>
+        <v>-99.9962</v>
       </c>
     </row>
     <row r="219">
@@ -6253,16 +6256,16 @@
         </is>
       </c>
       <c t="n" r="C228">
-        <v>9.0264</v>
+        <v>8.5369</v>
       </c>
       <c t="n" r="D228">
-        <v>4.6562</v>
+        <v>4.6235</v>
       </c>
       <c t="n" r="E228">
-        <v>19.6239</v>
+        <v>18.9646</v>
       </c>
       <c t="n" r="F228">
-        <v>14.8585</v>
+        <v>14.3428</v>
       </c>
     </row>
     <row r="229">
@@ -6301,16 +6304,16 @@
         </is>
       </c>
       <c t="n" r="C231">
-        <v>1.1789</v>
+        <v>1.2802</v>
       </c>
       <c t="n" r="D231">
-        <v>5.2221</v>
+        <v>5.2414</v>
       </c>
       <c t="n" r="E231">
-        <v>13.8678</v>
+        <v>13.8745</v>
       </c>
       <c t="n" r="F231">
-        <v>7.1575</v>
+        <v>7.2648</v>
       </c>
     </row>
     <row r="232">
@@ -6325,16 +6328,16 @@
         </is>
       </c>
       <c t="n" r="C232">
-        <v>3.0568</v>
+        <v>3.1623</v>
       </c>
       <c t="n" r="D232">
-        <v>9.5355</v>
+        <v>9.5353</v>
       </c>
       <c t="n" r="E232">
-        <v>20.7331</v>
+        <v>20.7369</v>
       </c>
       <c t="n" r="F232">
-        <v>11.6886</v>
+        <v>11.8030</v>
       </c>
     </row>
     <row r="233">
@@ -6349,16 +6352,16 @@
         </is>
       </c>
       <c t="n" r="C233">
-        <v>1.3693</v>
+        <v>1.3619</v>
       </c>
       <c t="n" r="D233">
-        <v>1.6369</v>
+        <v>1.6518</v>
       </c>
       <c t="n" r="E233">
-        <v>4.0882</v>
+        <v>4.0245</v>
       </c>
       <c t="n" r="F233">
-        <v>2.2589</v>
+        <v>2.2514</v>
       </c>
     </row>
     <row r="234">
@@ -6385,16 +6388,16 @@
         </is>
       </c>
       <c t="n" r="C235">
-        <v>1.2658</v>
+        <v>1.3671</v>
       </c>
       <c t="n" r="D235">
-        <v>5.3124</v>
+        <v>5.3317</v>
       </c>
       <c t="n" r="E235">
-        <v>13.9655</v>
+        <v>13.9721</v>
       </c>
       <c t="n" r="F235">
-        <v>7.2495</v>
+        <v>7.3568</v>
       </c>
     </row>
     <row r="236">
@@ -6445,13 +6448,13 @@
         </is>
       </c>
       <c t="n" r="C239">
-        <v>-1.4611</v>
+        <v>-1.4737</v>
       </c>
       <c t="n" r="D239">
-        <v>-80.5190</v>
+        <v>-80.2310</v>
       </c>
       <c t="n" r="F239">
-        <v>-84.7413</v>
+        <v>-84.7433</v>
       </c>
     </row>
     <row r="240">
@@ -6490,16 +6493,16 @@
         </is>
       </c>
       <c t="n" r="C242">
-        <v>-0.0647</v>
+        <v>-0.0669</v>
       </c>
       <c t="n" r="D242">
-        <v>-0.2345</v>
+        <v>-0.2343</v>
       </c>
       <c t="n" r="E242">
-        <v>1624.4586</v>
+        <v>1624.3930</v>
       </c>
       <c t="n" r="F242">
-        <v>-0.2739</v>
+        <v>-0.2761</v>
       </c>
     </row>
     <row r="243">
@@ -6550,13 +6553,13 @@
         </is>
       </c>
       <c t="n" r="C246">
-        <v>-5.3447</v>
+        <v>-5.5392</v>
       </c>
       <c t="n" r="D246">
-        <v>-15.4653</v>
+        <v>-15.4981</v>
       </c>
       <c t="n" r="F246">
-        <v>-17.8333</v>
+        <v>-18.0022</v>
       </c>
     </row>
     <row r="247">
@@ -6571,16 +6574,16 @@
         </is>
       </c>
       <c t="n" r="C247">
-        <v>-5.6790</v>
+        <v>-5.8580</v>
       </c>
       <c t="n" r="D247">
-        <v>-15.9059</v>
+        <v>-15.9446</v>
       </c>
       <c t="n" r="E247">
-        <v>-25.2164</v>
+        <v>-25.4906</v>
       </c>
       <c t="n" r="F247">
-        <v>-18.0013</v>
+        <v>-18.1569</v>
       </c>
     </row>
     <row r="248">
@@ -6679,16 +6682,16 @@
         </is>
       </c>
       <c t="n" r="C255">
-        <v>-86.0924</v>
+        <v>-86.1162</v>
       </c>
       <c t="n" r="D255">
-        <v>-88.5930</v>
+        <v>-88.6096</v>
       </c>
       <c t="n" r="E255">
-        <v>-75.2257</v>
+        <v>-75.2665</v>
       </c>
       <c t="n" r="F255">
-        <v>-88.6129</v>
+        <v>-88.6324</v>
       </c>
     </row>
     <row r="256">
@@ -6703,16 +6706,16 @@
         </is>
       </c>
       <c t="n" r="C256">
-        <v>-1.4092</v>
+        <v>-1.4580</v>
       </c>
       <c t="n" r="D256">
-        <v>-13.3533</v>
+        <v>-13.3583</v>
       </c>
       <c t="n" r="E256">
-        <v>607.4662</v>
+        <v>607.1658</v>
       </c>
       <c t="n" r="F256">
-        <v>-13.5410</v>
+        <v>-13.5837</v>
       </c>
     </row>
     <row r="257">
@@ -6727,16 +6730,16 @@
         </is>
       </c>
       <c t="n" r="C257">
-        <v>-5.8252</v>
+        <v>-5.8324</v>
       </c>
       <c t="n" r="D257">
-        <v>-6.4705</v>
+        <v>-6.4703</v>
       </c>
       <c t="n" r="E257">
-        <v>-9.3239</v>
+        <v>-9.3270</v>
       </c>
       <c t="n" r="F257">
-        <v>-4.6087</v>
+        <v>-4.6160</v>
       </c>
     </row>
     <row r="258">
@@ -6763,7 +6766,7 @@
         </is>
       </c>
       <c t="n" r="C259">
-        <v>3.3931</v>
+        <v>3.5006</v>
       </c>
     </row>
     <row r="260">
@@ -6778,7 +6781,7 @@
         </is>
       </c>
       <c t="n" r="C260">
-        <v>-0.0801</v>
+        <v>-0.0828</v>
       </c>
     </row>
     <row r="261">
@@ -6817,7 +6820,7 @@
         </is>
       </c>
       <c t="n" r="C263">
-        <v>8.9159</v>
+        <v>8.9201</v>
       </c>
     </row>
     <row r="264">
@@ -6844,13 +6847,13 @@
         </is>
       </c>
       <c t="n" r="C265">
-        <v>1.1667</v>
+        <v>1.2167</v>
       </c>
       <c t="n" r="D265">
-        <v>5.5508</v>
+        <v>5.5225</v>
       </c>
       <c t="n" r="F265">
-        <v>7.2210</v>
+        <v>7.2741</v>
       </c>
     </row>
     <row r="266">
@@ -6865,13 +6868,13 @@
         </is>
       </c>
       <c t="n" r="C266">
-        <v>1.1087</v>
+        <v>1.1558</v>
       </c>
       <c t="n" r="D266">
-        <v>5.4680</v>
+        <v>5.4366</v>
       </c>
       <c t="n" r="F266">
-        <v>7.1375</v>
+        <v>7.1875</v>
       </c>
     </row>
     <row r="267">
@@ -6898,16 +6901,16 @@
         </is>
       </c>
       <c t="n" r="C268">
-        <v>-29.3918</v>
+        <v>-29.3926</v>
       </c>
       <c t="n" r="D268">
-        <v>-28.1049</v>
+        <v>-28.1523</v>
       </c>
       <c t="n" r="E268">
-        <v>-23.9446</v>
+        <v>-23.9968</v>
       </c>
       <c t="n" r="F268">
-        <v>-27.2052</v>
+        <v>-27.2060</v>
       </c>
     </row>
     <row r="269">
@@ -6934,16 +6937,16 @@
         </is>
       </c>
       <c t="n" r="C270">
-        <v>-0.4468</v>
+        <v>-0.4567</v>
       </c>
       <c t="n" r="D270">
-        <v>-1.4532</v>
+        <v>-1.4565</v>
       </c>
       <c t="n" r="E270">
-        <v>-32.3712</v>
+        <v>-32.2452</v>
       </c>
       <c t="n" r="F270">
-        <v>95.6879</v>
+        <v>95.6683</v>
       </c>
     </row>
     <row r="271">
@@ -6958,7 +6961,7 @@
         </is>
       </c>
       <c t="n" r="C271">
-        <v>34.1998</v>
+        <v>34.3066</v>
       </c>
     </row>
     <row r="272">
@@ -6973,13 +6976,13 @@
         </is>
       </c>
       <c t="n" r="C272">
-        <v>-0.3314</v>
+        <v>-0.3409</v>
       </c>
       <c t="n" r="D272">
-        <v>-0.8515</v>
+        <v>-0.8471</v>
       </c>
       <c t="n" r="F272">
-        <v>-2.3424</v>
+        <v>-2.3516</v>
       </c>
     </row>
     <row r="273">
@@ -6994,16 +6997,16 @@
         </is>
       </c>
       <c t="n" r="C273">
-        <v>-77.5869</v>
+        <v>-77.8428</v>
       </c>
       <c t="n" r="D273">
-        <v>-87.9568</v>
+        <v>-88.0677</v>
       </c>
       <c t="n" r="E273">
-        <v>-46.4694</v>
+        <v>-46.4956</v>
       </c>
       <c t="n" r="F273">
-        <v>104.3596</v>
+        <v>102.0266</v>
       </c>
     </row>
     <row r="274">
@@ -7042,13 +7045,13 @@
         </is>
       </c>
       <c t="n" r="C276">
-        <v>-0.0512</v>
+        <v>-0.0523</v>
       </c>
       <c t="n" r="D276">
-        <v>-10.8914</v>
+        <v>-10.9519</v>
       </c>
       <c t="n" r="F276">
-        <v>-9.7157</v>
+        <v>-9.7166</v>
       </c>
     </row>
     <row r="277">
@@ -7075,16 +7078,16 @@
         </is>
       </c>
       <c t="n" r="C278">
-        <v>3.2604</v>
+        <v>3.3944</v>
       </c>
       <c t="n" r="D278">
-        <v>-58.7511</v>
+        <v>-58.4455</v>
       </c>
       <c t="n" r="E278">
-        <v>-98.8890</v>
+        <v>-98.8474</v>
       </c>
       <c t="n" r="F278">
-        <v>-98.1611</v>
+        <v>-98.1588</v>
       </c>
     </row>
     <row r="279">
@@ -7117,7 +7120,7 @@
         <v>0.8311</v>
       </c>
       <c t="n" r="E280">
-        <v>-96.0178</v>
+        <v>-95.5212</v>
       </c>
       <c t="n" r="F280">
         <v>0.8311</v>
@@ -7159,16 +7162,16 @@
         </is>
       </c>
       <c t="n" r="C283">
-        <v>-6.3116</v>
+        <v>-6.3295</v>
       </c>
       <c t="n" r="D283">
-        <v>-22.6033</v>
+        <v>-22.6065</v>
       </c>
       <c t="n" r="E283">
-        <v>4957.6045</v>
+        <v>4994.5360</v>
       </c>
       <c t="n" r="F283">
-        <v>11355.2071</v>
+        <v>11353.0123</v>
       </c>
     </row>
     <row r="284">
@@ -7183,13 +7186,13 @@
         </is>
       </c>
       <c t="n" r="C284">
-        <v>0.0003</v>
+        <v>0.0028</v>
       </c>
       <c t="n" r="D284">
-        <v>-0.0484</v>
+        <v>-0.0446</v>
       </c>
       <c t="n" r="F284">
-        <v>-0.0054</v>
+        <v>-0.0028</v>
       </c>
     </row>
     <row r="285">
@@ -7240,7 +7243,7 @@
         </is>
       </c>
       <c t="n" r="C288">
-        <v>-28.9269</v>
+        <v>-29.6960</v>
       </c>
     </row>
     <row r="289">
@@ -7267,16 +7270,16 @@
         </is>
       </c>
       <c t="n" r="C290">
-        <v>0.4950</v>
+        <v>0.4931</v>
       </c>
       <c t="n" r="D290">
-        <v>2.5505</v>
+        <v>2.5184</v>
       </c>
       <c t="n" r="E290">
-        <v>10.1936</v>
+        <v>10.1654</v>
       </c>
       <c t="n" r="F290">
-        <v>3.1352</v>
+        <v>3.1333</v>
       </c>
     </row>
     <row r="291">
@@ -7303,16 +7306,16 @@
         </is>
       </c>
       <c t="n" r="C292">
-        <v>-26.6108</v>
+        <v>-26.5940</v>
       </c>
       <c t="n" r="D292">
-        <v>-57.6853</v>
+        <v>-51.8404</v>
       </c>
       <c t="n" r="E292">
-        <v>-57.3752</v>
+        <v>-57.3705</v>
       </c>
       <c t="n" r="F292">
-        <v>-56.8568</v>
+        <v>-56.8468</v>
       </c>
     </row>
     <row r="293">
@@ -7411,16 +7414,16 @@
         </is>
       </c>
       <c t="n" r="C298">
-        <v>3.6767</v>
+        <v>3.8013</v>
       </c>
       <c t="n" r="D298">
-        <v>10.2571</v>
+        <v>10.2550</v>
       </c>
       <c t="n" r="E298">
-        <v>21.3702</v>
+        <v>21.3977</v>
       </c>
       <c t="n" r="F298">
-        <v>12.8529</v>
+        <v>12.9886</v>
       </c>
     </row>
     <row r="299">
@@ -7435,13 +7438,13 @@
         </is>
       </c>
       <c t="n" r="C299">
-        <v>3.1560</v>
+        <v>3.2786</v>
       </c>
       <c t="n" r="D299">
-        <v>9.0005</v>
+        <v>8.9952</v>
       </c>
       <c t="n" r="F299">
-        <v>11.5963</v>
+        <v>11.7289</v>
       </c>
     </row>
     <row r="300">
@@ -7468,13 +7471,13 @@
         </is>
       </c>
       <c t="n" r="C301">
-        <v>4.1757</v>
+        <v>4.3036</v>
       </c>
       <c t="n" r="D301">
-        <v>11.8413</v>
+        <v>11.8362</v>
       </c>
       <c t="n" r="F301">
-        <v>14.7335</v>
+        <v>14.8744</v>
       </c>
     </row>
     <row r="302">
@@ -7489,7 +7492,7 @@
         </is>
       </c>
       <c t="n" r="C302">
-        <v>-73.7474</v>
+        <v>-73.6171</v>
       </c>
     </row>
     <row r="303">
@@ -7504,10 +7507,10 @@
         </is>
       </c>
       <c t="n" r="C303">
-        <v>-0.0097</v>
+        <v>-0.0075</v>
       </c>
       <c t="n" r="D303">
-        <v>-0.8861</v>
+        <v>-0.8878</v>
       </c>
     </row>
     <row r="304">
@@ -7522,16 +7525,16 @@
         </is>
       </c>
       <c t="n" r="C304">
-        <v>1.0835</v>
+        <v>1.1666</v>
       </c>
       <c t="n" r="D304">
-        <v>6.1134</v>
+        <v>6.1159</v>
       </c>
       <c t="n" r="E304">
-        <v>14.4849</v>
+        <v>14.4764</v>
       </c>
       <c t="n" r="F304">
-        <v>7.7223</v>
+        <v>7.8109</v>
       </c>
     </row>
     <row r="305">
@@ -7570,16 +7573,16 @@
         </is>
       </c>
       <c t="n" r="C307">
-        <v>2.0547</v>
+        <v>2.0817</v>
       </c>
       <c t="n" r="D307">
-        <v>3.5173</v>
+        <v>3.4498</v>
       </c>
       <c t="n" r="E307">
-        <v>11.8418</v>
+        <v>11.7636</v>
       </c>
       <c t="n" r="F307">
-        <v>5.4524</v>
+        <v>5.4803</v>
       </c>
     </row>
     <row r="308">
@@ -7618,16 +7621,16 @@
         </is>
       </c>
       <c t="n" r="C310">
-        <v>-0.0724</v>
+        <v>-0.0743</v>
       </c>
       <c t="n" r="D310">
-        <v>-0.2190</v>
+        <v>-0.2195</v>
       </c>
       <c t="n" r="E310">
-        <v>0.6009</v>
+        <v>0.5999</v>
       </c>
       <c t="n" r="F310">
-        <v>-0.2522</v>
+        <v>-0.2541</v>
       </c>
     </row>
     <row r="311">
@@ -7666,16 +7669,16 @@
         </is>
       </c>
       <c t="n" r="C313">
-        <v>-0.0516</v>
+        <v>-0.0528</v>
       </c>
       <c t="n" r="D313">
-        <v>-0.1479</v>
+        <v>-0.1483</v>
       </c>
       <c t="n" r="E313">
-        <v>2.0813</v>
+        <v>1.9699</v>
       </c>
       <c t="n" r="F313">
-        <v>-0.1731</v>
+        <v>-0.1744</v>
       </c>
     </row>
     <row r="314">
@@ -7702,16 +7705,16 @@
         </is>
       </c>
       <c t="n" r="C315">
-        <v>-0.1545</v>
+        <v>-0.1568</v>
       </c>
       <c t="n" r="D315">
-        <v>-0.3508</v>
+        <v>-0.3509</v>
       </c>
       <c t="n" r="E315">
-        <v>3.0261</v>
+        <v>3.0258</v>
       </c>
       <c t="n" r="F315">
-        <v>-0.3988</v>
+        <v>-0.4012</v>
       </c>
     </row>
     <row r="316">
@@ -7726,7 +7729,7 @@
         </is>
       </c>
       <c t="n" r="C316">
-        <v>-0.1321</v>
+        <v>-0.1330</v>
       </c>
     </row>
     <row r="317">
@@ -7783,13 +7786,13 @@
         </is>
       </c>
       <c t="n" r="C320">
-        <v>-0.1090</v>
+        <v>-0.1080</v>
       </c>
       <c t="n" r="D320">
-        <v>-0.1090</v>
+        <v>-0.1099</v>
       </c>
       <c t="n" r="F320">
-        <v>-0.1183</v>
+        <v>-0.1173</v>
       </c>
     </row>
     <row r="321">
@@ -7828,7 +7831,7 @@
         </is>
       </c>
       <c t="n" r="C323">
-        <v>2.8273</v>
+        <v>2.9305</v>
       </c>
     </row>
     <row r="324">

--- a/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/gayrimenkul-yatirim-fonlari-getiri/data/gayrimenkul-yatirim-fonlari-getiri.xlsx
@@ -280,22 +280,22 @@
         </is>
       </c>
       <c t="n" r="C3">
-        <v>21.8477</v>
+        <v>12.8655</v>
       </c>
       <c t="n" r="D3">
-        <v>669.2501</v>
+        <v>670.0182</v>
       </c>
       <c t="n" r="E3">
-        <v>696.0894</v>
+        <v>696.8193</v>
       </c>
       <c t="n" r="F3">
-        <v>663.7140</v>
+        <v>664.3679</v>
       </c>
       <c t="n" r="G3">
-        <v>621.2344</v>
+        <v>622.0078</v>
       </c>
       <c t="n" r="H3">
-        <v>773.7566</v>
+        <v>774.5048</v>
       </c>
     </row>
     <row r="4">
@@ -310,340 +310,340 @@
         </is>
       </c>
       <c t="n" r="C4">
-        <v>16.2683</v>
+        <v>16.2114</v>
       </c>
       <c t="n" r="D4">
-        <v>20.4483</v>
+        <v>20.3943</v>
       </c>
       <c t="n" r="E4">
-        <v>248.4914</v>
+        <v>248.0579</v>
       </c>
       <c t="n" r="F4">
-        <v>21.2474</v>
+        <v>21.2954</v>
       </c>
       <c t="n" r="G4">
-        <v>372.1803</v>
+        <v>370.8737</v>
       </c>
     </row>
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">NYO</t>
+          <t xml:space="preserve">YE6</t>
         </is>
       </c>
       <c t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş NİLÜFER GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C5">
-        <v>0.9364</v>
+        <v>-0.2467</v>
       </c>
       <c t="n" r="D5">
-        <v>2.6591</v>
+        <v>36.7095</v>
       </c>
       <c t="n" r="E5">
-        <v>27.7596</v>
+        <v>52.8477</v>
       </c>
       <c t="n" r="F5">
-        <v>3.4373</v>
+        <v>42.3039</v>
       </c>
       <c t="n" r="G5">
-        <v>359.3357</v>
+        <v>240.2331</v>
+      </c>
+      <c t="n" r="H5">
+        <v>332.9122</v>
       </c>
     </row>
     <row r="6">
       <c t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">YE6</t>
+          <t xml:space="preserve">YE3</t>
         </is>
       </c>
       <c t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş NİLÜFER GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AKASYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C6">
-        <v>-0.3811</v>
+        <v>-0.0189</v>
       </c>
       <c t="n" r="D6">
-        <v>36.6681</v>
+        <v>-0.0480</v>
       </c>
       <c t="n" r="E6">
-        <v>52.8358</v>
+        <v>192.5071</v>
       </c>
       <c t="n" r="F6">
-        <v>42.3073</v>
+        <v>-0.0614</v>
       </c>
       <c t="n" r="G6">
-        <v>240.2122</v>
+        <v>191.4489</v>
       </c>
       <c t="n" r="H6">
-        <v>332.9227</v>
+        <v>167655.5315</v>
       </c>
     </row>
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">YE3</t>
+          <t xml:space="preserve">YZA</t>
         </is>
       </c>
       <c t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AKASYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ZAMBAK PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C7">
-        <v>-0.0185</v>
+        <v>-0.0348</v>
       </c>
       <c t="n" r="D7">
-        <v>-0.0487</v>
+        <v>4.0147</v>
       </c>
       <c t="n" r="E7">
-        <v>192.5069</v>
+        <v>3.9596</v>
       </c>
       <c t="n" r="F7">
-        <v>-0.0607</v>
+        <v>4.0188</v>
       </c>
       <c t="n" r="G7">
-        <v>191.4487</v>
-      </c>
-      <c t="n" r="H7">
-        <v>167656.7578</v>
+        <v>152.9356</v>
       </c>
     </row>
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">YZA</t>
+          <t xml:space="preserve">FT2</t>
         </is>
       </c>
       <c t="inlineStr" r="B8">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ZAMBAK PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C8">
-        <v>-0.0089</v>
+        <v>0.7125</v>
       </c>
       <c t="n" r="D8">
-        <v>4.0094</v>
+        <v>1.0566</v>
       </c>
       <c t="n" r="E8">
-        <v>3.9662</v>
+        <v>137.8718</v>
       </c>
       <c t="n" r="F8">
-        <v>4.0244</v>
+        <v>1.5260</v>
       </c>
       <c t="n" r="G8">
-        <v>152.9178</v>
+        <v>142.8924</v>
       </c>
     </row>
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">FT2</t>
+          <t xml:space="preserve">PBA</t>
         </is>
       </c>
       <c t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALBATROS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C9">
-        <v>0.7435</v>
+        <v>65.6586</v>
       </c>
       <c t="n" r="D9">
-        <v>1.0502</v>
+        <v>68.0800</v>
       </c>
       <c t="n" r="E9">
-        <v>137.9567</v>
+        <v>69.7996</v>
       </c>
       <c t="n" r="F9">
-        <v>1.5332</v>
+        <v>55.1729</v>
       </c>
       <c t="n" r="G9">
-        <v>142.9521</v>
+        <v>89.7499</v>
+      </c>
+      <c t="n" r="H9">
+        <v>114.9827</v>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">PBA</t>
+          <t xml:space="preserve">AB1</t>
         </is>
       </c>
       <c t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALBATROS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKFEN GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C10">
-        <v>65.7009</v>
+        <v>1.6443</v>
       </c>
       <c t="n" r="D10">
-        <v>68.0954</v>
+        <v>2.2140</v>
       </c>
       <c t="n" r="E10">
-        <v>69.7978</v>
+        <v>76.7623</v>
       </c>
       <c t="n" r="F10">
-        <v>55.1673</v>
+        <v>33.8276</v>
       </c>
       <c t="n" r="G10">
-        <v>89.8288</v>
+        <v>82.7942</v>
       </c>
       <c t="n" r="H10">
-        <v>114.9751</v>
+        <v>299.2462</v>
+      </c>
+      <c t="n" r="I10">
+        <v>1679.0139</v>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">AB1</t>
+          <t xml:space="preserve">NFG</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">AKFEN GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C11">
-        <v>1.7369</v>
+        <v>-0.1966</v>
       </c>
       <c t="n" r="D11">
-        <v>2.2248</v>
+        <v>-0.3522</v>
       </c>
       <c t="n" r="E11">
-        <v>76.8614</v>
+        <v>19.8682</v>
       </c>
       <c t="n" r="F11">
-        <v>33.8555</v>
+        <v>-1.0578</v>
       </c>
       <c t="n" r="G11">
-        <v>82.8408</v>
+        <v>61.3884</v>
       </c>
       <c t="n" r="H11">
-        <v>299.3294</v>
-      </c>
-      <c t="n" r="I11">
-        <v>1679.7970</v>
+        <v>695.6003</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">NFG</t>
+          <t xml:space="preserve">VVF</t>
         </is>
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C12">
-        <v>-0.1937</v>
+        <v>0.2157</v>
       </c>
       <c t="n" r="D12">
-        <v>-0.3554</v>
+        <v>1.4196</v>
       </c>
       <c t="n" r="E12">
-        <v>19.8906</v>
+        <v>37.9956</v>
       </c>
       <c t="n" r="F12">
-        <v>-1.0536</v>
+        <v>1.4498</v>
       </c>
       <c t="n" r="G12">
-        <v>61.3409</v>
+        <v>60.8980</v>
       </c>
       <c t="n" r="H12">
-        <v>695.6341</v>
+        <v>328.3085</v>
+      </c>
+      <c t="n" r="I12">
+        <v>1095.4450</v>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">VVF</t>
+          <t xml:space="preserve">BRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C13">
-        <v>0.2767</v>
+        <v>7.2579</v>
       </c>
       <c t="n" r="D13">
-        <v>1.4152</v>
+        <v>26.2198</v>
       </c>
       <c t="n" r="E13">
-        <v>38.2021</v>
+        <v>34.1063</v>
       </c>
       <c t="n" r="F13">
-        <v>1.4311</v>
+        <v>35.1121</v>
       </c>
       <c t="n" r="G13">
-        <v>61.0194</v>
-      </c>
-      <c t="n" r="H13">
-        <v>328.2295</v>
-      </c>
-      <c t="n" r="I13">
-        <v>1095.2244</v>
+        <v>58.9543</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">TNG</t>
+          <t xml:space="preserve">AR9</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TUNA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C14">
-        <v>3.8277</v>
+        <v>-0.1201</v>
       </c>
       <c t="n" r="D14">
-        <v>10.3367</v>
+        <v>0.2781</v>
       </c>
       <c t="n" r="E14">
-        <v>27.7977</v>
+        <v>60.0153</v>
       </c>
       <c t="n" r="F14">
-        <v>12.0352</v>
+        <v>-4.4753</v>
       </c>
       <c t="n" r="G14">
-        <v>58.6333</v>
+        <v>58.6114</v>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">AR9</t>
+          <t xml:space="preserve">TNG</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TUNA PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C15">
-        <v>-0.1171</v>
+        <v>3.5192</v>
       </c>
       <c t="n" r="D15">
-        <v>0.2724</v>
+        <v>10.2595</v>
       </c>
       <c t="n" r="E15">
-        <v>60.0160</v>
+        <v>27.7108</v>
       </c>
       <c t="n" r="F15">
-        <v>-4.4700</v>
+        <v>12.2048</v>
       </c>
       <c t="n" r="G15">
-        <v>58.6119</v>
+        <v>58.5584</v>
       </c>
     </row>
     <row r="16">
@@ -658,76 +658,79 @@
         </is>
       </c>
       <c t="n" r="C16">
-        <v>3.4876</v>
+        <v>3.2071</v>
       </c>
       <c t="n" r="D16">
-        <v>8.9261</v>
+        <v>8.9994</v>
       </c>
       <c t="n" r="E16">
-        <v>26.3973</v>
+        <v>26.2589</v>
       </c>
       <c t="n" r="F16">
-        <v>18.7210</v>
+        <v>18.8422</v>
       </c>
       <c t="n" r="G16">
-        <v>57.2351</v>
+        <v>57.2007</v>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">BRE</t>
+          <t xml:space="preserve">HP2</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. POLAT BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C17">
-        <v>7.9052</v>
+        <v>0.7377</v>
       </c>
       <c t="n" r="D17">
-        <v>24.6928</v>
+        <v>1.9976</v>
       </c>
       <c t="n" r="E17">
-        <v>32.3636</v>
+        <v>50.4550</v>
       </c>
       <c t="n" r="F17">
-        <v>33.3821</v>
+        <v>48.3221</v>
       </c>
       <c t="n" r="G17">
-        <v>57.1862</v>
+        <v>56.2366</v>
+      </c>
+      <c t="n" r="H17">
+        <v>462.6391</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">HP2</t>
+          <t xml:space="preserve">OGC</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÇATI KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C18">
-        <v>0.7534</v>
+        <v>0.3567</v>
       </c>
       <c t="n" r="D18">
-        <v>1.9985</v>
+        <v>0.9107</v>
       </c>
       <c t="n" r="E18">
-        <v>50.4590</v>
+        <v>1.4440</v>
       </c>
       <c t="n" r="F18">
-        <v>48.3142</v>
+        <v>0.9880</v>
       </c>
       <c t="n" r="G18">
-        <v>56.2349</v>
+        <v>55.3585</v>
       </c>
       <c t="n" r="H18">
-        <v>462.6094</v>
+        <v>410.7679</v>
       </c>
     </row>
     <row r="19">
@@ -742,19 +745,19 @@
         </is>
       </c>
       <c t="n" r="C19">
-        <v>3.9330</v>
+        <v>3.5791</v>
       </c>
       <c t="n" r="D19">
-        <v>10.5147</v>
+        <v>10.3935</v>
       </c>
       <c t="n" r="E19">
-        <v>22.2695</v>
+        <v>22.1212</v>
       </c>
       <c t="n" r="F19">
-        <v>12.8475</v>
+        <v>12.9738</v>
       </c>
       <c t="n" r="G19">
-        <v>55.6090</v>
+        <v>55.3329</v>
       </c>
     </row>
     <row r="20">
@@ -769,763 +772,766 @@
         </is>
       </c>
       <c t="n" r="C20">
-        <v>3.9327</v>
+        <v>3.5788</v>
       </c>
       <c t="n" r="D20">
-        <v>10.5138</v>
+        <v>10.3924</v>
       </c>
       <c t="n" r="E20">
-        <v>22.2671</v>
+        <v>22.1188</v>
       </c>
       <c t="n" r="F20">
-        <v>12.8462</v>
+        <v>12.9724</v>
       </c>
       <c t="n" r="G20">
-        <v>55.6013</v>
+        <v>55.3250</v>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">OGC</t>
+          <t xml:space="preserve">OYK</t>
         </is>
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. ÇATI KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ÇEŞME GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C21">
-        <v>0.3771</v>
+        <v>-0.2029</v>
       </c>
       <c t="n" r="D21">
-        <v>0.9027</v>
+        <v>-0.2153</v>
       </c>
       <c t="n" r="E21">
-        <v>1.4451</v>
+        <v>55.3889</v>
       </c>
       <c t="n" r="F21">
-        <v>0.9913</v>
+        <v>-0.2323</v>
       </c>
       <c t="n" r="G21">
-        <v>55.3459</v>
+        <v>54.4066</v>
       </c>
       <c t="n" r="H21">
-        <v>410.7846</v>
+        <v>172.5009</v>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">OYK</t>
+          <t xml:space="preserve">RGF</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ÇEŞME GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. TSL PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C22">
-        <v>-0.2024</v>
+        <v>-0.0045</v>
       </c>
       <c t="n" r="D22">
-        <v>-0.2154</v>
+        <v>0.3414</v>
       </c>
       <c t="n" r="E22">
-        <v>55.3895</v>
+        <v>19.2474</v>
       </c>
       <c t="n" r="F22">
-        <v>-0.2321</v>
+        <v>6.9202</v>
       </c>
       <c t="n" r="G22">
-        <v>54.4074</v>
-      </c>
-      <c t="n" r="H22">
-        <v>172.5014</v>
+        <v>53.6750</v>
       </c>
     </row>
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">RGF</t>
+          <t xml:space="preserve">NO1</t>
         </is>
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. TSL PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C23">
-        <v>0.0463</v>
+        <v>3.5155</v>
       </c>
       <c t="n" r="D23">
-        <v>6.3825</v>
+        <v>3.9809</v>
       </c>
       <c t="n" r="E23">
-        <v>19.3452</v>
+        <v>22.0200</v>
       </c>
       <c t="n" r="F23">
-        <v>6.9149</v>
+        <v>14.6872</v>
       </c>
       <c t="n" r="G23">
-        <v>53.9847</v>
+        <v>52.0828</v>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">NO1</t>
+          <t xml:space="preserve">YD7</t>
         </is>
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.KARDELEN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C24">
-        <v>4.1375</v>
+        <v>0.9551</v>
       </c>
       <c t="n" r="D24">
-        <v>5.5836</v>
+        <v>-0.1954</v>
       </c>
       <c t="n" r="E24">
-        <v>22.3757</v>
+        <v>30.0225</v>
       </c>
       <c t="n" r="F24">
-        <v>14.7778</v>
+        <v>-0.5839</v>
       </c>
       <c t="n" r="G24">
-        <v>52.3925</v>
+        <v>50.8871</v>
+      </c>
+      <c t="n" r="H24">
+        <v>171.4186</v>
+      </c>
+      <c t="n" r="I24">
+        <v>1157.7798</v>
       </c>
     </row>
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">YD7</t>
+          <t xml:space="preserve">IGJ</t>
         </is>
       </c>
       <c t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.KARDELEN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C25">
-        <v>0.9279</v>
+        <v>-0.0212</v>
       </c>
       <c t="n" r="D25">
-        <v>-0.2735</v>
+        <v>0.0344</v>
       </c>
       <c t="n" r="E25">
-        <v>29.9946</v>
+        <v>36.0594</v>
       </c>
       <c t="n" r="F25">
-        <v>-0.5892</v>
+        <v>0.2773</v>
       </c>
       <c t="n" r="G25">
-        <v>50.8447</v>
-      </c>
-      <c t="n" r="H25">
-        <v>171.4041</v>
-      </c>
-      <c t="n" r="I25">
-        <v>1157.7130</v>
+        <v>50.2469</v>
       </c>
     </row>
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">IGJ</t>
+          <t xml:space="preserve">YD5</t>
         </is>
       </c>
       <c t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C26">
-        <v>0.0480</v>
+        <v>-0.0409</v>
       </c>
       <c t="n" r="D26">
-        <v>0.0469</v>
+        <v>-0.1864</v>
       </c>
       <c t="n" r="E26">
-        <v>36.1141</v>
+        <v>16.2972</v>
       </c>
       <c t="n" r="F26">
-        <v>0.2815</v>
+        <v>-0.4410</v>
       </c>
       <c t="n" r="G26">
-        <v>50.5293</v>
+        <v>48.4926</v>
+      </c>
+      <c t="n" r="H26">
+        <v>197.6313</v>
+      </c>
+      <c t="n" r="I26">
+        <v>1325.0187</v>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">YD5</t>
+          <t xml:space="preserve">RAA</t>
         </is>
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. AVRUPA-ANADOLU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C27">
-        <v>-0.0554</v>
+        <v>4.8697</v>
       </c>
       <c t="n" r="D27">
-        <v>-0.2090</v>
+        <v>11.5842</v>
       </c>
       <c t="n" r="E27">
-        <v>16.2954</v>
+        <v>20.7729</v>
       </c>
       <c t="n" r="F27">
-        <v>-0.4274</v>
+        <v>13.7677</v>
       </c>
       <c t="n" r="G27">
-        <v>48.4834</v>
-      </c>
-      <c t="n" r="H27">
-        <v>197.6721</v>
-      </c>
-      <c t="n" r="I27">
-        <v>1325.2140</v>
+        <v>47.4734</v>
       </c>
     </row>
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">RAA</t>
+          <t xml:space="preserve">NG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. AVRUPA-ANADOLU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C28">
-        <v>4.9830</v>
+        <v>0.4002</v>
       </c>
       <c t="n" r="D28">
-        <v>11.7877</v>
+        <v>1.6185</v>
       </c>
       <c t="n" r="E28">
-        <v>20.9032</v>
+        <v>43.6656</v>
       </c>
       <c t="n" r="F28">
-        <v>13.7104</v>
+        <v>6.0265</v>
       </c>
       <c t="n" r="G28">
-        <v>47.6495</v>
+        <v>45.4892</v>
+      </c>
+      <c t="n" r="H28">
+        <v>465.2551</v>
       </c>
     </row>
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">NG7</t>
+          <t xml:space="preserve">YYF</t>
         </is>
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C29">
-        <v>0.4377</v>
+        <v>3.1499</v>
       </c>
       <c t="n" r="D29">
-        <v>6.3680</v>
+        <v>8.8943</v>
       </c>
       <c t="n" r="E29">
-        <v>43.6910</v>
+        <v>19.1487</v>
       </c>
       <c t="n" r="F29">
-        <v>6.0107</v>
+        <v>11.3293</v>
       </c>
       <c t="n" r="G29">
-        <v>45.4754</v>
-      </c>
-      <c t="n" r="H29">
-        <v>465.1706</v>
+        <v>44.2901</v>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">YYF</t>
+          <t xml:space="preserve">ZGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BGF KATILIM ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C30">
-        <v>3.4647</v>
+        <v>0.2505</v>
       </c>
       <c t="n" r="D30">
-        <v>8.9959</v>
+        <v>-0.4540</v>
       </c>
       <c t="n" r="E30">
-        <v>19.2787</v>
+        <v>29.3986</v>
       </c>
       <c t="n" r="F30">
-        <v>11.2189</v>
+        <v>1.7266</v>
       </c>
       <c t="n" r="G30">
-        <v>44.4887</v>
+        <v>44.2813</v>
       </c>
     </row>
     <row r="31">
       <c t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">ZGG</t>
+          <t xml:space="preserve">ZGU</t>
         </is>
       </c>
       <c t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BGF KATILIM ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C31">
-        <v>0.2586</v>
+        <v>1.4397</v>
       </c>
       <c t="n" r="D31">
-        <v>-0.4460</v>
+        <v>2.7904</v>
       </c>
       <c t="n" r="E31">
-        <v>29.4183</v>
+        <v>24.7168</v>
       </c>
       <c t="n" r="F31">
-        <v>1.7127</v>
+        <v>8.8054</v>
       </c>
       <c t="n" r="G31">
-        <v>44.2654</v>
+        <v>43.0785</v>
       </c>
     </row>
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">ZGU</t>
+          <t xml:space="preserve">ORV</t>
         </is>
       </c>
       <c t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AVRASYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C32">
-        <v>2.3298</v>
+        <v>-0.2501</v>
       </c>
       <c t="n" r="D32">
-        <v>3.3552</v>
+        <v>-0.7049</v>
       </c>
       <c t="n" r="E32">
-        <v>24.5088</v>
+        <v>27.5280</v>
       </c>
       <c t="n" r="F32">
-        <v>8.9360</v>
+        <v>0.1036</v>
       </c>
       <c t="n" r="G32">
-        <v>43.2903</v>
+        <v>41.7748</v>
       </c>
     </row>
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">FNR</t>
+          <t xml:space="preserve">RG3</t>
         </is>
       </c>
       <c t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TRAKYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C33">
-        <v>2.6120</v>
+        <v>-0.0793</v>
       </c>
       <c t="n" r="D33">
-        <v>-0.3568</v>
+        <v>-0.3323</v>
       </c>
       <c t="n" r="E33">
-        <v>16.3303</v>
+        <v>42.2719</v>
       </c>
       <c t="n" r="F33">
-        <v>5.6978</v>
+        <v>-0.5067</v>
       </c>
       <c t="n" r="G33">
-        <v>42.9038</v>
+        <v>41.6793</v>
+      </c>
+      <c t="n" r="H33">
+        <v>213.3019</v>
+      </c>
+      <c t="n" r="I33">
+        <v>711.0711</v>
       </c>
     </row>
     <row r="34">
       <c t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">RG3</t>
+          <t xml:space="preserve">KGB</t>
         </is>
       </c>
       <c t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TRAKYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C34">
-        <v>-0.0784</v>
+        <v>0.1608</v>
       </c>
       <c t="n" r="D34">
-        <v>-0.3341</v>
+        <v>0.5406</v>
       </c>
       <c t="n" r="E34">
-        <v>42.2724</v>
+        <v>38.6354</v>
       </c>
       <c t="n" r="F34">
-        <v>-0.5049</v>
+        <v>0.7047</v>
       </c>
       <c t="n" r="G34">
-        <v>41.6786</v>
+        <v>41.6760</v>
       </c>
       <c t="n" r="H34">
-        <v>213.3075</v>
+        <v>241.9488</v>
       </c>
       <c t="n" r="I34">
-        <v>718.2115</v>
+        <v>847.7698</v>
       </c>
     </row>
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">KGB</t>
+          <t xml:space="preserve">KGG</t>
         </is>
       </c>
       <c t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C35">
-        <v>0.1747</v>
+        <v>0.1473</v>
       </c>
       <c t="n" r="D35">
-        <v>0.5318</v>
+        <v>0.0215</v>
       </c>
       <c t="n" r="E35">
-        <v>38.6427</v>
+        <v>41.1585</v>
       </c>
       <c t="n" r="F35">
-        <v>0.7156</v>
+        <v>0.2355</v>
       </c>
       <c t="n" r="G35">
-        <v>41.6747</v>
+        <v>41.4387</v>
       </c>
       <c t="n" r="H35">
-        <v>241.9860</v>
-      </c>
-      <c t="n" r="I35">
-        <v>847.8730</v>
+        <v>251.8921</v>
       </c>
     </row>
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">ORV</t>
+          <t xml:space="preserve">MPG</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">ORAGON GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AVRASYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM (TL) FONU</t>
         </is>
       </c>
       <c t="n" r="C36">
-        <v>-0.2471</v>
+        <v>0.5279</v>
       </c>
       <c t="n" r="D36">
-        <v>-0.5126</v>
+        <v>1.5253</v>
       </c>
       <c t="n" r="E36">
-        <v>27.2935</v>
+        <v>29.0293</v>
       </c>
       <c t="n" r="F36">
-        <v>0.1053</v>
+        <v>1.5979</v>
       </c>
       <c t="n" r="G36">
-        <v>41.6709</v>
+        <v>40.7078</v>
+      </c>
+      <c t="n" r="H36">
+        <v>172.4735</v>
+      </c>
+      <c t="n" r="I36">
+        <v>400.8731</v>
       </c>
     </row>
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">KGG</t>
+          <t xml:space="preserve">ISZ</t>
         </is>
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">KIZILAY GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C37">
-        <v>0.1558</v>
+        <v>0.4578</v>
       </c>
       <c t="n" r="D37">
-        <v>0.0095</v>
+        <v>1.6230</v>
       </c>
       <c t="n" r="E37">
-        <v>41.1567</v>
+        <v>16.1801</v>
       </c>
       <c t="n" r="F37">
-        <v>0.2485</v>
+        <v>2.0940</v>
       </c>
       <c t="n" r="G37">
-        <v>41.4373</v>
+        <v>40.2156</v>
       </c>
       <c t="n" r="H37">
-        <v>251.9377</v>
+        <v>295.3695</v>
+      </c>
+      <c t="n" r="I37">
+        <v>916.1917</v>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">MPG</t>
+          <t xml:space="preserve">FNR</t>
         </is>
       </c>
       <c t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">AKTİF PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM (TL) FONU</t>
+          <t xml:space="preserve">FONMAP PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C38">
-        <v>0.5443</v>
+        <v>1.5451</v>
       </c>
       <c t="n" r="D38">
-        <v>1.5363</v>
+        <v>-5.1703</v>
       </c>
       <c t="n" r="E38">
-        <v>28.9879</v>
+        <v>12.4440</v>
       </c>
       <c t="n" r="F38">
-        <v>1.5796</v>
+        <v>4.1946</v>
       </c>
       <c t="n" r="G38">
-        <v>40.7192</v>
-      </c>
-      <c t="n" r="H38">
-        <v>172.4245</v>
-      </c>
-      <c t="n" r="I38">
-        <v>400.7830</v>
+        <v>39.8637</v>
       </c>
     </row>
     <row r="39">
       <c t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">ISZ</t>
+          <t xml:space="preserve">RG4</t>
         </is>
       </c>
       <c t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C39">
-        <v>0.4771</v>
+        <v>0.8311</v>
       </c>
       <c t="n" r="D39">
-        <v>1.6243</v>
+        <v>5.5143</v>
       </c>
       <c t="n" r="E39">
-        <v>16.1871</v>
+        <v>34.9257</v>
       </c>
       <c t="n" r="F39">
-        <v>2.0885</v>
+        <v>13.3350</v>
       </c>
       <c t="n" r="G39">
-        <v>40.2376</v>
+        <v>39.1327</v>
       </c>
       <c t="n" r="H39">
-        <v>295.3483</v>
-      </c>
-      <c t="n" r="I39">
-        <v>916.1052</v>
+        <v>840.7661</v>
       </c>
     </row>
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">RG4</t>
+          <t xml:space="preserve">RGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. GÖKSU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C40">
-        <v>0.8369</v>
+        <v>0.6903</v>
       </c>
       <c t="n" r="D40">
-        <v>5.5404</v>
+        <v>2.1076</v>
       </c>
       <c t="n" r="E40">
-        <v>34.9349</v>
+        <v>31.0058</v>
       </c>
       <c t="n" r="F40">
-        <v>13.3525</v>
+        <v>2.6846</v>
       </c>
       <c t="n" r="G40">
-        <v>39.1814</v>
-      </c>
-      <c t="n" r="H40">
-        <v>840.9113</v>
+        <v>38.4389</v>
       </c>
     </row>
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">RGO</t>
+          <t xml:space="preserve">YD2</t>
         </is>
       </c>
       <c t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. GÖKSU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALZAMİL KİRA GETİRİLİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C41">
-        <v>0.6998</v>
+        <v>0.1749</v>
       </c>
       <c t="n" r="D41">
-        <v>2.1079</v>
+        <v>-0.9217</v>
       </c>
       <c t="n" r="E41">
-        <v>30.8572</v>
+        <v>26.0497</v>
       </c>
       <c t="n" r="F41">
-        <v>2.6852</v>
+        <v>-0.5735</v>
       </c>
       <c t="n" r="G41">
-        <v>38.5009</v>
+        <v>38.3879</v>
+      </c>
+      <c t="n" r="H41">
+        <v>326.7305</v>
+      </c>
+      <c t="n" r="I41">
+        <v>712.8104</v>
       </c>
     </row>
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">YD2</t>
+          <t xml:space="preserve">IIY</t>
         </is>
       </c>
       <c t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALZAMİL KİRA GETİRİLİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ  GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C42">
-        <v>0.1810</v>
+        <v>1.1249</v>
       </c>
       <c t="n" r="D42">
-        <v>-0.9320</v>
+        <v>4.4654</v>
       </c>
       <c t="n" r="E42">
-        <v>26.0496</v>
+        <v>14.4008</v>
       </c>
       <c t="n" r="F42">
-        <v>-0.5614</v>
+        <v>3.6909</v>
       </c>
       <c t="n" r="G42">
-        <v>38.3873</v>
+        <v>37.8903</v>
       </c>
       <c t="n" r="H42">
-        <v>326.7824</v>
+        <v>141.4608</v>
       </c>
       <c t="n" r="I42">
-        <v>712.9093</v>
+        <v>261.1180</v>
       </c>
     </row>
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">IIY</t>
+          <t xml:space="preserve">IKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ  GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C43">
-        <v>1.1364</v>
+        <v>1.4709</v>
       </c>
       <c t="n" r="D43">
-        <v>4.4477</v>
+        <v>4.1002</v>
       </c>
       <c t="n" r="E43">
-        <v>14.4412</v>
+        <v>13.8932</v>
       </c>
       <c t="n" r="F43">
-        <v>3.6673</v>
+        <v>5.2362</v>
       </c>
       <c t="n" r="G43">
-        <v>37.8756</v>
+        <v>37.5045</v>
       </c>
       <c t="n" r="H43">
-        <v>141.4059</v>
+        <v>180.2285</v>
       </c>
       <c t="n" r="I43">
-        <v>261.0203</v>
+        <v>415.7584</v>
       </c>
     </row>
     <row r="44">
       <c t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">IKG</t>
+          <t xml:space="preserve">TGI</t>
         </is>
       </c>
       <c t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">AK PORTFÖY YÖNETİMİ A.Ş.İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C44">
-        <v>1.4182</v>
+        <v>1.8458</v>
       </c>
       <c t="n" r="D44">
-        <v>4.1815</v>
+        <v>5.3321</v>
       </c>
       <c t="n" r="E44">
-        <v>13.8933</v>
+        <v>21.4580</v>
       </c>
       <c t="n" r="F44">
-        <v>5.1346</v>
+        <v>6.0909</v>
       </c>
       <c t="n" r="G44">
-        <v>37.4932</v>
-      </c>
-      <c t="n" r="H44">
-        <v>179.9580</v>
-      </c>
-      <c t="n" r="I44">
-        <v>415.9704</v>
+        <v>35.9739</v>
       </c>
     </row>
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">TGI</t>
+          <t xml:space="preserve">RP1</t>
         </is>
       </c>
       <c t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NOVADA URFA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C45">
-        <v>1.7752</v>
+        <v>0.7268</v>
       </c>
       <c t="n" r="D45">
-        <v>5.2929</v>
+        <v>-0.4197</v>
       </c>
       <c t="n" r="E45">
-        <v>21.4233</v>
+        <v>32.6758</v>
       </c>
       <c t="n" r="F45">
-        <v>5.9516</v>
+        <v>-0.4794</v>
       </c>
       <c t="n" r="G45">
-        <v>36.3903</v>
+        <v>35.5663</v>
+      </c>
+      <c t="n" r="H45">
+        <v>244.2968</v>
+      </c>
+      <c t="n" r="I45">
+        <v>921.6632</v>
       </c>
     </row>
     <row r="46">
@@ -1540,109 +1546,103 @@
         </is>
       </c>
       <c t="n" r="C46">
-        <v>2.9298</v>
+        <v>2.6050</v>
       </c>
       <c t="n" r="D46">
-        <v>7.0980</v>
+        <v>7.0494</v>
       </c>
       <c t="n" r="E46">
-        <v>15.3648</v>
+        <v>15.2470</v>
       </c>
       <c t="n" r="F46">
-        <v>8.9320</v>
+        <v>9.0039</v>
       </c>
       <c t="n" r="G46">
-        <v>35.6892</v>
+        <v>35.4900</v>
       </c>
     </row>
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">RP1</t>
+          <t xml:space="preserve">NNP</t>
         </is>
       </c>
       <c t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. NOVADA URFA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AVANTAJ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C47">
-        <v>0.7277</v>
+        <v>0.5614</v>
       </c>
       <c t="n" r="D47">
-        <v>-0.4213</v>
+        <v>1.7357</v>
       </c>
       <c t="n" r="E47">
-        <v>32.6757</v>
+        <v>26.7535</v>
       </c>
       <c t="n" r="F47">
-        <v>-0.4781</v>
+        <v>2.3873</v>
       </c>
       <c t="n" r="G47">
-        <v>35.5660</v>
+        <v>34.9138</v>
       </c>
       <c t="n" r="H47">
-        <v>244.3013</v>
-      </c>
-      <c t="n" r="I47">
-        <v>921.6480</v>
+        <v>576.9650</v>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">NNP</t>
+          <t xml:space="preserve">RGK</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. AVANTAJ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C48">
-        <v>0.6300</v>
+        <v>-0.0252</v>
       </c>
       <c t="n" r="D48">
-        <v>1.8050</v>
+        <v>-0.1079</v>
       </c>
       <c t="n" r="E48">
-        <v>26.7380</v>
+        <v>34.0368</v>
       </c>
       <c t="n" r="F48">
-        <v>2.3621</v>
+        <v>-0.1193</v>
       </c>
       <c t="n" r="G48">
-        <v>34.9270</v>
-      </c>
-      <c t="n" r="H48">
-        <v>576.7979</v>
+        <v>34.5330</v>
       </c>
     </row>
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">RGK</t>
+          <t xml:space="preserve">NYO</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. ONBİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C49">
-        <v>-0.0216</v>
+        <v>0.9015</v>
       </c>
       <c t="n" r="D49">
-        <v>-0.1094</v>
+        <v>2.6561</v>
       </c>
       <c t="n" r="E49">
-        <v>34.0392</v>
+        <v>27.7577</v>
       </c>
       <c t="n" r="F49">
-        <v>-0.1175</v>
+        <v>3.4455</v>
       </c>
       <c t="n" r="G49">
-        <v>34.5341</v>
+        <v>34.4838</v>
       </c>
     </row>
     <row r="50">
@@ -1657,19 +1657,19 @@
         </is>
       </c>
       <c t="n" r="C50">
-        <v>1.0300</v>
+        <v>0.9202</v>
       </c>
       <c t="n" r="D50">
-        <v>3.8694</v>
+        <v>3.8388</v>
       </c>
       <c t="n" r="E50">
-        <v>13.1326</v>
+        <v>13.1420</v>
       </c>
       <c t="n" r="F50">
-        <v>4.1249</v>
+        <v>4.1615</v>
       </c>
       <c t="n" r="G50">
-        <v>33.7705</v>
+        <v>33.7926</v>
       </c>
     </row>
     <row r="51">
@@ -1684,19 +1684,19 @@
         </is>
       </c>
       <c t="n" r="C51">
-        <v>1.5983</v>
+        <v>1.2939</v>
       </c>
       <c t="n" r="D51">
-        <v>2.5965</v>
+        <v>2.3104</v>
       </c>
       <c t="n" r="E51">
-        <v>10.7856</v>
+        <v>10.6791</v>
       </c>
       <c t="n" r="F51">
-        <v>3.8844</v>
+        <v>3.8370</v>
       </c>
       <c t="n" r="G51">
-        <v>33.0300</v>
+        <v>33.6585</v>
       </c>
     </row>
     <row r="52">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c t="n" r="C52">
-        <v>0.2705</v>
+        <v>0.2647</v>
       </c>
       <c t="n" r="D52">
-        <v>0.7726</v>
+        <v>0.7775</v>
       </c>
       <c t="n" r="E52">
-        <v>31.5275</v>
+        <v>31.5278</v>
       </c>
       <c t="n" r="F52">
-        <v>1.0976</v>
+        <v>1.0936</v>
       </c>
       <c t="n" r="G52">
-        <v>33.0286</v>
+        <v>33.0300</v>
       </c>
       <c t="n" r="H52">
-        <v>316.3817</v>
+        <v>316.3650</v>
       </c>
     </row>
     <row r="53">
@@ -1741,25 +1741,25 @@
         </is>
       </c>
       <c t="n" r="C53">
-        <v>-0.0040</v>
+        <v>0.0000</v>
       </c>
       <c t="n" r="D53">
-        <v>-0.1790</v>
+        <v>-0.1638</v>
       </c>
       <c t="n" r="E53">
-        <v>32.8971</v>
+        <v>32.9099</v>
       </c>
       <c t="n" r="F53">
-        <v>-2.9898</v>
+        <v>-2.9858</v>
       </c>
       <c t="n" r="G53">
-        <v>31.7576</v>
+        <v>31.7705</v>
       </c>
       <c t="n" r="H53">
-        <v>214.9481</v>
+        <v>214.9611</v>
       </c>
       <c t="n" r="I53">
-        <v>684.4187</v>
+        <v>684.4511</v>
       </c>
     </row>
     <row r="54">
@@ -1774,25 +1774,25 @@
         </is>
       </c>
       <c t="n" r="C54">
-        <v>0.2211</v>
+        <v>0.2091</v>
       </c>
       <c t="n" r="D54">
-        <v>-0.5353</v>
+        <v>-0.0637</v>
       </c>
       <c t="n" r="E54">
-        <v>31.2861</v>
+        <v>31.2790</v>
       </c>
       <c t="n" r="F54">
-        <v>0.0854</v>
+        <v>0.0763</v>
       </c>
       <c t="n" r="G54">
-        <v>31.5455</v>
+        <v>31.5603</v>
       </c>
       <c t="n" r="H54">
-        <v>683.7593</v>
+        <v>683.6880</v>
       </c>
       <c t="n" r="I54">
-        <v>1727.6635</v>
+        <v>1727.3480</v>
       </c>
     </row>
     <row r="55">
@@ -1807,19 +1807,19 @@
         </is>
       </c>
       <c t="n" r="C55">
-        <v>-1.3422</v>
+        <v>-1.3495</v>
       </c>
       <c t="n" r="D55">
-        <v>-0.3422</v>
+        <v>-0.3410</v>
       </c>
       <c t="n" r="E55">
-        <v>26.0640</v>
+        <v>26.0521</v>
       </c>
       <c t="n" r="F55">
-        <v>-0.3759</v>
+        <v>-0.3778</v>
       </c>
       <c t="n" r="G55">
-        <v>31.3799</v>
+        <v>31.3790</v>
       </c>
     </row>
     <row r="56">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c t="n" r="C56">
-        <v>0.0103</v>
+        <v>-0.0082</v>
       </c>
       <c t="n" r="D56">
-        <v>0.0454</v>
+        <v>0.0477</v>
       </c>
       <c t="n" r="E56">
-        <v>28.9032</v>
+        <v>28.8979</v>
       </c>
       <c t="n" r="F56">
-        <v>0.2707</v>
+        <v>0.2647</v>
       </c>
       <c t="n" r="G56">
-        <v>31.2018</v>
+        <v>31.1957</v>
       </c>
     </row>
     <row r="57">
@@ -1861,25 +1861,25 @@
         </is>
       </c>
       <c t="n" r="C57">
-        <v>0.3308</v>
+        <v>0.3172</v>
       </c>
       <c t="n" r="D57">
-        <v>1.2026</v>
+        <v>1.2084</v>
       </c>
       <c t="n" r="E57">
-        <v>13.1220</v>
+        <v>13.1200</v>
       </c>
       <c t="n" r="F57">
-        <v>1.4643</v>
+        <v>1.4631</v>
       </c>
       <c t="n" r="G57">
-        <v>30.9793</v>
+        <v>30.9469</v>
       </c>
       <c t="n" r="H57">
-        <v>156.8055</v>
+        <v>156.8025</v>
       </c>
       <c t="n" r="I57">
-        <v>487.1943</v>
+        <v>487.5123</v>
       </c>
     </row>
     <row r="58">
@@ -1894,160 +1894,160 @@
         </is>
       </c>
       <c t="n" r="C58">
-        <v>0.1291</v>
+        <v>0.1186</v>
       </c>
       <c t="n" r="D58">
-        <v>0.8783</v>
+        <v>0.8498</v>
       </c>
       <c t="n" r="E58">
-        <v>27.6042</v>
+        <v>27.6312</v>
       </c>
       <c t="n" r="F58">
-        <v>-5.9538</v>
+        <v>-5.9615</v>
       </c>
       <c t="n" r="G58">
-        <v>29.9856</v>
+        <v>29.9469</v>
       </c>
       <c t="n" r="H58">
-        <v>172.0417</v>
+        <v>172.0196</v>
       </c>
       <c t="n" r="I58">
-        <v>828.0917</v>
+        <v>828.0163</v>
       </c>
     </row>
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">HRE</t>
+          <t xml:space="preserve">ROG</t>
         </is>
       </c>
       <c t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C59">
-        <v>1.5053</v>
+        <v>0.2262</v>
       </c>
       <c t="n" r="D59">
-        <v>3.7619</v>
+        <v>0.7801</v>
       </c>
       <c t="n" r="E59">
-        <v>11.0528</v>
+        <v>-1.0535</v>
       </c>
       <c t="n" r="F59">
-        <v>5.8687</v>
+        <v>1.0830</v>
       </c>
       <c t="n" r="G59">
-        <v>29.7644</v>
+        <v>29.6803</v>
       </c>
     </row>
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">GF2</t>
+          <t xml:space="preserve">NGO</t>
         </is>
       </c>
       <c t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C60">
-        <v>0.1683</v>
+        <v>2.8993</v>
       </c>
       <c t="n" r="D60">
-        <v>4.2742</v>
+        <v>8.1827</v>
       </c>
       <c t="n" r="E60">
-        <v>16.3994</v>
+        <v>15.9731</v>
       </c>
       <c t="n" r="F60">
-        <v>6.7424</v>
+        <v>12.6851</v>
       </c>
       <c t="n" r="G60">
-        <v>29.7254</v>
+        <v>29.6802</v>
       </c>
     </row>
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">FT1</t>
+          <t xml:space="preserve">HRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">HEDEF PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C61">
-        <v>0.1244</v>
+        <v>0.9798</v>
       </c>
       <c t="n" r="D61">
-        <v>0.2133</v>
+        <v>3.6882</v>
       </c>
       <c t="n" r="E61">
-        <v>4.6874</v>
+        <v>11.5380</v>
       </c>
       <c t="n" r="F61">
-        <v>0.2606</v>
+        <v>5.9464</v>
       </c>
       <c t="n" r="G61">
-        <v>29.6828</v>
+        <v>29.5924</v>
       </c>
     </row>
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">ROG</t>
+          <t xml:space="preserve">GF2</t>
         </is>
       </c>
       <c t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ONE PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C62">
-        <v>0.2379</v>
+        <v>0.1909</v>
       </c>
       <c t="n" r="D62">
-        <v>0.7793</v>
+        <v>3.3839</v>
       </c>
       <c t="n" r="E62">
-        <v>-1.0531</v>
+        <v>16.1740</v>
       </c>
       <c t="n" r="F62">
-        <v>1.0822</v>
+        <v>6.6467</v>
       </c>
       <c t="n" r="G62">
-        <v>29.6787</v>
+        <v>29.3648</v>
       </c>
     </row>
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">NGO</t>
+          <t xml:space="preserve">FT1</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. ONUNCU GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">FT GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C63">
-        <v>3.2185</v>
+        <v>0.0941</v>
       </c>
       <c t="n" r="D63">
-        <v>8.9462</v>
+        <v>0.2159</v>
       </c>
       <c t="n" r="E63">
-        <v>15.9853</v>
+        <v>4.4646</v>
       </c>
       <c t="n" r="F63">
-        <v>12.5752</v>
+        <v>0.2582</v>
       </c>
       <c t="n" r="G63">
-        <v>29.5980</v>
+        <v>29.3419</v>
       </c>
     </row>
     <row r="64">
@@ -2062,25 +2062,25 @@
         </is>
       </c>
       <c t="n" r="C64">
-        <v>0.1284</v>
+        <v>0.1116</v>
       </c>
       <c t="n" r="D64">
-        <v>0.2858</v>
+        <v>0.2830</v>
       </c>
       <c t="n" r="E64">
-        <v>28.6619</v>
+        <v>28.6524</v>
       </c>
       <c t="n" r="F64">
-        <v>0.3683</v>
+        <v>0.3716</v>
       </c>
       <c t="n" r="G64">
-        <v>29.1263</v>
+        <v>29.1220</v>
       </c>
       <c t="n" r="H64">
-        <v>230.7314</v>
+        <v>230.7425</v>
       </c>
       <c t="n" r="I64">
-        <v>353.7995</v>
+        <v>353.8146</v>
       </c>
     </row>
     <row r="65">
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c t="n" r="C65">
-        <v>-0.0517</v>
+        <v>-0.0534</v>
       </c>
       <c t="n" r="D65">
-        <v>-0.1419</v>
+        <v>-0.1391</v>
       </c>
       <c t="n" r="E65">
-        <v>30.4723</v>
+        <v>30.4718</v>
       </c>
       <c t="n" r="F65">
-        <v>-0.1794</v>
+        <v>-0.1827</v>
       </c>
       <c t="n" r="G65">
-        <v>28.9968</v>
+        <v>28.8369</v>
       </c>
     </row>
     <row r="66">
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c t="n" r="C66">
-        <v>0.3546</v>
+        <v>0.3397</v>
       </c>
       <c t="n" r="D66">
-        <v>0.6580</v>
+        <v>0.6473</v>
       </c>
       <c t="n" r="E66">
-        <v>26.7127</v>
+        <v>26.7073</v>
       </c>
       <c t="n" r="F66">
-        <v>2.4717</v>
+        <v>2.4745</v>
       </c>
       <c t="n" r="G66">
-        <v>28.7598</v>
+        <v>28.7349</v>
       </c>
     </row>
     <row r="67">
@@ -2149,16 +2149,16 @@
         </is>
       </c>
       <c t="n" r="C67">
-        <v>-0.0182</v>
+        <v>-0.0183</v>
       </c>
       <c t="n" r="D67">
-        <v>-0.0587</v>
+        <v>-0.0586</v>
       </c>
       <c t="n" r="E67">
         <v>28.1682</v>
       </c>
       <c t="n" r="F67">
-        <v>-0.0780</v>
+        <v>-0.0782</v>
       </c>
       <c t="n" r="G67">
         <v>28.0128</v>
@@ -2176,25 +2176,25 @@
         </is>
       </c>
       <c t="n" r="C68">
-        <v>1.2694</v>
+        <v>1.2438</v>
       </c>
       <c t="n" r="D68">
-        <v>4.1943</v>
+        <v>4.1862</v>
       </c>
       <c t="n" r="E68">
-        <v>16.3025</v>
+        <v>16.3016</v>
       </c>
       <c t="n" r="F68">
-        <v>4.4983</v>
+        <v>4.5186</v>
       </c>
       <c t="n" r="G68">
-        <v>27.8959</v>
+        <v>27.9029</v>
       </c>
       <c t="n" r="H68">
-        <v>130.9556</v>
+        <v>131.0004</v>
       </c>
       <c t="n" r="I68">
-        <v>636302.5393</v>
+        <v>636425.8859</v>
       </c>
     </row>
     <row r="69">
@@ -2209,25 +2209,25 @@
         </is>
       </c>
       <c t="n" r="C69">
-        <v>0.5629</v>
+        <v>0.5530</v>
       </c>
       <c t="n" r="D69">
-        <v>-1.7699</v>
+        <v>-1.8402</v>
       </c>
       <c t="n" r="E69">
-        <v>24.7468</v>
+        <v>24.8965</v>
       </c>
       <c t="n" r="F69">
-        <v>-20.3922</v>
+        <v>-20.3965</v>
       </c>
       <c t="n" r="G69">
-        <v>27.1789</v>
+        <v>27.1256</v>
       </c>
       <c t="n" r="H69">
-        <v>242.9197</v>
+        <v>242.9009</v>
       </c>
       <c t="n" r="I69">
-        <v>1973.9311</v>
+        <v>1973.8174</v>
       </c>
     </row>
     <row r="70">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c t="n" r="C70">
-        <v>0.7951</v>
+        <v>0.7940</v>
       </c>
       <c t="n" r="D70">
-        <v>-1.1819</v>
+        <v>-1.1366</v>
       </c>
       <c t="n" r="E70">
-        <v>25.3975</v>
+        <v>25.3250</v>
       </c>
       <c t="n" r="F70">
-        <v>-0.3214</v>
+        <v>-0.3237</v>
       </c>
       <c t="n" r="G70">
-        <v>26.1219</v>
+        <v>26.1230</v>
       </c>
       <c t="n" r="H70">
-        <v>49.1317</v>
+        <v>49.1283</v>
       </c>
       <c t="n" r="I70">
-        <v>980.7928</v>
+        <v>980.7680</v>
       </c>
     </row>
     <row r="71">
@@ -2275,25 +2275,25 @@
         </is>
       </c>
       <c t="n" r="C71">
-        <v>1.2617</v>
+        <v>1.2164</v>
       </c>
       <c t="n" r="D71">
-        <v>3.4002</v>
+        <v>3.3821</v>
       </c>
       <c t="n" r="E71">
-        <v>17.4396</v>
+        <v>17.4232</v>
       </c>
       <c t="n" r="F71">
-        <v>5.0015</v>
+        <v>5.0303</v>
       </c>
       <c t="n" r="G71">
-        <v>25.7885</v>
+        <v>25.8034</v>
       </c>
       <c t="n" r="H71">
-        <v>220.7156</v>
+        <v>220.8035</v>
       </c>
       <c t="n" r="I71">
-        <v>502.4595</v>
+        <v>502.6631</v>
       </c>
     </row>
     <row r="72">
@@ -2308,25 +2308,25 @@
         </is>
       </c>
       <c t="n" r="C72">
-        <v>4.1313</v>
+        <v>4.0944</v>
       </c>
       <c t="n" r="D72">
-        <v>4.9276</v>
+        <v>4.8696</v>
       </c>
       <c t="n" r="E72">
-        <v>14.2756</v>
+        <v>14.2468</v>
       </c>
       <c t="n" r="F72">
-        <v>1.0324</v>
+        <v>1.0202</v>
       </c>
       <c t="n" r="G72">
-        <v>25.4675</v>
+        <v>25.4262</v>
       </c>
       <c t="n" r="H72">
-        <v>331.4108</v>
+        <v>331.3588</v>
       </c>
       <c t="n" r="I72">
-        <v>836.8971</v>
+        <v>836.7842</v>
       </c>
     </row>
     <row r="73">
@@ -2341,22 +2341,22 @@
         </is>
       </c>
       <c t="n" r="C73">
-        <v>1.4798</v>
+        <v>1.3605</v>
       </c>
       <c t="n" r="D73">
-        <v>3.7841</v>
+        <v>3.6792</v>
       </c>
       <c t="n" r="E73">
-        <v>-0.1318</v>
+        <v>-0.2062</v>
       </c>
       <c t="n" r="F73">
-        <v>4.3759</v>
+        <v>4.4060</v>
       </c>
       <c t="n" r="G73">
-        <v>25.4672</v>
+        <v>25.4028</v>
       </c>
       <c t="n" r="H73">
-        <v>162.7206</v>
+        <v>162.7964</v>
       </c>
     </row>
     <row r="74">
@@ -2371,25 +2371,25 @@
         </is>
       </c>
       <c t="n" r="C74">
-        <v>-0.0811</v>
+        <v>-0.0836</v>
       </c>
       <c t="n" r="D74">
-        <v>-0.2626</v>
+        <v>-0.2686</v>
       </c>
       <c t="n" r="E74">
-        <v>25.3585</v>
+        <v>25.3587</v>
       </c>
       <c t="n" r="F74">
-        <v>0.0414</v>
+        <v>0.0382</v>
       </c>
       <c t="n" r="G74">
-        <v>25.3287</v>
+        <v>25.3286</v>
       </c>
       <c t="n" r="H74">
-        <v>200.1661</v>
+        <v>200.1567</v>
       </c>
       <c t="n" r="I74">
-        <v>400.3803</v>
+        <v>400.3880</v>
       </c>
     </row>
     <row r="75">
@@ -2404,19 +2404,19 @@
         </is>
       </c>
       <c t="n" r="C75">
-        <v>-2.2705</v>
+        <v>-2.3560</v>
       </c>
       <c t="n" r="D75">
-        <v>0.0612</v>
+        <v>0.0420</v>
       </c>
       <c t="n" r="E75">
-        <v>17.0705</v>
+        <v>17.0508</v>
       </c>
       <c t="n" r="F75">
-        <v>1.1275</v>
+        <v>1.1473</v>
       </c>
       <c t="n" r="G75">
-        <v>24.9729</v>
+        <v>24.9886</v>
       </c>
     </row>
     <row r="76">
@@ -2431,19 +2431,19 @@
         </is>
       </c>
       <c t="n" r="C76">
-        <v>0.4040</v>
+        <v>0.3966</v>
       </c>
       <c t="n" r="D76">
-        <v>-0.0997</v>
+        <v>-0.1006</v>
       </c>
       <c t="n" r="E76">
-        <v>23.1935</v>
+        <v>23.1885</v>
       </c>
       <c t="n" r="F76">
-        <v>-0.1254</v>
+        <v>-0.1302</v>
       </c>
       <c t="n" r="G76">
-        <v>24.9272</v>
+        <v>24.9263</v>
       </c>
     </row>
     <row r="77">
@@ -2458,22 +2458,22 @@
         </is>
       </c>
       <c t="n" r="C77">
-        <v>-2.6067</v>
+        <v>-2.6326</v>
       </c>
       <c t="n" r="D77">
-        <v>-2.3274</v>
+        <v>-2.2623</v>
       </c>
       <c t="n" r="E77">
-        <v>8.0189</v>
+        <v>7.9559</v>
       </c>
       <c t="n" r="F77">
-        <v>-2.7835</v>
+        <v>-2.8003</v>
       </c>
       <c t="n" r="G77">
-        <v>24.5422</v>
+        <v>24.5372</v>
       </c>
       <c t="n" r="H77">
-        <v>148.1098</v>
+        <v>148.0669</v>
       </c>
     </row>
     <row r="78">
@@ -2488,25 +2488,25 @@
         </is>
       </c>
       <c t="n" r="C78">
-        <v>-1.2841</v>
+        <v>-1.2618</v>
       </c>
       <c t="n" r="D78">
-        <v>5.5717</v>
+        <v>5.6018</v>
       </c>
       <c t="n" r="E78">
-        <v>24.8277</v>
+        <v>24.8633</v>
       </c>
       <c t="n" r="F78">
-        <v>-1.5959</v>
+        <v>-1.5597</v>
       </c>
       <c t="n" r="G78">
-        <v>23.6738</v>
+        <v>23.7416</v>
       </c>
       <c t="n" r="H78">
-        <v>253.2997</v>
+        <v>253.4298</v>
       </c>
       <c t="n" r="I78">
-        <v>783.9845</v>
+        <v>788.8851</v>
       </c>
     </row>
     <row r="79">
@@ -2521,25 +2521,25 @@
         </is>
       </c>
       <c t="n" r="C79">
-        <v>6.5790</v>
+        <v>6.5667</v>
       </c>
       <c t="n" r="D79">
-        <v>8.2565</v>
+        <v>8.3148</v>
       </c>
       <c t="n" r="E79">
-        <v>16.0730</v>
+        <v>16.1947</v>
       </c>
       <c t="n" r="F79">
-        <v>6.9623</v>
+        <v>6.9902</v>
       </c>
       <c t="n" r="G79">
-        <v>23.1284</v>
+        <v>23.1558</v>
       </c>
       <c t="n" r="H79">
-        <v>244.2741</v>
+        <v>244.3638</v>
       </c>
       <c t="n" r="I79">
-        <v>781.2917</v>
+        <v>781.5213</v>
       </c>
     </row>
     <row r="80">
@@ -2554,22 +2554,22 @@
         </is>
       </c>
       <c t="n" r="C80">
-        <v>-0.2503</v>
+        <v>-0.2515</v>
       </c>
       <c t="n" r="D80">
-        <v>-0.7563</v>
+        <v>-0.7554</v>
       </c>
       <c t="n" r="E80">
-        <v>22.9093</v>
+        <v>22.9084</v>
       </c>
       <c t="n" r="F80">
-        <v>-0.8725</v>
+        <v>-0.8742</v>
       </c>
       <c t="n" r="G80">
-        <v>21.6906</v>
+        <v>21.6866</v>
       </c>
       <c t="n" r="H80">
-        <v>170.7667</v>
+        <v>170.7621</v>
       </c>
     </row>
     <row r="81">
@@ -2584,25 +2584,25 @@
         </is>
       </c>
       <c t="n" r="C81">
-        <v>0.4043</v>
+        <v>0.3741</v>
       </c>
       <c t="n" r="D81">
-        <v>1.0179</v>
+        <v>1.0233</v>
       </c>
       <c t="n" r="E81">
-        <v>3.7945</v>
+        <v>3.7656</v>
       </c>
       <c t="n" r="F81">
-        <v>1.4084</v>
+        <v>1.4070</v>
       </c>
       <c t="n" r="G81">
-        <v>21.4339</v>
+        <v>21.4215</v>
       </c>
       <c t="n" r="H81">
-        <v>264.5354</v>
+        <v>264.5304</v>
       </c>
       <c t="n" r="I81">
-        <v>794.6134</v>
+        <v>794.5208</v>
       </c>
     </row>
     <row r="82">
@@ -2617,22 +2617,22 @@
         </is>
       </c>
       <c t="n" r="C82">
-        <v>-0.1025</v>
+        <v>-0.1058</v>
       </c>
       <c t="n" r="D82">
-        <v>-0.3079</v>
+        <v>-0.3023</v>
       </c>
       <c t="n" r="E82">
-        <v>23.5578</v>
+        <v>23.5575</v>
       </c>
       <c t="n" r="F82">
-        <v>-2.4900</v>
+        <v>-2.4954</v>
       </c>
       <c t="n" r="G82">
         <v>21.2900</v>
       </c>
       <c t="n" r="H82">
-        <v>46.6381</v>
+        <v>46.6299</v>
       </c>
     </row>
     <row r="83">
@@ -2647,22 +2647,22 @@
         </is>
       </c>
       <c t="n" r="C83">
-        <v>1.1175</v>
+        <v>1.2245</v>
       </c>
       <c t="n" r="D83">
-        <v>2.8360</v>
+        <v>2.8226</v>
       </c>
       <c t="n" r="E83">
-        <v>12.1051</v>
+        <v>12.0502</v>
       </c>
       <c t="n" r="F83">
-        <v>2.0076</v>
+        <v>1.9880</v>
       </c>
       <c t="n" r="G83">
-        <v>21.2013</v>
+        <v>21.1677</v>
       </c>
       <c t="n" r="H83">
-        <v>81.5806</v>
+        <v>81.5457</v>
       </c>
     </row>
     <row r="84">
@@ -2677,25 +2677,25 @@
         </is>
       </c>
       <c t="n" r="C84">
-        <v>0.2722</v>
+        <v>0.2775</v>
       </c>
       <c t="n" r="D84">
-        <v>0.9443</v>
+        <v>0.9460</v>
       </c>
       <c t="n" r="E84">
-        <v>5.6646</v>
+        <v>5.6674</v>
       </c>
       <c t="n" r="F84">
-        <v>1.1275</v>
+        <v>1.1304</v>
       </c>
       <c t="n" r="G84">
-        <v>20.9285</v>
+        <v>20.9317</v>
       </c>
       <c t="n" r="H84">
-        <v>221.1313</v>
+        <v>221.1403</v>
       </c>
       <c t="n" r="I84">
-        <v>990.0077</v>
+        <v>990.1064</v>
       </c>
     </row>
     <row r="85">
@@ -2710,25 +2710,25 @@
         </is>
       </c>
       <c t="n" r="C85">
-        <v>0.4647</v>
+        <v>0.4544</v>
       </c>
       <c t="n" r="D85">
-        <v>0.8260</v>
+        <v>0.8160</v>
       </c>
       <c t="n" r="E85">
-        <v>17.2982</v>
+        <v>17.2588</v>
       </c>
       <c t="n" r="F85">
-        <v>1.0157</v>
+        <v>1.0073</v>
       </c>
       <c t="n" r="G85">
-        <v>20.6188</v>
+        <v>20.5778</v>
       </c>
       <c t="n" r="H85">
-        <v>174.3878</v>
+        <v>174.3650</v>
       </c>
       <c t="n" r="I85">
-        <v>1191.4738</v>
+        <v>1190.9930</v>
       </c>
     </row>
     <row r="86">
@@ -2743,88 +2743,88 @@
         </is>
       </c>
       <c t="n" r="C86">
-        <v>-1.6157</v>
+        <v>-1.7317</v>
       </c>
       <c t="n" r="D86">
-        <v>-0.2041</v>
+        <v>-0.3172</v>
       </c>
       <c t="n" r="E86">
-        <v>16.6177</v>
+        <v>16.4914</v>
       </c>
       <c t="n" r="F86">
-        <v>0.5254</v>
+        <v>0.4196</v>
       </c>
       <c t="n" r="G86">
-        <v>20.2492</v>
+        <v>20.1199</v>
       </c>
       <c t="n" r="H86">
-        <v>368.8855</v>
+        <v>368.3919</v>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">AZ6</t>
+          <t xml:space="preserve">OG2</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.UFUK KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C87">
-        <v>-0.1280</v>
+        <v>0.0525</v>
       </c>
       <c t="n" r="D87">
-        <v>1.2716</v>
+        <v>-0.0946</v>
       </c>
       <c t="n" r="E87">
-        <v>14.8556</v>
+        <v>15.2805</v>
       </c>
       <c t="n" r="F87">
-        <v>-2.7636</v>
+        <v>0.3862</v>
       </c>
       <c t="n" r="G87">
-        <v>19.4917</v>
+        <v>19.3695</v>
       </c>
       <c t="n" r="H87">
-        <v>150.3859</v>
+        <v>116.2443</v>
       </c>
       <c t="n" r="I87">
-        <v>419.0029</v>
+        <v>1159.6388</v>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">OG2</t>
+          <t xml:space="preserve">AZ6</t>
         </is>
       </c>
       <c t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">OMURGA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.UFUK KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. DÖRDÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C88">
-        <v>0.0689</v>
+        <v>-0.1511</v>
       </c>
       <c t="n" r="D88">
-        <v>-0.1084</v>
+        <v>1.0790</v>
       </c>
       <c t="n" r="E88">
-        <v>15.2832</v>
+        <v>15.0460</v>
       </c>
       <c t="n" r="F88">
-        <v>0.3875</v>
+        <v>-2.7969</v>
       </c>
       <c t="n" r="G88">
-        <v>19.3693</v>
+        <v>19.2522</v>
       </c>
       <c t="n" r="H88">
-        <v>116.2470</v>
+        <v>150.3002</v>
       </c>
       <c t="n" r="I88">
-        <v>1159.6547</v>
+        <v>418.8253</v>
       </c>
     </row>
     <row r="89">
@@ -2839,22 +2839,22 @@
         </is>
       </c>
       <c t="n" r="C89">
-        <v>0.5180</v>
+        <v>0.4787</v>
       </c>
       <c t="n" r="D89">
-        <v>1.2178</v>
+        <v>1.1991</v>
       </c>
       <c t="n" r="E89">
-        <v>11.5916</v>
+        <v>11.6500</v>
       </c>
       <c t="n" r="F89">
-        <v>-0.7445</v>
+        <v>-0.7557</v>
       </c>
       <c t="n" r="G89">
-        <v>19.0998</v>
+        <v>19.0783</v>
       </c>
       <c t="n" r="H89">
-        <v>152.0923</v>
+        <v>152.0638</v>
       </c>
     </row>
     <row r="90">
@@ -2869,148 +2869,148 @@
         </is>
       </c>
       <c t="n" r="C90">
-        <v>-0.2673</v>
+        <v>-0.2480</v>
       </c>
       <c t="n" r="D90">
-        <v>-0.1760</v>
+        <v>-0.1767</v>
       </c>
       <c t="n" r="E90">
-        <v>19.1434</v>
+        <v>19.1420</v>
       </c>
       <c t="n" r="F90">
-        <v>-0.0348</v>
+        <v>-0.0342</v>
       </c>
       <c t="n" r="G90">
-        <v>18.8328</v>
+        <v>18.8318</v>
       </c>
       <c t="n" r="H90">
-        <v>1436.5442</v>
+        <v>1436.5535</v>
       </c>
     </row>
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">UNC</t>
+          <t xml:space="preserve">YD4</t>
         </is>
       </c>
       <c t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C91">
-        <v>0.4658</v>
+        <v>-0.2146</v>
       </c>
       <c t="n" r="D91">
-        <v>1.7921</v>
+        <v>-0.5440</v>
       </c>
       <c t="n" r="E91">
-        <v>8.7156</v>
+        <v>11.1788</v>
       </c>
       <c t="n" r="F91">
-        <v>1.7210</v>
+        <v>-0.6298</v>
       </c>
       <c t="n" r="G91">
-        <v>18.0346</v>
+        <v>17.9954</v>
       </c>
       <c t="n" r="H91">
-        <v>75.7846</v>
+        <v>245.6621</v>
+      </c>
+      <c t="n" r="I91">
+        <v>1014.0707</v>
       </c>
     </row>
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">YD4</t>
+          <t xml:space="preserve">UNC</t>
         </is>
       </c>
       <c t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C92">
-        <v>-0.2103</v>
+        <v>0.4492</v>
       </c>
       <c t="n" r="D92">
-        <v>-0.5535</v>
+        <v>1.8029</v>
       </c>
       <c t="n" r="E92">
-        <v>11.1788</v>
+        <v>8.7065</v>
       </c>
       <c t="n" r="F92">
-        <v>-0.6201</v>
+        <v>1.7135</v>
       </c>
       <c t="n" r="G92">
-        <v>17.9938</v>
+        <v>17.9951</v>
       </c>
       <c t="n" r="H92">
-        <v>245.6962</v>
-      </c>
-      <c t="n" r="I92">
-        <v>1013.6160</v>
+        <v>75.7717</v>
       </c>
     </row>
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">RP2</t>
+          <t xml:space="preserve">NMC</t>
         </is>
       </c>
       <c t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. M CHARM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C93">
-        <v>0.7465</v>
+        <v>-1.5598</v>
       </c>
       <c t="n" r="D93">
-        <v>1.7929</v>
+        <v>-1.0647</v>
       </c>
       <c t="n" r="E93">
-        <v>16.8409</v>
+        <v>25.3558</v>
       </c>
       <c t="n" r="F93">
-        <v>2.1710</v>
+        <v>-0.8549</v>
       </c>
       <c t="n" r="G93">
-        <v>17.9670</v>
+        <v>17.8396</v>
       </c>
       <c t="n" r="H93">
-        <v>143.3566</v>
-      </c>
-      <c t="n" r="I93">
-        <v>448.2166</v>
+        <v>215.9918</v>
       </c>
     </row>
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">NMC</t>
+          <t xml:space="preserve">RP2</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. M CHARM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİM A.Ş. ANADOLU STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C94">
-        <v>-1.5427</v>
+        <v>0.5414</v>
       </c>
       <c t="n" r="D94">
-        <v>-1.0650</v>
+        <v>1.3675</v>
       </c>
       <c t="n" r="E94">
-        <v>25.6597</v>
+        <v>16.7312</v>
       </c>
       <c t="n" r="F94">
-        <v>-0.8523</v>
+        <v>1.9781</v>
       </c>
       <c t="n" r="G94">
-        <v>17.8368</v>
+        <v>17.7119</v>
       </c>
       <c t="n" r="H94">
-        <v>215.9999</v>
+        <v>142.8972</v>
+      </c>
+      <c t="n" r="I94">
+        <v>447.0069</v>
       </c>
     </row>
     <row r="95">
@@ -3025,22 +3025,22 @@
         </is>
       </c>
       <c t="n" r="C95">
-        <v>-0.1292</v>
+        <v>-0.1528</v>
       </c>
       <c t="n" r="D95">
-        <v>-0.3946</v>
+        <v>-0.4054</v>
       </c>
       <c t="n" r="E95">
-        <v>26.9064</v>
+        <v>26.8820</v>
       </c>
       <c t="n" r="F95">
-        <v>-0.4775</v>
+        <v>-0.5054</v>
       </c>
       <c t="n" r="G95">
-        <v>17.7020</v>
+        <v>17.6791</v>
       </c>
       <c t="n" r="H95">
-        <v>775.5096</v>
+        <v>775.2640</v>
       </c>
     </row>
     <row r="96">
@@ -3055,25 +3055,25 @@
         </is>
       </c>
       <c t="n" r="C96">
-        <v>-0.3195</v>
+        <v>-0.1554</v>
       </c>
       <c t="n" r="D96">
-        <v>-2.1316</v>
+        <v>-2.0516</v>
       </c>
       <c t="n" r="E96">
-        <v>11.7644</v>
+        <v>11.7608</v>
       </c>
       <c t="n" r="F96">
-        <v>-2.3186</v>
+        <v>-2.3312</v>
       </c>
       <c t="n" r="G96">
-        <v>17.1613</v>
+        <v>17.1631</v>
       </c>
       <c t="n" r="H96">
-        <v>148.5449</v>
+        <v>148.5127</v>
       </c>
       <c t="n" r="I96">
-        <v>654.1030</v>
+        <v>655.0441</v>
       </c>
     </row>
     <row r="97">
@@ -3088,25 +3088,25 @@
         </is>
       </c>
       <c t="n" r="C97">
-        <v>-0.2022</v>
+        <v>-0.2144</v>
       </c>
       <c t="n" r="D97">
-        <v>0.6261</v>
+        <v>0.6240</v>
       </c>
       <c t="n" r="E97">
-        <v>6.2037</v>
+        <v>6.2031</v>
       </c>
       <c t="n" r="F97">
-        <v>-0.6563</v>
+        <v>-0.6518</v>
       </c>
       <c t="n" r="G97">
-        <v>16.9527</v>
+        <v>16.9569</v>
       </c>
       <c t="n" r="H97">
-        <v>320.7766</v>
+        <v>320.7958</v>
       </c>
       <c t="n" r="I97">
-        <v>1601.5938</v>
+        <v>1601.6717</v>
       </c>
     </row>
     <row r="98">
@@ -3121,19 +3121,19 @@
         </is>
       </c>
       <c t="n" r="C98">
-        <v>-0.2508</v>
+        <v>-0.2510</v>
       </c>
       <c t="n" r="D98">
         <v>-0.2529</v>
       </c>
       <c t="n" r="E98">
-        <v>5.3807</v>
+        <v>5.3805</v>
       </c>
       <c t="n" r="F98">
         <v>-0.5035</v>
       </c>
       <c t="n" r="G98">
-        <v>16.9171</v>
+        <v>16.9169</v>
       </c>
     </row>
     <row r="99">
@@ -3148,22 +3148,22 @@
         </is>
       </c>
       <c t="n" r="C99">
-        <v>-0.0008</v>
+        <v>-0.0011</v>
       </c>
       <c t="n" r="D99">
-        <v>-0.0403</v>
+        <v>-0.0402</v>
       </c>
       <c t="n" r="E99">
-        <v>16.1307</v>
+        <v>16.1306</v>
       </c>
       <c t="n" r="F99">
-        <v>-0.0462</v>
+        <v>-0.0463</v>
       </c>
       <c t="n" r="G99">
-        <v>16.0174</v>
+        <v>16.0173</v>
       </c>
       <c t="n" r="H99">
-        <v>580.0909</v>
+        <v>580.0902</v>
       </c>
     </row>
     <row r="100">
@@ -3178,25 +3178,25 @@
         </is>
       </c>
       <c t="n" r="C100">
-        <v>1.0019</v>
+        <v>0.9012</v>
       </c>
       <c t="n" r="D100">
-        <v>-0.7528</v>
+        <v>-0.8190</v>
       </c>
       <c t="n" r="E100">
-        <v>-0.2189</v>
+        <v>0.4231</v>
       </c>
       <c t="n" r="F100">
-        <v>0.3234</v>
+        <v>0.3539</v>
       </c>
       <c t="n" r="G100">
-        <v>15.6837</v>
+        <v>15.6138</v>
       </c>
       <c t="n" r="H100">
-        <v>0.8715</v>
+        <v>0.9022</v>
       </c>
       <c t="n" r="I100">
-        <v>59.0137</v>
+        <v>59.0621</v>
       </c>
     </row>
     <row r="101">
@@ -3211,22 +3211,22 @@
         </is>
       </c>
       <c t="n" r="C101">
-        <v>0.3578</v>
+        <v>0.2823</v>
       </c>
       <c t="n" r="D101">
-        <v>2.3991</v>
+        <v>2.0474</v>
       </c>
       <c t="n" r="E101">
-        <v>14.9621</v>
+        <v>15.0261</v>
       </c>
       <c t="n" r="F101">
-        <v>3.6846</v>
+        <v>3.6764</v>
       </c>
       <c t="n" r="G101">
-        <v>15.0775</v>
+        <v>14.7884</v>
       </c>
       <c t="n" r="H101">
-        <v>188.1793</v>
+        <v>188.1564</v>
       </c>
     </row>
     <row r="102">
@@ -3241,19 +3241,19 @@
         </is>
       </c>
       <c t="n" r="C102">
-        <v>-0.4327</v>
+        <v>-0.4333</v>
       </c>
       <c t="n" r="D102">
-        <v>-0.8165</v>
+        <v>-0.8043</v>
       </c>
       <c t="n" r="E102">
-        <v>16.3903</v>
+        <v>16.3908</v>
       </c>
       <c t="n" r="F102">
-        <v>-0.9471</v>
+        <v>-0.9597</v>
       </c>
       <c t="n" r="G102">
-        <v>14.7232</v>
+        <v>14.7249</v>
       </c>
     </row>
     <row r="103">
@@ -3268,25 +3268,25 @@
         </is>
       </c>
       <c t="n" r="C103">
-        <v>0.0237</v>
+        <v>0.0158</v>
       </c>
       <c t="n" r="D103">
-        <v>1.5594</v>
+        <v>1.4736</v>
       </c>
       <c t="n" r="E103">
-        <v>4.6288</v>
+        <v>4.7084</v>
       </c>
       <c t="n" r="F103">
-        <v>1.1911</v>
+        <v>1.1699</v>
       </c>
       <c t="n" r="G103">
-        <v>14.2367</v>
+        <v>14.1274</v>
       </c>
       <c t="n" r="H103">
-        <v>266.1086</v>
+        <v>266.0318</v>
       </c>
       <c t="n" r="I103">
-        <v>1193.3946</v>
+        <v>1193.1231</v>
       </c>
     </row>
     <row r="104">
@@ -3301,58 +3301,52 @@
         </is>
       </c>
       <c t="n" r="C104">
-        <v>-0.1294</v>
+        <v>-0.1379</v>
       </c>
       <c t="n" r="D104">
-        <v>0.5155</v>
+        <v>0.5005</v>
       </c>
       <c t="n" r="E104">
-        <v>12.7231</v>
+        <v>12.6998</v>
       </c>
       <c t="n" r="F104">
-        <v>1.2264</v>
+        <v>1.2230</v>
       </c>
       <c t="n" r="G104">
-        <v>13.9576</v>
+        <v>13.9739</v>
       </c>
       <c t="n" r="H104">
-        <v>262.6431</v>
+        <v>262.6310</v>
       </c>
       <c t="n" r="I104">
-        <v>474.6751</v>
+        <v>474.6771</v>
       </c>
     </row>
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">FRG</t>
+          <t xml:space="preserve">NBA</t>
         </is>
       </c>
       <c t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C105">
-        <v>1.7330</v>
+        <v>-29.6122</v>
       </c>
       <c t="n" r="D105">
-        <v>2.1226</v>
+        <v>-33.0098</v>
       </c>
       <c t="n" r="E105">
-        <v>14.9717</v>
+        <v>1864.4598</v>
       </c>
       <c t="n" r="F105">
-        <v>4.6487</v>
+        <v>-33.2342</v>
       </c>
       <c t="n" r="G105">
-        <v>13.7531</v>
-      </c>
-      <c t="n" r="H105">
-        <v>93.2712</v>
-      </c>
-      <c t="n" r="I105">
-        <v>441.1140</v>
+        <v>13.7676</v>
       </c>
     </row>
     <row r="106">
@@ -3367,22 +3361,22 @@
         </is>
       </c>
       <c t="n" r="C106">
-        <v>0.0096</v>
+        <v>0.0081</v>
       </c>
       <c t="n" r="D106">
-        <v>0.1233</v>
+        <v>0.1251</v>
       </c>
       <c t="n" r="E106">
-        <v>13.7657</v>
+        <v>13.7633</v>
       </c>
       <c t="n" r="F106">
-        <v>-0.9470</v>
+        <v>-0.9496</v>
       </c>
       <c t="n" r="G106">
-        <v>13.7073</v>
+        <v>13.7101</v>
       </c>
       <c t="n" r="H106">
-        <v>226.6047</v>
+        <v>226.5963</v>
       </c>
     </row>
     <row r="107">
@@ -3397,52 +3391,52 @@
         </is>
       </c>
       <c t="n" r="C107">
-        <v>0.0277</v>
+        <v>0.0310</v>
       </c>
       <c t="n" r="D107">
-        <v>2.2693</v>
+        <v>2.2727</v>
       </c>
       <c t="n" r="E107">
-        <v>3.5999</v>
+        <v>3.5868</v>
       </c>
       <c t="n" r="F107">
-        <v>2.4588</v>
+        <v>2.4560</v>
       </c>
       <c t="n" r="G107">
-        <v>13.4129</v>
+        <v>13.3983</v>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">RP4</t>
+          <t xml:space="preserve">FRG</t>
         </is>
       </c>
       <c t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. FIRSAT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C108">
-        <v>1.4469</v>
+        <v>1.1749</v>
       </c>
       <c t="n" r="D108">
-        <v>-5.7004</v>
+        <v>0.8899</v>
       </c>
       <c t="n" r="E108">
-        <v>10.5556</v>
+        <v>14.6364</v>
       </c>
       <c t="n" r="F108">
-        <v>-4.5790</v>
+        <v>4.1499</v>
       </c>
       <c t="n" r="G108">
-        <v>13.2854</v>
+        <v>13.1019</v>
       </c>
       <c t="n" r="H108">
-        <v>109.5691</v>
+        <v>92.3500</v>
       </c>
       <c t="n" r="I108">
-        <v>359.9718</v>
+        <v>438.0770</v>
       </c>
     </row>
     <row r="109">
@@ -3457,199 +3451,205 @@
         </is>
       </c>
       <c t="n" r="C109">
-        <v>-0.0540</v>
+        <v>-0.0550</v>
       </c>
       <c t="n" r="D109">
-        <v>-0.3443</v>
+        <v>-0.3412</v>
       </c>
       <c t="n" r="E109">
         <v>13.7144</v>
       </c>
       <c t="n" r="F109">
-        <v>-0.5489</v>
+        <v>-0.5508</v>
       </c>
       <c t="n" r="G109">
-        <v>13.0495</v>
+        <v>13.0506</v>
       </c>
       <c t="n" r="H109">
-        <v>493.7423</v>
+        <v>493.7309</v>
       </c>
     </row>
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">ZVE</t>
+          <t xml:space="preserve">YG7</t>
         </is>
       </c>
       <c t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C110">
-        <v>-0.0219</v>
+        <v>1.0058</v>
       </c>
       <c t="n" r="D110">
-        <v>0.1432</v>
+        <v>1.6489</v>
       </c>
       <c t="n" r="E110">
-        <v>-1.0548</v>
+        <v>10.4820</v>
       </c>
       <c t="n" r="F110">
-        <v>0.0752</v>
+        <v>1.6270</v>
       </c>
       <c t="n" r="G110">
-        <v>12.9194</v>
+        <v>12.9773</v>
       </c>
       <c t="n" r="H110">
-        <v>124.4294</v>
+        <v>-17.7700</v>
       </c>
     </row>
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">NBA</t>
+          <t xml:space="preserve">ZVE</t>
         </is>
       </c>
       <c t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">NUROL PORTFÖY YÖNETİMİ A.Ş. BABACAN MERİDİAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C111">
-        <v>-29.5926</v>
+        <v>-0.0303</v>
       </c>
       <c t="n" r="D111">
-        <v>-33.0173</v>
+        <v>0.1497</v>
       </c>
       <c t="n" r="E111">
-        <v>1814.2098</v>
+        <v>-1.0515</v>
       </c>
       <c t="n" r="F111">
-        <v>-33.2042</v>
+        <v>0.0793</v>
       </c>
       <c t="n" r="G111">
-        <v>12.7660</v>
+        <v>12.9254</v>
+      </c>
+      <c t="n" r="H111">
+        <v>124.4386</v>
       </c>
     </row>
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">OYE</t>
+          <t xml:space="preserve">RP4</t>
         </is>
       </c>
       <c t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALTINCI KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. AVRASYA STRATEJİK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C112">
-        <v>-0.3172</v>
+        <v>1.0692</v>
       </c>
       <c t="n" r="D112">
-        <v>0.6243</v>
+        <v>-6.5196</v>
       </c>
       <c t="n" r="E112">
-        <v>8.8629</v>
+        <v>10.2842</v>
       </c>
       <c t="n" r="F112">
-        <v>-1.1024</v>
+        <v>-4.8995</v>
       </c>
       <c t="n" r="G112">
-        <v>12.5884</v>
+        <v>12.8957</v>
       </c>
       <c t="n" r="H112">
-        <v>201.5753</v>
+        <v>108.8653</v>
       </c>
       <c t="n" r="I112">
-        <v>576.5506</v>
+        <v>358.2718</v>
       </c>
     </row>
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">YG7</t>
+          <t xml:space="preserve">OYE</t>
         </is>
       </c>
       <c t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ALTINCI KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C113">
-        <v>0.1366</v>
+        <v>-0.3301</v>
       </c>
       <c t="n" r="D113">
-        <v>0.7670</v>
+        <v>0.6256</v>
       </c>
       <c t="n" r="E113">
-        <v>9.5924</v>
+        <v>8.8560</v>
       </c>
       <c t="n" r="F113">
-        <v>0.7744</v>
+        <v>-1.1017</v>
       </c>
       <c t="n" r="G113">
-        <v>12.0639</v>
+        <v>12.5831</v>
       </c>
       <c t="n" r="H113">
-        <v>-18.4598</v>
+        <v>201.5774</v>
+      </c>
+      <c t="n" r="I113">
+        <v>576.5554</v>
       </c>
     </row>
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">YG1</t>
+          <t xml:space="preserve">NH2</t>
         </is>
       </c>
       <c t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LOTUS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş CORNERSTONE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C114">
-        <v>0.0924</v>
+        <v>0.7265</v>
       </c>
       <c t="n" r="D114">
-        <v>0.0692</v>
+        <v>1.3864</v>
       </c>
       <c t="n" r="E114">
-        <v>10.3602</v>
+        <v>4.2942</v>
       </c>
       <c t="n" r="F114">
-        <v>0.0418</v>
+        <v>3.4768</v>
       </c>
       <c t="n" r="G114">
-        <v>12.0458</v>
-      </c>
-      <c t="n" r="H114">
-        <v>302.3307</v>
+        <v>12.4365</v>
       </c>
     </row>
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">NH2</t>
+          <t xml:space="preserve">YG1</t>
         </is>
       </c>
       <c t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş CORNERSTONE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LOTUS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C115">
-        <v>0.8404</v>
+        <v>0.0920</v>
       </c>
       <c t="n" r="D115">
-        <v>1.7172</v>
+        <v>0.0700</v>
       </c>
       <c t="n" r="E115">
-        <v>4.3044</v>
+        <v>10.3600</v>
       </c>
       <c t="n" r="F115">
-        <v>3.4633</v>
+        <v>0.0415</v>
       </c>
       <c t="n" r="G115">
-        <v>11.0688</v>
+        <v>12.0461</v>
+      </c>
+      <c t="n" r="H115">
+        <v>302.3292</v>
       </c>
     </row>
     <row r="116">
@@ -3664,22 +3664,22 @@
         </is>
       </c>
       <c t="n" r="C116">
-        <v>-1.6516</v>
+        <v>-1.6255</v>
       </c>
       <c t="n" r="D116">
-        <v>-5.1694</v>
+        <v>-5.1809</v>
       </c>
       <c t="n" r="E116">
-        <v>33.2360</v>
+        <v>33.2019</v>
       </c>
       <c t="n" r="F116">
-        <v>-5.2345</v>
+        <v>-5.2545</v>
       </c>
       <c t="n" r="G116">
-        <v>10.5053</v>
+        <v>10.5014</v>
       </c>
       <c t="n" r="H116">
-        <v>399.3346</v>
+        <v>399.2296</v>
       </c>
     </row>
     <row r="117">
@@ -3694,22 +3694,22 @@
         </is>
       </c>
       <c t="n" r="C117">
-        <v>-0.0227</v>
+        <v>0.1256</v>
       </c>
       <c t="n" r="D117">
-        <v>0.3472</v>
+        <v>0.3533</v>
       </c>
       <c t="n" r="E117">
-        <v>27.6205</v>
+        <v>27.6265</v>
       </c>
       <c t="n" r="F117">
-        <v>0.2644</v>
+        <v>0.2642</v>
       </c>
       <c t="n" r="G117">
-        <v>10.4293</v>
+        <v>10.4296</v>
       </c>
       <c t="n" r="H117">
-        <v>134.4185</v>
+        <v>134.4181</v>
       </c>
     </row>
     <row r="118">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c t="n" r="C118">
-        <v>-0.0734</v>
+        <v>-0.0764</v>
       </c>
       <c t="n" r="D118">
-        <v>-0.1851</v>
+        <v>-0.1821</v>
       </c>
       <c t="n" r="E118">
-        <v>10.8867</v>
+        <v>10.8854</v>
       </c>
       <c t="n" r="F118">
-        <v>-0.2385</v>
+        <v>-0.2427</v>
       </c>
       <c t="n" r="G118">
-        <v>10.3861</v>
+        <v>10.3808</v>
       </c>
     </row>
     <row r="119">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c t="n" r="C119">
-        <v>-0.3427</v>
+        <v>-0.3634</v>
       </c>
       <c t="n" r="D119">
-        <v>-1.0793</v>
+        <v>-1.0243</v>
       </c>
       <c t="n" r="E119">
-        <v>12.3843</v>
+        <v>12.3768</v>
       </c>
       <c t="n" r="F119">
-        <v>-1.4228</v>
+        <v>-1.4510</v>
       </c>
       <c t="n" r="G119">
-        <v>10.2772</v>
+        <v>10.2674</v>
       </c>
     </row>
     <row r="120">
@@ -3778,19 +3778,19 @@
         </is>
       </c>
       <c t="n" r="C120">
-        <v>0.4392</v>
+        <v>0.4403</v>
       </c>
       <c t="n" r="D120">
-        <v>0.3576</v>
+        <v>0.3601</v>
       </c>
       <c t="n" r="E120">
-        <v>10.3915</v>
+        <v>10.4098</v>
       </c>
       <c t="n" r="F120">
-        <v>0.3978</v>
+        <v>0.3985</v>
       </c>
       <c t="n" r="G120">
-        <v>9.6581</v>
+        <v>9.6778</v>
       </c>
     </row>
     <row r="121">
@@ -3805,25 +3805,25 @@
         </is>
       </c>
       <c t="n" r="C121">
-        <v>0.1643</v>
+        <v>0.1320</v>
       </c>
       <c t="n" r="D121">
-        <v>0.4103</v>
+        <v>0.3986</v>
       </c>
       <c t="n" r="E121">
-        <v>2.1606</v>
+        <v>2.0642</v>
       </c>
       <c t="n" r="F121">
-        <v>1.1185</v>
+        <v>1.0930</v>
       </c>
       <c t="n" r="G121">
-        <v>9.5754</v>
+        <v>9.5643</v>
       </c>
       <c t="n" r="H121">
-        <v>129.3180</v>
+        <v>129.2602</v>
       </c>
       <c t="n" r="I121">
-        <v>422.3719</v>
+        <v>421.3728</v>
       </c>
     </row>
     <row r="122">
@@ -3838,22 +3838,22 @@
         </is>
       </c>
       <c t="n" r="C122">
-        <v>0.6764</v>
+        <v>0.6753</v>
       </c>
       <c t="n" r="D122">
-        <v>2.0005</v>
+        <v>2.0025</v>
       </c>
       <c t="n" r="E122">
-        <v>8.6551</v>
+        <v>8.7810</v>
       </c>
       <c t="n" r="F122">
-        <v>1.9418</v>
+        <v>1.9397</v>
       </c>
       <c t="n" r="G122">
-        <v>9.2457</v>
+        <v>9.2460</v>
       </c>
       <c t="n" r="H122">
-        <v>127.7290</v>
+        <v>127.7243</v>
       </c>
     </row>
     <row r="123">
@@ -3868,22 +3868,22 @@
         </is>
       </c>
       <c t="n" r="C123">
-        <v>0.0371</v>
+        <v>0.0336</v>
       </c>
       <c t="n" r="D123">
-        <v>-0.1157</v>
+        <v>-0.1122</v>
       </c>
       <c t="n" r="E123">
-        <v>9.1730</v>
+        <v>9.1726</v>
       </c>
       <c t="n" r="F123">
-        <v>-0.0567</v>
+        <v>-0.0609</v>
       </c>
       <c t="n" r="G123">
-        <v>9.0109</v>
+        <v>9.0135</v>
       </c>
       <c t="n" r="H123">
-        <v>253.8367</v>
+        <v>253.8217</v>
       </c>
     </row>
     <row r="124">
@@ -3898,19 +3898,19 @@
         </is>
       </c>
       <c t="n" r="C124">
-        <v>0.4586</v>
+        <v>0.4604</v>
       </c>
       <c t="n" r="D124">
-        <v>1.6859</v>
+        <v>1.6849</v>
       </c>
       <c t="n" r="E124">
-        <v>6.6025</v>
+        <v>6.6049</v>
       </c>
       <c t="n" r="F124">
-        <v>1.2635</v>
+        <v>1.2674</v>
       </c>
       <c t="n" r="G124">
-        <v>8.7849</v>
+        <v>8.7157</v>
       </c>
     </row>
     <row r="125">
@@ -3925,22 +3925,22 @@
         </is>
       </c>
       <c t="n" r="C125">
-        <v>0.1886</v>
+        <v>0.1871</v>
       </c>
       <c t="n" r="D125">
-        <v>0.4695</v>
+        <v>0.4722</v>
       </c>
       <c t="n" r="E125">
-        <v>3.9956</v>
+        <v>3.9948</v>
       </c>
       <c t="n" r="F125">
-        <v>0.5424</v>
+        <v>0.5379</v>
       </c>
       <c t="n" r="G125">
-        <v>8.5982</v>
+        <v>8.5968</v>
       </c>
       <c t="n" r="H125">
-        <v>244.3494</v>
+        <v>244.3342</v>
       </c>
     </row>
     <row r="126">
@@ -3955,19 +3955,19 @@
         </is>
       </c>
       <c t="n" r="C126">
-        <v>0.3924</v>
+        <v>0.3874</v>
       </c>
       <c t="n" r="D126">
-        <v>-1.9187</v>
+        <v>-1.8835</v>
       </c>
       <c t="n" r="E126">
-        <v>7.5287</v>
+        <v>7.5255</v>
       </c>
       <c t="n" r="F126">
-        <v>-1.4468</v>
+        <v>-1.4528</v>
       </c>
       <c t="n" r="G126">
-        <v>8.4502</v>
+        <v>8.4483</v>
       </c>
     </row>
     <row r="127">
@@ -3982,19 +3982,19 @@
         </is>
       </c>
       <c t="n" r="C127">
-        <v>-0.5051</v>
+        <v>-0.5151</v>
       </c>
       <c t="n" r="D127">
-        <v>-0.6578</v>
+        <v>-0.6496</v>
       </c>
       <c t="n" r="E127">
-        <v>8.8824</v>
+        <v>8.8770</v>
       </c>
       <c t="n" r="F127">
-        <v>-0.4964</v>
+        <v>-0.5073</v>
       </c>
       <c t="n" r="G127">
-        <v>8.3615</v>
+        <v>8.3576</v>
       </c>
     </row>
     <row r="128">
@@ -4009,22 +4009,22 @@
         </is>
       </c>
       <c t="n" r="C128">
-        <v>-0.3462</v>
+        <v>-0.3475</v>
       </c>
       <c t="n" r="D128">
-        <v>-0.2243</v>
+        <v>-0.2193</v>
       </c>
       <c t="n" r="E128">
-        <v>12.1018</v>
+        <v>12.0988</v>
       </c>
       <c t="n" r="F128">
-        <v>-0.9776</v>
+        <v>-0.9793</v>
       </c>
       <c t="n" r="G128">
-        <v>7.2824</v>
+        <v>7.2835</v>
       </c>
       <c t="n" r="H128">
-        <v>209.1013</v>
+        <v>209.0961</v>
       </c>
     </row>
     <row r="129">
@@ -4039,22 +4039,22 @@
         </is>
       </c>
       <c t="n" r="C129">
-        <v>1.2920</v>
+        <v>1.2570</v>
       </c>
       <c t="n" r="D129">
-        <v>0.8809</v>
+        <v>0.8958</v>
       </c>
       <c t="n" r="E129">
-        <v>6.6229</v>
+        <v>6.6359</v>
       </c>
       <c t="n" r="F129">
-        <v>0.7913</v>
+        <v>0.8004</v>
       </c>
       <c t="n" r="G129">
-        <v>6.6766</v>
+        <v>6.6992</v>
       </c>
       <c t="n" r="H129">
-        <v>160.8314</v>
+        <v>160.8549</v>
       </c>
     </row>
     <row r="130">
@@ -4069,22 +4069,22 @@
         </is>
       </c>
       <c t="n" r="C130">
-        <v>-0.6730</v>
+        <v>-0.7016</v>
       </c>
       <c t="n" r="D130">
-        <v>-0.5086</v>
+        <v>-0.5012</v>
       </c>
       <c t="n" r="E130">
-        <v>5.9462</v>
+        <v>5.9550</v>
       </c>
       <c t="n" r="F130">
-        <v>-0.4343</v>
+        <v>-0.4286</v>
       </c>
       <c t="n" r="G130">
-        <v>6.6165</v>
+        <v>6.6402</v>
       </c>
       <c t="n" r="H130">
-        <v>110.6512</v>
+        <v>110.6632</v>
       </c>
     </row>
     <row r="131">
@@ -4105,13 +4105,13 @@
         <v>-0.4051</v>
       </c>
       <c t="n" r="E131">
-        <v>7.2278</v>
+        <v>7.2282</v>
       </c>
       <c t="n" r="F131">
         <v>-0.3807</v>
       </c>
       <c t="n" r="G131">
-        <v>6.5277</v>
+        <v>6.5275</v>
       </c>
       <c t="n" r="H131">
         <v>233.3698</v>
@@ -4129,22 +4129,22 @@
         </is>
       </c>
       <c t="n" r="C132">
-        <v>-0.0498</v>
+        <v>-0.0510</v>
       </c>
       <c t="n" r="D132">
-        <v>-0.1440</v>
+        <v>-0.1416</v>
       </c>
       <c t="n" r="E132">
-        <v>6.6170</v>
+        <v>6.6166</v>
       </c>
       <c t="n" r="F132">
-        <v>-0.1801</v>
+        <v>-0.1824</v>
       </c>
       <c t="n" r="G132">
-        <v>6.3472</v>
+        <v>6.3467</v>
       </c>
       <c t="n" r="H132">
-        <v>305.8489</v>
+        <v>305.8393</v>
       </c>
     </row>
     <row r="133">
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c t="n" r="C133">
-        <v>0.3068</v>
+        <v>0.2838</v>
       </c>
       <c t="n" r="D133">
-        <v>0.9910</v>
+        <v>0.9380</v>
       </c>
       <c t="n" r="E133">
-        <v>13.4907</v>
+        <v>13.4944</v>
       </c>
       <c t="n" r="F133">
-        <v>1.3396</v>
+        <v>1.3390</v>
       </c>
       <c t="n" r="G133">
-        <v>5.8206</v>
+        <v>5.7553</v>
       </c>
       <c t="n" r="H133">
-        <v>195.6013</v>
+        <v>195.5996</v>
       </c>
     </row>
     <row r="134">
@@ -4189,22 +4189,22 @@
         </is>
       </c>
       <c t="n" r="C134">
-        <v>0.3332</v>
+        <v>0.3358</v>
       </c>
       <c t="n" r="D134">
-        <v>1.2966</v>
+        <v>1.2988</v>
       </c>
       <c t="n" r="E134">
-        <v>11.4763</v>
+        <v>11.4800</v>
       </c>
       <c t="n" r="F134">
-        <v>1.5040</v>
+        <v>1.5046</v>
       </c>
       <c t="n" r="G134">
-        <v>5.6038</v>
+        <v>5.5984</v>
       </c>
       <c t="n" r="H134">
-        <v>154.3353</v>
+        <v>154.3369</v>
       </c>
     </row>
     <row r="135">
@@ -4219,22 +4219,22 @@
         </is>
       </c>
       <c t="n" r="C135">
-        <v>1.2786</v>
+        <v>1.1049</v>
       </c>
       <c t="n" r="D135">
-        <v>3.7608</v>
+        <v>3.7268</v>
       </c>
       <c t="n" r="E135">
-        <v>10.0298</v>
+        <v>10.1000</v>
       </c>
       <c t="n" r="F135">
-        <v>4.7579</v>
+        <v>4.8033</v>
       </c>
       <c t="n" r="G135">
-        <v>5.4186</v>
+        <v>5.4855</v>
       </c>
       <c t="n" r="H135">
-        <v>90.5170</v>
+        <v>90.5995</v>
       </c>
     </row>
     <row r="136">
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c t="n" r="C136">
-        <v>-0.0449</v>
+        <v>-0.0456</v>
       </c>
       <c t="n" r="D136">
-        <v>-0.1741</v>
+        <v>-0.1663</v>
       </c>
       <c t="n" r="E136">
-        <v>8.3683</v>
+        <v>8.3708</v>
       </c>
       <c t="n" r="F136">
-        <v>2.1378</v>
+        <v>2.1362</v>
       </c>
       <c t="n" r="G136">
-        <v>5.3244</v>
+        <v>5.3257</v>
       </c>
     </row>
     <row r="137">
@@ -4276,19 +4276,19 @@
         </is>
       </c>
       <c t="n" r="C137">
-        <v>0.1684</v>
+        <v>0.1566</v>
       </c>
       <c t="n" r="D137">
-        <v>-10.5563</v>
+        <v>-10.5770</v>
       </c>
       <c t="n" r="E137">
-        <v>0.2566</v>
+        <v>0.2354</v>
       </c>
       <c t="n" r="F137">
-        <v>-10.4666</v>
+        <v>-10.4665</v>
       </c>
       <c t="n" r="G137">
-        <v>4.7354</v>
+        <v>4.7280</v>
       </c>
     </row>
     <row r="138">
@@ -4303,22 +4303,22 @@
         </is>
       </c>
       <c t="n" r="C138">
-        <v>-0.2232</v>
+        <v>-0.2305</v>
       </c>
       <c t="n" r="D138">
-        <v>-0.6593</v>
+        <v>-0.6454</v>
       </c>
       <c t="n" r="E138">
-        <v>5.9043</v>
+        <v>5.9050</v>
       </c>
       <c t="n" r="F138">
-        <v>-0.8196</v>
+        <v>-0.8340</v>
       </c>
       <c t="n" r="G138">
-        <v>4.4762</v>
+        <v>4.4747</v>
       </c>
       <c t="n" r="H138">
-        <v>113.2746</v>
+        <v>113.2436</v>
       </c>
     </row>
     <row r="139">
@@ -4333,25 +4333,25 @@
         </is>
       </c>
       <c t="n" r="C139">
-        <v>-0.0314</v>
+        <v>-0.2013</v>
       </c>
       <c t="n" r="D139">
-        <v>-0.8558</v>
+        <v>-0.9079</v>
       </c>
       <c t="n" r="E139">
-        <v>0.9661</v>
+        <v>0.9395</v>
       </c>
       <c t="n" r="F139">
-        <v>-0.6259</v>
+        <v>-0.6721</v>
       </c>
       <c t="n" r="G139">
-        <v>4.1739</v>
+        <v>4.2448</v>
       </c>
       <c t="n" r="H139">
-        <v>89.3154</v>
+        <v>89.2274</v>
       </c>
       <c t="n" r="I139">
-        <v>58.4047</v>
+        <v>58.3311</v>
       </c>
     </row>
     <row r="140">
@@ -4366,19 +4366,19 @@
         </is>
       </c>
       <c t="n" r="C140">
-        <v>-0.5989</v>
+        <v>-0.6214</v>
       </c>
       <c t="n" r="D140">
-        <v>-1.6703</v>
+        <v>-1.6371</v>
       </c>
       <c t="n" r="E140">
-        <v>-14.9731</v>
+        <v>-14.2760</v>
       </c>
       <c t="n" r="F140">
-        <v>-2.6777</v>
+        <v>-2.7183</v>
       </c>
       <c t="n" r="G140">
-        <v>3.8892</v>
+        <v>3.8530</v>
       </c>
     </row>
     <row r="141">
@@ -4393,22 +4393,22 @@
         </is>
       </c>
       <c t="n" r="C141">
-        <v>-0.2200</v>
+        <v>-0.2266</v>
       </c>
       <c t="n" r="D141">
-        <v>-0.7718</v>
+        <v>-0.7054</v>
       </c>
       <c t="n" r="E141">
-        <v>0.7128</v>
+        <v>0.7131</v>
       </c>
       <c t="n" r="F141">
-        <v>-0.9762</v>
+        <v>-0.9876</v>
       </c>
       <c t="n" r="G141">
-        <v>3.5200</v>
+        <v>3.5204</v>
       </c>
       <c t="n" r="H141">
-        <v>171.0391</v>
+        <v>171.0081</v>
       </c>
     </row>
     <row r="142">
@@ -4423,22 +4423,22 @@
         </is>
       </c>
       <c t="n" r="C142">
-        <v>-0.0949</v>
+        <v>-0.0988</v>
       </c>
       <c t="n" r="D142">
-        <v>-0.2667</v>
+        <v>-0.2576</v>
       </c>
       <c t="n" r="E142">
-        <v>9.4812</v>
+        <v>9.4785</v>
       </c>
       <c t="n" r="F142">
-        <v>-0.3566</v>
+        <v>-0.3610</v>
       </c>
       <c t="n" r="G142">
-        <v>3.1552</v>
+        <v>3.1555</v>
       </c>
       <c t="n" r="H142">
-        <v>132.8984</v>
+        <v>132.8881</v>
       </c>
     </row>
     <row r="143">
@@ -4453,22 +4453,22 @@
         </is>
       </c>
       <c t="n" r="C143">
-        <v>-0.1864</v>
+        <v>-0.1932</v>
       </c>
       <c t="n" r="D143">
-        <v>-0.4107</v>
+        <v>-0.4090</v>
       </c>
       <c t="n" r="E143">
-        <v>16.4595</v>
+        <v>16.4610</v>
       </c>
       <c t="n" r="F143">
-        <v>-0.5716</v>
+        <v>-0.5696</v>
       </c>
       <c t="n" r="G143">
-        <v>3.0082</v>
+        <v>3.0103</v>
       </c>
       <c t="n" r="H143">
-        <v>268.5118</v>
+        <v>268.5192</v>
       </c>
     </row>
     <row r="144">
@@ -4483,22 +4483,22 @@
         </is>
       </c>
       <c t="n" r="C144">
-        <v>1.2388</v>
+        <v>1.2387</v>
       </c>
       <c t="n" r="D144">
-        <v>1.3498</v>
+        <v>1.3062</v>
       </c>
       <c t="n" r="E144">
-        <v>5.0025</v>
+        <v>4.9846</v>
       </c>
       <c t="n" r="F144">
         <v>-0.6786</v>
       </c>
       <c t="n" r="G144">
-        <v>2.8545</v>
+        <v>2.8426</v>
       </c>
       <c t="n" r="H144">
-        <v>266.2381</v>
+        <v>266.2383</v>
       </c>
     </row>
     <row r="145">
@@ -4513,19 +4513,19 @@
         </is>
       </c>
       <c t="n" r="C145">
-        <v>0.6693</v>
+        <v>0.6715</v>
       </c>
       <c t="n" r="D145">
-        <v>-1.9239</v>
+        <v>-1.9275</v>
       </c>
       <c t="n" r="E145">
-        <v>1.9097</v>
+        <v>1.9098</v>
       </c>
       <c t="n" r="F145">
-        <v>-1.1910</v>
+        <v>-1.1901</v>
       </c>
       <c t="n" r="G145">
-        <v>2.5579</v>
+        <v>2.5611</v>
       </c>
     </row>
     <row r="146">
@@ -4540,19 +4540,19 @@
         </is>
       </c>
       <c t="n" r="C146">
-        <v>-0.6878</v>
+        <v>-0.6990</v>
       </c>
       <c t="n" r="D146">
-        <v>-1.5553</v>
+        <v>-1.5617</v>
       </c>
       <c t="n" r="E146">
-        <v>99.0519</v>
+        <v>98.6091</v>
       </c>
       <c t="n" r="F146">
-        <v>-2.1593</v>
+        <v>-2.1717</v>
       </c>
       <c t="n" r="G146">
-        <v>2.5514</v>
+        <v>2.4293</v>
       </c>
     </row>
     <row r="147">
@@ -4567,79 +4567,79 @@
         </is>
       </c>
       <c t="n" r="C147">
-        <v>0.0004</v>
+        <v>-0.0152</v>
       </c>
       <c t="n" r="D147">
-        <v>-0.3224</v>
+        <v>-0.2674</v>
       </c>
       <c t="n" r="E147">
-        <v>7.8820</v>
+        <v>7.9342</v>
       </c>
       <c t="n" r="F147">
-        <v>-0.3756</v>
+        <v>-0.3802</v>
       </c>
       <c t="n" r="G147">
-        <v>2.2540</v>
+        <v>2.2517</v>
       </c>
       <c t="n" r="H147">
-        <v>131.0172</v>
+        <v>131.0065</v>
       </c>
     </row>
     <row r="148">
       <c t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">AHR</t>
+          <t xml:space="preserve">OKG</t>
         </is>
       </c>
       <c t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ONUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. EMLAK JET GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C148">
-        <v>-1.9881</v>
+        <v>-0.1506</v>
       </c>
       <c t="n" r="D148">
-        <v>-1.7291</v>
+        <v>-0.6718</v>
       </c>
       <c t="n" r="E148">
-        <v>3.6889</v>
+        <v>2.1704</v>
       </c>
       <c t="n" r="F148">
-        <v>-1.5736</v>
+        <v>-1.6166</v>
       </c>
       <c t="n" r="G148">
-        <v>1.0904</v>
+        <v>1.0906</v>
+      </c>
+      <c t="n" r="H148">
+        <v>69.7811</v>
       </c>
     </row>
     <row r="149">
       <c t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">OKG</t>
+          <t xml:space="preserve">AHR</t>
         </is>
       </c>
       <c t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. EMLAK JET GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ALBARAKA PORTFÖY YÖNETİMİ A.Ş. ONUNCU KARMA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="C149">
-        <v>-0.1198</v>
+        <v>-1.9922</v>
       </c>
       <c t="n" r="D149">
-        <v>-0.6694</v>
+        <v>-1.7283</v>
       </c>
       <c t="n" r="E149">
-        <v>2.1738</v>
+        <v>3.6882</v>
       </c>
       <c t="n" r="F149">
-        <v>-1.6146</v>
+        <v>-1.5739</v>
       </c>
       <c t="n" r="G149">
-        <v>1.0824</v>
-      </c>
-      <c t="n" r="H149">
-        <v>69.7845</v>
+        <v>1.0888</v>
       </c>
     </row>
     <row r="150">
@@ -4888,16 +4888,16 @@
         </is>
       </c>
       <c t="n" r="C162">
-        <v>-0.1863</v>
+        <v>-0.1923</v>
       </c>
       <c t="n" r="D162">
-        <v>-0.7035</v>
+        <v>-0.6958</v>
       </c>
       <c t="n" r="F162">
-        <v>-0.9574</v>
+        <v>-0.9657</v>
       </c>
       <c t="n" r="G162">
-        <v>-0.1662</v>
+        <v>-0.1848</v>
       </c>
     </row>
     <row r="163">
@@ -4912,25 +4912,25 @@
         </is>
       </c>
       <c t="n" r="C163">
-        <v>0.1915</v>
+        <v>0.1416</v>
       </c>
       <c t="n" r="D163">
-        <v>8.6893</v>
+        <v>8.6777</v>
       </c>
       <c t="n" r="E163">
-        <v>17.0000</v>
+        <v>16.9881</v>
       </c>
       <c t="n" r="F163">
-        <v>8.9196</v>
+        <v>8.9290</v>
       </c>
       <c t="n" r="G163">
-        <v>-0.5832</v>
+        <v>-0.5775</v>
       </c>
       <c t="n" r="H163">
-        <v>152.9843</v>
+        <v>153.0060</v>
       </c>
       <c t="n" r="I163">
-        <v>495.8387</v>
+        <v>495.9192</v>
       </c>
     </row>
     <row r="164">
@@ -4945,19 +4945,19 @@
         </is>
       </c>
       <c t="n" r="C164">
-        <v>-0.2599</v>
+        <v>-0.2690</v>
       </c>
       <c t="n" r="D164">
-        <v>-0.7753</v>
+        <v>-0.7601</v>
       </c>
       <c t="n" r="E164">
-        <v>-0.2735</v>
+        <v>-0.2766</v>
       </c>
       <c t="n" r="F164">
-        <v>-0.9158</v>
+        <v>-0.9334</v>
       </c>
       <c t="n" r="G164">
-        <v>-1.5981</v>
+        <v>-1.6013</v>
       </c>
     </row>
     <row r="165">
@@ -4972,19 +4972,19 @@
         </is>
       </c>
       <c t="n" r="C165">
-        <v>-2.2539</v>
+        <v>-2.2831</v>
       </c>
       <c t="n" r="D165">
-        <v>-7.6342</v>
+        <v>-7.6135</v>
       </c>
       <c t="n" r="E165">
-        <v>-11.9808</v>
+        <v>-9.6845</v>
       </c>
       <c t="n" r="F165">
-        <v>-10.3989</v>
+        <v>-10.4474</v>
       </c>
       <c t="n" r="G165">
-        <v>-7.5973</v>
+        <v>-7.6411</v>
       </c>
     </row>
     <row r="166">
@@ -4999,22 +4999,22 @@
         </is>
       </c>
       <c t="n" r="C166">
-        <v>6.2324</v>
+        <v>6.9268</v>
       </c>
       <c t="n" r="D166">
-        <v>3.7936</v>
+        <v>4.4756</v>
       </c>
       <c t="n" r="E166">
-        <v>1.8256</v>
+        <v>2.4751</v>
       </c>
       <c t="n" r="F166">
-        <v>5.1692</v>
+        <v>5.3332</v>
       </c>
       <c t="n" r="G166">
-        <v>-8.0115</v>
+        <v>-8.0449</v>
       </c>
       <c t="n" r="H166">
-        <v>94.2693</v>
+        <v>94.5722</v>
       </c>
     </row>
     <row r="167">
@@ -5029,19 +5029,19 @@
         </is>
       </c>
       <c t="n" r="C167">
-        <v>0.3908</v>
+        <v>0.3911</v>
       </c>
       <c t="n" r="D167">
-        <v>-0.5723</v>
+        <v>-0.5735</v>
       </c>
       <c t="n" r="E167">
-        <v>2.4330</v>
+        <v>2.4333</v>
       </c>
       <c t="n" r="F167">
-        <v>-0.2932</v>
+        <v>-0.2934</v>
       </c>
       <c t="n" r="G167">
-        <v>-11.4502</v>
+        <v>-11.4489</v>
       </c>
     </row>
     <row r="168">
@@ -5056,19 +5056,19 @@
         </is>
       </c>
       <c t="n" r="C168">
-        <v>0.1994</v>
+        <v>0.1743</v>
       </c>
       <c t="n" r="D168">
-        <v>4.3876</v>
+        <v>4.3985</v>
       </c>
       <c t="n" r="E168">
-        <v>4.8263</v>
+        <v>4.8348</v>
       </c>
       <c t="n" r="F168">
-        <v>4.1329</v>
+        <v>4.1392</v>
       </c>
       <c t="n" r="G168">
-        <v>-13.3574</v>
+        <v>-13.3495</v>
       </c>
     </row>
     <row r="169">
@@ -5083,22 +5083,22 @@
         </is>
       </c>
       <c t="n" r="C169">
-        <v>-0.0364</v>
+        <v>-0.0373</v>
       </c>
       <c t="n" r="D169">
-        <v>-0.1094</v>
+        <v>-0.1081</v>
       </c>
       <c t="n" r="E169">
-        <v>-17.3181</v>
+        <v>-17.3188</v>
       </c>
       <c t="n" r="F169">
-        <v>-0.1364</v>
+        <v>-0.1380</v>
       </c>
       <c t="n" r="G169">
-        <v>-13.9692</v>
+        <v>-13.9695</v>
       </c>
       <c t="n" r="H169">
-        <v>196.2695</v>
+        <v>196.2647</v>
       </c>
     </row>
     <row r="170">
@@ -5113,22 +5113,22 @@
         </is>
       </c>
       <c t="n" r="C170">
-        <v>-0.5000</v>
+        <v>-0.4876</v>
       </c>
       <c t="n" r="D170">
-        <v>-1.5151</v>
+        <v>-1.4930</v>
       </c>
       <c t="n" r="E170">
-        <v>-17.3128</v>
+        <v>-17.3080</v>
       </c>
       <c t="n" r="F170">
-        <v>-1.7905</v>
+        <v>-1.8088</v>
       </c>
       <c t="n" r="G170">
-        <v>-18.4620</v>
+        <v>-18.4622</v>
       </c>
       <c t="n" r="H170">
-        <v>-2.8678</v>
+        <v>-2.8859</v>
       </c>
     </row>
     <row r="171">
@@ -5143,22 +5143,22 @@
         </is>
       </c>
       <c t="n" r="C171">
-        <v>0.1066</v>
+        <v>0.1007</v>
       </c>
       <c t="n" r="D171">
-        <v>-0.5574</v>
+        <v>-0.5705</v>
       </c>
       <c t="n" r="E171">
-        <v>-17.9113</v>
+        <v>-17.9172</v>
       </c>
       <c t="n" r="F171">
-        <v>-0.0606</v>
+        <v>-0.0697</v>
       </c>
       <c t="n" r="G171">
-        <v>-18.7669</v>
+        <v>-18.7715</v>
       </c>
       <c t="n" r="H171">
-        <v>91.3540</v>
+        <v>91.3366</v>
       </c>
     </row>
     <row r="172">
@@ -5173,22 +5173,22 @@
         </is>
       </c>
       <c t="n" r="C172">
-        <v>-0.2961</v>
+        <v>-0.3035</v>
       </c>
       <c t="n" r="D172">
-        <v>-0.8460</v>
+        <v>-0.8315</v>
       </c>
       <c t="n" r="E172">
-        <v>-23.3518</v>
+        <v>-23.3523</v>
       </c>
       <c t="n" r="F172">
-        <v>-1.0104</v>
+        <v>-1.0250</v>
       </c>
       <c t="n" r="G172">
-        <v>-24.4712</v>
+        <v>-24.4724</v>
       </c>
       <c t="n" r="H172">
-        <v>350.2910</v>
+        <v>350.2244</v>
       </c>
     </row>
     <row r="173">
@@ -5206,16 +5206,16 @@
         <v>-0.0160</v>
       </c>
       <c t="n" r="D173">
-        <v>-0.0526</v>
+        <v>-0.0525</v>
       </c>
       <c t="n" r="E173">
-        <v>-0.0861</v>
+        <v>-0.0863</v>
       </c>
       <c t="n" r="F173">
         <v>-0.0611</v>
       </c>
       <c t="n" r="G173">
-        <v>-24.5006</v>
+        <v>-24.4986</v>
       </c>
     </row>
     <row r="174">
@@ -5230,25 +5230,25 @@
         </is>
       </c>
       <c t="n" r="C174">
-        <v>-0.0797</v>
+        <v>-0.0887</v>
       </c>
       <c t="n" r="D174">
-        <v>-0.2741</v>
+        <v>-0.2704</v>
       </c>
       <c t="n" r="E174">
-        <v>-50.8584</v>
+        <v>-50.9218</v>
       </c>
       <c t="n" r="F174">
-        <v>-1.0512</v>
+        <v>-1.0549</v>
       </c>
       <c t="n" r="G174">
-        <v>-30.3213</v>
+        <v>-30.3195</v>
       </c>
       <c t="n" r="H174">
-        <v>71.0687</v>
+        <v>71.0624</v>
       </c>
       <c t="n" r="I174">
-        <v>785.1469</v>
+        <v>785.1140</v>
       </c>
     </row>
     <row r="175">
@@ -5263,22 +5263,22 @@
         </is>
       </c>
       <c t="n" r="C175">
-        <v>-0.6761</v>
+        <v>-0.6653</v>
       </c>
       <c t="n" r="D175">
-        <v>-1.7562</v>
+        <v>-1.7405</v>
       </c>
       <c t="n" r="E175">
-        <v>-30.4572</v>
+        <v>-30.4538</v>
       </c>
       <c t="n" r="F175">
-        <v>-1.9875</v>
+        <v>-2.0054</v>
       </c>
       <c t="n" r="G175">
-        <v>-30.8591</v>
+        <v>-30.8689</v>
       </c>
       <c t="n" r="H175">
-        <v>102.9420</v>
+        <v>102.9050</v>
       </c>
     </row>
     <row r="176">
@@ -5293,22 +5293,22 @@
         </is>
       </c>
       <c t="n" r="C176">
-        <v>-0.2032</v>
+        <v>-0.2070</v>
       </c>
       <c t="n" r="D176">
-        <v>-3.4684</v>
+        <v>-3.4622</v>
       </c>
       <c t="n" r="E176">
-        <v>5.0805</v>
+        <v>5.0757</v>
       </c>
       <c t="n" r="F176">
-        <v>-7.3529</v>
+        <v>-7.3600</v>
       </c>
       <c t="n" r="G176">
-        <v>-40.9140</v>
+        <v>-40.9153</v>
       </c>
       <c t="n" r="H176">
-        <v>113.6496</v>
+        <v>113.6331</v>
       </c>
     </row>
     <row r="177">
@@ -5323,25 +5323,25 @@
         </is>
       </c>
       <c t="n" r="C177">
-        <v>-0.4562</v>
+        <v>-0.4520</v>
       </c>
       <c t="n" r="D177">
-        <v>-18.6061</v>
+        <v>-18.7053</v>
       </c>
       <c t="n" r="E177">
-        <v>-40.7793</v>
+        <v>-40.7748</v>
       </c>
       <c t="n" r="F177">
-        <v>-52.0194</v>
+        <v>-52.0177</v>
       </c>
       <c t="n" r="G177">
-        <v>-41.6931</v>
+        <v>-41.6896</v>
       </c>
       <c t="n" r="H177">
-        <v>-2.5869</v>
+        <v>-2.5833</v>
       </c>
       <c t="n" r="I177">
-        <v>217.4316</v>
+        <v>217.4432</v>
       </c>
     </row>
     <row r="178">
@@ -5356,22 +5356,22 @@
         </is>
       </c>
       <c t="n" r="C178">
-        <v>-0.1449</v>
+        <v>-0.1431</v>
       </c>
       <c t="n" r="D178">
-        <v>-23.7543</v>
+        <v>-23.7512</v>
       </c>
       <c t="n" r="E178">
-        <v>-23.0589</v>
+        <v>-23.0622</v>
       </c>
       <c t="n" r="F178">
-        <v>-26.0923</v>
+        <v>-26.0957</v>
       </c>
       <c t="n" r="G178">
-        <v>-43.1303</v>
+        <v>-43.1305</v>
       </c>
       <c t="n" r="H178">
-        <v>40.5756</v>
+        <v>40.5692</v>
       </c>
     </row>
     <row r="179">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c t="n" r="C179">
-        <v>-82.0808</v>
+        <v>-82.1043</v>
       </c>
       <c t="n" r="D179">
-        <v>-83.9860</v>
+        <v>-83.9986</v>
       </c>
       <c t="n" r="E179">
-        <v>-76.3643</v>
+        <v>-76.3967</v>
       </c>
       <c t="n" r="F179">
-        <v>-84.0151</v>
+        <v>-84.0392</v>
       </c>
       <c t="n" r="G179">
-        <v>-54.9490</v>
+        <v>-55.2269</v>
       </c>
     </row>
     <row r="180">
@@ -5413,25 +5413,25 @@
         </is>
       </c>
       <c t="n" r="C180">
-        <v>4.4745</v>
+        <v>4.2082</v>
       </c>
       <c t="n" r="D180">
-        <v>7.1791</v>
+        <v>6.2167</v>
       </c>
       <c t="n" r="E180">
-        <v>-10.1452</v>
+        <v>-10.1673</v>
       </c>
       <c t="n" r="F180">
-        <v>-12.5461</v>
+        <v>-12.5962</v>
       </c>
       <c t="n" r="G180">
-        <v>-58.8306</v>
+        <v>-58.8516</v>
       </c>
       <c t="n" r="H180">
-        <v>-19.7489</v>
+        <v>-19.7949</v>
       </c>
       <c t="n" r="I180">
-        <v>336.5008</v>
+        <v>336.2589</v>
       </c>
     </row>
     <row r="181">
@@ -5446,25 +5446,25 @@
         </is>
       </c>
       <c t="n" r="C181">
-        <v>-1.3057</v>
+        <v>-0.9928</v>
       </c>
       <c t="n" r="D181">
-        <v>37.2208</v>
+        <v>37.5783</v>
       </c>
       <c t="n" r="E181">
-        <v>-63.5001</v>
+        <v>-63.4725</v>
       </c>
       <c t="n" r="F181">
-        <v>55.0471</v>
+        <v>55.0986</v>
       </c>
       <c t="n" r="G181">
-        <v>-66.1619</v>
+        <v>-66.1618</v>
       </c>
       <c t="n" r="H181">
-        <v>-68.8963</v>
+        <v>-68.8860</v>
       </c>
       <c t="n" r="I181">
-        <v>-16.3364</v>
+        <v>-16.3024</v>
       </c>
     </row>
     <row r="182">
@@ -5479,25 +5479,25 @@
         </is>
       </c>
       <c t="n" r="C182">
-        <v>-24.8495</v>
+        <v>-26.1831</v>
       </c>
       <c t="n" r="D182">
-        <v>-76.9875</v>
+        <v>-76.9344</v>
       </c>
       <c t="n" r="E182">
-        <v>-75.8070</v>
+        <v>-75.7500</v>
       </c>
       <c t="n" r="F182">
-        <v>-77.0424</v>
+        <v>-76.9919</v>
       </c>
       <c t="n" r="G182">
-        <v>-67.2779</v>
+        <v>-67.1963</v>
       </c>
       <c t="n" r="H182">
-        <v>-84.9145</v>
+        <v>-84.8813</v>
       </c>
       <c t="n" r="I182">
-        <v>-44.9125</v>
+        <v>-44.7913</v>
       </c>
     </row>
     <row r="183">
@@ -5512,19 +5512,19 @@
         </is>
       </c>
       <c t="n" r="C183">
-        <v>-44.9491</v>
+        <v>-53.4151</v>
       </c>
       <c t="n" r="D183">
-        <v>-55.4436</v>
+        <v>-62.2102</v>
       </c>
       <c t="n" r="E183">
-        <v>329.9094</v>
+        <v>287.8847</v>
       </c>
       <c t="n" r="F183">
-        <v>-55.4706</v>
+        <v>-62.2509</v>
       </c>
       <c t="n" r="G183">
-        <v>-75.1606</v>
+        <v>-78.5312</v>
       </c>
     </row>
     <row r="184">
@@ -5569,22 +5569,22 @@
         </is>
       </c>
       <c t="n" r="C185">
-        <v>-98.8675</v>
+        <v>-98.8637</v>
       </c>
       <c t="n" r="D185">
-        <v>-99.1019</v>
+        <v>-99.0947</v>
       </c>
       <c t="n" r="E185">
-        <v>-99.0468</v>
+        <v>-99.0394</v>
       </c>
       <c t="n" r="F185">
-        <v>-99.1096</v>
+        <v>-99.1025</v>
       </c>
       <c t="n" r="G185">
-        <v>-99.1458</v>
+        <v>-99.1388</v>
       </c>
       <c t="n" r="H185">
-        <v>-98.5437</v>
+        <v>-98.5320</v>
       </c>
     </row>
     <row r="186">
@@ -5647,16 +5647,16 @@
         </is>
       </c>
       <c t="n" r="C190">
-        <v>1.6395</v>
+        <v>1.7312</v>
       </c>
       <c t="n" r="D190">
-        <v>3.5891</v>
+        <v>3.7267</v>
       </c>
       <c t="n" r="E190">
-        <v>33.6716</v>
+        <v>33.5930</v>
       </c>
       <c t="n" r="F190">
-        <v>4.3796</v>
+        <v>4.5417</v>
       </c>
     </row>
     <row r="191">
@@ -5695,13 +5695,13 @@
         </is>
       </c>
       <c t="n" r="C193">
-        <v>-17.6562</v>
+        <v>-18.8142</v>
       </c>
       <c t="n" r="D193">
-        <v>-39.6736</v>
+        <v>-39.4426</v>
       </c>
       <c t="n" r="F193">
-        <v>-44.0086</v>
+        <v>-44.9123</v>
       </c>
     </row>
     <row r="194">
@@ -5716,13 +5716,13 @@
         </is>
       </c>
       <c t="n" r="C194">
-        <v>-9.8075</v>
+        <v>-10.1433</v>
       </c>
       <c t="n" r="D194">
-        <v>-63.1159</v>
+        <v>-63.1770</v>
       </c>
       <c t="n" r="F194">
-        <v>-27.6363</v>
+        <v>-27.5310</v>
       </c>
     </row>
     <row r="195">
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c t="n" r="C196">
-        <v>1.6041</v>
+        <v>1.5978</v>
       </c>
     </row>
     <row r="197">
@@ -5764,13 +5764,13 @@
         </is>
       </c>
       <c t="n" r="C197">
-        <v>0.8135</v>
+        <v>0.8034</v>
       </c>
       <c t="n" r="D197">
-        <v>1.9953</v>
+        <v>1.9914</v>
       </c>
       <c t="n" r="F197">
-        <v>1.8864</v>
+        <v>1.8799</v>
       </c>
     </row>
     <row r="198">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c t="n" r="C204">
-        <v>0.6228</v>
+        <v>0.3691</v>
       </c>
       <c t="n" r="D204">
-        <v>2.7001</v>
+        <v>3.6277</v>
       </c>
     </row>
     <row r="205">
@@ -5875,16 +5875,16 @@
         </is>
       </c>
       <c t="n" r="C205">
-        <v>1.9971</v>
+        <v>1.8151</v>
       </c>
       <c t="n" r="D205">
-        <v>417.3992</v>
+        <v>417.1084</v>
       </c>
       <c t="n" r="E205">
-        <v>460.2199</v>
+        <v>459.5596</v>
       </c>
       <c t="n" r="F205">
-        <v>427.2679</v>
+        <v>427.6259</v>
       </c>
     </row>
     <row r="206">
@@ -5899,16 +5899,16 @@
         </is>
       </c>
       <c t="n" r="C206">
-        <v>11.8776</v>
+        <v>11.7512</v>
       </c>
       <c t="n" r="D206">
-        <v>43.3977</v>
+        <v>43.1154</v>
       </c>
       <c t="n" r="E206">
-        <v>57.7743</v>
+        <v>57.4263</v>
       </c>
       <c t="n" r="F206">
-        <v>46.4364</v>
+        <v>46.4386</v>
       </c>
     </row>
     <row r="207">
@@ -5935,16 +5935,16 @@
         </is>
       </c>
       <c t="n" r="C208">
-        <v>-0.0464</v>
+        <v>-0.0429</v>
       </c>
       <c t="n" r="D208">
-        <v>-0.1107</v>
+        <v>-0.1085</v>
       </c>
       <c t="n" r="E208">
-        <v>19.3780</v>
+        <v>19.3720</v>
       </c>
       <c t="n" r="F208">
-        <v>-0.1452</v>
+        <v>-0.1476</v>
       </c>
     </row>
     <row r="209">
@@ -5959,7 +5959,7 @@
         </is>
       </c>
       <c t="n" r="C209">
-        <v>-0.0131</v>
+        <v>-0.0242</v>
       </c>
     </row>
     <row r="210">
@@ -5986,16 +5986,16 @@
         </is>
       </c>
       <c t="n" r="C211">
-        <v>3.4643</v>
+        <v>3.1697</v>
       </c>
       <c t="n" r="D211">
-        <v>9.1821</v>
+        <v>9.0893</v>
       </c>
       <c t="n" r="E211">
-        <v>19.6354</v>
+        <v>19.5258</v>
       </c>
       <c t="n" r="F211">
-        <v>11.5074</v>
+        <v>11.6351</v>
       </c>
     </row>
     <row r="212">
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c t="n" r="C213">
-        <v>-0.1074</v>
+        <v>-0.1075</v>
       </c>
       <c t="n" r="D213">
-        <v>-0.3215</v>
+        <v>-0.3216</v>
       </c>
       <c t="n" r="F213">
         <v>-0.3290</v>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c t="n" r="C214">
-        <v>-0.9437</v>
+        <v>-0.9712</v>
       </c>
       <c t="n" r="D214">
-        <v>6.7113</v>
+        <v>6.7721</v>
       </c>
     </row>
     <row r="215">
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c t="n" r="C215">
-        <v>-0.1586</v>
+        <v>-0.1082</v>
       </c>
     </row>
     <row r="216">
@@ -6076,16 +6076,16 @@
         </is>
       </c>
       <c t="n" r="C216">
-        <v>-0.0363</v>
+        <v>-0.0373</v>
       </c>
       <c t="n" r="D216">
-        <v>-0.0997</v>
+        <v>-0.0978</v>
       </c>
       <c t="n" r="E216">
-        <v>12.7791</v>
+        <v>12.7788</v>
       </c>
       <c t="n" r="F216">
-        <v>-0.1215</v>
+        <v>-0.1236</v>
       </c>
     </row>
     <row r="217">
@@ -6100,16 +6100,16 @@
         </is>
       </c>
       <c t="n" r="C217">
-        <v>-0.0088</v>
+        <v>-0.0199</v>
       </c>
       <c t="n" r="D217">
-        <v>2.7775</v>
+        <v>2.7759</v>
       </c>
       <c t="n" r="E217">
-        <v>12.4879</v>
+        <v>12.4733</v>
       </c>
       <c t="n" r="F217">
-        <v>3.1033</v>
+        <v>3.1022</v>
       </c>
     </row>
     <row r="218">
@@ -6124,16 +6124,16 @@
         </is>
       </c>
       <c t="n" r="C218">
-        <v>-97.7895</v>
+        <v>-97.8284</v>
       </c>
       <c t="n" r="D218">
-        <v>-99.9777</v>
+        <v>-99.9780</v>
       </c>
       <c t="n" r="E218">
-        <v>-99.9979</v>
+        <v>-99.9978</v>
       </c>
       <c t="n" r="F218">
-        <v>-99.9962</v>
+        <v>-99.9963</v>
       </c>
     </row>
     <row r="219">
@@ -6256,16 +6256,16 @@
         </is>
       </c>
       <c t="n" r="C228">
-        <v>8.5369</v>
+        <v>7.8851</v>
       </c>
       <c t="n" r="D228">
-        <v>4.6235</v>
+        <v>2.5531</v>
       </c>
       <c t="n" r="E228">
-        <v>18.9646</v>
+        <v>19.1249</v>
       </c>
       <c t="n" r="F228">
-        <v>14.3428</v>
+        <v>14.7346</v>
       </c>
     </row>
     <row r="229">
@@ -6304,16 +6304,16 @@
         </is>
       </c>
       <c t="n" r="C231">
-        <v>1.2802</v>
+        <v>0.9511</v>
       </c>
       <c t="n" r="D231">
-        <v>5.2414</v>
+        <v>5.1801</v>
       </c>
       <c t="n" r="E231">
-        <v>13.8745</v>
+        <v>13.7550</v>
       </c>
       <c t="n" r="F231">
-        <v>7.2648</v>
+        <v>7.3486</v>
       </c>
     </row>
     <row r="232">
@@ -6328,16 +6328,16 @@
         </is>
       </c>
       <c t="n" r="C232">
-        <v>3.1623</v>
+        <v>3.2214</v>
       </c>
       <c t="n" r="D232">
-        <v>9.5353</v>
+        <v>9.3201</v>
       </c>
       <c t="n" r="E232">
-        <v>20.7369</v>
+        <v>20.7358</v>
       </c>
       <c t="n" r="F232">
-        <v>11.8030</v>
+        <v>12.0179</v>
       </c>
     </row>
     <row r="233">
@@ -6352,16 +6352,16 @@
         </is>
       </c>
       <c t="n" r="C233">
-        <v>1.3619</v>
+        <v>1.0232</v>
       </c>
       <c t="n" r="D233">
-        <v>1.6518</v>
+        <v>1.6716</v>
       </c>
       <c t="n" r="E233">
-        <v>4.0245</v>
+        <v>3.9025</v>
       </c>
       <c t="n" r="F233">
-        <v>2.2514</v>
+        <v>2.1881</v>
       </c>
     </row>
     <row r="234">
@@ -6388,16 +6388,16 @@
         </is>
       </c>
       <c t="n" r="C235">
-        <v>1.3671</v>
+        <v>1.0376</v>
       </c>
       <c t="n" r="D235">
-        <v>5.3317</v>
+        <v>5.2702</v>
       </c>
       <c t="n" r="E235">
-        <v>13.9721</v>
+        <v>13.8525</v>
       </c>
       <c t="n" r="F235">
-        <v>7.3568</v>
+        <v>7.4406</v>
       </c>
     </row>
     <row r="236">
@@ -6448,13 +6448,13 @@
         </is>
       </c>
       <c t="n" r="C239">
-        <v>-1.4737</v>
+        <v>-1.4316</v>
       </c>
       <c t="n" r="D239">
-        <v>-80.2310</v>
+        <v>-78.9790</v>
       </c>
       <c t="n" r="F239">
-        <v>-84.7433</v>
+        <v>-84.7472</v>
       </c>
     </row>
     <row r="240">
@@ -6493,16 +6493,16 @@
         </is>
       </c>
       <c t="n" r="C242">
-        <v>-0.0669</v>
+        <v>-0.0935</v>
       </c>
       <c t="n" r="D242">
-        <v>-0.2343</v>
+        <v>-0.2235</v>
       </c>
       <c t="n" r="E242">
-        <v>1624.3930</v>
+        <v>1624.1938</v>
       </c>
       <c t="n" r="F242">
-        <v>-0.2761</v>
+        <v>-0.2864</v>
       </c>
     </row>
     <row r="243">
@@ -6553,13 +6553,13 @@
         </is>
       </c>
       <c t="n" r="C246">
-        <v>-5.5392</v>
+        <v>-6.1952</v>
       </c>
       <c t="n" r="D246">
-        <v>-15.4981</v>
+        <v>-15.2066</v>
       </c>
       <c t="n" r="F246">
-        <v>-18.0022</v>
+        <v>-18.4342</v>
       </c>
     </row>
     <row r="247">
@@ -6574,16 +6574,16 @@
         </is>
       </c>
       <c t="n" r="C247">
-        <v>-5.8580</v>
+        <v>-6.4558</v>
       </c>
       <c t="n" r="D247">
-        <v>-15.9446</v>
+        <v>-15.7689</v>
       </c>
       <c t="n" r="E247">
-        <v>-25.4906</v>
+        <v>-25.9971</v>
       </c>
       <c t="n" r="F247">
-        <v>-18.1569</v>
+        <v>-18.5495</v>
       </c>
     </row>
     <row r="248">
@@ -6682,16 +6682,16 @@
         </is>
       </c>
       <c t="n" r="C255">
-        <v>-86.1162</v>
+        <v>-86.1599</v>
       </c>
       <c t="n" r="D255">
-        <v>-88.6096</v>
+        <v>-88.6371</v>
       </c>
       <c t="n" r="E255">
-        <v>-75.2665</v>
+        <v>-75.3482</v>
       </c>
       <c t="n" r="F255">
-        <v>-88.6324</v>
+        <v>-88.6715</v>
       </c>
     </row>
     <row r="256">
@@ -6706,16 +6706,16 @@
         </is>
       </c>
       <c t="n" r="C256">
-        <v>-1.4580</v>
+        <v>-1.5073</v>
       </c>
       <c t="n" r="D256">
-        <v>-13.3583</v>
+        <v>-13.2923</v>
       </c>
       <c t="n" r="E256">
-        <v>607.1658</v>
+        <v>606.5649</v>
       </c>
       <c t="n" r="F256">
-        <v>-13.5837</v>
+        <v>-13.6693</v>
       </c>
     </row>
     <row r="257">
@@ -6730,16 +6730,16 @@
         </is>
       </c>
       <c t="n" r="C257">
-        <v>-5.8324</v>
+        <v>-5.8418</v>
       </c>
       <c t="n" r="D257">
-        <v>-6.4703</v>
+        <v>-6.3996</v>
       </c>
       <c t="n" r="E257">
-        <v>-9.3270</v>
+        <v>-9.2041</v>
       </c>
       <c t="n" r="F257">
-        <v>-4.6160</v>
+        <v>-4.6312</v>
       </c>
     </row>
     <row r="258">
@@ -6766,7 +6766,10 @@
         </is>
       </c>
       <c t="n" r="C259">
-        <v>3.5006</v>
+        <v>3.1854</v>
+      </c>
+      <c t="n" r="D259">
+        <v>9.1041</v>
       </c>
     </row>
     <row r="260">
@@ -6781,7 +6784,7 @@
         </is>
       </c>
       <c t="n" r="C260">
-        <v>-0.0828</v>
+        <v>-0.0871</v>
       </c>
     </row>
     <row r="261">
@@ -6820,7 +6823,10 @@
         </is>
       </c>
       <c t="n" r="C263">
-        <v>8.9201</v>
+        <v>8.7114</v>
+      </c>
+      <c t="n" r="D263">
+        <v>79.8939</v>
       </c>
     </row>
     <row r="264">
@@ -6847,13 +6853,13 @@
         </is>
       </c>
       <c t="n" r="C265">
-        <v>1.2167</v>
+        <v>0.8523</v>
       </c>
       <c t="n" r="D265">
-        <v>5.5225</v>
+        <v>5.4120</v>
       </c>
       <c t="n" r="F265">
-        <v>7.2741</v>
+        <v>7.2784</v>
       </c>
     </row>
     <row r="266">
@@ -6868,13 +6874,13 @@
         </is>
       </c>
       <c t="n" r="C266">
-        <v>1.1558</v>
+        <v>0.7857</v>
       </c>
       <c t="n" r="D266">
-        <v>5.4366</v>
+        <v>5.3200</v>
       </c>
       <c t="n" r="F266">
-        <v>7.1875</v>
+        <v>7.1856</v>
       </c>
     </row>
     <row r="267">
@@ -6901,16 +6907,16 @@
         </is>
       </c>
       <c t="n" r="C268">
-        <v>-29.3926</v>
+        <v>-29.4079</v>
       </c>
       <c t="n" r="D268">
-        <v>-28.1523</v>
+        <v>-28.2363</v>
       </c>
       <c t="n" r="E268">
-        <v>-23.9968</v>
+        <v>-24.1509</v>
       </c>
       <c t="n" r="F268">
-        <v>-27.2060</v>
+        <v>-27.2130</v>
       </c>
     </row>
     <row r="269">
@@ -6937,16 +6943,16 @@
         </is>
       </c>
       <c t="n" r="C270">
-        <v>-0.4567</v>
+        <v>-0.4639</v>
       </c>
       <c t="n" r="D270">
-        <v>-1.4565</v>
+        <v>-1.4486</v>
       </c>
       <c t="n" r="E270">
-        <v>-32.2452</v>
+        <v>-31.9909</v>
       </c>
       <c t="n" r="F270">
-        <v>95.6683</v>
+        <v>95.6291</v>
       </c>
     </row>
     <row r="271">
@@ -6961,7 +6967,7 @@
         </is>
       </c>
       <c t="n" r="C271">
-        <v>34.3066</v>
+        <v>34.5722</v>
       </c>
     </row>
     <row r="272">
@@ -6976,13 +6982,13 @@
         </is>
       </c>
       <c t="n" r="C272">
-        <v>-0.3409</v>
+        <v>-0.3452</v>
       </c>
       <c t="n" r="D272">
-        <v>-0.8471</v>
+        <v>-0.8107</v>
       </c>
       <c t="n" r="F272">
-        <v>-2.3516</v>
+        <v>-2.3702</v>
       </c>
     </row>
     <row r="273">
@@ -6997,16 +7003,16 @@
         </is>
       </c>
       <c t="n" r="C273">
-        <v>-77.8428</v>
+        <v>-78.5346</v>
       </c>
       <c t="n" r="D273">
-        <v>-88.0677</v>
+        <v>-88.1915</v>
       </c>
       <c t="n" r="E273">
-        <v>-46.4956</v>
+        <v>-46.6002</v>
       </c>
       <c t="n" r="F273">
-        <v>102.0266</v>
+        <v>97.1457</v>
       </c>
     </row>
     <row r="274">
@@ -7045,13 +7051,13 @@
         </is>
       </c>
       <c t="n" r="C276">
-        <v>-0.0523</v>
+        <v>-0.0693</v>
       </c>
       <c t="n" r="D276">
-        <v>-10.9519</v>
+        <v>-11.0702</v>
       </c>
       <c t="n" r="F276">
-        <v>-9.7166</v>
+        <v>-9.7223</v>
       </c>
     </row>
     <row r="277">
@@ -7078,16 +7084,16 @@
         </is>
       </c>
       <c t="n" r="C278">
-        <v>3.3944</v>
+        <v>3.0694</v>
       </c>
       <c t="n" r="D278">
-        <v>-58.4455</v>
+        <v>-57.4003</v>
       </c>
       <c t="n" r="E278">
-        <v>-98.8474</v>
+        <v>-98.7925</v>
       </c>
       <c t="n" r="F278">
-        <v>-98.1588</v>
+        <v>-98.1572</v>
       </c>
     </row>
     <row r="279">
@@ -7117,10 +7123,10 @@
         <v>-0.2988</v>
       </c>
       <c t="n" r="D280">
-        <v>0.8311</v>
+        <v>0.0000</v>
       </c>
       <c t="n" r="E280">
-        <v>-95.5212</v>
+        <v>-94.6892</v>
       </c>
       <c t="n" r="F280">
         <v>0.8311</v>
@@ -7162,16 +7168,16 @@
         </is>
       </c>
       <c t="n" r="C283">
-        <v>-6.3295</v>
+        <v>-6.3940</v>
       </c>
       <c t="n" r="D283">
-        <v>-22.6065</v>
+        <v>-22.5521</v>
       </c>
       <c t="n" r="E283">
-        <v>4994.5360</v>
+        <v>5070.1877</v>
       </c>
       <c t="n" r="F283">
-        <v>11353.0123</v>
+        <v>11348.4810</v>
       </c>
     </row>
     <row r="284">
@@ -7186,13 +7192,16 @@
         </is>
       </c>
       <c t="n" r="C284">
-        <v>0.0028</v>
+        <v>-0.0441</v>
       </c>
       <c t="n" r="D284">
-        <v>-0.0446</v>
+        <v>-0.0332</v>
+      </c>
+      <c t="n" r="E284">
+        <v>-8.3959</v>
       </c>
       <c t="n" r="F284">
-        <v>-0.0028</v>
+        <v>-0.0060</v>
       </c>
     </row>
     <row r="285">
@@ -7243,7 +7252,10 @@
         </is>
       </c>
       <c t="n" r="C288">
-        <v>-29.6960</v>
+        <v>-30.7013</v>
+      </c>
+      <c t="n" r="D288">
+        <v>-81.1059</v>
       </c>
     </row>
     <row r="289">
@@ -7270,16 +7282,16 @@
         </is>
       </c>
       <c t="n" r="C290">
-        <v>0.4931</v>
+        <v>0.3022</v>
       </c>
       <c t="n" r="D290">
-        <v>2.5184</v>
+        <v>2.4680</v>
       </c>
       <c t="n" r="E290">
-        <v>10.1654</v>
+        <v>10.1014</v>
       </c>
       <c t="n" r="F290">
-        <v>3.1333</v>
+        <v>3.1233</v>
       </c>
     </row>
     <row r="291">
@@ -7306,16 +7318,16 @@
         </is>
       </c>
       <c t="n" r="C292">
-        <v>-26.5940</v>
+        <v>-26.9371</v>
       </c>
       <c t="n" r="D292">
-        <v>-51.8404</v>
+        <v>-51.9687</v>
       </c>
       <c t="n" r="E292">
-        <v>-57.3705</v>
+        <v>-57.4127</v>
       </c>
       <c t="n" r="F292">
-        <v>-56.8468</v>
+        <v>-56.8789</v>
       </c>
     </row>
     <row r="293">
@@ -7414,16 +7426,16 @@
         </is>
       </c>
       <c t="n" r="C298">
-        <v>3.8013</v>
+        <v>3.4255</v>
       </c>
       <c t="n" r="D298">
-        <v>10.2550</v>
+        <v>10.1316</v>
       </c>
       <c t="n" r="E298">
-        <v>21.3977</v>
+        <v>21.3258</v>
       </c>
       <c t="n" r="F298">
-        <v>12.9886</v>
+        <v>13.1214</v>
       </c>
     </row>
     <row r="299">
@@ -7438,13 +7450,13 @@
         </is>
       </c>
       <c t="n" r="C299">
-        <v>3.2786</v>
+        <v>2.9010</v>
       </c>
       <c t="n" r="D299">
-        <v>8.9952</v>
+        <v>8.8631</v>
       </c>
       <c t="n" r="F299">
-        <v>11.7289</v>
+        <v>11.8572</v>
       </c>
     </row>
     <row r="300">
@@ -7471,13 +7483,13 @@
         </is>
       </c>
       <c t="n" r="C301">
-        <v>4.3036</v>
+        <v>3.8943</v>
       </c>
       <c t="n" r="D301">
-        <v>11.8362</v>
+        <v>11.6894</v>
       </c>
       <c t="n" r="F301">
-        <v>14.8744</v>
+        <v>15.0143</v>
       </c>
     </row>
     <row r="302">
@@ -7492,7 +7504,7 @@
         </is>
       </c>
       <c t="n" r="C302">
-        <v>-73.6171</v>
+        <v>-73.3594</v>
       </c>
     </row>
     <row r="303">
@@ -7507,10 +7519,10 @@
         </is>
       </c>
       <c t="n" r="C303">
-        <v>-0.0075</v>
+        <v>-0.0916</v>
       </c>
       <c t="n" r="D303">
-        <v>-0.8878</v>
+        <v>-0.0639</v>
       </c>
     </row>
     <row r="304">
@@ -7525,16 +7537,16 @@
         </is>
       </c>
       <c t="n" r="C304">
-        <v>1.1666</v>
+        <v>0.8509</v>
       </c>
       <c t="n" r="D304">
-        <v>6.1159</v>
+        <v>5.6164</v>
       </c>
       <c t="n" r="E304">
-        <v>14.4764</v>
+        <v>14.0599</v>
       </c>
       <c t="n" r="F304">
-        <v>7.8109</v>
+        <v>7.6084</v>
       </c>
     </row>
     <row r="305">
@@ -7573,16 +7585,16 @@
         </is>
       </c>
       <c t="n" r="C307">
-        <v>2.0817</v>
+        <v>1.7320</v>
       </c>
       <c t="n" r="D307">
-        <v>3.4498</v>
+        <v>3.2953</v>
       </c>
       <c t="n" r="E307">
-        <v>11.7636</v>
+        <v>11.5458</v>
       </c>
       <c t="n" r="F307">
-        <v>5.4803</v>
+        <v>5.4620</v>
       </c>
     </row>
     <row r="308">
@@ -7621,16 +7633,16 @@
         </is>
       </c>
       <c t="n" r="C310">
-        <v>-0.0743</v>
+        <v>-0.0855</v>
       </c>
       <c t="n" r="D310">
-        <v>-0.2195</v>
+        <v>-0.2142</v>
       </c>
       <c t="n" r="E310">
-        <v>0.5999</v>
+        <v>0.5967</v>
       </c>
       <c t="n" r="F310">
-        <v>-0.2541</v>
+        <v>-0.2597</v>
       </c>
     </row>
     <row r="311">
@@ -7669,16 +7681,16 @@
         </is>
       </c>
       <c t="n" r="C313">
-        <v>-0.0528</v>
+        <v>-0.0590</v>
       </c>
       <c t="n" r="D313">
-        <v>-0.1483</v>
+        <v>-0.1450</v>
       </c>
       <c t="n" r="E313">
-        <v>1.9699</v>
+        <v>1.7271</v>
       </c>
       <c t="n" r="F313">
-        <v>-0.1744</v>
+        <v>-0.1777</v>
       </c>
     </row>
     <row r="314">
@@ -7705,16 +7717,16 @@
         </is>
       </c>
       <c t="n" r="C315">
-        <v>-0.1568</v>
+        <v>-0.1593</v>
       </c>
       <c t="n" r="D315">
-        <v>-0.3509</v>
+        <v>-0.3463</v>
       </c>
       <c t="n" r="E315">
-        <v>3.0258</v>
+        <v>3.0250</v>
       </c>
       <c t="n" r="F315">
-        <v>-0.4012</v>
+        <v>-0.4061</v>
       </c>
     </row>
     <row r="316">
@@ -7729,7 +7741,7 @@
         </is>
       </c>
       <c t="n" r="C316">
-        <v>-0.1330</v>
+        <v>-0.1340</v>
       </c>
     </row>
     <row r="317">
@@ -7786,13 +7798,13 @@
         </is>
       </c>
       <c t="n" r="C320">
-        <v>-0.1080</v>
+        <v>-0.1339</v>
       </c>
       <c t="n" r="D320">
-        <v>-0.1099</v>
+        <v>-0.1102</v>
       </c>
       <c t="n" r="F320">
-        <v>-0.1173</v>
+        <v>-0.1213</v>
       </c>
     </row>
     <row r="321">
@@ -7831,7 +7843,7 @@
         </is>
       </c>
       <c t="n" r="C323">
-        <v>2.9305</v>
+        <v>3.0253</v>
       </c>
     </row>
     <row r="324">
